--- a/api/1/clv3/xlsx/en/HumanitarianPlan.xlsx
+++ b/api/1/clv3/xlsx/en/HumanitarianPlan.xlsx
@@ -28,15 +28,15 @@
     <t>codeforiati:plan-type</t>
   </si>
   <si>
+    <t>codeforiati:plan-end-date</t>
+  </si>
+  <si>
+    <t>codeforiati:plan-year</t>
+  </si>
+  <si>
     <t>codeforiati:plan-start-date</t>
   </si>
   <si>
-    <t>codeforiati:plan-year</t>
-  </si>
-  <si>
-    <t>codeforiati:plan-end-date</t>
-  </si>
-  <si>
     <t>HAFG25</t>
   </si>
   <si>
@@ -49,15 +49,15 @@
     <t>Humanitarian needs and response plan</t>
   </si>
   <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
+    <t>2025</t>
+  </si>
+  <si>
     <t>2025-01-01</t>
   </si>
   <si>
-    <t>2025</t>
-  </si>
-  <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
     <t>RIRNPAK25</t>
   </si>
   <si>
@@ -355,15 +355,15 @@
     <t>Afghanistan Humanitarian Needs and Response Plan 2024</t>
   </si>
   <si>
+    <t>2024-12-31</t>
+  </si>
+  <si>
+    <t>2024</t>
+  </si>
+  <si>
     <t>2024-01-01</t>
   </si>
   <si>
-    <t>2024</t>
-  </si>
-  <si>
-    <t>2024-12-31</t>
-  </si>
-  <si>
     <t>RAFG_RRP24</t>
   </si>
   <si>
@@ -712,15 +712,15 @@
     <t>Afghanistan Humanitarian Response Plan 2023</t>
   </si>
   <si>
+    <t>2023-12-31</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
     <t>2023-01-01</t>
   </si>
   <si>
-    <t>2023</t>
-  </si>
-  <si>
-    <t>2023-12-31</t>
-  </si>
-  <si>
     <t>RAFG23</t>
   </si>
   <si>
@@ -841,24 +841,24 @@
     <t>Mongolia Dzud Early Action and Response Plan 2023</t>
   </si>
   <si>
+    <t>2023-05-31</t>
+  </si>
+  <si>
     <t>2022-12-01</t>
   </si>
   <si>
-    <t>2023-05-31</t>
-  </si>
-  <si>
     <t>OMOZ23</t>
   </si>
   <si>
     <t>Mozambique Cyclone Freddy, Floods and Cholera Response Plan 2023</t>
   </si>
   <si>
+    <t>2023-09-30</t>
+  </si>
+  <si>
     <t>2023-03-01</t>
   </si>
   <si>
-    <t>2023-09-30</t>
-  </si>
-  <si>
     <t>HMOZ23</t>
   </si>
   <si>
@@ -946,12 +946,12 @@
     <t>Sudan Emergency: Regional Refugee Response Plan 2023</t>
   </si>
   <si>
+    <t>2023-10-31</t>
+  </si>
+  <si>
     <t>2023-05-01</t>
   </si>
   <si>
-    <t>2023-10-31</t>
-  </si>
-  <si>
     <t>HSDN23</t>
   </si>
   <si>
@@ -1030,15 +1030,15 @@
     <t>Afghanistan Humanitarian Response Plan 2022</t>
   </si>
   <si>
+    <t>2022-12-31</t>
+  </si>
+  <si>
+    <t>2022</t>
+  </si>
+  <si>
     <t>2022-01-01</t>
   </si>
   <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>2022-12-31</t>
-  </si>
-  <si>
     <t>RAFG22</t>
   </si>
   <si>
@@ -1081,12 +1081,12 @@
     <t>Cuba Hurricane Ian Response - Plan of Action 2022</t>
   </si>
   <si>
+    <t>2023-03-31</t>
+  </si>
+  <si>
     <t>2022-10-20</t>
   </si>
   <si>
-    <t>2023-03-31</t>
-  </si>
-  <si>
     <t>RDRCRRP22</t>
   </si>
   <si>
@@ -1117,12 +1117,12 @@
     <t>Haïti Choléra+ Appel Éclair 2022</t>
   </si>
   <si>
+    <t>2023-04-15</t>
+  </si>
+  <si>
     <t>2022-10-16</t>
   </si>
   <si>
-    <t>2023-04-15</t>
-  </si>
-  <si>
     <t>FHTI22</t>
   </si>
   <si>
@@ -1180,12 +1180,12 @@
     <t>Malawi Flash Appeal 2022</t>
   </si>
   <si>
+    <t>2022-05-31</t>
+  </si>
+  <si>
     <t>2022-02-26</t>
   </si>
   <si>
-    <t>2022-05-31</t>
-  </si>
-  <si>
     <t>HMLI22</t>
   </si>
   <si>
@@ -1198,12 +1198,12 @@
     <t>Mozambique Gombe Emergency Response Plan 2022</t>
   </si>
   <si>
+    <t>2022-09-30</t>
+  </si>
+  <si>
     <t>2022-04-01</t>
   </si>
   <si>
-    <t>2022-09-30</t>
-  </si>
-  <si>
     <t>HMOZ22</t>
   </si>
   <si>
@@ -1255,12 +1255,12 @@
     <t>Philippines Super Typhoon Rai (Odette) Humanitarian Needs and Priorities 2022</t>
   </si>
   <si>
+    <t>2022-06-30</t>
+  </si>
+  <si>
     <t>2021-12-24</t>
   </si>
   <si>
-    <t>2022-06-30</t>
-  </si>
-  <si>
     <t>RREG22</t>
   </si>
   <si>
@@ -1378,15 +1378,15 @@
     <t>Afghanistan Flash Appeal 2021</t>
   </si>
   <si>
+    <t>2021-12-31</t>
+  </si>
+  <si>
+    <t>2021</t>
+  </si>
+  <si>
     <t>2021-09-01</t>
   </si>
   <si>
-    <t>2021</t>
-  </si>
-  <si>
-    <t>2021-12-31</t>
-  </si>
-  <si>
     <t>HAFG21</t>
   </si>
   <si>
@@ -1477,12 +1477,12 @@
     <t>Escalation of Hostilities in the OPT Flash Appeal 2021</t>
   </si>
   <si>
+    <t>2021-08-27</t>
+  </si>
+  <si>
     <t>2021-05-27</t>
   </si>
   <si>
-    <t>2021-08-27</t>
-  </si>
-  <si>
     <t>HETH21</t>
   </si>
   <si>
@@ -1507,12 +1507,12 @@
     <t>Haiti Earthquake Flash Appeal 2021</t>
   </si>
   <si>
+    <t>2022-02-15</t>
+  </si>
+  <si>
     <t>2021-08-16</t>
   </si>
   <si>
-    <t>2022-02-15</t>
-  </si>
-  <si>
     <t>HHTI21</t>
   </si>
   <si>
@@ -1525,12 +1525,12 @@
     <t>Honduras Tropical Storm Eta Flash Appeal 2021</t>
   </si>
   <si>
+    <t>2021-06-30</t>
+  </si>
+  <si>
     <t>2020-11-15</t>
   </si>
   <si>
-    <t>2021-06-30</t>
-  </si>
-  <si>
     <t>HHND21</t>
   </si>
   <si>
@@ -1564,12 +1564,12 @@
     <t>Lebanon Emergency Response Plan 2021</t>
   </si>
   <si>
+    <t>2022-07-31</t>
+  </si>
+  <si>
     <t>2021-08-03</t>
   </si>
   <si>
-    <t>2022-07-31</t>
-  </si>
-  <si>
     <t>HLBY21</t>
   </si>
   <si>
@@ -1735,15 +1735,15 @@
     <t>Afghanistan Humanitarian Response Plan 2020</t>
   </si>
   <si>
+    <t>2020-12-31</t>
+  </si>
+  <si>
+    <t>2020</t>
+  </si>
+  <si>
     <t>2020-01-01</t>
   </si>
   <si>
-    <t>2020</t>
-  </si>
-  <si>
-    <t>2020-12-31</t>
-  </si>
-  <si>
     <t>OBGD20</t>
   </si>
   <si>
@@ -1858,12 +1858,12 @@
     <t>Djibouti Flash Appeal 2020</t>
   </si>
   <si>
+    <t>2020-03-31</t>
+  </si>
+  <si>
     <t>2019-12-17</t>
   </si>
   <si>
-    <t>2020-03-31</t>
-  </si>
-  <si>
     <t>ODJI20</t>
   </si>
   <si>
@@ -1957,12 +1957,12 @@
     <t>Lebanon Flash Appeal 2020</t>
   </si>
   <si>
+    <t>2020-11-13</t>
+  </si>
+  <si>
     <t>2020-08-05</t>
   </si>
   <si>
-    <t>2020-11-13</t>
-  </si>
-  <si>
     <t>OLBN20</t>
   </si>
   <si>
@@ -1975,12 +1975,12 @@
     <t>Lesotho Flash Appeal 2019-2020</t>
   </si>
   <si>
+    <t>2020-04-30</t>
+  </si>
+  <si>
     <t>2019-11-01</t>
   </si>
   <si>
-    <t>2020-04-30</t>
-  </si>
-  <si>
     <t>OLBR20</t>
   </si>
   <si>
@@ -2170,15 +2170,15 @@
     <t>Afghanistan Humanitarian Response Plan 2019</t>
   </si>
   <si>
+    <t>2019-12-31</t>
+  </si>
+  <si>
+    <t>2019</t>
+  </si>
+  <si>
     <t>2019-01-01</t>
   </si>
   <si>
-    <t>2019</t>
-  </si>
-  <si>
-    <t>2019-12-31</t>
-  </si>
-  <si>
     <t>RBGD19</t>
   </si>
   <si>
@@ -2386,12 +2386,12 @@
     <t>Zimbabwe Flash Appeal 2019</t>
   </si>
   <si>
+    <t>2020-04-29</t>
+  </si>
+  <si>
     <t>2019-02-01</t>
   </si>
   <si>
-    <t>2020-04-29</t>
-  </si>
-  <si>
     <t>FZWE1820</t>
   </si>
   <si>
@@ -2407,15 +2407,15 @@
     <t>Afghanistan Humanitarian Response Plan 2018</t>
   </si>
   <si>
+    <t>2018-12-31</t>
+  </si>
+  <si>
+    <t>2018</t>
+  </si>
+  <si>
     <t>2018-01-01</t>
   </si>
   <si>
-    <t>2018</t>
-  </si>
-  <si>
-    <t>2018-12-31</t>
-  </si>
-  <si>
     <t>OBGD18</t>
   </si>
   <si>
@@ -2590,12 +2590,12 @@
     <t>Syrian Arab Republic Humanitarian Response Plan 2018</t>
   </si>
   <si>
+    <t>2018-12-30</t>
+  </si>
+  <si>
     <t>2018-11-30</t>
   </si>
   <si>
-    <t>2018-12-30</t>
-  </si>
-  <si>
     <t>RSYR18</t>
   </si>
   <si>
@@ -2632,15 +2632,15 @@
     <t>2017 Europe Situation - Regional Refugee and Migrant Response</t>
   </si>
   <si>
+    <t>2017-12-31</t>
+  </si>
+  <si>
+    <t>2017</t>
+  </si>
+  <si>
     <t>2017-01-01</t>
   </si>
   <si>
-    <t>2017</t>
-  </si>
-  <si>
-    <t>2017-12-31</t>
-  </si>
-  <si>
     <t>HAFG17</t>
   </si>
   <si>
@@ -2716,12 +2716,12 @@
     <t>Dominica Flash Appeal 2017</t>
   </si>
   <si>
+    <t>2017-12-29</t>
+  </si>
+  <si>
     <t>2017-09-28</t>
   </si>
   <si>
-    <t>2017-12-29</t>
-  </si>
-  <si>
     <t>OPRK17</t>
   </si>
   <si>
@@ -2761,12 +2761,12 @@
     <t>Kenya Flash Appeal 2017</t>
   </si>
   <si>
+    <t>2017-11-30</t>
+  </si>
+  <si>
     <t>2017-02-10</t>
   </si>
   <si>
-    <t>2017-11-30</t>
-  </si>
-  <si>
     <t>HLBY17</t>
   </si>
   <si>
@@ -2779,12 +2779,12 @@
     <t>Madagascar Flash Appeal 2017</t>
   </si>
   <si>
+    <t>2017-06-20</t>
+  </si>
+  <si>
     <t>2017-03-20</t>
   </si>
   <si>
-    <t>2017-06-20</t>
-  </si>
-  <si>
     <t>HMLI17</t>
   </si>
   <si>
@@ -2803,12 +2803,12 @@
     <t>Mozambique Cyclone Dineo Flash Appeal 2017</t>
   </si>
   <si>
+    <t>2017-05-31</t>
+  </si>
+  <si>
     <t>2017-02-28</t>
   </si>
   <si>
-    <t>2017-05-31</t>
-  </si>
-  <si>
     <t>HMMR17</t>
   </si>
   <si>
@@ -2845,12 +2845,12 @@
     <t>Peru Flash Appeal 2017</t>
   </si>
   <si>
+    <t>2017-10-31</t>
+  </si>
+  <si>
     <t>2017-04-01</t>
   </si>
   <si>
-    <t>2017-10-31</t>
-  </si>
-  <si>
     <t>HCOG17</t>
   </si>
   <si>
@@ -2920,15 +2920,15 @@
     <t>2016 Europe Situation -Regional Refugee and Migrant Response</t>
   </si>
   <si>
+    <t>2016-12-31</t>
+  </si>
+  <si>
+    <t>2016</t>
+  </si>
+  <si>
     <t>2016-01-01</t>
   </si>
   <si>
-    <t>2016</t>
-  </si>
-  <si>
-    <t>2016-12-31</t>
-  </si>
-  <si>
     <t>HAFG16</t>
   </si>
   <si>
@@ -3001,24 +3001,24 @@
     <t>Ecuador Earthquake Flash Appeal 2016</t>
   </si>
   <si>
+    <t>2016-10-31</t>
+  </si>
+  <si>
     <t>2016-04-16</t>
   </si>
   <si>
-    <t>2016-10-31</t>
-  </si>
-  <si>
     <t>FFJI16</t>
   </si>
   <si>
     <t>Fiji Tropical Cyclone Flash Appeal 2016</t>
   </si>
   <si>
+    <t>2016-05-30</t>
+  </si>
+  <si>
     <t>2016-02-20</t>
   </si>
   <si>
-    <t>2016-05-30</t>
-  </si>
-  <si>
     <t>HGMB16</t>
   </si>
   <si>
@@ -3094,12 +3094,12 @@
     <t>Mosul Flash Appeal 2016</t>
   </si>
   <si>
+    <t>2016-10-01</t>
+  </si>
+  <si>
     <t>2016-07-20</t>
   </si>
   <si>
-    <t>2016-10-01</t>
-  </si>
-  <si>
     <t>HMMR16</t>
   </si>
   <si>
@@ -3184,12 +3184,12 @@
     <t>Zimbabwe Humanitarian Response Plan 2016</t>
   </si>
   <si>
+    <t>2017-03-31</t>
+  </si>
+  <si>
     <t>2016-04-01</t>
   </si>
   <si>
-    <t>2017-03-31</t>
-  </si>
-  <si>
     <t>HAFG15</t>
   </si>
   <si>
@@ -3199,15 +3199,15 @@
     <t>Strategic response plan</t>
   </si>
   <si>
+    <t>2015-12-31</t>
+  </si>
+  <si>
+    <t>2015</t>
+  </si>
+  <si>
     <t>2015-01-01</t>
   </si>
   <si>
-    <t>2015</t>
-  </si>
-  <si>
-    <t>2015-12-31</t>
-  </si>
-  <si>
     <t>HBFA15</t>
   </si>
   <si>
@@ -3262,12 +3262,12 @@
     <t>Guatemala Plan de Respuesta Sequia 2015</t>
   </si>
   <si>
+    <t>2015-09-30</t>
+  </si>
+  <si>
     <t>2014-11-03</t>
   </si>
   <si>
-    <t>2015-09-30</t>
-  </si>
-  <si>
     <t>FHTI15</t>
   </si>
   <si>
@@ -3292,12 +3292,12 @@
     <t>Vanuatu Emergency Response Plan for Tropical Cyclone PAM 2015</t>
   </si>
   <si>
+    <t>2015-10-31</t>
+  </si>
+  <si>
     <t>2015-03-24</t>
   </si>
   <si>
-    <t>2015-10-31</t>
-  </si>
-  <si>
     <t>HIRQ15</t>
   </si>
   <si>
@@ -3310,12 +3310,12 @@
     <t>Libya Humanitarian Appeal 2014- 2015</t>
   </si>
   <si>
+    <t>2015-05-31</t>
+  </si>
+  <si>
     <t>2014-10-01</t>
   </si>
   <si>
-    <t>2015-05-31</t>
-  </si>
-  <si>
     <t>HMLI15</t>
   </si>
   <si>
@@ -3427,15 +3427,15 @@
     <t>Afghanistan Strategic Response Plan 2014</t>
   </si>
   <si>
+    <t>2014-12-31</t>
+  </si>
+  <si>
+    <t>2014</t>
+  </si>
+  <si>
     <t>2014-01-01</t>
   </si>
   <si>
-    <t>2014</t>
-  </si>
-  <si>
-    <t>2014-12-31</t>
-  </si>
-  <si>
     <t>HBFA1314</t>
   </si>
   <si>
@@ -3571,24 +3571,24 @@
     <t>Philippines Bohol Earthquake Flash Appeal 2014</t>
   </si>
   <si>
+    <t>2014-04-22</t>
+  </si>
+  <si>
     <t>2013-10-22</t>
   </si>
   <si>
-    <t>2014-04-22</t>
-  </si>
-  <si>
     <t>SPHL1314</t>
   </si>
   <si>
     <t>Philippines Typhoon Haiyan Strategic Response Plan 2014</t>
   </si>
   <si>
+    <t>2014-11-07</t>
+  </si>
+  <si>
     <t>2013-11-08</t>
   </si>
   <si>
-    <t>2014-11-07</t>
-  </si>
-  <si>
     <t>HPHL1314</t>
   </si>
   <si>
@@ -3604,12 +3604,12 @@
     <t>Philippines Zamboanga Crisis Flash Appeal 2014</t>
   </si>
   <si>
+    <t>2014-08-31</t>
+  </si>
+  <si>
     <t>2013-10-01</t>
   </si>
   <si>
-    <t>2014-08-31</t>
-  </si>
-  <si>
     <t>SCOD14</t>
   </si>
   <si>
@@ -3718,12 +3718,12 @@
     <t>Consolidated appeals process</t>
   </si>
   <si>
+    <t>2013-12-31</t>
+  </si>
+  <si>
     <t>2013</t>
   </si>
   <si>
-    <t>2013-12-31</t>
-  </si>
-  <si>
     <t>CBFA13</t>
   </si>
   <si>
@@ -3877,15 +3877,15 @@
     <t>2012+ Kenya Emergency Humanitarian Response Plan</t>
   </si>
   <si>
+    <t>2012-12-31</t>
+  </si>
+  <si>
+    <t>2012</t>
+  </si>
+  <si>
     <t>2012-01-01</t>
   </si>
   <si>
-    <t>2012</t>
-  </si>
-  <si>
-    <t>2012-12-31</t>
-  </si>
-  <si>
     <t>CAFG1112</t>
   </si>
   <si>
@@ -3955,12 +3955,12 @@
     <t>Lesotho Food Insecurity (September 2012 - March 2013)</t>
   </si>
   <si>
+    <t>2013-03-25</t>
+  </si>
+  <si>
     <t>2012-09-18</t>
   </si>
   <si>
-    <t>2013-03-25</t>
-  </si>
-  <si>
     <t>CLBR12</t>
   </si>
   <si>
@@ -4033,12 +4033,12 @@
     <t>Syria Humanitarian Assistance Response Plan (SHARP) 2012</t>
   </si>
   <si>
+    <t>2012-12-05</t>
+  </si>
+  <si>
     <t>2012-06-05</t>
   </si>
   <si>
-    <t>2012-12-05</t>
-  </si>
-  <si>
     <t>CYEM12</t>
   </si>
   <si>
@@ -4063,12 +4063,12 @@
     <t>2011+ Kenya Emergency Humanitarian Response Plan</t>
   </si>
   <si>
+    <t>2011</t>
+  </si>
+  <si>
     <t>2011-01-01</t>
   </si>
   <si>
-    <t>2011</t>
-  </si>
-  <si>
     <t>CAFG11</t>
   </si>
   <si>
@@ -4111,12 +4111,12 @@
     <t>El Salvador Flash Appeal (October 2011 - April 2012)</t>
   </si>
   <si>
+    <t>2012-04-25</t>
+  </si>
+  <si>
     <t>2011-10-25</t>
   </si>
   <si>
-    <t>2012-04-25</t>
-  </si>
-  <si>
     <t>CHTI1011</t>
   </si>
   <si>
@@ -4147,24 +4147,24 @@
     <t>Namibia Flash Appeal (April - October 2011)</t>
   </si>
   <si>
+    <t>2011-10-11</t>
+  </si>
+  <si>
     <t>2011-04-11</t>
   </si>
   <si>
-    <t>2011-10-11</t>
-  </si>
-  <si>
     <t>FNIC1112</t>
   </si>
   <si>
     <t>Nicaragua Flash Appeal (October 2011 - April 2012)</t>
   </si>
   <si>
+    <t>2012-04-26</t>
+  </si>
+  <si>
     <t>2011-10-27</t>
   </si>
   <si>
-    <t>2012-04-26</t>
-  </si>
-  <si>
     <t>CNER11</t>
   </si>
   <si>
@@ -4177,12 +4177,12 @@
     <t>Pakistan Rapid Response Plan Floods 2011 (September - March 2012)</t>
   </si>
   <si>
+    <t>2012-06-30</t>
+  </si>
+  <si>
     <t>2011-09-15</t>
   </si>
   <si>
-    <t>2012-06-30</t>
-  </si>
-  <si>
     <t>FXLBYREG11</t>
   </si>
   <si>
@@ -4258,27 +4258,27 @@
     <t>Afghanistan Humanitarian Action Plan 2010</t>
   </si>
   <si>
+    <t>2010-12-31</t>
+  </si>
+  <si>
+    <t>2010</t>
+  </si>
+  <si>
     <t>2010-01-01</t>
   </si>
   <si>
-    <t>2010</t>
-  </si>
-  <si>
-    <t>2010-12-31</t>
-  </si>
-  <si>
     <t>OBFA1011</t>
   </si>
   <si>
     <t>Burkina Faso Emergency Humanitarian Action Plan 2010</t>
   </si>
   <si>
+    <t>2011-01-31</t>
+  </si>
+  <si>
     <t>2010-08-01</t>
   </si>
   <si>
-    <t>2011-01-31</t>
-  </si>
-  <si>
     <t>CCAF10</t>
   </si>
   <si>
@@ -4303,36 +4303,36 @@
     <t>El Salvador Flash Appeal (Revised) (November 2009 - May 2010)</t>
   </si>
   <si>
+    <t>2010-05-31</t>
+  </si>
+  <si>
     <t>2009-11-01</t>
   </si>
   <si>
-    <t>2010-05-31</t>
-  </si>
-  <si>
     <t>FGTM10</t>
   </si>
   <si>
     <t>Guatemala Flash Appeal (Revised) (June - December 2010)</t>
   </si>
   <si>
+    <t>2010-12-09</t>
+  </si>
+  <si>
     <t>2010-06-10</t>
   </si>
   <si>
-    <t>2010-12-09</t>
-  </si>
-  <si>
     <t>CGTM10</t>
   </si>
   <si>
     <t>Guatemala Food Insecurity and Acute Malnutrition Appeal 2010</t>
   </si>
   <si>
+    <t>2010-08-11</t>
+  </si>
+  <si>
     <t>2010-02-12</t>
   </si>
   <si>
-    <t>2010-08-11</t>
-  </si>
-  <si>
     <t>FHTI10</t>
   </si>
   <si>
@@ -4360,12 +4360,12 @@
     <t>Kyrgyzstan Flash Appeal (Revised) (June 2010 - June 2011)</t>
   </si>
   <si>
+    <t>2011-06-30</t>
+  </si>
+  <si>
     <t>2010-06-01</t>
   </si>
   <si>
-    <t>2011-06-30</t>
-  </si>
-  <si>
     <t>CMNG1011</t>
   </si>
   <si>
@@ -4468,27 +4468,27 @@
     <t>Afghanistan Humanitarian Action Plan 2009</t>
   </si>
   <si>
+    <t>2009-12-31</t>
+  </si>
+  <si>
+    <t>2009</t>
+  </si>
+  <si>
     <t>2009-01-01</t>
   </si>
   <si>
-    <t>2009</t>
-  </si>
-  <si>
-    <t>2009-12-31</t>
-  </si>
-  <si>
     <t>FBFA0910</t>
   </si>
   <si>
     <t>Burkina Faso Flash Appeal (September 2009 - February 2010)</t>
   </si>
   <si>
+    <t>2010-03-09</t>
+  </si>
+  <si>
     <t>2009-09-10</t>
   </si>
   <si>
-    <t>2010-03-09</t>
-  </si>
-  <si>
     <t>CCAF09</t>
   </si>
   <si>
@@ -4552,24 +4552,24 @@
     <t>Madagascar Flash Appeal (Revised) (April - October 2009)</t>
   </si>
   <si>
+    <t>2009-10-31</t>
+  </si>
+  <si>
     <t>2009-04-01</t>
   </si>
   <si>
-    <t>2009-10-31</t>
-  </si>
-  <si>
     <t>FNAM09</t>
   </si>
   <si>
     <t>Namibia Flash Appeal (Revised) (March - November 2009)</t>
   </si>
   <si>
+    <t>2009-09-30</t>
+  </si>
+  <si>
     <t>2009-03-20</t>
   </si>
   <si>
-    <t>2009-09-30</t>
-  </si>
-  <si>
     <t>ONPL09</t>
   </si>
   <si>
@@ -4591,12 +4591,12 @@
     <t>Philippines Flash Appeal (Revised) (October 2009 - March 2010)</t>
   </si>
   <si>
+    <t>2010-03-31</t>
+  </si>
+  <si>
     <t>2009-10-03</t>
   </si>
   <si>
-    <t>2010-03-31</t>
-  </si>
-  <si>
     <t>CSOM09</t>
   </si>
   <si>
@@ -4621,12 +4621,12 @@
     <t>Syria Drought Response Plan (Revised) (July 2009 - June 2010)</t>
   </si>
   <si>
+    <t>2010-06-14</t>
+  </si>
+  <si>
     <t>2009-07-15</t>
   </si>
   <si>
-    <t>2010-06-14</t>
-  </si>
-  <si>
     <t>OTJK09</t>
   </si>
   <si>
@@ -4684,27 +4684,27 @@
     <t>Afghanistan Joint Appeal 2008: Humanitarian Consequences of Rise in Food Prices (February - June 2008)</t>
   </si>
   <si>
+    <t>2008-06-30</t>
+  </si>
+  <si>
+    <t>2008</t>
+  </si>
+  <si>
     <t>2008-02-01</t>
   </si>
   <si>
-    <t>2008</t>
-  </si>
-  <si>
-    <t>2008-06-30</t>
-  </si>
-  <si>
     <t>OAFG0809</t>
   </si>
   <si>
     <t>Afghanistan Joint Emergency Appeal 2008: High Food Price and Drought Crisis (July 2008 - June 2009)</t>
   </si>
   <si>
+    <t>2009-06-30</t>
+  </si>
+  <si>
     <t>2008-07-01</t>
   </si>
   <si>
-    <t>2009-06-30</t>
-  </si>
-  <si>
     <t>FBOL08</t>
   </si>
   <si>
@@ -4720,12 +4720,12 @@
     <t>Central African Republic 2008</t>
   </si>
   <si>
+    <t>2008-12-31</t>
+  </si>
+  <si>
     <t>2008-01-01</t>
   </si>
   <si>
-    <t>2008-12-31</t>
-  </si>
-  <si>
     <t>CTCD08</t>
   </si>
   <si>
@@ -4756,24 +4756,24 @@
     <t>Djibouti Joint Appeal 2008: Response Plan for Drought, Food and Nutrition Crisis</t>
   </si>
   <si>
+    <t>2009-02-28</t>
+  </si>
+  <si>
     <t>2008-08-01</t>
   </si>
   <si>
-    <t>2009-02-28</t>
-  </si>
-  <si>
     <t>FGEO0809</t>
   </si>
   <si>
     <t>Georgia Crisis Flash Appeal (Revised) 2008</t>
   </si>
   <si>
+    <t>2009-02-09</t>
+  </si>
+  <si>
     <t>2008-08-09</t>
   </si>
   <si>
-    <t>2009-02-09</t>
-  </si>
-  <si>
     <t>FHTI0809</t>
   </si>
   <si>
@@ -4789,12 +4789,12 @@
     <t>Honduras Flash Appeal (Updated) (November - April) 2008</t>
   </si>
   <si>
+    <t>2009-04-30</t>
+  </si>
+  <si>
     <t>2008-11-01</t>
   </si>
   <si>
-    <t>2009-04-30</t>
-  </si>
-  <si>
     <t>CIRQ08</t>
   </si>
   <si>
@@ -4813,12 +4813,12 @@
     <t>Kyrgyzstan Flash Appeal (Revised) 2008</t>
   </si>
   <si>
+    <t>2009-05-31</t>
+  </si>
+  <si>
     <t>2008-12-01</t>
   </si>
   <si>
-    <t>2009-05-31</t>
-  </si>
-  <si>
     <t>OLAO0809</t>
   </si>
   <si>
@@ -4849,12 +4849,12 @@
     <t>Myanmar Flash Appeal (Revised) 2008</t>
   </si>
   <si>
+    <t>2008-11-30</t>
+  </si>
+  <si>
     <t>2008-05-01</t>
   </si>
   <si>
-    <t>2008-11-30</t>
-  </si>
-  <si>
     <t>ONPL08</t>
   </si>
   <si>
@@ -4951,39 +4951,39 @@
     <t>Bolivia Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2007-08-21</t>
+  </si>
+  <si>
+    <t>2007</t>
+  </si>
+  <si>
     <t>2007-02-22</t>
   </si>
   <si>
-    <t>2007</t>
-  </si>
-  <si>
-    <t>2007-08-21</t>
-  </si>
-  <si>
     <t>FBFA0708</t>
   </si>
   <si>
     <t>Burkina Faso Floods Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2008-01-31</t>
+  </si>
+  <si>
     <t>2007-11-01</t>
   </si>
   <si>
-    <t>2008-01-31</t>
-  </si>
-  <si>
     <t>CBDI07</t>
   </si>
   <si>
     <t>Burundi 2007</t>
   </si>
   <si>
+    <t>2007-12-31</t>
+  </si>
+  <si>
     <t>2007-01-01</t>
   </si>
   <si>
-    <t>2007-12-31</t>
-  </si>
-  <si>
     <t>CCAF07</t>
   </si>
   <si>
@@ -5023,12 +5023,12 @@
     <t>Ghana Floods Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2008-03-31</t>
+  </si>
+  <si>
     <t>2007-09-01</t>
   </si>
   <si>
-    <t>2008-03-31</t>
-  </si>
-  <si>
     <t>CXGLR07</t>
   </si>
   <si>
@@ -5050,36 +5050,36 @@
     <t>Korea DPR Flash Appeal: Floods Emergency 2007</t>
   </si>
   <si>
+    <t>2007-11-30</t>
+  </si>
+  <si>
     <t>2007-08-28</t>
   </si>
   <si>
-    <t>2007-11-30</t>
-  </si>
-  <si>
     <t>OLBN07</t>
   </si>
   <si>
     <t>Lebanon Crisis Appeal 2007</t>
   </si>
   <si>
+    <t>2007-09-03</t>
+  </si>
+  <si>
     <t>2007-06-04</t>
   </si>
   <si>
-    <t>2007-09-03</t>
-  </si>
-  <si>
     <t>FLSO0708</t>
   </si>
   <si>
     <t>Lesotho Drought Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2008-01-28</t>
+  </si>
+  <si>
     <t>2007-07-28</t>
   </si>
   <si>
-    <t>2008-01-28</t>
-  </si>
-  <si>
     <t>CLBR07</t>
   </si>
   <si>
@@ -5092,24 +5092,24 @@
     <t>Madagascar Floods Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2007-09-15</t>
+  </si>
+  <si>
     <t>2007-03-15</t>
   </si>
   <si>
-    <t>2007-09-15</t>
-  </si>
-  <si>
     <t>FMOZ07</t>
   </si>
   <si>
     <t>Mozambique Floods and Cyclone Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2007-06-30</t>
+  </si>
+  <si>
     <t>2007-03-01</t>
   </si>
   <si>
-    <t>2007-06-30</t>
-  </si>
-  <si>
     <t>ONPL07</t>
   </si>
   <si>
@@ -5122,12 +5122,12 @@
     <t>Nicaragua Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2008-02-28</t>
+  </si>
+  <si>
     <t>2007-09-07</t>
   </si>
   <si>
-    <t>2008-02-28</t>
-  </si>
-  <si>
     <t>ORUS07</t>
   </si>
   <si>
@@ -5140,12 +5140,12 @@
     <t>Pakistan Cyclone and Floods Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2007-10-31</t>
+  </si>
+  <si>
     <t>2007-07-15</t>
   </si>
   <si>
-    <t>2007-10-31</t>
-  </si>
-  <si>
     <t>FPER0708</t>
   </si>
   <si>
@@ -5203,12 +5203,12 @@
     <t>Swaziland Drought Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2008-01-20</t>
+  </si>
+  <si>
     <t>2007-07-20</t>
   </si>
   <si>
-    <t>2008-01-20</t>
-  </si>
-  <si>
     <t>CTLS07</t>
   </si>
   <si>
@@ -5257,15 +5257,15 @@
     <t>Afghanistan Drought Joint Appeal 2006</t>
   </si>
   <si>
+    <t>2006-12-31</t>
+  </si>
+  <si>
+    <t>2006</t>
+  </si>
+  <si>
     <t>2006-07-01</t>
   </si>
   <si>
-    <t>2006</t>
-  </si>
-  <si>
-    <t>2006-12-31</t>
-  </si>
-  <si>
     <t>CBDI06</t>
   </si>
   <si>
@@ -5311,24 +5311,24 @@
     <t>Ethiopia Floods Joint Appeal 2006</t>
   </si>
   <si>
+    <t>2006-11-25</t>
+  </si>
+  <si>
     <t>2006-08-25</t>
   </si>
   <si>
-    <t>2006-11-25</t>
-  </si>
-  <si>
     <t>OETH0607</t>
   </si>
   <si>
     <t>Ethiopia: 2006 Govt-UN Joint Emergency Flood Appeal for Somali Region</t>
   </si>
   <si>
+    <t>2007-01-22</t>
+  </si>
+  <si>
     <t>2006-11-23</t>
   </si>
   <si>
-    <t>2007-01-22</t>
-  </si>
-  <si>
     <t>CXGLR06</t>
   </si>
   <si>
@@ -5347,12 +5347,12 @@
     <t>Guinea-Bissau 2006</t>
   </si>
   <si>
+    <t>2006-11-30</t>
+  </si>
+  <si>
     <t>2006-05-01</t>
   </si>
   <si>
-    <t>2006-11-30</t>
-  </si>
-  <si>
     <t>CXHAF06</t>
   </si>
   <si>
@@ -5371,12 +5371,12 @@
     <t>Kenya 2006</t>
   </si>
   <si>
+    <t>2007-04-15</t>
+  </si>
+  <si>
     <t>2006-10-16</t>
   </si>
   <si>
-    <t>2007-04-15</t>
-  </si>
-  <si>
     <t>FKEN06</t>
   </si>
   <si>
@@ -5392,12 +5392,12 @@
     <t>Lebanon Crisis 2006</t>
   </si>
   <si>
+    <t>2006-10-23</t>
+  </si>
+  <si>
     <t>2006-07-24</t>
   </si>
   <si>
-    <t>2006-10-23</t>
-  </si>
-  <si>
     <t>CLBR06</t>
   </si>
   <si>
@@ -5446,12 +5446,12 @@
     <t>Somalia: 2006 Flood Response Plan</t>
   </si>
   <si>
+    <t>2007-03-05</t>
+  </si>
+  <si>
     <t>2006-12-05</t>
   </si>
   <si>
-    <t>2007-03-05</t>
-  </si>
-  <si>
     <t>OLKA06</t>
   </si>
   <si>
@@ -5512,39 +5512,39 @@
     <t>Angola Marburg VHF 2005</t>
   </si>
   <si>
+    <t>2005-06-30</t>
+  </si>
+  <si>
+    <t>2005</t>
+  </si>
+  <si>
     <t>2005-04-01</t>
   </si>
   <si>
-    <t>2005</t>
-  </si>
-  <si>
-    <t>2005-06-30</t>
-  </si>
-  <si>
     <t>FBEN05</t>
   </si>
   <si>
     <t>Benin 2005</t>
   </si>
   <si>
+    <t>2005-10-31</t>
+  </si>
+  <si>
     <t>2005-05-01</t>
   </si>
   <si>
-    <t>2005-10-31</t>
-  </si>
-  <si>
     <t>CBDI05</t>
   </si>
   <si>
     <t>Burundi 2005</t>
   </si>
   <si>
+    <t>2005-12-31</t>
+  </si>
+  <si>
     <t>2005-01-01</t>
   </si>
   <si>
-    <t>2005-12-31</t>
-  </si>
-  <si>
     <t>CCAF05</t>
   </si>
   <si>
@@ -5620,12 +5620,12 @@
     <t>Guyana 2005</t>
   </si>
   <si>
+    <t>2005-08-01</t>
+  </si>
+  <si>
     <t>2005-02-01</t>
   </si>
   <si>
-    <t>2005-08-01</t>
-  </si>
-  <si>
     <t>FXINDTSU05</t>
   </si>
   <si>
@@ -5647,12 +5647,12 @@
     <t>Niger 2005</t>
   </si>
   <si>
+    <t>2005-09-30</t>
+  </si>
+  <si>
     <t>2005-06-01</t>
   </si>
   <si>
-    <t>2005-09-30</t>
-  </si>
-  <si>
     <t>CCOG05</t>
   </si>
   <si>
@@ -5671,12 +5671,12 @@
     <t>South Asia Earthquake 2005</t>
   </si>
   <si>
+    <t>2006-04-10</t>
+  </si>
+  <si>
     <t>2005-10-11</t>
   </si>
   <si>
-    <t>2006-04-10</t>
-  </si>
-  <si>
     <t>CSDN05</t>
   </si>
   <si>
@@ -5701,12 +5701,12 @@
     <t>West and Central Africa Region Cholera 2005</t>
   </si>
   <si>
+    <t>2006-05-31</t>
+  </si>
+  <si>
     <t>2005-11-01</t>
   </si>
   <si>
-    <t>2006-05-31</t>
-  </si>
-  <si>
     <t>CPSE05</t>
   </si>
   <si>
@@ -5719,15 +5719,15 @@
     <t>Afghanistan UN-Government Drought Appeal 2004</t>
   </si>
   <si>
+    <t>2004-12-31</t>
+  </si>
+  <si>
+    <t>2004</t>
+  </si>
+  <si>
     <t>2004-09-01</t>
   </si>
   <si>
-    <t>2004</t>
-  </si>
-  <si>
-    <t>2004-12-31</t>
-  </si>
-  <si>
     <t>CAGO04</t>
   </si>
   <si>
@@ -5743,24 +5743,24 @@
     <t>Bangladesh 2004</t>
   </si>
   <si>
+    <t>2005-01-31</t>
+  </si>
+  <si>
     <t>2004-08-01</t>
   </si>
   <si>
-    <t>2005-01-31</t>
-  </si>
-  <si>
     <t>FBOL0405</t>
   </si>
   <si>
     <t>Bolivia 2004</t>
   </si>
   <si>
+    <t>2005-05-31</t>
+  </si>
+  <si>
     <t>2004-11-01</t>
   </si>
   <si>
-    <t>2005-05-31</t>
-  </si>
-  <si>
     <t>CBDI04</t>
   </si>
   <si>
@@ -5887,24 +5887,24 @@
     <t>Madagascar 2004</t>
   </si>
   <si>
+    <t>2004-06-19</t>
+  </si>
+  <si>
     <t>2004-03-19</t>
   </si>
   <si>
-    <t>2004-06-19</t>
-  </si>
-  <si>
     <t>FPHL0405</t>
   </si>
   <si>
     <t>Philippines 2004</t>
   </si>
   <si>
+    <t>2005-03-15</t>
+  </si>
+  <si>
     <t>2004-12-15</t>
   </si>
   <si>
-    <t>2005-03-15</t>
-  </si>
-  <si>
     <t>CSLE04</t>
   </si>
   <si>
@@ -5965,15 +5965,15 @@
     <t>Afghanistan TAPA 2003</t>
   </si>
   <si>
+    <t>2003-12-31</t>
+  </si>
+  <si>
+    <t>2003</t>
+  </si>
+  <si>
     <t>2003-01-01</t>
   </si>
   <si>
-    <t>2003</t>
-  </si>
-  <si>
-    <t>2003-12-31</t>
-  </si>
-  <si>
     <t>CAGO03</t>
   </si>
   <si>
@@ -5992,12 +5992,12 @@
     <t>Central African Republic 2003</t>
   </si>
   <si>
+    <t>2003-06-30</t>
+  </si>
+  <si>
     <t>2003-04-01</t>
   </si>
   <si>
-    <t>2003-06-30</t>
-  </si>
-  <si>
     <t>CRUS03</t>
   </si>
   <si>
@@ -6022,12 +6022,12 @@
     <t>Côte d'Ivoire and the West Africa Sub-Region 2002-2003</t>
   </si>
   <si>
+    <t>2003-01-31</t>
+  </si>
+  <si>
     <t>2002-11-01</t>
   </si>
   <si>
-    <t>2003-01-31</t>
-  </si>
-  <si>
     <t>CPRK03</t>
   </si>
   <si>
@@ -6064,24 +6064,24 @@
     <t>Haiti (PIR) 2003</t>
   </si>
   <si>
+    <t>2003-08-31</t>
+  </si>
+  <si>
     <t>2003-03-01</t>
   </si>
   <si>
-    <t>2003-08-31</t>
-  </si>
-  <si>
     <t>CLSO0304</t>
   </si>
   <si>
     <t>Humanitarian Crisis in Southern Africa - LESOTHO (July 2003 - June 2004)</t>
   </si>
   <si>
+    <t>2004-06-30</t>
+  </si>
+  <si>
     <t>2003-07-01</t>
   </si>
   <si>
-    <t>2004-06-30</t>
-  </si>
-  <si>
     <t>CMWI03</t>
   </si>
   <si>
@@ -6184,15 +6184,15 @@
     <t>Afghanistan 2002 (ITAP for the Afghan People)</t>
   </si>
   <si>
+    <t>2002-12-31</t>
+  </si>
+  <si>
+    <t>2002</t>
+  </si>
+  <si>
     <t>2001-10-01</t>
   </si>
   <si>
-    <t>2002</t>
-  </si>
-  <si>
-    <t>2002-12-31</t>
-  </si>
-  <si>
     <t>CAGO02</t>
   </si>
   <si>
@@ -6370,15 +6370,15 @@
     <t>Afghanistan 2001</t>
   </si>
   <si>
+    <t>2001-09-30</t>
+  </si>
+  <si>
+    <t>2001</t>
+  </si>
+  <si>
     <t>2001-01-01</t>
   </si>
   <si>
-    <t>2001</t>
-  </si>
-  <si>
-    <t>2001-09-30</t>
-  </si>
-  <si>
     <t>CAGO01</t>
   </si>
   <si>
@@ -6520,15 +6520,15 @@
     <t>Angola 2000</t>
   </si>
   <si>
+    <t>2000-12-31</t>
+  </si>
+  <si>
+    <t>2000</t>
+  </si>
+  <si>
     <t>2000-01-01</t>
   </si>
   <si>
-    <t>2000</t>
-  </si>
-  <si>
-    <t>2000-12-31</t>
-  </si>
-  <si>
     <t>CBDI00</t>
   </si>
   <si>
@@ -6616,10 +6616,10 @@
     <t>East Timor 1999</t>
   </si>
   <si>
+    <t>1999</t>
+  </si>
+  <si>
     <t>1999-10-01</t>
-  </si>
-  <si>
-    <t>1999</t>
   </si>
   <si>
     <t>CRUS9900</t>
@@ -7052,13 +7052,13 @@
         <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F4" t="s">
         <v>12</v>
       </c>
       <c r="G4" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -7282,13 +7282,13 @@
         <v>34</v>
       </c>
       <c r="E14" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F14" t="s">
         <v>12</v>
       </c>
       <c r="G14" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -7305,13 +7305,13 @@
         <v>34</v>
       </c>
       <c r="E15" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="F15" t="s">
         <v>12</v>
       </c>
       <c r="G15" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -7351,13 +7351,13 @@
         <v>34</v>
       </c>
       <c r="E17" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="F17" t="s">
         <v>12</v>
       </c>
       <c r="G17" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -7397,13 +7397,13 @@
         <v>34</v>
       </c>
       <c r="E19" t="s">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="F19" t="s">
         <v>12</v>
       </c>
       <c r="G19" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -7420,13 +7420,13 @@
         <v>10</v>
       </c>
       <c r="E20" t="s">
-        <v>58</v>
+        <v>11</v>
       </c>
       <c r="F20" t="s">
         <v>12</v>
       </c>
       <c r="G20" t="s">
-        <v>13</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -7512,13 +7512,13 @@
         <v>19</v>
       </c>
       <c r="E24" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="F24" t="s">
         <v>12</v>
       </c>
       <c r="G24" t="s">
-        <v>67</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -7742,13 +7742,13 @@
         <v>34</v>
       </c>
       <c r="E34" t="s">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="F34" t="s">
         <v>12</v>
       </c>
       <c r="G34" t="s">
-        <v>13</v>
+        <v>88</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -7926,13 +7926,13 @@
         <v>19</v>
       </c>
       <c r="E42" t="s">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="F42" t="s">
         <v>12</v>
       </c>
       <c r="G42" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -7972,13 +7972,13 @@
         <v>34</v>
       </c>
       <c r="E44" t="s">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="F44" t="s">
         <v>12</v>
       </c>
       <c r="G44" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -7995,13 +7995,13 @@
         <v>34</v>
       </c>
       <c r="E45" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="F45" t="s">
         <v>12</v>
       </c>
       <c r="G45" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -8064,13 +8064,13 @@
         <v>19</v>
       </c>
       <c r="E48" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="F48" t="s">
         <v>114</v>
       </c>
       <c r="G48" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -8110,13 +8110,13 @@
         <v>19</v>
       </c>
       <c r="E50" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="F50" t="s">
         <v>114</v>
       </c>
       <c r="G50" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -8271,13 +8271,13 @@
         <v>34</v>
       </c>
       <c r="E57" t="s">
-        <v>140</v>
+        <v>113</v>
       </c>
       <c r="F57" t="s">
         <v>114</v>
       </c>
       <c r="G57" t="s">
-        <v>115</v>
+        <v>140</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -8363,13 +8363,13 @@
         <v>19</v>
       </c>
       <c r="E61" t="s">
-        <v>149</v>
+        <v>113</v>
       </c>
       <c r="F61" t="s">
         <v>114</v>
       </c>
       <c r="G61" t="s">
-        <v>115</v>
+        <v>149</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -8386,13 +8386,13 @@
         <v>34</v>
       </c>
       <c r="E62" t="s">
-        <v>149</v>
+        <v>113</v>
       </c>
       <c r="F62" t="s">
         <v>114</v>
       </c>
       <c r="G62" t="s">
-        <v>115</v>
+        <v>149</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -8409,13 +8409,13 @@
         <v>34</v>
       </c>
       <c r="E63" t="s">
-        <v>113</v>
+        <v>154</v>
       </c>
       <c r="F63" t="s">
         <v>114</v>
       </c>
       <c r="G63" t="s">
-        <v>154</v>
+        <v>115</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -8432,13 +8432,13 @@
         <v>34</v>
       </c>
       <c r="E64" t="s">
-        <v>113</v>
+        <v>157</v>
       </c>
       <c r="F64" t="s">
         <v>114</v>
       </c>
       <c r="G64" t="s">
-        <v>157</v>
+        <v>115</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -8455,13 +8455,13 @@
         <v>34</v>
       </c>
       <c r="E65" t="s">
-        <v>160</v>
+        <v>113</v>
       </c>
       <c r="F65" t="s">
         <v>114</v>
       </c>
       <c r="G65" t="s">
-        <v>115</v>
+        <v>160</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -8501,13 +8501,13 @@
         <v>19</v>
       </c>
       <c r="E67" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="F67" t="s">
         <v>114</v>
       </c>
       <c r="G67" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -8524,13 +8524,13 @@
         <v>34</v>
       </c>
       <c r="E68" t="s">
-        <v>168</v>
+        <v>113</v>
       </c>
       <c r="F68" t="s">
         <v>114</v>
       </c>
       <c r="G68" t="s">
-        <v>115</v>
+        <v>168</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -8593,13 +8593,13 @@
         <v>19</v>
       </c>
       <c r="E71" t="s">
-        <v>175</v>
+        <v>113</v>
       </c>
       <c r="F71" t="s">
         <v>114</v>
       </c>
       <c r="G71" t="s">
-        <v>115</v>
+        <v>175</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -8662,13 +8662,13 @@
         <v>19</v>
       </c>
       <c r="E74" t="s">
-        <v>182</v>
+        <v>113</v>
       </c>
       <c r="F74" t="s">
         <v>114</v>
       </c>
       <c r="G74" t="s">
-        <v>115</v>
+        <v>182</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -8800,13 +8800,13 @@
         <v>34</v>
       </c>
       <c r="E80" t="s">
-        <v>140</v>
+        <v>113</v>
       </c>
       <c r="F80" t="s">
         <v>114</v>
       </c>
       <c r="G80" t="s">
-        <v>115</v>
+        <v>140</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -9099,13 +9099,13 @@
         <v>19</v>
       </c>
       <c r="E93" t="s">
-        <v>222</v>
+        <v>113</v>
       </c>
       <c r="F93" t="s">
         <v>114</v>
       </c>
       <c r="G93" t="s">
-        <v>115</v>
+        <v>222</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -9145,13 +9145,13 @@
         <v>34</v>
       </c>
       <c r="E95" t="s">
-        <v>227</v>
+        <v>113</v>
       </c>
       <c r="F95" t="s">
         <v>114</v>
       </c>
       <c r="G95" t="s">
-        <v>115</v>
+        <v>227</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -9168,13 +9168,13 @@
         <v>34</v>
       </c>
       <c r="E96" t="s">
-        <v>227</v>
+        <v>113</v>
       </c>
       <c r="F96" t="s">
         <v>114</v>
       </c>
       <c r="G96" t="s">
-        <v>115</v>
+        <v>227</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -9375,13 +9375,13 @@
         <v>34</v>
       </c>
       <c r="E105" t="s">
-        <v>251</v>
+        <v>232</v>
       </c>
       <c r="F105" t="s">
         <v>233</v>
       </c>
       <c r="G105" t="s">
-        <v>234</v>
+        <v>251</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -9559,13 +9559,13 @@
         <v>34</v>
       </c>
       <c r="E113" t="s">
-        <v>268</v>
+        <v>232</v>
       </c>
       <c r="F113" t="s">
         <v>233</v>
       </c>
       <c r="G113" t="s">
-        <v>234</v>
+        <v>268</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -9766,13 +9766,13 @@
         <v>25</v>
       </c>
       <c r="E122" t="s">
-        <v>232</v>
+        <v>279</v>
       </c>
       <c r="F122" t="s">
         <v>233</v>
       </c>
       <c r="G122" t="s">
-        <v>280</v>
+        <v>234</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -9789,13 +9789,13 @@
         <v>19</v>
       </c>
       <c r="E123" t="s">
-        <v>232</v>
+        <v>275</v>
       </c>
       <c r="F123" t="s">
         <v>233</v>
       </c>
       <c r="G123" t="s">
-        <v>276</v>
+        <v>234</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -10042,13 +10042,13 @@
         <v>34</v>
       </c>
       <c r="E134" t="s">
-        <v>316</v>
+        <v>275</v>
       </c>
       <c r="F134" t="s">
         <v>233</v>
       </c>
       <c r="G134" t="s">
-        <v>276</v>
+        <v>316</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -10088,13 +10088,13 @@
         <v>34</v>
       </c>
       <c r="E136" t="s">
-        <v>321</v>
+        <v>275</v>
       </c>
       <c r="F136" t="s">
         <v>233</v>
       </c>
       <c r="G136" t="s">
-        <v>276</v>
+        <v>321</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -10571,13 +10571,13 @@
         <v>34</v>
       </c>
       <c r="E157" t="s">
-        <v>367</v>
+        <v>338</v>
       </c>
       <c r="F157" t="s">
         <v>339</v>
       </c>
       <c r="G157" t="s">
-        <v>340</v>
+        <v>368</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -10663,13 +10663,13 @@
         <v>34</v>
       </c>
       <c r="E161" t="s">
-        <v>338</v>
+        <v>379</v>
       </c>
       <c r="F161" t="s">
         <v>339</v>
       </c>
       <c r="G161" t="s">
-        <v>379</v>
+        <v>340</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -10939,13 +10939,13 @@
         <v>19</v>
       </c>
       <c r="E173" t="s">
-        <v>408</v>
+        <v>338</v>
       </c>
       <c r="F173" t="s">
         <v>339</v>
       </c>
       <c r="G173" t="s">
-        <v>340</v>
+        <v>408</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -10962,13 +10962,13 @@
         <v>19</v>
       </c>
       <c r="E174" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="F174" t="s">
         <v>339</v>
       </c>
       <c r="G174" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -11169,13 +11169,13 @@
         <v>19</v>
       </c>
       <c r="E183" t="s">
-        <v>431</v>
+        <v>338</v>
       </c>
       <c r="F183" t="s">
         <v>339</v>
       </c>
       <c r="G183" t="s">
-        <v>340</v>
+        <v>431</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -11284,13 +11284,13 @@
         <v>34</v>
       </c>
       <c r="E188" t="s">
-        <v>442</v>
+        <v>338</v>
       </c>
       <c r="F188" t="s">
         <v>339</v>
       </c>
       <c r="G188" t="s">
-        <v>340</v>
+        <v>442</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -11330,13 +11330,13 @@
         <v>16</v>
       </c>
       <c r="E190" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="F190" t="s">
         <v>339</v>
       </c>
       <c r="G190" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -11422,13 +11422,13 @@
         <v>25</v>
       </c>
       <c r="E194" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="F194" t="s">
         <v>455</v>
       </c>
       <c r="G194" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -11445,13 +11445,13 @@
         <v>16</v>
       </c>
       <c r="E195" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="F195" t="s">
         <v>455</v>
       </c>
       <c r="G195" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -11468,13 +11468,13 @@
         <v>25</v>
       </c>
       <c r="E196" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="F196" t="s">
         <v>455</v>
       </c>
       <c r="G196" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -11491,13 +11491,13 @@
         <v>25</v>
       </c>
       <c r="E197" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="F197" t="s">
         <v>455</v>
       </c>
       <c r="G197" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -11514,13 +11514,13 @@
         <v>16</v>
       </c>
       <c r="E198" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="F198" t="s">
         <v>455</v>
       </c>
       <c r="G198" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -11537,13 +11537,13 @@
         <v>25</v>
       </c>
       <c r="E199" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="F199" t="s">
         <v>455</v>
       </c>
       <c r="G199" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -11560,13 +11560,13 @@
         <v>25</v>
       </c>
       <c r="E200" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="F200" t="s">
         <v>455</v>
       </c>
       <c r="G200" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -11583,13 +11583,13 @@
         <v>25</v>
       </c>
       <c r="E201" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="F201" t="s">
         <v>455</v>
       </c>
       <c r="G201" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -11606,13 +11606,13 @@
         <v>25</v>
       </c>
       <c r="E202" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="F202" t="s">
         <v>455</v>
       </c>
       <c r="G202" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -11629,13 +11629,13 @@
         <v>25</v>
       </c>
       <c r="E203" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="F203" t="s">
         <v>455</v>
       </c>
       <c r="G203" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -11652,13 +11652,13 @@
         <v>16</v>
       </c>
       <c r="E204" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="F204" t="s">
         <v>455</v>
       </c>
       <c r="G204" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -11675,13 +11675,13 @@
         <v>25</v>
       </c>
       <c r="E205" t="s">
-        <v>482</v>
+        <v>454</v>
       </c>
       <c r="F205" t="s">
         <v>455</v>
       </c>
       <c r="G205" t="s">
-        <v>456</v>
+        <v>482</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -11698,13 +11698,13 @@
         <v>25</v>
       </c>
       <c r="E206" t="s">
-        <v>482</v>
+        <v>338</v>
       </c>
       <c r="F206" t="s">
         <v>455</v>
       </c>
       <c r="G206" t="s">
-        <v>340</v>
+        <v>482</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -11744,13 +11744,13 @@
         <v>25</v>
       </c>
       <c r="E208" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="F208" t="s">
         <v>455</v>
       </c>
       <c r="G208" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -11767,13 +11767,13 @@
         <v>25</v>
       </c>
       <c r="E209" t="s">
-        <v>482</v>
+        <v>454</v>
       </c>
       <c r="F209" t="s">
         <v>455</v>
       </c>
       <c r="G209" t="s">
-        <v>456</v>
+        <v>482</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -11790,13 +11790,13 @@
         <v>25</v>
       </c>
       <c r="E210" t="s">
-        <v>482</v>
+        <v>338</v>
       </c>
       <c r="F210" t="s">
         <v>455</v>
       </c>
       <c r="G210" t="s">
-        <v>340</v>
+        <v>482</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -11836,13 +11836,13 @@
         <v>25</v>
       </c>
       <c r="E212" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="F212" t="s">
         <v>455</v>
       </c>
       <c r="G212" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -11882,13 +11882,13 @@
         <v>25</v>
       </c>
       <c r="E214" t="s">
-        <v>482</v>
+        <v>454</v>
       </c>
       <c r="F214" t="s">
         <v>455</v>
       </c>
       <c r="G214" t="s">
-        <v>456</v>
+        <v>482</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -11905,13 +11905,13 @@
         <v>25</v>
       </c>
       <c r="E215" t="s">
-        <v>482</v>
+        <v>338</v>
       </c>
       <c r="F215" t="s">
         <v>455</v>
       </c>
       <c r="G215" t="s">
-        <v>340</v>
+        <v>482</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -11928,13 +11928,13 @@
         <v>25</v>
       </c>
       <c r="E216" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="F216" t="s">
         <v>455</v>
       </c>
       <c r="G216" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -11951,13 +11951,13 @@
         <v>34</v>
       </c>
       <c r="E217" t="s">
-        <v>513</v>
+        <v>454</v>
       </c>
       <c r="F217" t="s">
         <v>455</v>
       </c>
       <c r="G217" t="s">
-        <v>456</v>
+        <v>513</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -11997,13 +11997,13 @@
         <v>25</v>
       </c>
       <c r="E219" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="F219" t="s">
         <v>455</v>
       </c>
       <c r="G219" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -12020,13 +12020,13 @@
         <v>34</v>
       </c>
       <c r="E220" t="s">
-        <v>459</v>
+        <v>388</v>
       </c>
       <c r="F220" t="s">
         <v>455</v>
       </c>
       <c r="G220" t="s">
-        <v>389</v>
+        <v>459</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -12043,13 +12043,13 @@
         <v>34</v>
       </c>
       <c r="E221" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="F221" t="s">
         <v>455</v>
       </c>
       <c r="G221" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -12066,13 +12066,13 @@
         <v>25</v>
       </c>
       <c r="E222" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="F222" t="s">
         <v>455</v>
       </c>
       <c r="G222" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -12089,13 +12089,13 @@
         <v>25</v>
       </c>
       <c r="E223" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="F223" t="s">
         <v>455</v>
       </c>
       <c r="G223" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -12112,13 +12112,13 @@
         <v>25</v>
       </c>
       <c r="E224" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="F224" t="s">
         <v>455</v>
       </c>
       <c r="G224" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -12135,13 +12135,13 @@
         <v>19</v>
       </c>
       <c r="E225" t="s">
-        <v>532</v>
+        <v>454</v>
       </c>
       <c r="F225" t="s">
         <v>455</v>
       </c>
       <c r="G225" t="s">
-        <v>456</v>
+        <v>532</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -12158,13 +12158,13 @@
         <v>19</v>
       </c>
       <c r="E226" t="s">
-        <v>535</v>
+        <v>454</v>
       </c>
       <c r="F226" t="s">
         <v>455</v>
       </c>
       <c r="G226" t="s">
-        <v>456</v>
+        <v>535</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -12181,13 +12181,13 @@
         <v>25</v>
       </c>
       <c r="E227" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="F227" t="s">
         <v>455</v>
       </c>
       <c r="G227" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -12204,13 +12204,13 @@
         <v>25</v>
       </c>
       <c r="E228" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="F228" t="s">
         <v>455</v>
       </c>
       <c r="G228" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -12227,13 +12227,13 @@
         <v>34</v>
       </c>
       <c r="E229" t="s">
-        <v>535</v>
+        <v>454</v>
       </c>
       <c r="F229" t="s">
         <v>455</v>
       </c>
       <c r="G229" t="s">
-        <v>456</v>
+        <v>535</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -12250,13 +12250,13 @@
         <v>19</v>
       </c>
       <c r="E230" t="s">
-        <v>535</v>
+        <v>454</v>
       </c>
       <c r="F230" t="s">
         <v>455</v>
       </c>
       <c r="G230" t="s">
-        <v>456</v>
+        <v>535</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -12273,13 +12273,13 @@
         <v>25</v>
       </c>
       <c r="E231" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="F231" t="s">
         <v>455</v>
       </c>
       <c r="G231" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -12296,13 +12296,13 @@
         <v>25</v>
       </c>
       <c r="E232" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="F232" t="s">
         <v>455</v>
       </c>
       <c r="G232" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -12319,13 +12319,13 @@
         <v>16</v>
       </c>
       <c r="E233" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="F233" t="s">
         <v>455</v>
       </c>
       <c r="G233" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="234" spans="1:7">
@@ -12342,13 +12342,13 @@
         <v>16</v>
       </c>
       <c r="E234" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="F234" t="s">
         <v>455</v>
       </c>
       <c r="G234" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -12365,13 +12365,13 @@
         <v>25</v>
       </c>
       <c r="E235" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="F235" t="s">
         <v>455</v>
       </c>
       <c r="G235" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -12388,13 +12388,13 @@
         <v>25</v>
       </c>
       <c r="E236" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="F236" t="s">
         <v>455</v>
       </c>
       <c r="G236" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="237" spans="1:7">
@@ -12411,13 +12411,13 @@
         <v>16</v>
       </c>
       <c r="E237" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="F237" t="s">
         <v>455</v>
       </c>
       <c r="G237" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="238" spans="1:7">
@@ -12434,13 +12434,13 @@
         <v>25</v>
       </c>
       <c r="E238" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="F238" t="s">
         <v>455</v>
       </c>
       <c r="G238" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="239" spans="1:7">
@@ -12457,13 +12457,13 @@
         <v>25</v>
       </c>
       <c r="E239" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="F239" t="s">
         <v>455</v>
       </c>
       <c r="G239" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="240" spans="1:7">
@@ -12480,13 +12480,13 @@
         <v>16</v>
       </c>
       <c r="E240" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="F240" t="s">
         <v>455</v>
       </c>
       <c r="G240" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="241" spans="1:7">
@@ -12503,13 +12503,13 @@
         <v>25</v>
       </c>
       <c r="E241" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="F241" t="s">
         <v>455</v>
       </c>
       <c r="G241" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="242" spans="1:7">
@@ -12526,13 +12526,13 @@
         <v>25</v>
       </c>
       <c r="E242" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="F242" t="s">
         <v>455</v>
       </c>
       <c r="G242" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="243" spans="1:7">
@@ -12549,13 +12549,13 @@
         <v>25</v>
       </c>
       <c r="E243" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="F243" t="s">
         <v>455</v>
       </c>
       <c r="G243" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="244" spans="1:7">
@@ -12572,13 +12572,13 @@
         <v>25</v>
       </c>
       <c r="E244" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="F244" t="s">
         <v>455</v>
       </c>
       <c r="G244" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="245" spans="1:7">
@@ -12618,13 +12618,13 @@
         <v>19</v>
       </c>
       <c r="E246" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="F246" t="s">
         <v>574</v>
       </c>
       <c r="G246" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -12664,13 +12664,13 @@
         <v>19</v>
       </c>
       <c r="E248" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="F248" t="s">
         <v>574</v>
       </c>
       <c r="G248" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
     </row>
     <row r="249" spans="1:7">
@@ -12756,13 +12756,13 @@
         <v>19</v>
       </c>
       <c r="E252" t="s">
-        <v>591</v>
+        <v>573</v>
       </c>
       <c r="F252" t="s">
         <v>574</v>
       </c>
       <c r="G252" t="s">
-        <v>575</v>
+        <v>591</v>
       </c>
     </row>
     <row r="253" spans="1:7">
@@ -12802,13 +12802,13 @@
         <v>25</v>
       </c>
       <c r="E254" t="s">
-        <v>596</v>
+        <v>459</v>
       </c>
       <c r="F254" t="s">
         <v>574</v>
       </c>
       <c r="G254" t="s">
-        <v>459</v>
+        <v>596</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -12871,13 +12871,13 @@
         <v>19</v>
       </c>
       <c r="E257" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="F257" t="s">
         <v>574</v>
       </c>
       <c r="G257" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
     </row>
     <row r="258" spans="1:7">
@@ -12894,13 +12894,13 @@
         <v>19</v>
       </c>
       <c r="E258" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="F258" t="s">
         <v>574</v>
       </c>
       <c r="G258" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
     </row>
     <row r="259" spans="1:7">
@@ -12917,13 +12917,13 @@
         <v>25</v>
       </c>
       <c r="E259" t="s">
-        <v>607</v>
+        <v>573</v>
       </c>
       <c r="F259" t="s">
         <v>574</v>
       </c>
       <c r="G259" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
     </row>
     <row r="260" spans="1:7">
@@ -13009,13 +13009,13 @@
         <v>19</v>
       </c>
       <c r="E263" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="F263" t="s">
         <v>574</v>
       </c>
       <c r="G263" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
     </row>
     <row r="264" spans="1:7">
@@ -13032,13 +13032,13 @@
         <v>19</v>
       </c>
       <c r="E264" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="F264" t="s">
         <v>574</v>
       </c>
       <c r="G264" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
     </row>
     <row r="265" spans="1:7">
@@ -13078,13 +13078,13 @@
         <v>19</v>
       </c>
       <c r="E266" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="F266" t="s">
         <v>574</v>
       </c>
       <c r="G266" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
     </row>
     <row r="267" spans="1:7">
@@ -13124,13 +13124,13 @@
         <v>19</v>
       </c>
       <c r="E268" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="F268" t="s">
         <v>574</v>
       </c>
       <c r="G268" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
     </row>
     <row r="269" spans="1:7">
@@ -13147,13 +13147,13 @@
         <v>19</v>
       </c>
       <c r="E269" t="s">
-        <v>607</v>
+        <v>573</v>
       </c>
       <c r="F269" t="s">
         <v>574</v>
       </c>
       <c r="G269" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
     </row>
     <row r="270" spans="1:7">
@@ -13170,13 +13170,13 @@
         <v>19</v>
       </c>
       <c r="E270" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="F270" t="s">
         <v>574</v>
       </c>
       <c r="G270" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
     </row>
     <row r="271" spans="1:7">
@@ -13193,13 +13193,13 @@
         <v>19</v>
       </c>
       <c r="E271" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="F271" t="s">
         <v>574</v>
       </c>
       <c r="G271" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
     </row>
     <row r="272" spans="1:7">
@@ -13239,13 +13239,13 @@
         <v>19</v>
       </c>
       <c r="E273" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="F273" t="s">
         <v>574</v>
       </c>
       <c r="G273" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
     </row>
     <row r="274" spans="1:7">
@@ -13285,13 +13285,13 @@
         <v>19</v>
       </c>
       <c r="E275" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="F275" t="s">
         <v>574</v>
       </c>
       <c r="G275" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
     </row>
     <row r="276" spans="1:7">
@@ -13308,13 +13308,13 @@
         <v>19</v>
       </c>
       <c r="E276" t="s">
-        <v>644</v>
+        <v>573</v>
       </c>
       <c r="F276" t="s">
         <v>574</v>
       </c>
       <c r="G276" t="s">
-        <v>575</v>
+        <v>644</v>
       </c>
     </row>
     <row r="277" spans="1:7">
@@ -13354,13 +13354,13 @@
         <v>19</v>
       </c>
       <c r="E278" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="F278" t="s">
         <v>574</v>
       </c>
       <c r="G278" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
     </row>
     <row r="279" spans="1:7">
@@ -13400,13 +13400,13 @@
         <v>19</v>
       </c>
       <c r="E280" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="F280" t="s">
         <v>574</v>
       </c>
       <c r="G280" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
     </row>
     <row r="281" spans="1:7">
@@ -13469,13 +13469,13 @@
         <v>19</v>
       </c>
       <c r="E283" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="F283" t="s">
         <v>574</v>
       </c>
       <c r="G283" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
     </row>
     <row r="284" spans="1:7">
@@ -13584,13 +13584,13 @@
         <v>19</v>
       </c>
       <c r="E288" t="s">
-        <v>644</v>
+        <v>573</v>
       </c>
       <c r="F288" t="s">
         <v>574</v>
       </c>
       <c r="G288" t="s">
-        <v>575</v>
+        <v>644</v>
       </c>
     </row>
     <row r="289" spans="1:7">
@@ -13607,13 +13607,13 @@
         <v>19</v>
       </c>
       <c r="E289" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="F289" t="s">
         <v>574</v>
       </c>
       <c r="G289" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
     </row>
     <row r="290" spans="1:7">
@@ -13676,13 +13676,13 @@
         <v>19</v>
       </c>
       <c r="E292" t="s">
-        <v>644</v>
+        <v>573</v>
       </c>
       <c r="F292" t="s">
         <v>574</v>
       </c>
       <c r="G292" t="s">
-        <v>575</v>
+        <v>644</v>
       </c>
     </row>
     <row r="293" spans="1:7">
@@ -13699,13 +13699,13 @@
         <v>19</v>
       </c>
       <c r="E293" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="F293" t="s">
         <v>574</v>
       </c>
       <c r="G293" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
     </row>
     <row r="294" spans="1:7">
@@ -13860,13 +13860,13 @@
         <v>19</v>
       </c>
       <c r="E300" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="F300" t="s">
         <v>574</v>
       </c>
       <c r="G300" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
     </row>
     <row r="301" spans="1:7">
@@ -13883,13 +13883,13 @@
         <v>19</v>
       </c>
       <c r="E301" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="F301" t="s">
         <v>574</v>
       </c>
       <c r="G301" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
     </row>
     <row r="302" spans="1:7">
@@ -13906,13 +13906,13 @@
         <v>19</v>
       </c>
       <c r="E302" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="F302" t="s">
         <v>574</v>
       </c>
       <c r="G302" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
     </row>
     <row r="303" spans="1:7">
@@ -13952,13 +13952,13 @@
         <v>19</v>
       </c>
       <c r="E304" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="F304" t="s">
         <v>574</v>
       </c>
       <c r="G304" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
     </row>
     <row r="305" spans="1:7">
@@ -14021,13 +14021,13 @@
         <v>19</v>
       </c>
       <c r="E307" t="s">
-        <v>711</v>
+        <v>614</v>
       </c>
       <c r="F307" t="s">
         <v>574</v>
       </c>
       <c r="G307" t="s">
-        <v>615</v>
+        <v>711</v>
       </c>
     </row>
     <row r="308" spans="1:7">
@@ -14044,13 +14044,13 @@
         <v>19</v>
       </c>
       <c r="E308" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="F308" t="s">
         <v>574</v>
       </c>
       <c r="G308" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
     </row>
     <row r="309" spans="1:7">
@@ -14389,13 +14389,13 @@
         <v>19</v>
       </c>
       <c r="E323" t="s">
-        <v>747</v>
+        <v>718</v>
       </c>
       <c r="F323" t="s">
         <v>719</v>
       </c>
       <c r="G323" t="s">
-        <v>720</v>
+        <v>747</v>
       </c>
     </row>
     <row r="324" spans="1:7">
@@ -14435,13 +14435,13 @@
         <v>34</v>
       </c>
       <c r="E325" t="s">
-        <v>718</v>
+        <v>752</v>
       </c>
       <c r="F325" t="s">
         <v>719</v>
       </c>
       <c r="G325" t="s">
-        <v>752</v>
+        <v>720</v>
       </c>
     </row>
     <row r="326" spans="1:7">
@@ -14573,13 +14573,13 @@
         <v>25</v>
       </c>
       <c r="E331" t="s">
-        <v>718</v>
+        <v>765</v>
       </c>
       <c r="F331" t="s">
         <v>719</v>
       </c>
       <c r="G331" t="s">
-        <v>765</v>
+        <v>720</v>
       </c>
     </row>
     <row r="332" spans="1:7">
@@ -14872,13 +14872,13 @@
         <v>34</v>
       </c>
       <c r="E344" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="F344" t="s">
         <v>719</v>
       </c>
       <c r="G344" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
     </row>
     <row r="345" spans="1:7">
@@ -14918,13 +14918,13 @@
         <v>19</v>
       </c>
       <c r="E346" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
       <c r="F346" t="s">
         <v>798</v>
       </c>
       <c r="G346" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
     </row>
     <row r="347" spans="1:7">
@@ -15148,13 +15148,13 @@
         <v>19</v>
       </c>
       <c r="E356" t="s">
-        <v>823</v>
+        <v>797</v>
       </c>
       <c r="F356" t="s">
         <v>798</v>
       </c>
       <c r="G356" t="s">
-        <v>799</v>
+        <v>823</v>
       </c>
     </row>
     <row r="357" spans="1:7">
@@ -15378,13 +15378,13 @@
         <v>19</v>
       </c>
       <c r="E366" t="s">
-        <v>844</v>
+        <v>797</v>
       </c>
       <c r="F366" t="s">
         <v>798</v>
       </c>
       <c r="G366" t="s">
-        <v>799</v>
+        <v>844</v>
       </c>
     </row>
     <row r="367" spans="1:7">
@@ -15401,13 +15401,13 @@
         <v>16</v>
       </c>
       <c r="E367" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
       <c r="F367" t="s">
         <v>798</v>
       </c>
       <c r="G367" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
     </row>
     <row r="368" spans="1:7">
@@ -15493,13 +15493,13 @@
         <v>25</v>
       </c>
       <c r="E371" t="s">
-        <v>797</v>
+        <v>855</v>
       </c>
       <c r="F371" t="s">
         <v>798</v>
       </c>
       <c r="G371" t="s">
-        <v>855</v>
+        <v>799</v>
       </c>
     </row>
     <row r="372" spans="1:7">
@@ -15700,13 +15700,13 @@
         <v>16</v>
       </c>
       <c r="E380" t="s">
-        <v>879</v>
+        <v>872</v>
       </c>
       <c r="F380" t="s">
         <v>873</v>
       </c>
       <c r="G380" t="s">
-        <v>874</v>
+        <v>879</v>
       </c>
     </row>
     <row r="381" spans="1:7">
@@ -15838,13 +15838,13 @@
         <v>19</v>
       </c>
       <c r="E386" t="s">
-        <v>892</v>
+        <v>872</v>
       </c>
       <c r="F386" t="s">
         <v>873</v>
       </c>
       <c r="G386" t="s">
-        <v>874</v>
+        <v>892</v>
       </c>
     </row>
     <row r="387" spans="1:7">
@@ -15861,13 +15861,13 @@
         <v>25</v>
       </c>
       <c r="E387" t="s">
-        <v>895</v>
+        <v>872</v>
       </c>
       <c r="F387" t="s">
         <v>873</v>
       </c>
       <c r="G387" t="s">
-        <v>874</v>
+        <v>895</v>
       </c>
     </row>
     <row r="388" spans="1:7">
@@ -15999,13 +15999,13 @@
         <v>19</v>
       </c>
       <c r="E393" t="s">
-        <v>910</v>
+        <v>872</v>
       </c>
       <c r="F393" t="s">
         <v>873</v>
       </c>
       <c r="G393" t="s">
-        <v>874</v>
+        <v>910</v>
       </c>
     </row>
     <row r="394" spans="1:7">
@@ -16321,13 +16321,13 @@
         <v>25</v>
       </c>
       <c r="E407" t="s">
-        <v>947</v>
+        <v>872</v>
       </c>
       <c r="F407" t="s">
         <v>873</v>
       </c>
       <c r="G407" t="s">
-        <v>874</v>
+        <v>947</v>
       </c>
     </row>
     <row r="408" spans="1:7">
@@ -16597,13 +16597,13 @@
         <v>34</v>
       </c>
       <c r="E419" t="s">
-        <v>975</v>
+        <v>968</v>
       </c>
       <c r="F419" t="s">
         <v>969</v>
       </c>
       <c r="G419" t="s">
-        <v>970</v>
+        <v>975</v>
       </c>
     </row>
     <row r="420" spans="1:7">
@@ -16643,13 +16643,13 @@
         <v>25</v>
       </c>
       <c r="E421" t="s">
-        <v>980</v>
+        <v>968</v>
       </c>
       <c r="F421" t="s">
         <v>969</v>
       </c>
       <c r="G421" t="s">
-        <v>970</v>
+        <v>980</v>
       </c>
     </row>
     <row r="422" spans="1:7">
@@ -16919,13 +16919,13 @@
         <v>34</v>
       </c>
       <c r="E433" t="s">
-        <v>1009</v>
+        <v>968</v>
       </c>
       <c r="F433" t="s">
         <v>969</v>
       </c>
       <c r="G433" t="s">
-        <v>970</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="434" spans="1:7">
@@ -16988,13 +16988,13 @@
         <v>34</v>
       </c>
       <c r="E436" t="s">
-        <v>1016</v>
+        <v>968</v>
       </c>
       <c r="F436" t="s">
         <v>969</v>
       </c>
       <c r="G436" t="s">
-        <v>970</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="437" spans="1:7">
@@ -17011,13 +17011,13 @@
         <v>25</v>
       </c>
       <c r="E437" t="s">
-        <v>1019</v>
+        <v>968</v>
       </c>
       <c r="F437" t="s">
         <v>969</v>
       </c>
       <c r="G437" t="s">
-        <v>970</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="438" spans="1:7">
@@ -17655,13 +17655,13 @@
         <v>34</v>
       </c>
       <c r="E465" t="s">
-        <v>1086</v>
+        <v>1061</v>
       </c>
       <c r="F465" t="s">
         <v>1062</v>
       </c>
       <c r="G465" t="s">
-        <v>1063</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="466" spans="1:7">
@@ -17678,13 +17678,13 @@
         <v>34</v>
       </c>
       <c r="E466" t="s">
-        <v>1089</v>
+        <v>1082</v>
       </c>
       <c r="F466" t="s">
         <v>1062</v>
       </c>
       <c r="G466" t="s">
-        <v>1083</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="467" spans="1:7">
@@ -17839,13 +17839,13 @@
         <v>34</v>
       </c>
       <c r="E473" t="s">
-        <v>1108</v>
+        <v>1082</v>
       </c>
       <c r="F473" t="s">
         <v>1062</v>
       </c>
       <c r="G473" t="s">
-        <v>1083</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="474" spans="1:7">
@@ -18184,13 +18184,13 @@
         <v>1060</v>
       </c>
       <c r="E488" t="s">
-        <v>1142</v>
+        <v>1137</v>
       </c>
       <c r="F488" t="s">
         <v>1138</v>
       </c>
       <c r="G488" t="s">
-        <v>1139</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="489" spans="1:7">
@@ -18276,13 +18276,13 @@
         <v>25</v>
       </c>
       <c r="E492" t="s">
-        <v>1137</v>
+        <v>1151</v>
       </c>
       <c r="F492" t="s">
         <v>1138</v>
       </c>
       <c r="G492" t="s">
-        <v>1151</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="493" spans="1:7">
@@ -18322,13 +18322,13 @@
         <v>16</v>
       </c>
       <c r="E494" t="s">
-        <v>1098</v>
+        <v>1156</v>
       </c>
       <c r="F494" t="s">
         <v>1138</v>
       </c>
       <c r="G494" t="s">
-        <v>1156</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="495" spans="1:7">
@@ -18345,13 +18345,13 @@
         <v>19</v>
       </c>
       <c r="E495" t="s">
-        <v>1098</v>
+        <v>1156</v>
       </c>
       <c r="F495" t="s">
         <v>1138</v>
       </c>
       <c r="G495" t="s">
-        <v>1156</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="496" spans="1:7">
@@ -18414,13 +18414,13 @@
         <v>1060</v>
       </c>
       <c r="E498" t="s">
-        <v>1165</v>
+        <v>1137</v>
       </c>
       <c r="F498" t="s">
         <v>1138</v>
       </c>
       <c r="G498" t="s">
-        <v>1139</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="499" spans="1:7">
@@ -18506,13 +18506,13 @@
         <v>25</v>
       </c>
       <c r="E502" t="s">
-        <v>1174</v>
+        <v>1137</v>
       </c>
       <c r="F502" t="s">
         <v>1138</v>
       </c>
       <c r="G502" t="s">
-        <v>1139</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="503" spans="1:7">
@@ -18667,13 +18667,13 @@
         <v>25</v>
       </c>
       <c r="E509" t="s">
-        <v>1189</v>
+        <v>1193</v>
       </c>
       <c r="F509" t="s">
         <v>1138</v>
       </c>
       <c r="G509" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="510" spans="1:7">
@@ -18736,13 +18736,13 @@
         <v>19</v>
       </c>
       <c r="E512" t="s">
-        <v>1202</v>
+        <v>1137</v>
       </c>
       <c r="F512" t="s">
         <v>1138</v>
       </c>
       <c r="G512" t="s">
-        <v>1139</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="513" spans="1:7">
@@ -18759,13 +18759,13 @@
         <v>25</v>
       </c>
       <c r="E513" t="s">
-        <v>1137</v>
+        <v>1205</v>
       </c>
       <c r="F513" t="s">
         <v>1138</v>
       </c>
       <c r="G513" t="s">
-        <v>1205</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="514" spans="1:7">
@@ -18943,13 +18943,13 @@
         <v>25</v>
       </c>
       <c r="E521" t="s">
-        <v>1222</v>
+        <v>1137</v>
       </c>
       <c r="F521" t="s">
         <v>1138</v>
       </c>
       <c r="G521" t="s">
-        <v>1139</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="522" spans="1:7">
@@ -18966,13 +18966,13 @@
         <v>16</v>
       </c>
       <c r="E522" t="s">
-        <v>1225</v>
+        <v>1137</v>
       </c>
       <c r="F522" t="s">
         <v>1138</v>
       </c>
       <c r="G522" t="s">
-        <v>1139</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="523" spans="1:7">
@@ -18989,13 +18989,13 @@
         <v>34</v>
       </c>
       <c r="E523" t="s">
-        <v>1228</v>
+        <v>1137</v>
       </c>
       <c r="F523" t="s">
         <v>1138</v>
       </c>
       <c r="G523" t="s">
-        <v>1139</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="524" spans="1:7">
@@ -19035,13 +19035,13 @@
         <v>1233</v>
       </c>
       <c r="E525" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F525" t="s">
+        <v>1235</v>
+      </c>
+      <c r="G525" t="s">
         <v>1142</v>
-      </c>
-      <c r="F525" t="s">
-        <v>1234</v>
-      </c>
-      <c r="G525" t="s">
-        <v>1235</v>
       </c>
     </row>
     <row r="526" spans="1:7">
@@ -19058,13 +19058,13 @@
         <v>1233</v>
       </c>
       <c r="E526" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F526" t="s">
+        <v>1235</v>
+      </c>
+      <c r="G526" t="s">
         <v>1142</v>
-      </c>
-      <c r="F526" t="s">
-        <v>1234</v>
-      </c>
-      <c r="G526" t="s">
-        <v>1235</v>
       </c>
     </row>
     <row r="527" spans="1:7">
@@ -19081,13 +19081,13 @@
         <v>1233</v>
       </c>
       <c r="E527" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F527" t="s">
+        <v>1235</v>
+      </c>
+      <c r="G527" t="s">
         <v>1142</v>
-      </c>
-      <c r="F527" t="s">
-        <v>1234</v>
-      </c>
-      <c r="G527" t="s">
-        <v>1235</v>
       </c>
     </row>
     <row r="528" spans="1:7">
@@ -19104,13 +19104,13 @@
         <v>1233</v>
       </c>
       <c r="E528" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F528" t="s">
+        <v>1235</v>
+      </c>
+      <c r="G528" t="s">
         <v>1142</v>
-      </c>
-      <c r="F528" t="s">
-        <v>1234</v>
-      </c>
-      <c r="G528" t="s">
-        <v>1235</v>
       </c>
     </row>
     <row r="529" spans="1:7">
@@ -19127,13 +19127,13 @@
         <v>19</v>
       </c>
       <c r="E529" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F529" t="s">
+        <v>1235</v>
+      </c>
+      <c r="G529" t="s">
         <v>1244</v>
-      </c>
-      <c r="F529" t="s">
-        <v>1234</v>
-      </c>
-      <c r="G529" t="s">
-        <v>1235</v>
       </c>
     </row>
     <row r="530" spans="1:7">
@@ -19150,13 +19150,13 @@
         <v>1233</v>
       </c>
       <c r="E530" t="s">
+        <v>1247</v>
+      </c>
+      <c r="F530" t="s">
+        <v>1235</v>
+      </c>
+      <c r="G530" t="s">
         <v>1142</v>
-      </c>
-      <c r="F530" t="s">
-        <v>1234</v>
-      </c>
-      <c r="G530" t="s">
-        <v>1247</v>
       </c>
     </row>
     <row r="531" spans="1:7">
@@ -19173,13 +19173,13 @@
         <v>1233</v>
       </c>
       <c r="E531" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F531" t="s">
+        <v>1235</v>
+      </c>
+      <c r="G531" t="s">
         <v>1142</v>
-      </c>
-      <c r="F531" t="s">
-        <v>1234</v>
-      </c>
-      <c r="G531" t="s">
-        <v>1235</v>
       </c>
     </row>
     <row r="532" spans="1:7">
@@ -19196,13 +19196,13 @@
         <v>1233</v>
       </c>
       <c r="E532" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F532" t="s">
+        <v>1235</v>
+      </c>
+      <c r="G532" t="s">
         <v>1142</v>
-      </c>
-      <c r="F532" t="s">
-        <v>1234</v>
-      </c>
-      <c r="G532" t="s">
-        <v>1235</v>
       </c>
     </row>
     <row r="533" spans="1:7">
@@ -19219,13 +19219,13 @@
         <v>1233</v>
       </c>
       <c r="E533" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F533" t="s">
+        <v>1235</v>
+      </c>
+      <c r="G533" t="s">
         <v>1142</v>
-      </c>
-      <c r="F533" t="s">
-        <v>1234</v>
-      </c>
-      <c r="G533" t="s">
-        <v>1235</v>
       </c>
     </row>
     <row r="534" spans="1:7">
@@ -19242,13 +19242,13 @@
         <v>1233</v>
       </c>
       <c r="E534" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F534" t="s">
+        <v>1235</v>
+      </c>
+      <c r="G534" t="s">
         <v>1142</v>
-      </c>
-      <c r="F534" t="s">
-        <v>1234</v>
-      </c>
-      <c r="G534" t="s">
-        <v>1235</v>
       </c>
     </row>
     <row r="535" spans="1:7">
@@ -19265,13 +19265,13 @@
         <v>1233</v>
       </c>
       <c r="E535" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F535" t="s">
+        <v>1235</v>
+      </c>
+      <c r="G535" t="s">
         <v>1142</v>
-      </c>
-      <c r="F535" t="s">
-        <v>1234</v>
-      </c>
-      <c r="G535" t="s">
-        <v>1235</v>
       </c>
     </row>
     <row r="536" spans="1:7">
@@ -19288,13 +19288,13 @@
         <v>19</v>
       </c>
       <c r="E536" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F536" t="s">
+        <v>1235</v>
+      </c>
+      <c r="G536" t="s">
         <v>1260</v>
-      </c>
-      <c r="F536" t="s">
-        <v>1234</v>
-      </c>
-      <c r="G536" t="s">
-        <v>1235</v>
       </c>
     </row>
     <row r="537" spans="1:7">
@@ -19311,13 +19311,13 @@
         <v>19</v>
       </c>
       <c r="E537" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F537" t="s">
+        <v>1235</v>
+      </c>
+      <c r="G537" t="s">
         <v>1263</v>
-      </c>
-      <c r="F537" t="s">
-        <v>1234</v>
-      </c>
-      <c r="G537" t="s">
-        <v>1235</v>
       </c>
     </row>
     <row r="538" spans="1:7">
@@ -19334,13 +19334,13 @@
         <v>1233</v>
       </c>
       <c r="E538" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F538" t="s">
+        <v>1235</v>
+      </c>
+      <c r="G538" t="s">
         <v>1142</v>
-      </c>
-      <c r="F538" t="s">
-        <v>1234</v>
-      </c>
-      <c r="G538" t="s">
-        <v>1235</v>
       </c>
     </row>
     <row r="539" spans="1:7">
@@ -19357,13 +19357,13 @@
         <v>1233</v>
       </c>
       <c r="E539" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F539" t="s">
+        <v>1235</v>
+      </c>
+      <c r="G539" t="s">
         <v>1142</v>
-      </c>
-      <c r="F539" t="s">
-        <v>1234</v>
-      </c>
-      <c r="G539" t="s">
-        <v>1235</v>
       </c>
     </row>
     <row r="540" spans="1:7">
@@ -19380,13 +19380,13 @@
         <v>1233</v>
       </c>
       <c r="E540" t="s">
+        <v>1196</v>
+      </c>
+      <c r="F540" t="s">
+        <v>1235</v>
+      </c>
+      <c r="G540" t="s">
         <v>1142</v>
-      </c>
-      <c r="F540" t="s">
-        <v>1234</v>
-      </c>
-      <c r="G540" t="s">
-        <v>1197</v>
       </c>
     </row>
     <row r="541" spans="1:7">
@@ -19403,13 +19403,13 @@
         <v>1233</v>
       </c>
       <c r="E541" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F541" t="s">
+        <v>1235</v>
+      </c>
+      <c r="G541" t="s">
         <v>1142</v>
-      </c>
-      <c r="F541" t="s">
-        <v>1234</v>
-      </c>
-      <c r="G541" t="s">
-        <v>1235</v>
       </c>
     </row>
     <row r="542" spans="1:7">
@@ -19426,13 +19426,13 @@
         <v>1233</v>
       </c>
       <c r="E542" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F542" t="s">
+        <v>1235</v>
+      </c>
+      <c r="G542" t="s">
         <v>1142</v>
-      </c>
-      <c r="F542" t="s">
-        <v>1234</v>
-      </c>
-      <c r="G542" t="s">
-        <v>1235</v>
       </c>
     </row>
     <row r="543" spans="1:7">
@@ -19449,13 +19449,13 @@
         <v>1233</v>
       </c>
       <c r="E543" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F543" t="s">
+        <v>1235</v>
+      </c>
+      <c r="G543" t="s">
         <v>1142</v>
-      </c>
-      <c r="F543" t="s">
-        <v>1234</v>
-      </c>
-      <c r="G543" t="s">
-        <v>1235</v>
       </c>
     </row>
     <row r="544" spans="1:7">
@@ -19472,13 +19472,13 @@
         <v>1233</v>
       </c>
       <c r="E544" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F544" t="s">
+        <v>1235</v>
+      </c>
+      <c r="G544" t="s">
         <v>1142</v>
-      </c>
-      <c r="F544" t="s">
-        <v>1234</v>
-      </c>
-      <c r="G544" t="s">
-        <v>1235</v>
       </c>
     </row>
     <row r="545" spans="1:7">
@@ -19495,13 +19495,13 @@
         <v>16</v>
       </c>
       <c r="E545" t="s">
+        <v>1280</v>
+      </c>
+      <c r="F545" t="s">
+        <v>1235</v>
+      </c>
+      <c r="G545" t="s">
         <v>1142</v>
-      </c>
-      <c r="F545" t="s">
-        <v>1234</v>
-      </c>
-      <c r="G545" t="s">
-        <v>1280</v>
       </c>
     </row>
     <row r="546" spans="1:7">
@@ -19518,13 +19518,13 @@
         <v>1233</v>
       </c>
       <c r="E546" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F546" t="s">
+        <v>1235</v>
+      </c>
+      <c r="G546" t="s">
         <v>1142</v>
-      </c>
-      <c r="F546" t="s">
-        <v>1234</v>
-      </c>
-      <c r="G546" t="s">
-        <v>1235</v>
       </c>
     </row>
     <row r="547" spans="1:7">
@@ -19541,13 +19541,13 @@
         <v>19</v>
       </c>
       <c r="E547" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F547" t="s">
+        <v>1235</v>
+      </c>
+      <c r="G547" t="s">
         <v>1142</v>
-      </c>
-      <c r="F547" t="s">
-        <v>1234</v>
-      </c>
-      <c r="G547" t="s">
-        <v>1235</v>
       </c>
     </row>
     <row r="548" spans="1:7">
@@ -19587,13 +19587,13 @@
         <v>1233</v>
       </c>
       <c r="E549" t="s">
-        <v>1292</v>
+        <v>1287</v>
       </c>
       <c r="F549" t="s">
         <v>1288</v>
       </c>
       <c r="G549" t="s">
-        <v>1289</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="550" spans="1:7">
@@ -19610,13 +19610,13 @@
         <v>1233</v>
       </c>
       <c r="E550" t="s">
-        <v>1295</v>
+        <v>1287</v>
       </c>
       <c r="F550" t="s">
         <v>1288</v>
       </c>
       <c r="G550" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="551" spans="1:7">
@@ -19702,13 +19702,13 @@
         <v>1233</v>
       </c>
       <c r="E554" t="s">
-        <v>1287</v>
+        <v>1304</v>
       </c>
       <c r="F554" t="s">
         <v>1288</v>
       </c>
       <c r="G554" t="s">
-        <v>1304</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="555" spans="1:7">
@@ -19840,13 +19840,13 @@
         <v>1233</v>
       </c>
       <c r="E560" t="s">
-        <v>1319</v>
+        <v>1287</v>
       </c>
       <c r="F560" t="s">
         <v>1288</v>
       </c>
       <c r="G560" t="s">
-        <v>1289</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="561" spans="1:7">
@@ -19863,13 +19863,13 @@
         <v>1233</v>
       </c>
       <c r="E561" t="s">
-        <v>1319</v>
+        <v>1287</v>
       </c>
       <c r="F561" t="s">
         <v>1288</v>
       </c>
       <c r="G561" t="s">
-        <v>1289</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="562" spans="1:7">
@@ -19909,13 +19909,13 @@
         <v>19</v>
       </c>
       <c r="E563" t="s">
-        <v>1287</v>
+        <v>1326</v>
       </c>
       <c r="F563" t="s">
         <v>1288</v>
       </c>
       <c r="G563" t="s">
-        <v>1326</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="564" spans="1:7">
@@ -20139,13 +20139,13 @@
         <v>1233</v>
       </c>
       <c r="E573" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F573" t="s">
         <v>1349</v>
       </c>
-      <c r="F573" t="s">
+      <c r="G573" t="s">
         <v>1350</v>
-      </c>
-      <c r="G573" t="s">
-        <v>1235</v>
       </c>
     </row>
     <row r="574" spans="1:7">
@@ -20162,13 +20162,13 @@
         <v>1233</v>
       </c>
       <c r="E574" t="s">
+        <v>1353</v>
+      </c>
+      <c r="F574" t="s">
         <v>1349</v>
       </c>
-      <c r="F574" t="s">
+      <c r="G574" t="s">
         <v>1350</v>
-      </c>
-      <c r="G574" t="s">
-        <v>1353</v>
       </c>
     </row>
     <row r="575" spans="1:7">
@@ -20185,13 +20185,13 @@
         <v>1233</v>
       </c>
       <c r="E575" t="s">
+        <v>1353</v>
+      </c>
+      <c r="F575" t="s">
         <v>1349</v>
       </c>
-      <c r="F575" t="s">
+      <c r="G575" t="s">
         <v>1350</v>
-      </c>
-      <c r="G575" t="s">
-        <v>1353</v>
       </c>
     </row>
     <row r="576" spans="1:7">
@@ -20208,13 +20208,13 @@
         <v>1233</v>
       </c>
       <c r="E576" t="s">
+        <v>1353</v>
+      </c>
+      <c r="F576" t="s">
         <v>1349</v>
       </c>
-      <c r="F576" t="s">
+      <c r="G576" t="s">
         <v>1350</v>
-      </c>
-      <c r="G576" t="s">
-        <v>1353</v>
       </c>
     </row>
     <row r="577" spans="1:7">
@@ -20231,13 +20231,13 @@
         <v>1233</v>
       </c>
       <c r="E577" t="s">
+        <v>1287</v>
+      </c>
+      <c r="F577" t="s">
         <v>1349</v>
       </c>
-      <c r="F577" t="s">
+      <c r="G577" t="s">
         <v>1350</v>
-      </c>
-      <c r="G577" t="s">
-        <v>1289</v>
       </c>
     </row>
     <row r="578" spans="1:7">
@@ -20254,13 +20254,13 @@
         <v>1233</v>
       </c>
       <c r="E578" t="s">
+        <v>1353</v>
+      </c>
+      <c r="F578" t="s">
+        <v>1349</v>
+      </c>
+      <c r="G578" t="s">
         <v>1362</v>
-      </c>
-      <c r="F578" t="s">
-        <v>1350</v>
-      </c>
-      <c r="G578" t="s">
-        <v>1353</v>
       </c>
     </row>
     <row r="579" spans="1:7">
@@ -20280,7 +20280,7 @@
         <v>1365</v>
       </c>
       <c r="F579" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="G579" t="s">
         <v>1366</v>
@@ -20300,13 +20300,13 @@
         <v>1233</v>
       </c>
       <c r="E580" t="s">
+        <v>1353</v>
+      </c>
+      <c r="F580" t="s">
+        <v>1349</v>
+      </c>
+      <c r="G580" t="s">
         <v>1369</v>
-      </c>
-      <c r="F580" t="s">
-        <v>1350</v>
-      </c>
-      <c r="G580" t="s">
-        <v>1353</v>
       </c>
     </row>
     <row r="581" spans="1:7">
@@ -20323,13 +20323,13 @@
         <v>19</v>
       </c>
       <c r="E581" t="s">
+        <v>1353</v>
+      </c>
+      <c r="F581" t="s">
+        <v>1349</v>
+      </c>
+      <c r="G581" t="s">
         <v>1372</v>
-      </c>
-      <c r="F581" t="s">
-        <v>1350</v>
-      </c>
-      <c r="G581" t="s">
-        <v>1353</v>
       </c>
     </row>
     <row r="582" spans="1:7">
@@ -20346,13 +20346,13 @@
         <v>19</v>
       </c>
       <c r="E582" t="s">
+        <v>1353</v>
+      </c>
+      <c r="F582" t="s">
         <v>1349</v>
       </c>
-      <c r="F582" t="s">
+      <c r="G582" t="s">
         <v>1350</v>
-      </c>
-      <c r="G582" t="s">
-        <v>1353</v>
       </c>
     </row>
     <row r="583" spans="1:7">
@@ -20372,7 +20372,7 @@
         <v>1377</v>
       </c>
       <c r="F583" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="G583" t="s">
         <v>1378</v>
@@ -20395,7 +20395,7 @@
         <v>1381</v>
       </c>
       <c r="F584" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="G584" t="s">
         <v>1382</v>
@@ -20415,13 +20415,13 @@
         <v>1233</v>
       </c>
       <c r="E585" t="s">
+        <v>1353</v>
+      </c>
+      <c r="F585" t="s">
         <v>1349</v>
       </c>
-      <c r="F585" t="s">
+      <c r="G585" t="s">
         <v>1350</v>
-      </c>
-      <c r="G585" t="s">
-        <v>1353</v>
       </c>
     </row>
     <row r="586" spans="1:7">
@@ -20441,7 +20441,7 @@
         <v>1387</v>
       </c>
       <c r="F586" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="G586" t="s">
         <v>1388</v>
@@ -20461,13 +20461,13 @@
         <v>16</v>
       </c>
       <c r="E587" t="s">
+        <v>1353</v>
+      </c>
+      <c r="F587" t="s">
+        <v>1349</v>
+      </c>
+      <c r="G587" t="s">
         <v>1391</v>
-      </c>
-      <c r="F587" t="s">
-        <v>1350</v>
-      </c>
-      <c r="G587" t="s">
-        <v>1353</v>
       </c>
     </row>
     <row r="588" spans="1:7">
@@ -20484,13 +20484,13 @@
         <v>1233</v>
       </c>
       <c r="E588" t="s">
+        <v>1353</v>
+      </c>
+      <c r="F588" t="s">
+        <v>1349</v>
+      </c>
+      <c r="G588" t="s">
         <v>1394</v>
-      </c>
-      <c r="F588" t="s">
-        <v>1350</v>
-      </c>
-      <c r="G588" t="s">
-        <v>1353</v>
       </c>
     </row>
     <row r="589" spans="1:7">
@@ -20507,13 +20507,13 @@
         <v>1233</v>
       </c>
       <c r="E589" t="s">
+        <v>1353</v>
+      </c>
+      <c r="F589" t="s">
         <v>1349</v>
       </c>
-      <c r="F589" t="s">
+      <c r="G589" t="s">
         <v>1350</v>
-      </c>
-      <c r="G589" t="s">
-        <v>1353</v>
       </c>
     </row>
     <row r="590" spans="1:7">
@@ -20530,13 +20530,13 @@
         <v>34</v>
       </c>
       <c r="E590" t="s">
+        <v>1353</v>
+      </c>
+      <c r="F590" t="s">
         <v>1349</v>
       </c>
-      <c r="F590" t="s">
+      <c r="G590" t="s">
         <v>1350</v>
-      </c>
-      <c r="G590" t="s">
-        <v>1353</v>
       </c>
     </row>
     <row r="591" spans="1:7">
@@ -20553,13 +20553,13 @@
         <v>19</v>
       </c>
       <c r="E591" t="s">
+        <v>1353</v>
+      </c>
+      <c r="F591" t="s">
         <v>1349</v>
       </c>
-      <c r="F591" t="s">
+      <c r="G591" t="s">
         <v>1350</v>
-      </c>
-      <c r="G591" t="s">
-        <v>1353</v>
       </c>
     </row>
     <row r="592" spans="1:7">
@@ -20576,13 +20576,13 @@
         <v>1233</v>
       </c>
       <c r="E592" t="s">
+        <v>1403</v>
+      </c>
+      <c r="F592" t="s">
         <v>1349</v>
       </c>
-      <c r="F592" t="s">
+      <c r="G592" t="s">
         <v>1350</v>
-      </c>
-      <c r="G592" t="s">
-        <v>1403</v>
       </c>
     </row>
     <row r="593" spans="1:7">
@@ -20599,13 +20599,13 @@
         <v>16</v>
       </c>
       <c r="E593" t="s">
+        <v>1353</v>
+      </c>
+      <c r="F593" t="s">
         <v>1349</v>
       </c>
-      <c r="F593" t="s">
+      <c r="G593" t="s">
         <v>1350</v>
-      </c>
-      <c r="G593" t="s">
-        <v>1353</v>
       </c>
     </row>
     <row r="594" spans="1:7">
@@ -20622,13 +20622,13 @@
         <v>1233</v>
       </c>
       <c r="E594" t="s">
+        <v>1353</v>
+      </c>
+      <c r="F594" t="s">
         <v>1349</v>
       </c>
-      <c r="F594" t="s">
+      <c r="G594" t="s">
         <v>1350</v>
-      </c>
-      <c r="G594" t="s">
-        <v>1353</v>
       </c>
     </row>
     <row r="595" spans="1:7">
@@ -20645,13 +20645,13 @@
         <v>1233</v>
       </c>
       <c r="E595" t="s">
+        <v>1353</v>
+      </c>
+      <c r="F595" t="s">
         <v>1349</v>
       </c>
-      <c r="F595" t="s">
+      <c r="G595" t="s">
         <v>1350</v>
-      </c>
-      <c r="G595" t="s">
-        <v>1353</v>
       </c>
     </row>
     <row r="596" spans="1:7">
@@ -20668,13 +20668,13 @@
         <v>1233</v>
       </c>
       <c r="E596" t="s">
+        <v>1353</v>
+      </c>
+      <c r="F596" t="s">
         <v>1349</v>
       </c>
-      <c r="F596" t="s">
+      <c r="G596" t="s">
         <v>1350</v>
-      </c>
-      <c r="G596" t="s">
-        <v>1353</v>
       </c>
     </row>
     <row r="597" spans="1:7">
@@ -20875,13 +20875,13 @@
         <v>34</v>
       </c>
       <c r="E605" t="s">
-        <v>1441</v>
+        <v>1414</v>
       </c>
       <c r="F605" t="s">
         <v>1415</v>
       </c>
       <c r="G605" t="s">
-        <v>1416</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="606" spans="1:7">
@@ -20967,13 +20967,13 @@
         <v>1233</v>
       </c>
       <c r="E609" t="s">
-        <v>1452</v>
+        <v>1391</v>
       </c>
       <c r="F609" t="s">
         <v>1415</v>
       </c>
       <c r="G609" t="s">
-        <v>1391</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="610" spans="1:7">
@@ -21013,13 +21013,13 @@
         <v>34</v>
       </c>
       <c r="E611" t="s">
-        <v>1419</v>
+        <v>1457</v>
       </c>
       <c r="F611" t="s">
         <v>1415</v>
       </c>
       <c r="G611" t="s">
-        <v>1457</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="612" spans="1:7">
@@ -21036,13 +21036,13 @@
         <v>19</v>
       </c>
       <c r="E612" t="s">
-        <v>1460</v>
+        <v>1414</v>
       </c>
       <c r="F612" t="s">
         <v>1415</v>
       </c>
       <c r="G612" t="s">
-        <v>1416</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="613" spans="1:7">
@@ -21082,13 +21082,13 @@
         <v>1233</v>
       </c>
       <c r="E614" t="s">
-        <v>1465</v>
+        <v>1414</v>
       </c>
       <c r="F614" t="s">
         <v>1415</v>
       </c>
       <c r="G614" t="s">
-        <v>1416</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="615" spans="1:7">
@@ -21404,13 +21404,13 @@
         <v>1233</v>
       </c>
       <c r="E628" t="s">
-        <v>1484</v>
+        <v>1499</v>
       </c>
       <c r="F628" t="s">
         <v>1485</v>
       </c>
       <c r="G628" t="s">
-        <v>1499</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="629" spans="1:7">
@@ -21427,13 +21427,13 @@
         <v>34</v>
       </c>
       <c r="E629" t="s">
-        <v>1502</v>
+        <v>1484</v>
       </c>
       <c r="F629" t="s">
         <v>1485</v>
       </c>
       <c r="G629" t="s">
-        <v>1486</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="630" spans="1:7">
@@ -21496,13 +21496,13 @@
         <v>34</v>
       </c>
       <c r="E632" t="s">
-        <v>1502</v>
+        <v>1509</v>
       </c>
       <c r="F632" t="s">
         <v>1485</v>
       </c>
       <c r="G632" t="s">
-        <v>1509</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="633" spans="1:7">
@@ -21588,13 +21588,13 @@
         <v>1233</v>
       </c>
       <c r="E636" t="s">
-        <v>1522</v>
+        <v>1484</v>
       </c>
       <c r="F636" t="s">
         <v>1485</v>
       </c>
       <c r="G636" t="s">
-        <v>1486</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="637" spans="1:7">
@@ -21726,13 +21726,13 @@
         <v>19</v>
       </c>
       <c r="E642" t="s">
-        <v>1539</v>
+        <v>1484</v>
       </c>
       <c r="F642" t="s">
         <v>1485</v>
       </c>
       <c r="G642" t="s">
-        <v>1486</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="643" spans="1:7">
@@ -21749,13 +21749,13 @@
         <v>19</v>
       </c>
       <c r="E643" t="s">
-        <v>1542</v>
+        <v>1484</v>
       </c>
       <c r="F643" t="s">
         <v>1485</v>
       </c>
       <c r="G643" t="s">
-        <v>1486</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="644" spans="1:7">
@@ -21818,13 +21818,13 @@
         <v>34</v>
       </c>
       <c r="E646" t="s">
-        <v>1549</v>
+        <v>1484</v>
       </c>
       <c r="F646" t="s">
         <v>1485</v>
       </c>
       <c r="G646" t="s">
-        <v>1486</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="647" spans="1:7">
@@ -21933,13 +21933,13 @@
         <v>34</v>
       </c>
       <c r="E651" t="s">
-        <v>1556</v>
+        <v>1565</v>
       </c>
       <c r="F651" t="s">
         <v>1557</v>
       </c>
       <c r="G651" t="s">
-        <v>1565</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="652" spans="1:7">
@@ -22002,13 +22002,13 @@
         <v>19</v>
       </c>
       <c r="E654" t="s">
-        <v>1542</v>
+        <v>1484</v>
       </c>
       <c r="F654" t="s">
         <v>1557</v>
       </c>
       <c r="G654" t="s">
-        <v>1486</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="655" spans="1:7">
@@ -22117,13 +22117,13 @@
         <v>34</v>
       </c>
       <c r="E659" t="s">
-        <v>1522</v>
+        <v>1588</v>
       </c>
       <c r="F659" t="s">
         <v>1557</v>
       </c>
       <c r="G659" t="s">
-        <v>1588</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="660" spans="1:7">
@@ -22186,13 +22186,13 @@
         <v>34</v>
       </c>
       <c r="E662" t="s">
-        <v>1568</v>
+        <v>1562</v>
       </c>
       <c r="F662" t="s">
         <v>1557</v>
       </c>
       <c r="G662" t="s">
-        <v>1561</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="663" spans="1:7">
@@ -22232,13 +22232,13 @@
         <v>19</v>
       </c>
       <c r="E664" t="s">
-        <v>1542</v>
+        <v>1603</v>
       </c>
       <c r="F664" t="s">
         <v>1557</v>
       </c>
       <c r="G664" t="s">
-        <v>1603</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="665" spans="1:7">
@@ -22255,13 +22255,13 @@
         <v>1233</v>
       </c>
       <c r="E665" t="s">
-        <v>1606</v>
+        <v>1568</v>
       </c>
       <c r="F665" t="s">
         <v>1557</v>
       </c>
       <c r="G665" t="s">
-        <v>1569</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="666" spans="1:7">
@@ -22278,13 +22278,13 @@
         <v>34</v>
       </c>
       <c r="E666" t="s">
-        <v>1606</v>
+        <v>1556</v>
       </c>
       <c r="F666" t="s">
         <v>1557</v>
       </c>
       <c r="G666" t="s">
-        <v>1558</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="667" spans="1:7">
@@ -22347,13 +22347,13 @@
         <v>19</v>
       </c>
       <c r="E669" t="s">
-        <v>1542</v>
+        <v>1588</v>
       </c>
       <c r="F669" t="s">
         <v>1557</v>
       </c>
       <c r="G669" t="s">
-        <v>1588</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="670" spans="1:7">
@@ -22393,13 +22393,13 @@
         <v>34</v>
       </c>
       <c r="E671" t="s">
-        <v>1556</v>
+        <v>1621</v>
       </c>
       <c r="F671" t="s">
         <v>1557</v>
       </c>
       <c r="G671" t="s">
-        <v>1621</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="672" spans="1:7">
@@ -22462,13 +22462,13 @@
         <v>19</v>
       </c>
       <c r="E674" t="s">
-        <v>1542</v>
+        <v>1591</v>
       </c>
       <c r="F674" t="s">
         <v>1557</v>
       </c>
       <c r="G674" t="s">
-        <v>1592</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="675" spans="1:7">
@@ -22485,13 +22485,13 @@
         <v>34</v>
       </c>
       <c r="E675" t="s">
-        <v>1556</v>
+        <v>1565</v>
       </c>
       <c r="F675" t="s">
         <v>1557</v>
       </c>
       <c r="G675" t="s">
-        <v>1565</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="676" spans="1:7">
@@ -22508,13 +22508,13 @@
         <v>19</v>
       </c>
       <c r="E676" t="s">
-        <v>1632</v>
+        <v>1568</v>
       </c>
       <c r="F676" t="s">
         <v>1557</v>
       </c>
       <c r="G676" t="s">
-        <v>1569</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="677" spans="1:7">
@@ -22807,13 +22807,13 @@
         <v>34</v>
       </c>
       <c r="E689" t="s">
-        <v>1650</v>
+        <v>1666</v>
       </c>
       <c r="F689" t="s">
         <v>1646</v>
       </c>
       <c r="G689" t="s">
-        <v>1666</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="690" spans="1:7">
@@ -22876,13 +22876,13 @@
         <v>19</v>
       </c>
       <c r="E692" t="s">
-        <v>1675</v>
+        <v>1568</v>
       </c>
       <c r="F692" t="s">
         <v>1646</v>
       </c>
       <c r="G692" t="s">
-        <v>1569</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="693" spans="1:7">
@@ -23129,13 +23129,13 @@
         <v>34</v>
       </c>
       <c r="E703" t="s">
-        <v>1712</v>
+        <v>1702</v>
       </c>
       <c r="F703" t="s">
         <v>1646</v>
       </c>
       <c r="G703" t="s">
-        <v>1703</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="704" spans="1:7">
@@ -23175,13 +23175,13 @@
         <v>19</v>
       </c>
       <c r="E705" t="s">
-        <v>1717</v>
+        <v>1696</v>
       </c>
       <c r="F705" t="s">
         <v>1646</v>
       </c>
       <c r="G705" t="s">
-        <v>1697</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="706" spans="1:7">
@@ -23221,13 +23221,13 @@
         <v>19</v>
       </c>
       <c r="E707" t="s">
-        <v>1654</v>
+        <v>1696</v>
       </c>
       <c r="F707" t="s">
         <v>1646</v>
       </c>
       <c r="G707" t="s">
-        <v>1697</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="708" spans="1:7">
@@ -23244,13 +23244,13 @@
         <v>34</v>
       </c>
       <c r="E708" t="s">
-        <v>1724</v>
+        <v>1650</v>
       </c>
       <c r="F708" t="s">
         <v>1646</v>
       </c>
       <c r="G708" t="s">
-        <v>1651</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="709" spans="1:7">
@@ -23313,13 +23313,13 @@
         <v>1233</v>
       </c>
       <c r="E711" t="s">
-        <v>1654</v>
+        <v>1696</v>
       </c>
       <c r="F711" t="s">
         <v>1646</v>
       </c>
       <c r="G711" t="s">
-        <v>1697</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="712" spans="1:7">
@@ -23405,13 +23405,13 @@
         <v>34</v>
       </c>
       <c r="E715" t="s">
-        <v>1692</v>
+        <v>1696</v>
       </c>
       <c r="F715" t="s">
         <v>1646</v>
       </c>
       <c r="G715" t="s">
-        <v>1697</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="716" spans="1:7">
@@ -23497,13 +23497,13 @@
         <v>1233</v>
       </c>
       <c r="E719" t="s">
-        <v>1752</v>
+        <v>1747</v>
       </c>
       <c r="F719" t="s">
         <v>1748</v>
       </c>
       <c r="G719" t="s">
-        <v>1749</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="720" spans="1:7">
@@ -23520,13 +23520,13 @@
         <v>1233</v>
       </c>
       <c r="E720" t="s">
-        <v>1752</v>
+        <v>1747</v>
       </c>
       <c r="F720" t="s">
         <v>1748</v>
       </c>
       <c r="G720" t="s">
-        <v>1749</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="721" spans="1:7">
@@ -23543,13 +23543,13 @@
         <v>1233</v>
       </c>
       <c r="E721" t="s">
-        <v>1752</v>
+        <v>1747</v>
       </c>
       <c r="F721" t="s">
         <v>1748</v>
       </c>
       <c r="G721" t="s">
-        <v>1749</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="722" spans="1:7">
@@ -23566,13 +23566,13 @@
         <v>1233</v>
       </c>
       <c r="E722" t="s">
-        <v>1752</v>
+        <v>1747</v>
       </c>
       <c r="F722" t="s">
         <v>1748</v>
       </c>
       <c r="G722" t="s">
-        <v>1749</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="723" spans="1:7">
@@ -23589,13 +23589,13 @@
         <v>1233</v>
       </c>
       <c r="E723" t="s">
-        <v>1752</v>
+        <v>1747</v>
       </c>
       <c r="F723" t="s">
         <v>1748</v>
       </c>
       <c r="G723" t="s">
-        <v>1749</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="724" spans="1:7">
@@ -23612,13 +23612,13 @@
         <v>19</v>
       </c>
       <c r="E724" t="s">
-        <v>1752</v>
+        <v>1747</v>
       </c>
       <c r="F724" t="s">
         <v>1748</v>
       </c>
       <c r="G724" t="s">
-        <v>1749</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="725" spans="1:7">
@@ -23681,13 +23681,13 @@
         <v>1233</v>
       </c>
       <c r="E727" t="s">
-        <v>1752</v>
+        <v>1747</v>
       </c>
       <c r="F727" t="s">
         <v>1748</v>
       </c>
       <c r="G727" t="s">
-        <v>1749</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="728" spans="1:7">
@@ -23704,13 +23704,13 @@
         <v>1233</v>
       </c>
       <c r="E728" t="s">
-        <v>1752</v>
+        <v>1747</v>
       </c>
       <c r="F728" t="s">
         <v>1748</v>
       </c>
       <c r="G728" t="s">
-        <v>1749</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="729" spans="1:7">
@@ -23750,13 +23750,13 @@
         <v>16</v>
       </c>
       <c r="E730" t="s">
-        <v>1752</v>
+        <v>1747</v>
       </c>
       <c r="F730" t="s">
         <v>1748</v>
       </c>
       <c r="G730" t="s">
-        <v>1749</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="731" spans="1:7">
@@ -23819,13 +23819,13 @@
         <v>34</v>
       </c>
       <c r="E733" t="s">
-        <v>1789</v>
+        <v>1747</v>
       </c>
       <c r="F733" t="s">
         <v>1748</v>
       </c>
       <c r="G733" t="s">
-        <v>1749</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="734" spans="1:7">
@@ -23865,13 +23865,13 @@
         <v>1233</v>
       </c>
       <c r="E735" t="s">
-        <v>1752</v>
+        <v>1747</v>
       </c>
       <c r="F735" t="s">
         <v>1748</v>
       </c>
       <c r="G735" t="s">
-        <v>1749</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="736" spans="1:7">
@@ -23888,13 +23888,13 @@
         <v>1233</v>
       </c>
       <c r="E736" t="s">
-        <v>1798</v>
+        <v>1747</v>
       </c>
       <c r="F736" t="s">
         <v>1748</v>
       </c>
       <c r="G736" t="s">
-        <v>1749</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="737" spans="1:7">
@@ -23911,13 +23911,13 @@
         <v>19</v>
       </c>
       <c r="E737" t="s">
-        <v>1752</v>
+        <v>1747</v>
       </c>
       <c r="F737" t="s">
         <v>1748</v>
       </c>
       <c r="G737" t="s">
-        <v>1749</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="738" spans="1:7">
@@ -23934,13 +23934,13 @@
         <v>19</v>
       </c>
       <c r="E738" t="s">
-        <v>1803</v>
+        <v>1654</v>
       </c>
       <c r="F738" t="s">
         <v>1748</v>
       </c>
       <c r="G738" t="s">
-        <v>1655</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="739" spans="1:7">
@@ -23957,13 +23957,13 @@
         <v>1233</v>
       </c>
       <c r="E739" t="s">
-        <v>1752</v>
+        <v>1747</v>
       </c>
       <c r="F739" t="s">
         <v>1748</v>
       </c>
       <c r="G739" t="s">
-        <v>1749</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="740" spans="1:7">
@@ -23980,13 +23980,13 @@
         <v>1233</v>
       </c>
       <c r="E740" t="s">
-        <v>1752</v>
+        <v>1747</v>
       </c>
       <c r="F740" t="s">
         <v>1748</v>
       </c>
       <c r="G740" t="s">
-        <v>1749</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="741" spans="1:7">
@@ -24026,13 +24026,13 @@
         <v>19</v>
       </c>
       <c r="E742" t="s">
-        <v>1814</v>
+        <v>1747</v>
       </c>
       <c r="F742" t="s">
         <v>1748</v>
       </c>
       <c r="G742" t="s">
-        <v>1749</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="743" spans="1:7">
@@ -24049,13 +24049,13 @@
         <v>1233</v>
       </c>
       <c r="E743" t="s">
-        <v>1752</v>
+        <v>1747</v>
       </c>
       <c r="F743" t="s">
         <v>1748</v>
       </c>
       <c r="G743" t="s">
-        <v>1749</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="744" spans="1:7">
@@ -24095,13 +24095,13 @@
         <v>34</v>
       </c>
       <c r="E745" t="s">
-        <v>1821</v>
+        <v>1747</v>
       </c>
       <c r="F745" t="s">
         <v>1748</v>
       </c>
       <c r="G745" t="s">
-        <v>1749</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="746" spans="1:7">
@@ -24118,13 +24118,13 @@
         <v>1233</v>
       </c>
       <c r="E746" t="s">
-        <v>1752</v>
+        <v>1747</v>
       </c>
       <c r="F746" t="s">
         <v>1748</v>
       </c>
       <c r="G746" t="s">
-        <v>1749</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="747" spans="1:7">
@@ -24141,13 +24141,13 @@
         <v>1233</v>
       </c>
       <c r="E747" t="s">
-        <v>1752</v>
+        <v>1747</v>
       </c>
       <c r="F747" t="s">
         <v>1748</v>
       </c>
       <c r="G747" t="s">
-        <v>1749</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="748" spans="1:7">
@@ -24164,13 +24164,13 @@
         <v>1233</v>
       </c>
       <c r="E748" t="s">
-        <v>1752</v>
+        <v>1747</v>
       </c>
       <c r="F748" t="s">
         <v>1748</v>
       </c>
       <c r="G748" t="s">
-        <v>1749</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="749" spans="1:7">
@@ -24187,13 +24187,13 @@
         <v>1233</v>
       </c>
       <c r="E749" t="s">
-        <v>1752</v>
+        <v>1747</v>
       </c>
       <c r="F749" t="s">
         <v>1748</v>
       </c>
       <c r="G749" t="s">
-        <v>1749</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="750" spans="1:7">
@@ -24394,13 +24394,13 @@
         <v>34</v>
       </c>
       <c r="E758" t="s">
-        <v>1832</v>
+        <v>1837</v>
       </c>
       <c r="F758" t="s">
         <v>1833</v>
       </c>
       <c r="G758" t="s">
-        <v>1838</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="759" spans="1:7">
@@ -24417,13 +24417,13 @@
         <v>19</v>
       </c>
       <c r="E759" t="s">
-        <v>1798</v>
+        <v>1841</v>
       </c>
       <c r="F759" t="s">
         <v>1833</v>
       </c>
       <c r="G759" t="s">
-        <v>1842</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="760" spans="1:7">
@@ -24486,13 +24486,13 @@
         <v>34</v>
       </c>
       <c r="E762" t="s">
-        <v>1798</v>
+        <v>1863</v>
       </c>
       <c r="F762" t="s">
         <v>1833</v>
       </c>
       <c r="G762" t="s">
-        <v>1863</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="763" spans="1:7">
@@ -24555,13 +24555,13 @@
         <v>34</v>
       </c>
       <c r="E765" t="s">
-        <v>1841</v>
+        <v>1832</v>
       </c>
       <c r="F765" t="s">
         <v>1833</v>
       </c>
       <c r="G765" t="s">
-        <v>1834</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="766" spans="1:7">
@@ -24578,13 +24578,13 @@
         <v>34</v>
       </c>
       <c r="E766" t="s">
-        <v>1874</v>
+        <v>1863</v>
       </c>
       <c r="F766" t="s">
         <v>1833</v>
       </c>
       <c r="G766" t="s">
-        <v>1863</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="767" spans="1:7">
@@ -24831,13 +24831,13 @@
         <v>1233</v>
       </c>
       <c r="E777" t="s">
-        <v>1906</v>
+        <v>1901</v>
       </c>
       <c r="F777" t="s">
         <v>1902</v>
       </c>
       <c r="G777" t="s">
-        <v>1903</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="778" spans="1:7">
@@ -24900,13 +24900,13 @@
         <v>1233</v>
       </c>
       <c r="E780" t="s">
-        <v>1906</v>
+        <v>1901</v>
       </c>
       <c r="F780" t="s">
         <v>1902</v>
       </c>
       <c r="G780" t="s">
-        <v>1903</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="781" spans="1:7">
@@ -24923,13 +24923,13 @@
         <v>1233</v>
       </c>
       <c r="E781" t="s">
-        <v>1906</v>
+        <v>1901</v>
       </c>
       <c r="F781" t="s">
         <v>1902</v>
       </c>
       <c r="G781" t="s">
-        <v>1903</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="782" spans="1:7">
@@ -24946,13 +24946,13 @@
         <v>1233</v>
       </c>
       <c r="E782" t="s">
-        <v>1921</v>
+        <v>1901</v>
       </c>
       <c r="F782" t="s">
         <v>1902</v>
       </c>
       <c r="G782" t="s">
-        <v>1903</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="783" spans="1:7">
@@ -24969,13 +24969,13 @@
         <v>1233</v>
       </c>
       <c r="E783" t="s">
-        <v>1906</v>
+        <v>1901</v>
       </c>
       <c r="F783" t="s">
         <v>1902</v>
       </c>
       <c r="G783" t="s">
-        <v>1903</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="784" spans="1:7">
@@ -24992,13 +24992,13 @@
         <v>1233</v>
       </c>
       <c r="E784" t="s">
-        <v>1906</v>
+        <v>1901</v>
       </c>
       <c r="F784" t="s">
         <v>1902</v>
       </c>
       <c r="G784" t="s">
-        <v>1903</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="785" spans="1:7">
@@ -25015,13 +25015,13 @@
         <v>1233</v>
       </c>
       <c r="E785" t="s">
-        <v>1906</v>
+        <v>1901</v>
       </c>
       <c r="F785" t="s">
         <v>1902</v>
       </c>
       <c r="G785" t="s">
-        <v>1903</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="786" spans="1:7">
@@ -25038,13 +25038,13 @@
         <v>1233</v>
       </c>
       <c r="E786" t="s">
-        <v>1906</v>
+        <v>1901</v>
       </c>
       <c r="F786" t="s">
         <v>1902</v>
       </c>
       <c r="G786" t="s">
-        <v>1903</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="787" spans="1:7">
@@ -25061,13 +25061,13 @@
         <v>1233</v>
       </c>
       <c r="E787" t="s">
-        <v>1906</v>
+        <v>1901</v>
       </c>
       <c r="F787" t="s">
         <v>1902</v>
       </c>
       <c r="G787" t="s">
-        <v>1903</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="788" spans="1:7">
@@ -25084,13 +25084,13 @@
         <v>1233</v>
       </c>
       <c r="E788" t="s">
-        <v>1906</v>
+        <v>1901</v>
       </c>
       <c r="F788" t="s">
         <v>1902</v>
       </c>
       <c r="G788" t="s">
-        <v>1903</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="789" spans="1:7">
@@ -25107,13 +25107,13 @@
         <v>34</v>
       </c>
       <c r="E789" t="s">
-        <v>1901</v>
+        <v>1936</v>
       </c>
       <c r="F789" t="s">
         <v>1902</v>
       </c>
       <c r="G789" t="s">
-        <v>1936</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="790" spans="1:7">
@@ -25130,13 +25130,13 @@
         <v>1233</v>
       </c>
       <c r="E790" t="s">
-        <v>1906</v>
+        <v>1901</v>
       </c>
       <c r="F790" t="s">
         <v>1902</v>
       </c>
       <c r="G790" t="s">
-        <v>1903</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="791" spans="1:7">
@@ -25153,13 +25153,13 @@
         <v>34</v>
       </c>
       <c r="E791" t="s">
-        <v>1921</v>
+        <v>1941</v>
       </c>
       <c r="F791" t="s">
         <v>1902</v>
       </c>
       <c r="G791" t="s">
-        <v>1941</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="792" spans="1:7">
@@ -25176,13 +25176,13 @@
         <v>34</v>
       </c>
       <c r="E792" t="s">
-        <v>1944</v>
+        <v>1936</v>
       </c>
       <c r="F792" t="s">
         <v>1902</v>
       </c>
       <c r="G792" t="s">
-        <v>1936</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="793" spans="1:7">
@@ -25199,13 +25199,13 @@
         <v>1233</v>
       </c>
       <c r="E793" t="s">
-        <v>1906</v>
+        <v>1901</v>
       </c>
       <c r="F793" t="s">
         <v>1902</v>
       </c>
       <c r="G793" t="s">
-        <v>1903</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="794" spans="1:7">
@@ -25222,13 +25222,13 @@
         <v>34</v>
       </c>
       <c r="E794" t="s">
-        <v>1906</v>
+        <v>1949</v>
       </c>
       <c r="F794" t="s">
         <v>1902</v>
       </c>
       <c r="G794" t="s">
-        <v>1949</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="795" spans="1:7">
@@ -25245,13 +25245,13 @@
         <v>34</v>
       </c>
       <c r="E795" t="s">
-        <v>1952</v>
+        <v>1901</v>
       </c>
       <c r="F795" t="s">
         <v>1902</v>
       </c>
       <c r="G795" t="s">
-        <v>1903</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="796" spans="1:7">
@@ -25268,13 +25268,13 @@
         <v>1233</v>
       </c>
       <c r="E796" t="s">
-        <v>1906</v>
+        <v>1901</v>
       </c>
       <c r="F796" t="s">
         <v>1902</v>
       </c>
       <c r="G796" t="s">
-        <v>1903</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="797" spans="1:7">
@@ -25337,13 +25337,13 @@
         <v>1233</v>
       </c>
       <c r="E799" t="s">
-        <v>1906</v>
+        <v>1901</v>
       </c>
       <c r="F799" t="s">
         <v>1902</v>
       </c>
       <c r="G799" t="s">
-        <v>1903</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="800" spans="1:7">
@@ -25360,13 +25360,13 @@
         <v>1233</v>
       </c>
       <c r="E800" t="s">
-        <v>1906</v>
+        <v>1901</v>
       </c>
       <c r="F800" t="s">
         <v>1902</v>
       </c>
       <c r="G800" t="s">
-        <v>1903</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="801" spans="1:7">
@@ -25383,13 +25383,13 @@
         <v>1233</v>
       </c>
       <c r="E801" t="s">
-        <v>1906</v>
+        <v>1901</v>
       </c>
       <c r="F801" t="s">
         <v>1902</v>
       </c>
       <c r="G801" t="s">
-        <v>1903</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="802" spans="1:7">
@@ -25406,13 +25406,13 @@
         <v>1233</v>
       </c>
       <c r="E802" t="s">
-        <v>1906</v>
+        <v>1901</v>
       </c>
       <c r="F802" t="s">
         <v>1902</v>
       </c>
       <c r="G802" t="s">
-        <v>1903</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="803" spans="1:7">
@@ -25429,13 +25429,13 @@
         <v>1233</v>
       </c>
       <c r="E803" t="s">
-        <v>1906</v>
+        <v>1901</v>
       </c>
       <c r="F803" t="s">
         <v>1902</v>
       </c>
       <c r="G803" t="s">
-        <v>1903</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="804" spans="1:7">
@@ -25452,13 +25452,13 @@
         <v>1233</v>
       </c>
       <c r="E804" t="s">
-        <v>1906</v>
+        <v>1901</v>
       </c>
       <c r="F804" t="s">
         <v>1902</v>
       </c>
       <c r="G804" t="s">
-        <v>1903</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="805" spans="1:7">
@@ -25475,13 +25475,13 @@
         <v>1233</v>
       </c>
       <c r="E805" t="s">
-        <v>1906</v>
+        <v>1901</v>
       </c>
       <c r="F805" t="s">
         <v>1902</v>
       </c>
       <c r="G805" t="s">
-        <v>1903</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="806" spans="1:7">
@@ -25498,13 +25498,13 @@
         <v>1233</v>
       </c>
       <c r="E806" t="s">
-        <v>1906</v>
+        <v>1901</v>
       </c>
       <c r="F806" t="s">
         <v>1902</v>
       </c>
       <c r="G806" t="s">
-        <v>1903</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="807" spans="1:7">
@@ -25521,13 +25521,13 @@
         <v>1233</v>
       </c>
       <c r="E807" t="s">
-        <v>1906</v>
+        <v>1901</v>
       </c>
       <c r="F807" t="s">
         <v>1902</v>
       </c>
       <c r="G807" t="s">
-        <v>1903</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="808" spans="1:7">
@@ -25682,13 +25682,13 @@
         <v>1233</v>
       </c>
       <c r="E814" t="s">
-        <v>1992</v>
+        <v>1983</v>
       </c>
       <c r="F814" t="s">
         <v>1984</v>
       </c>
       <c r="G814" t="s">
-        <v>1985</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="815" spans="1:7">
@@ -25889,13 +25889,13 @@
         <v>1233</v>
       </c>
       <c r="E823" t="s">
-        <v>2020</v>
+        <v>1983</v>
       </c>
       <c r="F823" t="s">
         <v>1984</v>
       </c>
       <c r="G823" t="s">
-        <v>1985</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="824" spans="1:7">
@@ -26004,13 +26004,13 @@
         <v>1233</v>
       </c>
       <c r="E828" t="s">
-        <v>2020</v>
+        <v>1983</v>
       </c>
       <c r="F828" t="s">
         <v>1984</v>
       </c>
       <c r="G828" t="s">
-        <v>1985</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="829" spans="1:7">
@@ -26050,13 +26050,13 @@
         <v>1233</v>
       </c>
       <c r="E830" t="s">
-        <v>1992</v>
+        <v>1983</v>
       </c>
       <c r="F830" t="s">
         <v>1984</v>
       </c>
       <c r="G830" t="s">
-        <v>1985</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="831" spans="1:7">
@@ -26280,13 +26280,13 @@
         <v>1233</v>
       </c>
       <c r="E840" t="s">
-        <v>2061</v>
+        <v>2056</v>
       </c>
       <c r="F840" t="s">
         <v>2057</v>
       </c>
       <c r="G840" t="s">
-        <v>2058</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="841" spans="1:7">
@@ -26303,13 +26303,13 @@
         <v>1233</v>
       </c>
       <c r="E841" t="s">
-        <v>2061</v>
+        <v>2056</v>
       </c>
       <c r="F841" t="s">
         <v>2057</v>
       </c>
       <c r="G841" t="s">
-        <v>2058</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="842" spans="1:7">
@@ -26326,13 +26326,13 @@
         <v>1233</v>
       </c>
       <c r="E842" t="s">
-        <v>2061</v>
+        <v>2056</v>
       </c>
       <c r="F842" t="s">
         <v>2057</v>
       </c>
       <c r="G842" t="s">
-        <v>2058</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="843" spans="1:7">
@@ -26349,13 +26349,13 @@
         <v>1233</v>
       </c>
       <c r="E843" t="s">
-        <v>2061</v>
+        <v>2056</v>
       </c>
       <c r="F843" t="s">
         <v>2057</v>
       </c>
       <c r="G843" t="s">
-        <v>2058</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="844" spans="1:7">
@@ -26372,13 +26372,13 @@
         <v>1233</v>
       </c>
       <c r="E844" t="s">
-        <v>2061</v>
+        <v>2056</v>
       </c>
       <c r="F844" t="s">
         <v>2057</v>
       </c>
       <c r="G844" t="s">
-        <v>2058</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="845" spans="1:7">
@@ -26395,13 +26395,13 @@
         <v>1233</v>
       </c>
       <c r="E845" t="s">
-        <v>2061</v>
+        <v>2056</v>
       </c>
       <c r="F845" t="s">
         <v>2057</v>
       </c>
       <c r="G845" t="s">
-        <v>2058</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="846" spans="1:7">
@@ -26418,13 +26418,13 @@
         <v>1233</v>
       </c>
       <c r="E846" t="s">
-        <v>2061</v>
+        <v>2056</v>
       </c>
       <c r="F846" t="s">
         <v>2057</v>
       </c>
       <c r="G846" t="s">
-        <v>2058</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="847" spans="1:7">
@@ -26441,13 +26441,13 @@
         <v>1233</v>
       </c>
       <c r="E847" t="s">
-        <v>2076</v>
+        <v>1992</v>
       </c>
       <c r="F847" t="s">
         <v>2057</v>
       </c>
       <c r="G847" t="s">
-        <v>1993</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="848" spans="1:7">
@@ -26464,13 +26464,13 @@
         <v>1233</v>
       </c>
       <c r="E848" t="s">
-        <v>2076</v>
+        <v>1992</v>
       </c>
       <c r="F848" t="s">
         <v>2057</v>
       </c>
       <c r="G848" t="s">
-        <v>1993</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="849" spans="1:7">
@@ -26487,13 +26487,13 @@
         <v>1233</v>
       </c>
       <c r="E849" t="s">
-        <v>2076</v>
+        <v>1992</v>
       </c>
       <c r="F849" t="s">
         <v>2057</v>
       </c>
       <c r="G849" t="s">
-        <v>1993</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="850" spans="1:7">
@@ -26510,13 +26510,13 @@
         <v>1233</v>
       </c>
       <c r="E850" t="s">
-        <v>2076</v>
+        <v>2083</v>
       </c>
       <c r="F850" t="s">
         <v>2057</v>
       </c>
       <c r="G850" t="s">
-        <v>2083</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="851" spans="1:7">
@@ -26533,13 +26533,13 @@
         <v>1233</v>
       </c>
       <c r="E851" t="s">
-        <v>2076</v>
+        <v>1992</v>
       </c>
       <c r="F851" t="s">
         <v>2057</v>
       </c>
       <c r="G851" t="s">
-        <v>1993</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="852" spans="1:7">
@@ -26556,13 +26556,13 @@
         <v>1233</v>
       </c>
       <c r="E852" t="s">
-        <v>2076</v>
+        <v>1992</v>
       </c>
       <c r="F852" t="s">
         <v>2057</v>
       </c>
       <c r="G852" t="s">
-        <v>1993</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="853" spans="1:7">
@@ -26579,13 +26579,13 @@
         <v>1233</v>
       </c>
       <c r="E853" t="s">
-        <v>2061</v>
+        <v>2056</v>
       </c>
       <c r="F853" t="s">
         <v>2057</v>
       </c>
       <c r="G853" t="s">
-        <v>2058</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="854" spans="1:7">
@@ -26602,13 +26602,13 @@
         <v>19</v>
       </c>
       <c r="E854" t="s">
-        <v>2061</v>
+        <v>2056</v>
       </c>
       <c r="F854" t="s">
         <v>2057</v>
       </c>
       <c r="G854" t="s">
-        <v>2058</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="855" spans="1:7">
@@ -26625,13 +26625,13 @@
         <v>19</v>
       </c>
       <c r="E855" t="s">
-        <v>2061</v>
+        <v>2056</v>
       </c>
       <c r="F855" t="s">
         <v>2057</v>
       </c>
       <c r="G855" t="s">
-        <v>2058</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="856" spans="1:7">
@@ -26648,13 +26648,13 @@
         <v>19</v>
       </c>
       <c r="E856" t="s">
-        <v>2061</v>
+        <v>2056</v>
       </c>
       <c r="F856" t="s">
         <v>2057</v>
       </c>
       <c r="G856" t="s">
-        <v>2058</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="857" spans="1:7">
@@ -26671,13 +26671,13 @@
         <v>1233</v>
       </c>
       <c r="E857" t="s">
-        <v>2061</v>
+        <v>2056</v>
       </c>
       <c r="F857" t="s">
         <v>2057</v>
       </c>
       <c r="G857" t="s">
-        <v>2058</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="858" spans="1:7">
@@ -26694,13 +26694,13 @@
         <v>1233</v>
       </c>
       <c r="E858" t="s">
-        <v>2061</v>
+        <v>2056</v>
       </c>
       <c r="F858" t="s">
         <v>2057</v>
       </c>
       <c r="G858" t="s">
-        <v>2058</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="859" spans="1:7">
@@ -26717,13 +26717,13 @@
         <v>19</v>
       </c>
       <c r="E859" t="s">
-        <v>2061</v>
+        <v>2056</v>
       </c>
       <c r="F859" t="s">
         <v>2057</v>
       </c>
       <c r="G859" t="s">
-        <v>2058</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="860" spans="1:7">
@@ -26740,13 +26740,13 @@
         <v>1233</v>
       </c>
       <c r="E860" t="s">
-        <v>2061</v>
+        <v>2056</v>
       </c>
       <c r="F860" t="s">
         <v>2057</v>
       </c>
       <c r="G860" t="s">
-        <v>2058</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="861" spans="1:7">
@@ -26763,13 +26763,13 @@
         <v>1233</v>
       </c>
       <c r="E861" t="s">
-        <v>2061</v>
+        <v>2056</v>
       </c>
       <c r="F861" t="s">
         <v>2057</v>
       </c>
       <c r="G861" t="s">
-        <v>2058</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="862" spans="1:7">
@@ -26786,13 +26786,13 @@
         <v>1233</v>
       </c>
       <c r="E862" t="s">
-        <v>2061</v>
+        <v>2056</v>
       </c>
       <c r="F862" t="s">
         <v>2057</v>
       </c>
       <c r="G862" t="s">
-        <v>2058</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="863" spans="1:7">
@@ -26809,13 +26809,13 @@
         <v>1233</v>
       </c>
       <c r="E863" t="s">
-        <v>2061</v>
+        <v>2056</v>
       </c>
       <c r="F863" t="s">
         <v>2057</v>
       </c>
       <c r="G863" t="s">
-        <v>2058</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="864" spans="1:7">
@@ -26832,13 +26832,13 @@
         <v>1233</v>
       </c>
       <c r="E864" t="s">
-        <v>2061</v>
+        <v>2056</v>
       </c>
       <c r="F864" t="s">
         <v>2057</v>
       </c>
       <c r="G864" t="s">
-        <v>2058</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="865" spans="1:7">
@@ -26855,13 +26855,13 @@
         <v>1233</v>
       </c>
       <c r="E865" t="s">
-        <v>2061</v>
+        <v>2056</v>
       </c>
       <c r="F865" t="s">
         <v>2057</v>
       </c>
       <c r="G865" t="s">
-        <v>2058</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="866" spans="1:7">
@@ -26878,13 +26878,13 @@
         <v>1233</v>
       </c>
       <c r="E866" t="s">
-        <v>2061</v>
+        <v>2056</v>
       </c>
       <c r="F866" t="s">
         <v>2057</v>
       </c>
       <c r="G866" t="s">
-        <v>2058</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="867" spans="1:7">
@@ -26924,13 +26924,13 @@
         <v>1233</v>
       </c>
       <c r="E868" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="F868" t="s">
         <v>2119</v>
       </c>
       <c r="G868" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="869" spans="1:7">
@@ -26947,13 +26947,13 @@
         <v>1233</v>
       </c>
       <c r="E869" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="F869" t="s">
         <v>2119</v>
       </c>
       <c r="G869" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="870" spans="1:7">
@@ -26970,13 +26970,13 @@
         <v>1233</v>
       </c>
       <c r="E870" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="F870" t="s">
         <v>2119</v>
       </c>
       <c r="G870" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="871" spans="1:7">
@@ -26993,13 +26993,13 @@
         <v>1233</v>
       </c>
       <c r="E871" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="F871" t="s">
         <v>2119</v>
       </c>
       <c r="G871" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="872" spans="1:7">
@@ -27016,13 +27016,13 @@
         <v>19</v>
       </c>
       <c r="E872" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="F872" t="s">
         <v>2119</v>
       </c>
       <c r="G872" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="873" spans="1:7">
@@ -27039,13 +27039,13 @@
         <v>19</v>
       </c>
       <c r="E873" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="F873" t="s">
         <v>2119</v>
       </c>
       <c r="G873" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="874" spans="1:7">
@@ -27062,13 +27062,13 @@
         <v>1233</v>
       </c>
       <c r="E874" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="F874" t="s">
         <v>2119</v>
       </c>
       <c r="G874" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="875" spans="1:7">
@@ -27085,13 +27085,13 @@
         <v>1233</v>
       </c>
       <c r="E875" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="F875" t="s">
         <v>2119</v>
       </c>
       <c r="G875" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="876" spans="1:7">
@@ -27108,13 +27108,13 @@
         <v>1233</v>
       </c>
       <c r="E876" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="F876" t="s">
         <v>2119</v>
       </c>
       <c r="G876" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="877" spans="1:7">
@@ -27131,13 +27131,13 @@
         <v>19</v>
       </c>
       <c r="E877" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="F877" t="s">
         <v>2119</v>
       </c>
       <c r="G877" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="878" spans="1:7">
@@ -27154,13 +27154,13 @@
         <v>1233</v>
       </c>
       <c r="E878" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="F878" t="s">
         <v>2119</v>
       </c>
       <c r="G878" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="879" spans="1:7">
@@ -27177,13 +27177,13 @@
         <v>1233</v>
       </c>
       <c r="E879" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="F879" t="s">
         <v>2119</v>
       </c>
       <c r="G879" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="880" spans="1:7">
@@ -27200,13 +27200,13 @@
         <v>1233</v>
       </c>
       <c r="E880" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="F880" t="s">
         <v>2119</v>
       </c>
       <c r="G880" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="881" spans="1:7">
@@ -27223,13 +27223,13 @@
         <v>1233</v>
       </c>
       <c r="E881" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="F881" t="s">
         <v>2119</v>
       </c>
       <c r="G881" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="882" spans="1:7">
@@ -27246,13 +27246,13 @@
         <v>1233</v>
       </c>
       <c r="E882" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="F882" t="s">
         <v>2119</v>
       </c>
       <c r="G882" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="883" spans="1:7">
@@ -27269,13 +27269,13 @@
         <v>1233</v>
       </c>
       <c r="E883" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="F883" t="s">
         <v>2119</v>
       </c>
       <c r="G883" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="884" spans="1:7">
@@ -27292,13 +27292,13 @@
         <v>1233</v>
       </c>
       <c r="E884" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="F884" t="s">
         <v>2119</v>
       </c>
       <c r="G884" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="885" spans="1:7">
@@ -27315,13 +27315,13 @@
         <v>1233</v>
       </c>
       <c r="E885" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="F885" t="s">
         <v>2119</v>
       </c>
       <c r="G885" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="886" spans="1:7">
@@ -27338,13 +27338,13 @@
         <v>1233</v>
       </c>
       <c r="E886" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="F886" t="s">
         <v>2119</v>
       </c>
       <c r="G886" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="887" spans="1:7">
@@ -27361,13 +27361,13 @@
         <v>19</v>
       </c>
       <c r="E887" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="F887" t="s">
         <v>2119</v>
       </c>
       <c r="G887" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="888" spans="1:7">
@@ -27384,13 +27384,13 @@
         <v>1233</v>
       </c>
       <c r="E888" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="F888" t="s">
         <v>2119</v>
       </c>
       <c r="G888" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="889" spans="1:7">
@@ -27407,13 +27407,13 @@
         <v>1233</v>
       </c>
       <c r="E889" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="F889" t="s">
         <v>2119</v>
       </c>
       <c r="G889" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="890" spans="1:7">
@@ -27545,13 +27545,13 @@
         <v>1233</v>
       </c>
       <c r="E895" t="s">
-        <v>2181</v>
+        <v>2168</v>
       </c>
       <c r="F895" t="s">
         <v>2169</v>
       </c>
       <c r="G895" t="s">
-        <v>2170</v>
+        <v>2181</v>
       </c>
     </row>
     <row r="896" spans="1:7">
@@ -27752,13 +27752,13 @@
         <v>1233</v>
       </c>
       <c r="E904" t="s">
+        <v>2168</v>
+      </c>
+      <c r="F904" t="s">
         <v>2200</v>
       </c>
-      <c r="F904" t="s">
+      <c r="G904" t="s">
         <v>2201</v>
-      </c>
-      <c r="G904" t="s">
-        <v>2170</v>
       </c>
     </row>
     <row r="905" spans="1:7">
@@ -27775,13 +27775,13 @@
         <v>1233</v>
       </c>
       <c r="E905" t="s">
+        <v>2168</v>
+      </c>
+      <c r="F905" t="s">
+        <v>2200</v>
+      </c>
+      <c r="G905" t="s">
         <v>2204</v>
-      </c>
-      <c r="F905" t="s">
-        <v>2201</v>
-      </c>
-      <c r="G905" t="s">
-        <v>2170</v>
       </c>
     </row>
     <row r="906" spans="1:7">
@@ -27798,13 +27798,13 @@
         <v>1233</v>
       </c>
       <c r="E906" t="s">
+        <v>2168</v>
+      </c>
+      <c r="F906" t="s">
         <v>2200</v>
       </c>
-      <c r="F906" t="s">
+      <c r="G906" t="s">
         <v>2201</v>
-      </c>
-      <c r="G906" t="s">
-        <v>2170</v>
       </c>
     </row>
   </sheetData>

--- a/api/1/clv3/xlsx/en/HumanitarianPlan.xlsx
+++ b/api/1/clv3/xlsx/en/HumanitarianPlan.xlsx
@@ -28,12 +28,12 @@
     <t>codeforiati:plan-start-date</t>
   </si>
   <si>
+    <t>codeforiati:plan-end-date</t>
+  </si>
+  <si>
     <t>codeforiati:plan-year</t>
   </si>
   <si>
-    <t>codeforiati:plan-end-date</t>
-  </si>
-  <si>
     <t>codeforiati:plan-type</t>
   </si>
   <si>
@@ -49,12 +49,12 @@
     <t>2025-01-01</t>
   </si>
   <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
     <t>2025</t>
   </si>
   <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
     <t>Humanitarian needs and response plan</t>
   </si>
   <si>
@@ -358,12 +358,12 @@
     <t>2024-01-01</t>
   </si>
   <si>
+    <t>2024-12-31</t>
+  </si>
+  <si>
     <t>2024</t>
   </si>
   <si>
-    <t>2024-12-31</t>
-  </si>
-  <si>
     <t>RAFG_RRP24</t>
   </si>
   <si>
@@ -715,12 +715,12 @@
     <t>2023-01-01</t>
   </si>
   <si>
+    <t>2023-12-31</t>
+  </si>
+  <si>
     <t>2023</t>
   </si>
   <si>
-    <t>2023-12-31</t>
-  </si>
-  <si>
     <t>RAFG23</t>
   </si>
   <si>
@@ -1033,12 +1033,12 @@
     <t>2022-01-01</t>
   </si>
   <si>
+    <t>2022-12-31</t>
+  </si>
+  <si>
     <t>2022</t>
   </si>
   <si>
-    <t>2022-12-31</t>
-  </si>
-  <si>
     <t>RAFG22</t>
   </si>
   <si>
@@ -1381,12 +1381,12 @@
     <t>2021-09-01</t>
   </si>
   <si>
+    <t>2021-12-31</t>
+  </si>
+  <si>
     <t>2021</t>
   </si>
   <si>
-    <t>2021-12-31</t>
-  </si>
-  <si>
     <t>HAFG21</t>
   </si>
   <si>
@@ -1738,12 +1738,12 @@
     <t>2020-01-01</t>
   </si>
   <si>
+    <t>2020-12-31</t>
+  </si>
+  <si>
     <t>2020</t>
   </si>
   <si>
-    <t>2020-12-31</t>
-  </si>
-  <si>
     <t>OBGD20</t>
   </si>
   <si>
@@ -2173,12 +2173,12 @@
     <t>2019-01-01</t>
   </si>
   <si>
+    <t>2019-12-31</t>
+  </si>
+  <si>
     <t>2019</t>
   </si>
   <si>
-    <t>2019-12-31</t>
-  </si>
-  <si>
     <t>RBGD19</t>
   </si>
   <si>
@@ -2410,12 +2410,12 @@
     <t>2018-01-01</t>
   </si>
   <si>
+    <t>2018-12-31</t>
+  </si>
+  <si>
     <t>2018</t>
   </si>
   <si>
-    <t>2018-12-31</t>
-  </si>
-  <si>
     <t>OBGD18</t>
   </si>
   <si>
@@ -2635,12 +2635,12 @@
     <t>2017-01-01</t>
   </si>
   <si>
+    <t>2017-12-31</t>
+  </si>
+  <si>
     <t>2017</t>
   </si>
   <si>
-    <t>2017-12-31</t>
-  </si>
-  <si>
     <t>HAFG17</t>
   </si>
   <si>
@@ -2920,12 +2920,12 @@
     <t>2016-01-01</t>
   </si>
   <si>
+    <t>2016-12-31</t>
+  </si>
+  <si>
     <t>2016</t>
   </si>
   <si>
-    <t>2016-12-31</t>
-  </si>
-  <si>
     <t>HAFG16</t>
   </si>
   <si>
@@ -3196,12 +3196,12 @@
     <t>2015-01-01</t>
   </si>
   <si>
+    <t>2015-12-31</t>
+  </si>
+  <si>
     <t>2015</t>
   </si>
   <si>
-    <t>2015-12-31</t>
-  </si>
-  <si>
     <t>Strategic response plan</t>
   </si>
   <si>
@@ -3427,12 +3427,12 @@
     <t>2014-01-01</t>
   </si>
   <si>
+    <t>2014-12-31</t>
+  </si>
+  <si>
     <t>2014</t>
   </si>
   <si>
-    <t>2014-12-31</t>
-  </si>
-  <si>
     <t>HBFA1314</t>
   </si>
   <si>
@@ -3712,12 +3712,12 @@
     <t>Afghanistan 2013</t>
   </si>
   <si>
+    <t>2013-12-31</t>
+  </si>
+  <si>
     <t>2013</t>
   </si>
   <si>
-    <t>2013-12-31</t>
-  </si>
-  <si>
     <t>Consolidated appeals process</t>
   </si>
   <si>
@@ -3877,12 +3877,12 @@
     <t>2012-01-01</t>
   </si>
   <si>
+    <t>2012-12-31</t>
+  </si>
+  <si>
     <t>2012</t>
   </si>
   <si>
-    <t>2012-12-31</t>
-  </si>
-  <si>
     <t>CAFG1112</t>
   </si>
   <si>
@@ -4258,12 +4258,12 @@
     <t>2010-01-01</t>
   </si>
   <si>
+    <t>2010-12-31</t>
+  </si>
+  <si>
     <t>2010</t>
   </si>
   <si>
-    <t>2010-12-31</t>
-  </si>
-  <si>
     <t>OBFA1011</t>
   </si>
   <si>
@@ -4468,12 +4468,12 @@
     <t>2009-01-01</t>
   </si>
   <si>
+    <t>2009-12-31</t>
+  </si>
+  <si>
     <t>2009</t>
   </si>
   <si>
-    <t>2009-12-31</t>
-  </si>
-  <si>
     <t>FBFA0910</t>
   </si>
   <si>
@@ -4684,12 +4684,12 @@
     <t>2008-02-01</t>
   </si>
   <si>
+    <t>2008-06-30</t>
+  </si>
+  <si>
     <t>2008</t>
   </si>
   <si>
-    <t>2008-06-30</t>
-  </si>
-  <si>
     <t>OAFG0809</t>
   </si>
   <si>
@@ -4951,12 +4951,12 @@
     <t>2007-02-22</t>
   </si>
   <si>
+    <t>2007-08-21</t>
+  </si>
+  <si>
     <t>2007</t>
   </si>
   <si>
-    <t>2007-08-21</t>
-  </si>
-  <si>
     <t>FBFA0708</t>
   </si>
   <si>
@@ -5257,12 +5257,12 @@
     <t>2006-07-01</t>
   </si>
   <si>
+    <t>2006-12-31</t>
+  </si>
+  <si>
     <t>2006</t>
   </si>
   <si>
-    <t>2006-12-31</t>
-  </si>
-  <si>
     <t>CBDI06</t>
   </si>
   <si>
@@ -5512,12 +5512,12 @@
     <t>2005-04-01</t>
   </si>
   <si>
+    <t>2005-06-30</t>
+  </si>
+  <si>
     <t>2005</t>
   </si>
   <si>
-    <t>2005-06-30</t>
-  </si>
-  <si>
     <t>FBEN05</t>
   </si>
   <si>
@@ -5719,12 +5719,12 @@
     <t>2004-09-01</t>
   </si>
   <si>
+    <t>2004-12-31</t>
+  </si>
+  <si>
     <t>2004</t>
   </si>
   <si>
-    <t>2004-12-31</t>
-  </si>
-  <si>
     <t>CAGO04</t>
   </si>
   <si>
@@ -5965,12 +5965,12 @@
     <t>2003-01-01</t>
   </si>
   <si>
+    <t>2003-12-31</t>
+  </si>
+  <si>
     <t>2003</t>
   </si>
   <si>
-    <t>2003-12-31</t>
-  </si>
-  <si>
     <t>CAGO03</t>
   </si>
   <si>
@@ -6187,12 +6187,12 @@
     <t>2001-10-01</t>
   </si>
   <si>
+    <t>2002-12-31</t>
+  </si>
+  <si>
     <t>2002</t>
   </si>
   <si>
-    <t>2002-12-31</t>
-  </si>
-  <si>
     <t>CAGO02</t>
   </si>
   <si>
@@ -6373,12 +6373,12 @@
     <t>2001-01-01</t>
   </si>
   <si>
+    <t>2001-09-30</t>
+  </si>
+  <si>
     <t>2001</t>
   </si>
   <si>
-    <t>2001-09-30</t>
-  </si>
-  <si>
     <t>CAGO01</t>
   </si>
   <si>
@@ -6523,10 +6523,10 @@
     <t>2000-01-01</t>
   </si>
   <si>
+    <t>2000-12-31</t>
+  </si>
+  <si>
     <t>2000</t>
-  </si>
-  <si>
-    <t>2000-12-31</t>
   </si>
   <si>
     <t>CBDI00</t>
@@ -7055,10 +7055,10 @@
         <v>10</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F4" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G4" t="s">
         <v>20</v>
@@ -7285,10 +7285,10 @@
         <v>10</v>
       </c>
       <c r="E14" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F14" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G14" t="s">
         <v>34</v>
@@ -7308,10 +7308,10 @@
         <v>10</v>
       </c>
       <c r="E15" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="F15" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="G15" t="s">
         <v>34</v>
@@ -7354,10 +7354,10 @@
         <v>10</v>
       </c>
       <c r="E17" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="F17" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="G17" t="s">
         <v>34</v>
@@ -7400,10 +7400,10 @@
         <v>10</v>
       </c>
       <c r="E19" t="s">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="F19" t="s">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="G19" t="s">
         <v>34</v>
@@ -7515,10 +7515,10 @@
         <v>10</v>
       </c>
       <c r="E24" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="F24" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="G24" t="s">
         <v>20</v>
@@ -7929,10 +7929,10 @@
         <v>10</v>
       </c>
       <c r="E42" t="s">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="F42" t="s">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="G42" t="s">
         <v>20</v>
@@ -7975,10 +7975,10 @@
         <v>10</v>
       </c>
       <c r="E44" t="s">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="F44" t="s">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="G44" t="s">
         <v>34</v>
@@ -7998,10 +7998,10 @@
         <v>10</v>
       </c>
       <c r="E45" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="F45" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="G45" t="s">
         <v>34</v>
@@ -8412,10 +8412,10 @@
         <v>113</v>
       </c>
       <c r="E63" t="s">
-        <v>114</v>
+        <v>154</v>
       </c>
       <c r="F63" t="s">
-        <v>154</v>
+        <v>115</v>
       </c>
       <c r="G63" t="s">
         <v>34</v>
@@ -8435,10 +8435,10 @@
         <v>113</v>
       </c>
       <c r="E64" t="s">
-        <v>114</v>
+        <v>157</v>
       </c>
       <c r="F64" t="s">
-        <v>157</v>
+        <v>115</v>
       </c>
       <c r="G64" t="s">
         <v>34</v>
@@ -8504,10 +8504,10 @@
         <v>165</v>
       </c>
       <c r="E67" t="s">
-        <v>114</v>
+        <v>157</v>
       </c>
       <c r="F67" t="s">
-        <v>157</v>
+        <v>115</v>
       </c>
       <c r="G67" t="s">
         <v>20</v>
@@ -9631,10 +9631,10 @@
         <v>275</v>
       </c>
       <c r="E116" t="s">
-        <v>233</v>
+        <v>276</v>
       </c>
       <c r="F116" t="s">
-        <v>276</v>
+        <v>234</v>
       </c>
       <c r="G116" t="s">
         <v>20</v>
@@ -9654,10 +9654,10 @@
         <v>279</v>
       </c>
       <c r="E117" t="s">
-        <v>233</v>
+        <v>280</v>
       </c>
       <c r="F117" t="s">
-        <v>280</v>
+        <v>234</v>
       </c>
       <c r="G117" t="s">
         <v>20</v>
@@ -9769,10 +9769,10 @@
         <v>232</v>
       </c>
       <c r="E122" t="s">
-        <v>233</v>
+        <v>280</v>
       </c>
       <c r="F122" t="s">
-        <v>280</v>
+        <v>234</v>
       </c>
       <c r="G122" t="s">
         <v>25</v>
@@ -9792,10 +9792,10 @@
         <v>232</v>
       </c>
       <c r="E123" t="s">
-        <v>233</v>
+        <v>276</v>
       </c>
       <c r="F123" t="s">
-        <v>276</v>
+        <v>234</v>
       </c>
       <c r="G123" t="s">
         <v>20</v>
@@ -9999,10 +9999,10 @@
         <v>310</v>
       </c>
       <c r="E132" t="s">
-        <v>233</v>
+        <v>311</v>
       </c>
       <c r="F132" t="s">
-        <v>311</v>
+        <v>234</v>
       </c>
       <c r="G132" t="s">
         <v>16</v>
@@ -10045,10 +10045,10 @@
         <v>316</v>
       </c>
       <c r="E134" t="s">
-        <v>233</v>
+        <v>276</v>
       </c>
       <c r="F134" t="s">
-        <v>276</v>
+        <v>234</v>
       </c>
       <c r="G134" t="s">
         <v>34</v>
@@ -10091,10 +10091,10 @@
         <v>321</v>
       </c>
       <c r="E136" t="s">
-        <v>233</v>
+        <v>276</v>
       </c>
       <c r="F136" t="s">
-        <v>276</v>
+        <v>234</v>
       </c>
       <c r="G136" t="s">
         <v>34</v>
@@ -10436,10 +10436,10 @@
         <v>355</v>
       </c>
       <c r="E151" t="s">
-        <v>339</v>
+        <v>356</v>
       </c>
       <c r="F151" t="s">
-        <v>356</v>
+        <v>340</v>
       </c>
       <c r="G151" t="s">
         <v>20</v>
@@ -10551,10 +10551,10 @@
         <v>367</v>
       </c>
       <c r="E156" t="s">
-        <v>339</v>
+        <v>368</v>
       </c>
       <c r="F156" t="s">
-        <v>368</v>
+        <v>340</v>
       </c>
       <c r="G156" t="s">
         <v>34</v>
@@ -10666,10 +10666,10 @@
         <v>338</v>
       </c>
       <c r="E161" t="s">
-        <v>339</v>
+        <v>379</v>
       </c>
       <c r="F161" t="s">
-        <v>379</v>
+        <v>340</v>
       </c>
       <c r="G161" t="s">
         <v>34</v>
@@ -10758,10 +10758,10 @@
         <v>388</v>
       </c>
       <c r="E165" t="s">
-        <v>339</v>
+        <v>389</v>
       </c>
       <c r="F165" t="s">
-        <v>389</v>
+        <v>340</v>
       </c>
       <c r="G165" t="s">
         <v>34</v>
@@ -10804,10 +10804,10 @@
         <v>394</v>
       </c>
       <c r="E167" t="s">
-        <v>339</v>
+        <v>395</v>
       </c>
       <c r="F167" t="s">
-        <v>395</v>
+        <v>340</v>
       </c>
       <c r="G167" t="s">
         <v>34</v>
@@ -10965,10 +10965,10 @@
         <v>408</v>
       </c>
       <c r="E174" t="s">
-        <v>339</v>
+        <v>410</v>
       </c>
       <c r="F174" t="s">
-        <v>410</v>
+        <v>340</v>
       </c>
       <c r="G174" t="s">
         <v>20</v>
@@ -10988,10 +10988,10 @@
         <v>413</v>
       </c>
       <c r="E175" t="s">
-        <v>339</v>
+        <v>414</v>
       </c>
       <c r="F175" t="s">
-        <v>414</v>
+        <v>340</v>
       </c>
       <c r="G175" t="s">
         <v>20</v>
@@ -11333,10 +11333,10 @@
         <v>442</v>
       </c>
       <c r="E190" t="s">
-        <v>339</v>
+        <v>447</v>
       </c>
       <c r="F190" t="s">
-        <v>447</v>
+        <v>340</v>
       </c>
       <c r="G190" t="s">
         <v>16</v>
@@ -11701,10 +11701,10 @@
         <v>482</v>
       </c>
       <c r="E206" t="s">
-        <v>455</v>
+        <v>339</v>
       </c>
       <c r="F206" t="s">
-        <v>340</v>
+        <v>456</v>
       </c>
       <c r="G206" t="s">
         <v>25</v>
@@ -11724,10 +11724,10 @@
         <v>487</v>
       </c>
       <c r="E207" t="s">
-        <v>455</v>
+        <v>488</v>
       </c>
       <c r="F207" t="s">
-        <v>488</v>
+        <v>456</v>
       </c>
       <c r="G207" t="s">
         <v>34</v>
@@ -11793,10 +11793,10 @@
         <v>482</v>
       </c>
       <c r="E210" t="s">
-        <v>455</v>
+        <v>339</v>
       </c>
       <c r="F210" t="s">
-        <v>340</v>
+        <v>456</v>
       </c>
       <c r="G210" t="s">
         <v>25</v>
@@ -11816,10 +11816,10 @@
         <v>497</v>
       </c>
       <c r="E211" t="s">
-        <v>455</v>
+        <v>498</v>
       </c>
       <c r="F211" t="s">
-        <v>498</v>
+        <v>456</v>
       </c>
       <c r="G211" t="s">
         <v>34</v>
@@ -11862,10 +11862,10 @@
         <v>503</v>
       </c>
       <c r="E213" t="s">
-        <v>455</v>
+        <v>504</v>
       </c>
       <c r="F213" t="s">
-        <v>504</v>
+        <v>456</v>
       </c>
       <c r="G213" t="s">
         <v>34</v>
@@ -11908,10 +11908,10 @@
         <v>482</v>
       </c>
       <c r="E215" t="s">
-        <v>455</v>
+        <v>339</v>
       </c>
       <c r="F215" t="s">
-        <v>340</v>
+        <v>456</v>
       </c>
       <c r="G215" t="s">
         <v>25</v>
@@ -11977,10 +11977,10 @@
         <v>516</v>
       </c>
       <c r="E218" t="s">
-        <v>455</v>
+        <v>517</v>
       </c>
       <c r="F218" t="s">
-        <v>517</v>
+        <v>456</v>
       </c>
       <c r="G218" t="s">
         <v>20</v>
@@ -12023,10 +12023,10 @@
         <v>459</v>
       </c>
       <c r="E220" t="s">
-        <v>455</v>
+        <v>389</v>
       </c>
       <c r="F220" t="s">
-        <v>389</v>
+        <v>456</v>
       </c>
       <c r="G220" t="s">
         <v>34</v>
@@ -12805,10 +12805,10 @@
         <v>596</v>
       </c>
       <c r="E254" t="s">
-        <v>574</v>
+        <v>459</v>
       </c>
       <c r="F254" t="s">
-        <v>459</v>
+        <v>575</v>
       </c>
       <c r="G254" t="s">
         <v>25</v>
@@ -12989,10 +12989,10 @@
         <v>614</v>
       </c>
       <c r="E262" t="s">
-        <v>574</v>
+        <v>615</v>
       </c>
       <c r="F262" t="s">
-        <v>615</v>
+        <v>575</v>
       </c>
       <c r="G262" t="s">
         <v>34</v>
@@ -13334,10 +13334,10 @@
         <v>647</v>
       </c>
       <c r="E277" t="s">
-        <v>574</v>
+        <v>648</v>
       </c>
       <c r="F277" t="s">
-        <v>648</v>
+        <v>575</v>
       </c>
       <c r="G277" t="s">
         <v>34</v>
@@ -13380,10 +13380,10 @@
         <v>653</v>
       </c>
       <c r="E279" t="s">
-        <v>574</v>
+        <v>654</v>
       </c>
       <c r="F279" t="s">
-        <v>654</v>
+        <v>575</v>
       </c>
       <c r="G279" t="s">
         <v>34</v>
@@ -14024,10 +14024,10 @@
         <v>711</v>
       </c>
       <c r="E307" t="s">
-        <v>574</v>
+        <v>615</v>
       </c>
       <c r="F307" t="s">
-        <v>615</v>
+        <v>575</v>
       </c>
       <c r="G307" t="s">
         <v>20</v>
@@ -14438,10 +14438,10 @@
         <v>718</v>
       </c>
       <c r="E325" t="s">
-        <v>719</v>
+        <v>752</v>
       </c>
       <c r="F325" t="s">
-        <v>752</v>
+        <v>720</v>
       </c>
       <c r="G325" t="s">
         <v>34</v>
@@ -14576,10 +14576,10 @@
         <v>718</v>
       </c>
       <c r="E331" t="s">
-        <v>719</v>
+        <v>765</v>
       </c>
       <c r="F331" t="s">
-        <v>765</v>
+        <v>720</v>
       </c>
       <c r="G331" t="s">
         <v>25</v>
@@ -14852,10 +14852,10 @@
         <v>790</v>
       </c>
       <c r="E343" t="s">
-        <v>719</v>
+        <v>791</v>
       </c>
       <c r="F343" t="s">
-        <v>791</v>
+        <v>720</v>
       </c>
       <c r="G343" t="s">
         <v>34</v>
@@ -14875,10 +14875,10 @@
         <v>794</v>
       </c>
       <c r="E344" t="s">
-        <v>719</v>
+        <v>791</v>
       </c>
       <c r="F344" t="s">
-        <v>791</v>
+        <v>720</v>
       </c>
       <c r="G344" t="s">
         <v>34</v>
@@ -15496,10 +15496,10 @@
         <v>797</v>
       </c>
       <c r="E371" t="s">
-        <v>798</v>
+        <v>855</v>
       </c>
       <c r="F371" t="s">
-        <v>855</v>
+        <v>799</v>
       </c>
       <c r="G371" t="s">
         <v>25</v>
@@ -15519,10 +15519,10 @@
         <v>858</v>
       </c>
       <c r="E372" t="s">
-        <v>798</v>
+        <v>859</v>
       </c>
       <c r="F372" t="s">
-        <v>859</v>
+        <v>799</v>
       </c>
       <c r="G372" t="s">
         <v>25</v>
@@ -15565,10 +15565,10 @@
         <v>858</v>
       </c>
       <c r="E374" t="s">
-        <v>798</v>
+        <v>859</v>
       </c>
       <c r="F374" t="s">
-        <v>859</v>
+        <v>799</v>
       </c>
       <c r="G374" t="s">
         <v>25</v>
@@ -15910,10 +15910,10 @@
         <v>900</v>
       </c>
       <c r="E389" t="s">
-        <v>873</v>
+        <v>901</v>
       </c>
       <c r="F389" t="s">
-        <v>901</v>
+        <v>874</v>
       </c>
       <c r="G389" t="s">
         <v>34</v>
@@ -16048,10 +16048,10 @@
         <v>915</v>
       </c>
       <c r="E395" t="s">
-        <v>873</v>
+        <v>916</v>
       </c>
       <c r="F395" t="s">
-        <v>916</v>
+        <v>874</v>
       </c>
       <c r="G395" t="s">
         <v>34</v>
@@ -16094,10 +16094,10 @@
         <v>921</v>
       </c>
       <c r="E397" t="s">
-        <v>873</v>
+        <v>922</v>
       </c>
       <c r="F397" t="s">
-        <v>922</v>
+        <v>874</v>
       </c>
       <c r="G397" t="s">
         <v>34</v>
@@ -16163,10 +16163,10 @@
         <v>929</v>
       </c>
       <c r="E400" t="s">
-        <v>873</v>
+        <v>930</v>
       </c>
       <c r="F400" t="s">
-        <v>930</v>
+        <v>874</v>
       </c>
       <c r="G400" t="s">
         <v>34</v>
@@ -16301,10 +16301,10 @@
         <v>943</v>
       </c>
       <c r="E406" t="s">
-        <v>873</v>
+        <v>944</v>
       </c>
       <c r="F406" t="s">
-        <v>944</v>
+        <v>874</v>
       </c>
       <c r="G406" t="s">
         <v>34</v>
@@ -16807,10 +16807,10 @@
         <v>994</v>
       </c>
       <c r="E428" t="s">
-        <v>968</v>
+        <v>995</v>
       </c>
       <c r="F428" t="s">
-        <v>995</v>
+        <v>969</v>
       </c>
       <c r="G428" t="s">
         <v>34</v>
@@ -16830,10 +16830,10 @@
         <v>998</v>
       </c>
       <c r="E429" t="s">
-        <v>968</v>
+        <v>999</v>
       </c>
       <c r="F429" t="s">
-        <v>999</v>
+        <v>969</v>
       </c>
       <c r="G429" t="s">
         <v>34</v>
@@ -17083,10 +17083,10 @@
         <v>1025</v>
       </c>
       <c r="E440" t="s">
-        <v>968</v>
+        <v>1026</v>
       </c>
       <c r="F440" t="s">
-        <v>1026</v>
+        <v>969</v>
       </c>
       <c r="G440" t="s">
         <v>34</v>
@@ -17405,10 +17405,10 @@
         <v>1055</v>
       </c>
       <c r="E454" t="s">
-        <v>968</v>
+        <v>1056</v>
       </c>
       <c r="F454" t="s">
-        <v>1056</v>
+        <v>969</v>
       </c>
       <c r="G454" t="s">
         <v>25</v>
@@ -17635,10 +17635,10 @@
         <v>1081</v>
       </c>
       <c r="E464" t="s">
-        <v>1060</v>
+        <v>1082</v>
       </c>
       <c r="F464" t="s">
-        <v>1082</v>
+        <v>1061</v>
       </c>
       <c r="G464" t="s">
         <v>34</v>
@@ -17681,10 +17681,10 @@
         <v>1088</v>
       </c>
       <c r="E466" t="s">
-        <v>1060</v>
+        <v>1082</v>
       </c>
       <c r="F466" t="s">
-        <v>1082</v>
+        <v>1061</v>
       </c>
       <c r="G466" t="s">
         <v>34</v>
@@ -17704,10 +17704,10 @@
         <v>1091</v>
       </c>
       <c r="E467" t="s">
-        <v>1060</v>
+        <v>1092</v>
       </c>
       <c r="F467" t="s">
-        <v>1092</v>
+        <v>1061</v>
       </c>
       <c r="G467" t="s">
         <v>34</v>
@@ -17750,10 +17750,10 @@
         <v>1097</v>
       </c>
       <c r="E469" t="s">
-        <v>1060</v>
+        <v>1098</v>
       </c>
       <c r="F469" t="s">
-        <v>1098</v>
+        <v>1061</v>
       </c>
       <c r="G469" t="s">
         <v>34</v>
@@ -17842,10 +17842,10 @@
         <v>1107</v>
       </c>
       <c r="E473" t="s">
-        <v>1060</v>
+        <v>1082</v>
       </c>
       <c r="F473" t="s">
-        <v>1082</v>
+        <v>1061</v>
       </c>
       <c r="G473" t="s">
         <v>34</v>
@@ -18279,10 +18279,10 @@
         <v>1136</v>
       </c>
       <c r="E492" t="s">
-        <v>1137</v>
+        <v>1150</v>
       </c>
       <c r="F492" t="s">
-        <v>1150</v>
+        <v>1138</v>
       </c>
       <c r="G492" t="s">
         <v>25</v>
@@ -18325,10 +18325,10 @@
         <v>1097</v>
       </c>
       <c r="E494" t="s">
-        <v>1137</v>
+        <v>1155</v>
       </c>
       <c r="F494" t="s">
-        <v>1155</v>
+        <v>1138</v>
       </c>
       <c r="G494" t="s">
         <v>16</v>
@@ -18348,10 +18348,10 @@
         <v>1097</v>
       </c>
       <c r="E495" t="s">
-        <v>1137</v>
+        <v>1155</v>
       </c>
       <c r="F495" t="s">
-        <v>1155</v>
+        <v>1138</v>
       </c>
       <c r="G495" t="s">
         <v>20</v>
@@ -18624,10 +18624,10 @@
         <v>1184</v>
       </c>
       <c r="E507" t="s">
-        <v>1137</v>
+        <v>1185</v>
       </c>
       <c r="F507" t="s">
-        <v>1185</v>
+        <v>1138</v>
       </c>
       <c r="G507" t="s">
         <v>34</v>
@@ -18647,10 +18647,10 @@
         <v>1188</v>
       </c>
       <c r="E508" t="s">
-        <v>1137</v>
+        <v>1189</v>
       </c>
       <c r="F508" t="s">
-        <v>1189</v>
+        <v>1138</v>
       </c>
       <c r="G508" t="s">
         <v>1062</v>
@@ -18670,10 +18670,10 @@
         <v>1188</v>
       </c>
       <c r="E509" t="s">
-        <v>1137</v>
+        <v>1192</v>
       </c>
       <c r="F509" t="s">
-        <v>1192</v>
+        <v>1138</v>
       </c>
       <c r="G509" t="s">
         <v>25</v>
@@ -18693,10 +18693,10 @@
         <v>1195</v>
       </c>
       <c r="E510" t="s">
-        <v>1137</v>
+        <v>1196</v>
       </c>
       <c r="F510" t="s">
-        <v>1196</v>
+        <v>1138</v>
       </c>
       <c r="G510" t="s">
         <v>34</v>
@@ -18762,10 +18762,10 @@
         <v>1136</v>
       </c>
       <c r="E513" t="s">
-        <v>1137</v>
+        <v>1204</v>
       </c>
       <c r="F513" t="s">
-        <v>1204</v>
+        <v>1138</v>
       </c>
       <c r="G513" t="s">
         <v>25</v>
@@ -19153,10 +19153,10 @@
         <v>1141</v>
       </c>
       <c r="E530" t="s">
-        <v>1232</v>
+        <v>1246</v>
       </c>
       <c r="F530" t="s">
-        <v>1246</v>
+        <v>1233</v>
       </c>
       <c r="G530" t="s">
         <v>1234</v>
@@ -19383,10 +19383,10 @@
         <v>1141</v>
       </c>
       <c r="E540" t="s">
-        <v>1232</v>
+        <v>1196</v>
       </c>
       <c r="F540" t="s">
-        <v>1196</v>
+        <v>1233</v>
       </c>
       <c r="G540" t="s">
         <v>1234</v>
@@ -19498,10 +19498,10 @@
         <v>1141</v>
       </c>
       <c r="E545" t="s">
-        <v>1232</v>
+        <v>1279</v>
       </c>
       <c r="F545" t="s">
-        <v>1279</v>
+        <v>1233</v>
       </c>
       <c r="G545" t="s">
         <v>16</v>
@@ -19705,10 +19705,10 @@
         <v>1286</v>
       </c>
       <c r="E554" t="s">
-        <v>1287</v>
+        <v>1303</v>
       </c>
       <c r="F554" t="s">
-        <v>1303</v>
+        <v>1288</v>
       </c>
       <c r="G554" t="s">
         <v>1234</v>
@@ -19797,10 +19797,10 @@
         <v>1312</v>
       </c>
       <c r="E558" t="s">
-        <v>1287</v>
+        <v>1313</v>
       </c>
       <c r="F558" t="s">
-        <v>1313</v>
+        <v>1288</v>
       </c>
       <c r="G558" t="s">
         <v>34</v>
@@ -19912,10 +19912,10 @@
         <v>1286</v>
       </c>
       <c r="E563" t="s">
-        <v>1287</v>
+        <v>1325</v>
       </c>
       <c r="F563" t="s">
-        <v>1325</v>
+        <v>1288</v>
       </c>
       <c r="G563" t="s">
         <v>20</v>
@@ -20050,10 +20050,10 @@
         <v>1338</v>
       </c>
       <c r="E569" t="s">
-        <v>1287</v>
+        <v>1339</v>
       </c>
       <c r="F569" t="s">
-        <v>1339</v>
+        <v>1288</v>
       </c>
       <c r="G569" t="s">
         <v>1234</v>
@@ -20142,10 +20142,10 @@
         <v>1348</v>
       </c>
       <c r="E573" t="s">
+        <v>1232</v>
+      </c>
+      <c r="F573" t="s">
         <v>1349</v>
-      </c>
-      <c r="F573" t="s">
-        <v>1233</v>
       </c>
       <c r="G573" t="s">
         <v>1234</v>
@@ -20165,10 +20165,10 @@
         <v>1348</v>
       </c>
       <c r="E574" t="s">
+        <v>1352</v>
+      </c>
+      <c r="F574" t="s">
         <v>1349</v>
-      </c>
-      <c r="F574" t="s">
-        <v>1352</v>
       </c>
       <c r="G574" t="s">
         <v>1234</v>
@@ -20188,10 +20188,10 @@
         <v>1348</v>
       </c>
       <c r="E575" t="s">
+        <v>1352</v>
+      </c>
+      <c r="F575" t="s">
         <v>1349</v>
-      </c>
-      <c r="F575" t="s">
-        <v>1352</v>
       </c>
       <c r="G575" t="s">
         <v>1234</v>
@@ -20211,10 +20211,10 @@
         <v>1348</v>
       </c>
       <c r="E576" t="s">
+        <v>1352</v>
+      </c>
+      <c r="F576" t="s">
         <v>1349</v>
-      </c>
-      <c r="F576" t="s">
-        <v>1352</v>
       </c>
       <c r="G576" t="s">
         <v>1234</v>
@@ -20234,10 +20234,10 @@
         <v>1348</v>
       </c>
       <c r="E577" t="s">
+        <v>1287</v>
+      </c>
+      <c r="F577" t="s">
         <v>1349</v>
-      </c>
-      <c r="F577" t="s">
-        <v>1288</v>
       </c>
       <c r="G577" t="s">
         <v>1234</v>
@@ -20257,10 +20257,10 @@
         <v>1361</v>
       </c>
       <c r="E578" t="s">
+        <v>1352</v>
+      </c>
+      <c r="F578" t="s">
         <v>1349</v>
-      </c>
-      <c r="F578" t="s">
-        <v>1352</v>
       </c>
       <c r="G578" t="s">
         <v>1234</v>
@@ -20280,10 +20280,10 @@
         <v>1364</v>
       </c>
       <c r="E579" t="s">
+        <v>1365</v>
+      </c>
+      <c r="F579" t="s">
         <v>1349</v>
-      </c>
-      <c r="F579" t="s">
-        <v>1365</v>
       </c>
       <c r="G579" t="s">
         <v>34</v>
@@ -20303,10 +20303,10 @@
         <v>1368</v>
       </c>
       <c r="E580" t="s">
+        <v>1352</v>
+      </c>
+      <c r="F580" t="s">
         <v>1349</v>
-      </c>
-      <c r="F580" t="s">
-        <v>1352</v>
       </c>
       <c r="G580" t="s">
         <v>1234</v>
@@ -20326,10 +20326,10 @@
         <v>1371</v>
       </c>
       <c r="E581" t="s">
+        <v>1352</v>
+      </c>
+      <c r="F581" t="s">
         <v>1349</v>
-      </c>
-      <c r="F581" t="s">
-        <v>1352</v>
       </c>
       <c r="G581" t="s">
         <v>20</v>
@@ -20349,10 +20349,10 @@
         <v>1348</v>
       </c>
       <c r="E582" t="s">
+        <v>1352</v>
+      </c>
+      <c r="F582" t="s">
         <v>1349</v>
-      </c>
-      <c r="F582" t="s">
-        <v>1352</v>
       </c>
       <c r="G582" t="s">
         <v>20</v>
@@ -20372,10 +20372,10 @@
         <v>1376</v>
       </c>
       <c r="E583" t="s">
+        <v>1377</v>
+      </c>
+      <c r="F583" t="s">
         <v>1349</v>
-      </c>
-      <c r="F583" t="s">
-        <v>1377</v>
       </c>
       <c r="G583" t="s">
         <v>34</v>
@@ -20395,10 +20395,10 @@
         <v>1380</v>
       </c>
       <c r="E584" t="s">
+        <v>1381</v>
+      </c>
+      <c r="F584" t="s">
         <v>1349</v>
-      </c>
-      <c r="F584" t="s">
-        <v>1381</v>
       </c>
       <c r="G584" t="s">
         <v>34</v>
@@ -20418,10 +20418,10 @@
         <v>1348</v>
       </c>
       <c r="E585" t="s">
+        <v>1352</v>
+      </c>
+      <c r="F585" t="s">
         <v>1349</v>
-      </c>
-      <c r="F585" t="s">
-        <v>1352</v>
       </c>
       <c r="G585" t="s">
         <v>1234</v>
@@ -20441,10 +20441,10 @@
         <v>1386</v>
       </c>
       <c r="E586" t="s">
+        <v>1387</v>
+      </c>
+      <c r="F586" t="s">
         <v>1349</v>
-      </c>
-      <c r="F586" t="s">
-        <v>1387</v>
       </c>
       <c r="G586" t="s">
         <v>34</v>
@@ -20464,10 +20464,10 @@
         <v>1390</v>
       </c>
       <c r="E587" t="s">
+        <v>1352</v>
+      </c>
+      <c r="F587" t="s">
         <v>1349</v>
-      </c>
-      <c r="F587" t="s">
-        <v>1352</v>
       </c>
       <c r="G587" t="s">
         <v>16</v>
@@ -20487,10 +20487,10 @@
         <v>1393</v>
       </c>
       <c r="E588" t="s">
+        <v>1352</v>
+      </c>
+      <c r="F588" t="s">
         <v>1349</v>
-      </c>
-      <c r="F588" t="s">
-        <v>1352</v>
       </c>
       <c r="G588" t="s">
         <v>1234</v>
@@ -20510,10 +20510,10 @@
         <v>1348</v>
       </c>
       <c r="E589" t="s">
+        <v>1352</v>
+      </c>
+      <c r="F589" t="s">
         <v>1349</v>
-      </c>
-      <c r="F589" t="s">
-        <v>1352</v>
       </c>
       <c r="G589" t="s">
         <v>1234</v>
@@ -20533,10 +20533,10 @@
         <v>1348</v>
       </c>
       <c r="E590" t="s">
+        <v>1352</v>
+      </c>
+      <c r="F590" t="s">
         <v>1349</v>
-      </c>
-      <c r="F590" t="s">
-        <v>1352</v>
       </c>
       <c r="G590" t="s">
         <v>34</v>
@@ -20556,10 +20556,10 @@
         <v>1348</v>
       </c>
       <c r="E591" t="s">
+        <v>1352</v>
+      </c>
+      <c r="F591" t="s">
         <v>1349</v>
-      </c>
-      <c r="F591" t="s">
-        <v>1352</v>
       </c>
       <c r="G591" t="s">
         <v>20</v>
@@ -20579,10 +20579,10 @@
         <v>1348</v>
       </c>
       <c r="E592" t="s">
+        <v>1402</v>
+      </c>
+      <c r="F592" t="s">
         <v>1349</v>
-      </c>
-      <c r="F592" t="s">
-        <v>1402</v>
       </c>
       <c r="G592" t="s">
         <v>1234</v>
@@ -20602,10 +20602,10 @@
         <v>1348</v>
       </c>
       <c r="E593" t="s">
+        <v>1352</v>
+      </c>
+      <c r="F593" t="s">
         <v>1349</v>
-      </c>
-      <c r="F593" t="s">
-        <v>1352</v>
       </c>
       <c r="G593" t="s">
         <v>16</v>
@@ -20625,10 +20625,10 @@
         <v>1348</v>
       </c>
       <c r="E594" t="s">
+        <v>1352</v>
+      </c>
+      <c r="F594" t="s">
         <v>1349</v>
-      </c>
-      <c r="F594" t="s">
-        <v>1352</v>
       </c>
       <c r="G594" t="s">
         <v>1234</v>
@@ -20648,10 +20648,10 @@
         <v>1348</v>
       </c>
       <c r="E595" t="s">
+        <v>1352</v>
+      </c>
+      <c r="F595" t="s">
         <v>1349</v>
-      </c>
-      <c r="F595" t="s">
-        <v>1352</v>
       </c>
       <c r="G595" t="s">
         <v>1234</v>
@@ -20671,10 +20671,10 @@
         <v>1348</v>
       </c>
       <c r="E596" t="s">
+        <v>1352</v>
+      </c>
+      <c r="F596" t="s">
         <v>1349</v>
-      </c>
-      <c r="F596" t="s">
-        <v>1352</v>
       </c>
       <c r="G596" t="s">
         <v>1234</v>
@@ -20717,10 +20717,10 @@
         <v>1418</v>
       </c>
       <c r="E598" t="s">
-        <v>1414</v>
+        <v>1419</v>
       </c>
       <c r="F598" t="s">
-        <v>1419</v>
+        <v>1415</v>
       </c>
       <c r="G598" t="s">
         <v>20</v>
@@ -20809,10 +20809,10 @@
         <v>1428</v>
       </c>
       <c r="E602" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="F602" t="s">
-        <v>1429</v>
+        <v>1415</v>
       </c>
       <c r="G602" t="s">
         <v>34</v>
@@ -20832,10 +20832,10 @@
         <v>1432</v>
       </c>
       <c r="E603" t="s">
-        <v>1414</v>
+        <v>1433</v>
       </c>
       <c r="F603" t="s">
-        <v>1433</v>
+        <v>1415</v>
       </c>
       <c r="G603" t="s">
         <v>34</v>
@@ -20855,10 +20855,10 @@
         <v>1436</v>
       </c>
       <c r="E604" t="s">
-        <v>1414</v>
+        <v>1437</v>
       </c>
       <c r="F604" t="s">
-        <v>1437</v>
+        <v>1415</v>
       </c>
       <c r="G604" t="s">
         <v>1234</v>
@@ -20947,10 +20947,10 @@
         <v>1447</v>
       </c>
       <c r="E608" t="s">
-        <v>1414</v>
+        <v>1448</v>
       </c>
       <c r="F608" t="s">
-        <v>1448</v>
+        <v>1415</v>
       </c>
       <c r="G608" t="s">
         <v>34</v>
@@ -20970,10 +20970,10 @@
         <v>1451</v>
       </c>
       <c r="E609" t="s">
-        <v>1414</v>
+        <v>1390</v>
       </c>
       <c r="F609" t="s">
-        <v>1390</v>
+        <v>1415</v>
       </c>
       <c r="G609" t="s">
         <v>1234</v>
@@ -21016,10 +21016,10 @@
         <v>1418</v>
       </c>
       <c r="E611" t="s">
-        <v>1414</v>
+        <v>1456</v>
       </c>
       <c r="F611" t="s">
-        <v>1456</v>
+        <v>1415</v>
       </c>
       <c r="G611" t="s">
         <v>34</v>
@@ -21315,10 +21315,10 @@
         <v>1488</v>
       </c>
       <c r="E624" t="s">
-        <v>1484</v>
+        <v>1489</v>
       </c>
       <c r="F624" t="s">
-        <v>1489</v>
+        <v>1485</v>
       </c>
       <c r="G624" t="s">
         <v>34</v>
@@ -21407,10 +21407,10 @@
         <v>1483</v>
       </c>
       <c r="E628" t="s">
-        <v>1484</v>
+        <v>1498</v>
       </c>
       <c r="F628" t="s">
-        <v>1498</v>
+        <v>1485</v>
       </c>
       <c r="G628" t="s">
         <v>1234</v>
@@ -21499,10 +21499,10 @@
         <v>1501</v>
       </c>
       <c r="E632" t="s">
-        <v>1484</v>
+        <v>1508</v>
       </c>
       <c r="F632" t="s">
-        <v>1508</v>
+        <v>1485</v>
       </c>
       <c r="G632" t="s">
         <v>34</v>
@@ -21522,10 +21522,10 @@
         <v>1511</v>
       </c>
       <c r="E633" t="s">
-        <v>1484</v>
+        <v>1512</v>
       </c>
       <c r="F633" t="s">
-        <v>1512</v>
+        <v>1485</v>
       </c>
       <c r="G633" t="s">
         <v>34</v>
@@ -21545,10 +21545,10 @@
         <v>1515</v>
       </c>
       <c r="E634" t="s">
-        <v>1484</v>
+        <v>1516</v>
       </c>
       <c r="F634" t="s">
-        <v>1516</v>
+        <v>1485</v>
       </c>
       <c r="G634" t="s">
         <v>34</v>
@@ -21614,10 +21614,10 @@
         <v>1524</v>
       </c>
       <c r="E637" t="s">
-        <v>1484</v>
+        <v>1525</v>
       </c>
       <c r="F637" t="s">
-        <v>1525</v>
+        <v>1485</v>
       </c>
       <c r="G637" t="s">
         <v>34</v>
@@ -21706,10 +21706,10 @@
         <v>1534</v>
       </c>
       <c r="E641" t="s">
-        <v>1484</v>
+        <v>1535</v>
       </c>
       <c r="F641" t="s">
-        <v>1535</v>
+        <v>1485</v>
       </c>
       <c r="G641" t="s">
         <v>20</v>
@@ -21913,10 +21913,10 @@
         <v>1560</v>
       </c>
       <c r="E650" t="s">
-        <v>1556</v>
+        <v>1561</v>
       </c>
       <c r="F650" t="s">
-        <v>1561</v>
+        <v>1557</v>
       </c>
       <c r="G650" t="s">
         <v>20</v>
@@ -21936,10 +21936,10 @@
         <v>1555</v>
       </c>
       <c r="E651" t="s">
-        <v>1556</v>
+        <v>1564</v>
       </c>
       <c r="F651" t="s">
-        <v>1564</v>
+        <v>1557</v>
       </c>
       <c r="G651" t="s">
         <v>34</v>
@@ -21959,10 +21959,10 @@
         <v>1567</v>
       </c>
       <c r="E652" t="s">
-        <v>1556</v>
+        <v>1568</v>
       </c>
       <c r="F652" t="s">
-        <v>1568</v>
+        <v>1557</v>
       </c>
       <c r="G652" t="s">
         <v>1234</v>
@@ -21982,10 +21982,10 @@
         <v>1567</v>
       </c>
       <c r="E653" t="s">
-        <v>1556</v>
+        <v>1568</v>
       </c>
       <c r="F653" t="s">
-        <v>1568</v>
+        <v>1557</v>
       </c>
       <c r="G653" t="s">
         <v>1234</v>
@@ -22005,10 +22005,10 @@
         <v>1541</v>
       </c>
       <c r="E654" t="s">
-        <v>1556</v>
+        <v>1484</v>
       </c>
       <c r="F654" t="s">
-        <v>1485</v>
+        <v>1557</v>
       </c>
       <c r="G654" t="s">
         <v>20</v>
@@ -22028,10 +22028,10 @@
         <v>1567</v>
       </c>
       <c r="E655" t="s">
-        <v>1556</v>
+        <v>1568</v>
       </c>
       <c r="F655" t="s">
-        <v>1568</v>
+        <v>1557</v>
       </c>
       <c r="G655" t="s">
         <v>1234</v>
@@ -22051,10 +22051,10 @@
         <v>1567</v>
       </c>
       <c r="E656" t="s">
-        <v>1556</v>
+        <v>1568</v>
       </c>
       <c r="F656" t="s">
-        <v>1568</v>
+        <v>1557</v>
       </c>
       <c r="G656" t="s">
         <v>1234</v>
@@ -22074,10 +22074,10 @@
         <v>1579</v>
       </c>
       <c r="E657" t="s">
-        <v>1556</v>
+        <v>1580</v>
       </c>
       <c r="F657" t="s">
-        <v>1580</v>
+        <v>1557</v>
       </c>
       <c r="G657" t="s">
         <v>20</v>
@@ -22097,10 +22097,10 @@
         <v>1583</v>
       </c>
       <c r="E658" t="s">
-        <v>1556</v>
+        <v>1584</v>
       </c>
       <c r="F658" t="s">
-        <v>1584</v>
+        <v>1557</v>
       </c>
       <c r="G658" t="s">
         <v>34</v>
@@ -22120,10 +22120,10 @@
         <v>1521</v>
       </c>
       <c r="E659" t="s">
-        <v>1556</v>
+        <v>1587</v>
       </c>
       <c r="F659" t="s">
-        <v>1587</v>
+        <v>1557</v>
       </c>
       <c r="G659" t="s">
         <v>34</v>
@@ -22143,10 +22143,10 @@
         <v>1590</v>
       </c>
       <c r="E660" t="s">
-        <v>1556</v>
+        <v>1591</v>
       </c>
       <c r="F660" t="s">
-        <v>1591</v>
+        <v>1557</v>
       </c>
       <c r="G660" t="s">
         <v>34</v>
@@ -22166,10 +22166,10 @@
         <v>1567</v>
       </c>
       <c r="E661" t="s">
-        <v>1556</v>
+        <v>1568</v>
       </c>
       <c r="F661" t="s">
-        <v>1568</v>
+        <v>1557</v>
       </c>
       <c r="G661" t="s">
         <v>1234</v>
@@ -22189,10 +22189,10 @@
         <v>1567</v>
       </c>
       <c r="E662" t="s">
-        <v>1556</v>
+        <v>1560</v>
       </c>
       <c r="F662" t="s">
-        <v>1560</v>
+        <v>1557</v>
       </c>
       <c r="G662" t="s">
         <v>34</v>
@@ -22212,10 +22212,10 @@
         <v>1598</v>
       </c>
       <c r="E663" t="s">
-        <v>1556</v>
+        <v>1599</v>
       </c>
       <c r="F663" t="s">
-        <v>1599</v>
+        <v>1557</v>
       </c>
       <c r="G663" t="s">
         <v>34</v>
@@ -22235,10 +22235,10 @@
         <v>1541</v>
       </c>
       <c r="E664" t="s">
-        <v>1556</v>
+        <v>1602</v>
       </c>
       <c r="F664" t="s">
-        <v>1602</v>
+        <v>1557</v>
       </c>
       <c r="G664" t="s">
         <v>20</v>
@@ -22258,10 +22258,10 @@
         <v>1605</v>
       </c>
       <c r="E665" t="s">
-        <v>1556</v>
+        <v>1568</v>
       </c>
       <c r="F665" t="s">
-        <v>1568</v>
+        <v>1557</v>
       </c>
       <c r="G665" t="s">
         <v>1234</v>
@@ -22304,10 +22304,10 @@
         <v>1610</v>
       </c>
       <c r="E667" t="s">
-        <v>1556</v>
+        <v>1611</v>
       </c>
       <c r="F667" t="s">
-        <v>1611</v>
+        <v>1557</v>
       </c>
       <c r="G667" t="s">
         <v>34</v>
@@ -22327,10 +22327,10 @@
         <v>1567</v>
       </c>
       <c r="E668" t="s">
-        <v>1556</v>
+        <v>1568</v>
       </c>
       <c r="F668" t="s">
-        <v>1568</v>
+        <v>1557</v>
       </c>
       <c r="G668" t="s">
         <v>20</v>
@@ -22350,10 +22350,10 @@
         <v>1541</v>
       </c>
       <c r="E669" t="s">
-        <v>1556</v>
+        <v>1587</v>
       </c>
       <c r="F669" t="s">
-        <v>1587</v>
+        <v>1557</v>
       </c>
       <c r="G669" t="s">
         <v>20</v>
@@ -22373,10 +22373,10 @@
         <v>1567</v>
       </c>
       <c r="E670" t="s">
-        <v>1556</v>
+        <v>1568</v>
       </c>
       <c r="F670" t="s">
-        <v>1568</v>
+        <v>1557</v>
       </c>
       <c r="G670" t="s">
         <v>1234</v>
@@ -22396,10 +22396,10 @@
         <v>1555</v>
       </c>
       <c r="E671" t="s">
-        <v>1556</v>
+        <v>1620</v>
       </c>
       <c r="F671" t="s">
-        <v>1620</v>
+        <v>1557</v>
       </c>
       <c r="G671" t="s">
         <v>34</v>
@@ -22419,10 +22419,10 @@
         <v>1567</v>
       </c>
       <c r="E672" t="s">
-        <v>1556</v>
+        <v>1568</v>
       </c>
       <c r="F672" t="s">
-        <v>1568</v>
+        <v>1557</v>
       </c>
       <c r="G672" t="s">
         <v>20</v>
@@ -22442,10 +22442,10 @@
         <v>1567</v>
       </c>
       <c r="E673" t="s">
-        <v>1556</v>
+        <v>1568</v>
       </c>
       <c r="F673" t="s">
-        <v>1568</v>
+        <v>1557</v>
       </c>
       <c r="G673" t="s">
         <v>1234</v>
@@ -22465,10 +22465,10 @@
         <v>1541</v>
       </c>
       <c r="E674" t="s">
-        <v>1556</v>
+        <v>1591</v>
       </c>
       <c r="F674" t="s">
-        <v>1591</v>
+        <v>1557</v>
       </c>
       <c r="G674" t="s">
         <v>20</v>
@@ -22488,10 +22488,10 @@
         <v>1555</v>
       </c>
       <c r="E675" t="s">
-        <v>1556</v>
+        <v>1564</v>
       </c>
       <c r="F675" t="s">
-        <v>1564</v>
+        <v>1557</v>
       </c>
       <c r="G675" t="s">
         <v>34</v>
@@ -22511,10 +22511,10 @@
         <v>1631</v>
       </c>
       <c r="E676" t="s">
-        <v>1556</v>
+        <v>1568</v>
       </c>
       <c r="F676" t="s">
-        <v>1568</v>
+        <v>1557</v>
       </c>
       <c r="G676" t="s">
         <v>20</v>
@@ -22534,10 +22534,10 @@
         <v>1567</v>
       </c>
       <c r="E677" t="s">
-        <v>1556</v>
+        <v>1568</v>
       </c>
       <c r="F677" t="s">
-        <v>1568</v>
+        <v>1557</v>
       </c>
       <c r="G677" t="s">
         <v>1234</v>
@@ -22557,10 +22557,10 @@
         <v>1567</v>
       </c>
       <c r="E678" t="s">
-        <v>1556</v>
+        <v>1568</v>
       </c>
       <c r="F678" t="s">
-        <v>1568</v>
+        <v>1557</v>
       </c>
       <c r="G678" t="s">
         <v>1234</v>
@@ -22580,10 +22580,10 @@
         <v>1590</v>
       </c>
       <c r="E679" t="s">
-        <v>1556</v>
+        <v>1591</v>
       </c>
       <c r="F679" t="s">
-        <v>1591</v>
+        <v>1557</v>
       </c>
       <c r="G679" t="s">
         <v>34</v>
@@ -22603,10 +22603,10 @@
         <v>1567</v>
       </c>
       <c r="E680" t="s">
-        <v>1556</v>
+        <v>1568</v>
       </c>
       <c r="F680" t="s">
-        <v>1568</v>
+        <v>1557</v>
       </c>
       <c r="G680" t="s">
         <v>1234</v>
@@ -22626,10 +22626,10 @@
         <v>1567</v>
       </c>
       <c r="E681" t="s">
-        <v>1556</v>
+        <v>1568</v>
       </c>
       <c r="F681" t="s">
-        <v>1568</v>
+        <v>1557</v>
       </c>
       <c r="G681" t="s">
         <v>1234</v>
@@ -22672,10 +22672,10 @@
         <v>1649</v>
       </c>
       <c r="E683" t="s">
-        <v>1645</v>
+        <v>1650</v>
       </c>
       <c r="F683" t="s">
-        <v>1650</v>
+        <v>1646</v>
       </c>
       <c r="G683" t="s">
         <v>34</v>
@@ -22695,10 +22695,10 @@
         <v>1653</v>
       </c>
       <c r="E684" t="s">
-        <v>1645</v>
+        <v>1654</v>
       </c>
       <c r="F684" t="s">
-        <v>1654</v>
+        <v>1646</v>
       </c>
       <c r="G684" t="s">
         <v>1234</v>
@@ -22718,10 +22718,10 @@
         <v>1653</v>
       </c>
       <c r="E685" t="s">
-        <v>1645</v>
+        <v>1654</v>
       </c>
       <c r="F685" t="s">
-        <v>1654</v>
+        <v>1646</v>
       </c>
       <c r="G685" t="s">
         <v>1234</v>
@@ -22741,10 +22741,10 @@
         <v>1653</v>
       </c>
       <c r="E686" t="s">
-        <v>1645</v>
+        <v>1654</v>
       </c>
       <c r="F686" t="s">
-        <v>1654</v>
+        <v>1646</v>
       </c>
       <c r="G686" t="s">
         <v>1234</v>
@@ -22764,10 +22764,10 @@
         <v>1653</v>
       </c>
       <c r="E687" t="s">
-        <v>1645</v>
+        <v>1654</v>
       </c>
       <c r="F687" t="s">
-        <v>1654</v>
+        <v>1646</v>
       </c>
       <c r="G687" t="s">
         <v>1234</v>
@@ -22787,10 +22787,10 @@
         <v>1653</v>
       </c>
       <c r="E688" t="s">
-        <v>1645</v>
+        <v>1654</v>
       </c>
       <c r="F688" t="s">
-        <v>1654</v>
+        <v>1646</v>
       </c>
       <c r="G688" t="s">
         <v>1234</v>
@@ -22810,10 +22810,10 @@
         <v>1649</v>
       </c>
       <c r="E689" t="s">
-        <v>1645</v>
+        <v>1665</v>
       </c>
       <c r="F689" t="s">
-        <v>1665</v>
+        <v>1646</v>
       </c>
       <c r="G689" t="s">
         <v>34</v>
@@ -22833,10 +22833,10 @@
         <v>1668</v>
       </c>
       <c r="E690" t="s">
-        <v>1645</v>
+        <v>1669</v>
       </c>
       <c r="F690" t="s">
-        <v>1669</v>
+        <v>1646</v>
       </c>
       <c r="G690" t="s">
         <v>34</v>
@@ -22856,10 +22856,10 @@
         <v>1653</v>
       </c>
       <c r="E691" t="s">
-        <v>1645</v>
+        <v>1654</v>
       </c>
       <c r="F691" t="s">
-        <v>1654</v>
+        <v>1646</v>
       </c>
       <c r="G691" t="s">
         <v>16</v>
@@ -22879,10 +22879,10 @@
         <v>1674</v>
       </c>
       <c r="E692" t="s">
-        <v>1645</v>
+        <v>1568</v>
       </c>
       <c r="F692" t="s">
-        <v>1568</v>
+        <v>1646</v>
       </c>
       <c r="G692" t="s">
         <v>20</v>
@@ -22902,10 +22902,10 @@
         <v>1677</v>
       </c>
       <c r="E693" t="s">
-        <v>1645</v>
+        <v>1678</v>
       </c>
       <c r="F693" t="s">
-        <v>1678</v>
+        <v>1646</v>
       </c>
       <c r="G693" t="s">
         <v>34</v>
@@ -22925,10 +22925,10 @@
         <v>1681</v>
       </c>
       <c r="E694" t="s">
-        <v>1645</v>
+        <v>1682</v>
       </c>
       <c r="F694" t="s">
-        <v>1682</v>
+        <v>1646</v>
       </c>
       <c r="G694" t="s">
         <v>20</v>
@@ -22948,10 +22948,10 @@
         <v>1685</v>
       </c>
       <c r="E695" t="s">
-        <v>1645</v>
+        <v>1686</v>
       </c>
       <c r="F695" t="s">
-        <v>1686</v>
+        <v>1646</v>
       </c>
       <c r="G695" t="s">
         <v>34</v>
@@ -22971,10 +22971,10 @@
         <v>1653</v>
       </c>
       <c r="E696" t="s">
-        <v>1645</v>
+        <v>1654</v>
       </c>
       <c r="F696" t="s">
-        <v>1654</v>
+        <v>1646</v>
       </c>
       <c r="G696" t="s">
         <v>1234</v>
@@ -22994,10 +22994,10 @@
         <v>1691</v>
       </c>
       <c r="E697" t="s">
-        <v>1645</v>
+        <v>1692</v>
       </c>
       <c r="F697" t="s">
-        <v>1692</v>
+        <v>1646</v>
       </c>
       <c r="G697" t="s">
         <v>34</v>
@@ -23017,10 +23017,10 @@
         <v>1695</v>
       </c>
       <c r="E698" t="s">
-        <v>1645</v>
+        <v>1696</v>
       </c>
       <c r="F698" t="s">
-        <v>1696</v>
+        <v>1646</v>
       </c>
       <c r="G698" t="s">
         <v>34</v>
@@ -23040,10 +23040,10 @@
         <v>1653</v>
       </c>
       <c r="E699" t="s">
-        <v>1645</v>
+        <v>1654</v>
       </c>
       <c r="F699" t="s">
-        <v>1654</v>
+        <v>1646</v>
       </c>
       <c r="G699" t="s">
         <v>20</v>
@@ -23063,10 +23063,10 @@
         <v>1701</v>
       </c>
       <c r="E700" t="s">
-        <v>1645</v>
+        <v>1702</v>
       </c>
       <c r="F700" t="s">
-        <v>1702</v>
+        <v>1646</v>
       </c>
       <c r="G700" t="s">
         <v>34</v>
@@ -23086,10 +23086,10 @@
         <v>1653</v>
       </c>
       <c r="E701" t="s">
-        <v>1645</v>
+        <v>1654</v>
       </c>
       <c r="F701" t="s">
-        <v>1654</v>
+        <v>1646</v>
       </c>
       <c r="G701" t="s">
         <v>20</v>
@@ -23109,10 +23109,10 @@
         <v>1707</v>
       </c>
       <c r="E702" t="s">
-        <v>1645</v>
+        <v>1708</v>
       </c>
       <c r="F702" t="s">
-        <v>1708</v>
+        <v>1646</v>
       </c>
       <c r="G702" t="s">
         <v>34</v>
@@ -23132,10 +23132,10 @@
         <v>1711</v>
       </c>
       <c r="E703" t="s">
-        <v>1645</v>
+        <v>1702</v>
       </c>
       <c r="F703" t="s">
-        <v>1702</v>
+        <v>1646</v>
       </c>
       <c r="G703" t="s">
         <v>34</v>
@@ -23155,10 +23155,10 @@
         <v>1653</v>
       </c>
       <c r="E704" t="s">
-        <v>1645</v>
+        <v>1654</v>
       </c>
       <c r="F704" t="s">
-        <v>1654</v>
+        <v>1646</v>
       </c>
       <c r="G704" t="s">
         <v>1234</v>
@@ -23178,10 +23178,10 @@
         <v>1716</v>
       </c>
       <c r="E705" t="s">
-        <v>1645</v>
+        <v>1696</v>
       </c>
       <c r="F705" t="s">
-        <v>1696</v>
+        <v>1646</v>
       </c>
       <c r="G705" t="s">
         <v>20</v>
@@ -23201,10 +23201,10 @@
         <v>1653</v>
       </c>
       <c r="E706" t="s">
-        <v>1645</v>
+        <v>1654</v>
       </c>
       <c r="F706" t="s">
-        <v>1654</v>
+        <v>1646</v>
       </c>
       <c r="G706" t="s">
         <v>1234</v>
@@ -23224,10 +23224,10 @@
         <v>1653</v>
       </c>
       <c r="E707" t="s">
-        <v>1645</v>
+        <v>1696</v>
       </c>
       <c r="F707" t="s">
-        <v>1696</v>
+        <v>1646</v>
       </c>
       <c r="G707" t="s">
         <v>20</v>
@@ -23247,10 +23247,10 @@
         <v>1723</v>
       </c>
       <c r="E708" t="s">
-        <v>1645</v>
+        <v>1650</v>
       </c>
       <c r="F708" t="s">
-        <v>1650</v>
+        <v>1646</v>
       </c>
       <c r="G708" t="s">
         <v>34</v>
@@ -23270,10 +23270,10 @@
         <v>1653</v>
       </c>
       <c r="E709" t="s">
-        <v>1645</v>
+        <v>1654</v>
       </c>
       <c r="F709" t="s">
-        <v>1654</v>
+        <v>1646</v>
       </c>
       <c r="G709" t="s">
         <v>1234</v>
@@ -23293,10 +23293,10 @@
         <v>1728</v>
       </c>
       <c r="E710" t="s">
-        <v>1645</v>
+        <v>1729</v>
       </c>
       <c r="F710" t="s">
-        <v>1729</v>
+        <v>1646</v>
       </c>
       <c r="G710" t="s">
         <v>34</v>
@@ -23316,10 +23316,10 @@
         <v>1653</v>
       </c>
       <c r="E711" t="s">
-        <v>1645</v>
+        <v>1696</v>
       </c>
       <c r="F711" t="s">
-        <v>1696</v>
+        <v>1646</v>
       </c>
       <c r="G711" t="s">
         <v>1234</v>
@@ -23339,10 +23339,10 @@
         <v>1653</v>
       </c>
       <c r="E712" t="s">
-        <v>1645</v>
+        <v>1654</v>
       </c>
       <c r="F712" t="s">
-        <v>1654</v>
+        <v>1646</v>
       </c>
       <c r="G712" t="s">
         <v>1234</v>
@@ -23362,10 +23362,10 @@
         <v>1668</v>
       </c>
       <c r="E713" t="s">
-        <v>1645</v>
+        <v>1669</v>
       </c>
       <c r="F713" t="s">
-        <v>1669</v>
+        <v>1646</v>
       </c>
       <c r="G713" t="s">
         <v>34</v>
@@ -23385,10 +23385,10 @@
         <v>1653</v>
       </c>
       <c r="E714" t="s">
-        <v>1645</v>
+        <v>1654</v>
       </c>
       <c r="F714" t="s">
-        <v>1654</v>
+        <v>1646</v>
       </c>
       <c r="G714" t="s">
         <v>1234</v>
@@ -23408,10 +23408,10 @@
         <v>1691</v>
       </c>
       <c r="E715" t="s">
-        <v>1645</v>
+        <v>1696</v>
       </c>
       <c r="F715" t="s">
-        <v>1696</v>
+        <v>1646</v>
       </c>
       <c r="G715" t="s">
         <v>34</v>
@@ -23431,10 +23431,10 @@
         <v>1653</v>
       </c>
       <c r="E716" t="s">
-        <v>1645</v>
+        <v>1654</v>
       </c>
       <c r="F716" t="s">
-        <v>1654</v>
+        <v>1646</v>
       </c>
       <c r="G716" t="s">
         <v>1234</v>
@@ -23454,10 +23454,10 @@
         <v>1653</v>
       </c>
       <c r="E717" t="s">
-        <v>1645</v>
+        <v>1654</v>
       </c>
       <c r="F717" t="s">
-        <v>1654</v>
+        <v>1646</v>
       </c>
       <c r="G717" t="s">
         <v>1234</v>
@@ -23638,10 +23638,10 @@
         <v>1764</v>
       </c>
       <c r="E725" t="s">
-        <v>1747</v>
+        <v>1765</v>
       </c>
       <c r="F725" t="s">
-        <v>1765</v>
+        <v>1748</v>
       </c>
       <c r="G725" t="s">
         <v>20</v>
@@ -23661,10 +23661,10 @@
         <v>1768</v>
       </c>
       <c r="E726" t="s">
-        <v>1747</v>
+        <v>1769</v>
       </c>
       <c r="F726" t="s">
-        <v>1769</v>
+        <v>1748</v>
       </c>
       <c r="G726" t="s">
         <v>20</v>
@@ -23730,10 +23730,10 @@
         <v>1776</v>
       </c>
       <c r="E729" t="s">
-        <v>1747</v>
+        <v>1777</v>
       </c>
       <c r="F729" t="s">
-        <v>1777</v>
+        <v>1748</v>
       </c>
       <c r="G729" t="s">
         <v>34</v>
@@ -23776,10 +23776,10 @@
         <v>1776</v>
       </c>
       <c r="E731" t="s">
-        <v>1747</v>
+        <v>1777</v>
       </c>
       <c r="F731" t="s">
-        <v>1777</v>
+        <v>1748</v>
       </c>
       <c r="G731" t="s">
         <v>34</v>
@@ -23799,10 +23799,10 @@
         <v>1784</v>
       </c>
       <c r="E732" t="s">
-        <v>1747</v>
+        <v>1785</v>
       </c>
       <c r="F732" t="s">
-        <v>1785</v>
+        <v>1748</v>
       </c>
       <c r="G732" t="s">
         <v>34</v>
@@ -23845,10 +23845,10 @@
         <v>1791</v>
       </c>
       <c r="E734" t="s">
-        <v>1747</v>
+        <v>1792</v>
       </c>
       <c r="F734" t="s">
-        <v>1792</v>
+        <v>1748</v>
       </c>
       <c r="G734" t="s">
         <v>34</v>
@@ -23937,10 +23937,10 @@
         <v>1802</v>
       </c>
       <c r="E738" t="s">
-        <v>1747</v>
+        <v>1654</v>
       </c>
       <c r="F738" t="s">
-        <v>1654</v>
+        <v>1748</v>
       </c>
       <c r="G738" t="s">
         <v>20</v>
@@ -24006,10 +24006,10 @@
         <v>1809</v>
       </c>
       <c r="E741" t="s">
-        <v>1747</v>
+        <v>1810</v>
       </c>
       <c r="F741" t="s">
-        <v>1810</v>
+        <v>1748</v>
       </c>
       <c r="G741" t="s">
         <v>34</v>
@@ -24236,10 +24236,10 @@
         <v>1836</v>
       </c>
       <c r="E751" t="s">
-        <v>1832</v>
+        <v>1837</v>
       </c>
       <c r="F751" t="s">
-        <v>1837</v>
+        <v>1833</v>
       </c>
       <c r="G751" t="s">
         <v>34</v>
@@ -24259,10 +24259,10 @@
         <v>1840</v>
       </c>
       <c r="E752" t="s">
-        <v>1832</v>
+        <v>1841</v>
       </c>
       <c r="F752" t="s">
-        <v>1841</v>
+        <v>1833</v>
       </c>
       <c r="G752" t="s">
         <v>1234</v>
@@ -24282,10 +24282,10 @@
         <v>1840</v>
       </c>
       <c r="E753" t="s">
-        <v>1832</v>
+        <v>1841</v>
       </c>
       <c r="F753" t="s">
-        <v>1841</v>
+        <v>1833</v>
       </c>
       <c r="G753" t="s">
         <v>1234</v>
@@ -24305,10 +24305,10 @@
         <v>1840</v>
       </c>
       <c r="E754" t="s">
-        <v>1832</v>
+        <v>1841</v>
       </c>
       <c r="F754" t="s">
-        <v>1841</v>
+        <v>1833</v>
       </c>
       <c r="G754" t="s">
         <v>1234</v>
@@ -24328,10 +24328,10 @@
         <v>1840</v>
       </c>
       <c r="E755" t="s">
-        <v>1832</v>
+        <v>1841</v>
       </c>
       <c r="F755" t="s">
-        <v>1841</v>
+        <v>1833</v>
       </c>
       <c r="G755" t="s">
         <v>1234</v>
@@ -24351,10 +24351,10 @@
         <v>1840</v>
       </c>
       <c r="E756" t="s">
-        <v>1832</v>
+        <v>1841</v>
       </c>
       <c r="F756" t="s">
-        <v>1841</v>
+        <v>1833</v>
       </c>
       <c r="G756" t="s">
         <v>1234</v>
@@ -24374,10 +24374,10 @@
         <v>1840</v>
       </c>
       <c r="E757" t="s">
-        <v>1832</v>
+        <v>1841</v>
       </c>
       <c r="F757" t="s">
-        <v>1841</v>
+        <v>1833</v>
       </c>
       <c r="G757" t="s">
         <v>1234</v>
@@ -24397,10 +24397,10 @@
         <v>1831</v>
       </c>
       <c r="E758" t="s">
-        <v>1832</v>
+        <v>1837</v>
       </c>
       <c r="F758" t="s">
-        <v>1837</v>
+        <v>1833</v>
       </c>
       <c r="G758" t="s">
         <v>34</v>
@@ -24420,10 +24420,10 @@
         <v>1797</v>
       </c>
       <c r="E759" t="s">
-        <v>1832</v>
+        <v>1841</v>
       </c>
       <c r="F759" t="s">
-        <v>1841</v>
+        <v>1833</v>
       </c>
       <c r="G759" t="s">
         <v>20</v>
@@ -24443,10 +24443,10 @@
         <v>1840</v>
       </c>
       <c r="E760" t="s">
-        <v>1832</v>
+        <v>1841</v>
       </c>
       <c r="F760" t="s">
-        <v>1841</v>
+        <v>1833</v>
       </c>
       <c r="G760" t="s">
         <v>1234</v>
@@ -24466,10 +24466,10 @@
         <v>1840</v>
       </c>
       <c r="E761" t="s">
-        <v>1832</v>
+        <v>1841</v>
       </c>
       <c r="F761" t="s">
-        <v>1841</v>
+        <v>1833</v>
       </c>
       <c r="G761" t="s">
         <v>1234</v>
@@ -24489,10 +24489,10 @@
         <v>1797</v>
       </c>
       <c r="E762" t="s">
-        <v>1832</v>
+        <v>1862</v>
       </c>
       <c r="F762" t="s">
-        <v>1862</v>
+        <v>1833</v>
       </c>
       <c r="G762" t="s">
         <v>34</v>
@@ -24512,10 +24512,10 @@
         <v>1840</v>
       </c>
       <c r="E763" t="s">
-        <v>1832</v>
+        <v>1841</v>
       </c>
       <c r="F763" t="s">
-        <v>1841</v>
+        <v>1833</v>
       </c>
       <c r="G763" t="s">
         <v>1234</v>
@@ -24535,10 +24535,10 @@
         <v>1867</v>
       </c>
       <c r="E764" t="s">
-        <v>1832</v>
+        <v>1868</v>
       </c>
       <c r="F764" t="s">
-        <v>1868</v>
+        <v>1833</v>
       </c>
       <c r="G764" t="s">
         <v>34</v>
@@ -24581,10 +24581,10 @@
         <v>1873</v>
       </c>
       <c r="E766" t="s">
-        <v>1832</v>
+        <v>1862</v>
       </c>
       <c r="F766" t="s">
-        <v>1862</v>
+        <v>1833</v>
       </c>
       <c r="G766" t="s">
         <v>34</v>
@@ -24604,10 +24604,10 @@
         <v>1876</v>
       </c>
       <c r="E767" t="s">
-        <v>1832</v>
+        <v>1877</v>
       </c>
       <c r="F767" t="s">
-        <v>1877</v>
+        <v>1833</v>
       </c>
       <c r="G767" t="s">
         <v>34</v>
@@ -24627,10 +24627,10 @@
         <v>1840</v>
       </c>
       <c r="E768" t="s">
-        <v>1832</v>
+        <v>1841</v>
       </c>
       <c r="F768" t="s">
-        <v>1841</v>
+        <v>1833</v>
       </c>
       <c r="G768" t="s">
         <v>1234</v>
@@ -24650,10 +24650,10 @@
         <v>1840</v>
       </c>
       <c r="E769" t="s">
-        <v>1832</v>
+        <v>1841</v>
       </c>
       <c r="F769" t="s">
-        <v>1841</v>
+        <v>1833</v>
       </c>
       <c r="G769" t="s">
         <v>1234</v>
@@ -24673,10 +24673,10 @@
         <v>1884</v>
       </c>
       <c r="E770" t="s">
-        <v>1832</v>
+        <v>1885</v>
       </c>
       <c r="F770" t="s">
-        <v>1885</v>
+        <v>1833</v>
       </c>
       <c r="G770" t="s">
         <v>34</v>
@@ -24696,10 +24696,10 @@
         <v>1840</v>
       </c>
       <c r="E771" t="s">
-        <v>1832</v>
+        <v>1841</v>
       </c>
       <c r="F771" t="s">
-        <v>1841</v>
+        <v>1833</v>
       </c>
       <c r="G771" t="s">
         <v>1234</v>
@@ -24719,10 +24719,10 @@
         <v>1840</v>
       </c>
       <c r="E772" t="s">
-        <v>1832</v>
+        <v>1841</v>
       </c>
       <c r="F772" t="s">
-        <v>1841</v>
+        <v>1833</v>
       </c>
       <c r="G772" t="s">
         <v>1234</v>
@@ -24742,10 +24742,10 @@
         <v>1840</v>
       </c>
       <c r="E773" t="s">
-        <v>1832</v>
+        <v>1841</v>
       </c>
       <c r="F773" t="s">
-        <v>1841</v>
+        <v>1833</v>
       </c>
       <c r="G773" t="s">
         <v>1234</v>
@@ -24765,10 +24765,10 @@
         <v>1894</v>
       </c>
       <c r="E774" t="s">
-        <v>1832</v>
+        <v>1895</v>
       </c>
       <c r="F774" t="s">
-        <v>1895</v>
+        <v>1833</v>
       </c>
       <c r="G774" t="s">
         <v>34</v>
@@ -24788,10 +24788,10 @@
         <v>1840</v>
       </c>
       <c r="E775" t="s">
-        <v>1832</v>
+        <v>1841</v>
       </c>
       <c r="F775" t="s">
-        <v>1841</v>
+        <v>1833</v>
       </c>
       <c r="G775" t="s">
         <v>1234</v>
@@ -24857,10 +24857,10 @@
         <v>1908</v>
       </c>
       <c r="E778" t="s">
-        <v>1901</v>
+        <v>1909</v>
       </c>
       <c r="F778" t="s">
-        <v>1909</v>
+        <v>1902</v>
       </c>
       <c r="G778" t="s">
         <v>34</v>
@@ -24880,10 +24880,10 @@
         <v>1912</v>
       </c>
       <c r="E779" t="s">
-        <v>1901</v>
+        <v>1913</v>
       </c>
       <c r="F779" t="s">
-        <v>1913</v>
+        <v>1902</v>
       </c>
       <c r="G779" t="s">
         <v>34</v>
@@ -25110,10 +25110,10 @@
         <v>1900</v>
       </c>
       <c r="E789" t="s">
-        <v>1901</v>
+        <v>1935</v>
       </c>
       <c r="F789" t="s">
-        <v>1935</v>
+        <v>1902</v>
       </c>
       <c r="G789" t="s">
         <v>34</v>
@@ -25156,10 +25156,10 @@
         <v>1920</v>
       </c>
       <c r="E791" t="s">
-        <v>1901</v>
+        <v>1940</v>
       </c>
       <c r="F791" t="s">
-        <v>1940</v>
+        <v>1902</v>
       </c>
       <c r="G791" t="s">
         <v>34</v>
@@ -25179,10 +25179,10 @@
         <v>1943</v>
       </c>
       <c r="E792" t="s">
-        <v>1901</v>
+        <v>1935</v>
       </c>
       <c r="F792" t="s">
-        <v>1935</v>
+        <v>1902</v>
       </c>
       <c r="G792" t="s">
         <v>34</v>
@@ -25225,10 +25225,10 @@
         <v>1905</v>
       </c>
       <c r="E794" t="s">
-        <v>1901</v>
+        <v>1948</v>
       </c>
       <c r="F794" t="s">
-        <v>1948</v>
+        <v>1902</v>
       </c>
       <c r="G794" t="s">
         <v>34</v>
@@ -25294,10 +25294,10 @@
         <v>1956</v>
       </c>
       <c r="E797" t="s">
-        <v>1901</v>
+        <v>1957</v>
       </c>
       <c r="F797" t="s">
-        <v>1957</v>
+        <v>1902</v>
       </c>
       <c r="G797" t="s">
         <v>34</v>
@@ -25317,10 +25317,10 @@
         <v>1960</v>
       </c>
       <c r="E798" t="s">
-        <v>1901</v>
+        <v>1961</v>
       </c>
       <c r="F798" t="s">
-        <v>1961</v>
+        <v>1902</v>
       </c>
       <c r="G798" t="s">
         <v>34</v>
@@ -25616,10 +25616,10 @@
         <v>1992</v>
       </c>
       <c r="E811" t="s">
-        <v>1983</v>
+        <v>1993</v>
       </c>
       <c r="F811" t="s">
-        <v>1993</v>
+        <v>1984</v>
       </c>
       <c r="G811" t="s">
         <v>34</v>
@@ -25708,10 +25708,10 @@
         <v>2002</v>
       </c>
       <c r="E815" t="s">
-        <v>1983</v>
+        <v>2003</v>
       </c>
       <c r="F815" t="s">
-        <v>2003</v>
+        <v>1984</v>
       </c>
       <c r="G815" t="s">
         <v>34</v>
@@ -25846,10 +25846,10 @@
         <v>2016</v>
       </c>
       <c r="E821" t="s">
-        <v>1983</v>
+        <v>2017</v>
       </c>
       <c r="F821" t="s">
-        <v>2017</v>
+        <v>1984</v>
       </c>
       <c r="G821" t="s">
         <v>20</v>
@@ -25869,10 +25869,10 @@
         <v>2020</v>
       </c>
       <c r="E822" t="s">
-        <v>1983</v>
+        <v>2021</v>
       </c>
       <c r="F822" t="s">
-        <v>2021</v>
+        <v>1984</v>
       </c>
       <c r="G822" t="s">
         <v>1987</v>
@@ -25915,10 +25915,10 @@
         <v>2020</v>
       </c>
       <c r="E824" t="s">
-        <v>1983</v>
+        <v>2021</v>
       </c>
       <c r="F824" t="s">
-        <v>2021</v>
+        <v>1984</v>
       </c>
       <c r="G824" t="s">
         <v>1987</v>
@@ -25938,10 +25938,10 @@
         <v>2020</v>
       </c>
       <c r="E825" t="s">
-        <v>1983</v>
+        <v>2021</v>
       </c>
       <c r="F825" t="s">
-        <v>2021</v>
+        <v>1984</v>
       </c>
       <c r="G825" t="s">
         <v>1234</v>
@@ -25961,10 +25961,10 @@
         <v>2020</v>
       </c>
       <c r="E826" t="s">
-        <v>1983</v>
+        <v>2021</v>
       </c>
       <c r="F826" t="s">
-        <v>2021</v>
+        <v>1984</v>
       </c>
       <c r="G826" t="s">
         <v>1987</v>
@@ -25984,10 +25984,10 @@
         <v>2020</v>
       </c>
       <c r="E827" t="s">
-        <v>1983</v>
+        <v>2021</v>
       </c>
       <c r="F827" t="s">
-        <v>2021</v>
+        <v>1984</v>
       </c>
       <c r="G827" t="s">
         <v>1987</v>
@@ -26444,10 +26444,10 @@
         <v>2076</v>
       </c>
       <c r="E847" t="s">
-        <v>2057</v>
+        <v>1993</v>
       </c>
       <c r="F847" t="s">
-        <v>1993</v>
+        <v>2058</v>
       </c>
       <c r="G847" t="s">
         <v>1987</v>
@@ -26467,10 +26467,10 @@
         <v>2076</v>
       </c>
       <c r="E848" t="s">
-        <v>2057</v>
+        <v>1993</v>
       </c>
       <c r="F848" t="s">
-        <v>1993</v>
+        <v>2058</v>
       </c>
       <c r="G848" t="s">
         <v>1987</v>
@@ -26490,10 +26490,10 @@
         <v>2076</v>
       </c>
       <c r="E849" t="s">
-        <v>2057</v>
+        <v>1993</v>
       </c>
       <c r="F849" t="s">
-        <v>1993</v>
+        <v>2058</v>
       </c>
       <c r="G849" t="s">
         <v>1234</v>
@@ -26513,10 +26513,10 @@
         <v>2076</v>
       </c>
       <c r="E850" t="s">
-        <v>2057</v>
+        <v>2083</v>
       </c>
       <c r="F850" t="s">
-        <v>2083</v>
+        <v>2058</v>
       </c>
       <c r="G850" t="s">
         <v>1987</v>
@@ -26536,10 +26536,10 @@
         <v>2076</v>
       </c>
       <c r="E851" t="s">
-        <v>2057</v>
+        <v>1993</v>
       </c>
       <c r="F851" t="s">
-        <v>1993</v>
+        <v>2058</v>
       </c>
       <c r="G851" t="s">
         <v>1987</v>
@@ -26559,10 +26559,10 @@
         <v>2076</v>
       </c>
       <c r="E852" t="s">
-        <v>2057</v>
+        <v>1993</v>
       </c>
       <c r="F852" t="s">
-        <v>1993</v>
+        <v>2058</v>
       </c>
       <c r="G852" t="s">
         <v>1987</v>
@@ -26927,10 +26927,10 @@
         <v>2118</v>
       </c>
       <c r="E868" t="s">
-        <v>2119</v>
+        <v>2123</v>
       </c>
       <c r="F868" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
       <c r="G868" t="s">
         <v>1987</v>
@@ -26950,10 +26950,10 @@
         <v>2118</v>
       </c>
       <c r="E869" t="s">
-        <v>2119</v>
+        <v>2123</v>
       </c>
       <c r="F869" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
       <c r="G869" t="s">
         <v>1987</v>
@@ -26973,10 +26973,10 @@
         <v>2118</v>
       </c>
       <c r="E870" t="s">
-        <v>2119</v>
+        <v>2123</v>
       </c>
       <c r="F870" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
       <c r="G870" t="s">
         <v>1987</v>
@@ -26996,10 +26996,10 @@
         <v>2118</v>
       </c>
       <c r="E871" t="s">
-        <v>2119</v>
+        <v>2123</v>
       </c>
       <c r="F871" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
       <c r="G871" t="s">
         <v>1987</v>
@@ -27019,10 +27019,10 @@
         <v>2118</v>
       </c>
       <c r="E872" t="s">
-        <v>2119</v>
+        <v>2123</v>
       </c>
       <c r="F872" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
       <c r="G872" t="s">
         <v>20</v>
@@ -27042,10 +27042,10 @@
         <v>2118</v>
       </c>
       <c r="E873" t="s">
-        <v>2119</v>
+        <v>2123</v>
       </c>
       <c r="F873" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
       <c r="G873" t="s">
         <v>20</v>
@@ -27065,10 +27065,10 @@
         <v>2118</v>
       </c>
       <c r="E874" t="s">
-        <v>2119</v>
+        <v>2123</v>
       </c>
       <c r="F874" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
       <c r="G874" t="s">
         <v>1987</v>
@@ -27088,10 +27088,10 @@
         <v>2118</v>
       </c>
       <c r="E875" t="s">
-        <v>2119</v>
+        <v>2123</v>
       </c>
       <c r="F875" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
       <c r="G875" t="s">
         <v>1987</v>
@@ -27111,10 +27111,10 @@
         <v>2118</v>
       </c>
       <c r="E876" t="s">
-        <v>2119</v>
+        <v>2123</v>
       </c>
       <c r="F876" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
       <c r="G876" t="s">
         <v>1234</v>
@@ -27134,10 +27134,10 @@
         <v>2118</v>
       </c>
       <c r="E877" t="s">
-        <v>2119</v>
+        <v>2123</v>
       </c>
       <c r="F877" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
       <c r="G877" t="s">
         <v>20</v>
@@ -27157,10 +27157,10 @@
         <v>2118</v>
       </c>
       <c r="E878" t="s">
-        <v>2119</v>
+        <v>2123</v>
       </c>
       <c r="F878" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
       <c r="G878" t="s">
         <v>1987</v>
@@ -27180,10 +27180,10 @@
         <v>2118</v>
       </c>
       <c r="E879" t="s">
-        <v>2119</v>
+        <v>2123</v>
       </c>
       <c r="F879" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
       <c r="G879" t="s">
         <v>1987</v>
@@ -27203,10 +27203,10 @@
         <v>2118</v>
       </c>
       <c r="E880" t="s">
-        <v>2119</v>
+        <v>2123</v>
       </c>
       <c r="F880" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
       <c r="G880" t="s">
         <v>1987</v>
@@ -27226,10 +27226,10 @@
         <v>2118</v>
       </c>
       <c r="E881" t="s">
-        <v>2119</v>
+        <v>2123</v>
       </c>
       <c r="F881" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
       <c r="G881" t="s">
         <v>1987</v>
@@ -27249,10 +27249,10 @@
         <v>2118</v>
       </c>
       <c r="E882" t="s">
-        <v>2119</v>
+        <v>2123</v>
       </c>
       <c r="F882" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
       <c r="G882" t="s">
         <v>1987</v>
@@ -27272,10 +27272,10 @@
         <v>2118</v>
       </c>
       <c r="E883" t="s">
-        <v>2119</v>
+        <v>2123</v>
       </c>
       <c r="F883" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
       <c r="G883" t="s">
         <v>1234</v>
@@ -27295,10 +27295,10 @@
         <v>2118</v>
       </c>
       <c r="E884" t="s">
-        <v>2119</v>
+        <v>2123</v>
       </c>
       <c r="F884" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
       <c r="G884" t="s">
         <v>1987</v>
@@ -27318,10 +27318,10 @@
         <v>2118</v>
       </c>
       <c r="E885" t="s">
-        <v>2119</v>
+        <v>2123</v>
       </c>
       <c r="F885" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
       <c r="G885" t="s">
         <v>1987</v>
@@ -27341,10 +27341,10 @@
         <v>2118</v>
       </c>
       <c r="E886" t="s">
-        <v>2119</v>
+        <v>2123</v>
       </c>
       <c r="F886" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
       <c r="G886" t="s">
         <v>1987</v>
@@ -27364,10 +27364,10 @@
         <v>2118</v>
       </c>
       <c r="E887" t="s">
-        <v>2119</v>
+        <v>2123</v>
       </c>
       <c r="F887" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
       <c r="G887" t="s">
         <v>20</v>
@@ -27387,10 +27387,10 @@
         <v>2118</v>
       </c>
       <c r="E888" t="s">
-        <v>2119</v>
+        <v>2123</v>
       </c>
       <c r="F888" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
       <c r="G888" t="s">
         <v>1987</v>
@@ -27410,10 +27410,10 @@
         <v>2118</v>
       </c>
       <c r="E889" t="s">
-        <v>2119</v>
+        <v>2123</v>
       </c>
       <c r="F889" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
       <c r="G889" t="s">
         <v>1234</v>
@@ -27778,10 +27778,10 @@
         <v>2201</v>
       </c>
       <c r="E905" t="s">
+        <v>2169</v>
+      </c>
+      <c r="F905" t="s">
         <v>2202</v>
-      </c>
-      <c r="F905" t="s">
-        <v>2170</v>
       </c>
       <c r="G905" t="s">
         <v>1987</v>
@@ -27801,10 +27801,10 @@
         <v>2205</v>
       </c>
       <c r="E906" t="s">
+        <v>2169</v>
+      </c>
+      <c r="F906" t="s">
         <v>2202</v>
-      </c>
-      <c r="F906" t="s">
-        <v>2170</v>
       </c>
       <c r="G906" t="s">
         <v>1987</v>
@@ -27824,10 +27824,10 @@
         <v>2201</v>
       </c>
       <c r="E907" t="s">
+        <v>2169</v>
+      </c>
+      <c r="F907" t="s">
         <v>2202</v>
-      </c>
-      <c r="F907" t="s">
-        <v>2170</v>
       </c>
       <c r="G907" t="s">
         <v>1987</v>

--- a/api/1/clv3/xlsx/en/HumanitarianPlan.xlsx
+++ b/api/1/clv3/xlsx/en/HumanitarianPlan.xlsx
@@ -25,15 +25,15 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:plan-year</t>
+  </si>
+  <si>
+    <t>codeforiati:plan-end-date</t>
+  </si>
+  <si>
     <t>codeforiati:plan-start-date</t>
   </si>
   <si>
-    <t>codeforiati:plan-end-date</t>
-  </si>
-  <si>
-    <t>codeforiati:plan-year</t>
-  </si>
-  <si>
     <t>codeforiati:plan-type</t>
   </si>
   <si>
@@ -46,15 +46,15 @@
     <t>active</t>
   </si>
   <si>
+    <t>2025</t>
+  </si>
+  <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
     <t>2025-01-01</t>
   </si>
   <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
-    <t>2025</t>
-  </si>
-  <si>
     <t>Humanitarian needs and response plan</t>
   </si>
   <si>
@@ -355,15 +355,15 @@
     <t>Afghanistan Humanitarian Needs and Response Plan 2024</t>
   </si>
   <si>
+    <t>2024</t>
+  </si>
+  <si>
+    <t>2024-12-31</t>
+  </si>
+  <si>
     <t>2024-01-01</t>
   </si>
   <si>
-    <t>2024-12-31</t>
-  </si>
-  <si>
-    <t>2024</t>
-  </si>
-  <si>
     <t>RAFG_RRP24</t>
   </si>
   <si>
@@ -712,15 +712,15 @@
     <t>Afghanistan Humanitarian Response Plan 2023</t>
   </si>
   <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>2023-12-31</t>
+  </si>
+  <si>
     <t>2023-01-01</t>
   </si>
   <si>
-    <t>2023-12-31</t>
-  </si>
-  <si>
-    <t>2023</t>
-  </si>
-  <si>
     <t>RAFG23</t>
   </si>
   <si>
@@ -841,24 +841,24 @@
     <t>Mongolia Dzud Early Action and Response Plan 2023</t>
   </si>
   <si>
+    <t>2023-05-31</t>
+  </si>
+  <si>
     <t>2022-12-01</t>
   </si>
   <si>
-    <t>2023-05-31</t>
-  </si>
-  <si>
     <t>OMOZ23</t>
   </si>
   <si>
     <t>Mozambique Cyclone Freddy, Floods and Cholera Response Plan 2023</t>
   </si>
   <si>
+    <t>2023-09-30</t>
+  </si>
+  <si>
     <t>2023-03-01</t>
   </si>
   <si>
-    <t>2023-09-30</t>
-  </si>
-  <si>
     <t>HMOZ23</t>
   </si>
   <si>
@@ -946,12 +946,12 @@
     <t>Sudan Emergency: Regional Refugee Response Plan 2023</t>
   </si>
   <si>
+    <t>2023-10-31</t>
+  </si>
+  <si>
     <t>2023-05-01</t>
   </si>
   <si>
-    <t>2023-10-31</t>
-  </si>
-  <si>
     <t>HSDN23</t>
   </si>
   <si>
@@ -1030,15 +1030,15 @@
     <t>Afghanistan Humanitarian Response Plan 2022</t>
   </si>
   <si>
+    <t>2022</t>
+  </si>
+  <si>
+    <t>2022-12-31</t>
+  </si>
+  <si>
     <t>2022-01-01</t>
   </si>
   <si>
-    <t>2022-12-31</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
     <t>RAFG22</t>
   </si>
   <si>
@@ -1081,12 +1081,12 @@
     <t>Cuba Hurricane Ian Response - Plan of Action 2022</t>
   </si>
   <si>
+    <t>2023-03-31</t>
+  </si>
+  <si>
     <t>2022-10-20</t>
   </si>
   <si>
-    <t>2023-03-31</t>
-  </si>
-  <si>
     <t>RDRCRRP22</t>
   </si>
   <si>
@@ -1117,12 +1117,12 @@
     <t>Haïti Choléra+ Appel Éclair 2022</t>
   </si>
   <si>
+    <t>2023-04-15</t>
+  </si>
+  <si>
     <t>2022-10-16</t>
   </si>
   <si>
-    <t>2023-04-15</t>
-  </si>
-  <si>
     <t>FHTI22</t>
   </si>
   <si>
@@ -1180,12 +1180,12 @@
     <t>Malawi Flash Appeal 2022</t>
   </si>
   <si>
+    <t>2022-05-31</t>
+  </si>
+  <si>
     <t>2022-02-26</t>
   </si>
   <si>
-    <t>2022-05-31</t>
-  </si>
-  <si>
     <t>HMLI22</t>
   </si>
   <si>
@@ -1198,12 +1198,12 @@
     <t>Mozambique Gombe Emergency Response Plan 2022</t>
   </si>
   <si>
+    <t>2022-09-30</t>
+  </si>
+  <si>
     <t>2022-04-01</t>
   </si>
   <si>
-    <t>2022-09-30</t>
-  </si>
-  <si>
     <t>HMOZ22</t>
   </si>
   <si>
@@ -1255,12 +1255,12 @@
     <t>Philippines Super Typhoon Rai (Odette) Humanitarian Needs and Priorities 2022</t>
   </si>
   <si>
+    <t>2022-06-30</t>
+  </si>
+  <si>
     <t>2021-12-24</t>
   </si>
   <si>
-    <t>2022-06-30</t>
-  </si>
-  <si>
     <t>RREG22</t>
   </si>
   <si>
@@ -1378,15 +1378,15 @@
     <t>Afghanistan Flash Appeal 2021</t>
   </si>
   <si>
+    <t>2021</t>
+  </si>
+  <si>
+    <t>2021-12-31</t>
+  </si>
+  <si>
     <t>2021-09-01</t>
   </si>
   <si>
-    <t>2021-12-31</t>
-  </si>
-  <si>
-    <t>2021</t>
-  </si>
-  <si>
     <t>HAFG21</t>
   </si>
   <si>
@@ -1477,12 +1477,12 @@
     <t>Escalation of Hostilities in the OPT Flash Appeal 2021</t>
   </si>
   <si>
+    <t>2021-08-27</t>
+  </si>
+  <si>
     <t>2021-05-27</t>
   </si>
   <si>
-    <t>2021-08-27</t>
-  </si>
-  <si>
     <t>HETH21</t>
   </si>
   <si>
@@ -1507,12 +1507,12 @@
     <t>Haiti Earthquake Flash Appeal 2021</t>
   </si>
   <si>
+    <t>2022-02-15</t>
+  </si>
+  <si>
     <t>2021-08-16</t>
   </si>
   <si>
-    <t>2022-02-15</t>
-  </si>
-  <si>
     <t>HHTI21</t>
   </si>
   <si>
@@ -1525,12 +1525,12 @@
     <t>Honduras Tropical Storm Eta Flash Appeal 2021</t>
   </si>
   <si>
+    <t>2021-06-30</t>
+  </si>
+  <si>
     <t>2020-11-15</t>
   </si>
   <si>
-    <t>2021-06-30</t>
-  </si>
-  <si>
     <t>HHND21</t>
   </si>
   <si>
@@ -1564,12 +1564,12 @@
     <t>Lebanon Emergency Response Plan 2021</t>
   </si>
   <si>
+    <t>2022-07-31</t>
+  </si>
+  <si>
     <t>2021-08-03</t>
   </si>
   <si>
-    <t>2022-07-31</t>
-  </si>
-  <si>
     <t>HLBY21</t>
   </si>
   <si>
@@ -1735,15 +1735,15 @@
     <t>Afghanistan Humanitarian Response Plan 2020</t>
   </si>
   <si>
+    <t>2020</t>
+  </si>
+  <si>
+    <t>2020-12-31</t>
+  </si>
+  <si>
     <t>2020-01-01</t>
   </si>
   <si>
-    <t>2020-12-31</t>
-  </si>
-  <si>
-    <t>2020</t>
-  </si>
-  <si>
     <t>OBGD20</t>
   </si>
   <si>
@@ -1858,12 +1858,12 @@
     <t>Djibouti Flash Appeal 2020</t>
   </si>
   <si>
+    <t>2020-03-31</t>
+  </si>
+  <si>
     <t>2019-12-17</t>
   </si>
   <si>
-    <t>2020-03-31</t>
-  </si>
-  <si>
     <t>ODJI20</t>
   </si>
   <si>
@@ -1957,12 +1957,12 @@
     <t>Lebanon Flash Appeal 2020</t>
   </si>
   <si>
+    <t>2020-11-13</t>
+  </si>
+  <si>
     <t>2020-08-05</t>
   </si>
   <si>
-    <t>2020-11-13</t>
-  </si>
-  <si>
     <t>OLBN20</t>
   </si>
   <si>
@@ -1975,12 +1975,12 @@
     <t>Lesotho Flash Appeal 2019-2020</t>
   </si>
   <si>
+    <t>2020-04-30</t>
+  </si>
+  <si>
     <t>2019-11-01</t>
   </si>
   <si>
-    <t>2020-04-30</t>
-  </si>
-  <si>
     <t>OLBR20</t>
   </si>
   <si>
@@ -2170,15 +2170,15 @@
     <t>Afghanistan Humanitarian Response Plan 2019</t>
   </si>
   <si>
+    <t>2019</t>
+  </si>
+  <si>
+    <t>2019-12-31</t>
+  </si>
+  <si>
     <t>2019-01-01</t>
   </si>
   <si>
-    <t>2019-12-31</t>
-  </si>
-  <si>
-    <t>2019</t>
-  </si>
-  <si>
     <t>RBGD19</t>
   </si>
   <si>
@@ -2386,12 +2386,12 @@
     <t>Zimbabwe Flash Appeal 2019</t>
   </si>
   <si>
+    <t>2020-04-29</t>
+  </si>
+  <si>
     <t>2019-02-01</t>
   </si>
   <si>
-    <t>2020-04-29</t>
-  </si>
-  <si>
     <t>FZWE1820</t>
   </si>
   <si>
@@ -2407,15 +2407,15 @@
     <t>Afghanistan Humanitarian Response Plan 2018</t>
   </si>
   <si>
+    <t>2018</t>
+  </si>
+  <si>
+    <t>2018-12-31</t>
+  </si>
+  <si>
     <t>2018-01-01</t>
   </si>
   <si>
-    <t>2018-12-31</t>
-  </si>
-  <si>
-    <t>2018</t>
-  </si>
-  <si>
     <t>OBGD18</t>
   </si>
   <si>
@@ -2590,12 +2590,12 @@
     <t>Syrian Arab Republic Humanitarian Response Plan 2018</t>
   </si>
   <si>
+    <t>2018-12-30</t>
+  </si>
+  <si>
     <t>2018-11-30</t>
   </si>
   <si>
-    <t>2018-12-30</t>
-  </si>
-  <si>
     <t>RSYR18</t>
   </si>
   <si>
@@ -2632,15 +2632,15 @@
     <t>Regional Refugee and Migrant Response Plan for Europe 2017</t>
   </si>
   <si>
+    <t>2017</t>
+  </si>
+  <si>
+    <t>2017-12-31</t>
+  </si>
+  <si>
     <t>2017-01-01</t>
   </si>
   <si>
-    <t>2017-12-31</t>
-  </si>
-  <si>
-    <t>2017</t>
-  </si>
-  <si>
     <t>HAFG17</t>
   </si>
   <si>
@@ -2716,12 +2716,12 @@
     <t>Dominica Hurricane Maria Flash Appeal 2017</t>
   </si>
   <si>
+    <t>2017-12-29</t>
+  </si>
+  <si>
     <t>2017-09-28</t>
   </si>
   <si>
-    <t>2017-12-29</t>
-  </si>
-  <si>
     <t>OPRK17</t>
   </si>
   <si>
@@ -2761,12 +2761,12 @@
     <t>Kenya Flash Appeal 2017</t>
   </si>
   <si>
+    <t>2017-11-30</t>
+  </si>
+  <si>
     <t>2017-02-10</t>
   </si>
   <si>
-    <t>2017-11-30</t>
-  </si>
-  <si>
     <t>HLBY17</t>
   </si>
   <si>
@@ -2779,12 +2779,12 @@
     <t>Madagascar Tropical Cyclone Enawo Flash Appeal 2017</t>
   </si>
   <si>
+    <t>2017-06-20</t>
+  </si>
+  <si>
     <t>2017-03-20</t>
   </si>
   <si>
-    <t>2017-06-20</t>
-  </si>
-  <si>
     <t>HMLI17</t>
   </si>
   <si>
@@ -2803,12 +2803,12 @@
     <t>Mozambique Cyclone Dineo Flash Appeal 2017</t>
   </si>
   <si>
+    <t>2017-05-31</t>
+  </si>
+  <si>
     <t>2017-02-28</t>
   </si>
   <si>
-    <t>2017-05-31</t>
-  </si>
-  <si>
     <t>HMMR17</t>
   </si>
   <si>
@@ -2845,12 +2845,12 @@
     <t>Perú Costa Norte Flash Appeal 2017</t>
   </si>
   <si>
+    <t>2017-10-31</t>
+  </si>
+  <si>
     <t>2017-04-01</t>
   </si>
   <si>
-    <t>2017-10-31</t>
-  </si>
-  <si>
     <t>HCOG17</t>
   </si>
   <si>
@@ -2917,15 +2917,15 @@
     <t>Regional Refugee and Migrant Response Plan for Europe 2016</t>
   </si>
   <si>
+    <t>2016</t>
+  </si>
+  <si>
+    <t>2016-12-31</t>
+  </si>
+  <si>
     <t>2016-01-01</t>
   </si>
   <si>
-    <t>2016-12-31</t>
-  </si>
-  <si>
-    <t>2016</t>
-  </si>
-  <si>
     <t>HAFG16</t>
   </si>
   <si>
@@ -2998,24 +2998,24 @@
     <t>Ecuador Terremoto Flash Appeal 2016</t>
   </si>
   <si>
+    <t>2016-10-31</t>
+  </si>
+  <si>
     <t>2016-04-16</t>
   </si>
   <si>
-    <t>2016-10-31</t>
-  </si>
-  <si>
     <t>FFJI16</t>
   </si>
   <si>
     <t>Fiji Tropical Cyclone Winston Flash Appeal 2016</t>
   </si>
   <si>
+    <t>2016-05-30</t>
+  </si>
+  <si>
     <t>2016-02-20</t>
   </si>
   <si>
-    <t>2016-05-30</t>
-  </si>
-  <si>
     <t>HGMB16</t>
   </si>
   <si>
@@ -3091,12 +3091,12 @@
     <t>Iraq Mosul Flash Appeal 2016</t>
   </si>
   <si>
+    <t>2016-10-01</t>
+  </si>
+  <si>
     <t>2016-07-20</t>
   </si>
   <si>
-    <t>2016-10-01</t>
-  </si>
-  <si>
     <t>HMMR16</t>
   </si>
   <si>
@@ -3181,27 +3181,27 @@
     <t>Zimbabwe Humanitarian Response Plan 2016</t>
   </si>
   <si>
+    <t>2017-03-31</t>
+  </si>
+  <si>
     <t>2016-04-01</t>
   </si>
   <si>
-    <t>2017-03-31</t>
-  </si>
-  <si>
     <t>HAFG15</t>
   </si>
   <si>
     <t>Afghanistan Strategic Response Plan 2015</t>
   </si>
   <si>
+    <t>2015</t>
+  </si>
+  <si>
+    <t>2015-12-31</t>
+  </si>
+  <si>
     <t>2015-01-01</t>
   </si>
   <si>
-    <t>2015-12-31</t>
-  </si>
-  <si>
-    <t>2015</t>
-  </si>
-  <si>
     <t>Strategic response plan</t>
   </si>
   <si>
@@ -3259,12 +3259,12 @@
     <t>Guatemala Plan de Respuesta Sequia 2015</t>
   </si>
   <si>
+    <t>2015-09-30</t>
+  </si>
+  <si>
     <t>2014-11-03</t>
   </si>
   <si>
-    <t>2015-09-30</t>
-  </si>
-  <si>
     <t>FHTI15</t>
   </si>
   <si>
@@ -3289,12 +3289,12 @@
     <t>Vanuatu Emergency Response Plan for Tropical Cyclone PAM 2015</t>
   </si>
   <si>
+    <t>2015-10-31</t>
+  </si>
+  <si>
     <t>2015-03-24</t>
   </si>
   <si>
-    <t>2015-10-31</t>
-  </si>
-  <si>
     <t>HIRQ15</t>
   </si>
   <si>
@@ -3307,12 +3307,12 @@
     <t>Libya Humanitarian Appeal 2014- 2015</t>
   </si>
   <si>
+    <t>2015-05-31</t>
+  </si>
+  <si>
     <t>2014-10-01</t>
   </si>
   <si>
-    <t>2015-05-31</t>
-  </si>
-  <si>
     <t>HMLI15</t>
   </si>
   <si>
@@ -3424,15 +3424,15 @@
     <t>Afghanistan Strategic Response Plan 2014</t>
   </si>
   <si>
+    <t>2014</t>
+  </si>
+  <si>
+    <t>2014-12-31</t>
+  </si>
+  <si>
     <t>2014-01-01</t>
   </si>
   <si>
-    <t>2014-12-31</t>
-  </si>
-  <si>
-    <t>2014</t>
-  </si>
-  <si>
     <t>HBFA1314</t>
   </si>
   <si>
@@ -3568,24 +3568,24 @@
     <t>Philippines Bohol Earthquake Flash Appeal 2014</t>
   </si>
   <si>
+    <t>2014-04-22</t>
+  </si>
+  <si>
     <t>2013-10-22</t>
   </si>
   <si>
-    <t>2014-04-22</t>
-  </si>
-  <si>
     <t>SPHL1314</t>
   </si>
   <si>
     <t>Philippines Typhoon Haiyan Strategic Response Plan 2014</t>
   </si>
   <si>
+    <t>2014-11-07</t>
+  </si>
+  <si>
     <t>2013-11-08</t>
   </si>
   <si>
-    <t>2014-11-07</t>
-  </si>
-  <si>
     <t>HPHL1314</t>
   </si>
   <si>
@@ -3601,12 +3601,12 @@
     <t>Philippines Zamboanga Crisis Flash Appeal 2014</t>
   </si>
   <si>
+    <t>2014-08-31</t>
+  </si>
+  <si>
     <t>2013-10-01</t>
   </si>
   <si>
-    <t>2014-08-31</t>
-  </si>
-  <si>
     <t>SCOD14</t>
   </si>
   <si>
@@ -3712,12 +3712,12 @@
     <t>Afghanistan 2013</t>
   </si>
   <si>
+    <t>2013</t>
+  </si>
+  <si>
     <t>2013-12-31</t>
   </si>
   <si>
-    <t>2013</t>
-  </si>
-  <si>
     <t>Consolidated appeals process</t>
   </si>
   <si>
@@ -3874,15 +3874,15 @@
     <t>2012+ Kenya Emergency Humanitarian Response Plan</t>
   </si>
   <si>
+    <t>2012</t>
+  </si>
+  <si>
+    <t>2012-12-31</t>
+  </si>
+  <si>
     <t>2012-01-01</t>
   </si>
   <si>
-    <t>2012-12-31</t>
-  </si>
-  <si>
-    <t>2012</t>
-  </si>
-  <si>
     <t>CAFG1112</t>
   </si>
   <si>
@@ -3952,12 +3952,12 @@
     <t>Lesotho Food Insecurity (September 2012 - March 2013)</t>
   </si>
   <si>
+    <t>2013-03-25</t>
+  </si>
+  <si>
     <t>2012-09-18</t>
   </si>
   <si>
-    <t>2013-03-25</t>
-  </si>
-  <si>
     <t>CLBR12</t>
   </si>
   <si>
@@ -4030,12 +4030,12 @@
     <t>Syria Humanitarian Assistance Response Plan (SHARP) 2012</t>
   </si>
   <si>
+    <t>2012-12-05</t>
+  </si>
+  <si>
     <t>2012-06-05</t>
   </si>
   <si>
-    <t>2012-12-05</t>
-  </si>
-  <si>
     <t>CYEM12</t>
   </si>
   <si>
@@ -4060,12 +4060,12 @@
     <t>2011+ Kenya Emergency Humanitarian Response Plan</t>
   </si>
   <si>
+    <t>2011</t>
+  </si>
+  <si>
     <t>2011-01-01</t>
   </si>
   <si>
-    <t>2011</t>
-  </si>
-  <si>
     <t>CAFG11</t>
   </si>
   <si>
@@ -4108,12 +4108,12 @@
     <t>El Salvador Flash Appeal (October 2011 - April 2012)</t>
   </si>
   <si>
+    <t>2012-04-25</t>
+  </si>
+  <si>
     <t>2011-10-25</t>
   </si>
   <si>
-    <t>2012-04-25</t>
-  </si>
-  <si>
     <t>CHTI1011</t>
   </si>
   <si>
@@ -4144,24 +4144,24 @@
     <t>Namibia Flash Appeal (April - October 2011)</t>
   </si>
   <si>
+    <t>2011-10-11</t>
+  </si>
+  <si>
     <t>2011-04-11</t>
   </si>
   <si>
-    <t>2011-10-11</t>
-  </si>
-  <si>
     <t>FNIC1112</t>
   </si>
   <si>
     <t>Nicaragua Flash Appeal (October 2011 - April 2012)</t>
   </si>
   <si>
+    <t>2012-04-26</t>
+  </si>
+  <si>
     <t>2011-10-27</t>
   </si>
   <si>
-    <t>2012-04-26</t>
-  </si>
-  <si>
     <t>CNER11</t>
   </si>
   <si>
@@ -4174,12 +4174,12 @@
     <t>Pakistan Rapid Response Plan Floods 2011 (September - March 2012)</t>
   </si>
   <si>
+    <t>2012-06-30</t>
+  </si>
+  <si>
     <t>2011-09-15</t>
   </si>
   <si>
-    <t>2012-06-30</t>
-  </si>
-  <si>
     <t>FXLBYREG11</t>
   </si>
   <si>
@@ -4255,27 +4255,27 @@
     <t>Afghanistan Humanitarian Action Plan 2010</t>
   </si>
   <si>
+    <t>2010</t>
+  </si>
+  <si>
+    <t>2010-12-31</t>
+  </si>
+  <si>
     <t>2010-01-01</t>
   </si>
   <si>
-    <t>2010-12-31</t>
-  </si>
-  <si>
-    <t>2010</t>
-  </si>
-  <si>
     <t>OBFA1011</t>
   </si>
   <si>
     <t>Burkina Faso Emergency Humanitarian Action Plan 2010</t>
   </si>
   <si>
+    <t>2011-01-31</t>
+  </si>
+  <si>
     <t>2010-08-01</t>
   </si>
   <si>
-    <t>2011-01-31</t>
-  </si>
-  <si>
     <t>CCAF10</t>
   </si>
   <si>
@@ -4300,36 +4300,36 @@
     <t>El Salvador Flash Appeal (Revised) (November 2009 - May 2010)</t>
   </si>
   <si>
+    <t>2010-05-31</t>
+  </si>
+  <si>
     <t>2009-11-01</t>
   </si>
   <si>
-    <t>2010-05-31</t>
-  </si>
-  <si>
     <t>FGTM10</t>
   </si>
   <si>
     <t>Guatemala Flash Appeal (Revised) (June - December 2010)</t>
   </si>
   <si>
+    <t>2010-12-09</t>
+  </si>
+  <si>
     <t>2010-06-10</t>
   </si>
   <si>
-    <t>2010-12-09</t>
-  </si>
-  <si>
     <t>CGTM10</t>
   </si>
   <si>
     <t>Guatemala Food Insecurity and Acute Malnutrition Appeal 2010</t>
   </si>
   <si>
+    <t>2010-08-11</t>
+  </si>
+  <si>
     <t>2010-02-12</t>
   </si>
   <si>
-    <t>2010-08-11</t>
-  </si>
-  <si>
     <t>FHTI10</t>
   </si>
   <si>
@@ -4357,12 +4357,12 @@
     <t>Kyrgyzstan Flash Appeal (Revised) (June 2010 - June 2011)</t>
   </si>
   <si>
+    <t>2011-06-30</t>
+  </si>
+  <si>
     <t>2010-06-01</t>
   </si>
   <si>
-    <t>2011-06-30</t>
-  </si>
-  <si>
     <t>CMNG1011</t>
   </si>
   <si>
@@ -4465,27 +4465,27 @@
     <t>Afghanistan Humanitarian Action Plan 2009</t>
   </si>
   <si>
+    <t>2009</t>
+  </si>
+  <si>
+    <t>2009-12-31</t>
+  </si>
+  <si>
     <t>2009-01-01</t>
   </si>
   <si>
-    <t>2009-12-31</t>
-  </si>
-  <si>
-    <t>2009</t>
-  </si>
-  <si>
     <t>FBFA0910</t>
   </si>
   <si>
     <t>Burkina Faso Flash Appeal (September 2009 - February 2010)</t>
   </si>
   <si>
+    <t>2010-03-09</t>
+  </si>
+  <si>
     <t>2009-09-10</t>
   </si>
   <si>
-    <t>2010-03-09</t>
-  </si>
-  <si>
     <t>CCAF09</t>
   </si>
   <si>
@@ -4549,24 +4549,24 @@
     <t>Madagascar Flash Appeal (Revised) (April - October 2009)</t>
   </si>
   <si>
+    <t>2009-10-31</t>
+  </si>
+  <si>
     <t>2009-04-01</t>
   </si>
   <si>
-    <t>2009-10-31</t>
-  </si>
-  <si>
     <t>FNAM09</t>
   </si>
   <si>
     <t>Namibia Flash Appeal (Revised) (March - November 2009)</t>
   </si>
   <si>
+    <t>2009-09-30</t>
+  </si>
+  <si>
     <t>2009-03-20</t>
   </si>
   <si>
-    <t>2009-09-30</t>
-  </si>
-  <si>
     <t>ONPL09</t>
   </si>
   <si>
@@ -4588,12 +4588,12 @@
     <t>Philippines Flash Appeal (Revised) (October 2009 - March 2010)</t>
   </si>
   <si>
+    <t>2010-03-31</t>
+  </si>
+  <si>
     <t>2009-10-03</t>
   </si>
   <si>
-    <t>2010-03-31</t>
-  </si>
-  <si>
     <t>CSOM09</t>
   </si>
   <si>
@@ -4618,12 +4618,12 @@
     <t>Syria Drought Response Plan (Revised) (July 2009 - June 2010)</t>
   </si>
   <si>
+    <t>2010-06-14</t>
+  </si>
+  <si>
     <t>2009-07-15</t>
   </si>
   <si>
-    <t>2010-06-14</t>
-  </si>
-  <si>
     <t>OTJK09</t>
   </si>
   <si>
@@ -4681,27 +4681,27 @@
     <t>Afghanistan Joint Appeal 2008: Humanitarian Consequences of Rise in Food Prices (February - June 2008)</t>
   </si>
   <si>
+    <t>2008</t>
+  </si>
+  <si>
+    <t>2008-06-30</t>
+  </si>
+  <si>
     <t>2008-02-01</t>
   </si>
   <si>
-    <t>2008-06-30</t>
-  </si>
-  <si>
-    <t>2008</t>
-  </si>
-  <si>
     <t>OAFG0809</t>
   </si>
   <si>
     <t>Afghanistan Joint Emergency Appeal 2008: High Food Price and Drought Crisis (July 2008 - June 2009)</t>
   </si>
   <si>
+    <t>2009-06-30</t>
+  </si>
+  <si>
     <t>2008-07-01</t>
   </si>
   <si>
-    <t>2009-06-30</t>
-  </si>
-  <si>
     <t>FBOL08</t>
   </si>
   <si>
@@ -4717,12 +4717,12 @@
     <t>Central African Republic 2008</t>
   </si>
   <si>
+    <t>2008-12-31</t>
+  </si>
+  <si>
     <t>2008-01-01</t>
   </si>
   <si>
-    <t>2008-12-31</t>
-  </si>
-  <si>
     <t>CTCD08</t>
   </si>
   <si>
@@ -4753,24 +4753,24 @@
     <t>Djibouti Joint Appeal 2008: Response Plan for Drought, Food and Nutrition Crisis</t>
   </si>
   <si>
+    <t>2009-02-28</t>
+  </si>
+  <si>
     <t>2008-08-01</t>
   </si>
   <si>
-    <t>2009-02-28</t>
-  </si>
-  <si>
     <t>FGEO0809</t>
   </si>
   <si>
     <t>Georgia Crisis Flash Appeal (Revised) 2008</t>
   </si>
   <si>
+    <t>2009-02-09</t>
+  </si>
+  <si>
     <t>2008-08-09</t>
   </si>
   <si>
-    <t>2009-02-09</t>
-  </si>
-  <si>
     <t>FHTI0809</t>
   </si>
   <si>
@@ -4786,12 +4786,12 @@
     <t>Honduras Flash Appeal (Updated) (November - April) 2008</t>
   </si>
   <si>
+    <t>2009-04-30</t>
+  </si>
+  <si>
     <t>2008-11-01</t>
   </si>
   <si>
-    <t>2009-04-30</t>
-  </si>
-  <si>
     <t>CIRQ08</t>
   </si>
   <si>
@@ -4810,12 +4810,12 @@
     <t>Kyrgyzstan Flash Appeal (Revised) 2008</t>
   </si>
   <si>
+    <t>2009-05-31</t>
+  </si>
+  <si>
     <t>2008-12-01</t>
   </si>
   <si>
-    <t>2009-05-31</t>
-  </si>
-  <si>
     <t>OLAO0809</t>
   </si>
   <si>
@@ -4846,12 +4846,12 @@
     <t>Myanmar Flash Appeal (Revised) 2008</t>
   </si>
   <si>
+    <t>2008-11-30</t>
+  </si>
+  <si>
     <t>2008-05-01</t>
   </si>
   <si>
-    <t>2008-11-30</t>
-  </si>
-  <si>
     <t>ONPL08</t>
   </si>
   <si>
@@ -4948,39 +4948,39 @@
     <t>Bolivia Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2007</t>
+  </si>
+  <si>
+    <t>2007-08-21</t>
+  </si>
+  <si>
     <t>2007-02-22</t>
   </si>
   <si>
-    <t>2007-08-21</t>
-  </si>
-  <si>
-    <t>2007</t>
-  </si>
-  <si>
     <t>FBFA0708</t>
   </si>
   <si>
     <t>Burkina Faso Floods Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2008-01-31</t>
+  </si>
+  <si>
     <t>2007-11-01</t>
   </si>
   <si>
-    <t>2008-01-31</t>
-  </si>
-  <si>
     <t>CBDI07</t>
   </si>
   <si>
     <t>Burundi 2007</t>
   </si>
   <si>
+    <t>2007-12-31</t>
+  </si>
+  <si>
     <t>2007-01-01</t>
   </si>
   <si>
-    <t>2007-12-31</t>
-  </si>
-  <si>
     <t>CCAF07</t>
   </si>
   <si>
@@ -5020,12 +5020,12 @@
     <t>Ghana Floods Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2008-03-31</t>
+  </si>
+  <si>
     <t>2007-09-01</t>
   </si>
   <si>
-    <t>2008-03-31</t>
-  </si>
-  <si>
     <t>CXGLR07</t>
   </si>
   <si>
@@ -5047,36 +5047,36 @@
     <t>Korea DPR Flash Appeal: Floods Emergency 2007</t>
   </si>
   <si>
+    <t>2007-11-30</t>
+  </si>
+  <si>
     <t>2007-08-28</t>
   </si>
   <si>
-    <t>2007-11-30</t>
-  </si>
-  <si>
     <t>OLBN07</t>
   </si>
   <si>
     <t>Lebanon Crisis Appeal 2007</t>
   </si>
   <si>
+    <t>2007-09-03</t>
+  </si>
+  <si>
     <t>2007-06-04</t>
   </si>
   <si>
-    <t>2007-09-03</t>
-  </si>
-  <si>
     <t>FLSO0708</t>
   </si>
   <si>
     <t>Lesotho Drought Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2008-01-28</t>
+  </si>
+  <si>
     <t>2007-07-28</t>
   </si>
   <si>
-    <t>2008-01-28</t>
-  </si>
-  <si>
     <t>CLBR07</t>
   </si>
   <si>
@@ -5089,24 +5089,24 @@
     <t>Madagascar Floods Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2007-09-15</t>
+  </si>
+  <si>
     <t>2007-03-15</t>
   </si>
   <si>
-    <t>2007-09-15</t>
-  </si>
-  <si>
     <t>FMOZ07</t>
   </si>
   <si>
     <t>Mozambique Floods and Cyclone Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2007-06-30</t>
+  </si>
+  <si>
     <t>2007-03-01</t>
   </si>
   <si>
-    <t>2007-06-30</t>
-  </si>
-  <si>
     <t>ONPL07</t>
   </si>
   <si>
@@ -5119,12 +5119,12 @@
     <t>Nicaragua Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2008-02-28</t>
+  </si>
+  <si>
     <t>2007-09-07</t>
   </si>
   <si>
-    <t>2008-02-28</t>
-  </si>
-  <si>
     <t>ORUS07</t>
   </si>
   <si>
@@ -5137,12 +5137,12 @@
     <t>Pakistan Cyclone and Floods Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2007-10-31</t>
+  </si>
+  <si>
     <t>2007-07-15</t>
   </si>
   <si>
-    <t>2007-10-31</t>
-  </si>
-  <si>
     <t>FPER0708</t>
   </si>
   <si>
@@ -5200,12 +5200,12 @@
     <t>Swaziland Drought Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2008-01-20</t>
+  </si>
+  <si>
     <t>2007-07-20</t>
   </si>
   <si>
-    <t>2008-01-20</t>
-  </si>
-  <si>
     <t>CTLS07</t>
   </si>
   <si>
@@ -5254,15 +5254,15 @@
     <t>Afghanistan Drought Joint Appeal 2006</t>
   </si>
   <si>
+    <t>2006</t>
+  </si>
+  <si>
+    <t>2006-12-31</t>
+  </si>
+  <si>
     <t>2006-07-01</t>
   </si>
   <si>
-    <t>2006-12-31</t>
-  </si>
-  <si>
-    <t>2006</t>
-  </si>
-  <si>
     <t>CBDI06</t>
   </si>
   <si>
@@ -5308,24 +5308,24 @@
     <t>Ethiopia Floods Joint Appeal 2006</t>
   </si>
   <si>
+    <t>2006-11-25</t>
+  </si>
+  <si>
     <t>2006-08-25</t>
   </si>
   <si>
-    <t>2006-11-25</t>
-  </si>
-  <si>
     <t>OETH0607</t>
   </si>
   <si>
     <t>Ethiopia: 2006 Govt-UN Joint Emergency Flood Appeal for Somali Region</t>
   </si>
   <si>
+    <t>2007-01-22</t>
+  </si>
+  <si>
     <t>2006-11-23</t>
   </si>
   <si>
-    <t>2007-01-22</t>
-  </si>
-  <si>
     <t>CXGLR06</t>
   </si>
   <si>
@@ -5344,12 +5344,12 @@
     <t>Guinea-Bissau 2006</t>
   </si>
   <si>
+    <t>2006-11-30</t>
+  </si>
+  <si>
     <t>2006-05-01</t>
   </si>
   <si>
-    <t>2006-11-30</t>
-  </si>
-  <si>
     <t>CXHAF06</t>
   </si>
   <si>
@@ -5368,12 +5368,12 @@
     <t>Kenya 2006</t>
   </si>
   <si>
+    <t>2007-04-15</t>
+  </si>
+  <si>
     <t>2006-10-16</t>
   </si>
   <si>
-    <t>2007-04-15</t>
-  </si>
-  <si>
     <t>FKEN06</t>
   </si>
   <si>
@@ -5389,12 +5389,12 @@
     <t>Lebanon Crisis 2006</t>
   </si>
   <si>
+    <t>2006-10-23</t>
+  </si>
+  <si>
     <t>2006-07-24</t>
   </si>
   <si>
-    <t>2006-10-23</t>
-  </si>
-  <si>
     <t>CLBR06</t>
   </si>
   <si>
@@ -5443,12 +5443,12 @@
     <t>Somalia: 2006 Flood Response Plan</t>
   </si>
   <si>
+    <t>2007-03-05</t>
+  </si>
+  <si>
     <t>2006-12-05</t>
   </si>
   <si>
-    <t>2007-03-05</t>
-  </si>
-  <si>
     <t>OLKA06</t>
   </si>
   <si>
@@ -5509,39 +5509,39 @@
     <t>Angola Marburg VHF 2005</t>
   </si>
   <si>
+    <t>2005</t>
+  </si>
+  <si>
+    <t>2005-06-30</t>
+  </si>
+  <si>
     <t>2005-04-01</t>
   </si>
   <si>
-    <t>2005-06-30</t>
-  </si>
-  <si>
-    <t>2005</t>
-  </si>
-  <si>
     <t>FBEN05</t>
   </si>
   <si>
     <t>Benin 2005</t>
   </si>
   <si>
+    <t>2005-10-31</t>
+  </si>
+  <si>
     <t>2005-05-01</t>
   </si>
   <si>
-    <t>2005-10-31</t>
-  </si>
-  <si>
     <t>CBDI05</t>
   </si>
   <si>
     <t>Burundi 2005</t>
   </si>
   <si>
+    <t>2005-12-31</t>
+  </si>
+  <si>
     <t>2005-01-01</t>
   </si>
   <si>
-    <t>2005-12-31</t>
-  </si>
-  <si>
     <t>CCAF05</t>
   </si>
   <si>
@@ -5617,12 +5617,12 @@
     <t>Guyana 2005</t>
   </si>
   <si>
+    <t>2005-08-01</t>
+  </si>
+  <si>
     <t>2005-02-01</t>
   </si>
   <si>
-    <t>2005-08-01</t>
-  </si>
-  <si>
     <t>FXINDTSU05</t>
   </si>
   <si>
@@ -5644,12 +5644,12 @@
     <t>Niger 2005</t>
   </si>
   <si>
+    <t>2005-09-30</t>
+  </si>
+  <si>
     <t>2005-06-01</t>
   </si>
   <si>
-    <t>2005-09-30</t>
-  </si>
-  <si>
     <t>CCOG05</t>
   </si>
   <si>
@@ -5668,12 +5668,12 @@
     <t>South Asia Earthquake 2005</t>
   </si>
   <si>
+    <t>2006-04-10</t>
+  </si>
+  <si>
     <t>2005-10-11</t>
   </si>
   <si>
-    <t>2006-04-10</t>
-  </si>
-  <si>
     <t>CSDN05</t>
   </si>
   <si>
@@ -5698,12 +5698,12 @@
     <t>West and Central Africa Region Cholera 2005</t>
   </si>
   <si>
+    <t>2006-05-31</t>
+  </si>
+  <si>
     <t>2005-11-01</t>
   </si>
   <si>
-    <t>2006-05-31</t>
-  </si>
-  <si>
     <t>CPSE05</t>
   </si>
   <si>
@@ -5716,15 +5716,15 @@
     <t>Afghanistan UN-Government Drought Appeal 2004</t>
   </si>
   <si>
+    <t>2004</t>
+  </si>
+  <si>
+    <t>2004-12-31</t>
+  </si>
+  <si>
     <t>2004-09-01</t>
   </si>
   <si>
-    <t>2004-12-31</t>
-  </si>
-  <si>
-    <t>2004</t>
-  </si>
-  <si>
     <t>CAGO04</t>
   </si>
   <si>
@@ -5740,24 +5740,24 @@
     <t>Bangladesh 2004</t>
   </si>
   <si>
+    <t>2005-01-31</t>
+  </si>
+  <si>
     <t>2004-08-01</t>
   </si>
   <si>
-    <t>2005-01-31</t>
-  </si>
-  <si>
     <t>FBOL0405</t>
   </si>
   <si>
     <t>Bolivia 2004</t>
   </si>
   <si>
+    <t>2005-05-31</t>
+  </si>
+  <si>
     <t>2004-11-01</t>
   </si>
   <si>
-    <t>2005-05-31</t>
-  </si>
-  <si>
     <t>CBDI04</t>
   </si>
   <si>
@@ -5884,24 +5884,24 @@
     <t>Madagascar 2004</t>
   </si>
   <si>
+    <t>2004-06-19</t>
+  </si>
+  <si>
     <t>2004-03-19</t>
   </si>
   <si>
-    <t>2004-06-19</t>
-  </si>
-  <si>
     <t>FPHL0405</t>
   </si>
   <si>
     <t>Philippines 2004</t>
   </si>
   <si>
+    <t>2005-03-15</t>
+  </si>
+  <si>
     <t>2004-12-15</t>
   </si>
   <si>
-    <t>2005-03-15</t>
-  </si>
-  <si>
     <t>CSLE04</t>
   </si>
   <si>
@@ -5962,15 +5962,15 @@
     <t>Afghanistan TAPA 2003</t>
   </si>
   <si>
+    <t>2003</t>
+  </si>
+  <si>
+    <t>2003-12-31</t>
+  </si>
+  <si>
     <t>2003-01-01</t>
   </si>
   <si>
-    <t>2003-12-31</t>
-  </si>
-  <si>
-    <t>2003</t>
-  </si>
-  <si>
     <t>CAGO03</t>
   </si>
   <si>
@@ -5992,12 +5992,12 @@
     <t>Central African Republic 2003</t>
   </si>
   <si>
+    <t>2003-06-30</t>
+  </si>
+  <si>
     <t>2003-04-01</t>
   </si>
   <si>
-    <t>2003-06-30</t>
-  </si>
-  <si>
     <t>CRUS03</t>
   </si>
   <si>
@@ -6022,12 +6022,12 @@
     <t>Côte d'Ivoire and the West Africa Sub-Region 2002-2003</t>
   </si>
   <si>
+    <t>2003-01-31</t>
+  </si>
+  <si>
     <t>2002-11-01</t>
   </si>
   <si>
-    <t>2003-01-31</t>
-  </si>
-  <si>
     <t>CPRK03</t>
   </si>
   <si>
@@ -6064,24 +6064,24 @@
     <t>Haiti (PIR) 2003</t>
   </si>
   <si>
+    <t>2003-08-31</t>
+  </si>
+  <si>
     <t>2003-03-01</t>
   </si>
   <si>
-    <t>2003-08-31</t>
-  </si>
-  <si>
     <t>CLSO0304</t>
   </si>
   <si>
     <t>Humanitarian Crisis in Southern Africa - LESOTHO (July 2003 - June 2004)</t>
   </si>
   <si>
+    <t>2004-06-30</t>
+  </si>
+  <si>
     <t>2003-07-01</t>
   </si>
   <si>
-    <t>2004-06-30</t>
-  </si>
-  <si>
     <t>CMWI03</t>
   </si>
   <si>
@@ -6184,15 +6184,15 @@
     <t>Afghanistan 2002 (ITAP for the Afghan People)</t>
   </si>
   <si>
+    <t>2002</t>
+  </si>
+  <si>
+    <t>2002-12-31</t>
+  </si>
+  <si>
     <t>2001-10-01</t>
   </si>
   <si>
-    <t>2002-12-31</t>
-  </si>
-  <si>
-    <t>2002</t>
-  </si>
-  <si>
     <t>CAGO02</t>
   </si>
   <si>
@@ -6370,15 +6370,15 @@
     <t>Afghanistan 2001</t>
   </si>
   <si>
+    <t>2001</t>
+  </si>
+  <si>
+    <t>2001-09-30</t>
+  </si>
+  <si>
     <t>2001-01-01</t>
   </si>
   <si>
-    <t>2001-09-30</t>
-  </si>
-  <si>
-    <t>2001</t>
-  </si>
-  <si>
     <t>CAGO01</t>
   </si>
   <si>
@@ -6520,15 +6520,15 @@
     <t>Angola 2000</t>
   </si>
   <si>
+    <t>2000</t>
+  </si>
+  <si>
+    <t>2000-12-31</t>
+  </si>
+  <si>
     <t>2000-01-01</t>
   </si>
   <si>
-    <t>2000-12-31</t>
-  </si>
-  <si>
-    <t>2000</t>
-  </si>
-  <si>
     <t>CBDI00</t>
   </si>
   <si>
@@ -6619,10 +6619,10 @@
     <t>East Timor Consolidated Inter Agency Appeal 2000</t>
   </si>
   <si>
+    <t>1999</t>
+  </si>
+  <si>
     <t>1999-10-01</t>
-  </si>
-  <si>
-    <t>1999</t>
   </si>
   <si>
     <t>CRUS9900</t>
@@ -7420,13 +7420,13 @@
         <v>9</v>
       </c>
       <c r="D20" t="s">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="E20" t="s">
         <v>11</v>
       </c>
       <c r="F20" t="s">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="G20" t="s">
         <v>13</v>
@@ -7742,13 +7742,13 @@
         <v>9</v>
       </c>
       <c r="D34" t="s">
-        <v>88</v>
+        <v>10</v>
       </c>
       <c r="E34" t="s">
         <v>11</v>
       </c>
       <c r="F34" t="s">
-        <v>12</v>
+        <v>88</v>
       </c>
       <c r="G34" t="s">
         <v>34</v>
@@ -8064,13 +8064,13 @@
         <v>9</v>
       </c>
       <c r="D48" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="E48" t="s">
         <v>114</v>
       </c>
       <c r="F48" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="G48" t="s">
         <v>20</v>
@@ -8110,13 +8110,13 @@
         <v>9</v>
       </c>
       <c r="D50" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="E50" t="s">
         <v>114</v>
       </c>
       <c r="F50" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="G50" t="s">
         <v>20</v>
@@ -8271,13 +8271,13 @@
         <v>9</v>
       </c>
       <c r="D57" t="s">
-        <v>140</v>
+        <v>113</v>
       </c>
       <c r="E57" t="s">
         <v>114</v>
       </c>
       <c r="F57" t="s">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="G57" t="s">
         <v>34</v>
@@ -8363,13 +8363,13 @@
         <v>9</v>
       </c>
       <c r="D61" t="s">
-        <v>149</v>
+        <v>113</v>
       </c>
       <c r="E61" t="s">
         <v>114</v>
       </c>
       <c r="F61" t="s">
-        <v>115</v>
+        <v>149</v>
       </c>
       <c r="G61" t="s">
         <v>20</v>
@@ -8386,13 +8386,13 @@
         <v>9</v>
       </c>
       <c r="D62" t="s">
-        <v>149</v>
+        <v>113</v>
       </c>
       <c r="E62" t="s">
         <v>114</v>
       </c>
       <c r="F62" t="s">
-        <v>115</v>
+        <v>149</v>
       </c>
       <c r="G62" t="s">
         <v>34</v>
@@ -8455,13 +8455,13 @@
         <v>9</v>
       </c>
       <c r="D65" t="s">
-        <v>160</v>
+        <v>113</v>
       </c>
       <c r="E65" t="s">
         <v>114</v>
       </c>
       <c r="F65" t="s">
-        <v>115</v>
+        <v>160</v>
       </c>
       <c r="G65" t="s">
         <v>34</v>
@@ -8501,13 +8501,13 @@
         <v>9</v>
       </c>
       <c r="D67" t="s">
-        <v>165</v>
+        <v>113</v>
       </c>
       <c r="E67" t="s">
         <v>157</v>
       </c>
       <c r="F67" t="s">
-        <v>115</v>
+        <v>165</v>
       </c>
       <c r="G67" t="s">
         <v>20</v>
@@ -8524,13 +8524,13 @@
         <v>9</v>
       </c>
       <c r="D68" t="s">
-        <v>168</v>
+        <v>113</v>
       </c>
       <c r="E68" t="s">
         <v>114</v>
       </c>
       <c r="F68" t="s">
-        <v>115</v>
+        <v>168</v>
       </c>
       <c r="G68" t="s">
         <v>34</v>
@@ -8593,13 +8593,13 @@
         <v>9</v>
       </c>
       <c r="D71" t="s">
-        <v>175</v>
+        <v>113</v>
       </c>
       <c r="E71" t="s">
         <v>114</v>
       </c>
       <c r="F71" t="s">
-        <v>115</v>
+        <v>175</v>
       </c>
       <c r="G71" t="s">
         <v>20</v>
@@ -8662,13 +8662,13 @@
         <v>9</v>
       </c>
       <c r="D74" t="s">
-        <v>182</v>
+        <v>113</v>
       </c>
       <c r="E74" t="s">
         <v>114</v>
       </c>
       <c r="F74" t="s">
-        <v>115</v>
+        <v>182</v>
       </c>
       <c r="G74" t="s">
         <v>20</v>
@@ -8800,13 +8800,13 @@
         <v>9</v>
       </c>
       <c r="D80" t="s">
-        <v>140</v>
+        <v>113</v>
       </c>
       <c r="E80" t="s">
         <v>114</v>
       </c>
       <c r="F80" t="s">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="G80" t="s">
         <v>34</v>
@@ -9099,13 +9099,13 @@
         <v>9</v>
       </c>
       <c r="D93" t="s">
-        <v>222</v>
+        <v>113</v>
       </c>
       <c r="E93" t="s">
         <v>114</v>
       </c>
       <c r="F93" t="s">
-        <v>115</v>
+        <v>222</v>
       </c>
       <c r="G93" t="s">
         <v>20</v>
@@ -9145,13 +9145,13 @@
         <v>9</v>
       </c>
       <c r="D95" t="s">
-        <v>227</v>
+        <v>113</v>
       </c>
       <c r="E95" t="s">
         <v>114</v>
       </c>
       <c r="F95" t="s">
-        <v>115</v>
+        <v>227</v>
       </c>
       <c r="G95" t="s">
         <v>34</v>
@@ -9168,13 +9168,13 @@
         <v>9</v>
       </c>
       <c r="D96" t="s">
-        <v>227</v>
+        <v>113</v>
       </c>
       <c r="E96" t="s">
         <v>114</v>
       </c>
       <c r="F96" t="s">
-        <v>115</v>
+        <v>227</v>
       </c>
       <c r="G96" t="s">
         <v>34</v>
@@ -9375,13 +9375,13 @@
         <v>9</v>
       </c>
       <c r="D105" t="s">
-        <v>251</v>
+        <v>232</v>
       </c>
       <c r="E105" t="s">
         <v>233</v>
       </c>
       <c r="F105" t="s">
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="G105" t="s">
         <v>34</v>
@@ -9559,13 +9559,13 @@
         <v>9</v>
       </c>
       <c r="D113" t="s">
-        <v>268</v>
+        <v>232</v>
       </c>
       <c r="E113" t="s">
         <v>233</v>
       </c>
       <c r="F113" t="s">
-        <v>234</v>
+        <v>268</v>
       </c>
       <c r="G113" t="s">
         <v>34</v>
@@ -9628,13 +9628,13 @@
         <v>9</v>
       </c>
       <c r="D116" t="s">
+        <v>232</v>
+      </c>
+      <c r="E116" t="s">
         <v>275</v>
       </c>
-      <c r="E116" t="s">
+      <c r="F116" t="s">
         <v>276</v>
-      </c>
-      <c r="F116" t="s">
-        <v>234</v>
       </c>
       <c r="G116" t="s">
         <v>20</v>
@@ -9651,13 +9651,13 @@
         <v>9</v>
       </c>
       <c r="D117" t="s">
+        <v>232</v>
+      </c>
+      <c r="E117" t="s">
         <v>279</v>
       </c>
-      <c r="E117" t="s">
+      <c r="F117" t="s">
         <v>280</v>
-      </c>
-      <c r="F117" t="s">
-        <v>234</v>
       </c>
       <c r="G117" t="s">
         <v>20</v>
@@ -9769,7 +9769,7 @@
         <v>232</v>
       </c>
       <c r="E122" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F122" t="s">
         <v>234</v>
@@ -9792,7 +9792,7 @@
         <v>232</v>
       </c>
       <c r="E123" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F123" t="s">
         <v>234</v>
@@ -9996,13 +9996,13 @@
         <v>9</v>
       </c>
       <c r="D132" t="s">
+        <v>232</v>
+      </c>
+      <c r="E132" t="s">
         <v>310</v>
       </c>
-      <c r="E132" t="s">
+      <c r="F132" t="s">
         <v>311</v>
-      </c>
-      <c r="F132" t="s">
-        <v>234</v>
       </c>
       <c r="G132" t="s">
         <v>16</v>
@@ -10042,13 +10042,13 @@
         <v>9</v>
       </c>
       <c r="D134" t="s">
+        <v>232</v>
+      </c>
+      <c r="E134" t="s">
+        <v>275</v>
+      </c>
+      <c r="F134" t="s">
         <v>316</v>
-      </c>
-      <c r="E134" t="s">
-        <v>276</v>
-      </c>
-      <c r="F134" t="s">
-        <v>234</v>
       </c>
       <c r="G134" t="s">
         <v>34</v>
@@ -10088,13 +10088,13 @@
         <v>9</v>
       </c>
       <c r="D136" t="s">
+        <v>232</v>
+      </c>
+      <c r="E136" t="s">
+        <v>275</v>
+      </c>
+      <c r="F136" t="s">
         <v>321</v>
-      </c>
-      <c r="E136" t="s">
-        <v>276</v>
-      </c>
-      <c r="F136" t="s">
-        <v>234</v>
       </c>
       <c r="G136" t="s">
         <v>34</v>
@@ -10433,13 +10433,13 @@
         <v>9</v>
       </c>
       <c r="D151" t="s">
+        <v>338</v>
+      </c>
+      <c r="E151" t="s">
         <v>355</v>
       </c>
-      <c r="E151" t="s">
+      <c r="F151" t="s">
         <v>356</v>
-      </c>
-      <c r="F151" t="s">
-        <v>340</v>
       </c>
       <c r="G151" t="s">
         <v>20</v>
@@ -10548,13 +10548,13 @@
         <v>9</v>
       </c>
       <c r="D156" t="s">
+        <v>338</v>
+      </c>
+      <c r="E156" t="s">
         <v>367</v>
       </c>
-      <c r="E156" t="s">
+      <c r="F156" t="s">
         <v>368</v>
-      </c>
-      <c r="F156" t="s">
-        <v>340</v>
       </c>
       <c r="G156" t="s">
         <v>34</v>
@@ -10571,13 +10571,13 @@
         <v>185</v>
       </c>
       <c r="D157" t="s">
-        <v>367</v>
+        <v>338</v>
       </c>
       <c r="E157" t="s">
         <v>339</v>
       </c>
       <c r="F157" t="s">
-        <v>340</v>
+        <v>368</v>
       </c>
       <c r="G157" t="s">
         <v>34</v>
@@ -10755,13 +10755,13 @@
         <v>9</v>
       </c>
       <c r="D165" t="s">
+        <v>338</v>
+      </c>
+      <c r="E165" t="s">
         <v>388</v>
       </c>
-      <c r="E165" t="s">
+      <c r="F165" t="s">
         <v>389</v>
-      </c>
-      <c r="F165" t="s">
-        <v>340</v>
       </c>
       <c r="G165" t="s">
         <v>34</v>
@@ -10801,13 +10801,13 @@
         <v>9</v>
       </c>
       <c r="D167" t="s">
+        <v>338</v>
+      </c>
+      <c r="E167" t="s">
         <v>394</v>
       </c>
-      <c r="E167" t="s">
+      <c r="F167" t="s">
         <v>395</v>
-      </c>
-      <c r="F167" t="s">
-        <v>340</v>
       </c>
       <c r="G167" t="s">
         <v>34</v>
@@ -10939,13 +10939,13 @@
         <v>9</v>
       </c>
       <c r="D173" t="s">
-        <v>408</v>
+        <v>338</v>
       </c>
       <c r="E173" t="s">
         <v>339</v>
       </c>
       <c r="F173" t="s">
-        <v>340</v>
+        <v>408</v>
       </c>
       <c r="G173" t="s">
         <v>20</v>
@@ -10962,13 +10962,13 @@
         <v>185</v>
       </c>
       <c r="D174" t="s">
-        <v>408</v>
+        <v>338</v>
       </c>
       <c r="E174" t="s">
         <v>410</v>
       </c>
       <c r="F174" t="s">
-        <v>340</v>
+        <v>408</v>
       </c>
       <c r="G174" t="s">
         <v>20</v>
@@ -10985,13 +10985,13 @@
         <v>9</v>
       </c>
       <c r="D175" t="s">
+        <v>338</v>
+      </c>
+      <c r="E175" t="s">
         <v>413</v>
       </c>
-      <c r="E175" t="s">
+      <c r="F175" t="s">
         <v>414</v>
-      </c>
-      <c r="F175" t="s">
-        <v>340</v>
       </c>
       <c r="G175" t="s">
         <v>20</v>
@@ -11169,13 +11169,13 @@
         <v>9</v>
       </c>
       <c r="D183" t="s">
-        <v>431</v>
+        <v>338</v>
       </c>
       <c r="E183" t="s">
         <v>339</v>
       </c>
       <c r="F183" t="s">
-        <v>340</v>
+        <v>431</v>
       </c>
       <c r="G183" t="s">
         <v>20</v>
@@ -11284,13 +11284,13 @@
         <v>9</v>
       </c>
       <c r="D188" t="s">
-        <v>442</v>
+        <v>338</v>
       </c>
       <c r="E188" t="s">
         <v>339</v>
       </c>
       <c r="F188" t="s">
-        <v>340</v>
+        <v>442</v>
       </c>
       <c r="G188" t="s">
         <v>34</v>
@@ -11330,13 +11330,13 @@
         <v>9</v>
       </c>
       <c r="D190" t="s">
-        <v>442</v>
+        <v>338</v>
       </c>
       <c r="E190" t="s">
         <v>447</v>
       </c>
       <c r="F190" t="s">
-        <v>340</v>
+        <v>442</v>
       </c>
       <c r="G190" t="s">
         <v>16</v>
@@ -11422,13 +11422,13 @@
         <v>9</v>
       </c>
       <c r="D194" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="E194" t="s">
         <v>455</v>
       </c>
       <c r="F194" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="G194" t="s">
         <v>25</v>
@@ -11445,13 +11445,13 @@
         <v>9</v>
       </c>
       <c r="D195" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="E195" t="s">
         <v>455</v>
       </c>
       <c r="F195" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="G195" t="s">
         <v>16</v>
@@ -11468,13 +11468,13 @@
         <v>9</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="E196" t="s">
         <v>455</v>
       </c>
       <c r="F196" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="G196" t="s">
         <v>25</v>
@@ -11491,13 +11491,13 @@
         <v>9</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="E197" t="s">
         <v>455</v>
       </c>
       <c r="F197" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="G197" t="s">
         <v>25</v>
@@ -11514,13 +11514,13 @@
         <v>9</v>
       </c>
       <c r="D198" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="E198" t="s">
         <v>455</v>
       </c>
       <c r="F198" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="G198" t="s">
         <v>16</v>
@@ -11537,13 +11537,13 @@
         <v>9</v>
       </c>
       <c r="D199" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="E199" t="s">
         <v>455</v>
       </c>
       <c r="F199" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="G199" t="s">
         <v>25</v>
@@ -11560,13 +11560,13 @@
         <v>9</v>
       </c>
       <c r="D200" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="E200" t="s">
         <v>455</v>
       </c>
       <c r="F200" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="G200" t="s">
         <v>25</v>
@@ -11583,13 +11583,13 @@
         <v>9</v>
       </c>
       <c r="D201" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="E201" t="s">
         <v>455</v>
       </c>
       <c r="F201" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="G201" t="s">
         <v>25</v>
@@ -11606,13 +11606,13 @@
         <v>9</v>
       </c>
       <c r="D202" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="E202" t="s">
         <v>455</v>
       </c>
       <c r="F202" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="G202" t="s">
         <v>25</v>
@@ -11629,13 +11629,13 @@
         <v>9</v>
       </c>
       <c r="D203" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="E203" t="s">
         <v>455</v>
       </c>
       <c r="F203" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="G203" t="s">
         <v>25</v>
@@ -11652,13 +11652,13 @@
         <v>9</v>
       </c>
       <c r="D204" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="E204" t="s">
         <v>455</v>
       </c>
       <c r="F204" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="G204" t="s">
         <v>16</v>
@@ -11675,13 +11675,13 @@
         <v>9</v>
       </c>
       <c r="D205" t="s">
-        <v>482</v>
+        <v>454</v>
       </c>
       <c r="E205" t="s">
         <v>455</v>
       </c>
       <c r="F205" t="s">
-        <v>456</v>
+        <v>482</v>
       </c>
       <c r="G205" t="s">
         <v>25</v>
@@ -11698,13 +11698,13 @@
         <v>185</v>
       </c>
       <c r="D206" t="s">
-        <v>482</v>
+        <v>454</v>
       </c>
       <c r="E206" t="s">
         <v>339</v>
       </c>
       <c r="F206" t="s">
-        <v>456</v>
+        <v>482</v>
       </c>
       <c r="G206" t="s">
         <v>25</v>
@@ -11721,13 +11721,13 @@
         <v>9</v>
       </c>
       <c r="D207" t="s">
+        <v>454</v>
+      </c>
+      <c r="E207" t="s">
         <v>487</v>
       </c>
-      <c r="E207" t="s">
+      <c r="F207" t="s">
         <v>488</v>
-      </c>
-      <c r="F207" t="s">
-        <v>456</v>
       </c>
       <c r="G207" t="s">
         <v>34</v>
@@ -11744,13 +11744,13 @@
         <v>9</v>
       </c>
       <c r="D208" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="E208" t="s">
         <v>455</v>
       </c>
       <c r="F208" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="G208" t="s">
         <v>25</v>
@@ -11767,13 +11767,13 @@
         <v>9</v>
       </c>
       <c r="D209" t="s">
-        <v>482</v>
+        <v>454</v>
       </c>
       <c r="E209" t="s">
         <v>455</v>
       </c>
       <c r="F209" t="s">
-        <v>456</v>
+        <v>482</v>
       </c>
       <c r="G209" t="s">
         <v>25</v>
@@ -11790,13 +11790,13 @@
         <v>185</v>
       </c>
       <c r="D210" t="s">
-        <v>482</v>
+        <v>454</v>
       </c>
       <c r="E210" t="s">
         <v>339</v>
       </c>
       <c r="F210" t="s">
-        <v>456</v>
+        <v>482</v>
       </c>
       <c r="G210" t="s">
         <v>25</v>
@@ -11813,13 +11813,13 @@
         <v>9</v>
       </c>
       <c r="D211" t="s">
+        <v>454</v>
+      </c>
+      <c r="E211" t="s">
         <v>497</v>
       </c>
-      <c r="E211" t="s">
+      <c r="F211" t="s">
         <v>498</v>
-      </c>
-      <c r="F211" t="s">
-        <v>456</v>
       </c>
       <c r="G211" t="s">
         <v>34</v>
@@ -11836,13 +11836,13 @@
         <v>9</v>
       </c>
       <c r="D212" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="E212" t="s">
         <v>455</v>
       </c>
       <c r="F212" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="G212" t="s">
         <v>25</v>
@@ -11859,13 +11859,13 @@
         <v>9</v>
       </c>
       <c r="D213" t="s">
+        <v>454</v>
+      </c>
+      <c r="E213" t="s">
         <v>503</v>
       </c>
-      <c r="E213" t="s">
+      <c r="F213" t="s">
         <v>504</v>
-      </c>
-      <c r="F213" t="s">
-        <v>456</v>
       </c>
       <c r="G213" t="s">
         <v>34</v>
@@ -11882,13 +11882,13 @@
         <v>9</v>
       </c>
       <c r="D214" t="s">
-        <v>482</v>
+        <v>454</v>
       </c>
       <c r="E214" t="s">
         <v>455</v>
       </c>
       <c r="F214" t="s">
-        <v>456</v>
+        <v>482</v>
       </c>
       <c r="G214" t="s">
         <v>25</v>
@@ -11905,13 +11905,13 @@
         <v>185</v>
       </c>
       <c r="D215" t="s">
-        <v>482</v>
+        <v>454</v>
       </c>
       <c r="E215" t="s">
         <v>339</v>
       </c>
       <c r="F215" t="s">
-        <v>456</v>
+        <v>482</v>
       </c>
       <c r="G215" t="s">
         <v>25</v>
@@ -11928,13 +11928,13 @@
         <v>9</v>
       </c>
       <c r="D216" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="E216" t="s">
         <v>455</v>
       </c>
       <c r="F216" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="G216" t="s">
         <v>25</v>
@@ -11951,13 +11951,13 @@
         <v>9</v>
       </c>
       <c r="D217" t="s">
-        <v>513</v>
+        <v>454</v>
       </c>
       <c r="E217" t="s">
         <v>455</v>
       </c>
       <c r="F217" t="s">
-        <v>456</v>
+        <v>513</v>
       </c>
       <c r="G217" t="s">
         <v>34</v>
@@ -11974,13 +11974,13 @@
         <v>9</v>
       </c>
       <c r="D218" t="s">
+        <v>454</v>
+      </c>
+      <c r="E218" t="s">
         <v>516</v>
       </c>
-      <c r="E218" t="s">
+      <c r="F218" t="s">
         <v>517</v>
-      </c>
-      <c r="F218" t="s">
-        <v>456</v>
       </c>
       <c r="G218" t="s">
         <v>20</v>
@@ -11997,13 +11997,13 @@
         <v>9</v>
       </c>
       <c r="D219" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="E219" t="s">
         <v>455</v>
       </c>
       <c r="F219" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="G219" t="s">
         <v>25</v>
@@ -12020,13 +12020,13 @@
         <v>185</v>
       </c>
       <c r="D220" t="s">
+        <v>454</v>
+      </c>
+      <c r="E220" t="s">
+        <v>388</v>
+      </c>
+      <c r="F220" t="s">
         <v>459</v>
-      </c>
-      <c r="E220" t="s">
-        <v>389</v>
-      </c>
-      <c r="F220" t="s">
-        <v>456</v>
       </c>
       <c r="G220" t="s">
         <v>34</v>
@@ -12043,13 +12043,13 @@
         <v>9</v>
       </c>
       <c r="D221" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="E221" t="s">
         <v>455</v>
       </c>
       <c r="F221" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="G221" t="s">
         <v>34</v>
@@ -12066,13 +12066,13 @@
         <v>9</v>
       </c>
       <c r="D222" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="E222" t="s">
         <v>455</v>
       </c>
       <c r="F222" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="G222" t="s">
         <v>25</v>
@@ -12089,13 +12089,13 @@
         <v>9</v>
       </c>
       <c r="D223" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="E223" t="s">
         <v>455</v>
       </c>
       <c r="F223" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="G223" t="s">
         <v>25</v>
@@ -12112,13 +12112,13 @@
         <v>9</v>
       </c>
       <c r="D224" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="E224" t="s">
         <v>455</v>
       </c>
       <c r="F224" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="G224" t="s">
         <v>25</v>
@@ -12135,13 +12135,13 @@
         <v>9</v>
       </c>
       <c r="D225" t="s">
-        <v>532</v>
+        <v>454</v>
       </c>
       <c r="E225" t="s">
         <v>455</v>
       </c>
       <c r="F225" t="s">
-        <v>456</v>
+        <v>532</v>
       </c>
       <c r="G225" t="s">
         <v>20</v>
@@ -12158,13 +12158,13 @@
         <v>9</v>
       </c>
       <c r="D226" t="s">
-        <v>535</v>
+        <v>454</v>
       </c>
       <c r="E226" t="s">
         <v>455</v>
       </c>
       <c r="F226" t="s">
-        <v>456</v>
+        <v>535</v>
       </c>
       <c r="G226" t="s">
         <v>20</v>
@@ -12181,13 +12181,13 @@
         <v>9</v>
       </c>
       <c r="D227" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="E227" t="s">
         <v>455</v>
       </c>
       <c r="F227" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="G227" t="s">
         <v>25</v>
@@ -12204,13 +12204,13 @@
         <v>9</v>
       </c>
       <c r="D228" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="E228" t="s">
         <v>455</v>
       </c>
       <c r="F228" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="G228" t="s">
         <v>25</v>
@@ -12227,13 +12227,13 @@
         <v>9</v>
       </c>
       <c r="D229" t="s">
-        <v>535</v>
+        <v>454</v>
       </c>
       <c r="E229" t="s">
         <v>455</v>
       </c>
       <c r="F229" t="s">
-        <v>456</v>
+        <v>535</v>
       </c>
       <c r="G229" t="s">
         <v>34</v>
@@ -12250,13 +12250,13 @@
         <v>185</v>
       </c>
       <c r="D230" t="s">
-        <v>535</v>
+        <v>454</v>
       </c>
       <c r="E230" t="s">
         <v>455</v>
       </c>
       <c r="F230" t="s">
-        <v>456</v>
+        <v>535</v>
       </c>
       <c r="G230" t="s">
         <v>20</v>
@@ -12273,13 +12273,13 @@
         <v>9</v>
       </c>
       <c r="D231" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="E231" t="s">
         <v>455</v>
       </c>
       <c r="F231" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="G231" t="s">
         <v>25</v>
@@ -12296,13 +12296,13 @@
         <v>9</v>
       </c>
       <c r="D232" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="E232" t="s">
         <v>455</v>
       </c>
       <c r="F232" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="G232" t="s">
         <v>25</v>
@@ -12319,13 +12319,13 @@
         <v>9</v>
       </c>
       <c r="D233" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="E233" t="s">
         <v>455</v>
       </c>
       <c r="F233" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="G233" t="s">
         <v>16</v>
@@ -12342,13 +12342,13 @@
         <v>9</v>
       </c>
       <c r="D234" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="E234" t="s">
         <v>455</v>
       </c>
       <c r="F234" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="G234" t="s">
         <v>16</v>
@@ -12365,13 +12365,13 @@
         <v>9</v>
       </c>
       <c r="D235" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="E235" t="s">
         <v>455</v>
       </c>
       <c r="F235" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="G235" t="s">
         <v>25</v>
@@ -12388,13 +12388,13 @@
         <v>9</v>
       </c>
       <c r="D236" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="E236" t="s">
         <v>455</v>
       </c>
       <c r="F236" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="G236" t="s">
         <v>25</v>
@@ -12411,13 +12411,13 @@
         <v>9</v>
       </c>
       <c r="D237" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="E237" t="s">
         <v>455</v>
       </c>
       <c r="F237" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="G237" t="s">
         <v>16</v>
@@ -12434,13 +12434,13 @@
         <v>9</v>
       </c>
       <c r="D238" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="E238" t="s">
         <v>455</v>
       </c>
       <c r="F238" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="G238" t="s">
         <v>25</v>
@@ -12457,13 +12457,13 @@
         <v>9</v>
       </c>
       <c r="D239" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="E239" t="s">
         <v>455</v>
       </c>
       <c r="F239" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="G239" t="s">
         <v>25</v>
@@ -12480,13 +12480,13 @@
         <v>9</v>
       </c>
       <c r="D240" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="E240" t="s">
         <v>455</v>
       </c>
       <c r="F240" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="G240" t="s">
         <v>16</v>
@@ -12503,13 +12503,13 @@
         <v>9</v>
       </c>
       <c r="D241" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="E241" t="s">
         <v>455</v>
       </c>
       <c r="F241" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="G241" t="s">
         <v>25</v>
@@ -12526,13 +12526,13 @@
         <v>9</v>
       </c>
       <c r="D242" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="E242" t="s">
         <v>455</v>
       </c>
       <c r="F242" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="G242" t="s">
         <v>25</v>
@@ -12549,13 +12549,13 @@
         <v>9</v>
       </c>
       <c r="D243" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="E243" t="s">
         <v>455</v>
       </c>
       <c r="F243" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="G243" t="s">
         <v>25</v>
@@ -12572,13 +12572,13 @@
         <v>9</v>
       </c>
       <c r="D244" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="E244" t="s">
         <v>455</v>
       </c>
       <c r="F244" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="G244" t="s">
         <v>25</v>
@@ -12618,13 +12618,13 @@
         <v>9</v>
       </c>
       <c r="D246" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E246" t="s">
         <v>574</v>
       </c>
       <c r="F246" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="G246" t="s">
         <v>20</v>
@@ -12664,13 +12664,13 @@
         <v>9</v>
       </c>
       <c r="D248" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E248" t="s">
         <v>574</v>
       </c>
       <c r="F248" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="G248" t="s">
         <v>20</v>
@@ -12756,13 +12756,13 @@
         <v>9</v>
       </c>
       <c r="D252" t="s">
-        <v>591</v>
+        <v>573</v>
       </c>
       <c r="E252" t="s">
         <v>574</v>
       </c>
       <c r="F252" t="s">
-        <v>575</v>
+        <v>591</v>
       </c>
       <c r="G252" t="s">
         <v>20</v>
@@ -12802,13 +12802,13 @@
         <v>9</v>
       </c>
       <c r="D254" t="s">
-        <v>596</v>
+        <v>573</v>
       </c>
       <c r="E254" t="s">
         <v>459</v>
       </c>
       <c r="F254" t="s">
-        <v>575</v>
+        <v>596</v>
       </c>
       <c r="G254" t="s">
         <v>25</v>
@@ -12871,13 +12871,13 @@
         <v>9</v>
       </c>
       <c r="D257" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E257" t="s">
         <v>574</v>
       </c>
       <c r="F257" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="G257" t="s">
         <v>20</v>
@@ -12894,13 +12894,13 @@
         <v>9</v>
       </c>
       <c r="D258" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E258" t="s">
         <v>574</v>
       </c>
       <c r="F258" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="G258" t="s">
         <v>20</v>
@@ -12917,13 +12917,13 @@
         <v>185</v>
       </c>
       <c r="D259" t="s">
-        <v>607</v>
+        <v>573</v>
       </c>
       <c r="E259" t="s">
         <v>574</v>
       </c>
       <c r="F259" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="G259" t="s">
         <v>25</v>
@@ -12986,13 +12986,13 @@
         <v>9</v>
       </c>
       <c r="D262" t="s">
+        <v>573</v>
+      </c>
+      <c r="E262" t="s">
         <v>614</v>
       </c>
-      <c r="E262" t="s">
+      <c r="F262" t="s">
         <v>615</v>
-      </c>
-      <c r="F262" t="s">
-        <v>575</v>
       </c>
       <c r="G262" t="s">
         <v>34</v>
@@ -13009,13 +13009,13 @@
         <v>9</v>
       </c>
       <c r="D263" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E263" t="s">
         <v>574</v>
       </c>
       <c r="F263" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="G263" t="s">
         <v>20</v>
@@ -13032,13 +13032,13 @@
         <v>185</v>
       </c>
       <c r="D264" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E264" t="s">
         <v>574</v>
       </c>
       <c r="F264" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="G264" t="s">
         <v>20</v>
@@ -13078,13 +13078,13 @@
         <v>9</v>
       </c>
       <c r="D266" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E266" t="s">
         <v>574</v>
       </c>
       <c r="F266" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="G266" t="s">
         <v>20</v>
@@ -13124,13 +13124,13 @@
         <v>9</v>
       </c>
       <c r="D268" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E268" t="s">
         <v>574</v>
       </c>
       <c r="F268" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="G268" t="s">
         <v>20</v>
@@ -13147,13 +13147,13 @@
         <v>9</v>
       </c>
       <c r="D269" t="s">
-        <v>607</v>
+        <v>573</v>
       </c>
       <c r="E269" t="s">
         <v>574</v>
       </c>
       <c r="F269" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="G269" t="s">
         <v>20</v>
@@ -13170,13 +13170,13 @@
         <v>185</v>
       </c>
       <c r="D270" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E270" t="s">
         <v>574</v>
       </c>
       <c r="F270" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="G270" t="s">
         <v>20</v>
@@ -13193,13 +13193,13 @@
         <v>9</v>
       </c>
       <c r="D271" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E271" t="s">
         <v>574</v>
       </c>
       <c r="F271" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="G271" t="s">
         <v>20</v>
@@ -13239,13 +13239,13 @@
         <v>9</v>
       </c>
       <c r="D273" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E273" t="s">
         <v>574</v>
       </c>
       <c r="F273" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="G273" t="s">
         <v>20</v>
@@ -13285,13 +13285,13 @@
         <v>9</v>
       </c>
       <c r="D275" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E275" t="s">
         <v>574</v>
       </c>
       <c r="F275" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="G275" t="s">
         <v>20</v>
@@ -13308,13 +13308,13 @@
         <v>9</v>
       </c>
       <c r="D276" t="s">
-        <v>644</v>
+        <v>573</v>
       </c>
       <c r="E276" t="s">
         <v>574</v>
       </c>
       <c r="F276" t="s">
-        <v>575</v>
+        <v>644</v>
       </c>
       <c r="G276" t="s">
         <v>20</v>
@@ -13331,13 +13331,13 @@
         <v>9</v>
       </c>
       <c r="D277" t="s">
+        <v>573</v>
+      </c>
+      <c r="E277" t="s">
         <v>647</v>
       </c>
-      <c r="E277" t="s">
+      <c r="F277" t="s">
         <v>648</v>
-      </c>
-      <c r="F277" t="s">
-        <v>575</v>
       </c>
       <c r="G277" t="s">
         <v>34</v>
@@ -13354,13 +13354,13 @@
         <v>9</v>
       </c>
       <c r="D278" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E278" t="s">
         <v>574</v>
       </c>
       <c r="F278" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="G278" t="s">
         <v>20</v>
@@ -13377,13 +13377,13 @@
         <v>9</v>
       </c>
       <c r="D279" t="s">
+        <v>573</v>
+      </c>
+      <c r="E279" t="s">
         <v>653</v>
       </c>
-      <c r="E279" t="s">
+      <c r="F279" t="s">
         <v>654</v>
-      </c>
-      <c r="F279" t="s">
-        <v>575</v>
       </c>
       <c r="G279" t="s">
         <v>34</v>
@@ -13400,13 +13400,13 @@
         <v>9</v>
       </c>
       <c r="D280" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E280" t="s">
         <v>574</v>
       </c>
       <c r="F280" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="G280" t="s">
         <v>20</v>
@@ -13469,13 +13469,13 @@
         <v>9</v>
       </c>
       <c r="D283" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E283" t="s">
         <v>574</v>
       </c>
       <c r="F283" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="G283" t="s">
         <v>20</v>
@@ -13584,13 +13584,13 @@
         <v>9</v>
       </c>
       <c r="D288" t="s">
-        <v>644</v>
+        <v>573</v>
       </c>
       <c r="E288" t="s">
         <v>574</v>
       </c>
       <c r="F288" t="s">
-        <v>575</v>
+        <v>644</v>
       </c>
       <c r="G288" t="s">
         <v>20</v>
@@ -13607,13 +13607,13 @@
         <v>9</v>
       </c>
       <c r="D289" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E289" t="s">
         <v>574</v>
       </c>
       <c r="F289" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="G289" t="s">
         <v>20</v>
@@ -13676,13 +13676,13 @@
         <v>9</v>
       </c>
       <c r="D292" t="s">
-        <v>644</v>
+        <v>573</v>
       </c>
       <c r="E292" t="s">
         <v>574</v>
       </c>
       <c r="F292" t="s">
-        <v>575</v>
+        <v>644</v>
       </c>
       <c r="G292" t="s">
         <v>20</v>
@@ -13699,13 +13699,13 @@
         <v>9</v>
       </c>
       <c r="D293" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E293" t="s">
         <v>574</v>
       </c>
       <c r="F293" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="G293" t="s">
         <v>20</v>
@@ -13860,13 +13860,13 @@
         <v>9</v>
       </c>
       <c r="D300" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E300" t="s">
         <v>574</v>
       </c>
       <c r="F300" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="G300" t="s">
         <v>20</v>
@@ -13883,13 +13883,13 @@
         <v>9</v>
       </c>
       <c r="D301" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E301" t="s">
         <v>574</v>
       </c>
       <c r="F301" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="G301" t="s">
         <v>20</v>
@@ -13906,13 +13906,13 @@
         <v>9</v>
       </c>
       <c r="D302" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E302" t="s">
         <v>574</v>
       </c>
       <c r="F302" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="G302" t="s">
         <v>20</v>
@@ -13952,13 +13952,13 @@
         <v>9</v>
       </c>
       <c r="D304" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E304" t="s">
         <v>574</v>
       </c>
       <c r="F304" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="G304" t="s">
         <v>20</v>
@@ -14021,13 +14021,13 @@
         <v>9</v>
       </c>
       <c r="D307" t="s">
+        <v>573</v>
+      </c>
+      <c r="E307" t="s">
+        <v>614</v>
+      </c>
+      <c r="F307" t="s">
         <v>711</v>
-      </c>
-      <c r="E307" t="s">
-        <v>615</v>
-      </c>
-      <c r="F307" t="s">
-        <v>575</v>
       </c>
       <c r="G307" t="s">
         <v>20</v>
@@ -14044,13 +14044,13 @@
         <v>9</v>
       </c>
       <c r="D308" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E308" t="s">
         <v>574</v>
       </c>
       <c r="F308" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="G308" t="s">
         <v>20</v>
@@ -14389,13 +14389,13 @@
         <v>9</v>
       </c>
       <c r="D323" t="s">
-        <v>747</v>
+        <v>718</v>
       </c>
       <c r="E323" t="s">
         <v>719</v>
       </c>
       <c r="F323" t="s">
-        <v>720</v>
+        <v>747</v>
       </c>
       <c r="G323" t="s">
         <v>20</v>
@@ -14849,13 +14849,13 @@
         <v>9</v>
       </c>
       <c r="D343" t="s">
+        <v>718</v>
+      </c>
+      <c r="E343" t="s">
         <v>790</v>
       </c>
-      <c r="E343" t="s">
+      <c r="F343" t="s">
         <v>791</v>
-      </c>
-      <c r="F343" t="s">
-        <v>720</v>
       </c>
       <c r="G343" t="s">
         <v>34</v>
@@ -14872,13 +14872,13 @@
         <v>185</v>
       </c>
       <c r="D344" t="s">
+        <v>718</v>
+      </c>
+      <c r="E344" t="s">
+        <v>790</v>
+      </c>
+      <c r="F344" t="s">
         <v>794</v>
-      </c>
-      <c r="E344" t="s">
-        <v>791</v>
-      </c>
-      <c r="F344" t="s">
-        <v>720</v>
       </c>
       <c r="G344" t="s">
         <v>34</v>
@@ -14918,13 +14918,13 @@
         <v>185</v>
       </c>
       <c r="D346" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
       <c r="E346" t="s">
         <v>798</v>
       </c>
       <c r="F346" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="G346" t="s">
         <v>20</v>
@@ -15148,13 +15148,13 @@
         <v>9</v>
       </c>
       <c r="D356" t="s">
-        <v>823</v>
+        <v>797</v>
       </c>
       <c r="E356" t="s">
         <v>798</v>
       </c>
       <c r="F356" t="s">
-        <v>799</v>
+        <v>823</v>
       </c>
       <c r="G356" t="s">
         <v>20</v>
@@ -15378,13 +15378,13 @@
         <v>9</v>
       </c>
       <c r="D366" t="s">
-        <v>844</v>
+        <v>797</v>
       </c>
       <c r="E366" t="s">
         <v>798</v>
       </c>
       <c r="F366" t="s">
-        <v>799</v>
+        <v>844</v>
       </c>
       <c r="G366" t="s">
         <v>20</v>
@@ -15401,13 +15401,13 @@
         <v>9</v>
       </c>
       <c r="D367" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
       <c r="E367" t="s">
         <v>798</v>
       </c>
       <c r="F367" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="G367" t="s">
         <v>16</v>
@@ -15516,13 +15516,13 @@
         <v>9</v>
       </c>
       <c r="D372" t="s">
+        <v>797</v>
+      </c>
+      <c r="E372" t="s">
         <v>858</v>
       </c>
-      <c r="E372" t="s">
+      <c r="F372" t="s">
         <v>859</v>
-      </c>
-      <c r="F372" t="s">
-        <v>799</v>
       </c>
       <c r="G372" t="s">
         <v>25</v>
@@ -15562,13 +15562,13 @@
         <v>185</v>
       </c>
       <c r="D374" t="s">
+        <v>797</v>
+      </c>
+      <c r="E374" t="s">
         <v>858</v>
       </c>
-      <c r="E374" t="s">
+      <c r="F374" t="s">
         <v>859</v>
-      </c>
-      <c r="F374" t="s">
-        <v>799</v>
       </c>
       <c r="G374" t="s">
         <v>25</v>
@@ -15700,13 +15700,13 @@
         <v>9</v>
       </c>
       <c r="D380" t="s">
-        <v>879</v>
+        <v>872</v>
       </c>
       <c r="E380" t="s">
         <v>873</v>
       </c>
       <c r="F380" t="s">
-        <v>874</v>
+        <v>879</v>
       </c>
       <c r="G380" t="s">
         <v>16</v>
@@ -15838,13 +15838,13 @@
         <v>9</v>
       </c>
       <c r="D386" t="s">
-        <v>892</v>
+        <v>872</v>
       </c>
       <c r="E386" t="s">
         <v>873</v>
       </c>
       <c r="F386" t="s">
-        <v>874</v>
+        <v>892</v>
       </c>
       <c r="G386" t="s">
         <v>20</v>
@@ -15861,13 +15861,13 @@
         <v>9</v>
       </c>
       <c r="D387" t="s">
-        <v>895</v>
+        <v>872</v>
       </c>
       <c r="E387" t="s">
         <v>873</v>
       </c>
       <c r="F387" t="s">
-        <v>874</v>
+        <v>895</v>
       </c>
       <c r="G387" t="s">
         <v>25</v>
@@ -15907,13 +15907,13 @@
         <v>9</v>
       </c>
       <c r="D389" t="s">
+        <v>872</v>
+      </c>
+      <c r="E389" t="s">
         <v>900</v>
       </c>
-      <c r="E389" t="s">
+      <c r="F389" t="s">
         <v>901</v>
-      </c>
-      <c r="F389" t="s">
-        <v>874</v>
       </c>
       <c r="G389" t="s">
         <v>34</v>
@@ -15999,13 +15999,13 @@
         <v>9</v>
       </c>
       <c r="D393" t="s">
-        <v>910</v>
+        <v>872</v>
       </c>
       <c r="E393" t="s">
         <v>873</v>
       </c>
       <c r="F393" t="s">
-        <v>874</v>
+        <v>910</v>
       </c>
       <c r="G393" t="s">
         <v>20</v>
@@ -16045,13 +16045,13 @@
         <v>9</v>
       </c>
       <c r="D395" t="s">
+        <v>872</v>
+      </c>
+      <c r="E395" t="s">
         <v>915</v>
       </c>
-      <c r="E395" t="s">
+      <c r="F395" t="s">
         <v>916</v>
-      </c>
-      <c r="F395" t="s">
-        <v>874</v>
       </c>
       <c r="G395" t="s">
         <v>34</v>
@@ -16091,13 +16091,13 @@
         <v>9</v>
       </c>
       <c r="D397" t="s">
+        <v>872</v>
+      </c>
+      <c r="E397" t="s">
         <v>921</v>
       </c>
-      <c r="E397" t="s">
+      <c r="F397" t="s">
         <v>922</v>
-      </c>
-      <c r="F397" t="s">
-        <v>874</v>
       </c>
       <c r="G397" t="s">
         <v>34</v>
@@ -16160,13 +16160,13 @@
         <v>9</v>
       </c>
       <c r="D400" t="s">
+        <v>872</v>
+      </c>
+      <c r="E400" t="s">
         <v>929</v>
       </c>
-      <c r="E400" t="s">
+      <c r="F400" t="s">
         <v>930</v>
-      </c>
-      <c r="F400" t="s">
-        <v>874</v>
       </c>
       <c r="G400" t="s">
         <v>34</v>
@@ -16298,13 +16298,13 @@
         <v>9</v>
       </c>
       <c r="D406" t="s">
+        <v>872</v>
+      </c>
+      <c r="E406" t="s">
         <v>943</v>
       </c>
-      <c r="E406" t="s">
+      <c r="F406" t="s">
         <v>944</v>
-      </c>
-      <c r="F406" t="s">
-        <v>874</v>
       </c>
       <c r="G406" t="s">
         <v>34</v>
@@ -16321,13 +16321,13 @@
         <v>9</v>
       </c>
       <c r="D407" t="s">
-        <v>947</v>
+        <v>872</v>
       </c>
       <c r="E407" t="s">
         <v>873</v>
       </c>
       <c r="F407" t="s">
-        <v>874</v>
+        <v>947</v>
       </c>
       <c r="G407" t="s">
         <v>25</v>
@@ -16597,13 +16597,13 @@
         <v>9</v>
       </c>
       <c r="D419" t="s">
-        <v>974</v>
+        <v>967</v>
       </c>
       <c r="E419" t="s">
         <v>968</v>
       </c>
       <c r="F419" t="s">
-        <v>969</v>
+        <v>974</v>
       </c>
       <c r="G419" t="s">
         <v>34</v>
@@ -16643,13 +16643,13 @@
         <v>9</v>
       </c>
       <c r="D421" t="s">
-        <v>979</v>
+        <v>967</v>
       </c>
       <c r="E421" t="s">
         <v>968</v>
       </c>
       <c r="F421" t="s">
-        <v>969</v>
+        <v>979</v>
       </c>
       <c r="G421" t="s">
         <v>25</v>
@@ -16804,13 +16804,13 @@
         <v>9</v>
       </c>
       <c r="D428" t="s">
+        <v>967</v>
+      </c>
+      <c r="E428" t="s">
         <v>994</v>
       </c>
-      <c r="E428" t="s">
+      <c r="F428" t="s">
         <v>995</v>
-      </c>
-      <c r="F428" t="s">
-        <v>969</v>
       </c>
       <c r="G428" t="s">
         <v>34</v>
@@ -16827,13 +16827,13 @@
         <v>9</v>
       </c>
       <c r="D429" t="s">
+        <v>967</v>
+      </c>
+      <c r="E429" t="s">
         <v>998</v>
       </c>
-      <c r="E429" t="s">
+      <c r="F429" t="s">
         <v>999</v>
-      </c>
-      <c r="F429" t="s">
-        <v>969</v>
       </c>
       <c r="G429" t="s">
         <v>34</v>
@@ -16919,13 +16919,13 @@
         <v>9</v>
       </c>
       <c r="D433" t="s">
-        <v>1008</v>
+        <v>967</v>
       </c>
       <c r="E433" t="s">
         <v>968</v>
       </c>
       <c r="F433" t="s">
-        <v>969</v>
+        <v>1008</v>
       </c>
       <c r="G433" t="s">
         <v>34</v>
@@ -16988,13 +16988,13 @@
         <v>9</v>
       </c>
       <c r="D436" t="s">
-        <v>1015</v>
+        <v>967</v>
       </c>
       <c r="E436" t="s">
         <v>968</v>
       </c>
       <c r="F436" t="s">
-        <v>969</v>
+        <v>1015</v>
       </c>
       <c r="G436" t="s">
         <v>34</v>
@@ -17011,13 +17011,13 @@
         <v>9</v>
       </c>
       <c r="D437" t="s">
-        <v>1018</v>
+        <v>967</v>
       </c>
       <c r="E437" t="s">
         <v>968</v>
       </c>
       <c r="F437" t="s">
-        <v>969</v>
+        <v>1018</v>
       </c>
       <c r="G437" t="s">
         <v>25</v>
@@ -17080,13 +17080,13 @@
         <v>9</v>
       </c>
       <c r="D440" t="s">
+        <v>967</v>
+      </c>
+      <c r="E440" t="s">
         <v>1025</v>
       </c>
-      <c r="E440" t="s">
+      <c r="F440" t="s">
         <v>1026</v>
-      </c>
-      <c r="F440" t="s">
-        <v>969</v>
       </c>
       <c r="G440" t="s">
         <v>34</v>
@@ -17402,13 +17402,13 @@
         <v>9</v>
       </c>
       <c r="D454" t="s">
+        <v>967</v>
+      </c>
+      <c r="E454" t="s">
         <v>1055</v>
       </c>
-      <c r="E454" t="s">
+      <c r="F454" t="s">
         <v>1056</v>
-      </c>
-      <c r="F454" t="s">
-        <v>969</v>
       </c>
       <c r="G454" t="s">
         <v>25</v>
@@ -17632,13 +17632,13 @@
         <v>9</v>
       </c>
       <c r="D464" t="s">
+        <v>1059</v>
+      </c>
+      <c r="E464" t="s">
         <v>1081</v>
       </c>
-      <c r="E464" t="s">
+      <c r="F464" t="s">
         <v>1082</v>
-      </c>
-      <c r="F464" t="s">
-        <v>1061</v>
       </c>
       <c r="G464" t="s">
         <v>34</v>
@@ -17655,13 +17655,13 @@
         <v>9</v>
       </c>
       <c r="D465" t="s">
-        <v>1085</v>
+        <v>1059</v>
       </c>
       <c r="E465" t="s">
         <v>1060</v>
       </c>
       <c r="F465" t="s">
-        <v>1061</v>
+        <v>1085</v>
       </c>
       <c r="G465" t="s">
         <v>34</v>
@@ -17678,13 +17678,13 @@
         <v>9</v>
       </c>
       <c r="D466" t="s">
+        <v>1059</v>
+      </c>
+      <c r="E466" t="s">
+        <v>1081</v>
+      </c>
+      <c r="F466" t="s">
         <v>1088</v>
-      </c>
-      <c r="E466" t="s">
-        <v>1082</v>
-      </c>
-      <c r="F466" t="s">
-        <v>1061</v>
       </c>
       <c r="G466" t="s">
         <v>34</v>
@@ -17701,13 +17701,13 @@
         <v>9</v>
       </c>
       <c r="D467" t="s">
+        <v>1059</v>
+      </c>
+      <c r="E467" t="s">
         <v>1091</v>
       </c>
-      <c r="E467" t="s">
+      <c r="F467" t="s">
         <v>1092</v>
-      </c>
-      <c r="F467" t="s">
-        <v>1061</v>
       </c>
       <c r="G467" t="s">
         <v>34</v>
@@ -17747,13 +17747,13 @@
         <v>9</v>
       </c>
       <c r="D469" t="s">
+        <v>1059</v>
+      </c>
+      <c r="E469" t="s">
         <v>1097</v>
       </c>
-      <c r="E469" t="s">
+      <c r="F469" t="s">
         <v>1098</v>
-      </c>
-      <c r="F469" t="s">
-        <v>1061</v>
       </c>
       <c r="G469" t="s">
         <v>34</v>
@@ -17839,13 +17839,13 @@
         <v>9</v>
       </c>
       <c r="D473" t="s">
+        <v>1059</v>
+      </c>
+      <c r="E473" t="s">
+        <v>1081</v>
+      </c>
+      <c r="F473" t="s">
         <v>1107</v>
-      </c>
-      <c r="E473" t="s">
-        <v>1082</v>
-      </c>
-      <c r="F473" t="s">
-        <v>1061</v>
       </c>
       <c r="G473" t="s">
         <v>34</v>
@@ -18184,13 +18184,13 @@
         <v>9</v>
       </c>
       <c r="D488" t="s">
-        <v>1141</v>
+        <v>1136</v>
       </c>
       <c r="E488" t="s">
         <v>1137</v>
       </c>
       <c r="F488" t="s">
-        <v>1138</v>
+        <v>1141</v>
       </c>
       <c r="G488" t="s">
         <v>1062</v>
@@ -18322,13 +18322,13 @@
         <v>9</v>
       </c>
       <c r="D494" t="s">
-        <v>1097</v>
+        <v>1136</v>
       </c>
       <c r="E494" t="s">
         <v>1155</v>
       </c>
       <c r="F494" t="s">
-        <v>1138</v>
+        <v>1098</v>
       </c>
       <c r="G494" t="s">
         <v>16</v>
@@ -18345,13 +18345,13 @@
         <v>185</v>
       </c>
       <c r="D495" t="s">
-        <v>1097</v>
+        <v>1136</v>
       </c>
       <c r="E495" t="s">
         <v>1155</v>
       </c>
       <c r="F495" t="s">
-        <v>1138</v>
+        <v>1098</v>
       </c>
       <c r="G495" t="s">
         <v>20</v>
@@ -18414,13 +18414,13 @@
         <v>9</v>
       </c>
       <c r="D498" t="s">
-        <v>1164</v>
+        <v>1136</v>
       </c>
       <c r="E498" t="s">
         <v>1137</v>
       </c>
       <c r="F498" t="s">
-        <v>1138</v>
+        <v>1164</v>
       </c>
       <c r="G498" t="s">
         <v>1062</v>
@@ -18506,13 +18506,13 @@
         <v>185</v>
       </c>
       <c r="D502" t="s">
-        <v>1173</v>
+        <v>1136</v>
       </c>
       <c r="E502" t="s">
         <v>1137</v>
       </c>
       <c r="F502" t="s">
-        <v>1138</v>
+        <v>1173</v>
       </c>
       <c r="G502" t="s">
         <v>25</v>
@@ -18621,13 +18621,13 @@
         <v>9</v>
       </c>
       <c r="D507" t="s">
+        <v>1136</v>
+      </c>
+      <c r="E507" t="s">
         <v>1184</v>
       </c>
-      <c r="E507" t="s">
+      <c r="F507" t="s">
         <v>1185</v>
-      </c>
-      <c r="F507" t="s">
-        <v>1138</v>
       </c>
       <c r="G507" t="s">
         <v>34</v>
@@ -18644,13 +18644,13 @@
         <v>9</v>
       </c>
       <c r="D508" t="s">
+        <v>1136</v>
+      </c>
+      <c r="E508" t="s">
         <v>1188</v>
       </c>
-      <c r="E508" t="s">
+      <c r="F508" t="s">
         <v>1189</v>
-      </c>
-      <c r="F508" t="s">
-        <v>1138</v>
       </c>
       <c r="G508" t="s">
         <v>1062</v>
@@ -18667,13 +18667,13 @@
         <v>185</v>
       </c>
       <c r="D509" t="s">
-        <v>1188</v>
+        <v>1136</v>
       </c>
       <c r="E509" t="s">
         <v>1192</v>
       </c>
       <c r="F509" t="s">
-        <v>1138</v>
+        <v>1189</v>
       </c>
       <c r="G509" t="s">
         <v>25</v>
@@ -18690,13 +18690,13 @@
         <v>9</v>
       </c>
       <c r="D510" t="s">
+        <v>1136</v>
+      </c>
+      <c r="E510" t="s">
         <v>1195</v>
       </c>
-      <c r="E510" t="s">
+      <c r="F510" t="s">
         <v>1196</v>
-      </c>
-      <c r="F510" t="s">
-        <v>1138</v>
       </c>
       <c r="G510" t="s">
         <v>34</v>
@@ -18736,13 +18736,13 @@
         <v>9</v>
       </c>
       <c r="D512" t="s">
-        <v>1201</v>
+        <v>1136</v>
       </c>
       <c r="E512" t="s">
         <v>1137</v>
       </c>
       <c r="F512" t="s">
-        <v>1138</v>
+        <v>1201</v>
       </c>
       <c r="G512" t="s">
         <v>20</v>
@@ -18943,13 +18943,13 @@
         <v>185</v>
       </c>
       <c r="D521" t="s">
-        <v>1221</v>
+        <v>1136</v>
       </c>
       <c r="E521" t="s">
         <v>1137</v>
       </c>
       <c r="F521" t="s">
-        <v>1138</v>
+        <v>1221</v>
       </c>
       <c r="G521" t="s">
         <v>25</v>
@@ -18966,13 +18966,13 @@
         <v>185</v>
       </c>
       <c r="D522" t="s">
-        <v>1224</v>
+        <v>1136</v>
       </c>
       <c r="E522" t="s">
         <v>1137</v>
       </c>
       <c r="F522" t="s">
-        <v>1138</v>
+        <v>1224</v>
       </c>
       <c r="G522" t="s">
         <v>16</v>
@@ -18989,13 +18989,13 @@
         <v>9</v>
       </c>
       <c r="D523" t="s">
-        <v>1227</v>
+        <v>1136</v>
       </c>
       <c r="E523" t="s">
         <v>1137</v>
       </c>
       <c r="F523" t="s">
-        <v>1138</v>
+        <v>1227</v>
       </c>
       <c r="G523" t="s">
         <v>34</v>
@@ -19035,13 +19035,13 @@
         <v>9</v>
       </c>
       <c r="D525" t="s">
+        <v>1232</v>
+      </c>
+      <c r="E525" t="s">
+        <v>1233</v>
+      </c>
+      <c r="F525" t="s">
         <v>1141</v>
-      </c>
-      <c r="E525" t="s">
-        <v>1232</v>
-      </c>
-      <c r="F525" t="s">
-        <v>1233</v>
       </c>
       <c r="G525" t="s">
         <v>1234</v>
@@ -19058,13 +19058,13 @@
         <v>9</v>
       </c>
       <c r="D526" t="s">
+        <v>1232</v>
+      </c>
+      <c r="E526" t="s">
+        <v>1233</v>
+      </c>
+      <c r="F526" t="s">
         <v>1141</v>
-      </c>
-      <c r="E526" t="s">
-        <v>1232</v>
-      </c>
-      <c r="F526" t="s">
-        <v>1233</v>
       </c>
       <c r="G526" t="s">
         <v>1234</v>
@@ -19081,13 +19081,13 @@
         <v>9</v>
       </c>
       <c r="D527" t="s">
+        <v>1232</v>
+      </c>
+      <c r="E527" t="s">
+        <v>1233</v>
+      </c>
+      <c r="F527" t="s">
         <v>1141</v>
-      </c>
-      <c r="E527" t="s">
-        <v>1232</v>
-      </c>
-      <c r="F527" t="s">
-        <v>1233</v>
       </c>
       <c r="G527" t="s">
         <v>1234</v>
@@ -19104,13 +19104,13 @@
         <v>9</v>
       </c>
       <c r="D528" t="s">
+        <v>1232</v>
+      </c>
+      <c r="E528" t="s">
+        <v>1233</v>
+      </c>
+      <c r="F528" t="s">
         <v>1141</v>
-      </c>
-      <c r="E528" t="s">
-        <v>1232</v>
-      </c>
-      <c r="F528" t="s">
-        <v>1233</v>
       </c>
       <c r="G528" t="s">
         <v>1234</v>
@@ -19127,13 +19127,13 @@
         <v>9</v>
       </c>
       <c r="D529" t="s">
+        <v>1232</v>
+      </c>
+      <c r="E529" t="s">
+        <v>1233</v>
+      </c>
+      <c r="F529" t="s">
         <v>1243</v>
-      </c>
-      <c r="E529" t="s">
-        <v>1232</v>
-      </c>
-      <c r="F529" t="s">
-        <v>1233</v>
       </c>
       <c r="G529" t="s">
         <v>20</v>
@@ -19150,13 +19150,13 @@
         <v>9</v>
       </c>
       <c r="D530" t="s">
-        <v>1141</v>
+        <v>1232</v>
       </c>
       <c r="E530" t="s">
         <v>1246</v>
       </c>
       <c r="F530" t="s">
-        <v>1233</v>
+        <v>1141</v>
       </c>
       <c r="G530" t="s">
         <v>1234</v>
@@ -19173,13 +19173,13 @@
         <v>9</v>
       </c>
       <c r="D531" t="s">
+        <v>1232</v>
+      </c>
+      <c r="E531" t="s">
+        <v>1233</v>
+      </c>
+      <c r="F531" t="s">
         <v>1141</v>
-      </c>
-      <c r="E531" t="s">
-        <v>1232</v>
-      </c>
-      <c r="F531" t="s">
-        <v>1233</v>
       </c>
       <c r="G531" t="s">
         <v>1234</v>
@@ -19196,13 +19196,13 @@
         <v>9</v>
       </c>
       <c r="D532" t="s">
+        <v>1232</v>
+      </c>
+      <c r="E532" t="s">
+        <v>1233</v>
+      </c>
+      <c r="F532" t="s">
         <v>1141</v>
-      </c>
-      <c r="E532" t="s">
-        <v>1232</v>
-      </c>
-      <c r="F532" t="s">
-        <v>1233</v>
       </c>
       <c r="G532" t="s">
         <v>1234</v>
@@ -19219,13 +19219,13 @@
         <v>9</v>
       </c>
       <c r="D533" t="s">
+        <v>1232</v>
+      </c>
+      <c r="E533" t="s">
+        <v>1233</v>
+      </c>
+      <c r="F533" t="s">
         <v>1141</v>
-      </c>
-      <c r="E533" t="s">
-        <v>1232</v>
-      </c>
-      <c r="F533" t="s">
-        <v>1233</v>
       </c>
       <c r="G533" t="s">
         <v>1234</v>
@@ -19242,13 +19242,13 @@
         <v>9</v>
       </c>
       <c r="D534" t="s">
+        <v>1232</v>
+      </c>
+      <c r="E534" t="s">
+        <v>1233</v>
+      </c>
+      <c r="F534" t="s">
         <v>1141</v>
-      </c>
-      <c r="E534" t="s">
-        <v>1232</v>
-      </c>
-      <c r="F534" t="s">
-        <v>1233</v>
       </c>
       <c r="G534" t="s">
         <v>1234</v>
@@ -19265,13 +19265,13 @@
         <v>9</v>
       </c>
       <c r="D535" t="s">
+        <v>1232</v>
+      </c>
+      <c r="E535" t="s">
+        <v>1233</v>
+      </c>
+      <c r="F535" t="s">
         <v>1141</v>
-      </c>
-      <c r="E535" t="s">
-        <v>1232</v>
-      </c>
-      <c r="F535" t="s">
-        <v>1233</v>
       </c>
       <c r="G535" t="s">
         <v>1234</v>
@@ -19288,13 +19288,13 @@
         <v>9</v>
       </c>
       <c r="D536" t="s">
+        <v>1232</v>
+      </c>
+      <c r="E536" t="s">
+        <v>1233</v>
+      </c>
+      <c r="F536" t="s">
         <v>1259</v>
-      </c>
-      <c r="E536" t="s">
-        <v>1232</v>
-      </c>
-      <c r="F536" t="s">
-        <v>1233</v>
       </c>
       <c r="G536" t="s">
         <v>20</v>
@@ -19311,13 +19311,13 @@
         <v>9</v>
       </c>
       <c r="D537" t="s">
+        <v>1232</v>
+      </c>
+      <c r="E537" t="s">
+        <v>1233</v>
+      </c>
+      <c r="F537" t="s">
         <v>1262</v>
-      </c>
-      <c r="E537" t="s">
-        <v>1232</v>
-      </c>
-      <c r="F537" t="s">
-        <v>1233</v>
       </c>
       <c r="G537" t="s">
         <v>20</v>
@@ -19334,13 +19334,13 @@
         <v>9</v>
       </c>
       <c r="D538" t="s">
+        <v>1232</v>
+      </c>
+      <c r="E538" t="s">
+        <v>1233</v>
+      </c>
+      <c r="F538" t="s">
         <v>1141</v>
-      </c>
-      <c r="E538" t="s">
-        <v>1232</v>
-      </c>
-      <c r="F538" t="s">
-        <v>1233</v>
       </c>
       <c r="G538" t="s">
         <v>1234</v>
@@ -19357,13 +19357,13 @@
         <v>9</v>
       </c>
       <c r="D539" t="s">
+        <v>1232</v>
+      </c>
+      <c r="E539" t="s">
+        <v>1233</v>
+      </c>
+      <c r="F539" t="s">
         <v>1141</v>
-      </c>
-      <c r="E539" t="s">
-        <v>1232</v>
-      </c>
-      <c r="F539" t="s">
-        <v>1233</v>
       </c>
       <c r="G539" t="s">
         <v>1234</v>
@@ -19380,13 +19380,13 @@
         <v>9</v>
       </c>
       <c r="D540" t="s">
+        <v>1232</v>
+      </c>
+      <c r="E540" t="s">
+        <v>1195</v>
+      </c>
+      <c r="F540" t="s">
         <v>1141</v>
-      </c>
-      <c r="E540" t="s">
-        <v>1196</v>
-      </c>
-      <c r="F540" t="s">
-        <v>1233</v>
       </c>
       <c r="G540" t="s">
         <v>1234</v>
@@ -19403,13 +19403,13 @@
         <v>9</v>
       </c>
       <c r="D541" t="s">
+        <v>1232</v>
+      </c>
+      <c r="E541" t="s">
+        <v>1233</v>
+      </c>
+      <c r="F541" t="s">
         <v>1141</v>
-      </c>
-      <c r="E541" t="s">
-        <v>1232</v>
-      </c>
-      <c r="F541" t="s">
-        <v>1233</v>
       </c>
       <c r="G541" t="s">
         <v>1234</v>
@@ -19426,13 +19426,13 @@
         <v>9</v>
       </c>
       <c r="D542" t="s">
+        <v>1232</v>
+      </c>
+      <c r="E542" t="s">
+        <v>1233</v>
+      </c>
+      <c r="F542" t="s">
         <v>1141</v>
-      </c>
-      <c r="E542" t="s">
-        <v>1232</v>
-      </c>
-      <c r="F542" t="s">
-        <v>1233</v>
       </c>
       <c r="G542" t="s">
         <v>1234</v>
@@ -19449,13 +19449,13 @@
         <v>9</v>
       </c>
       <c r="D543" t="s">
+        <v>1232</v>
+      </c>
+      <c r="E543" t="s">
+        <v>1233</v>
+      </c>
+      <c r="F543" t="s">
         <v>1141</v>
-      </c>
-      <c r="E543" t="s">
-        <v>1232</v>
-      </c>
-      <c r="F543" t="s">
-        <v>1233</v>
       </c>
       <c r="G543" t="s">
         <v>1234</v>
@@ -19472,13 +19472,13 @@
         <v>9</v>
       </c>
       <c r="D544" t="s">
+        <v>1232</v>
+      </c>
+      <c r="E544" t="s">
+        <v>1233</v>
+      </c>
+      <c r="F544" t="s">
         <v>1141</v>
-      </c>
-      <c r="E544" t="s">
-        <v>1232</v>
-      </c>
-      <c r="F544" t="s">
-        <v>1233</v>
       </c>
       <c r="G544" t="s">
         <v>1234</v>
@@ -19495,13 +19495,13 @@
         <v>9</v>
       </c>
       <c r="D545" t="s">
-        <v>1141</v>
+        <v>1232</v>
       </c>
       <c r="E545" t="s">
         <v>1279</v>
       </c>
       <c r="F545" t="s">
-        <v>1233</v>
+        <v>1141</v>
       </c>
       <c r="G545" t="s">
         <v>16</v>
@@ -19518,13 +19518,13 @@
         <v>9</v>
       </c>
       <c r="D546" t="s">
+        <v>1232</v>
+      </c>
+      <c r="E546" t="s">
+        <v>1233</v>
+      </c>
+      <c r="F546" t="s">
         <v>1141</v>
-      </c>
-      <c r="E546" t="s">
-        <v>1232</v>
-      </c>
-      <c r="F546" t="s">
-        <v>1233</v>
       </c>
       <c r="G546" t="s">
         <v>1234</v>
@@ -19541,13 +19541,13 @@
         <v>9</v>
       </c>
       <c r="D547" t="s">
+        <v>1232</v>
+      </c>
+      <c r="E547" t="s">
+        <v>1233</v>
+      </c>
+      <c r="F547" t="s">
         <v>1141</v>
-      </c>
-      <c r="E547" t="s">
-        <v>1232</v>
-      </c>
-      <c r="F547" t="s">
-        <v>1233</v>
       </c>
       <c r="G547" t="s">
         <v>20</v>
@@ -19587,13 +19587,13 @@
         <v>9</v>
       </c>
       <c r="D549" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
       <c r="E549" t="s">
         <v>1287</v>
       </c>
       <c r="F549" t="s">
-        <v>1288</v>
+        <v>1291</v>
       </c>
       <c r="G549" t="s">
         <v>1234</v>
@@ -19610,13 +19610,13 @@
         <v>9</v>
       </c>
       <c r="D550" t="s">
-        <v>1294</v>
+        <v>1286</v>
       </c>
       <c r="E550" t="s">
         <v>1287</v>
       </c>
       <c r="F550" t="s">
-        <v>1288</v>
+        <v>1294</v>
       </c>
       <c r="G550" t="s">
         <v>1234</v>
@@ -19794,13 +19794,13 @@
         <v>9</v>
       </c>
       <c r="D558" t="s">
+        <v>1286</v>
+      </c>
+      <c r="E558" t="s">
         <v>1312</v>
       </c>
-      <c r="E558" t="s">
+      <c r="F558" t="s">
         <v>1313</v>
-      </c>
-      <c r="F558" t="s">
-        <v>1288</v>
       </c>
       <c r="G558" t="s">
         <v>34</v>
@@ -19840,13 +19840,13 @@
         <v>9</v>
       </c>
       <c r="D560" t="s">
-        <v>1318</v>
+        <v>1286</v>
       </c>
       <c r="E560" t="s">
         <v>1287</v>
       </c>
       <c r="F560" t="s">
-        <v>1288</v>
+        <v>1318</v>
       </c>
       <c r="G560" t="s">
         <v>1234</v>
@@ -19863,13 +19863,13 @@
         <v>9</v>
       </c>
       <c r="D561" t="s">
-        <v>1318</v>
+        <v>1286</v>
       </c>
       <c r="E561" t="s">
         <v>1287</v>
       </c>
       <c r="F561" t="s">
-        <v>1288</v>
+        <v>1318</v>
       </c>
       <c r="G561" t="s">
         <v>1234</v>
@@ -20047,13 +20047,13 @@
         <v>9</v>
       </c>
       <c r="D569" t="s">
+        <v>1286</v>
+      </c>
+      <c r="E569" t="s">
         <v>1338</v>
       </c>
-      <c r="E569" t="s">
+      <c r="F569" t="s">
         <v>1339</v>
-      </c>
-      <c r="F569" t="s">
-        <v>1288</v>
       </c>
       <c r="G569" t="s">
         <v>1234</v>
@@ -20142,7 +20142,7 @@
         <v>1348</v>
       </c>
       <c r="E573" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="F573" t="s">
         <v>1349</v>
@@ -20254,13 +20254,13 @@
         <v>9</v>
       </c>
       <c r="D578" t="s">
-        <v>1361</v>
+        <v>1348</v>
       </c>
       <c r="E578" t="s">
         <v>1352</v>
       </c>
       <c r="F578" t="s">
-        <v>1349</v>
+        <v>1361</v>
       </c>
       <c r="G578" t="s">
         <v>1234</v>
@@ -20277,13 +20277,13 @@
         <v>9</v>
       </c>
       <c r="D579" t="s">
+        <v>1348</v>
+      </c>
+      <c r="E579" t="s">
         <v>1364</v>
       </c>
-      <c r="E579" t="s">
+      <c r="F579" t="s">
         <v>1365</v>
-      </c>
-      <c r="F579" t="s">
-        <v>1349</v>
       </c>
       <c r="G579" t="s">
         <v>34</v>
@@ -20300,13 +20300,13 @@
         <v>9</v>
       </c>
       <c r="D580" t="s">
-        <v>1368</v>
+        <v>1348</v>
       </c>
       <c r="E580" t="s">
         <v>1352</v>
       </c>
       <c r="F580" t="s">
-        <v>1349</v>
+        <v>1368</v>
       </c>
       <c r="G580" t="s">
         <v>1234</v>
@@ -20323,13 +20323,13 @@
         <v>9</v>
       </c>
       <c r="D581" t="s">
-        <v>1371</v>
+        <v>1348</v>
       </c>
       <c r="E581" t="s">
         <v>1352</v>
       </c>
       <c r="F581" t="s">
-        <v>1349</v>
+        <v>1371</v>
       </c>
       <c r="G581" t="s">
         <v>20</v>
@@ -20369,13 +20369,13 @@
         <v>9</v>
       </c>
       <c r="D583" t="s">
+        <v>1348</v>
+      </c>
+      <c r="E583" t="s">
         <v>1376</v>
       </c>
-      <c r="E583" t="s">
+      <c r="F583" t="s">
         <v>1377</v>
-      </c>
-      <c r="F583" t="s">
-        <v>1349</v>
       </c>
       <c r="G583" t="s">
         <v>34</v>
@@ -20392,13 +20392,13 @@
         <v>9</v>
       </c>
       <c r="D584" t="s">
+        <v>1348</v>
+      </c>
+      <c r="E584" t="s">
         <v>1380</v>
       </c>
-      <c r="E584" t="s">
+      <c r="F584" t="s">
         <v>1381</v>
-      </c>
-      <c r="F584" t="s">
-        <v>1349</v>
       </c>
       <c r="G584" t="s">
         <v>34</v>
@@ -20438,13 +20438,13 @@
         <v>9</v>
       </c>
       <c r="D586" t="s">
+        <v>1348</v>
+      </c>
+      <c r="E586" t="s">
         <v>1386</v>
       </c>
-      <c r="E586" t="s">
+      <c r="F586" t="s">
         <v>1387</v>
-      </c>
-      <c r="F586" t="s">
-        <v>1349</v>
       </c>
       <c r="G586" t="s">
         <v>34</v>
@@ -20461,13 +20461,13 @@
         <v>9</v>
       </c>
       <c r="D587" t="s">
-        <v>1390</v>
+        <v>1348</v>
       </c>
       <c r="E587" t="s">
         <v>1352</v>
       </c>
       <c r="F587" t="s">
-        <v>1349</v>
+        <v>1390</v>
       </c>
       <c r="G587" t="s">
         <v>16</v>
@@ -20484,13 +20484,13 @@
         <v>9</v>
       </c>
       <c r="D588" t="s">
-        <v>1393</v>
+        <v>1348</v>
       </c>
       <c r="E588" t="s">
         <v>1352</v>
       </c>
       <c r="F588" t="s">
-        <v>1349</v>
+        <v>1393</v>
       </c>
       <c r="G588" t="s">
         <v>1234</v>
@@ -20714,13 +20714,13 @@
         <v>9</v>
       </c>
       <c r="D598" t="s">
+        <v>1413</v>
+      </c>
+      <c r="E598" t="s">
         <v>1418</v>
       </c>
-      <c r="E598" t="s">
+      <c r="F598" t="s">
         <v>1419</v>
-      </c>
-      <c r="F598" t="s">
-        <v>1415</v>
       </c>
       <c r="G598" t="s">
         <v>20</v>
@@ -20806,13 +20806,13 @@
         <v>9</v>
       </c>
       <c r="D602" t="s">
+        <v>1413</v>
+      </c>
+      <c r="E602" t="s">
         <v>1428</v>
       </c>
-      <c r="E602" t="s">
+      <c r="F602" t="s">
         <v>1429</v>
-      </c>
-      <c r="F602" t="s">
-        <v>1415</v>
       </c>
       <c r="G602" t="s">
         <v>34</v>
@@ -20829,13 +20829,13 @@
         <v>9</v>
       </c>
       <c r="D603" t="s">
+        <v>1413</v>
+      </c>
+      <c r="E603" t="s">
         <v>1432</v>
       </c>
-      <c r="E603" t="s">
+      <c r="F603" t="s">
         <v>1433</v>
-      </c>
-      <c r="F603" t="s">
-        <v>1415</v>
       </c>
       <c r="G603" t="s">
         <v>34</v>
@@ -20852,13 +20852,13 @@
         <v>9</v>
       </c>
       <c r="D604" t="s">
+        <v>1413</v>
+      </c>
+      <c r="E604" t="s">
         <v>1436</v>
       </c>
-      <c r="E604" t="s">
+      <c r="F604" t="s">
         <v>1437</v>
-      </c>
-      <c r="F604" t="s">
-        <v>1415</v>
       </c>
       <c r="G604" t="s">
         <v>1234</v>
@@ -20875,13 +20875,13 @@
         <v>9</v>
       </c>
       <c r="D605" t="s">
-        <v>1440</v>
+        <v>1413</v>
       </c>
       <c r="E605" t="s">
         <v>1414</v>
       </c>
       <c r="F605" t="s">
-        <v>1415</v>
+        <v>1440</v>
       </c>
       <c r="G605" t="s">
         <v>34</v>
@@ -20944,13 +20944,13 @@
         <v>9</v>
       </c>
       <c r="D608" t="s">
+        <v>1413</v>
+      </c>
+      <c r="E608" t="s">
         <v>1447</v>
       </c>
-      <c r="E608" t="s">
+      <c r="F608" t="s">
         <v>1448</v>
-      </c>
-      <c r="F608" t="s">
-        <v>1415</v>
       </c>
       <c r="G608" t="s">
         <v>34</v>
@@ -20967,13 +20967,13 @@
         <v>9</v>
       </c>
       <c r="D609" t="s">
-        <v>1451</v>
+        <v>1413</v>
       </c>
       <c r="E609" t="s">
         <v>1390</v>
       </c>
       <c r="F609" t="s">
-        <v>1415</v>
+        <v>1451</v>
       </c>
       <c r="G609" t="s">
         <v>1234</v>
@@ -21013,13 +21013,13 @@
         <v>9</v>
       </c>
       <c r="D611" t="s">
-        <v>1418</v>
+        <v>1413</v>
       </c>
       <c r="E611" t="s">
         <v>1456</v>
       </c>
       <c r="F611" t="s">
-        <v>1415</v>
+        <v>1419</v>
       </c>
       <c r="G611" t="s">
         <v>34</v>
@@ -21036,13 +21036,13 @@
         <v>9</v>
       </c>
       <c r="D612" t="s">
-        <v>1459</v>
+        <v>1413</v>
       </c>
       <c r="E612" t="s">
         <v>1414</v>
       </c>
       <c r="F612" t="s">
-        <v>1415</v>
+        <v>1459</v>
       </c>
       <c r="G612" t="s">
         <v>20</v>
@@ -21082,13 +21082,13 @@
         <v>9</v>
       </c>
       <c r="D614" t="s">
-        <v>1464</v>
+        <v>1413</v>
       </c>
       <c r="E614" t="s">
         <v>1414</v>
       </c>
       <c r="F614" t="s">
-        <v>1415</v>
+        <v>1464</v>
       </c>
       <c r="G614" t="s">
         <v>1234</v>
@@ -21312,13 +21312,13 @@
         <v>9</v>
       </c>
       <c r="D624" t="s">
+        <v>1483</v>
+      </c>
+      <c r="E624" t="s">
         <v>1488</v>
       </c>
-      <c r="E624" t="s">
+      <c r="F624" t="s">
         <v>1489</v>
-      </c>
-      <c r="F624" t="s">
-        <v>1485</v>
       </c>
       <c r="G624" t="s">
         <v>34</v>
@@ -21427,13 +21427,13 @@
         <v>9</v>
       </c>
       <c r="D629" t="s">
-        <v>1501</v>
+        <v>1483</v>
       </c>
       <c r="E629" t="s">
         <v>1484</v>
       </c>
       <c r="F629" t="s">
-        <v>1485</v>
+        <v>1501</v>
       </c>
       <c r="G629" t="s">
         <v>34</v>
@@ -21496,13 +21496,13 @@
         <v>9</v>
       </c>
       <c r="D632" t="s">
-        <v>1501</v>
+        <v>1483</v>
       </c>
       <c r="E632" t="s">
         <v>1508</v>
       </c>
       <c r="F632" t="s">
-        <v>1485</v>
+        <v>1501</v>
       </c>
       <c r="G632" t="s">
         <v>34</v>
@@ -21519,13 +21519,13 @@
         <v>9</v>
       </c>
       <c r="D633" t="s">
+        <v>1483</v>
+      </c>
+      <c r="E633" t="s">
         <v>1511</v>
       </c>
-      <c r="E633" t="s">
+      <c r="F633" t="s">
         <v>1512</v>
-      </c>
-      <c r="F633" t="s">
-        <v>1485</v>
       </c>
       <c r="G633" t="s">
         <v>34</v>
@@ -21542,13 +21542,13 @@
         <v>9</v>
       </c>
       <c r="D634" t="s">
+        <v>1483</v>
+      </c>
+      <c r="E634" t="s">
         <v>1515</v>
       </c>
-      <c r="E634" t="s">
+      <c r="F634" t="s">
         <v>1516</v>
-      </c>
-      <c r="F634" t="s">
-        <v>1485</v>
       </c>
       <c r="G634" t="s">
         <v>34</v>
@@ -21588,13 +21588,13 @@
         <v>9</v>
       </c>
       <c r="D636" t="s">
-        <v>1521</v>
+        <v>1483</v>
       </c>
       <c r="E636" t="s">
         <v>1484</v>
       </c>
       <c r="F636" t="s">
-        <v>1485</v>
+        <v>1521</v>
       </c>
       <c r="G636" t="s">
         <v>1234</v>
@@ -21611,13 +21611,13 @@
         <v>9</v>
       </c>
       <c r="D637" t="s">
+        <v>1483</v>
+      </c>
+      <c r="E637" t="s">
         <v>1524</v>
       </c>
-      <c r="E637" t="s">
+      <c r="F637" t="s">
         <v>1525</v>
-      </c>
-      <c r="F637" t="s">
-        <v>1485</v>
       </c>
       <c r="G637" t="s">
         <v>34</v>
@@ -21703,13 +21703,13 @@
         <v>9</v>
       </c>
       <c r="D641" t="s">
+        <v>1483</v>
+      </c>
+      <c r="E641" t="s">
         <v>1534</v>
       </c>
-      <c r="E641" t="s">
+      <c r="F641" t="s">
         <v>1535</v>
-      </c>
-      <c r="F641" t="s">
-        <v>1485</v>
       </c>
       <c r="G641" t="s">
         <v>20</v>
@@ -21726,13 +21726,13 @@
         <v>9</v>
       </c>
       <c r="D642" t="s">
-        <v>1538</v>
+        <v>1483</v>
       </c>
       <c r="E642" t="s">
         <v>1484</v>
       </c>
       <c r="F642" t="s">
-        <v>1485</v>
+        <v>1538</v>
       </c>
       <c r="G642" t="s">
         <v>20</v>
@@ -21749,13 +21749,13 @@
         <v>9</v>
       </c>
       <c r="D643" t="s">
-        <v>1541</v>
+        <v>1483</v>
       </c>
       <c r="E643" t="s">
         <v>1484</v>
       </c>
       <c r="F643" t="s">
-        <v>1485</v>
+        <v>1541</v>
       </c>
       <c r="G643" t="s">
         <v>20</v>
@@ -21818,13 +21818,13 @@
         <v>9</v>
       </c>
       <c r="D646" t="s">
-        <v>1548</v>
+        <v>1483</v>
       </c>
       <c r="E646" t="s">
         <v>1484</v>
       </c>
       <c r="F646" t="s">
-        <v>1485</v>
+        <v>1548</v>
       </c>
       <c r="G646" t="s">
         <v>34</v>
@@ -21910,13 +21910,13 @@
         <v>9</v>
       </c>
       <c r="D650" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E650" t="s">
         <v>1560</v>
       </c>
-      <c r="E650" t="s">
+      <c r="F650" t="s">
         <v>1561</v>
-      </c>
-      <c r="F650" t="s">
-        <v>1557</v>
       </c>
       <c r="G650" t="s">
         <v>20</v>
@@ -21956,13 +21956,13 @@
         <v>9</v>
       </c>
       <c r="D652" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E652" t="s">
         <v>1567</v>
       </c>
-      <c r="E652" t="s">
+      <c r="F652" t="s">
         <v>1568</v>
-      </c>
-      <c r="F652" t="s">
-        <v>1557</v>
       </c>
       <c r="G652" t="s">
         <v>1234</v>
@@ -21979,13 +21979,13 @@
         <v>9</v>
       </c>
       <c r="D653" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E653" t="s">
         <v>1567</v>
       </c>
-      <c r="E653" t="s">
+      <c r="F653" t="s">
         <v>1568</v>
-      </c>
-      <c r="F653" t="s">
-        <v>1557</v>
       </c>
       <c r="G653" t="s">
         <v>1234</v>
@@ -22002,13 +22002,13 @@
         <v>9</v>
       </c>
       <c r="D654" t="s">
-        <v>1541</v>
+        <v>1555</v>
       </c>
       <c r="E654" t="s">
         <v>1484</v>
       </c>
       <c r="F654" t="s">
-        <v>1557</v>
+        <v>1541</v>
       </c>
       <c r="G654" t="s">
         <v>20</v>
@@ -22025,13 +22025,13 @@
         <v>9</v>
       </c>
       <c r="D655" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E655" t="s">
         <v>1567</v>
       </c>
-      <c r="E655" t="s">
+      <c r="F655" t="s">
         <v>1568</v>
-      </c>
-      <c r="F655" t="s">
-        <v>1557</v>
       </c>
       <c r="G655" t="s">
         <v>1234</v>
@@ -22048,13 +22048,13 @@
         <v>9</v>
       </c>
       <c r="D656" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E656" t="s">
         <v>1567</v>
       </c>
-      <c r="E656" t="s">
+      <c r="F656" t="s">
         <v>1568</v>
-      </c>
-      <c r="F656" t="s">
-        <v>1557</v>
       </c>
       <c r="G656" t="s">
         <v>1234</v>
@@ -22071,13 +22071,13 @@
         <v>9</v>
       </c>
       <c r="D657" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E657" t="s">
         <v>1579</v>
       </c>
-      <c r="E657" t="s">
+      <c r="F657" t="s">
         <v>1580</v>
-      </c>
-      <c r="F657" t="s">
-        <v>1557</v>
       </c>
       <c r="G657" t="s">
         <v>20</v>
@@ -22094,13 +22094,13 @@
         <v>9</v>
       </c>
       <c r="D658" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E658" t="s">
         <v>1583</v>
       </c>
-      <c r="E658" t="s">
+      <c r="F658" t="s">
         <v>1584</v>
-      </c>
-      <c r="F658" t="s">
-        <v>1557</v>
       </c>
       <c r="G658" t="s">
         <v>34</v>
@@ -22117,13 +22117,13 @@
         <v>9</v>
       </c>
       <c r="D659" t="s">
-        <v>1521</v>
+        <v>1555</v>
       </c>
       <c r="E659" t="s">
         <v>1587</v>
       </c>
       <c r="F659" t="s">
-        <v>1557</v>
+        <v>1521</v>
       </c>
       <c r="G659" t="s">
         <v>34</v>
@@ -22140,13 +22140,13 @@
         <v>9</v>
       </c>
       <c r="D660" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E660" t="s">
         <v>1590</v>
       </c>
-      <c r="E660" t="s">
+      <c r="F660" t="s">
         <v>1591</v>
-      </c>
-      <c r="F660" t="s">
-        <v>1557</v>
       </c>
       <c r="G660" t="s">
         <v>34</v>
@@ -22163,13 +22163,13 @@
         <v>9</v>
       </c>
       <c r="D661" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E661" t="s">
         <v>1567</v>
       </c>
-      <c r="E661" t="s">
+      <c r="F661" t="s">
         <v>1568</v>
-      </c>
-      <c r="F661" t="s">
-        <v>1557</v>
       </c>
       <c r="G661" t="s">
         <v>1234</v>
@@ -22186,13 +22186,13 @@
         <v>9</v>
       </c>
       <c r="D662" t="s">
-        <v>1567</v>
+        <v>1555</v>
       </c>
       <c r="E662" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="F662" t="s">
-        <v>1557</v>
+        <v>1568</v>
       </c>
       <c r="G662" t="s">
         <v>34</v>
@@ -22209,13 +22209,13 @@
         <v>9</v>
       </c>
       <c r="D663" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E663" t="s">
         <v>1598</v>
       </c>
-      <c r="E663" t="s">
+      <c r="F663" t="s">
         <v>1599</v>
-      </c>
-      <c r="F663" t="s">
-        <v>1557</v>
       </c>
       <c r="G663" t="s">
         <v>34</v>
@@ -22232,13 +22232,13 @@
         <v>9</v>
       </c>
       <c r="D664" t="s">
-        <v>1541</v>
+        <v>1555</v>
       </c>
       <c r="E664" t="s">
         <v>1602</v>
       </c>
       <c r="F664" t="s">
-        <v>1557</v>
+        <v>1541</v>
       </c>
       <c r="G664" t="s">
         <v>20</v>
@@ -22255,13 +22255,13 @@
         <v>9</v>
       </c>
       <c r="D665" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E665" t="s">
+        <v>1567</v>
+      </c>
+      <c r="F665" t="s">
         <v>1605</v>
-      </c>
-      <c r="E665" t="s">
-        <v>1568</v>
-      </c>
-      <c r="F665" t="s">
-        <v>1557</v>
       </c>
       <c r="G665" t="s">
         <v>1234</v>
@@ -22278,13 +22278,13 @@
         <v>9</v>
       </c>
       <c r="D666" t="s">
-        <v>1605</v>
+        <v>1555</v>
       </c>
       <c r="E666" t="s">
         <v>1556</v>
       </c>
       <c r="F666" t="s">
-        <v>1557</v>
+        <v>1605</v>
       </c>
       <c r="G666" t="s">
         <v>34</v>
@@ -22301,13 +22301,13 @@
         <v>9</v>
       </c>
       <c r="D667" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E667" t="s">
         <v>1610</v>
       </c>
-      <c r="E667" t="s">
+      <c r="F667" t="s">
         <v>1611</v>
-      </c>
-      <c r="F667" t="s">
-        <v>1557</v>
       </c>
       <c r="G667" t="s">
         <v>34</v>
@@ -22324,13 +22324,13 @@
         <v>9</v>
       </c>
       <c r="D668" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E668" t="s">
         <v>1567</v>
       </c>
-      <c r="E668" t="s">
+      <c r="F668" t="s">
         <v>1568</v>
-      </c>
-      <c r="F668" t="s">
-        <v>1557</v>
       </c>
       <c r="G668" t="s">
         <v>20</v>
@@ -22347,13 +22347,13 @@
         <v>9</v>
       </c>
       <c r="D669" t="s">
-        <v>1541</v>
+        <v>1555</v>
       </c>
       <c r="E669" t="s">
         <v>1587</v>
       </c>
       <c r="F669" t="s">
-        <v>1557</v>
+        <v>1541</v>
       </c>
       <c r="G669" t="s">
         <v>20</v>
@@ -22370,13 +22370,13 @@
         <v>9</v>
       </c>
       <c r="D670" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E670" t="s">
         <v>1567</v>
       </c>
-      <c r="E670" t="s">
+      <c r="F670" t="s">
         <v>1568</v>
-      </c>
-      <c r="F670" t="s">
-        <v>1557</v>
       </c>
       <c r="G670" t="s">
         <v>1234</v>
@@ -22416,13 +22416,13 @@
         <v>9</v>
       </c>
       <c r="D672" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E672" t="s">
         <v>1567</v>
       </c>
-      <c r="E672" t="s">
+      <c r="F672" t="s">
         <v>1568</v>
-      </c>
-      <c r="F672" t="s">
-        <v>1557</v>
       </c>
       <c r="G672" t="s">
         <v>20</v>
@@ -22439,13 +22439,13 @@
         <v>9</v>
       </c>
       <c r="D673" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E673" t="s">
         <v>1567</v>
       </c>
-      <c r="E673" t="s">
+      <c r="F673" t="s">
         <v>1568</v>
-      </c>
-      <c r="F673" t="s">
-        <v>1557</v>
       </c>
       <c r="G673" t="s">
         <v>1234</v>
@@ -22462,13 +22462,13 @@
         <v>9</v>
       </c>
       <c r="D674" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E674" t="s">
+        <v>1590</v>
+      </c>
+      <c r="F674" t="s">
         <v>1541</v>
-      </c>
-      <c r="E674" t="s">
-        <v>1591</v>
-      </c>
-      <c r="F674" t="s">
-        <v>1557</v>
       </c>
       <c r="G674" t="s">
         <v>20</v>
@@ -22508,13 +22508,13 @@
         <v>9</v>
       </c>
       <c r="D676" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E676" t="s">
+        <v>1567</v>
+      </c>
+      <c r="F676" t="s">
         <v>1631</v>
-      </c>
-      <c r="E676" t="s">
-        <v>1568</v>
-      </c>
-      <c r="F676" t="s">
-        <v>1557</v>
       </c>
       <c r="G676" t="s">
         <v>20</v>
@@ -22531,13 +22531,13 @@
         <v>9</v>
       </c>
       <c r="D677" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E677" t="s">
         <v>1567</v>
       </c>
-      <c r="E677" t="s">
+      <c r="F677" t="s">
         <v>1568</v>
-      </c>
-      <c r="F677" t="s">
-        <v>1557</v>
       </c>
       <c r="G677" t="s">
         <v>1234</v>
@@ -22554,13 +22554,13 @@
         <v>9</v>
       </c>
       <c r="D678" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E678" t="s">
         <v>1567</v>
       </c>
-      <c r="E678" t="s">
+      <c r="F678" t="s">
         <v>1568</v>
-      </c>
-      <c r="F678" t="s">
-        <v>1557</v>
       </c>
       <c r="G678" t="s">
         <v>1234</v>
@@ -22577,13 +22577,13 @@
         <v>9</v>
       </c>
       <c r="D679" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E679" t="s">
         <v>1590</v>
       </c>
-      <c r="E679" t="s">
+      <c r="F679" t="s">
         <v>1591</v>
-      </c>
-      <c r="F679" t="s">
-        <v>1557</v>
       </c>
       <c r="G679" t="s">
         <v>34</v>
@@ -22600,13 +22600,13 @@
         <v>9</v>
       </c>
       <c r="D680" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E680" t="s">
         <v>1567</v>
       </c>
-      <c r="E680" t="s">
+      <c r="F680" t="s">
         <v>1568</v>
-      </c>
-      <c r="F680" t="s">
-        <v>1557</v>
       </c>
       <c r="G680" t="s">
         <v>1234</v>
@@ -22623,13 +22623,13 @@
         <v>9</v>
       </c>
       <c r="D681" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E681" t="s">
         <v>1567</v>
       </c>
-      <c r="E681" t="s">
+      <c r="F681" t="s">
         <v>1568</v>
-      </c>
-      <c r="F681" t="s">
-        <v>1557</v>
       </c>
       <c r="G681" t="s">
         <v>1234</v>
@@ -22669,13 +22669,13 @@
         <v>9</v>
       </c>
       <c r="D683" t="s">
+        <v>1644</v>
+      </c>
+      <c r="E683" t="s">
         <v>1649</v>
       </c>
-      <c r="E683" t="s">
+      <c r="F683" t="s">
         <v>1650</v>
-      </c>
-      <c r="F683" t="s">
-        <v>1646</v>
       </c>
       <c r="G683" t="s">
         <v>34</v>
@@ -22692,13 +22692,13 @@
         <v>9</v>
       </c>
       <c r="D684" t="s">
+        <v>1644</v>
+      </c>
+      <c r="E684" t="s">
         <v>1653</v>
       </c>
-      <c r="E684" t="s">
+      <c r="F684" t="s">
         <v>1654</v>
-      </c>
-      <c r="F684" t="s">
-        <v>1646</v>
       </c>
       <c r="G684" t="s">
         <v>1234</v>
@@ -22715,13 +22715,13 @@
         <v>9</v>
       </c>
       <c r="D685" t="s">
+        <v>1644</v>
+      </c>
+      <c r="E685" t="s">
         <v>1653</v>
       </c>
-      <c r="E685" t="s">
+      <c r="F685" t="s">
         <v>1654</v>
-      </c>
-      <c r="F685" t="s">
-        <v>1646</v>
       </c>
       <c r="G685" t="s">
         <v>1234</v>
@@ -22738,13 +22738,13 @@
         <v>9</v>
       </c>
       <c r="D686" t="s">
+        <v>1644</v>
+      </c>
+      <c r="E686" t="s">
         <v>1653</v>
       </c>
-      <c r="E686" t="s">
+      <c r="F686" t="s">
         <v>1654</v>
-      </c>
-      <c r="F686" t="s">
-        <v>1646</v>
       </c>
       <c r="G686" t="s">
         <v>1234</v>
@@ -22761,13 +22761,13 @@
         <v>9</v>
       </c>
       <c r="D687" t="s">
+        <v>1644</v>
+      </c>
+      <c r="E687" t="s">
         <v>1653</v>
       </c>
-      <c r="E687" t="s">
+      <c r="F687" t="s">
         <v>1654</v>
-      </c>
-      <c r="F687" t="s">
-        <v>1646</v>
       </c>
       <c r="G687" t="s">
         <v>1234</v>
@@ -22784,13 +22784,13 @@
         <v>9</v>
       </c>
       <c r="D688" t="s">
+        <v>1644</v>
+      </c>
+      <c r="E688" t="s">
         <v>1653</v>
       </c>
-      <c r="E688" t="s">
+      <c r="F688" t="s">
         <v>1654</v>
-      </c>
-      <c r="F688" t="s">
-        <v>1646</v>
       </c>
       <c r="G688" t="s">
         <v>1234</v>
@@ -22807,13 +22807,13 @@
         <v>9</v>
       </c>
       <c r="D689" t="s">
-        <v>1649</v>
+        <v>1644</v>
       </c>
       <c r="E689" t="s">
         <v>1665</v>
       </c>
       <c r="F689" t="s">
-        <v>1646</v>
+        <v>1650</v>
       </c>
       <c r="G689" t="s">
         <v>34</v>
@@ -22830,13 +22830,13 @@
         <v>9</v>
       </c>
       <c r="D690" t="s">
+        <v>1644</v>
+      </c>
+      <c r="E690" t="s">
         <v>1668</v>
       </c>
-      <c r="E690" t="s">
+      <c r="F690" t="s">
         <v>1669</v>
-      </c>
-      <c r="F690" t="s">
-        <v>1646</v>
       </c>
       <c r="G690" t="s">
         <v>34</v>
@@ -22853,13 +22853,13 @@
         <v>9</v>
       </c>
       <c r="D691" t="s">
+        <v>1644</v>
+      </c>
+      <c r="E691" t="s">
         <v>1653</v>
       </c>
-      <c r="E691" t="s">
+      <c r="F691" t="s">
         <v>1654</v>
-      </c>
-      <c r="F691" t="s">
-        <v>1646</v>
       </c>
       <c r="G691" t="s">
         <v>16</v>
@@ -22876,13 +22876,13 @@
         <v>9</v>
       </c>
       <c r="D692" t="s">
+        <v>1644</v>
+      </c>
+      <c r="E692" t="s">
+        <v>1567</v>
+      </c>
+      <c r="F692" t="s">
         <v>1674</v>
-      </c>
-      <c r="E692" t="s">
-        <v>1568</v>
-      </c>
-      <c r="F692" t="s">
-        <v>1646</v>
       </c>
       <c r="G692" t="s">
         <v>20</v>
@@ -22899,13 +22899,13 @@
         <v>9</v>
       </c>
       <c r="D693" t="s">
+        <v>1644</v>
+      </c>
+      <c r="E693" t="s">
         <v>1677</v>
       </c>
-      <c r="E693" t="s">
+      <c r="F693" t="s">
         <v>1678</v>
-      </c>
-      <c r="F693" t="s">
-        <v>1646</v>
       </c>
       <c r="G693" t="s">
         <v>34</v>
@@ -22922,13 +22922,13 @@
         <v>9</v>
       </c>
       <c r="D694" t="s">
+        <v>1644</v>
+      </c>
+      <c r="E694" t="s">
         <v>1681</v>
       </c>
-      <c r="E694" t="s">
+      <c r="F694" t="s">
         <v>1682</v>
-      </c>
-      <c r="F694" t="s">
-        <v>1646</v>
       </c>
       <c r="G694" t="s">
         <v>20</v>
@@ -22945,13 +22945,13 @@
         <v>9</v>
       </c>
       <c r="D695" t="s">
+        <v>1644</v>
+      </c>
+      <c r="E695" t="s">
         <v>1685</v>
       </c>
-      <c r="E695" t="s">
+      <c r="F695" t="s">
         <v>1686</v>
-      </c>
-      <c r="F695" t="s">
-        <v>1646</v>
       </c>
       <c r="G695" t="s">
         <v>34</v>
@@ -22968,13 +22968,13 @@
         <v>9</v>
       </c>
       <c r="D696" t="s">
+        <v>1644</v>
+      </c>
+      <c r="E696" t="s">
         <v>1653</v>
       </c>
-      <c r="E696" t="s">
+      <c r="F696" t="s">
         <v>1654</v>
-      </c>
-      <c r="F696" t="s">
-        <v>1646</v>
       </c>
       <c r="G696" t="s">
         <v>1234</v>
@@ -22991,13 +22991,13 @@
         <v>9</v>
       </c>
       <c r="D697" t="s">
+        <v>1644</v>
+      </c>
+      <c r="E697" t="s">
         <v>1691</v>
       </c>
-      <c r="E697" t="s">
+      <c r="F697" t="s">
         <v>1692</v>
-      </c>
-      <c r="F697" t="s">
-        <v>1646</v>
       </c>
       <c r="G697" t="s">
         <v>34</v>
@@ -23014,13 +23014,13 @@
         <v>9</v>
       </c>
       <c r="D698" t="s">
+        <v>1644</v>
+      </c>
+      <c r="E698" t="s">
         <v>1695</v>
       </c>
-      <c r="E698" t="s">
+      <c r="F698" t="s">
         <v>1696</v>
-      </c>
-      <c r="F698" t="s">
-        <v>1646</v>
       </c>
       <c r="G698" t="s">
         <v>34</v>
@@ -23037,13 +23037,13 @@
         <v>9</v>
       </c>
       <c r="D699" t="s">
+        <v>1644</v>
+      </c>
+      <c r="E699" t="s">
         <v>1653</v>
       </c>
-      <c r="E699" t="s">
+      <c r="F699" t="s">
         <v>1654</v>
-      </c>
-      <c r="F699" t="s">
-        <v>1646</v>
       </c>
       <c r="G699" t="s">
         <v>20</v>
@@ -23060,13 +23060,13 @@
         <v>9</v>
       </c>
       <c r="D700" t="s">
+        <v>1644</v>
+      </c>
+      <c r="E700" t="s">
         <v>1701</v>
       </c>
-      <c r="E700" t="s">
+      <c r="F700" t="s">
         <v>1702</v>
-      </c>
-      <c r="F700" t="s">
-        <v>1646</v>
       </c>
       <c r="G700" t="s">
         <v>34</v>
@@ -23083,13 +23083,13 @@
         <v>9</v>
       </c>
       <c r="D701" t="s">
+        <v>1644</v>
+      </c>
+      <c r="E701" t="s">
         <v>1653</v>
       </c>
-      <c r="E701" t="s">
+      <c r="F701" t="s">
         <v>1654</v>
-      </c>
-      <c r="F701" t="s">
-        <v>1646</v>
       </c>
       <c r="G701" t="s">
         <v>20</v>
@@ -23106,13 +23106,13 @@
         <v>9</v>
       </c>
       <c r="D702" t="s">
+        <v>1644</v>
+      </c>
+      <c r="E702" t="s">
         <v>1707</v>
       </c>
-      <c r="E702" t="s">
+      <c r="F702" t="s">
         <v>1708</v>
-      </c>
-      <c r="F702" t="s">
-        <v>1646</v>
       </c>
       <c r="G702" t="s">
         <v>34</v>
@@ -23129,13 +23129,13 @@
         <v>9</v>
       </c>
       <c r="D703" t="s">
+        <v>1644</v>
+      </c>
+      <c r="E703" t="s">
+        <v>1701</v>
+      </c>
+      <c r="F703" t="s">
         <v>1711</v>
-      </c>
-      <c r="E703" t="s">
-        <v>1702</v>
-      </c>
-      <c r="F703" t="s">
-        <v>1646</v>
       </c>
       <c r="G703" t="s">
         <v>34</v>
@@ -23152,13 +23152,13 @@
         <v>9</v>
       </c>
       <c r="D704" t="s">
+        <v>1644</v>
+      </c>
+      <c r="E704" t="s">
         <v>1653</v>
       </c>
-      <c r="E704" t="s">
+      <c r="F704" t="s">
         <v>1654</v>
-      </c>
-      <c r="F704" t="s">
-        <v>1646</v>
       </c>
       <c r="G704" t="s">
         <v>1234</v>
@@ -23175,13 +23175,13 @@
         <v>9</v>
       </c>
       <c r="D705" t="s">
+        <v>1644</v>
+      </c>
+      <c r="E705" t="s">
+        <v>1695</v>
+      </c>
+      <c r="F705" t="s">
         <v>1716</v>
-      </c>
-      <c r="E705" t="s">
-        <v>1696</v>
-      </c>
-      <c r="F705" t="s">
-        <v>1646</v>
       </c>
       <c r="G705" t="s">
         <v>20</v>
@@ -23198,13 +23198,13 @@
         <v>9</v>
       </c>
       <c r="D706" t="s">
+        <v>1644</v>
+      </c>
+      <c r="E706" t="s">
         <v>1653</v>
       </c>
-      <c r="E706" t="s">
+      <c r="F706" t="s">
         <v>1654</v>
-      </c>
-      <c r="F706" t="s">
-        <v>1646</v>
       </c>
       <c r="G706" t="s">
         <v>1234</v>
@@ -23221,13 +23221,13 @@
         <v>9</v>
       </c>
       <c r="D707" t="s">
-        <v>1653</v>
+        <v>1644</v>
       </c>
       <c r="E707" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
       <c r="F707" t="s">
-        <v>1646</v>
+        <v>1654</v>
       </c>
       <c r="G707" t="s">
         <v>20</v>
@@ -23244,13 +23244,13 @@
         <v>9</v>
       </c>
       <c r="D708" t="s">
+        <v>1644</v>
+      </c>
+      <c r="E708" t="s">
+        <v>1649</v>
+      </c>
+      <c r="F708" t="s">
         <v>1723</v>
-      </c>
-      <c r="E708" t="s">
-        <v>1650</v>
-      </c>
-      <c r="F708" t="s">
-        <v>1646</v>
       </c>
       <c r="G708" t="s">
         <v>34</v>
@@ -23267,13 +23267,13 @@
         <v>9</v>
       </c>
       <c r="D709" t="s">
+        <v>1644</v>
+      </c>
+      <c r="E709" t="s">
         <v>1653</v>
       </c>
-      <c r="E709" t="s">
+      <c r="F709" t="s">
         <v>1654</v>
-      </c>
-      <c r="F709" t="s">
-        <v>1646</v>
       </c>
       <c r="G709" t="s">
         <v>1234</v>
@@ -23290,13 +23290,13 @@
         <v>9</v>
       </c>
       <c r="D710" t="s">
+        <v>1644</v>
+      </c>
+      <c r="E710" t="s">
         <v>1728</v>
       </c>
-      <c r="E710" t="s">
+      <c r="F710" t="s">
         <v>1729</v>
-      </c>
-      <c r="F710" t="s">
-        <v>1646</v>
       </c>
       <c r="G710" t="s">
         <v>34</v>
@@ -23313,13 +23313,13 @@
         <v>9</v>
       </c>
       <c r="D711" t="s">
-        <v>1653</v>
+        <v>1644</v>
       </c>
       <c r="E711" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
       <c r="F711" t="s">
-        <v>1646</v>
+        <v>1654</v>
       </c>
       <c r="G711" t="s">
         <v>1234</v>
@@ -23336,13 +23336,13 @@
         <v>9</v>
       </c>
       <c r="D712" t="s">
+        <v>1644</v>
+      </c>
+      <c r="E712" t="s">
         <v>1653</v>
       </c>
-      <c r="E712" t="s">
+      <c r="F712" t="s">
         <v>1654</v>
-      </c>
-      <c r="F712" t="s">
-        <v>1646</v>
       </c>
       <c r="G712" t="s">
         <v>1234</v>
@@ -23359,13 +23359,13 @@
         <v>9</v>
       </c>
       <c r="D713" t="s">
+        <v>1644</v>
+      </c>
+      <c r="E713" t="s">
         <v>1668</v>
       </c>
-      <c r="E713" t="s">
+      <c r="F713" t="s">
         <v>1669</v>
-      </c>
-      <c r="F713" t="s">
-        <v>1646</v>
       </c>
       <c r="G713" t="s">
         <v>34</v>
@@ -23382,13 +23382,13 @@
         <v>9</v>
       </c>
       <c r="D714" t="s">
+        <v>1644</v>
+      </c>
+      <c r="E714" t="s">
         <v>1653</v>
       </c>
-      <c r="E714" t="s">
+      <c r="F714" t="s">
         <v>1654</v>
-      </c>
-      <c r="F714" t="s">
-        <v>1646</v>
       </c>
       <c r="G714" t="s">
         <v>1234</v>
@@ -23405,13 +23405,13 @@
         <v>9</v>
       </c>
       <c r="D715" t="s">
-        <v>1691</v>
+        <v>1644</v>
       </c>
       <c r="E715" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
       <c r="F715" t="s">
-        <v>1646</v>
+        <v>1692</v>
       </c>
       <c r="G715" t="s">
         <v>34</v>
@@ -23428,13 +23428,13 @@
         <v>9</v>
       </c>
       <c r="D716" t="s">
+        <v>1644</v>
+      </c>
+      <c r="E716" t="s">
         <v>1653</v>
       </c>
-      <c r="E716" t="s">
+      <c r="F716" t="s">
         <v>1654</v>
-      </c>
-      <c r="F716" t="s">
-        <v>1646</v>
       </c>
       <c r="G716" t="s">
         <v>1234</v>
@@ -23451,13 +23451,13 @@
         <v>9</v>
       </c>
       <c r="D717" t="s">
+        <v>1644</v>
+      </c>
+      <c r="E717" t="s">
         <v>1653</v>
       </c>
-      <c r="E717" t="s">
+      <c r="F717" t="s">
         <v>1654</v>
-      </c>
-      <c r="F717" t="s">
-        <v>1646</v>
       </c>
       <c r="G717" t="s">
         <v>1234</v>
@@ -23497,13 +23497,13 @@
         <v>9</v>
       </c>
       <c r="D719" t="s">
-        <v>1751</v>
+        <v>1746</v>
       </c>
       <c r="E719" t="s">
         <v>1747</v>
       </c>
       <c r="F719" t="s">
-        <v>1748</v>
+        <v>1751</v>
       </c>
       <c r="G719" t="s">
         <v>1234</v>
@@ -23520,13 +23520,13 @@
         <v>9</v>
       </c>
       <c r="D720" t="s">
-        <v>1751</v>
+        <v>1746</v>
       </c>
       <c r="E720" t="s">
         <v>1747</v>
       </c>
       <c r="F720" t="s">
-        <v>1748</v>
+        <v>1751</v>
       </c>
       <c r="G720" t="s">
         <v>1234</v>
@@ -23543,13 +23543,13 @@
         <v>9</v>
       </c>
       <c r="D721" t="s">
-        <v>1751</v>
+        <v>1746</v>
       </c>
       <c r="E721" t="s">
         <v>1747</v>
       </c>
       <c r="F721" t="s">
-        <v>1748</v>
+        <v>1751</v>
       </c>
       <c r="G721" t="s">
         <v>1234</v>
@@ -23566,13 +23566,13 @@
         <v>9</v>
       </c>
       <c r="D722" t="s">
-        <v>1751</v>
+        <v>1746</v>
       </c>
       <c r="E722" t="s">
         <v>1747</v>
       </c>
       <c r="F722" t="s">
-        <v>1748</v>
+        <v>1751</v>
       </c>
       <c r="G722" t="s">
         <v>1234</v>
@@ -23589,13 +23589,13 @@
         <v>9</v>
       </c>
       <c r="D723" t="s">
-        <v>1751</v>
+        <v>1746</v>
       </c>
       <c r="E723" t="s">
         <v>1747</v>
       </c>
       <c r="F723" t="s">
-        <v>1748</v>
+        <v>1751</v>
       </c>
       <c r="G723" t="s">
         <v>1234</v>
@@ -23612,13 +23612,13 @@
         <v>9</v>
       </c>
       <c r="D724" t="s">
-        <v>1751</v>
+        <v>1746</v>
       </c>
       <c r="E724" t="s">
         <v>1747</v>
       </c>
       <c r="F724" t="s">
-        <v>1748</v>
+        <v>1751</v>
       </c>
       <c r="G724" t="s">
         <v>20</v>
@@ -23635,13 +23635,13 @@
         <v>9</v>
       </c>
       <c r="D725" t="s">
+        <v>1746</v>
+      </c>
+      <c r="E725" t="s">
         <v>1764</v>
       </c>
-      <c r="E725" t="s">
+      <c r="F725" t="s">
         <v>1765</v>
-      </c>
-      <c r="F725" t="s">
-        <v>1748</v>
       </c>
       <c r="G725" t="s">
         <v>20</v>
@@ -23658,13 +23658,13 @@
         <v>9</v>
       </c>
       <c r="D726" t="s">
+        <v>1746</v>
+      </c>
+      <c r="E726" t="s">
         <v>1768</v>
       </c>
-      <c r="E726" t="s">
+      <c r="F726" t="s">
         <v>1769</v>
-      </c>
-      <c r="F726" t="s">
-        <v>1748</v>
       </c>
       <c r="G726" t="s">
         <v>20</v>
@@ -23681,13 +23681,13 @@
         <v>9</v>
       </c>
       <c r="D727" t="s">
-        <v>1751</v>
+        <v>1746</v>
       </c>
       <c r="E727" t="s">
         <v>1747</v>
       </c>
       <c r="F727" t="s">
-        <v>1748</v>
+        <v>1751</v>
       </c>
       <c r="G727" t="s">
         <v>1234</v>
@@ -23704,13 +23704,13 @@
         <v>9</v>
       </c>
       <c r="D728" t="s">
-        <v>1751</v>
+        <v>1746</v>
       </c>
       <c r="E728" t="s">
         <v>1747</v>
       </c>
       <c r="F728" t="s">
-        <v>1748</v>
+        <v>1751</v>
       </c>
       <c r="G728" t="s">
         <v>1234</v>
@@ -23727,13 +23727,13 @@
         <v>9</v>
       </c>
       <c r="D729" t="s">
+        <v>1746</v>
+      </c>
+      <c r="E729" t="s">
         <v>1776</v>
       </c>
-      <c r="E729" t="s">
+      <c r="F729" t="s">
         <v>1777</v>
-      </c>
-      <c r="F729" t="s">
-        <v>1748</v>
       </c>
       <c r="G729" t="s">
         <v>34</v>
@@ -23750,13 +23750,13 @@
         <v>9</v>
       </c>
       <c r="D730" t="s">
-        <v>1751</v>
+        <v>1746</v>
       </c>
       <c r="E730" t="s">
         <v>1747</v>
       </c>
       <c r="F730" t="s">
-        <v>1748</v>
+        <v>1751</v>
       </c>
       <c r="G730" t="s">
         <v>16</v>
@@ -23773,13 +23773,13 @@
         <v>9</v>
       </c>
       <c r="D731" t="s">
+        <v>1746</v>
+      </c>
+      <c r="E731" t="s">
         <v>1776</v>
       </c>
-      <c r="E731" t="s">
+      <c r="F731" t="s">
         <v>1777</v>
-      </c>
-      <c r="F731" t="s">
-        <v>1748</v>
       </c>
       <c r="G731" t="s">
         <v>34</v>
@@ -23796,13 +23796,13 @@
         <v>9</v>
       </c>
       <c r="D732" t="s">
+        <v>1746</v>
+      </c>
+      <c r="E732" t="s">
         <v>1784</v>
       </c>
-      <c r="E732" t="s">
+      <c r="F732" t="s">
         <v>1785</v>
-      </c>
-      <c r="F732" t="s">
-        <v>1748</v>
       </c>
       <c r="G732" t="s">
         <v>34</v>
@@ -23819,13 +23819,13 @@
         <v>9</v>
       </c>
       <c r="D733" t="s">
-        <v>1788</v>
+        <v>1746</v>
       </c>
       <c r="E733" t="s">
         <v>1747</v>
       </c>
       <c r="F733" t="s">
-        <v>1748</v>
+        <v>1788</v>
       </c>
       <c r="G733" t="s">
         <v>34</v>
@@ -23842,13 +23842,13 @@
         <v>9</v>
       </c>
       <c r="D734" t="s">
+        <v>1746</v>
+      </c>
+      <c r="E734" t="s">
         <v>1791</v>
       </c>
-      <c r="E734" t="s">
+      <c r="F734" t="s">
         <v>1792</v>
-      </c>
-      <c r="F734" t="s">
-        <v>1748</v>
       </c>
       <c r="G734" t="s">
         <v>34</v>
@@ -23865,13 +23865,13 @@
         <v>9</v>
       </c>
       <c r="D735" t="s">
-        <v>1751</v>
+        <v>1746</v>
       </c>
       <c r="E735" t="s">
         <v>1747</v>
       </c>
       <c r="F735" t="s">
-        <v>1748</v>
+        <v>1751</v>
       </c>
       <c r="G735" t="s">
         <v>1234</v>
@@ -23888,13 +23888,13 @@
         <v>9</v>
       </c>
       <c r="D736" t="s">
-        <v>1797</v>
+        <v>1746</v>
       </c>
       <c r="E736" t="s">
         <v>1747</v>
       </c>
       <c r="F736" t="s">
-        <v>1748</v>
+        <v>1797</v>
       </c>
       <c r="G736" t="s">
         <v>1234</v>
@@ -23911,13 +23911,13 @@
         <v>9</v>
       </c>
       <c r="D737" t="s">
-        <v>1751</v>
+        <v>1746</v>
       </c>
       <c r="E737" t="s">
         <v>1747</v>
       </c>
       <c r="F737" t="s">
-        <v>1748</v>
+        <v>1751</v>
       </c>
       <c r="G737" t="s">
         <v>20</v>
@@ -23934,13 +23934,13 @@
         <v>9</v>
       </c>
       <c r="D738" t="s">
+        <v>1746</v>
+      </c>
+      <c r="E738" t="s">
+        <v>1653</v>
+      </c>
+      <c r="F738" t="s">
         <v>1802</v>
-      </c>
-      <c r="E738" t="s">
-        <v>1654</v>
-      </c>
-      <c r="F738" t="s">
-        <v>1748</v>
       </c>
       <c r="G738" t="s">
         <v>20</v>
@@ -23957,13 +23957,13 @@
         <v>9</v>
       </c>
       <c r="D739" t="s">
-        <v>1751</v>
+        <v>1746</v>
       </c>
       <c r="E739" t="s">
         <v>1747</v>
       </c>
       <c r="F739" t="s">
-        <v>1748</v>
+        <v>1751</v>
       </c>
       <c r="G739" t="s">
         <v>1234</v>
@@ -23980,13 +23980,13 @@
         <v>9</v>
       </c>
       <c r="D740" t="s">
-        <v>1751</v>
+        <v>1746</v>
       </c>
       <c r="E740" t="s">
         <v>1747</v>
       </c>
       <c r="F740" t="s">
-        <v>1748</v>
+        <v>1751</v>
       </c>
       <c r="G740" t="s">
         <v>1234</v>
@@ -24003,13 +24003,13 @@
         <v>9</v>
       </c>
       <c r="D741" t="s">
+        <v>1746</v>
+      </c>
+      <c r="E741" t="s">
         <v>1809</v>
       </c>
-      <c r="E741" t="s">
+      <c r="F741" t="s">
         <v>1810</v>
-      </c>
-      <c r="F741" t="s">
-        <v>1748</v>
       </c>
       <c r="G741" t="s">
         <v>34</v>
@@ -24026,13 +24026,13 @@
         <v>9</v>
       </c>
       <c r="D742" t="s">
-        <v>1813</v>
+        <v>1746</v>
       </c>
       <c r="E742" t="s">
         <v>1747</v>
       </c>
       <c r="F742" t="s">
-        <v>1748</v>
+        <v>1813</v>
       </c>
       <c r="G742" t="s">
         <v>20</v>
@@ -24049,13 +24049,13 @@
         <v>9</v>
       </c>
       <c r="D743" t="s">
-        <v>1751</v>
+        <v>1746</v>
       </c>
       <c r="E743" t="s">
         <v>1747</v>
       </c>
       <c r="F743" t="s">
-        <v>1748</v>
+        <v>1751</v>
       </c>
       <c r="G743" t="s">
         <v>1234</v>
@@ -24095,13 +24095,13 @@
         <v>9</v>
       </c>
       <c r="D745" t="s">
-        <v>1820</v>
+        <v>1746</v>
       </c>
       <c r="E745" t="s">
         <v>1747</v>
       </c>
       <c r="F745" t="s">
-        <v>1748</v>
+        <v>1820</v>
       </c>
       <c r="G745" t="s">
         <v>34</v>
@@ -24118,13 +24118,13 @@
         <v>9</v>
       </c>
       <c r="D746" t="s">
-        <v>1751</v>
+        <v>1746</v>
       </c>
       <c r="E746" t="s">
         <v>1747</v>
       </c>
       <c r="F746" t="s">
-        <v>1748</v>
+        <v>1751</v>
       </c>
       <c r="G746" t="s">
         <v>1234</v>
@@ -24141,13 +24141,13 @@
         <v>9</v>
       </c>
       <c r="D747" t="s">
-        <v>1751</v>
+        <v>1746</v>
       </c>
       <c r="E747" t="s">
         <v>1747</v>
       </c>
       <c r="F747" t="s">
-        <v>1748</v>
+        <v>1751</v>
       </c>
       <c r="G747" t="s">
         <v>1234</v>
@@ -24164,13 +24164,13 @@
         <v>9</v>
       </c>
       <c r="D748" t="s">
-        <v>1751</v>
+        <v>1746</v>
       </c>
       <c r="E748" t="s">
         <v>1747</v>
       </c>
       <c r="F748" t="s">
-        <v>1748</v>
+        <v>1751</v>
       </c>
       <c r="G748" t="s">
         <v>1234</v>
@@ -24187,13 +24187,13 @@
         <v>9</v>
       </c>
       <c r="D749" t="s">
-        <v>1751</v>
+        <v>1746</v>
       </c>
       <c r="E749" t="s">
         <v>1747</v>
       </c>
       <c r="F749" t="s">
-        <v>1748</v>
+        <v>1751</v>
       </c>
       <c r="G749" t="s">
         <v>1234</v>
@@ -24233,13 +24233,13 @@
         <v>9</v>
       </c>
       <c r="D751" t="s">
+        <v>1831</v>
+      </c>
+      <c r="E751" t="s">
         <v>1836</v>
       </c>
-      <c r="E751" t="s">
+      <c r="F751" t="s">
         <v>1837</v>
-      </c>
-      <c r="F751" t="s">
-        <v>1833</v>
       </c>
       <c r="G751" t="s">
         <v>34</v>
@@ -24256,13 +24256,13 @@
         <v>9</v>
       </c>
       <c r="D752" t="s">
+        <v>1831</v>
+      </c>
+      <c r="E752" t="s">
         <v>1840</v>
       </c>
-      <c r="E752" t="s">
+      <c r="F752" t="s">
         <v>1841</v>
-      </c>
-      <c r="F752" t="s">
-        <v>1833</v>
       </c>
       <c r="G752" t="s">
         <v>1234</v>
@@ -24279,13 +24279,13 @@
         <v>9</v>
       </c>
       <c r="D753" t="s">
+        <v>1831</v>
+      </c>
+      <c r="E753" t="s">
         <v>1840</v>
       </c>
-      <c r="E753" t="s">
+      <c r="F753" t="s">
         <v>1841</v>
-      </c>
-      <c r="F753" t="s">
-        <v>1833</v>
       </c>
       <c r="G753" t="s">
         <v>1234</v>
@@ -24302,13 +24302,13 @@
         <v>9</v>
       </c>
       <c r="D754" t="s">
+        <v>1831</v>
+      </c>
+      <c r="E754" t="s">
         <v>1840</v>
       </c>
-      <c r="E754" t="s">
+      <c r="F754" t="s">
         <v>1841</v>
-      </c>
-      <c r="F754" t="s">
-        <v>1833</v>
       </c>
       <c r="G754" t="s">
         <v>1234</v>
@@ -24325,13 +24325,13 @@
         <v>9</v>
       </c>
       <c r="D755" t="s">
+        <v>1831</v>
+      </c>
+      <c r="E755" t="s">
         <v>1840</v>
       </c>
-      <c r="E755" t="s">
+      <c r="F755" t="s">
         <v>1841</v>
-      </c>
-      <c r="F755" t="s">
-        <v>1833</v>
       </c>
       <c r="G755" t="s">
         <v>1234</v>
@@ -24348,13 +24348,13 @@
         <v>9</v>
       </c>
       <c r="D756" t="s">
+        <v>1831</v>
+      </c>
+      <c r="E756" t="s">
         <v>1840</v>
       </c>
-      <c r="E756" t="s">
+      <c r="F756" t="s">
         <v>1841</v>
-      </c>
-      <c r="F756" t="s">
-        <v>1833</v>
       </c>
       <c r="G756" t="s">
         <v>1234</v>
@@ -24371,13 +24371,13 @@
         <v>9</v>
       </c>
       <c r="D757" t="s">
+        <v>1831</v>
+      </c>
+      <c r="E757" t="s">
         <v>1840</v>
       </c>
-      <c r="E757" t="s">
+      <c r="F757" t="s">
         <v>1841</v>
-      </c>
-      <c r="F757" t="s">
-        <v>1833</v>
       </c>
       <c r="G757" t="s">
         <v>1234</v>
@@ -24397,7 +24397,7 @@
         <v>1831</v>
       </c>
       <c r="E758" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
       <c r="F758" t="s">
         <v>1833</v>
@@ -24417,13 +24417,13 @@
         <v>9</v>
       </c>
       <c r="D759" t="s">
+        <v>1831</v>
+      </c>
+      <c r="E759" t="s">
+        <v>1840</v>
+      </c>
+      <c r="F759" t="s">
         <v>1797</v>
-      </c>
-      <c r="E759" t="s">
-        <v>1841</v>
-      </c>
-      <c r="F759" t="s">
-        <v>1833</v>
       </c>
       <c r="G759" t="s">
         <v>20</v>
@@ -24440,13 +24440,13 @@
         <v>9</v>
       </c>
       <c r="D760" t="s">
+        <v>1831</v>
+      </c>
+      <c r="E760" t="s">
         <v>1840</v>
       </c>
-      <c r="E760" t="s">
+      <c r="F760" t="s">
         <v>1841</v>
-      </c>
-      <c r="F760" t="s">
-        <v>1833</v>
       </c>
       <c r="G760" t="s">
         <v>1234</v>
@@ -24463,13 +24463,13 @@
         <v>9</v>
       </c>
       <c r="D761" t="s">
+        <v>1831</v>
+      </c>
+      <c r="E761" t="s">
         <v>1840</v>
       </c>
-      <c r="E761" t="s">
+      <c r="F761" t="s">
         <v>1841</v>
-      </c>
-      <c r="F761" t="s">
-        <v>1833</v>
       </c>
       <c r="G761" t="s">
         <v>1234</v>
@@ -24486,13 +24486,13 @@
         <v>9</v>
       </c>
       <c r="D762" t="s">
-        <v>1797</v>
+        <v>1831</v>
       </c>
       <c r="E762" t="s">
         <v>1862</v>
       </c>
       <c r="F762" t="s">
-        <v>1833</v>
+        <v>1797</v>
       </c>
       <c r="G762" t="s">
         <v>34</v>
@@ -24509,13 +24509,13 @@
         <v>9</v>
       </c>
       <c r="D763" t="s">
+        <v>1831</v>
+      </c>
+      <c r="E763" t="s">
         <v>1840</v>
       </c>
-      <c r="E763" t="s">
+      <c r="F763" t="s">
         <v>1841</v>
-      </c>
-      <c r="F763" t="s">
-        <v>1833</v>
       </c>
       <c r="G763" t="s">
         <v>1234</v>
@@ -24532,13 +24532,13 @@
         <v>9</v>
       </c>
       <c r="D764" t="s">
+        <v>1831</v>
+      </c>
+      <c r="E764" t="s">
         <v>1867</v>
       </c>
-      <c r="E764" t="s">
+      <c r="F764" t="s">
         <v>1868</v>
-      </c>
-      <c r="F764" t="s">
-        <v>1833</v>
       </c>
       <c r="G764" t="s">
         <v>34</v>
@@ -24555,13 +24555,13 @@
         <v>9</v>
       </c>
       <c r="D765" t="s">
-        <v>1840</v>
+        <v>1831</v>
       </c>
       <c r="E765" t="s">
         <v>1832</v>
       </c>
       <c r="F765" t="s">
-        <v>1833</v>
+        <v>1841</v>
       </c>
       <c r="G765" t="s">
         <v>34</v>
@@ -24578,13 +24578,13 @@
         <v>9</v>
       </c>
       <c r="D766" t="s">
-        <v>1873</v>
+        <v>1831</v>
       </c>
       <c r="E766" t="s">
         <v>1862</v>
       </c>
       <c r="F766" t="s">
-        <v>1833</v>
+        <v>1873</v>
       </c>
       <c r="G766" t="s">
         <v>34</v>
@@ -24601,13 +24601,13 @@
         <v>9</v>
       </c>
       <c r="D767" t="s">
+        <v>1831</v>
+      </c>
+      <c r="E767" t="s">
         <v>1876</v>
       </c>
-      <c r="E767" t="s">
+      <c r="F767" t="s">
         <v>1877</v>
-      </c>
-      <c r="F767" t="s">
-        <v>1833</v>
       </c>
       <c r="G767" t="s">
         <v>34</v>
@@ -24624,13 +24624,13 @@
         <v>9</v>
       </c>
       <c r="D768" t="s">
+        <v>1831</v>
+      </c>
+      <c r="E768" t="s">
         <v>1840</v>
       </c>
-      <c r="E768" t="s">
+      <c r="F768" t="s">
         <v>1841</v>
-      </c>
-      <c r="F768" t="s">
-        <v>1833</v>
       </c>
       <c r="G768" t="s">
         <v>1234</v>
@@ -24647,13 +24647,13 @@
         <v>9</v>
       </c>
       <c r="D769" t="s">
+        <v>1831</v>
+      </c>
+      <c r="E769" t="s">
         <v>1840</v>
       </c>
-      <c r="E769" t="s">
+      <c r="F769" t="s">
         <v>1841</v>
-      </c>
-      <c r="F769" t="s">
-        <v>1833</v>
       </c>
       <c r="G769" t="s">
         <v>1234</v>
@@ -24670,13 +24670,13 @@
         <v>9</v>
       </c>
       <c r="D770" t="s">
+        <v>1831</v>
+      </c>
+      <c r="E770" t="s">
         <v>1884</v>
       </c>
-      <c r="E770" t="s">
+      <c r="F770" t="s">
         <v>1885</v>
-      </c>
-      <c r="F770" t="s">
-        <v>1833</v>
       </c>
       <c r="G770" t="s">
         <v>34</v>
@@ -24693,13 +24693,13 @@
         <v>9</v>
       </c>
       <c r="D771" t="s">
+        <v>1831</v>
+      </c>
+      <c r="E771" t="s">
         <v>1840</v>
       </c>
-      <c r="E771" t="s">
+      <c r="F771" t="s">
         <v>1841</v>
-      </c>
-      <c r="F771" t="s">
-        <v>1833</v>
       </c>
       <c r="G771" t="s">
         <v>1234</v>
@@ -24716,13 +24716,13 @@
         <v>9</v>
       </c>
       <c r="D772" t="s">
+        <v>1831</v>
+      </c>
+      <c r="E772" t="s">
         <v>1840</v>
       </c>
-      <c r="E772" t="s">
+      <c r="F772" t="s">
         <v>1841</v>
-      </c>
-      <c r="F772" t="s">
-        <v>1833</v>
       </c>
       <c r="G772" t="s">
         <v>1234</v>
@@ -24739,13 +24739,13 @@
         <v>9</v>
       </c>
       <c r="D773" t="s">
+        <v>1831</v>
+      </c>
+      <c r="E773" t="s">
         <v>1840</v>
       </c>
-      <c r="E773" t="s">
+      <c r="F773" t="s">
         <v>1841</v>
-      </c>
-      <c r="F773" t="s">
-        <v>1833</v>
       </c>
       <c r="G773" t="s">
         <v>1234</v>
@@ -24762,13 +24762,13 @@
         <v>9</v>
       </c>
       <c r="D774" t="s">
+        <v>1831</v>
+      </c>
+      <c r="E774" t="s">
         <v>1894</v>
       </c>
-      <c r="E774" t="s">
+      <c r="F774" t="s">
         <v>1895</v>
-      </c>
-      <c r="F774" t="s">
-        <v>1833</v>
       </c>
       <c r="G774" t="s">
         <v>34</v>
@@ -24785,13 +24785,13 @@
         <v>9</v>
       </c>
       <c r="D775" t="s">
+        <v>1831</v>
+      </c>
+      <c r="E775" t="s">
         <v>1840</v>
       </c>
-      <c r="E775" t="s">
+      <c r="F775" t="s">
         <v>1841</v>
-      </c>
-      <c r="F775" t="s">
-        <v>1833</v>
       </c>
       <c r="G775" t="s">
         <v>1234</v>
@@ -24831,13 +24831,13 @@
         <v>9</v>
       </c>
       <c r="D777" t="s">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="E777" t="s">
         <v>1901</v>
       </c>
       <c r="F777" t="s">
-        <v>1902</v>
+        <v>1905</v>
       </c>
       <c r="G777" t="s">
         <v>1234</v>
@@ -24854,13 +24854,13 @@
         <v>9</v>
       </c>
       <c r="D778" t="s">
+        <v>1900</v>
+      </c>
+      <c r="E778" t="s">
         <v>1908</v>
       </c>
-      <c r="E778" t="s">
+      <c r="F778" t="s">
         <v>1909</v>
-      </c>
-      <c r="F778" t="s">
-        <v>1902</v>
       </c>
       <c r="G778" t="s">
         <v>34</v>
@@ -24877,13 +24877,13 @@
         <v>9</v>
       </c>
       <c r="D779" t="s">
+        <v>1900</v>
+      </c>
+      <c r="E779" t="s">
         <v>1912</v>
       </c>
-      <c r="E779" t="s">
+      <c r="F779" t="s">
         <v>1913</v>
-      </c>
-      <c r="F779" t="s">
-        <v>1902</v>
       </c>
       <c r="G779" t="s">
         <v>34</v>
@@ -24900,13 +24900,13 @@
         <v>9</v>
       </c>
       <c r="D780" t="s">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="E780" t="s">
         <v>1901</v>
       </c>
       <c r="F780" t="s">
-        <v>1902</v>
+        <v>1905</v>
       </c>
       <c r="G780" t="s">
         <v>1234</v>
@@ -24923,13 +24923,13 @@
         <v>9</v>
       </c>
       <c r="D781" t="s">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="E781" t="s">
         <v>1901</v>
       </c>
       <c r="F781" t="s">
-        <v>1902</v>
+        <v>1905</v>
       </c>
       <c r="G781" t="s">
         <v>1234</v>
@@ -24946,13 +24946,13 @@
         <v>9</v>
       </c>
       <c r="D782" t="s">
-        <v>1920</v>
+        <v>1900</v>
       </c>
       <c r="E782" t="s">
         <v>1901</v>
       </c>
       <c r="F782" t="s">
-        <v>1902</v>
+        <v>1920</v>
       </c>
       <c r="G782" t="s">
         <v>1234</v>
@@ -24969,13 +24969,13 @@
         <v>9</v>
       </c>
       <c r="D783" t="s">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="E783" t="s">
         <v>1901</v>
       </c>
       <c r="F783" t="s">
-        <v>1902</v>
+        <v>1905</v>
       </c>
       <c r="G783" t="s">
         <v>1234</v>
@@ -24992,13 +24992,13 @@
         <v>9</v>
       </c>
       <c r="D784" t="s">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="E784" t="s">
         <v>1901</v>
       </c>
       <c r="F784" t="s">
-        <v>1902</v>
+        <v>1905</v>
       </c>
       <c r="G784" t="s">
         <v>1234</v>
@@ -25015,13 +25015,13 @@
         <v>9</v>
       </c>
       <c r="D785" t="s">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="E785" t="s">
         <v>1901</v>
       </c>
       <c r="F785" t="s">
-        <v>1902</v>
+        <v>1905</v>
       </c>
       <c r="G785" t="s">
         <v>1234</v>
@@ -25038,13 +25038,13 @@
         <v>9</v>
       </c>
       <c r="D786" t="s">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="E786" t="s">
         <v>1901</v>
       </c>
       <c r="F786" t="s">
-        <v>1902</v>
+        <v>1905</v>
       </c>
       <c r="G786" t="s">
         <v>1234</v>
@@ -25061,13 +25061,13 @@
         <v>9</v>
       </c>
       <c r="D787" t="s">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="E787" t="s">
         <v>1901</v>
       </c>
       <c r="F787" t="s">
-        <v>1902</v>
+        <v>1905</v>
       </c>
       <c r="G787" t="s">
         <v>1234</v>
@@ -25084,13 +25084,13 @@
         <v>9</v>
       </c>
       <c r="D788" t="s">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="E788" t="s">
         <v>1901</v>
       </c>
       <c r="F788" t="s">
-        <v>1902</v>
+        <v>1905</v>
       </c>
       <c r="G788" t="s">
         <v>1234</v>
@@ -25130,13 +25130,13 @@
         <v>9</v>
       </c>
       <c r="D790" t="s">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="E790" t="s">
         <v>1901</v>
       </c>
       <c r="F790" t="s">
-        <v>1902</v>
+        <v>1905</v>
       </c>
       <c r="G790" t="s">
         <v>1234</v>
@@ -25153,13 +25153,13 @@
         <v>9</v>
       </c>
       <c r="D791" t="s">
-        <v>1920</v>
+        <v>1900</v>
       </c>
       <c r="E791" t="s">
         <v>1940</v>
       </c>
       <c r="F791" t="s">
-        <v>1902</v>
+        <v>1920</v>
       </c>
       <c r="G791" t="s">
         <v>34</v>
@@ -25176,13 +25176,13 @@
         <v>9</v>
       </c>
       <c r="D792" t="s">
-        <v>1943</v>
+        <v>1900</v>
       </c>
       <c r="E792" t="s">
         <v>1935</v>
       </c>
       <c r="F792" t="s">
-        <v>1902</v>
+        <v>1943</v>
       </c>
       <c r="G792" t="s">
         <v>34</v>
@@ -25199,13 +25199,13 @@
         <v>9</v>
       </c>
       <c r="D793" t="s">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="E793" t="s">
         <v>1901</v>
       </c>
       <c r="F793" t="s">
-        <v>1902</v>
+        <v>1905</v>
       </c>
       <c r="G793" t="s">
         <v>1234</v>
@@ -25222,13 +25222,13 @@
         <v>9</v>
       </c>
       <c r="D794" t="s">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="E794" t="s">
         <v>1948</v>
       </c>
       <c r="F794" t="s">
-        <v>1902</v>
+        <v>1905</v>
       </c>
       <c r="G794" t="s">
         <v>34</v>
@@ -25245,13 +25245,13 @@
         <v>9</v>
       </c>
       <c r="D795" t="s">
-        <v>1951</v>
+        <v>1900</v>
       </c>
       <c r="E795" t="s">
         <v>1901</v>
       </c>
       <c r="F795" t="s">
-        <v>1902</v>
+        <v>1951</v>
       </c>
       <c r="G795" t="s">
         <v>34</v>
@@ -25268,13 +25268,13 @@
         <v>9</v>
       </c>
       <c r="D796" t="s">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="E796" t="s">
         <v>1901</v>
       </c>
       <c r="F796" t="s">
-        <v>1902</v>
+        <v>1905</v>
       </c>
       <c r="G796" t="s">
         <v>1234</v>
@@ -25291,13 +25291,13 @@
         <v>9</v>
       </c>
       <c r="D797" t="s">
+        <v>1900</v>
+      </c>
+      <c r="E797" t="s">
         <v>1956</v>
       </c>
-      <c r="E797" t="s">
+      <c r="F797" t="s">
         <v>1957</v>
-      </c>
-      <c r="F797" t="s">
-        <v>1902</v>
       </c>
       <c r="G797" t="s">
         <v>34</v>
@@ -25314,13 +25314,13 @@
         <v>9</v>
       </c>
       <c r="D798" t="s">
+        <v>1900</v>
+      </c>
+      <c r="E798" t="s">
         <v>1960</v>
       </c>
-      <c r="E798" t="s">
+      <c r="F798" t="s">
         <v>1961</v>
-      </c>
-      <c r="F798" t="s">
-        <v>1902</v>
       </c>
       <c r="G798" t="s">
         <v>34</v>
@@ -25337,13 +25337,13 @@
         <v>9</v>
       </c>
       <c r="D799" t="s">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="E799" t="s">
         <v>1901</v>
       </c>
       <c r="F799" t="s">
-        <v>1902</v>
+        <v>1905</v>
       </c>
       <c r="G799" t="s">
         <v>1234</v>
@@ -25360,13 +25360,13 @@
         <v>9</v>
       </c>
       <c r="D800" t="s">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="E800" t="s">
         <v>1901</v>
       </c>
       <c r="F800" t="s">
-        <v>1902</v>
+        <v>1905</v>
       </c>
       <c r="G800" t="s">
         <v>1234</v>
@@ -25383,13 +25383,13 @@
         <v>9</v>
       </c>
       <c r="D801" t="s">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="E801" t="s">
         <v>1901</v>
       </c>
       <c r="F801" t="s">
-        <v>1902</v>
+        <v>1905</v>
       </c>
       <c r="G801" t="s">
         <v>1234</v>
@@ -25406,13 +25406,13 @@
         <v>9</v>
       </c>
       <c r="D802" t="s">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="E802" t="s">
         <v>1901</v>
       </c>
       <c r="F802" t="s">
-        <v>1902</v>
+        <v>1905</v>
       </c>
       <c r="G802" t="s">
         <v>1234</v>
@@ -25429,13 +25429,13 @@
         <v>9</v>
       </c>
       <c r="D803" t="s">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="E803" t="s">
         <v>1901</v>
       </c>
       <c r="F803" t="s">
-        <v>1902</v>
+        <v>1905</v>
       </c>
       <c r="G803" t="s">
         <v>1234</v>
@@ -25452,13 +25452,13 @@
         <v>9</v>
       </c>
       <c r="D804" t="s">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="E804" t="s">
         <v>1901</v>
       </c>
       <c r="F804" t="s">
-        <v>1902</v>
+        <v>1905</v>
       </c>
       <c r="G804" t="s">
         <v>1234</v>
@@ -25475,13 +25475,13 @@
         <v>9</v>
       </c>
       <c r="D805" t="s">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="E805" t="s">
         <v>1901</v>
       </c>
       <c r="F805" t="s">
-        <v>1902</v>
+        <v>1905</v>
       </c>
       <c r="G805" t="s">
         <v>1234</v>
@@ -25498,13 +25498,13 @@
         <v>9</v>
       </c>
       <c r="D806" t="s">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="E806" t="s">
         <v>1901</v>
       </c>
       <c r="F806" t="s">
-        <v>1902</v>
+        <v>1905</v>
       </c>
       <c r="G806" t="s">
         <v>1234</v>
@@ -25521,13 +25521,13 @@
         <v>9</v>
       </c>
       <c r="D807" t="s">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="E807" t="s">
         <v>1901</v>
       </c>
       <c r="F807" t="s">
-        <v>1902</v>
+        <v>1905</v>
       </c>
       <c r="G807" t="s">
         <v>1234</v>
@@ -25613,13 +25613,13 @@
         <v>9</v>
       </c>
       <c r="D811" t="s">
+        <v>1982</v>
+      </c>
+      <c r="E811" t="s">
         <v>1992</v>
       </c>
-      <c r="E811" t="s">
+      <c r="F811" t="s">
         <v>1993</v>
-      </c>
-      <c r="F811" t="s">
-        <v>1984</v>
       </c>
       <c r="G811" t="s">
         <v>34</v>
@@ -25682,13 +25682,13 @@
         <v>9</v>
       </c>
       <c r="D814" t="s">
-        <v>1992</v>
+        <v>1982</v>
       </c>
       <c r="E814" t="s">
         <v>1983</v>
       </c>
       <c r="F814" t="s">
-        <v>1984</v>
+        <v>1993</v>
       </c>
       <c r="G814" t="s">
         <v>1234</v>
@@ -25705,13 +25705,13 @@
         <v>9</v>
       </c>
       <c r="D815" t="s">
+        <v>1982</v>
+      </c>
+      <c r="E815" t="s">
         <v>2002</v>
       </c>
-      <c r="E815" t="s">
+      <c r="F815" t="s">
         <v>2003</v>
-      </c>
-      <c r="F815" t="s">
-        <v>1984</v>
       </c>
       <c r="G815" t="s">
         <v>34</v>
@@ -25843,13 +25843,13 @@
         <v>9</v>
       </c>
       <c r="D821" t="s">
+        <v>1982</v>
+      </c>
+      <c r="E821" t="s">
         <v>2016</v>
       </c>
-      <c r="E821" t="s">
+      <c r="F821" t="s">
         <v>2017</v>
-      </c>
-      <c r="F821" t="s">
-        <v>1984</v>
       </c>
       <c r="G821" t="s">
         <v>20</v>
@@ -25866,13 +25866,13 @@
         <v>9</v>
       </c>
       <c r="D822" t="s">
+        <v>1982</v>
+      </c>
+      <c r="E822" t="s">
         <v>2020</v>
       </c>
-      <c r="E822" t="s">
+      <c r="F822" t="s">
         <v>2021</v>
-      </c>
-      <c r="F822" t="s">
-        <v>1984</v>
       </c>
       <c r="G822" t="s">
         <v>1987</v>
@@ -25889,13 +25889,13 @@
         <v>9</v>
       </c>
       <c r="D823" t="s">
-        <v>2020</v>
+        <v>1982</v>
       </c>
       <c r="E823" t="s">
         <v>1983</v>
       </c>
       <c r="F823" t="s">
-        <v>1984</v>
+        <v>2021</v>
       </c>
       <c r="G823" t="s">
         <v>1987</v>
@@ -25912,13 +25912,13 @@
         <v>9</v>
       </c>
       <c r="D824" t="s">
+        <v>1982</v>
+      </c>
+      <c r="E824" t="s">
         <v>2020</v>
       </c>
-      <c r="E824" t="s">
+      <c r="F824" t="s">
         <v>2021</v>
-      </c>
-      <c r="F824" t="s">
-        <v>1984</v>
       </c>
       <c r="G824" t="s">
         <v>1987</v>
@@ -25935,13 +25935,13 @@
         <v>9</v>
       </c>
       <c r="D825" t="s">
+        <v>1982</v>
+      </c>
+      <c r="E825" t="s">
         <v>2020</v>
       </c>
-      <c r="E825" t="s">
+      <c r="F825" t="s">
         <v>2021</v>
-      </c>
-      <c r="F825" t="s">
-        <v>1984</v>
       </c>
       <c r="G825" t="s">
         <v>1234</v>
@@ -25958,13 +25958,13 @@
         <v>9</v>
       </c>
       <c r="D826" t="s">
+        <v>1982</v>
+      </c>
+      <c r="E826" t="s">
         <v>2020</v>
       </c>
-      <c r="E826" t="s">
+      <c r="F826" t="s">
         <v>2021</v>
-      </c>
-      <c r="F826" t="s">
-        <v>1984</v>
       </c>
       <c r="G826" t="s">
         <v>1987</v>
@@ -25981,13 +25981,13 @@
         <v>9</v>
       </c>
       <c r="D827" t="s">
+        <v>1982</v>
+      </c>
+      <c r="E827" t="s">
         <v>2020</v>
       </c>
-      <c r="E827" t="s">
+      <c r="F827" t="s">
         <v>2021</v>
-      </c>
-      <c r="F827" t="s">
-        <v>1984</v>
       </c>
       <c r="G827" t="s">
         <v>1987</v>
@@ -26004,13 +26004,13 @@
         <v>9</v>
       </c>
       <c r="D828" t="s">
-        <v>2020</v>
+        <v>1982</v>
       </c>
       <c r="E828" t="s">
         <v>1983</v>
       </c>
       <c r="F828" t="s">
-        <v>1984</v>
+        <v>2021</v>
       </c>
       <c r="G828" t="s">
         <v>1987</v>
@@ -26050,13 +26050,13 @@
         <v>9</v>
       </c>
       <c r="D830" t="s">
-        <v>1992</v>
+        <v>1982</v>
       </c>
       <c r="E830" t="s">
         <v>1983</v>
       </c>
       <c r="F830" t="s">
-        <v>1984</v>
+        <v>1993</v>
       </c>
       <c r="G830" t="s">
         <v>1987</v>
@@ -26280,13 +26280,13 @@
         <v>9</v>
       </c>
       <c r="D840" t="s">
-        <v>2061</v>
+        <v>2056</v>
       </c>
       <c r="E840" t="s">
         <v>2057</v>
       </c>
       <c r="F840" t="s">
-        <v>2058</v>
+        <v>2061</v>
       </c>
       <c r="G840" t="s">
         <v>1987</v>
@@ -26303,13 +26303,13 @@
         <v>9</v>
       </c>
       <c r="D841" t="s">
-        <v>2061</v>
+        <v>2056</v>
       </c>
       <c r="E841" t="s">
         <v>2057</v>
       </c>
       <c r="F841" t="s">
-        <v>2058</v>
+        <v>2061</v>
       </c>
       <c r="G841" t="s">
         <v>1987</v>
@@ -26326,13 +26326,13 @@
         <v>9</v>
       </c>
       <c r="D842" t="s">
-        <v>2061</v>
+        <v>2056</v>
       </c>
       <c r="E842" t="s">
         <v>2057</v>
       </c>
       <c r="F842" t="s">
-        <v>2058</v>
+        <v>2061</v>
       </c>
       <c r="G842" t="s">
         <v>1987</v>
@@ -26349,13 +26349,13 @@
         <v>9</v>
       </c>
       <c r="D843" t="s">
-        <v>2061</v>
+        <v>2056</v>
       </c>
       <c r="E843" t="s">
         <v>2057</v>
       </c>
       <c r="F843" t="s">
-        <v>2058</v>
+        <v>2061</v>
       </c>
       <c r="G843" t="s">
         <v>1987</v>
@@ -26372,13 +26372,13 @@
         <v>9</v>
       </c>
       <c r="D844" t="s">
-        <v>2061</v>
+        <v>2056</v>
       </c>
       <c r="E844" t="s">
         <v>2057</v>
       </c>
       <c r="F844" t="s">
-        <v>2058</v>
+        <v>2061</v>
       </c>
       <c r="G844" t="s">
         <v>1987</v>
@@ -26395,13 +26395,13 @@
         <v>9</v>
       </c>
       <c r="D845" t="s">
-        <v>2061</v>
+        <v>2056</v>
       </c>
       <c r="E845" t="s">
         <v>2057</v>
       </c>
       <c r="F845" t="s">
-        <v>2058</v>
+        <v>2061</v>
       </c>
       <c r="G845" t="s">
         <v>1234</v>
@@ -26418,13 +26418,13 @@
         <v>9</v>
       </c>
       <c r="D846" t="s">
-        <v>2061</v>
+        <v>2056</v>
       </c>
       <c r="E846" t="s">
         <v>2057</v>
       </c>
       <c r="F846" t="s">
-        <v>2058</v>
+        <v>2061</v>
       </c>
       <c r="G846" t="s">
         <v>1987</v>
@@ -26441,13 +26441,13 @@
         <v>9</v>
       </c>
       <c r="D847" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E847" t="s">
+        <v>1992</v>
+      </c>
+      <c r="F847" t="s">
         <v>2076</v>
-      </c>
-      <c r="E847" t="s">
-        <v>1993</v>
-      </c>
-      <c r="F847" t="s">
-        <v>2058</v>
       </c>
       <c r="G847" t="s">
         <v>1987</v>
@@ -26464,13 +26464,13 @@
         <v>9</v>
       </c>
       <c r="D848" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E848" t="s">
+        <v>1992</v>
+      </c>
+      <c r="F848" t="s">
         <v>2076</v>
-      </c>
-      <c r="E848" t="s">
-        <v>1993</v>
-      </c>
-      <c r="F848" t="s">
-        <v>2058</v>
       </c>
       <c r="G848" t="s">
         <v>1987</v>
@@ -26487,13 +26487,13 @@
         <v>9</v>
       </c>
       <c r="D849" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E849" t="s">
+        <v>1992</v>
+      </c>
+      <c r="F849" t="s">
         <v>2076</v>
-      </c>
-      <c r="E849" t="s">
-        <v>1993</v>
-      </c>
-      <c r="F849" t="s">
-        <v>2058</v>
       </c>
       <c r="G849" t="s">
         <v>1234</v>
@@ -26510,13 +26510,13 @@
         <v>9</v>
       </c>
       <c r="D850" t="s">
-        <v>2076</v>
+        <v>2056</v>
       </c>
       <c r="E850" t="s">
         <v>2083</v>
       </c>
       <c r="F850" t="s">
-        <v>2058</v>
+        <v>2076</v>
       </c>
       <c r="G850" t="s">
         <v>1987</v>
@@ -26533,13 +26533,13 @@
         <v>9</v>
       </c>
       <c r="D851" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E851" t="s">
+        <v>1992</v>
+      </c>
+      <c r="F851" t="s">
         <v>2076</v>
-      </c>
-      <c r="E851" t="s">
-        <v>1993</v>
-      </c>
-      <c r="F851" t="s">
-        <v>2058</v>
       </c>
       <c r="G851" t="s">
         <v>1987</v>
@@ -26556,13 +26556,13 @@
         <v>9</v>
       </c>
       <c r="D852" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E852" t="s">
+        <v>1992</v>
+      </c>
+      <c r="F852" t="s">
         <v>2076</v>
-      </c>
-      <c r="E852" t="s">
-        <v>1993</v>
-      </c>
-      <c r="F852" t="s">
-        <v>2058</v>
       </c>
       <c r="G852" t="s">
         <v>1987</v>
@@ -26579,13 +26579,13 @@
         <v>9</v>
       </c>
       <c r="D853" t="s">
-        <v>2061</v>
+        <v>2056</v>
       </c>
       <c r="E853" t="s">
         <v>2057</v>
       </c>
       <c r="F853" t="s">
-        <v>2058</v>
+        <v>2061</v>
       </c>
       <c r="G853" t="s">
         <v>1987</v>
@@ -26602,13 +26602,13 @@
         <v>9</v>
       </c>
       <c r="D854" t="s">
-        <v>2061</v>
+        <v>2056</v>
       </c>
       <c r="E854" t="s">
         <v>2057</v>
       </c>
       <c r="F854" t="s">
-        <v>2058</v>
+        <v>2061</v>
       </c>
       <c r="G854" t="s">
         <v>20</v>
@@ -26625,13 +26625,13 @@
         <v>9</v>
       </c>
       <c r="D855" t="s">
-        <v>2061</v>
+        <v>2056</v>
       </c>
       <c r="E855" t="s">
         <v>2057</v>
       </c>
       <c r="F855" t="s">
-        <v>2058</v>
+        <v>2061</v>
       </c>
       <c r="G855" t="s">
         <v>20</v>
@@ -26648,13 +26648,13 @@
         <v>9</v>
       </c>
       <c r="D856" t="s">
-        <v>2061</v>
+        <v>2056</v>
       </c>
       <c r="E856" t="s">
         <v>2057</v>
       </c>
       <c r="F856" t="s">
-        <v>2058</v>
+        <v>2061</v>
       </c>
       <c r="G856" t="s">
         <v>20</v>
@@ -26671,13 +26671,13 @@
         <v>9</v>
       </c>
       <c r="D857" t="s">
-        <v>2061</v>
+        <v>2056</v>
       </c>
       <c r="E857" t="s">
         <v>2057</v>
       </c>
       <c r="F857" t="s">
-        <v>2058</v>
+        <v>2061</v>
       </c>
       <c r="G857" t="s">
         <v>1987</v>
@@ -26694,13 +26694,13 @@
         <v>9</v>
       </c>
       <c r="D858" t="s">
-        <v>2061</v>
+        <v>2056</v>
       </c>
       <c r="E858" t="s">
         <v>2057</v>
       </c>
       <c r="F858" t="s">
-        <v>2058</v>
+        <v>2061</v>
       </c>
       <c r="G858" t="s">
         <v>1987</v>
@@ -26717,13 +26717,13 @@
         <v>9</v>
       </c>
       <c r="D859" t="s">
-        <v>2061</v>
+        <v>2056</v>
       </c>
       <c r="E859" t="s">
         <v>2057</v>
       </c>
       <c r="F859" t="s">
-        <v>2058</v>
+        <v>2061</v>
       </c>
       <c r="G859" t="s">
         <v>20</v>
@@ -26740,13 +26740,13 @@
         <v>9</v>
       </c>
       <c r="D860" t="s">
-        <v>2061</v>
+        <v>2056</v>
       </c>
       <c r="E860" t="s">
         <v>2057</v>
       </c>
       <c r="F860" t="s">
-        <v>2058</v>
+        <v>2061</v>
       </c>
       <c r="G860" t="s">
         <v>1987</v>
@@ -26763,13 +26763,13 @@
         <v>9</v>
       </c>
       <c r="D861" t="s">
-        <v>2061</v>
+        <v>2056</v>
       </c>
       <c r="E861" t="s">
         <v>2057</v>
       </c>
       <c r="F861" t="s">
-        <v>2058</v>
+        <v>2061</v>
       </c>
       <c r="G861" t="s">
         <v>1987</v>
@@ -26786,13 +26786,13 @@
         <v>9</v>
       </c>
       <c r="D862" t="s">
-        <v>2061</v>
+        <v>2056</v>
       </c>
       <c r="E862" t="s">
         <v>2057</v>
       </c>
       <c r="F862" t="s">
-        <v>2058</v>
+        <v>2061</v>
       </c>
       <c r="G862" t="s">
         <v>1234</v>
@@ -26809,13 +26809,13 @@
         <v>9</v>
       </c>
       <c r="D863" t="s">
-        <v>2061</v>
+        <v>2056</v>
       </c>
       <c r="E863" t="s">
         <v>2057</v>
       </c>
       <c r="F863" t="s">
-        <v>2058</v>
+        <v>2061</v>
       </c>
       <c r="G863" t="s">
         <v>1987</v>
@@ -26832,13 +26832,13 @@
         <v>9</v>
       </c>
       <c r="D864" t="s">
-        <v>2061</v>
+        <v>2056</v>
       </c>
       <c r="E864" t="s">
         <v>2057</v>
       </c>
       <c r="F864" t="s">
-        <v>2058</v>
+        <v>2061</v>
       </c>
       <c r="G864" t="s">
         <v>1987</v>
@@ -26855,13 +26855,13 @@
         <v>9</v>
       </c>
       <c r="D865" t="s">
-        <v>2061</v>
+        <v>2056</v>
       </c>
       <c r="E865" t="s">
         <v>2057</v>
       </c>
       <c r="F865" t="s">
-        <v>2058</v>
+        <v>2061</v>
       </c>
       <c r="G865" t="s">
         <v>1987</v>
@@ -26878,13 +26878,13 @@
         <v>9</v>
       </c>
       <c r="D866" t="s">
-        <v>2061</v>
+        <v>2056</v>
       </c>
       <c r="E866" t="s">
         <v>2057</v>
       </c>
       <c r="F866" t="s">
-        <v>2058</v>
+        <v>2061</v>
       </c>
       <c r="G866" t="s">
         <v>1234</v>
@@ -27545,13 +27545,13 @@
         <v>9</v>
       </c>
       <c r="D895" t="s">
-        <v>2181</v>
+        <v>2168</v>
       </c>
       <c r="E895" t="s">
         <v>2169</v>
       </c>
       <c r="F895" t="s">
-        <v>2170</v>
+        <v>2181</v>
       </c>
       <c r="G895" t="s">
         <v>1987</v>
@@ -27568,13 +27568,13 @@
         <v>185</v>
       </c>
       <c r="D896" t="s">
-        <v>2181</v>
+        <v>2168</v>
       </c>
       <c r="E896" t="s">
         <v>2169</v>
       </c>
       <c r="F896" t="s">
-        <v>2170</v>
+        <v>2181</v>
       </c>
       <c r="G896" t="s">
         <v>1234</v>
@@ -27798,13 +27798,13 @@
         <v>9</v>
       </c>
       <c r="D906" t="s">
-        <v>2205</v>
+        <v>2201</v>
       </c>
       <c r="E906" t="s">
         <v>2169</v>
       </c>
       <c r="F906" t="s">
-        <v>2202</v>
+        <v>2205</v>
       </c>
       <c r="G906" t="s">
         <v>1987</v>

--- a/api/1/clv3/xlsx/en/HumanitarianPlan.xlsx
+++ b/api/1/clv3/xlsx/en/HumanitarianPlan.xlsx
@@ -28,15 +28,15 @@
     <t>codeforiati:plan-type</t>
   </si>
   <si>
+    <t>codeforiati:plan-end-date</t>
+  </si>
+  <si>
+    <t>codeforiati:plan-start-date</t>
+  </si>
+  <si>
     <t>codeforiati:plan-year</t>
   </si>
   <si>
-    <t>codeforiati:plan-end-date</t>
-  </si>
-  <si>
-    <t>codeforiati:plan-start-date</t>
-  </si>
-  <si>
     <t>HAFG25</t>
   </si>
   <si>
@@ -49,15 +49,15 @@
     <t>Humanitarian needs and response plan</t>
   </si>
   <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
+    <t>2025-01-01</t>
+  </si>
+  <si>
     <t>2025</t>
   </si>
   <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
-    <t>2025-01-01</t>
-  </si>
-  <si>
     <t>RIRNPAK25</t>
   </si>
   <si>
@@ -355,15 +355,15 @@
     <t>Afghanistan Humanitarian Needs and Response Plan 2024</t>
   </si>
   <si>
+    <t>2024-12-31</t>
+  </si>
+  <si>
+    <t>2024-01-01</t>
+  </si>
+  <si>
     <t>2024</t>
   </si>
   <si>
-    <t>2024-12-31</t>
-  </si>
-  <si>
-    <t>2024-01-01</t>
-  </si>
-  <si>
     <t>RAFG_RRP24</t>
   </si>
   <si>
@@ -712,15 +712,15 @@
     <t>Afghanistan Humanitarian Response Plan 2023</t>
   </si>
   <si>
+    <t>2023-12-31</t>
+  </si>
+  <si>
+    <t>2023-01-01</t>
+  </si>
+  <si>
     <t>2023</t>
   </si>
   <si>
-    <t>2023-12-31</t>
-  </si>
-  <si>
-    <t>2023-01-01</t>
-  </si>
-  <si>
     <t>RAFG23</t>
   </si>
   <si>
@@ -1030,15 +1030,15 @@
     <t>Afghanistan Humanitarian Response Plan 2022</t>
   </si>
   <si>
+    <t>2022-12-31</t>
+  </si>
+  <si>
+    <t>2022-01-01</t>
+  </si>
+  <si>
     <t>2022</t>
   </si>
   <si>
-    <t>2022-12-31</t>
-  </si>
-  <si>
-    <t>2022-01-01</t>
-  </si>
-  <si>
     <t>RAFG22</t>
   </si>
   <si>
@@ -1378,15 +1378,15 @@
     <t>Afghanistan Flash Appeal 2021</t>
   </si>
   <si>
+    <t>2021-12-31</t>
+  </si>
+  <si>
+    <t>2021-09-01</t>
+  </si>
+  <si>
     <t>2021</t>
   </si>
   <si>
-    <t>2021-12-31</t>
-  </si>
-  <si>
-    <t>2021-09-01</t>
-  </si>
-  <si>
     <t>HAFG21</t>
   </si>
   <si>
@@ -1735,15 +1735,15 @@
     <t>Afghanistan Humanitarian Response Plan 2020</t>
   </si>
   <si>
+    <t>2020-12-31</t>
+  </si>
+  <si>
+    <t>2020-01-01</t>
+  </si>
+  <si>
     <t>2020</t>
   </si>
   <si>
-    <t>2020-12-31</t>
-  </si>
-  <si>
-    <t>2020-01-01</t>
-  </si>
-  <si>
     <t>OBGD20</t>
   </si>
   <si>
@@ -2170,15 +2170,15 @@
     <t>Afghanistan Humanitarian Response Plan 2019</t>
   </si>
   <si>
+    <t>2019-12-31</t>
+  </si>
+  <si>
+    <t>2019-01-01</t>
+  </si>
+  <si>
     <t>2019</t>
   </si>
   <si>
-    <t>2019-12-31</t>
-  </si>
-  <si>
-    <t>2019-01-01</t>
-  </si>
-  <si>
     <t>RBGD19</t>
   </si>
   <si>
@@ -2407,15 +2407,15 @@
     <t>Afghanistan Humanitarian Response Plan 2018</t>
   </si>
   <si>
+    <t>2018-12-31</t>
+  </si>
+  <si>
+    <t>2018-01-01</t>
+  </si>
+  <si>
     <t>2018</t>
   </si>
   <si>
-    <t>2018-12-31</t>
-  </si>
-  <si>
-    <t>2018-01-01</t>
-  </si>
-  <si>
     <t>OBGD18</t>
   </si>
   <si>
@@ -2632,15 +2632,15 @@
     <t>Regional Refugee and Migrant Response Plan for Europe 2017</t>
   </si>
   <si>
+    <t>2017-12-31</t>
+  </si>
+  <si>
+    <t>2017-01-01</t>
+  </si>
+  <si>
     <t>2017</t>
   </si>
   <si>
-    <t>2017-12-31</t>
-  </si>
-  <si>
-    <t>2017-01-01</t>
-  </si>
-  <si>
     <t>HAFG17</t>
   </si>
   <si>
@@ -2917,15 +2917,15 @@
     <t>Regional Refugee and Migrant Response Plan for Europe 2016</t>
   </si>
   <si>
+    <t>2016-12-31</t>
+  </si>
+  <si>
+    <t>2016-01-01</t>
+  </si>
+  <si>
     <t>2016</t>
   </si>
   <si>
-    <t>2016-12-31</t>
-  </si>
-  <si>
-    <t>2016-01-01</t>
-  </si>
-  <si>
     <t>HAFG16</t>
   </si>
   <si>
@@ -3196,15 +3196,15 @@
     <t>Strategic response plan</t>
   </si>
   <si>
+    <t>2015-12-31</t>
+  </si>
+  <si>
+    <t>2015-01-01</t>
+  </si>
+  <si>
     <t>2015</t>
   </si>
   <si>
-    <t>2015-12-31</t>
-  </si>
-  <si>
-    <t>2015-01-01</t>
-  </si>
-  <si>
     <t>HBFA15</t>
   </si>
   <si>
@@ -3424,15 +3424,15 @@
     <t>Afghanistan Strategic Response Plan 2014</t>
   </si>
   <si>
+    <t>2014-12-31</t>
+  </si>
+  <si>
+    <t>2014-01-01</t>
+  </si>
+  <si>
     <t>2014</t>
   </si>
   <si>
-    <t>2014-12-31</t>
-  </si>
-  <si>
-    <t>2014-01-01</t>
-  </si>
-  <si>
     <t>HBFA1314</t>
   </si>
   <si>
@@ -3715,12 +3715,12 @@
     <t>Consolidated appeals process</t>
   </si>
   <si>
+    <t>2013-12-31</t>
+  </si>
+  <si>
     <t>2013</t>
   </si>
   <si>
-    <t>2013-12-31</t>
-  </si>
-  <si>
     <t>CBFA13</t>
   </si>
   <si>
@@ -3874,15 +3874,15 @@
     <t>2012+ Kenya Emergency Humanitarian Response Plan</t>
   </si>
   <si>
+    <t>2012-12-31</t>
+  </si>
+  <si>
+    <t>2012-01-01</t>
+  </si>
+  <si>
     <t>2012</t>
   </si>
   <si>
-    <t>2012-12-31</t>
-  </si>
-  <si>
-    <t>2012-01-01</t>
-  </si>
-  <si>
     <t>CAFG1112</t>
   </si>
   <si>
@@ -4060,12 +4060,12 @@
     <t>2011+ Kenya Emergency Humanitarian Response Plan</t>
   </si>
   <si>
+    <t>2011-01-01</t>
+  </si>
+  <si>
     <t>2011</t>
   </si>
   <si>
-    <t>2011-01-01</t>
-  </si>
-  <si>
     <t>CAFG11</t>
   </si>
   <si>
@@ -4255,15 +4255,15 @@
     <t>Afghanistan Humanitarian Action Plan 2010</t>
   </si>
   <si>
+    <t>2010-12-31</t>
+  </si>
+  <si>
+    <t>2010-01-01</t>
+  </si>
+  <si>
     <t>2010</t>
   </si>
   <si>
-    <t>2010-12-31</t>
-  </si>
-  <si>
-    <t>2010-01-01</t>
-  </si>
-  <si>
     <t>OBFA1011</t>
   </si>
   <si>
@@ -4465,15 +4465,15 @@
     <t>Afghanistan Humanitarian Action Plan 2009</t>
   </si>
   <si>
+    <t>2009-12-31</t>
+  </si>
+  <si>
+    <t>2009-01-01</t>
+  </si>
+  <si>
     <t>2009</t>
   </si>
   <si>
-    <t>2009-12-31</t>
-  </si>
-  <si>
-    <t>2009-01-01</t>
-  </si>
-  <si>
     <t>FBFA0910</t>
   </si>
   <si>
@@ -4681,15 +4681,15 @@
     <t>Afghanistan Joint Appeal 2008: Humanitarian Consequences of Rise in Food Prices (February - June 2008)</t>
   </si>
   <si>
+    <t>2008-06-30</t>
+  </si>
+  <si>
+    <t>2008-02-01</t>
+  </si>
+  <si>
     <t>2008</t>
   </si>
   <si>
-    <t>2008-06-30</t>
-  </si>
-  <si>
-    <t>2008-02-01</t>
-  </si>
-  <si>
     <t>OAFG0809</t>
   </si>
   <si>
@@ -4948,15 +4948,15 @@
     <t>Bolivia Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2007-08-21</t>
+  </si>
+  <si>
+    <t>2007-02-22</t>
+  </si>
+  <si>
     <t>2007</t>
   </si>
   <si>
-    <t>2007-08-21</t>
-  </si>
-  <si>
-    <t>2007-02-22</t>
-  </si>
-  <si>
     <t>FBFA0708</t>
   </si>
   <si>
@@ -5254,15 +5254,15 @@
     <t>Afghanistan Drought Joint Appeal 2006</t>
   </si>
   <si>
+    <t>2006-12-31</t>
+  </si>
+  <si>
+    <t>2006-07-01</t>
+  </si>
+  <si>
     <t>2006</t>
   </si>
   <si>
-    <t>2006-12-31</t>
-  </si>
-  <si>
-    <t>2006-07-01</t>
-  </si>
-  <si>
     <t>CBDI06</t>
   </si>
   <si>
@@ -5509,15 +5509,15 @@
     <t>Angola Marburg VHF 2005</t>
   </si>
   <si>
+    <t>2005-06-30</t>
+  </si>
+  <si>
+    <t>2005-04-01</t>
+  </si>
+  <si>
     <t>2005</t>
   </si>
   <si>
-    <t>2005-06-30</t>
-  </si>
-  <si>
-    <t>2005-04-01</t>
-  </si>
-  <si>
     <t>FBEN05</t>
   </si>
   <si>
@@ -5716,15 +5716,15 @@
     <t>Afghanistan UN-Government Drought Appeal 2004</t>
   </si>
   <si>
+    <t>2004-12-31</t>
+  </si>
+  <si>
+    <t>2004-09-01</t>
+  </si>
+  <si>
     <t>2004</t>
   </si>
   <si>
-    <t>2004-12-31</t>
-  </si>
-  <si>
-    <t>2004-09-01</t>
-  </si>
-  <si>
     <t>CAGO04</t>
   </si>
   <si>
@@ -5962,15 +5962,15 @@
     <t>Afghanistan TAPA 2003</t>
   </si>
   <si>
+    <t>2003-12-31</t>
+  </si>
+  <si>
+    <t>2003-01-01</t>
+  </si>
+  <si>
     <t>2003</t>
   </si>
   <si>
-    <t>2003-12-31</t>
-  </si>
-  <si>
-    <t>2003-01-01</t>
-  </si>
-  <si>
     <t>CAGO03</t>
   </si>
   <si>
@@ -6184,15 +6184,15 @@
     <t>Afghanistan 2002 (ITAP for the Afghan People)</t>
   </si>
   <si>
+    <t>2002-12-31</t>
+  </si>
+  <si>
+    <t>2001-10-01</t>
+  </si>
+  <si>
     <t>2002</t>
   </si>
   <si>
-    <t>2002-12-31</t>
-  </si>
-  <si>
-    <t>2001-10-01</t>
-  </si>
-  <si>
     <t>CAGO02</t>
   </si>
   <si>
@@ -6370,15 +6370,15 @@
     <t>Afghanistan 2001</t>
   </si>
   <si>
+    <t>2001-09-30</t>
+  </si>
+  <si>
+    <t>2001-01-01</t>
+  </si>
+  <si>
     <t>2001</t>
   </si>
   <si>
-    <t>2001-09-30</t>
-  </si>
-  <si>
-    <t>2001-01-01</t>
-  </si>
-  <si>
     <t>CAGO01</t>
   </si>
   <si>
@@ -6520,15 +6520,15 @@
     <t>Angola 2000</t>
   </si>
   <si>
+    <t>2000-12-31</t>
+  </si>
+  <si>
+    <t>2000-01-01</t>
+  </si>
+  <si>
     <t>2000</t>
   </si>
   <si>
-    <t>2000-12-31</t>
-  </si>
-  <si>
-    <t>2000-01-01</t>
-  </si>
-  <si>
     <t>CBDI00</t>
   </si>
   <si>
@@ -6619,10 +6619,10 @@
     <t>East Timor Consolidated Inter Agency Appeal 2000</t>
   </si>
   <si>
+    <t>1999-10-01</t>
+  </si>
+  <si>
     <t>1999</t>
-  </si>
-  <si>
-    <t>1999-10-01</t>
   </si>
   <si>
     <t>CRUS9900</t>
@@ -7055,10 +7055,10 @@
         <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F4" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G4" t="s">
         <v>13</v>
@@ -7285,10 +7285,10 @@
         <v>34</v>
       </c>
       <c r="E14" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F14" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G14" t="s">
         <v>13</v>
@@ -7308,10 +7308,10 @@
         <v>34</v>
       </c>
       <c r="E15" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="F15" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="G15" t="s">
         <v>13</v>
@@ -7354,10 +7354,10 @@
         <v>34</v>
       </c>
       <c r="E17" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="F17" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="G17" t="s">
         <v>13</v>
@@ -7400,10 +7400,10 @@
         <v>34</v>
       </c>
       <c r="E19" t="s">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="F19" t="s">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="G19" t="s">
         <v>13</v>
@@ -7426,10 +7426,10 @@
         <v>11</v>
       </c>
       <c r="F20" t="s">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="G20" t="s">
-        <v>58</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -7515,10 +7515,10 @@
         <v>19</v>
       </c>
       <c r="E24" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="F24" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="G24" t="s">
         <v>13</v>
@@ -7748,10 +7748,10 @@
         <v>11</v>
       </c>
       <c r="F34" t="s">
-        <v>12</v>
+        <v>88</v>
       </c>
       <c r="G34" t="s">
-        <v>88</v>
+        <v>13</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -7929,10 +7929,10 @@
         <v>19</v>
       </c>
       <c r="E42" t="s">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="F42" t="s">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="G42" t="s">
         <v>13</v>
@@ -7975,10 +7975,10 @@
         <v>34</v>
       </c>
       <c r="E44" t="s">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="F44" t="s">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="G44" t="s">
         <v>13</v>
@@ -7998,10 +7998,10 @@
         <v>34</v>
       </c>
       <c r="E45" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="F45" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="G45" t="s">
         <v>13</v>
@@ -8070,10 +8070,10 @@
         <v>113</v>
       </c>
       <c r="F48" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="G48" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -8116,10 +8116,10 @@
         <v>113</v>
       </c>
       <c r="F50" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="G50" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -8277,10 +8277,10 @@
         <v>113</v>
       </c>
       <c r="F57" t="s">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="G57" t="s">
-        <v>140</v>
+        <v>115</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -8369,10 +8369,10 @@
         <v>113</v>
       </c>
       <c r="F61" t="s">
-        <v>114</v>
+        <v>149</v>
       </c>
       <c r="G61" t="s">
-        <v>149</v>
+        <v>115</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -8392,10 +8392,10 @@
         <v>113</v>
       </c>
       <c r="F62" t="s">
-        <v>114</v>
+        <v>149</v>
       </c>
       <c r="G62" t="s">
-        <v>149</v>
+        <v>115</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -8412,10 +8412,10 @@
         <v>34</v>
       </c>
       <c r="E63" t="s">
-        <v>113</v>
+        <v>154</v>
       </c>
       <c r="F63" t="s">
-        <v>154</v>
+        <v>114</v>
       </c>
       <c r="G63" t="s">
         <v>115</v>
@@ -8435,10 +8435,10 @@
         <v>34</v>
       </c>
       <c r="E64" t="s">
-        <v>113</v>
+        <v>157</v>
       </c>
       <c r="F64" t="s">
-        <v>157</v>
+        <v>114</v>
       </c>
       <c r="G64" t="s">
         <v>115</v>
@@ -8461,10 +8461,10 @@
         <v>113</v>
       </c>
       <c r="F65" t="s">
-        <v>114</v>
+        <v>160</v>
       </c>
       <c r="G65" t="s">
-        <v>160</v>
+        <v>115</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -8504,13 +8504,13 @@
         <v>19</v>
       </c>
       <c r="E67" t="s">
-        <v>113</v>
+        <v>157</v>
       </c>
       <c r="F67" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="G67" t="s">
-        <v>165</v>
+        <v>115</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -8530,10 +8530,10 @@
         <v>113</v>
       </c>
       <c r="F68" t="s">
-        <v>114</v>
+        <v>168</v>
       </c>
       <c r="G68" t="s">
-        <v>168</v>
+        <v>115</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -8599,10 +8599,10 @@
         <v>113</v>
       </c>
       <c r="F71" t="s">
-        <v>114</v>
+        <v>175</v>
       </c>
       <c r="G71" t="s">
-        <v>175</v>
+        <v>115</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -8668,10 +8668,10 @@
         <v>113</v>
       </c>
       <c r="F74" t="s">
-        <v>114</v>
+        <v>182</v>
       </c>
       <c r="G74" t="s">
-        <v>182</v>
+        <v>115</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -8806,10 +8806,10 @@
         <v>113</v>
       </c>
       <c r="F80" t="s">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="G80" t="s">
-        <v>140</v>
+        <v>115</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -9105,10 +9105,10 @@
         <v>113</v>
       </c>
       <c r="F93" t="s">
-        <v>114</v>
+        <v>222</v>
       </c>
       <c r="G93" t="s">
-        <v>222</v>
+        <v>115</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -9151,10 +9151,10 @@
         <v>113</v>
       </c>
       <c r="F95" t="s">
-        <v>114</v>
+        <v>227</v>
       </c>
       <c r="G95" t="s">
-        <v>227</v>
+        <v>115</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -9174,10 +9174,10 @@
         <v>113</v>
       </c>
       <c r="F96" t="s">
-        <v>114</v>
+        <v>227</v>
       </c>
       <c r="G96" t="s">
-        <v>227</v>
+        <v>115</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -9381,10 +9381,10 @@
         <v>232</v>
       </c>
       <c r="F105" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="G105" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -9565,10 +9565,10 @@
         <v>232</v>
       </c>
       <c r="F113" t="s">
-        <v>233</v>
+        <v>268</v>
       </c>
       <c r="G113" t="s">
-        <v>268</v>
+        <v>234</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -9631,13 +9631,13 @@
         <v>19</v>
       </c>
       <c r="E116" t="s">
-        <v>232</v>
+        <v>275</v>
       </c>
       <c r="F116" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G116" t="s">
-        <v>276</v>
+        <v>234</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -9654,13 +9654,13 @@
         <v>19</v>
       </c>
       <c r="E117" t="s">
-        <v>232</v>
+        <v>279</v>
       </c>
       <c r="F117" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G117" t="s">
-        <v>280</v>
+        <v>234</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -9769,10 +9769,10 @@
         <v>25</v>
       </c>
       <c r="E122" t="s">
-        <v>232</v>
+        <v>279</v>
       </c>
       <c r="F122" t="s">
-        <v>279</v>
+        <v>233</v>
       </c>
       <c r="G122" t="s">
         <v>234</v>
@@ -9792,10 +9792,10 @@
         <v>19</v>
       </c>
       <c r="E123" t="s">
-        <v>232</v>
+        <v>275</v>
       </c>
       <c r="F123" t="s">
-        <v>275</v>
+        <v>233</v>
       </c>
       <c r="G123" t="s">
         <v>234</v>
@@ -9999,13 +9999,13 @@
         <v>16</v>
       </c>
       <c r="E132" t="s">
-        <v>232</v>
+        <v>310</v>
       </c>
       <c r="F132" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G132" t="s">
-        <v>311</v>
+        <v>234</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -10045,13 +10045,13 @@
         <v>34</v>
       </c>
       <c r="E134" t="s">
-        <v>232</v>
+        <v>275</v>
       </c>
       <c r="F134" t="s">
-        <v>275</v>
+        <v>316</v>
       </c>
       <c r="G134" t="s">
-        <v>316</v>
+        <v>234</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -10091,13 +10091,13 @@
         <v>34</v>
       </c>
       <c r="E136" t="s">
-        <v>232</v>
+        <v>275</v>
       </c>
       <c r="F136" t="s">
-        <v>275</v>
+        <v>321</v>
       </c>
       <c r="G136" t="s">
-        <v>321</v>
+        <v>234</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -10436,13 +10436,13 @@
         <v>19</v>
       </c>
       <c r="E151" t="s">
-        <v>338</v>
+        <v>355</v>
       </c>
       <c r="F151" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G151" t="s">
-        <v>356</v>
+        <v>340</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -10551,13 +10551,13 @@
         <v>34</v>
       </c>
       <c r="E156" t="s">
-        <v>338</v>
+        <v>367</v>
       </c>
       <c r="F156" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="G156" t="s">
-        <v>368</v>
+        <v>340</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -10577,10 +10577,10 @@
         <v>338</v>
       </c>
       <c r="F157" t="s">
-        <v>339</v>
+        <v>368</v>
       </c>
       <c r="G157" t="s">
-        <v>368</v>
+        <v>340</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -10666,10 +10666,10 @@
         <v>34</v>
       </c>
       <c r="E161" t="s">
-        <v>338</v>
+        <v>379</v>
       </c>
       <c r="F161" t="s">
-        <v>379</v>
+        <v>339</v>
       </c>
       <c r="G161" t="s">
         <v>340</v>
@@ -10758,13 +10758,13 @@
         <v>34</v>
       </c>
       <c r="E165" t="s">
-        <v>338</v>
+        <v>388</v>
       </c>
       <c r="F165" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G165" t="s">
-        <v>389</v>
+        <v>340</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -10804,13 +10804,13 @@
         <v>34</v>
       </c>
       <c r="E167" t="s">
-        <v>338</v>
+        <v>394</v>
       </c>
       <c r="F167" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="G167" t="s">
-        <v>395</v>
+        <v>340</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -10945,10 +10945,10 @@
         <v>338</v>
       </c>
       <c r="F173" t="s">
-        <v>339</v>
+        <v>408</v>
       </c>
       <c r="G173" t="s">
-        <v>408</v>
+        <v>340</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -10965,13 +10965,13 @@
         <v>19</v>
       </c>
       <c r="E174" t="s">
-        <v>338</v>
+        <v>410</v>
       </c>
       <c r="F174" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="G174" t="s">
-        <v>408</v>
+        <v>340</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -10988,13 +10988,13 @@
         <v>19</v>
       </c>
       <c r="E175" t="s">
-        <v>338</v>
+        <v>413</v>
       </c>
       <c r="F175" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G175" t="s">
-        <v>414</v>
+        <v>340</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -11175,10 +11175,10 @@
         <v>338</v>
       </c>
       <c r="F183" t="s">
-        <v>339</v>
+        <v>431</v>
       </c>
       <c r="G183" t="s">
-        <v>431</v>
+        <v>340</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -11290,10 +11290,10 @@
         <v>338</v>
       </c>
       <c r="F188" t="s">
-        <v>339</v>
+        <v>442</v>
       </c>
       <c r="G188" t="s">
-        <v>442</v>
+        <v>340</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -11333,13 +11333,13 @@
         <v>16</v>
       </c>
       <c r="E190" t="s">
-        <v>338</v>
+        <v>447</v>
       </c>
       <c r="F190" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="G190" t="s">
-        <v>442</v>
+        <v>340</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -11428,10 +11428,10 @@
         <v>454</v>
       </c>
       <c r="F194" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="G194" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -11451,10 +11451,10 @@
         <v>454</v>
       </c>
       <c r="F195" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="G195" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -11474,10 +11474,10 @@
         <v>454</v>
       </c>
       <c r="F196" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="G196" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -11497,10 +11497,10 @@
         <v>454</v>
       </c>
       <c r="F197" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="G197" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -11520,10 +11520,10 @@
         <v>454</v>
       </c>
       <c r="F198" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="G198" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -11543,10 +11543,10 @@
         <v>454</v>
       </c>
       <c r="F199" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="G199" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -11566,10 +11566,10 @@
         <v>454</v>
       </c>
       <c r="F200" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="G200" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -11589,10 +11589,10 @@
         <v>454</v>
       </c>
       <c r="F201" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="G201" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -11612,10 +11612,10 @@
         <v>454</v>
       </c>
       <c r="F202" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="G202" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -11635,10 +11635,10 @@
         <v>454</v>
       </c>
       <c r="F203" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="G203" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -11658,10 +11658,10 @@
         <v>454</v>
       </c>
       <c r="F204" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="G204" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -11681,10 +11681,10 @@
         <v>454</v>
       </c>
       <c r="F205" t="s">
-        <v>455</v>
+        <v>482</v>
       </c>
       <c r="G205" t="s">
-        <v>482</v>
+        <v>456</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -11701,13 +11701,13 @@
         <v>25</v>
       </c>
       <c r="E206" t="s">
-        <v>454</v>
+        <v>338</v>
       </c>
       <c r="F206" t="s">
-        <v>339</v>
+        <v>482</v>
       </c>
       <c r="G206" t="s">
-        <v>482</v>
+        <v>456</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -11724,13 +11724,13 @@
         <v>34</v>
       </c>
       <c r="E207" t="s">
-        <v>454</v>
+        <v>487</v>
       </c>
       <c r="F207" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="G207" t="s">
-        <v>488</v>
+        <v>456</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -11750,10 +11750,10 @@
         <v>454</v>
       </c>
       <c r="F208" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="G208" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -11773,10 +11773,10 @@
         <v>454</v>
       </c>
       <c r="F209" t="s">
-        <v>455</v>
+        <v>482</v>
       </c>
       <c r="G209" t="s">
-        <v>482</v>
+        <v>456</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -11793,13 +11793,13 @@
         <v>25</v>
       </c>
       <c r="E210" t="s">
-        <v>454</v>
+        <v>338</v>
       </c>
       <c r="F210" t="s">
-        <v>339</v>
+        <v>482</v>
       </c>
       <c r="G210" t="s">
-        <v>482</v>
+        <v>456</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -11816,13 +11816,13 @@
         <v>34</v>
       </c>
       <c r="E211" t="s">
-        <v>454</v>
+        <v>497</v>
       </c>
       <c r="F211" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="G211" t="s">
-        <v>498</v>
+        <v>456</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -11842,10 +11842,10 @@
         <v>454</v>
       </c>
       <c r="F212" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="G212" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -11862,13 +11862,13 @@
         <v>34</v>
       </c>
       <c r="E213" t="s">
-        <v>454</v>
+        <v>503</v>
       </c>
       <c r="F213" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="G213" t="s">
-        <v>504</v>
+        <v>456</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -11888,10 +11888,10 @@
         <v>454</v>
       </c>
       <c r="F214" t="s">
-        <v>455</v>
+        <v>482</v>
       </c>
       <c r="G214" t="s">
-        <v>482</v>
+        <v>456</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -11908,13 +11908,13 @@
         <v>25</v>
       </c>
       <c r="E215" t="s">
-        <v>454</v>
+        <v>338</v>
       </c>
       <c r="F215" t="s">
-        <v>339</v>
+        <v>482</v>
       </c>
       <c r="G215" t="s">
-        <v>482</v>
+        <v>456</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -11934,10 +11934,10 @@
         <v>454</v>
       </c>
       <c r="F216" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="G216" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -11957,10 +11957,10 @@
         <v>454</v>
       </c>
       <c r="F217" t="s">
-        <v>455</v>
+        <v>513</v>
       </c>
       <c r="G217" t="s">
-        <v>513</v>
+        <v>456</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -11977,13 +11977,13 @@
         <v>19</v>
       </c>
       <c r="E218" t="s">
-        <v>454</v>
+        <v>516</v>
       </c>
       <c r="F218" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="G218" t="s">
-        <v>517</v>
+        <v>456</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -12003,10 +12003,10 @@
         <v>454</v>
       </c>
       <c r="F219" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="G219" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -12023,13 +12023,13 @@
         <v>34</v>
       </c>
       <c r="E220" t="s">
-        <v>454</v>
+        <v>388</v>
       </c>
       <c r="F220" t="s">
-        <v>388</v>
+        <v>459</v>
       </c>
       <c r="G220" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -12049,10 +12049,10 @@
         <v>454</v>
       </c>
       <c r="F221" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="G221" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -12072,10 +12072,10 @@
         <v>454</v>
       </c>
       <c r="F222" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="G222" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -12095,10 +12095,10 @@
         <v>454</v>
       </c>
       <c r="F223" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="G223" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -12118,10 +12118,10 @@
         <v>454</v>
       </c>
       <c r="F224" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="G224" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -12141,10 +12141,10 @@
         <v>454</v>
       </c>
       <c r="F225" t="s">
-        <v>455</v>
+        <v>532</v>
       </c>
       <c r="G225" t="s">
-        <v>532</v>
+        <v>456</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -12164,10 +12164,10 @@
         <v>454</v>
       </c>
       <c r="F226" t="s">
-        <v>455</v>
+        <v>535</v>
       </c>
       <c r="G226" t="s">
-        <v>535</v>
+        <v>456</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -12187,10 +12187,10 @@
         <v>454</v>
       </c>
       <c r="F227" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="G227" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -12210,10 +12210,10 @@
         <v>454</v>
       </c>
       <c r="F228" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="G228" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -12233,10 +12233,10 @@
         <v>454</v>
       </c>
       <c r="F229" t="s">
-        <v>455</v>
+        <v>535</v>
       </c>
       <c r="G229" t="s">
-        <v>535</v>
+        <v>456</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -12256,10 +12256,10 @@
         <v>454</v>
       </c>
       <c r="F230" t="s">
-        <v>455</v>
+        <v>535</v>
       </c>
       <c r="G230" t="s">
-        <v>535</v>
+        <v>456</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -12279,10 +12279,10 @@
         <v>454</v>
       </c>
       <c r="F231" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="G231" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -12302,10 +12302,10 @@
         <v>454</v>
       </c>
       <c r="F232" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="G232" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -12325,10 +12325,10 @@
         <v>454</v>
       </c>
       <c r="F233" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="G233" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="234" spans="1:7">
@@ -12348,10 +12348,10 @@
         <v>454</v>
       </c>
       <c r="F234" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="G234" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -12371,10 +12371,10 @@
         <v>454</v>
       </c>
       <c r="F235" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="G235" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -12394,10 +12394,10 @@
         <v>454</v>
       </c>
       <c r="F236" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="G236" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="237" spans="1:7">
@@ -12417,10 +12417,10 @@
         <v>454</v>
       </c>
       <c r="F237" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="G237" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="238" spans="1:7">
@@ -12440,10 +12440,10 @@
         <v>454</v>
       </c>
       <c r="F238" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="G238" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="239" spans="1:7">
@@ -12463,10 +12463,10 @@
         <v>454</v>
       </c>
       <c r="F239" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="G239" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="240" spans="1:7">
@@ -12486,10 +12486,10 @@
         <v>454</v>
       </c>
       <c r="F240" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="G240" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="241" spans="1:7">
@@ -12509,10 +12509,10 @@
         <v>454</v>
       </c>
       <c r="F241" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="G241" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="242" spans="1:7">
@@ -12532,10 +12532,10 @@
         <v>454</v>
       </c>
       <c r="F242" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="G242" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="243" spans="1:7">
@@ -12555,10 +12555,10 @@
         <v>454</v>
       </c>
       <c r="F243" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="G243" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="244" spans="1:7">
@@ -12578,10 +12578,10 @@
         <v>454</v>
       </c>
       <c r="F244" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="G244" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="245" spans="1:7">
@@ -12624,10 +12624,10 @@
         <v>573</v>
       </c>
       <c r="F246" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="G246" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -12670,10 +12670,10 @@
         <v>573</v>
       </c>
       <c r="F248" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="G248" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="249" spans="1:7">
@@ -12762,10 +12762,10 @@
         <v>573</v>
       </c>
       <c r="F252" t="s">
-        <v>574</v>
+        <v>591</v>
       </c>
       <c r="G252" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
     </row>
     <row r="253" spans="1:7">
@@ -12805,13 +12805,13 @@
         <v>25</v>
       </c>
       <c r="E254" t="s">
-        <v>573</v>
+        <v>459</v>
       </c>
       <c r="F254" t="s">
-        <v>459</v>
+        <v>596</v>
       </c>
       <c r="G254" t="s">
-        <v>596</v>
+        <v>575</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -12877,10 +12877,10 @@
         <v>573</v>
       </c>
       <c r="F257" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="G257" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="258" spans="1:7">
@@ -12900,10 +12900,10 @@
         <v>573</v>
       </c>
       <c r="F258" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="G258" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="259" spans="1:7">
@@ -12923,10 +12923,10 @@
         <v>573</v>
       </c>
       <c r="F259" t="s">
-        <v>574</v>
+        <v>607</v>
       </c>
       <c r="G259" t="s">
-        <v>607</v>
+        <v>575</v>
       </c>
     </row>
     <row r="260" spans="1:7">
@@ -12989,13 +12989,13 @@
         <v>34</v>
       </c>
       <c r="E262" t="s">
-        <v>573</v>
+        <v>614</v>
       </c>
       <c r="F262" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="G262" t="s">
-        <v>615</v>
+        <v>575</v>
       </c>
     </row>
     <row r="263" spans="1:7">
@@ -13015,10 +13015,10 @@
         <v>573</v>
       </c>
       <c r="F263" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="G263" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="264" spans="1:7">
@@ -13038,10 +13038,10 @@
         <v>573</v>
       </c>
       <c r="F264" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="G264" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="265" spans="1:7">
@@ -13084,10 +13084,10 @@
         <v>573</v>
       </c>
       <c r="F266" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="G266" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="267" spans="1:7">
@@ -13130,10 +13130,10 @@
         <v>573</v>
       </c>
       <c r="F268" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="G268" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="269" spans="1:7">
@@ -13153,10 +13153,10 @@
         <v>573</v>
       </c>
       <c r="F269" t="s">
-        <v>574</v>
+        <v>607</v>
       </c>
       <c r="G269" t="s">
-        <v>607</v>
+        <v>575</v>
       </c>
     </row>
     <row r="270" spans="1:7">
@@ -13176,10 +13176,10 @@
         <v>573</v>
       </c>
       <c r="F270" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="G270" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="271" spans="1:7">
@@ -13199,10 +13199,10 @@
         <v>573</v>
       </c>
       <c r="F271" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="G271" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="272" spans="1:7">
@@ -13245,10 +13245,10 @@
         <v>573</v>
       </c>
       <c r="F273" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="G273" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="274" spans="1:7">
@@ -13291,10 +13291,10 @@
         <v>573</v>
       </c>
       <c r="F275" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="G275" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="276" spans="1:7">
@@ -13314,10 +13314,10 @@
         <v>573</v>
       </c>
       <c r="F276" t="s">
-        <v>574</v>
+        <v>644</v>
       </c>
       <c r="G276" t="s">
-        <v>644</v>
+        <v>575</v>
       </c>
     </row>
     <row r="277" spans="1:7">
@@ -13334,13 +13334,13 @@
         <v>34</v>
       </c>
       <c r="E277" t="s">
-        <v>573</v>
+        <v>647</v>
       </c>
       <c r="F277" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="G277" t="s">
-        <v>648</v>
+        <v>575</v>
       </c>
     </row>
     <row r="278" spans="1:7">
@@ -13360,10 +13360,10 @@
         <v>573</v>
       </c>
       <c r="F278" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="G278" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="279" spans="1:7">
@@ -13380,13 +13380,13 @@
         <v>34</v>
       </c>
       <c r="E279" t="s">
-        <v>573</v>
+        <v>653</v>
       </c>
       <c r="F279" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="G279" t="s">
-        <v>654</v>
+        <v>575</v>
       </c>
     </row>
     <row r="280" spans="1:7">
@@ -13406,10 +13406,10 @@
         <v>573</v>
       </c>
       <c r="F280" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="G280" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="281" spans="1:7">
@@ -13475,10 +13475,10 @@
         <v>573</v>
       </c>
       <c r="F283" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="G283" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="284" spans="1:7">
@@ -13590,10 +13590,10 @@
         <v>573</v>
       </c>
       <c r="F288" t="s">
-        <v>574</v>
+        <v>644</v>
       </c>
       <c r="G288" t="s">
-        <v>644</v>
+        <v>575</v>
       </c>
     </row>
     <row r="289" spans="1:7">
@@ -13613,10 +13613,10 @@
         <v>573</v>
       </c>
       <c r="F289" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="G289" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="290" spans="1:7">
@@ -13682,10 +13682,10 @@
         <v>573</v>
       </c>
       <c r="F292" t="s">
-        <v>574</v>
+        <v>644</v>
       </c>
       <c r="G292" t="s">
-        <v>644</v>
+        <v>575</v>
       </c>
     </row>
     <row r="293" spans="1:7">
@@ -13705,10 +13705,10 @@
         <v>573</v>
       </c>
       <c r="F293" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="G293" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="294" spans="1:7">
@@ -13866,10 +13866,10 @@
         <v>573</v>
       </c>
       <c r="F300" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="G300" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="301" spans="1:7">
@@ -13889,10 +13889,10 @@
         <v>573</v>
       </c>
       <c r="F301" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="G301" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="302" spans="1:7">
@@ -13912,10 +13912,10 @@
         <v>573</v>
       </c>
       <c r="F302" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="G302" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="303" spans="1:7">
@@ -13958,10 +13958,10 @@
         <v>573</v>
       </c>
       <c r="F304" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="G304" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="305" spans="1:7">
@@ -14024,13 +14024,13 @@
         <v>19</v>
       </c>
       <c r="E307" t="s">
-        <v>573</v>
+        <v>614</v>
       </c>
       <c r="F307" t="s">
-        <v>614</v>
+        <v>711</v>
       </c>
       <c r="G307" t="s">
-        <v>711</v>
+        <v>575</v>
       </c>
     </row>
     <row r="308" spans="1:7">
@@ -14050,10 +14050,10 @@
         <v>573</v>
       </c>
       <c r="F308" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="G308" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="309" spans="1:7">
@@ -14395,10 +14395,10 @@
         <v>718</v>
       </c>
       <c r="F323" t="s">
-        <v>719</v>
+        <v>747</v>
       </c>
       <c r="G323" t="s">
-        <v>747</v>
+        <v>720</v>
       </c>
     </row>
     <row r="324" spans="1:7">
@@ -14438,10 +14438,10 @@
         <v>34</v>
       </c>
       <c r="E325" t="s">
-        <v>718</v>
+        <v>752</v>
       </c>
       <c r="F325" t="s">
-        <v>752</v>
+        <v>719</v>
       </c>
       <c r="G325" t="s">
         <v>720</v>
@@ -14576,10 +14576,10 @@
         <v>25</v>
       </c>
       <c r="E331" t="s">
-        <v>718</v>
+        <v>765</v>
       </c>
       <c r="F331" t="s">
-        <v>765</v>
+        <v>719</v>
       </c>
       <c r="G331" t="s">
         <v>720</v>
@@ -14852,13 +14852,13 @@
         <v>34</v>
       </c>
       <c r="E343" t="s">
-        <v>718</v>
+        <v>790</v>
       </c>
       <c r="F343" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="G343" t="s">
-        <v>791</v>
+        <v>720</v>
       </c>
     </row>
     <row r="344" spans="1:7">
@@ -14875,13 +14875,13 @@
         <v>34</v>
       </c>
       <c r="E344" t="s">
-        <v>718</v>
+        <v>790</v>
       </c>
       <c r="F344" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="G344" t="s">
-        <v>794</v>
+        <v>720</v>
       </c>
     </row>
     <row r="345" spans="1:7">
@@ -14924,10 +14924,10 @@
         <v>797</v>
       </c>
       <c r="F346" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="G346" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
     </row>
     <row r="347" spans="1:7">
@@ -15154,10 +15154,10 @@
         <v>797</v>
       </c>
       <c r="F356" t="s">
-        <v>798</v>
+        <v>823</v>
       </c>
       <c r="G356" t="s">
-        <v>823</v>
+        <v>799</v>
       </c>
     </row>
     <row r="357" spans="1:7">
@@ -15384,10 +15384,10 @@
         <v>797</v>
       </c>
       <c r="F366" t="s">
-        <v>798</v>
+        <v>844</v>
       </c>
       <c r="G366" t="s">
-        <v>844</v>
+        <v>799</v>
       </c>
     </row>
     <row r="367" spans="1:7">
@@ -15407,10 +15407,10 @@
         <v>797</v>
       </c>
       <c r="F367" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="G367" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
     </row>
     <row r="368" spans="1:7">
@@ -15496,10 +15496,10 @@
         <v>25</v>
       </c>
       <c r="E371" t="s">
-        <v>797</v>
+        <v>855</v>
       </c>
       <c r="F371" t="s">
-        <v>855</v>
+        <v>798</v>
       </c>
       <c r="G371" t="s">
         <v>799</v>
@@ -15519,13 +15519,13 @@
         <v>25</v>
       </c>
       <c r="E372" t="s">
-        <v>797</v>
+        <v>858</v>
       </c>
       <c r="F372" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="G372" t="s">
-        <v>859</v>
+        <v>799</v>
       </c>
     </row>
     <row r="373" spans="1:7">
@@ -15565,13 +15565,13 @@
         <v>25</v>
       </c>
       <c r="E374" t="s">
-        <v>797</v>
+        <v>858</v>
       </c>
       <c r="F374" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="G374" t="s">
-        <v>859</v>
+        <v>799</v>
       </c>
     </row>
     <row r="375" spans="1:7">
@@ -15706,10 +15706,10 @@
         <v>872</v>
       </c>
       <c r="F380" t="s">
-        <v>873</v>
+        <v>879</v>
       </c>
       <c r="G380" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
     </row>
     <row r="381" spans="1:7">
@@ -15844,10 +15844,10 @@
         <v>872</v>
       </c>
       <c r="F386" t="s">
-        <v>873</v>
+        <v>892</v>
       </c>
       <c r="G386" t="s">
-        <v>892</v>
+        <v>874</v>
       </c>
     </row>
     <row r="387" spans="1:7">
@@ -15867,10 +15867,10 @@
         <v>872</v>
       </c>
       <c r="F387" t="s">
-        <v>873</v>
+        <v>895</v>
       </c>
       <c r="G387" t="s">
-        <v>895</v>
+        <v>874</v>
       </c>
     </row>
     <row r="388" spans="1:7">
@@ -15910,13 +15910,13 @@
         <v>34</v>
       </c>
       <c r="E389" t="s">
-        <v>872</v>
+        <v>900</v>
       </c>
       <c r="F389" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="G389" t="s">
-        <v>901</v>
+        <v>874</v>
       </c>
     </row>
     <row r="390" spans="1:7">
@@ -16005,10 +16005,10 @@
         <v>872</v>
       </c>
       <c r="F393" t="s">
-        <v>873</v>
+        <v>910</v>
       </c>
       <c r="G393" t="s">
-        <v>910</v>
+        <v>874</v>
       </c>
     </row>
     <row r="394" spans="1:7">
@@ -16048,13 +16048,13 @@
         <v>34</v>
       </c>
       <c r="E395" t="s">
-        <v>872</v>
+        <v>915</v>
       </c>
       <c r="F395" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="G395" t="s">
-        <v>916</v>
+        <v>874</v>
       </c>
     </row>
     <row r="396" spans="1:7">
@@ -16094,13 +16094,13 @@
         <v>34</v>
       </c>
       <c r="E397" t="s">
-        <v>872</v>
+        <v>921</v>
       </c>
       <c r="F397" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="G397" t="s">
-        <v>922</v>
+        <v>874</v>
       </c>
     </row>
     <row r="398" spans="1:7">
@@ -16163,13 +16163,13 @@
         <v>34</v>
       </c>
       <c r="E400" t="s">
-        <v>872</v>
+        <v>929</v>
       </c>
       <c r="F400" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="G400" t="s">
-        <v>930</v>
+        <v>874</v>
       </c>
     </row>
     <row r="401" spans="1:7">
@@ -16301,13 +16301,13 @@
         <v>34</v>
       </c>
       <c r="E406" t="s">
-        <v>872</v>
+        <v>943</v>
       </c>
       <c r="F406" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="G406" t="s">
-        <v>944</v>
+        <v>874</v>
       </c>
     </row>
     <row r="407" spans="1:7">
@@ -16327,10 +16327,10 @@
         <v>872</v>
       </c>
       <c r="F407" t="s">
-        <v>873</v>
+        <v>947</v>
       </c>
       <c r="G407" t="s">
-        <v>947</v>
+        <v>874</v>
       </c>
     </row>
     <row r="408" spans="1:7">
@@ -16603,10 +16603,10 @@
         <v>967</v>
       </c>
       <c r="F419" t="s">
-        <v>968</v>
+        <v>974</v>
       </c>
       <c r="G419" t="s">
-        <v>974</v>
+        <v>969</v>
       </c>
     </row>
     <row r="420" spans="1:7">
@@ -16649,10 +16649,10 @@
         <v>967</v>
       </c>
       <c r="F421" t="s">
-        <v>968</v>
+        <v>979</v>
       </c>
       <c r="G421" t="s">
-        <v>979</v>
+        <v>969</v>
       </c>
     </row>
     <row r="422" spans="1:7">
@@ -16807,13 +16807,13 @@
         <v>34</v>
       </c>
       <c r="E428" t="s">
-        <v>967</v>
+        <v>994</v>
       </c>
       <c r="F428" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="G428" t="s">
-        <v>995</v>
+        <v>969</v>
       </c>
     </row>
     <row r="429" spans="1:7">
@@ -16830,13 +16830,13 @@
         <v>34</v>
       </c>
       <c r="E429" t="s">
-        <v>967</v>
+        <v>998</v>
       </c>
       <c r="F429" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="G429" t="s">
-        <v>999</v>
+        <v>969</v>
       </c>
     </row>
     <row r="430" spans="1:7">
@@ -16925,10 +16925,10 @@
         <v>967</v>
       </c>
       <c r="F433" t="s">
-        <v>968</v>
+        <v>1008</v>
       </c>
       <c r="G433" t="s">
-        <v>1008</v>
+        <v>969</v>
       </c>
     </row>
     <row r="434" spans="1:7">
@@ -16994,10 +16994,10 @@
         <v>967</v>
       </c>
       <c r="F436" t="s">
-        <v>968</v>
+        <v>1015</v>
       </c>
       <c r="G436" t="s">
-        <v>1015</v>
+        <v>969</v>
       </c>
     </row>
     <row r="437" spans="1:7">
@@ -17017,10 +17017,10 @@
         <v>967</v>
       </c>
       <c r="F437" t="s">
-        <v>968</v>
+        <v>1018</v>
       </c>
       <c r="G437" t="s">
-        <v>1018</v>
+        <v>969</v>
       </c>
     </row>
     <row r="438" spans="1:7">
@@ -17083,13 +17083,13 @@
         <v>34</v>
       </c>
       <c r="E440" t="s">
-        <v>967</v>
+        <v>1025</v>
       </c>
       <c r="F440" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="G440" t="s">
-        <v>1026</v>
+        <v>969</v>
       </c>
     </row>
     <row r="441" spans="1:7">
@@ -17405,13 +17405,13 @@
         <v>25</v>
       </c>
       <c r="E454" t="s">
-        <v>967</v>
+        <v>1055</v>
       </c>
       <c r="F454" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="G454" t="s">
-        <v>1056</v>
+        <v>969</v>
       </c>
     </row>
     <row r="455" spans="1:7">
@@ -17635,13 +17635,13 @@
         <v>34</v>
       </c>
       <c r="E464" t="s">
-        <v>1060</v>
+        <v>1081</v>
       </c>
       <c r="F464" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="G464" t="s">
-        <v>1082</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="465" spans="1:7">
@@ -17661,10 +17661,10 @@
         <v>1060</v>
       </c>
       <c r="F465" t="s">
-        <v>1061</v>
+        <v>1085</v>
       </c>
       <c r="G465" t="s">
-        <v>1085</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="466" spans="1:7">
@@ -17681,13 +17681,13 @@
         <v>34</v>
       </c>
       <c r="E466" t="s">
-        <v>1060</v>
+        <v>1081</v>
       </c>
       <c r="F466" t="s">
-        <v>1081</v>
+        <v>1088</v>
       </c>
       <c r="G466" t="s">
-        <v>1088</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="467" spans="1:7">
@@ -17704,13 +17704,13 @@
         <v>34</v>
       </c>
       <c r="E467" t="s">
-        <v>1060</v>
+        <v>1091</v>
       </c>
       <c r="F467" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="G467" t="s">
-        <v>1092</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="468" spans="1:7">
@@ -17750,13 +17750,13 @@
         <v>34</v>
       </c>
       <c r="E469" t="s">
-        <v>1060</v>
+        <v>1097</v>
       </c>
       <c r="F469" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="G469" t="s">
-        <v>1098</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="470" spans="1:7">
@@ -17842,13 +17842,13 @@
         <v>34</v>
       </c>
       <c r="E473" t="s">
-        <v>1060</v>
+        <v>1081</v>
       </c>
       <c r="F473" t="s">
-        <v>1081</v>
+        <v>1107</v>
       </c>
       <c r="G473" t="s">
-        <v>1107</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="474" spans="1:7">
@@ -18190,10 +18190,10 @@
         <v>1136</v>
       </c>
       <c r="F488" t="s">
-        <v>1137</v>
+        <v>1141</v>
       </c>
       <c r="G488" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="489" spans="1:7">
@@ -18279,10 +18279,10 @@
         <v>25</v>
       </c>
       <c r="E492" t="s">
-        <v>1136</v>
+        <v>1150</v>
       </c>
       <c r="F492" t="s">
-        <v>1150</v>
+        <v>1137</v>
       </c>
       <c r="G492" t="s">
         <v>1138</v>
@@ -18325,13 +18325,13 @@
         <v>16</v>
       </c>
       <c r="E494" t="s">
-        <v>1136</v>
+        <v>1155</v>
       </c>
       <c r="F494" t="s">
-        <v>1155</v>
+        <v>1098</v>
       </c>
       <c r="G494" t="s">
-        <v>1098</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="495" spans="1:7">
@@ -18348,13 +18348,13 @@
         <v>19</v>
       </c>
       <c r="E495" t="s">
-        <v>1136</v>
+        <v>1155</v>
       </c>
       <c r="F495" t="s">
-        <v>1155</v>
+        <v>1098</v>
       </c>
       <c r="G495" t="s">
-        <v>1098</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="496" spans="1:7">
@@ -18420,10 +18420,10 @@
         <v>1136</v>
       </c>
       <c r="F498" t="s">
-        <v>1137</v>
+        <v>1164</v>
       </c>
       <c r="G498" t="s">
-        <v>1164</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="499" spans="1:7">
@@ -18512,10 +18512,10 @@
         <v>1136</v>
       </c>
       <c r="F502" t="s">
-        <v>1137</v>
+        <v>1173</v>
       </c>
       <c r="G502" t="s">
-        <v>1173</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="503" spans="1:7">
@@ -18624,13 +18624,13 @@
         <v>34</v>
       </c>
       <c r="E507" t="s">
-        <v>1136</v>
+        <v>1184</v>
       </c>
       <c r="F507" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="G507" t="s">
-        <v>1185</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="508" spans="1:7">
@@ -18647,13 +18647,13 @@
         <v>1059</v>
       </c>
       <c r="E508" t="s">
-        <v>1136</v>
+        <v>1188</v>
       </c>
       <c r="F508" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="G508" t="s">
-        <v>1189</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="509" spans="1:7">
@@ -18670,13 +18670,13 @@
         <v>25</v>
       </c>
       <c r="E509" t="s">
-        <v>1136</v>
+        <v>1192</v>
       </c>
       <c r="F509" t="s">
-        <v>1192</v>
+        <v>1189</v>
       </c>
       <c r="G509" t="s">
-        <v>1189</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="510" spans="1:7">
@@ -18693,13 +18693,13 @@
         <v>34</v>
       </c>
       <c r="E510" t="s">
-        <v>1136</v>
+        <v>1195</v>
       </c>
       <c r="F510" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="G510" t="s">
-        <v>1196</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="511" spans="1:7">
@@ -18742,10 +18742,10 @@
         <v>1136</v>
       </c>
       <c r="F512" t="s">
-        <v>1137</v>
+        <v>1201</v>
       </c>
       <c r="G512" t="s">
-        <v>1201</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="513" spans="1:7">
@@ -18762,10 +18762,10 @@
         <v>25</v>
       </c>
       <c r="E513" t="s">
-        <v>1136</v>
+        <v>1204</v>
       </c>
       <c r="F513" t="s">
-        <v>1204</v>
+        <v>1137</v>
       </c>
       <c r="G513" t="s">
         <v>1138</v>
@@ -18949,10 +18949,10 @@
         <v>1136</v>
       </c>
       <c r="F521" t="s">
-        <v>1137</v>
+        <v>1221</v>
       </c>
       <c r="G521" t="s">
-        <v>1221</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="522" spans="1:7">
@@ -18972,10 +18972,10 @@
         <v>1136</v>
       </c>
       <c r="F522" t="s">
-        <v>1137</v>
+        <v>1224</v>
       </c>
       <c r="G522" t="s">
-        <v>1224</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="523" spans="1:7">
@@ -18995,10 +18995,10 @@
         <v>1136</v>
       </c>
       <c r="F523" t="s">
-        <v>1137</v>
+        <v>1227</v>
       </c>
       <c r="G523" t="s">
-        <v>1227</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="524" spans="1:7">
@@ -19041,10 +19041,10 @@
         <v>1233</v>
       </c>
       <c r="F525" t="s">
+        <v>1141</v>
+      </c>
+      <c r="G525" t="s">
         <v>1234</v>
-      </c>
-      <c r="G525" t="s">
-        <v>1141</v>
       </c>
     </row>
     <row r="526" spans="1:7">
@@ -19064,10 +19064,10 @@
         <v>1233</v>
       </c>
       <c r="F526" t="s">
+        <v>1141</v>
+      </c>
+      <c r="G526" t="s">
         <v>1234</v>
-      </c>
-      <c r="G526" t="s">
-        <v>1141</v>
       </c>
     </row>
     <row r="527" spans="1:7">
@@ -19087,10 +19087,10 @@
         <v>1233</v>
       </c>
       <c r="F527" t="s">
+        <v>1141</v>
+      </c>
+      <c r="G527" t="s">
         <v>1234</v>
-      </c>
-      <c r="G527" t="s">
-        <v>1141</v>
       </c>
     </row>
     <row r="528" spans="1:7">
@@ -19110,10 +19110,10 @@
         <v>1233</v>
       </c>
       <c r="F528" t="s">
+        <v>1141</v>
+      </c>
+      <c r="G528" t="s">
         <v>1234</v>
-      </c>
-      <c r="G528" t="s">
-        <v>1141</v>
       </c>
     </row>
     <row r="529" spans="1:7">
@@ -19133,10 +19133,10 @@
         <v>1233</v>
       </c>
       <c r="F529" t="s">
+        <v>1243</v>
+      </c>
+      <c r="G529" t="s">
         <v>1234</v>
-      </c>
-      <c r="G529" t="s">
-        <v>1243</v>
       </c>
     </row>
     <row r="530" spans="1:7">
@@ -19153,13 +19153,13 @@
         <v>1232</v>
       </c>
       <c r="E530" t="s">
-        <v>1233</v>
+        <v>1246</v>
       </c>
       <c r="F530" t="s">
-        <v>1246</v>
+        <v>1141</v>
       </c>
       <c r="G530" t="s">
-        <v>1141</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="531" spans="1:7">
@@ -19179,10 +19179,10 @@
         <v>1233</v>
       </c>
       <c r="F531" t="s">
+        <v>1141</v>
+      </c>
+      <c r="G531" t="s">
         <v>1234</v>
-      </c>
-      <c r="G531" t="s">
-        <v>1141</v>
       </c>
     </row>
     <row r="532" spans="1:7">
@@ -19202,10 +19202,10 @@
         <v>1233</v>
       </c>
       <c r="F532" t="s">
+        <v>1141</v>
+      </c>
+      <c r="G532" t="s">
         <v>1234</v>
-      </c>
-      <c r="G532" t="s">
-        <v>1141</v>
       </c>
     </row>
     <row r="533" spans="1:7">
@@ -19225,10 +19225,10 @@
         <v>1233</v>
       </c>
       <c r="F533" t="s">
+        <v>1141</v>
+      </c>
+      <c r="G533" t="s">
         <v>1234</v>
-      </c>
-      <c r="G533" t="s">
-        <v>1141</v>
       </c>
     </row>
     <row r="534" spans="1:7">
@@ -19248,10 +19248,10 @@
         <v>1233</v>
       </c>
       <c r="F534" t="s">
+        <v>1141</v>
+      </c>
+      <c r="G534" t="s">
         <v>1234</v>
-      </c>
-      <c r="G534" t="s">
-        <v>1141</v>
       </c>
     </row>
     <row r="535" spans="1:7">
@@ -19271,10 +19271,10 @@
         <v>1233</v>
       </c>
       <c r="F535" t="s">
+        <v>1141</v>
+      </c>
+      <c r="G535" t="s">
         <v>1234</v>
-      </c>
-      <c r="G535" t="s">
-        <v>1141</v>
       </c>
     </row>
     <row r="536" spans="1:7">
@@ -19294,10 +19294,10 @@
         <v>1233</v>
       </c>
       <c r="F536" t="s">
+        <v>1259</v>
+      </c>
+      <c r="G536" t="s">
         <v>1234</v>
-      </c>
-      <c r="G536" t="s">
-        <v>1259</v>
       </c>
     </row>
     <row r="537" spans="1:7">
@@ -19317,10 +19317,10 @@
         <v>1233</v>
       </c>
       <c r="F537" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G537" t="s">
         <v>1234</v>
-      </c>
-      <c r="G537" t="s">
-        <v>1262</v>
       </c>
     </row>
     <row r="538" spans="1:7">
@@ -19340,10 +19340,10 @@
         <v>1233</v>
       </c>
       <c r="F538" t="s">
+        <v>1141</v>
+      </c>
+      <c r="G538" t="s">
         <v>1234</v>
-      </c>
-      <c r="G538" t="s">
-        <v>1141</v>
       </c>
     </row>
     <row r="539" spans="1:7">
@@ -19363,10 +19363,10 @@
         <v>1233</v>
       </c>
       <c r="F539" t="s">
+        <v>1141</v>
+      </c>
+      <c r="G539" t="s">
         <v>1234</v>
-      </c>
-      <c r="G539" t="s">
-        <v>1141</v>
       </c>
     </row>
     <row r="540" spans="1:7">
@@ -19383,13 +19383,13 @@
         <v>1232</v>
       </c>
       <c r="E540" t="s">
-        <v>1233</v>
+        <v>1195</v>
       </c>
       <c r="F540" t="s">
-        <v>1195</v>
+        <v>1141</v>
       </c>
       <c r="G540" t="s">
-        <v>1141</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="541" spans="1:7">
@@ -19409,10 +19409,10 @@
         <v>1233</v>
       </c>
       <c r="F541" t="s">
+        <v>1141</v>
+      </c>
+      <c r="G541" t="s">
         <v>1234</v>
-      </c>
-      <c r="G541" t="s">
-        <v>1141</v>
       </c>
     </row>
     <row r="542" spans="1:7">
@@ -19432,10 +19432,10 @@
         <v>1233</v>
       </c>
       <c r="F542" t="s">
+        <v>1141</v>
+      </c>
+      <c r="G542" t="s">
         <v>1234</v>
-      </c>
-      <c r="G542" t="s">
-        <v>1141</v>
       </c>
     </row>
     <row r="543" spans="1:7">
@@ -19455,10 +19455,10 @@
         <v>1233</v>
       </c>
       <c r="F543" t="s">
+        <v>1141</v>
+      </c>
+      <c r="G543" t="s">
         <v>1234</v>
-      </c>
-      <c r="G543" t="s">
-        <v>1141</v>
       </c>
     </row>
     <row r="544" spans="1:7">
@@ -19478,10 +19478,10 @@
         <v>1233</v>
       </c>
       <c r="F544" t="s">
+        <v>1141</v>
+      </c>
+      <c r="G544" t="s">
         <v>1234</v>
-      </c>
-      <c r="G544" t="s">
-        <v>1141</v>
       </c>
     </row>
     <row r="545" spans="1:7">
@@ -19498,13 +19498,13 @@
         <v>16</v>
       </c>
       <c r="E545" t="s">
-        <v>1233</v>
+        <v>1279</v>
       </c>
       <c r="F545" t="s">
-        <v>1279</v>
+        <v>1141</v>
       </c>
       <c r="G545" t="s">
-        <v>1141</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="546" spans="1:7">
@@ -19524,10 +19524,10 @@
         <v>1233</v>
       </c>
       <c r="F546" t="s">
+        <v>1141</v>
+      </c>
+      <c r="G546" t="s">
         <v>1234</v>
-      </c>
-      <c r="G546" t="s">
-        <v>1141</v>
       </c>
     </row>
     <row r="547" spans="1:7">
@@ -19547,10 +19547,10 @@
         <v>1233</v>
       </c>
       <c r="F547" t="s">
+        <v>1141</v>
+      </c>
+      <c r="G547" t="s">
         <v>1234</v>
-      </c>
-      <c r="G547" t="s">
-        <v>1141</v>
       </c>
     </row>
     <row r="548" spans="1:7">
@@ -19593,10 +19593,10 @@
         <v>1286</v>
       </c>
       <c r="F549" t="s">
-        <v>1287</v>
+        <v>1291</v>
       </c>
       <c r="G549" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="550" spans="1:7">
@@ -19616,10 +19616,10 @@
         <v>1286</v>
       </c>
       <c r="F550" t="s">
-        <v>1287</v>
+        <v>1294</v>
       </c>
       <c r="G550" t="s">
-        <v>1294</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="551" spans="1:7">
@@ -19705,10 +19705,10 @@
         <v>1232</v>
       </c>
       <c r="E554" t="s">
-        <v>1286</v>
+        <v>1303</v>
       </c>
       <c r="F554" t="s">
-        <v>1303</v>
+        <v>1287</v>
       </c>
       <c r="G554" t="s">
         <v>1288</v>
@@ -19797,13 +19797,13 @@
         <v>34</v>
       </c>
       <c r="E558" t="s">
-        <v>1286</v>
+        <v>1312</v>
       </c>
       <c r="F558" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="G558" t="s">
-        <v>1313</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="559" spans="1:7">
@@ -19846,10 +19846,10 @@
         <v>1286</v>
       </c>
       <c r="F560" t="s">
-        <v>1287</v>
+        <v>1318</v>
       </c>
       <c r="G560" t="s">
-        <v>1318</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="561" spans="1:7">
@@ -19869,10 +19869,10 @@
         <v>1286</v>
       </c>
       <c r="F561" t="s">
-        <v>1287</v>
+        <v>1318</v>
       </c>
       <c r="G561" t="s">
-        <v>1318</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="562" spans="1:7">
@@ -19912,10 +19912,10 @@
         <v>19</v>
       </c>
       <c r="E563" t="s">
-        <v>1286</v>
+        <v>1325</v>
       </c>
       <c r="F563" t="s">
-        <v>1325</v>
+        <v>1287</v>
       </c>
       <c r="G563" t="s">
         <v>1288</v>
@@ -20050,13 +20050,13 @@
         <v>1232</v>
       </c>
       <c r="E569" t="s">
-        <v>1286</v>
+        <v>1338</v>
       </c>
       <c r="F569" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="G569" t="s">
-        <v>1339</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="570" spans="1:7">
@@ -20142,10 +20142,10 @@
         <v>1232</v>
       </c>
       <c r="E573" t="s">
+        <v>1233</v>
+      </c>
+      <c r="F573" t="s">
         <v>1348</v>
-      </c>
-      <c r="F573" t="s">
-        <v>1234</v>
       </c>
       <c r="G573" t="s">
         <v>1349</v>
@@ -20165,10 +20165,10 @@
         <v>1232</v>
       </c>
       <c r="E574" t="s">
+        <v>1352</v>
+      </c>
+      <c r="F574" t="s">
         <v>1348</v>
-      </c>
-      <c r="F574" t="s">
-        <v>1352</v>
       </c>
       <c r="G574" t="s">
         <v>1349</v>
@@ -20188,10 +20188,10 @@
         <v>1232</v>
       </c>
       <c r="E575" t="s">
+        <v>1352</v>
+      </c>
+      <c r="F575" t="s">
         <v>1348</v>
-      </c>
-      <c r="F575" t="s">
-        <v>1352</v>
       </c>
       <c r="G575" t="s">
         <v>1349</v>
@@ -20211,10 +20211,10 @@
         <v>1232</v>
       </c>
       <c r="E576" t="s">
+        <v>1352</v>
+      </c>
+      <c r="F576" t="s">
         <v>1348</v>
-      </c>
-      <c r="F576" t="s">
-        <v>1352</v>
       </c>
       <c r="G576" t="s">
         <v>1349</v>
@@ -20234,10 +20234,10 @@
         <v>1232</v>
       </c>
       <c r="E577" t="s">
+        <v>1286</v>
+      </c>
+      <c r="F577" t="s">
         <v>1348</v>
-      </c>
-      <c r="F577" t="s">
-        <v>1287</v>
       </c>
       <c r="G577" t="s">
         <v>1349</v>
@@ -20257,13 +20257,13 @@
         <v>1232</v>
       </c>
       <c r="E578" t="s">
-        <v>1348</v>
+        <v>1352</v>
       </c>
       <c r="F578" t="s">
-        <v>1352</v>
+        <v>1361</v>
       </c>
       <c r="G578" t="s">
-        <v>1361</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="579" spans="1:7">
@@ -20280,13 +20280,13 @@
         <v>34</v>
       </c>
       <c r="E579" t="s">
-        <v>1348</v>
+        <v>1364</v>
       </c>
       <c r="F579" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="G579" t="s">
-        <v>1365</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="580" spans="1:7">
@@ -20303,13 +20303,13 @@
         <v>1232</v>
       </c>
       <c r="E580" t="s">
-        <v>1348</v>
+        <v>1352</v>
       </c>
       <c r="F580" t="s">
-        <v>1352</v>
+        <v>1368</v>
       </c>
       <c r="G580" t="s">
-        <v>1368</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="581" spans="1:7">
@@ -20326,13 +20326,13 @@
         <v>19</v>
       </c>
       <c r="E581" t="s">
-        <v>1348</v>
+        <v>1352</v>
       </c>
       <c r="F581" t="s">
-        <v>1352</v>
+        <v>1371</v>
       </c>
       <c r="G581" t="s">
-        <v>1371</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="582" spans="1:7">
@@ -20349,10 +20349,10 @@
         <v>19</v>
       </c>
       <c r="E582" t="s">
+        <v>1352</v>
+      </c>
+      <c r="F582" t="s">
         <v>1348</v>
-      </c>
-      <c r="F582" t="s">
-        <v>1352</v>
       </c>
       <c r="G582" t="s">
         <v>1349</v>
@@ -20372,13 +20372,13 @@
         <v>34</v>
       </c>
       <c r="E583" t="s">
-        <v>1348</v>
+        <v>1376</v>
       </c>
       <c r="F583" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="G583" t="s">
-        <v>1377</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="584" spans="1:7">
@@ -20395,13 +20395,13 @@
         <v>34</v>
       </c>
       <c r="E584" t="s">
-        <v>1348</v>
+        <v>1380</v>
       </c>
       <c r="F584" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="G584" t="s">
-        <v>1381</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="585" spans="1:7">
@@ -20418,10 +20418,10 @@
         <v>1232</v>
       </c>
       <c r="E585" t="s">
+        <v>1352</v>
+      </c>
+      <c r="F585" t="s">
         <v>1348</v>
-      </c>
-      <c r="F585" t="s">
-        <v>1352</v>
       </c>
       <c r="G585" t="s">
         <v>1349</v>
@@ -20441,13 +20441,13 @@
         <v>34</v>
       </c>
       <c r="E586" t="s">
-        <v>1348</v>
+        <v>1386</v>
       </c>
       <c r="F586" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="G586" t="s">
-        <v>1387</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="587" spans="1:7">
@@ -20464,13 +20464,13 @@
         <v>16</v>
       </c>
       <c r="E587" t="s">
-        <v>1348</v>
+        <v>1352</v>
       </c>
       <c r="F587" t="s">
-        <v>1352</v>
+        <v>1390</v>
       </c>
       <c r="G587" t="s">
-        <v>1390</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="588" spans="1:7">
@@ -20487,13 +20487,13 @@
         <v>1232</v>
       </c>
       <c r="E588" t="s">
-        <v>1348</v>
+        <v>1352</v>
       </c>
       <c r="F588" t="s">
-        <v>1352</v>
+        <v>1393</v>
       </c>
       <c r="G588" t="s">
-        <v>1393</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="589" spans="1:7">
@@ -20510,10 +20510,10 @@
         <v>1232</v>
       </c>
       <c r="E589" t="s">
+        <v>1352</v>
+      </c>
+      <c r="F589" t="s">
         <v>1348</v>
-      </c>
-      <c r="F589" t="s">
-        <v>1352</v>
       </c>
       <c r="G589" t="s">
         <v>1349</v>
@@ -20533,10 +20533,10 @@
         <v>34</v>
       </c>
       <c r="E590" t="s">
+        <v>1352</v>
+      </c>
+      <c r="F590" t="s">
         <v>1348</v>
-      </c>
-      <c r="F590" t="s">
-        <v>1352</v>
       </c>
       <c r="G590" t="s">
         <v>1349</v>
@@ -20556,10 +20556,10 @@
         <v>19</v>
       </c>
       <c r="E591" t="s">
+        <v>1352</v>
+      </c>
+      <c r="F591" t="s">
         <v>1348</v>
-      </c>
-      <c r="F591" t="s">
-        <v>1352</v>
       </c>
       <c r="G591" t="s">
         <v>1349</v>
@@ -20579,10 +20579,10 @@
         <v>1232</v>
       </c>
       <c r="E592" t="s">
+        <v>1402</v>
+      </c>
+      <c r="F592" t="s">
         <v>1348</v>
-      </c>
-      <c r="F592" t="s">
-        <v>1402</v>
       </c>
       <c r="G592" t="s">
         <v>1349</v>
@@ -20602,10 +20602,10 @@
         <v>16</v>
       </c>
       <c r="E593" t="s">
+        <v>1352</v>
+      </c>
+      <c r="F593" t="s">
         <v>1348</v>
-      </c>
-      <c r="F593" t="s">
-        <v>1352</v>
       </c>
       <c r="G593" t="s">
         <v>1349</v>
@@ -20625,10 +20625,10 @@
         <v>1232</v>
       </c>
       <c r="E594" t="s">
+        <v>1352</v>
+      </c>
+      <c r="F594" t="s">
         <v>1348</v>
-      </c>
-      <c r="F594" t="s">
-        <v>1352</v>
       </c>
       <c r="G594" t="s">
         <v>1349</v>
@@ -20648,10 +20648,10 @@
         <v>1232</v>
       </c>
       <c r="E595" t="s">
+        <v>1352</v>
+      </c>
+      <c r="F595" t="s">
         <v>1348</v>
-      </c>
-      <c r="F595" t="s">
-        <v>1352</v>
       </c>
       <c r="G595" t="s">
         <v>1349</v>
@@ -20671,10 +20671,10 @@
         <v>1232</v>
       </c>
       <c r="E596" t="s">
+        <v>1352</v>
+      </c>
+      <c r="F596" t="s">
         <v>1348</v>
-      </c>
-      <c r="F596" t="s">
-        <v>1352</v>
       </c>
       <c r="G596" t="s">
         <v>1349</v>
@@ -20717,13 +20717,13 @@
         <v>19</v>
       </c>
       <c r="E598" t="s">
-        <v>1413</v>
+        <v>1418</v>
       </c>
       <c r="F598" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="G598" t="s">
-        <v>1419</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="599" spans="1:7">
@@ -20809,13 +20809,13 @@
         <v>34</v>
       </c>
       <c r="E602" t="s">
-        <v>1413</v>
+        <v>1428</v>
       </c>
       <c r="F602" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="G602" t="s">
-        <v>1429</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="603" spans="1:7">
@@ -20832,13 +20832,13 @@
         <v>34</v>
       </c>
       <c r="E603" t="s">
-        <v>1413</v>
+        <v>1432</v>
       </c>
       <c r="F603" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="G603" t="s">
-        <v>1433</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="604" spans="1:7">
@@ -20855,13 +20855,13 @@
         <v>1232</v>
       </c>
       <c r="E604" t="s">
-        <v>1413</v>
+        <v>1436</v>
       </c>
       <c r="F604" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="G604" t="s">
-        <v>1437</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="605" spans="1:7">
@@ -20881,10 +20881,10 @@
         <v>1413</v>
       </c>
       <c r="F605" t="s">
-        <v>1414</v>
+        <v>1440</v>
       </c>
       <c r="G605" t="s">
-        <v>1440</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="606" spans="1:7">
@@ -20947,13 +20947,13 @@
         <v>34</v>
       </c>
       <c r="E608" t="s">
-        <v>1413</v>
+        <v>1447</v>
       </c>
       <c r="F608" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="G608" t="s">
-        <v>1448</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="609" spans="1:7">
@@ -20970,13 +20970,13 @@
         <v>1232</v>
       </c>
       <c r="E609" t="s">
-        <v>1413</v>
+        <v>1390</v>
       </c>
       <c r="F609" t="s">
-        <v>1390</v>
+        <v>1451</v>
       </c>
       <c r="G609" t="s">
-        <v>1451</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="610" spans="1:7">
@@ -21016,13 +21016,13 @@
         <v>34</v>
       </c>
       <c r="E611" t="s">
-        <v>1413</v>
+        <v>1456</v>
       </c>
       <c r="F611" t="s">
-        <v>1456</v>
+        <v>1419</v>
       </c>
       <c r="G611" t="s">
-        <v>1419</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="612" spans="1:7">
@@ -21042,10 +21042,10 @@
         <v>1413</v>
       </c>
       <c r="F612" t="s">
-        <v>1414</v>
+        <v>1459</v>
       </c>
       <c r="G612" t="s">
-        <v>1459</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="613" spans="1:7">
@@ -21088,10 +21088,10 @@
         <v>1413</v>
       </c>
       <c r="F614" t="s">
-        <v>1414</v>
+        <v>1464</v>
       </c>
       <c r="G614" t="s">
-        <v>1464</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="615" spans="1:7">
@@ -21315,13 +21315,13 @@
         <v>34</v>
       </c>
       <c r="E624" t="s">
-        <v>1483</v>
+        <v>1488</v>
       </c>
       <c r="F624" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="G624" t="s">
-        <v>1489</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="625" spans="1:7">
@@ -21407,10 +21407,10 @@
         <v>1232</v>
       </c>
       <c r="E628" t="s">
-        <v>1483</v>
+        <v>1498</v>
       </c>
       <c r="F628" t="s">
-        <v>1498</v>
+        <v>1484</v>
       </c>
       <c r="G628" t="s">
         <v>1485</v>
@@ -21433,10 +21433,10 @@
         <v>1483</v>
       </c>
       <c r="F629" t="s">
-        <v>1484</v>
+        <v>1501</v>
       </c>
       <c r="G629" t="s">
-        <v>1501</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="630" spans="1:7">
@@ -21499,13 +21499,13 @@
         <v>34</v>
       </c>
       <c r="E632" t="s">
-        <v>1483</v>
+        <v>1508</v>
       </c>
       <c r="F632" t="s">
-        <v>1508</v>
+        <v>1501</v>
       </c>
       <c r="G632" t="s">
-        <v>1501</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="633" spans="1:7">
@@ -21522,13 +21522,13 @@
         <v>34</v>
       </c>
       <c r="E633" t="s">
-        <v>1483</v>
+        <v>1511</v>
       </c>
       <c r="F633" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="G633" t="s">
-        <v>1512</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="634" spans="1:7">
@@ -21545,13 +21545,13 @@
         <v>34</v>
       </c>
       <c r="E634" t="s">
-        <v>1483</v>
+        <v>1515</v>
       </c>
       <c r="F634" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="G634" t="s">
-        <v>1516</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="635" spans="1:7">
@@ -21594,10 +21594,10 @@
         <v>1483</v>
       </c>
       <c r="F636" t="s">
-        <v>1484</v>
+        <v>1521</v>
       </c>
       <c r="G636" t="s">
-        <v>1521</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="637" spans="1:7">
@@ -21614,13 +21614,13 @@
         <v>34</v>
       </c>
       <c r="E637" t="s">
-        <v>1483</v>
+        <v>1524</v>
       </c>
       <c r="F637" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="G637" t="s">
-        <v>1525</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="638" spans="1:7">
@@ -21706,13 +21706,13 @@
         <v>19</v>
       </c>
       <c r="E641" t="s">
-        <v>1483</v>
+        <v>1534</v>
       </c>
       <c r="F641" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="G641" t="s">
-        <v>1535</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="642" spans="1:7">
@@ -21732,10 +21732,10 @@
         <v>1483</v>
       </c>
       <c r="F642" t="s">
-        <v>1484</v>
+        <v>1538</v>
       </c>
       <c r="G642" t="s">
-        <v>1538</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="643" spans="1:7">
@@ -21755,10 +21755,10 @@
         <v>1483</v>
       </c>
       <c r="F643" t="s">
-        <v>1484</v>
+        <v>1541</v>
       </c>
       <c r="G643" t="s">
-        <v>1541</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="644" spans="1:7">
@@ -21824,10 +21824,10 @@
         <v>1483</v>
       </c>
       <c r="F646" t="s">
-        <v>1484</v>
+        <v>1548</v>
       </c>
       <c r="G646" t="s">
-        <v>1548</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="647" spans="1:7">
@@ -21913,13 +21913,13 @@
         <v>19</v>
       </c>
       <c r="E650" t="s">
-        <v>1555</v>
+        <v>1560</v>
       </c>
       <c r="F650" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="G650" t="s">
-        <v>1561</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="651" spans="1:7">
@@ -21936,10 +21936,10 @@
         <v>34</v>
       </c>
       <c r="E651" t="s">
-        <v>1555</v>
+        <v>1564</v>
       </c>
       <c r="F651" t="s">
-        <v>1564</v>
+        <v>1556</v>
       </c>
       <c r="G651" t="s">
         <v>1557</v>
@@ -21959,13 +21959,13 @@
         <v>1232</v>
       </c>
       <c r="E652" t="s">
-        <v>1555</v>
+        <v>1567</v>
       </c>
       <c r="F652" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="G652" t="s">
-        <v>1568</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="653" spans="1:7">
@@ -21982,13 +21982,13 @@
         <v>1232</v>
       </c>
       <c r="E653" t="s">
-        <v>1555</v>
+        <v>1567</v>
       </c>
       <c r="F653" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="G653" t="s">
-        <v>1568</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="654" spans="1:7">
@@ -22005,13 +22005,13 @@
         <v>19</v>
       </c>
       <c r="E654" t="s">
-        <v>1555</v>
+        <v>1483</v>
       </c>
       <c r="F654" t="s">
-        <v>1484</v>
+        <v>1541</v>
       </c>
       <c r="G654" t="s">
-        <v>1541</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="655" spans="1:7">
@@ -22028,13 +22028,13 @@
         <v>1232</v>
       </c>
       <c r="E655" t="s">
-        <v>1555</v>
+        <v>1567</v>
       </c>
       <c r="F655" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="G655" t="s">
-        <v>1568</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="656" spans="1:7">
@@ -22051,13 +22051,13 @@
         <v>1232</v>
       </c>
       <c r="E656" t="s">
-        <v>1555</v>
+        <v>1567</v>
       </c>
       <c r="F656" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="G656" t="s">
-        <v>1568</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="657" spans="1:7">
@@ -22074,13 +22074,13 @@
         <v>19</v>
       </c>
       <c r="E657" t="s">
-        <v>1555</v>
+        <v>1579</v>
       </c>
       <c r="F657" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="G657" t="s">
-        <v>1580</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="658" spans="1:7">
@@ -22097,13 +22097,13 @@
         <v>34</v>
       </c>
       <c r="E658" t="s">
-        <v>1555</v>
+        <v>1583</v>
       </c>
       <c r="F658" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="G658" t="s">
-        <v>1584</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="659" spans="1:7">
@@ -22120,13 +22120,13 @@
         <v>34</v>
       </c>
       <c r="E659" t="s">
-        <v>1555</v>
+        <v>1587</v>
       </c>
       <c r="F659" t="s">
-        <v>1587</v>
+        <v>1521</v>
       </c>
       <c r="G659" t="s">
-        <v>1521</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="660" spans="1:7">
@@ -22143,13 +22143,13 @@
         <v>34</v>
       </c>
       <c r="E660" t="s">
-        <v>1555</v>
+        <v>1590</v>
       </c>
       <c r="F660" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="G660" t="s">
-        <v>1591</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="661" spans="1:7">
@@ -22166,13 +22166,13 @@
         <v>1232</v>
       </c>
       <c r="E661" t="s">
-        <v>1555</v>
+        <v>1567</v>
       </c>
       <c r="F661" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="G661" t="s">
-        <v>1568</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="662" spans="1:7">
@@ -22189,13 +22189,13 @@
         <v>34</v>
       </c>
       <c r="E662" t="s">
-        <v>1555</v>
+        <v>1561</v>
       </c>
       <c r="F662" t="s">
-        <v>1561</v>
+        <v>1568</v>
       </c>
       <c r="G662" t="s">
-        <v>1568</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="663" spans="1:7">
@@ -22212,13 +22212,13 @@
         <v>34</v>
       </c>
       <c r="E663" t="s">
-        <v>1555</v>
+        <v>1598</v>
       </c>
       <c r="F663" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="G663" t="s">
-        <v>1599</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="664" spans="1:7">
@@ -22235,13 +22235,13 @@
         <v>19</v>
       </c>
       <c r="E664" t="s">
-        <v>1555</v>
+        <v>1602</v>
       </c>
       <c r="F664" t="s">
-        <v>1602</v>
+        <v>1541</v>
       </c>
       <c r="G664" t="s">
-        <v>1541</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="665" spans="1:7">
@@ -22258,13 +22258,13 @@
         <v>1232</v>
       </c>
       <c r="E665" t="s">
-        <v>1555</v>
+        <v>1567</v>
       </c>
       <c r="F665" t="s">
-        <v>1567</v>
+        <v>1605</v>
       </c>
       <c r="G665" t="s">
-        <v>1605</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="666" spans="1:7">
@@ -22284,10 +22284,10 @@
         <v>1555</v>
       </c>
       <c r="F666" t="s">
-        <v>1556</v>
+        <v>1605</v>
       </c>
       <c r="G666" t="s">
-        <v>1605</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="667" spans="1:7">
@@ -22304,13 +22304,13 @@
         <v>34</v>
       </c>
       <c r="E667" t="s">
-        <v>1555</v>
+        <v>1610</v>
       </c>
       <c r="F667" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="G667" t="s">
-        <v>1611</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="668" spans="1:7">
@@ -22327,13 +22327,13 @@
         <v>19</v>
       </c>
       <c r="E668" t="s">
-        <v>1555</v>
+        <v>1567</v>
       </c>
       <c r="F668" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="G668" t="s">
-        <v>1568</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="669" spans="1:7">
@@ -22350,13 +22350,13 @@
         <v>19</v>
       </c>
       <c r="E669" t="s">
-        <v>1555</v>
+        <v>1587</v>
       </c>
       <c r="F669" t="s">
-        <v>1587</v>
+        <v>1541</v>
       </c>
       <c r="G669" t="s">
-        <v>1541</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="670" spans="1:7">
@@ -22373,13 +22373,13 @@
         <v>1232</v>
       </c>
       <c r="E670" t="s">
-        <v>1555</v>
+        <v>1567</v>
       </c>
       <c r="F670" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="G670" t="s">
-        <v>1568</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="671" spans="1:7">
@@ -22396,10 +22396,10 @@
         <v>34</v>
       </c>
       <c r="E671" t="s">
-        <v>1555</v>
+        <v>1620</v>
       </c>
       <c r="F671" t="s">
-        <v>1620</v>
+        <v>1556</v>
       </c>
       <c r="G671" t="s">
         <v>1557</v>
@@ -22419,13 +22419,13 @@
         <v>19</v>
       </c>
       <c r="E672" t="s">
-        <v>1555</v>
+        <v>1567</v>
       </c>
       <c r="F672" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="G672" t="s">
-        <v>1568</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="673" spans="1:7">
@@ -22442,13 +22442,13 @@
         <v>1232</v>
       </c>
       <c r="E673" t="s">
-        <v>1555</v>
+        <v>1567</v>
       </c>
       <c r="F673" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="G673" t="s">
-        <v>1568</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="674" spans="1:7">
@@ -22465,13 +22465,13 @@
         <v>19</v>
       </c>
       <c r="E674" t="s">
-        <v>1555</v>
+        <v>1590</v>
       </c>
       <c r="F674" t="s">
-        <v>1590</v>
+        <v>1541</v>
       </c>
       <c r="G674" t="s">
-        <v>1541</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="675" spans="1:7">
@@ -22488,10 +22488,10 @@
         <v>34</v>
       </c>
       <c r="E675" t="s">
-        <v>1555</v>
+        <v>1564</v>
       </c>
       <c r="F675" t="s">
-        <v>1564</v>
+        <v>1556</v>
       </c>
       <c r="G675" t="s">
         <v>1557</v>
@@ -22511,13 +22511,13 @@
         <v>19</v>
       </c>
       <c r="E676" t="s">
-        <v>1555</v>
+        <v>1567</v>
       </c>
       <c r="F676" t="s">
-        <v>1567</v>
+        <v>1631</v>
       </c>
       <c r="G676" t="s">
-        <v>1631</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="677" spans="1:7">
@@ -22534,13 +22534,13 @@
         <v>1232</v>
       </c>
       <c r="E677" t="s">
-        <v>1555</v>
+        <v>1567</v>
       </c>
       <c r="F677" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="G677" t="s">
-        <v>1568</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="678" spans="1:7">
@@ -22557,13 +22557,13 @@
         <v>1232</v>
       </c>
       <c r="E678" t="s">
-        <v>1555</v>
+        <v>1567</v>
       </c>
       <c r="F678" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="G678" t="s">
-        <v>1568</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="679" spans="1:7">
@@ -22580,13 +22580,13 @@
         <v>34</v>
       </c>
       <c r="E679" t="s">
-        <v>1555</v>
+        <v>1590</v>
       </c>
       <c r="F679" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="G679" t="s">
-        <v>1591</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="680" spans="1:7">
@@ -22603,13 +22603,13 @@
         <v>1232</v>
       </c>
       <c r="E680" t="s">
-        <v>1555</v>
+        <v>1567</v>
       </c>
       <c r="F680" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="G680" t="s">
-        <v>1568</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="681" spans="1:7">
@@ -22626,13 +22626,13 @@
         <v>1232</v>
       </c>
       <c r="E681" t="s">
-        <v>1555</v>
+        <v>1567</v>
       </c>
       <c r="F681" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="G681" t="s">
-        <v>1568</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="682" spans="1:7">
@@ -22672,13 +22672,13 @@
         <v>34</v>
       </c>
       <c r="E683" t="s">
-        <v>1644</v>
+        <v>1649</v>
       </c>
       <c r="F683" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="G683" t="s">
-        <v>1650</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="684" spans="1:7">
@@ -22695,13 +22695,13 @@
         <v>1232</v>
       </c>
       <c r="E684" t="s">
-        <v>1644</v>
+        <v>1653</v>
       </c>
       <c r="F684" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="G684" t="s">
-        <v>1654</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="685" spans="1:7">
@@ -22718,13 +22718,13 @@
         <v>1232</v>
       </c>
       <c r="E685" t="s">
-        <v>1644</v>
+        <v>1653</v>
       </c>
       <c r="F685" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="G685" t="s">
-        <v>1654</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="686" spans="1:7">
@@ -22741,13 +22741,13 @@
         <v>1232</v>
       </c>
       <c r="E686" t="s">
-        <v>1644</v>
+        <v>1653</v>
       </c>
       <c r="F686" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="G686" t="s">
-        <v>1654</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="687" spans="1:7">
@@ -22764,13 +22764,13 @@
         <v>1232</v>
       </c>
       <c r="E687" t="s">
-        <v>1644</v>
+        <v>1653</v>
       </c>
       <c r="F687" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="G687" t="s">
-        <v>1654</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="688" spans="1:7">
@@ -22787,13 +22787,13 @@
         <v>1232</v>
       </c>
       <c r="E688" t="s">
-        <v>1644</v>
+        <v>1653</v>
       </c>
       <c r="F688" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="G688" t="s">
-        <v>1654</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="689" spans="1:7">
@@ -22810,13 +22810,13 @@
         <v>34</v>
       </c>
       <c r="E689" t="s">
-        <v>1644</v>
+        <v>1665</v>
       </c>
       <c r="F689" t="s">
-        <v>1665</v>
+        <v>1650</v>
       </c>
       <c r="G689" t="s">
-        <v>1650</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="690" spans="1:7">
@@ -22833,13 +22833,13 @@
         <v>34</v>
       </c>
       <c r="E690" t="s">
-        <v>1644</v>
+        <v>1668</v>
       </c>
       <c r="F690" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="G690" t="s">
-        <v>1669</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="691" spans="1:7">
@@ -22856,13 +22856,13 @@
         <v>16</v>
       </c>
       <c r="E691" t="s">
-        <v>1644</v>
+        <v>1653</v>
       </c>
       <c r="F691" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="G691" t="s">
-        <v>1654</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="692" spans="1:7">
@@ -22879,13 +22879,13 @@
         <v>19</v>
       </c>
       <c r="E692" t="s">
-        <v>1644</v>
+        <v>1567</v>
       </c>
       <c r="F692" t="s">
-        <v>1567</v>
+        <v>1674</v>
       </c>
       <c r="G692" t="s">
-        <v>1674</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="693" spans="1:7">
@@ -22902,13 +22902,13 @@
         <v>34</v>
       </c>
       <c r="E693" t="s">
-        <v>1644</v>
+        <v>1677</v>
       </c>
       <c r="F693" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="G693" t="s">
-        <v>1678</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="694" spans="1:7">
@@ -22925,13 +22925,13 @@
         <v>19</v>
       </c>
       <c r="E694" t="s">
-        <v>1644</v>
+        <v>1681</v>
       </c>
       <c r="F694" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="G694" t="s">
-        <v>1682</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="695" spans="1:7">
@@ -22948,13 +22948,13 @@
         <v>34</v>
       </c>
       <c r="E695" t="s">
-        <v>1644</v>
+        <v>1685</v>
       </c>
       <c r="F695" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="G695" t="s">
-        <v>1686</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="696" spans="1:7">
@@ -22971,13 +22971,13 @@
         <v>1232</v>
       </c>
       <c r="E696" t="s">
-        <v>1644</v>
+        <v>1653</v>
       </c>
       <c r="F696" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="G696" t="s">
-        <v>1654</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="697" spans="1:7">
@@ -22994,13 +22994,13 @@
         <v>34</v>
       </c>
       <c r="E697" t="s">
-        <v>1644</v>
+        <v>1691</v>
       </c>
       <c r="F697" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="G697" t="s">
-        <v>1692</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="698" spans="1:7">
@@ -23017,13 +23017,13 @@
         <v>34</v>
       </c>
       <c r="E698" t="s">
-        <v>1644</v>
+        <v>1695</v>
       </c>
       <c r="F698" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="G698" t="s">
-        <v>1696</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="699" spans="1:7">
@@ -23040,13 +23040,13 @@
         <v>19</v>
       </c>
       <c r="E699" t="s">
-        <v>1644</v>
+        <v>1653</v>
       </c>
       <c r="F699" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="G699" t="s">
-        <v>1654</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="700" spans="1:7">
@@ -23063,13 +23063,13 @@
         <v>34</v>
       </c>
       <c r="E700" t="s">
-        <v>1644</v>
+        <v>1701</v>
       </c>
       <c r="F700" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="G700" t="s">
-        <v>1702</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="701" spans="1:7">
@@ -23086,13 +23086,13 @@
         <v>19</v>
       </c>
       <c r="E701" t="s">
-        <v>1644</v>
+        <v>1653</v>
       </c>
       <c r="F701" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="G701" t="s">
-        <v>1654</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="702" spans="1:7">
@@ -23109,13 +23109,13 @@
         <v>34</v>
       </c>
       <c r="E702" t="s">
-        <v>1644</v>
+        <v>1707</v>
       </c>
       <c r="F702" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="G702" t="s">
-        <v>1708</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="703" spans="1:7">
@@ -23132,13 +23132,13 @@
         <v>34</v>
       </c>
       <c r="E703" t="s">
-        <v>1644</v>
+        <v>1701</v>
       </c>
       <c r="F703" t="s">
-        <v>1701</v>
+        <v>1711</v>
       </c>
       <c r="G703" t="s">
-        <v>1711</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="704" spans="1:7">
@@ -23155,13 +23155,13 @@
         <v>1232</v>
       </c>
       <c r="E704" t="s">
-        <v>1644</v>
+        <v>1653</v>
       </c>
       <c r="F704" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="G704" t="s">
-        <v>1654</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="705" spans="1:7">
@@ -23178,13 +23178,13 @@
         <v>19</v>
       </c>
       <c r="E705" t="s">
-        <v>1644</v>
+        <v>1695</v>
       </c>
       <c r="F705" t="s">
-        <v>1695</v>
+        <v>1716</v>
       </c>
       <c r="G705" t="s">
-        <v>1716</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="706" spans="1:7">
@@ -23201,13 +23201,13 @@
         <v>1232</v>
       </c>
       <c r="E706" t="s">
-        <v>1644</v>
+        <v>1653</v>
       </c>
       <c r="F706" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="G706" t="s">
-        <v>1654</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="707" spans="1:7">
@@ -23224,13 +23224,13 @@
         <v>19</v>
       </c>
       <c r="E707" t="s">
-        <v>1644</v>
+        <v>1695</v>
       </c>
       <c r="F707" t="s">
-        <v>1695</v>
+        <v>1654</v>
       </c>
       <c r="G707" t="s">
-        <v>1654</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="708" spans="1:7">
@@ -23247,13 +23247,13 @@
         <v>34</v>
       </c>
       <c r="E708" t="s">
-        <v>1644</v>
+        <v>1649</v>
       </c>
       <c r="F708" t="s">
-        <v>1649</v>
+        <v>1723</v>
       </c>
       <c r="G708" t="s">
-        <v>1723</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="709" spans="1:7">
@@ -23270,13 +23270,13 @@
         <v>1232</v>
       </c>
       <c r="E709" t="s">
-        <v>1644</v>
+        <v>1653</v>
       </c>
       <c r="F709" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="G709" t="s">
-        <v>1654</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="710" spans="1:7">
@@ -23293,13 +23293,13 @@
         <v>34</v>
       </c>
       <c r="E710" t="s">
-        <v>1644</v>
+        <v>1728</v>
       </c>
       <c r="F710" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="G710" t="s">
-        <v>1729</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="711" spans="1:7">
@@ -23316,13 +23316,13 @@
         <v>1232</v>
       </c>
       <c r="E711" t="s">
-        <v>1644</v>
+        <v>1695</v>
       </c>
       <c r="F711" t="s">
-        <v>1695</v>
+        <v>1654</v>
       </c>
       <c r="G711" t="s">
-        <v>1654</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="712" spans="1:7">
@@ -23339,13 +23339,13 @@
         <v>1232</v>
       </c>
       <c r="E712" t="s">
-        <v>1644</v>
+        <v>1653</v>
       </c>
       <c r="F712" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="G712" t="s">
-        <v>1654</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="713" spans="1:7">
@@ -23362,13 +23362,13 @@
         <v>34</v>
       </c>
       <c r="E713" t="s">
-        <v>1644</v>
+        <v>1668</v>
       </c>
       <c r="F713" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="G713" t="s">
-        <v>1669</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="714" spans="1:7">
@@ -23385,13 +23385,13 @@
         <v>1232</v>
       </c>
       <c r="E714" t="s">
-        <v>1644</v>
+        <v>1653</v>
       </c>
       <c r="F714" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="G714" t="s">
-        <v>1654</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="715" spans="1:7">
@@ -23408,13 +23408,13 @@
         <v>34</v>
       </c>
       <c r="E715" t="s">
-        <v>1644</v>
+        <v>1695</v>
       </c>
       <c r="F715" t="s">
-        <v>1695</v>
+        <v>1692</v>
       </c>
       <c r="G715" t="s">
-        <v>1692</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="716" spans="1:7">
@@ -23431,13 +23431,13 @@
         <v>1232</v>
       </c>
       <c r="E716" t="s">
-        <v>1644</v>
+        <v>1653</v>
       </c>
       <c r="F716" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="G716" t="s">
-        <v>1654</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="717" spans="1:7">
@@ -23454,13 +23454,13 @@
         <v>1232</v>
       </c>
       <c r="E717" t="s">
-        <v>1644</v>
+        <v>1653</v>
       </c>
       <c r="F717" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="G717" t="s">
-        <v>1654</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="718" spans="1:7">
@@ -23503,10 +23503,10 @@
         <v>1746</v>
       </c>
       <c r="F719" t="s">
-        <v>1747</v>
+        <v>1751</v>
       </c>
       <c r="G719" t="s">
-        <v>1751</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="720" spans="1:7">
@@ -23526,10 +23526,10 @@
         <v>1746</v>
       </c>
       <c r="F720" t="s">
-        <v>1747</v>
+        <v>1751</v>
       </c>
       <c r="G720" t="s">
-        <v>1751</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="721" spans="1:7">
@@ -23549,10 +23549,10 @@
         <v>1746</v>
       </c>
       <c r="F721" t="s">
-        <v>1747</v>
+        <v>1751</v>
       </c>
       <c r="G721" t="s">
-        <v>1751</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="722" spans="1:7">
@@ -23572,10 +23572,10 @@
         <v>1746</v>
       </c>
       <c r="F722" t="s">
-        <v>1747</v>
+        <v>1751</v>
       </c>
       <c r="G722" t="s">
-        <v>1751</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="723" spans="1:7">
@@ -23595,10 +23595,10 @@
         <v>1746</v>
       </c>
       <c r="F723" t="s">
-        <v>1747</v>
+        <v>1751</v>
       </c>
       <c r="G723" t="s">
-        <v>1751</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="724" spans="1:7">
@@ -23618,10 +23618,10 @@
         <v>1746</v>
       </c>
       <c r="F724" t="s">
-        <v>1747</v>
+        <v>1751</v>
       </c>
       <c r="G724" t="s">
-        <v>1751</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="725" spans="1:7">
@@ -23638,13 +23638,13 @@
         <v>19</v>
       </c>
       <c r="E725" t="s">
-        <v>1746</v>
+        <v>1764</v>
       </c>
       <c r="F725" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="G725" t="s">
-        <v>1765</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="726" spans="1:7">
@@ -23661,13 +23661,13 @@
         <v>19</v>
       </c>
       <c r="E726" t="s">
-        <v>1746</v>
+        <v>1768</v>
       </c>
       <c r="F726" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="G726" t="s">
-        <v>1769</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="727" spans="1:7">
@@ -23687,10 +23687,10 @@
         <v>1746</v>
       </c>
       <c r="F727" t="s">
-        <v>1747</v>
+        <v>1751</v>
       </c>
       <c r="G727" t="s">
-        <v>1751</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="728" spans="1:7">
@@ -23710,10 +23710,10 @@
         <v>1746</v>
       </c>
       <c r="F728" t="s">
-        <v>1747</v>
+        <v>1751</v>
       </c>
       <c r="G728" t="s">
-        <v>1751</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="729" spans="1:7">
@@ -23730,13 +23730,13 @@
         <v>34</v>
       </c>
       <c r="E729" t="s">
-        <v>1746</v>
+        <v>1776</v>
       </c>
       <c r="F729" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="G729" t="s">
-        <v>1777</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="730" spans="1:7">
@@ -23756,10 +23756,10 @@
         <v>1746</v>
       </c>
       <c r="F730" t="s">
-        <v>1747</v>
+        <v>1751</v>
       </c>
       <c r="G730" t="s">
-        <v>1751</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="731" spans="1:7">
@@ -23776,13 +23776,13 @@
         <v>34</v>
       </c>
       <c r="E731" t="s">
-        <v>1746</v>
+        <v>1776</v>
       </c>
       <c r="F731" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="G731" t="s">
-        <v>1777</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="732" spans="1:7">
@@ -23799,13 +23799,13 @@
         <v>34</v>
       </c>
       <c r="E732" t="s">
-        <v>1746</v>
+        <v>1784</v>
       </c>
       <c r="F732" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="G732" t="s">
-        <v>1785</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="733" spans="1:7">
@@ -23825,10 +23825,10 @@
         <v>1746</v>
       </c>
       <c r="F733" t="s">
-        <v>1747</v>
+        <v>1788</v>
       </c>
       <c r="G733" t="s">
-        <v>1788</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="734" spans="1:7">
@@ -23845,13 +23845,13 @@
         <v>34</v>
       </c>
       <c r="E734" t="s">
-        <v>1746</v>
+        <v>1791</v>
       </c>
       <c r="F734" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="G734" t="s">
-        <v>1792</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="735" spans="1:7">
@@ -23871,10 +23871,10 @@
         <v>1746</v>
       </c>
       <c r="F735" t="s">
-        <v>1747</v>
+        <v>1751</v>
       </c>
       <c r="G735" t="s">
-        <v>1751</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="736" spans="1:7">
@@ -23894,10 +23894,10 @@
         <v>1746</v>
       </c>
       <c r="F736" t="s">
-        <v>1747</v>
+        <v>1797</v>
       </c>
       <c r="G736" t="s">
-        <v>1797</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="737" spans="1:7">
@@ -23917,10 +23917,10 @@
         <v>1746</v>
       </c>
       <c r="F737" t="s">
-        <v>1747</v>
+        <v>1751</v>
       </c>
       <c r="G737" t="s">
-        <v>1751</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="738" spans="1:7">
@@ -23937,13 +23937,13 @@
         <v>19</v>
       </c>
       <c r="E738" t="s">
-        <v>1746</v>
+        <v>1653</v>
       </c>
       <c r="F738" t="s">
-        <v>1653</v>
+        <v>1802</v>
       </c>
       <c r="G738" t="s">
-        <v>1802</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="739" spans="1:7">
@@ -23963,10 +23963,10 @@
         <v>1746</v>
       </c>
       <c r="F739" t="s">
-        <v>1747</v>
+        <v>1751</v>
       </c>
       <c r="G739" t="s">
-        <v>1751</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="740" spans="1:7">
@@ -23986,10 +23986,10 @@
         <v>1746</v>
       </c>
       <c r="F740" t="s">
-        <v>1747</v>
+        <v>1751</v>
       </c>
       <c r="G740" t="s">
-        <v>1751</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="741" spans="1:7">
@@ -24006,13 +24006,13 @@
         <v>34</v>
       </c>
       <c r="E741" t="s">
-        <v>1746</v>
+        <v>1809</v>
       </c>
       <c r="F741" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="G741" t="s">
-        <v>1810</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="742" spans="1:7">
@@ -24032,10 +24032,10 @@
         <v>1746</v>
       </c>
       <c r="F742" t="s">
-        <v>1747</v>
+        <v>1813</v>
       </c>
       <c r="G742" t="s">
-        <v>1813</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="743" spans="1:7">
@@ -24055,10 +24055,10 @@
         <v>1746</v>
       </c>
       <c r="F743" t="s">
-        <v>1747</v>
+        <v>1751</v>
       </c>
       <c r="G743" t="s">
-        <v>1751</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="744" spans="1:7">
@@ -24101,10 +24101,10 @@
         <v>1746</v>
       </c>
       <c r="F745" t="s">
-        <v>1747</v>
+        <v>1820</v>
       </c>
       <c r="G745" t="s">
-        <v>1820</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="746" spans="1:7">
@@ -24124,10 +24124,10 @@
         <v>1746</v>
       </c>
       <c r="F746" t="s">
-        <v>1747</v>
+        <v>1751</v>
       </c>
       <c r="G746" t="s">
-        <v>1751</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="747" spans="1:7">
@@ -24147,10 +24147,10 @@
         <v>1746</v>
       </c>
       <c r="F747" t="s">
-        <v>1747</v>
+        <v>1751</v>
       </c>
       <c r="G747" t="s">
-        <v>1751</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="748" spans="1:7">
@@ -24170,10 +24170,10 @@
         <v>1746</v>
       </c>
       <c r="F748" t="s">
-        <v>1747</v>
+        <v>1751</v>
       </c>
       <c r="G748" t="s">
-        <v>1751</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="749" spans="1:7">
@@ -24193,10 +24193,10 @@
         <v>1746</v>
       </c>
       <c r="F749" t="s">
-        <v>1747</v>
+        <v>1751</v>
       </c>
       <c r="G749" t="s">
-        <v>1751</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="750" spans="1:7">
@@ -24236,13 +24236,13 @@
         <v>34</v>
       </c>
       <c r="E751" t="s">
-        <v>1831</v>
+        <v>1836</v>
       </c>
       <c r="F751" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="G751" t="s">
-        <v>1837</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="752" spans="1:7">
@@ -24259,13 +24259,13 @@
         <v>1232</v>
       </c>
       <c r="E752" t="s">
-        <v>1831</v>
+        <v>1840</v>
       </c>
       <c r="F752" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="G752" t="s">
-        <v>1841</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="753" spans="1:7">
@@ -24282,13 +24282,13 @@
         <v>1232</v>
       </c>
       <c r="E753" t="s">
-        <v>1831</v>
+        <v>1840</v>
       </c>
       <c r="F753" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="G753" t="s">
-        <v>1841</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="754" spans="1:7">
@@ -24305,13 +24305,13 @@
         <v>1232</v>
       </c>
       <c r="E754" t="s">
-        <v>1831</v>
+        <v>1840</v>
       </c>
       <c r="F754" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="G754" t="s">
-        <v>1841</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="755" spans="1:7">
@@ -24328,13 +24328,13 @@
         <v>1232</v>
       </c>
       <c r="E755" t="s">
-        <v>1831</v>
+        <v>1840</v>
       </c>
       <c r="F755" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="G755" t="s">
-        <v>1841</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="756" spans="1:7">
@@ -24351,13 +24351,13 @@
         <v>1232</v>
       </c>
       <c r="E756" t="s">
-        <v>1831</v>
+        <v>1840</v>
       </c>
       <c r="F756" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="G756" t="s">
-        <v>1841</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="757" spans="1:7">
@@ -24374,13 +24374,13 @@
         <v>1232</v>
       </c>
       <c r="E757" t="s">
-        <v>1831</v>
+        <v>1840</v>
       </c>
       <c r="F757" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="G757" t="s">
-        <v>1841</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="758" spans="1:7">
@@ -24397,10 +24397,10 @@
         <v>34</v>
       </c>
       <c r="E758" t="s">
-        <v>1831</v>
+        <v>1836</v>
       </c>
       <c r="F758" t="s">
-        <v>1836</v>
+        <v>1832</v>
       </c>
       <c r="G758" t="s">
         <v>1833</v>
@@ -24420,13 +24420,13 @@
         <v>19</v>
       </c>
       <c r="E759" t="s">
-        <v>1831</v>
+        <v>1840</v>
       </c>
       <c r="F759" t="s">
-        <v>1840</v>
+        <v>1797</v>
       </c>
       <c r="G759" t="s">
-        <v>1797</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="760" spans="1:7">
@@ -24443,13 +24443,13 @@
         <v>1232</v>
       </c>
       <c r="E760" t="s">
-        <v>1831</v>
+        <v>1840</v>
       </c>
       <c r="F760" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="G760" t="s">
-        <v>1841</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="761" spans="1:7">
@@ -24466,13 +24466,13 @@
         <v>1232</v>
       </c>
       <c r="E761" t="s">
-        <v>1831</v>
+        <v>1840</v>
       </c>
       <c r="F761" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="G761" t="s">
-        <v>1841</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="762" spans="1:7">
@@ -24489,13 +24489,13 @@
         <v>34</v>
       </c>
       <c r="E762" t="s">
-        <v>1831</v>
+        <v>1862</v>
       </c>
       <c r="F762" t="s">
-        <v>1862</v>
+        <v>1797</v>
       </c>
       <c r="G762" t="s">
-        <v>1797</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="763" spans="1:7">
@@ -24512,13 +24512,13 @@
         <v>1232</v>
       </c>
       <c r="E763" t="s">
-        <v>1831</v>
+        <v>1840</v>
       </c>
       <c r="F763" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="G763" t="s">
-        <v>1841</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="764" spans="1:7">
@@ -24535,13 +24535,13 @@
         <v>34</v>
       </c>
       <c r="E764" t="s">
-        <v>1831</v>
+        <v>1867</v>
       </c>
       <c r="F764" t="s">
-        <v>1867</v>
+        <v>1868</v>
       </c>
       <c r="G764" t="s">
-        <v>1868</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="765" spans="1:7">
@@ -24561,10 +24561,10 @@
         <v>1831</v>
       </c>
       <c r="F765" t="s">
-        <v>1832</v>
+        <v>1841</v>
       </c>
       <c r="G765" t="s">
-        <v>1841</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="766" spans="1:7">
@@ -24581,13 +24581,13 @@
         <v>34</v>
       </c>
       <c r="E766" t="s">
-        <v>1831</v>
+        <v>1862</v>
       </c>
       <c r="F766" t="s">
-        <v>1862</v>
+        <v>1873</v>
       </c>
       <c r="G766" t="s">
-        <v>1873</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="767" spans="1:7">
@@ -24604,13 +24604,13 @@
         <v>34</v>
       </c>
       <c r="E767" t="s">
-        <v>1831</v>
+        <v>1876</v>
       </c>
       <c r="F767" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
       <c r="G767" t="s">
-        <v>1877</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="768" spans="1:7">
@@ -24627,13 +24627,13 @@
         <v>1232</v>
       </c>
       <c r="E768" t="s">
-        <v>1831</v>
+        <v>1840</v>
       </c>
       <c r="F768" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="G768" t="s">
-        <v>1841</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="769" spans="1:7">
@@ -24650,13 +24650,13 @@
         <v>1232</v>
       </c>
       <c r="E769" t="s">
-        <v>1831</v>
+        <v>1840</v>
       </c>
       <c r="F769" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="G769" t="s">
-        <v>1841</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="770" spans="1:7">
@@ -24673,13 +24673,13 @@
         <v>34</v>
       </c>
       <c r="E770" t="s">
-        <v>1831</v>
+        <v>1884</v>
       </c>
       <c r="F770" t="s">
-        <v>1884</v>
+        <v>1885</v>
       </c>
       <c r="G770" t="s">
-        <v>1885</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="771" spans="1:7">
@@ -24696,13 +24696,13 @@
         <v>1232</v>
       </c>
       <c r="E771" t="s">
-        <v>1831</v>
+        <v>1840</v>
       </c>
       <c r="F771" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="G771" t="s">
-        <v>1841</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="772" spans="1:7">
@@ -24719,13 +24719,13 @@
         <v>1232</v>
       </c>
       <c r="E772" t="s">
-        <v>1831</v>
+        <v>1840</v>
       </c>
       <c r="F772" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="G772" t="s">
-        <v>1841</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="773" spans="1:7">
@@ -24742,13 +24742,13 @@
         <v>1232</v>
       </c>
       <c r="E773" t="s">
-        <v>1831</v>
+        <v>1840</v>
       </c>
       <c r="F773" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="G773" t="s">
-        <v>1841</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="774" spans="1:7">
@@ -24765,13 +24765,13 @@
         <v>34</v>
       </c>
       <c r="E774" t="s">
-        <v>1831</v>
+        <v>1894</v>
       </c>
       <c r="F774" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
       <c r="G774" t="s">
-        <v>1895</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="775" spans="1:7">
@@ -24788,13 +24788,13 @@
         <v>1232</v>
       </c>
       <c r="E775" t="s">
-        <v>1831</v>
+        <v>1840</v>
       </c>
       <c r="F775" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="G775" t="s">
-        <v>1841</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="776" spans="1:7">
@@ -24837,10 +24837,10 @@
         <v>1900</v>
       </c>
       <c r="F777" t="s">
-        <v>1901</v>
+        <v>1905</v>
       </c>
       <c r="G777" t="s">
-        <v>1905</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="778" spans="1:7">
@@ -24857,13 +24857,13 @@
         <v>34</v>
       </c>
       <c r="E778" t="s">
-        <v>1900</v>
+        <v>1908</v>
       </c>
       <c r="F778" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
       <c r="G778" t="s">
-        <v>1909</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="779" spans="1:7">
@@ -24880,13 +24880,13 @@
         <v>34</v>
       </c>
       <c r="E779" t="s">
-        <v>1900</v>
+        <v>1912</v>
       </c>
       <c r="F779" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
       <c r="G779" t="s">
-        <v>1913</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="780" spans="1:7">
@@ -24906,10 +24906,10 @@
         <v>1900</v>
       </c>
       <c r="F780" t="s">
-        <v>1901</v>
+        <v>1905</v>
       </c>
       <c r="G780" t="s">
-        <v>1905</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="781" spans="1:7">
@@ -24929,10 +24929,10 @@
         <v>1900</v>
       </c>
       <c r="F781" t="s">
-        <v>1901</v>
+        <v>1905</v>
       </c>
       <c r="G781" t="s">
-        <v>1905</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="782" spans="1:7">
@@ -24952,10 +24952,10 @@
         <v>1900</v>
       </c>
       <c r="F782" t="s">
-        <v>1901</v>
+        <v>1920</v>
       </c>
       <c r="G782" t="s">
-        <v>1920</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="783" spans="1:7">
@@ -24975,10 +24975,10 @@
         <v>1900</v>
       </c>
       <c r="F783" t="s">
-        <v>1901</v>
+        <v>1905</v>
       </c>
       <c r="G783" t="s">
-        <v>1905</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="784" spans="1:7">
@@ -24998,10 +24998,10 @@
         <v>1900</v>
       </c>
       <c r="F784" t="s">
-        <v>1901</v>
+        <v>1905</v>
       </c>
       <c r="G784" t="s">
-        <v>1905</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="785" spans="1:7">
@@ -25021,10 +25021,10 @@
         <v>1900</v>
       </c>
       <c r="F785" t="s">
-        <v>1901</v>
+        <v>1905</v>
       </c>
       <c r="G785" t="s">
-        <v>1905</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="786" spans="1:7">
@@ -25044,10 +25044,10 @@
         <v>1900</v>
       </c>
       <c r="F786" t="s">
-        <v>1901</v>
+        <v>1905</v>
       </c>
       <c r="G786" t="s">
-        <v>1905</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="787" spans="1:7">
@@ -25067,10 +25067,10 @@
         <v>1900</v>
       </c>
       <c r="F787" t="s">
-        <v>1901</v>
+        <v>1905</v>
       </c>
       <c r="G787" t="s">
-        <v>1905</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="788" spans="1:7">
@@ -25090,10 +25090,10 @@
         <v>1900</v>
       </c>
       <c r="F788" t="s">
-        <v>1901</v>
+        <v>1905</v>
       </c>
       <c r="G788" t="s">
-        <v>1905</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="789" spans="1:7">
@@ -25110,10 +25110,10 @@
         <v>34</v>
       </c>
       <c r="E789" t="s">
-        <v>1900</v>
+        <v>1935</v>
       </c>
       <c r="F789" t="s">
-        <v>1935</v>
+        <v>1901</v>
       </c>
       <c r="G789" t="s">
         <v>1902</v>
@@ -25136,10 +25136,10 @@
         <v>1900</v>
       </c>
       <c r="F790" t="s">
-        <v>1901</v>
+        <v>1905</v>
       </c>
       <c r="G790" t="s">
-        <v>1905</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="791" spans="1:7">
@@ -25156,13 +25156,13 @@
         <v>34</v>
       </c>
       <c r="E791" t="s">
-        <v>1900</v>
+        <v>1940</v>
       </c>
       <c r="F791" t="s">
-        <v>1940</v>
+        <v>1920</v>
       </c>
       <c r="G791" t="s">
-        <v>1920</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="792" spans="1:7">
@@ -25179,13 +25179,13 @@
         <v>34</v>
       </c>
       <c r="E792" t="s">
-        <v>1900</v>
+        <v>1935</v>
       </c>
       <c r="F792" t="s">
-        <v>1935</v>
+        <v>1943</v>
       </c>
       <c r="G792" t="s">
-        <v>1943</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="793" spans="1:7">
@@ -25205,10 +25205,10 @@
         <v>1900</v>
       </c>
       <c r="F793" t="s">
-        <v>1901</v>
+        <v>1905</v>
       </c>
       <c r="G793" t="s">
-        <v>1905</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="794" spans="1:7">
@@ -25225,13 +25225,13 @@
         <v>34</v>
       </c>
       <c r="E794" t="s">
-        <v>1900</v>
+        <v>1948</v>
       </c>
       <c r="F794" t="s">
-        <v>1948</v>
+        <v>1905</v>
       </c>
       <c r="G794" t="s">
-        <v>1905</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="795" spans="1:7">
@@ -25251,10 +25251,10 @@
         <v>1900</v>
       </c>
       <c r="F795" t="s">
-        <v>1901</v>
+        <v>1951</v>
       </c>
       <c r="G795" t="s">
-        <v>1951</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="796" spans="1:7">
@@ -25274,10 +25274,10 @@
         <v>1900</v>
       </c>
       <c r="F796" t="s">
-        <v>1901</v>
+        <v>1905</v>
       </c>
       <c r="G796" t="s">
-        <v>1905</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="797" spans="1:7">
@@ -25294,13 +25294,13 @@
         <v>34</v>
       </c>
       <c r="E797" t="s">
-        <v>1900</v>
+        <v>1956</v>
       </c>
       <c r="F797" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
       <c r="G797" t="s">
-        <v>1957</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="798" spans="1:7">
@@ -25317,13 +25317,13 @@
         <v>34</v>
       </c>
       <c r="E798" t="s">
-        <v>1900</v>
+        <v>1960</v>
       </c>
       <c r="F798" t="s">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="G798" t="s">
-        <v>1961</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="799" spans="1:7">
@@ -25343,10 +25343,10 @@
         <v>1900</v>
       </c>
       <c r="F799" t="s">
-        <v>1901</v>
+        <v>1905</v>
       </c>
       <c r="G799" t="s">
-        <v>1905</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="800" spans="1:7">
@@ -25366,10 +25366,10 @@
         <v>1900</v>
       </c>
       <c r="F800" t="s">
-        <v>1901</v>
+        <v>1905</v>
       </c>
       <c r="G800" t="s">
-        <v>1905</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="801" spans="1:7">
@@ -25389,10 +25389,10 @@
         <v>1900</v>
       </c>
       <c r="F801" t="s">
-        <v>1901</v>
+        <v>1905</v>
       </c>
       <c r="G801" t="s">
-        <v>1905</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="802" spans="1:7">
@@ -25412,10 +25412,10 @@
         <v>1900</v>
       </c>
       <c r="F802" t="s">
-        <v>1901</v>
+        <v>1905</v>
       </c>
       <c r="G802" t="s">
-        <v>1905</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="803" spans="1:7">
@@ -25435,10 +25435,10 @@
         <v>1900</v>
       </c>
       <c r="F803" t="s">
-        <v>1901</v>
+        <v>1905</v>
       </c>
       <c r="G803" t="s">
-        <v>1905</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="804" spans="1:7">
@@ -25458,10 +25458,10 @@
         <v>1900</v>
       </c>
       <c r="F804" t="s">
-        <v>1901</v>
+        <v>1905</v>
       </c>
       <c r="G804" t="s">
-        <v>1905</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="805" spans="1:7">
@@ -25481,10 +25481,10 @@
         <v>1900</v>
       </c>
       <c r="F805" t="s">
-        <v>1901</v>
+        <v>1905</v>
       </c>
       <c r="G805" t="s">
-        <v>1905</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="806" spans="1:7">
@@ -25504,10 +25504,10 @@
         <v>1900</v>
       </c>
       <c r="F806" t="s">
-        <v>1901</v>
+        <v>1905</v>
       </c>
       <c r="G806" t="s">
-        <v>1905</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="807" spans="1:7">
@@ -25527,10 +25527,10 @@
         <v>1900</v>
       </c>
       <c r="F807" t="s">
-        <v>1901</v>
+        <v>1905</v>
       </c>
       <c r="G807" t="s">
-        <v>1905</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="808" spans="1:7">
@@ -25616,13 +25616,13 @@
         <v>34</v>
       </c>
       <c r="E811" t="s">
-        <v>1982</v>
+        <v>1992</v>
       </c>
       <c r="F811" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="G811" t="s">
-        <v>1993</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="812" spans="1:7">
@@ -25688,10 +25688,10 @@
         <v>1982</v>
       </c>
       <c r="F814" t="s">
-        <v>1983</v>
+        <v>1993</v>
       </c>
       <c r="G814" t="s">
-        <v>1993</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="815" spans="1:7">
@@ -25708,13 +25708,13 @@
         <v>34</v>
       </c>
       <c r="E815" t="s">
-        <v>1982</v>
+        <v>2002</v>
       </c>
       <c r="F815" t="s">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="G815" t="s">
-        <v>2003</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="816" spans="1:7">
@@ -25846,13 +25846,13 @@
         <v>19</v>
       </c>
       <c r="E821" t="s">
-        <v>1982</v>
+        <v>2016</v>
       </c>
       <c r="F821" t="s">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="G821" t="s">
-        <v>2017</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="822" spans="1:7">
@@ -25869,13 +25869,13 @@
         <v>1987</v>
       </c>
       <c r="E822" t="s">
-        <v>1982</v>
+        <v>2020</v>
       </c>
       <c r="F822" t="s">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="G822" t="s">
-        <v>2021</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="823" spans="1:7">
@@ -25895,10 +25895,10 @@
         <v>1982</v>
       </c>
       <c r="F823" t="s">
-        <v>1983</v>
+        <v>2021</v>
       </c>
       <c r="G823" t="s">
-        <v>2021</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="824" spans="1:7">
@@ -25915,13 +25915,13 @@
         <v>1987</v>
       </c>
       <c r="E824" t="s">
-        <v>1982</v>
+        <v>2020</v>
       </c>
       <c r="F824" t="s">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="G824" t="s">
-        <v>2021</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="825" spans="1:7">
@@ -25938,13 +25938,13 @@
         <v>1232</v>
       </c>
       <c r="E825" t="s">
-        <v>1982</v>
+        <v>2020</v>
       </c>
       <c r="F825" t="s">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="G825" t="s">
-        <v>2021</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="826" spans="1:7">
@@ -25961,13 +25961,13 @@
         <v>1987</v>
       </c>
       <c r="E826" t="s">
-        <v>1982</v>
+        <v>2020</v>
       </c>
       <c r="F826" t="s">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="G826" t="s">
-        <v>2021</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="827" spans="1:7">
@@ -25984,13 +25984,13 @@
         <v>1987</v>
       </c>
       <c r="E827" t="s">
-        <v>1982</v>
+        <v>2020</v>
       </c>
       <c r="F827" t="s">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="G827" t="s">
-        <v>2021</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="828" spans="1:7">
@@ -26010,10 +26010,10 @@
         <v>1982</v>
       </c>
       <c r="F828" t="s">
-        <v>1983</v>
+        <v>2021</v>
       </c>
       <c r="G828" t="s">
-        <v>2021</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="829" spans="1:7">
@@ -26056,10 +26056,10 @@
         <v>1982</v>
       </c>
       <c r="F830" t="s">
-        <v>1983</v>
+        <v>1993</v>
       </c>
       <c r="G830" t="s">
-        <v>1993</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="831" spans="1:7">
@@ -26286,10 +26286,10 @@
         <v>2056</v>
       </c>
       <c r="F840" t="s">
-        <v>2057</v>
+        <v>2061</v>
       </c>
       <c r="G840" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="841" spans="1:7">
@@ -26309,10 +26309,10 @@
         <v>2056</v>
       </c>
       <c r="F841" t="s">
-        <v>2057</v>
+        <v>2061</v>
       </c>
       <c r="G841" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="842" spans="1:7">
@@ -26332,10 +26332,10 @@
         <v>2056</v>
       </c>
       <c r="F842" t="s">
-        <v>2057</v>
+        <v>2061</v>
       </c>
       <c r="G842" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="843" spans="1:7">
@@ -26355,10 +26355,10 @@
         <v>2056</v>
       </c>
       <c r="F843" t="s">
-        <v>2057</v>
+        <v>2061</v>
       </c>
       <c r="G843" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="844" spans="1:7">
@@ -26378,10 +26378,10 @@
         <v>2056</v>
       </c>
       <c r="F844" t="s">
-        <v>2057</v>
+        <v>2061</v>
       </c>
       <c r="G844" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="845" spans="1:7">
@@ -26401,10 +26401,10 @@
         <v>2056</v>
       </c>
       <c r="F845" t="s">
-        <v>2057</v>
+        <v>2061</v>
       </c>
       <c r="G845" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="846" spans="1:7">
@@ -26424,10 +26424,10 @@
         <v>2056</v>
       </c>
       <c r="F846" t="s">
-        <v>2057</v>
+        <v>2061</v>
       </c>
       <c r="G846" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="847" spans="1:7">
@@ -26444,13 +26444,13 @@
         <v>1987</v>
       </c>
       <c r="E847" t="s">
-        <v>2056</v>
+        <v>1992</v>
       </c>
       <c r="F847" t="s">
-        <v>1992</v>
+        <v>2076</v>
       </c>
       <c r="G847" t="s">
-        <v>2076</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="848" spans="1:7">
@@ -26467,13 +26467,13 @@
         <v>1987</v>
       </c>
       <c r="E848" t="s">
-        <v>2056</v>
+        <v>1992</v>
       </c>
       <c r="F848" t="s">
-        <v>1992</v>
+        <v>2076</v>
       </c>
       <c r="G848" t="s">
-        <v>2076</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="849" spans="1:7">
@@ -26490,13 +26490,13 @@
         <v>1232</v>
       </c>
       <c r="E849" t="s">
-        <v>2056</v>
+        <v>1992</v>
       </c>
       <c r="F849" t="s">
-        <v>1992</v>
+        <v>2076</v>
       </c>
       <c r="G849" t="s">
-        <v>2076</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="850" spans="1:7">
@@ -26513,13 +26513,13 @@
         <v>1987</v>
       </c>
       <c r="E850" t="s">
-        <v>2056</v>
+        <v>2083</v>
       </c>
       <c r="F850" t="s">
-        <v>2083</v>
+        <v>2076</v>
       </c>
       <c r="G850" t="s">
-        <v>2076</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="851" spans="1:7">
@@ -26536,13 +26536,13 @@
         <v>1987</v>
       </c>
       <c r="E851" t="s">
-        <v>2056</v>
+        <v>1992</v>
       </c>
       <c r="F851" t="s">
-        <v>1992</v>
+        <v>2076</v>
       </c>
       <c r="G851" t="s">
-        <v>2076</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="852" spans="1:7">
@@ -26559,13 +26559,13 @@
         <v>1987</v>
       </c>
       <c r="E852" t="s">
-        <v>2056</v>
+        <v>1992</v>
       </c>
       <c r="F852" t="s">
-        <v>1992</v>
+        <v>2076</v>
       </c>
       <c r="G852" t="s">
-        <v>2076</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="853" spans="1:7">
@@ -26585,10 +26585,10 @@
         <v>2056</v>
       </c>
       <c r="F853" t="s">
-        <v>2057</v>
+        <v>2061</v>
       </c>
       <c r="G853" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="854" spans="1:7">
@@ -26608,10 +26608,10 @@
         <v>2056</v>
       </c>
       <c r="F854" t="s">
-        <v>2057</v>
+        <v>2061</v>
       </c>
       <c r="G854" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="855" spans="1:7">
@@ -26631,10 +26631,10 @@
         <v>2056</v>
       </c>
       <c r="F855" t="s">
-        <v>2057</v>
+        <v>2061</v>
       </c>
       <c r="G855" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="856" spans="1:7">
@@ -26654,10 +26654,10 @@
         <v>2056</v>
       </c>
       <c r="F856" t="s">
-        <v>2057</v>
+        <v>2061</v>
       </c>
       <c r="G856" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="857" spans="1:7">
@@ -26677,10 +26677,10 @@
         <v>2056</v>
       </c>
       <c r="F857" t="s">
-        <v>2057</v>
+        <v>2061</v>
       </c>
       <c r="G857" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="858" spans="1:7">
@@ -26700,10 +26700,10 @@
         <v>2056</v>
       </c>
       <c r="F858" t="s">
-        <v>2057</v>
+        <v>2061</v>
       </c>
       <c r="G858" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="859" spans="1:7">
@@ -26723,10 +26723,10 @@
         <v>2056</v>
       </c>
       <c r="F859" t="s">
-        <v>2057</v>
+        <v>2061</v>
       </c>
       <c r="G859" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="860" spans="1:7">
@@ -26746,10 +26746,10 @@
         <v>2056</v>
       </c>
       <c r="F860" t="s">
-        <v>2057</v>
+        <v>2061</v>
       </c>
       <c r="G860" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="861" spans="1:7">
@@ -26769,10 +26769,10 @@
         <v>2056</v>
       </c>
       <c r="F861" t="s">
-        <v>2057</v>
+        <v>2061</v>
       </c>
       <c r="G861" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="862" spans="1:7">
@@ -26792,10 +26792,10 @@
         <v>2056</v>
       </c>
       <c r="F862" t="s">
-        <v>2057</v>
+        <v>2061</v>
       </c>
       <c r="G862" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="863" spans="1:7">
@@ -26815,10 +26815,10 @@
         <v>2056</v>
       </c>
       <c r="F863" t="s">
-        <v>2057</v>
+        <v>2061</v>
       </c>
       <c r="G863" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="864" spans="1:7">
@@ -26838,10 +26838,10 @@
         <v>2056</v>
       </c>
       <c r="F864" t="s">
-        <v>2057</v>
+        <v>2061</v>
       </c>
       <c r="G864" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="865" spans="1:7">
@@ -26861,10 +26861,10 @@
         <v>2056</v>
       </c>
       <c r="F865" t="s">
-        <v>2057</v>
+        <v>2061</v>
       </c>
       <c r="G865" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="866" spans="1:7">
@@ -26884,10 +26884,10 @@
         <v>2056</v>
       </c>
       <c r="F866" t="s">
-        <v>2057</v>
+        <v>2061</v>
       </c>
       <c r="G866" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="867" spans="1:7">
@@ -26927,10 +26927,10 @@
         <v>1987</v>
       </c>
       <c r="E868" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="F868" t="s">
-        <v>2123</v>
+        <v>2119</v>
       </c>
       <c r="G868" t="s">
         <v>2120</v>
@@ -26950,10 +26950,10 @@
         <v>1987</v>
       </c>
       <c r="E869" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="F869" t="s">
-        <v>2123</v>
+        <v>2119</v>
       </c>
       <c r="G869" t="s">
         <v>2120</v>
@@ -26973,10 +26973,10 @@
         <v>1987</v>
       </c>
       <c r="E870" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="F870" t="s">
-        <v>2123</v>
+        <v>2119</v>
       </c>
       <c r="G870" t="s">
         <v>2120</v>
@@ -26996,10 +26996,10 @@
         <v>1987</v>
       </c>
       <c r="E871" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="F871" t="s">
-        <v>2123</v>
+        <v>2119</v>
       </c>
       <c r="G871" t="s">
         <v>2120</v>
@@ -27019,10 +27019,10 @@
         <v>19</v>
       </c>
       <c r="E872" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="F872" t="s">
-        <v>2123</v>
+        <v>2119</v>
       </c>
       <c r="G872" t="s">
         <v>2120</v>
@@ -27042,10 +27042,10 @@
         <v>19</v>
       </c>
       <c r="E873" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="F873" t="s">
-        <v>2123</v>
+        <v>2119</v>
       </c>
       <c r="G873" t="s">
         <v>2120</v>
@@ -27065,10 +27065,10 @@
         <v>1987</v>
       </c>
       <c r="E874" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="F874" t="s">
-        <v>2123</v>
+        <v>2119</v>
       </c>
       <c r="G874" t="s">
         <v>2120</v>
@@ -27088,10 +27088,10 @@
         <v>1987</v>
       </c>
       <c r="E875" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="F875" t="s">
-        <v>2123</v>
+        <v>2119</v>
       </c>
       <c r="G875" t="s">
         <v>2120</v>
@@ -27111,10 +27111,10 @@
         <v>1232</v>
       </c>
       <c r="E876" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="F876" t="s">
-        <v>2123</v>
+        <v>2119</v>
       </c>
       <c r="G876" t="s">
         <v>2120</v>
@@ -27134,10 +27134,10 @@
         <v>19</v>
       </c>
       <c r="E877" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="F877" t="s">
-        <v>2123</v>
+        <v>2119</v>
       </c>
       <c r="G877" t="s">
         <v>2120</v>
@@ -27157,10 +27157,10 @@
         <v>1987</v>
       </c>
       <c r="E878" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="F878" t="s">
-        <v>2123</v>
+        <v>2119</v>
       </c>
       <c r="G878" t="s">
         <v>2120</v>
@@ -27180,10 +27180,10 @@
         <v>1987</v>
       </c>
       <c r="E879" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="F879" t="s">
-        <v>2123</v>
+        <v>2119</v>
       </c>
       <c r="G879" t="s">
         <v>2120</v>
@@ -27203,10 +27203,10 @@
         <v>1987</v>
       </c>
       <c r="E880" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="F880" t="s">
-        <v>2123</v>
+        <v>2119</v>
       </c>
       <c r="G880" t="s">
         <v>2120</v>
@@ -27226,10 +27226,10 @@
         <v>1987</v>
       </c>
       <c r="E881" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="F881" t="s">
-        <v>2123</v>
+        <v>2119</v>
       </c>
       <c r="G881" t="s">
         <v>2120</v>
@@ -27249,10 +27249,10 @@
         <v>1987</v>
       </c>
       <c r="E882" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="F882" t="s">
-        <v>2123</v>
+        <v>2119</v>
       </c>
       <c r="G882" t="s">
         <v>2120</v>
@@ -27272,10 +27272,10 @@
         <v>1232</v>
       </c>
       <c r="E883" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="F883" t="s">
-        <v>2123</v>
+        <v>2119</v>
       </c>
       <c r="G883" t="s">
         <v>2120</v>
@@ -27295,10 +27295,10 @@
         <v>1987</v>
       </c>
       <c r="E884" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="F884" t="s">
-        <v>2123</v>
+        <v>2119</v>
       </c>
       <c r="G884" t="s">
         <v>2120</v>
@@ -27318,10 +27318,10 @@
         <v>1987</v>
       </c>
       <c r="E885" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="F885" t="s">
-        <v>2123</v>
+        <v>2119</v>
       </c>
       <c r="G885" t="s">
         <v>2120</v>
@@ -27341,10 +27341,10 @@
         <v>1987</v>
       </c>
       <c r="E886" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="F886" t="s">
-        <v>2123</v>
+        <v>2119</v>
       </c>
       <c r="G886" t="s">
         <v>2120</v>
@@ -27364,10 +27364,10 @@
         <v>19</v>
       </c>
       <c r="E887" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="F887" t="s">
-        <v>2123</v>
+        <v>2119</v>
       </c>
       <c r="G887" t="s">
         <v>2120</v>
@@ -27387,10 +27387,10 @@
         <v>1987</v>
       </c>
       <c r="E888" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="F888" t="s">
-        <v>2123</v>
+        <v>2119</v>
       </c>
       <c r="G888" t="s">
         <v>2120</v>
@@ -27410,10 +27410,10 @@
         <v>1232</v>
       </c>
       <c r="E889" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
       <c r="F889" t="s">
-        <v>2123</v>
+        <v>2119</v>
       </c>
       <c r="G889" t="s">
         <v>2120</v>
@@ -27551,10 +27551,10 @@
         <v>2168</v>
       </c>
       <c r="F895" t="s">
-        <v>2169</v>
+        <v>2181</v>
       </c>
       <c r="G895" t="s">
-        <v>2181</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="896" spans="1:7">
@@ -27574,10 +27574,10 @@
         <v>2168</v>
       </c>
       <c r="F896" t="s">
-        <v>2169</v>
+        <v>2181</v>
       </c>
       <c r="G896" t="s">
-        <v>2181</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="897" spans="1:7">
@@ -27778,10 +27778,10 @@
         <v>1987</v>
       </c>
       <c r="E905" t="s">
+        <v>2168</v>
+      </c>
+      <c r="F905" t="s">
         <v>2201</v>
-      </c>
-      <c r="F905" t="s">
-        <v>2169</v>
       </c>
       <c r="G905" t="s">
         <v>2202</v>
@@ -27801,13 +27801,13 @@
         <v>1987</v>
       </c>
       <c r="E906" t="s">
-        <v>2201</v>
+        <v>2168</v>
       </c>
       <c r="F906" t="s">
-        <v>2169</v>
+        <v>2205</v>
       </c>
       <c r="G906" t="s">
-        <v>2205</v>
+        <v>2202</v>
       </c>
     </row>
     <row r="907" spans="1:7">
@@ -27824,10 +27824,10 @@
         <v>1987</v>
       </c>
       <c r="E907" t="s">
+        <v>2168</v>
+      </c>
+      <c r="F907" t="s">
         <v>2201</v>
-      </c>
-      <c r="F907" t="s">
-        <v>2169</v>
       </c>
       <c r="G907" t="s">
         <v>2202</v>

--- a/api/1/clv3/xlsx/en/HumanitarianPlan.xlsx
+++ b/api/1/clv3/xlsx/en/HumanitarianPlan.xlsx
@@ -28,12 +28,12 @@
     <t>codeforiati:plan-type</t>
   </si>
   <si>
+    <t>codeforiati:plan-start-date</t>
+  </si>
+  <si>
     <t>codeforiati:plan-end-date</t>
   </si>
   <si>
-    <t>codeforiati:plan-start-date</t>
-  </si>
-  <si>
     <t>codeforiati:plan-year</t>
   </si>
   <si>
@@ -49,12 +49,12 @@
     <t>Humanitarian needs and response plan</t>
   </si>
   <si>
+    <t>2025-01-01</t>
+  </si>
+  <si>
     <t>2025-12-31</t>
   </si>
   <si>
-    <t>2025-01-01</t>
-  </si>
-  <si>
     <t>2025</t>
   </si>
   <si>
@@ -355,12 +355,12 @@
     <t>Afghanistan Humanitarian Needs and Response Plan 2024</t>
   </si>
   <si>
+    <t>2024-01-01</t>
+  </si>
+  <si>
     <t>2024-12-31</t>
   </si>
   <si>
-    <t>2024-01-01</t>
-  </si>
-  <si>
     <t>2024</t>
   </si>
   <si>
@@ -712,12 +712,12 @@
     <t>Afghanistan Humanitarian Response Plan 2023</t>
   </si>
   <si>
+    <t>2023-01-01</t>
+  </si>
+  <si>
     <t>2023-12-31</t>
   </si>
   <si>
-    <t>2023-01-01</t>
-  </si>
-  <si>
     <t>2023</t>
   </si>
   <si>
@@ -841,24 +841,24 @@
     <t>Mongolia Dzud Early Action and Response Plan 2023</t>
   </si>
   <si>
+    <t>2022-12-01</t>
+  </si>
+  <si>
     <t>2023-05-31</t>
   </si>
   <si>
-    <t>2022-12-01</t>
-  </si>
-  <si>
     <t>OMOZ23</t>
   </si>
   <si>
     <t>Mozambique Cyclone Freddy, Floods and Cholera Response Plan 2023</t>
   </si>
   <si>
+    <t>2023-03-01</t>
+  </si>
+  <si>
     <t>2023-09-30</t>
   </si>
   <si>
-    <t>2023-03-01</t>
-  </si>
-  <si>
     <t>HMOZ23</t>
   </si>
   <si>
@@ -946,12 +946,12 @@
     <t>Sudan Emergency: Regional Refugee Response Plan 2023</t>
   </si>
   <si>
+    <t>2023-05-01</t>
+  </si>
+  <si>
     <t>2023-10-31</t>
   </si>
   <si>
-    <t>2023-05-01</t>
-  </si>
-  <si>
     <t>HSDN23</t>
   </si>
   <si>
@@ -1030,12 +1030,12 @@
     <t>Afghanistan Humanitarian Response Plan 2022</t>
   </si>
   <si>
+    <t>2022-01-01</t>
+  </si>
+  <si>
     <t>2022-12-31</t>
   </si>
   <si>
-    <t>2022-01-01</t>
-  </si>
-  <si>
     <t>2022</t>
   </si>
   <si>
@@ -1081,12 +1081,12 @@
     <t>Cuba Hurricane Ian Response - Plan of Action 2022</t>
   </si>
   <si>
+    <t>2022-10-20</t>
+  </si>
+  <si>
     <t>2023-03-31</t>
   </si>
   <si>
-    <t>2022-10-20</t>
-  </si>
-  <si>
     <t>RDRCRRP22</t>
   </si>
   <si>
@@ -1117,12 +1117,12 @@
     <t>Haïti Choléra+ Appel Éclair 2022</t>
   </si>
   <si>
+    <t>2022-10-16</t>
+  </si>
+  <si>
     <t>2023-04-15</t>
   </si>
   <si>
-    <t>2022-10-16</t>
-  </si>
-  <si>
     <t>FHTI22</t>
   </si>
   <si>
@@ -1180,12 +1180,12 @@
     <t>Malawi Flash Appeal 2022</t>
   </si>
   <si>
+    <t>2022-02-26</t>
+  </si>
+  <si>
     <t>2022-05-31</t>
   </si>
   <si>
-    <t>2022-02-26</t>
-  </si>
-  <si>
     <t>HMLI22</t>
   </si>
   <si>
@@ -1198,12 +1198,12 @@
     <t>Mozambique Gombe Emergency Response Plan 2022</t>
   </si>
   <si>
+    <t>2022-04-01</t>
+  </si>
+  <si>
     <t>2022-09-30</t>
   </si>
   <si>
-    <t>2022-04-01</t>
-  </si>
-  <si>
     <t>HMOZ22</t>
   </si>
   <si>
@@ -1255,12 +1255,12 @@
     <t>Philippines Super Typhoon Rai (Odette) Humanitarian Needs and Priorities 2022</t>
   </si>
   <si>
+    <t>2021-12-24</t>
+  </si>
+  <si>
     <t>2022-06-30</t>
   </si>
   <si>
-    <t>2021-12-24</t>
-  </si>
-  <si>
     <t>RREG22</t>
   </si>
   <si>
@@ -1378,12 +1378,12 @@
     <t>Afghanistan Flash Appeal 2021</t>
   </si>
   <si>
+    <t>2021-09-01</t>
+  </si>
+  <si>
     <t>2021-12-31</t>
   </si>
   <si>
-    <t>2021-09-01</t>
-  </si>
-  <si>
     <t>2021</t>
   </si>
   <si>
@@ -1477,12 +1477,12 @@
     <t>Escalation of Hostilities in the OPT Flash Appeal 2021</t>
   </si>
   <si>
+    <t>2021-05-27</t>
+  </si>
+  <si>
     <t>2021-08-27</t>
   </si>
   <si>
-    <t>2021-05-27</t>
-  </si>
-  <si>
     <t>HETH21</t>
   </si>
   <si>
@@ -1507,12 +1507,12 @@
     <t>Haiti Earthquake Flash Appeal 2021</t>
   </si>
   <si>
+    <t>2021-08-16</t>
+  </si>
+  <si>
     <t>2022-02-15</t>
   </si>
   <si>
-    <t>2021-08-16</t>
-  </si>
-  <si>
     <t>HHTI21</t>
   </si>
   <si>
@@ -1525,12 +1525,12 @@
     <t>Honduras Tropical Storm Eta Flash Appeal 2021</t>
   </si>
   <si>
+    <t>2020-11-15</t>
+  </si>
+  <si>
     <t>2021-06-30</t>
   </si>
   <si>
-    <t>2020-11-15</t>
-  </si>
-  <si>
     <t>HHND21</t>
   </si>
   <si>
@@ -1564,12 +1564,12 @@
     <t>Lebanon Emergency Response Plan 2021</t>
   </si>
   <si>
+    <t>2021-08-03</t>
+  </si>
+  <si>
     <t>2022-07-31</t>
   </si>
   <si>
-    <t>2021-08-03</t>
-  </si>
-  <si>
     <t>HLBY21</t>
   </si>
   <si>
@@ -1735,12 +1735,12 @@
     <t>Afghanistan Humanitarian Response Plan 2020</t>
   </si>
   <si>
+    <t>2020-01-01</t>
+  </si>
+  <si>
     <t>2020-12-31</t>
   </si>
   <si>
-    <t>2020-01-01</t>
-  </si>
-  <si>
     <t>2020</t>
   </si>
   <si>
@@ -1858,12 +1858,12 @@
     <t>Djibouti Flash Appeal 2020</t>
   </si>
   <si>
+    <t>2019-12-17</t>
+  </si>
+  <si>
     <t>2020-03-31</t>
   </si>
   <si>
-    <t>2019-12-17</t>
-  </si>
-  <si>
     <t>ODJI20</t>
   </si>
   <si>
@@ -1957,12 +1957,12 @@
     <t>Lebanon Flash Appeal 2020</t>
   </si>
   <si>
+    <t>2020-08-05</t>
+  </si>
+  <si>
     <t>2020-11-13</t>
   </si>
   <si>
-    <t>2020-08-05</t>
-  </si>
-  <si>
     <t>OLBN20</t>
   </si>
   <si>
@@ -1975,12 +1975,12 @@
     <t>Lesotho Flash Appeal 2019-2020</t>
   </si>
   <si>
+    <t>2019-11-01</t>
+  </si>
+  <si>
     <t>2020-04-30</t>
   </si>
   <si>
-    <t>2019-11-01</t>
-  </si>
-  <si>
     <t>OLBR20</t>
   </si>
   <si>
@@ -2170,12 +2170,12 @@
     <t>Afghanistan Humanitarian Response Plan 2019</t>
   </si>
   <si>
+    <t>2019-01-01</t>
+  </si>
+  <si>
     <t>2019-12-31</t>
   </si>
   <si>
-    <t>2019-01-01</t>
-  </si>
-  <si>
     <t>2019</t>
   </si>
   <si>
@@ -2386,12 +2386,12 @@
     <t>Zimbabwe Flash Appeal 2019</t>
   </si>
   <si>
+    <t>2019-02-01</t>
+  </si>
+  <si>
     <t>2020-04-29</t>
   </si>
   <si>
-    <t>2019-02-01</t>
-  </si>
-  <si>
     <t>FZWE1820</t>
   </si>
   <si>
@@ -2407,12 +2407,12 @@
     <t>Afghanistan Humanitarian Response Plan 2018</t>
   </si>
   <si>
+    <t>2018-01-01</t>
+  </si>
+  <si>
     <t>2018-12-31</t>
   </si>
   <si>
-    <t>2018-01-01</t>
-  </si>
-  <si>
     <t>2018</t>
   </si>
   <si>
@@ -2590,12 +2590,12 @@
     <t>Syrian Arab Republic Humanitarian Response Plan 2018</t>
   </si>
   <si>
+    <t>2018-11-30</t>
+  </si>
+  <si>
     <t>2018-12-30</t>
   </si>
   <si>
-    <t>2018-11-30</t>
-  </si>
-  <si>
     <t>RSYR18</t>
   </si>
   <si>
@@ -2632,12 +2632,12 @@
     <t>Regional Refugee and Migrant Response Plan for Europe 2017</t>
   </si>
   <si>
+    <t>2017-01-01</t>
+  </si>
+  <si>
     <t>2017-12-31</t>
   </si>
   <si>
-    <t>2017-01-01</t>
-  </si>
-  <si>
     <t>2017</t>
   </si>
   <si>
@@ -2716,12 +2716,12 @@
     <t>Dominica Hurricane Maria Flash Appeal 2017</t>
   </si>
   <si>
+    <t>2017-09-28</t>
+  </si>
+  <si>
     <t>2017-12-29</t>
   </si>
   <si>
-    <t>2017-09-28</t>
-  </si>
-  <si>
     <t>OPRK17</t>
   </si>
   <si>
@@ -2761,12 +2761,12 @@
     <t>Kenya Flash Appeal 2017</t>
   </si>
   <si>
+    <t>2017-02-10</t>
+  </si>
+  <si>
     <t>2017-11-30</t>
   </si>
   <si>
-    <t>2017-02-10</t>
-  </si>
-  <si>
     <t>HLBY17</t>
   </si>
   <si>
@@ -2779,12 +2779,12 @@
     <t>Madagascar Tropical Cyclone Enawo Flash Appeal 2017</t>
   </si>
   <si>
+    <t>2017-03-20</t>
+  </si>
+  <si>
     <t>2017-06-20</t>
   </si>
   <si>
-    <t>2017-03-20</t>
-  </si>
-  <si>
     <t>HMLI17</t>
   </si>
   <si>
@@ -2803,12 +2803,12 @@
     <t>Mozambique Cyclone Dineo Flash Appeal 2017</t>
   </si>
   <si>
+    <t>2017-02-28</t>
+  </si>
+  <si>
     <t>2017-05-31</t>
   </si>
   <si>
-    <t>2017-02-28</t>
-  </si>
-  <si>
     <t>HMMR17</t>
   </si>
   <si>
@@ -2845,12 +2845,12 @@
     <t>Perú Costa Norte Flash Appeal 2017</t>
   </si>
   <si>
+    <t>2017-04-01</t>
+  </si>
+  <si>
     <t>2017-10-31</t>
   </si>
   <si>
-    <t>2017-04-01</t>
-  </si>
-  <si>
     <t>HCOG17</t>
   </si>
   <si>
@@ -2917,12 +2917,12 @@
     <t>Regional Refugee and Migrant Response Plan for Europe 2016</t>
   </si>
   <si>
+    <t>2016-01-01</t>
+  </si>
+  <si>
     <t>2016-12-31</t>
   </si>
   <si>
-    <t>2016-01-01</t>
-  </si>
-  <si>
     <t>2016</t>
   </si>
   <si>
@@ -2998,24 +2998,24 @@
     <t>Ecuador Terremoto Flash Appeal 2016</t>
   </si>
   <si>
+    <t>2016-04-16</t>
+  </si>
+  <si>
     <t>2016-10-31</t>
   </si>
   <si>
-    <t>2016-04-16</t>
-  </si>
-  <si>
     <t>FFJI16</t>
   </si>
   <si>
     <t>Fiji Tropical Cyclone Winston Flash Appeal 2016</t>
   </si>
   <si>
+    <t>2016-02-20</t>
+  </si>
+  <si>
     <t>2016-05-30</t>
   </si>
   <si>
-    <t>2016-02-20</t>
-  </si>
-  <si>
     <t>HGMB16</t>
   </si>
   <si>
@@ -3091,12 +3091,12 @@
     <t>Iraq Mosul Flash Appeal 2016</t>
   </si>
   <si>
+    <t>2016-07-20</t>
+  </si>
+  <si>
     <t>2016-10-01</t>
   </si>
   <si>
-    <t>2016-07-20</t>
-  </si>
-  <si>
     <t>HMMR16</t>
   </si>
   <si>
@@ -3181,12 +3181,12 @@
     <t>Zimbabwe Humanitarian Response Plan 2016</t>
   </si>
   <si>
+    <t>2016-04-01</t>
+  </si>
+  <si>
     <t>2017-03-31</t>
   </si>
   <si>
-    <t>2016-04-01</t>
-  </si>
-  <si>
     <t>HAFG15</t>
   </si>
   <si>
@@ -3196,12 +3196,12 @@
     <t>Strategic response plan</t>
   </si>
   <si>
+    <t>2015-01-01</t>
+  </si>
+  <si>
     <t>2015-12-31</t>
   </si>
   <si>
-    <t>2015-01-01</t>
-  </si>
-  <si>
     <t>2015</t>
   </si>
   <si>
@@ -3259,12 +3259,12 @@
     <t>Guatemala Plan de Respuesta Sequia 2015</t>
   </si>
   <si>
+    <t>2014-11-03</t>
+  </si>
+  <si>
     <t>2015-09-30</t>
   </si>
   <si>
-    <t>2014-11-03</t>
-  </si>
-  <si>
     <t>FHTI15</t>
   </si>
   <si>
@@ -3289,12 +3289,12 @@
     <t>Vanuatu Emergency Response Plan for Tropical Cyclone PAM 2015</t>
   </si>
   <si>
+    <t>2015-03-24</t>
+  </si>
+  <si>
     <t>2015-10-31</t>
   </si>
   <si>
-    <t>2015-03-24</t>
-  </si>
-  <si>
     <t>HIRQ15</t>
   </si>
   <si>
@@ -3307,12 +3307,12 @@
     <t>Libya Humanitarian Appeal 2014- 2015</t>
   </si>
   <si>
+    <t>2014-10-01</t>
+  </si>
+  <si>
     <t>2015-05-31</t>
   </si>
   <si>
-    <t>2014-10-01</t>
-  </si>
-  <si>
     <t>HMLI15</t>
   </si>
   <si>
@@ -3424,12 +3424,12 @@
     <t>Afghanistan Strategic Response Plan 2014</t>
   </si>
   <si>
+    <t>2014-01-01</t>
+  </si>
+  <si>
     <t>2014-12-31</t>
   </si>
   <si>
-    <t>2014-01-01</t>
-  </si>
-  <si>
     <t>2014</t>
   </si>
   <si>
@@ -3568,24 +3568,24 @@
     <t>Philippines Bohol Earthquake Flash Appeal 2014</t>
   </si>
   <si>
+    <t>2013-10-22</t>
+  </si>
+  <si>
     <t>2014-04-22</t>
   </si>
   <si>
-    <t>2013-10-22</t>
-  </si>
-  <si>
     <t>SPHL1314</t>
   </si>
   <si>
     <t>Philippines Typhoon Haiyan Strategic Response Plan 2014</t>
   </si>
   <si>
+    <t>2013-11-08</t>
+  </si>
+  <si>
     <t>2014-11-07</t>
   </si>
   <si>
-    <t>2013-11-08</t>
-  </si>
-  <si>
     <t>HPHL1314</t>
   </si>
   <si>
@@ -3601,12 +3601,12 @@
     <t>Philippines Zamboanga Crisis Flash Appeal 2014</t>
   </si>
   <si>
+    <t>2013-10-01</t>
+  </si>
+  <si>
     <t>2014-08-31</t>
   </si>
   <si>
-    <t>2013-10-01</t>
-  </si>
-  <si>
     <t>SCOD14</t>
   </si>
   <si>
@@ -3874,12 +3874,12 @@
     <t>2012+ Kenya Emergency Humanitarian Response Plan</t>
   </si>
   <si>
+    <t>2012-01-01</t>
+  </si>
+  <si>
     <t>2012-12-31</t>
   </si>
   <si>
-    <t>2012-01-01</t>
-  </si>
-  <si>
     <t>2012</t>
   </si>
   <si>
@@ -3952,12 +3952,12 @@
     <t>Lesotho Food Insecurity (September 2012 - March 2013)</t>
   </si>
   <si>
+    <t>2012-09-18</t>
+  </si>
+  <si>
     <t>2013-03-25</t>
   </si>
   <si>
-    <t>2012-09-18</t>
-  </si>
-  <si>
     <t>CLBR12</t>
   </si>
   <si>
@@ -4030,12 +4030,12 @@
     <t>Syria Humanitarian Assistance Response Plan (SHARP) 2012</t>
   </si>
   <si>
+    <t>2012-06-05</t>
+  </si>
+  <si>
     <t>2012-12-05</t>
   </si>
   <si>
-    <t>2012-06-05</t>
-  </si>
-  <si>
     <t>CYEM12</t>
   </si>
   <si>
@@ -4108,12 +4108,12 @@
     <t>El Salvador Flash Appeal (October 2011 - April 2012)</t>
   </si>
   <si>
+    <t>2011-10-25</t>
+  </si>
+  <si>
     <t>2012-04-25</t>
   </si>
   <si>
-    <t>2011-10-25</t>
-  </si>
-  <si>
     <t>CHTI1011</t>
   </si>
   <si>
@@ -4144,24 +4144,24 @@
     <t>Namibia Flash Appeal (April - October 2011)</t>
   </si>
   <si>
+    <t>2011-04-11</t>
+  </si>
+  <si>
     <t>2011-10-11</t>
   </si>
   <si>
-    <t>2011-04-11</t>
-  </si>
-  <si>
     <t>FNIC1112</t>
   </si>
   <si>
     <t>Nicaragua Flash Appeal (October 2011 - April 2012)</t>
   </si>
   <si>
+    <t>2011-10-27</t>
+  </si>
+  <si>
     <t>2012-04-26</t>
   </si>
   <si>
-    <t>2011-10-27</t>
-  </si>
-  <si>
     <t>CNER11</t>
   </si>
   <si>
@@ -4174,12 +4174,12 @@
     <t>Pakistan Rapid Response Plan Floods 2011 (September - March 2012)</t>
   </si>
   <si>
+    <t>2011-09-15</t>
+  </si>
+  <si>
     <t>2012-06-30</t>
   </si>
   <si>
-    <t>2011-09-15</t>
-  </si>
-  <si>
     <t>FXLBYREG11</t>
   </si>
   <si>
@@ -4255,12 +4255,12 @@
     <t>Afghanistan Humanitarian Action Plan 2010</t>
   </si>
   <si>
+    <t>2010-01-01</t>
+  </si>
+  <si>
     <t>2010-12-31</t>
   </si>
   <si>
-    <t>2010-01-01</t>
-  </si>
-  <si>
     <t>2010</t>
   </si>
   <si>
@@ -4270,12 +4270,12 @@
     <t>Burkina Faso Emergency Humanitarian Action Plan 2010</t>
   </si>
   <si>
+    <t>2010-08-01</t>
+  </si>
+  <si>
     <t>2011-01-31</t>
   </si>
   <si>
-    <t>2010-08-01</t>
-  </si>
-  <si>
     <t>CCAF10</t>
   </si>
   <si>
@@ -4300,36 +4300,36 @@
     <t>El Salvador Flash Appeal (Revised) (November 2009 - May 2010)</t>
   </si>
   <si>
+    <t>2009-11-01</t>
+  </si>
+  <si>
     <t>2010-05-31</t>
   </si>
   <si>
-    <t>2009-11-01</t>
-  </si>
-  <si>
     <t>FGTM10</t>
   </si>
   <si>
     <t>Guatemala Flash Appeal (Revised) (June - December 2010)</t>
   </si>
   <si>
+    <t>2010-06-10</t>
+  </si>
+  <si>
     <t>2010-12-09</t>
   </si>
   <si>
-    <t>2010-06-10</t>
-  </si>
-  <si>
     <t>CGTM10</t>
   </si>
   <si>
     <t>Guatemala Food Insecurity and Acute Malnutrition Appeal 2010</t>
   </si>
   <si>
+    <t>2010-02-12</t>
+  </si>
+  <si>
     <t>2010-08-11</t>
   </si>
   <si>
-    <t>2010-02-12</t>
-  </si>
-  <si>
     <t>FHTI10</t>
   </si>
   <si>
@@ -4357,12 +4357,12 @@
     <t>Kyrgyzstan Flash Appeal (Revised) (June 2010 - June 2011)</t>
   </si>
   <si>
+    <t>2010-06-01</t>
+  </si>
+  <si>
     <t>2011-06-30</t>
   </si>
   <si>
-    <t>2010-06-01</t>
-  </si>
-  <si>
     <t>CMNG1011</t>
   </si>
   <si>
@@ -4465,12 +4465,12 @@
     <t>Afghanistan Humanitarian Action Plan 2009</t>
   </si>
   <si>
+    <t>2009-01-01</t>
+  </si>
+  <si>
     <t>2009-12-31</t>
   </si>
   <si>
-    <t>2009-01-01</t>
-  </si>
-  <si>
     <t>2009</t>
   </si>
   <si>
@@ -4480,12 +4480,12 @@
     <t>Burkina Faso Flash Appeal (September 2009 - February 2010)</t>
   </si>
   <si>
+    <t>2009-09-10</t>
+  </si>
+  <si>
     <t>2010-03-09</t>
   </si>
   <si>
-    <t>2009-09-10</t>
-  </si>
-  <si>
     <t>CCAF09</t>
   </si>
   <si>
@@ -4549,24 +4549,24 @@
     <t>Madagascar Flash Appeal (Revised) (April - October 2009)</t>
   </si>
   <si>
+    <t>2009-04-01</t>
+  </si>
+  <si>
     <t>2009-10-31</t>
   </si>
   <si>
-    <t>2009-04-01</t>
-  </si>
-  <si>
     <t>FNAM09</t>
   </si>
   <si>
     <t>Namibia Flash Appeal (Revised) (March - November 2009)</t>
   </si>
   <si>
+    <t>2009-03-20</t>
+  </si>
+  <si>
     <t>2009-09-30</t>
   </si>
   <si>
-    <t>2009-03-20</t>
-  </si>
-  <si>
     <t>ONPL09</t>
   </si>
   <si>
@@ -4588,12 +4588,12 @@
     <t>Philippines Flash Appeal (Revised) (October 2009 - March 2010)</t>
   </si>
   <si>
+    <t>2009-10-03</t>
+  </si>
+  <si>
     <t>2010-03-31</t>
   </si>
   <si>
-    <t>2009-10-03</t>
-  </si>
-  <si>
     <t>CSOM09</t>
   </si>
   <si>
@@ -4618,12 +4618,12 @@
     <t>Syria Drought Response Plan (Revised) (July 2009 - June 2010)</t>
   </si>
   <si>
+    <t>2009-07-15</t>
+  </si>
+  <si>
     <t>2010-06-14</t>
   </si>
   <si>
-    <t>2009-07-15</t>
-  </si>
-  <si>
     <t>OTJK09</t>
   </si>
   <si>
@@ -4681,12 +4681,12 @@
     <t>Afghanistan Joint Appeal 2008: Humanitarian Consequences of Rise in Food Prices (February - June 2008)</t>
   </si>
   <si>
+    <t>2008-02-01</t>
+  </si>
+  <si>
     <t>2008-06-30</t>
   </si>
   <si>
-    <t>2008-02-01</t>
-  </si>
-  <si>
     <t>2008</t>
   </si>
   <si>
@@ -4696,12 +4696,12 @@
     <t>Afghanistan Joint Emergency Appeal 2008: High Food Price and Drought Crisis (July 2008 - June 2009)</t>
   </si>
   <si>
+    <t>2008-07-01</t>
+  </si>
+  <si>
     <t>2009-06-30</t>
   </si>
   <si>
-    <t>2008-07-01</t>
-  </si>
-  <si>
     <t>FBOL08</t>
   </si>
   <si>
@@ -4717,12 +4717,12 @@
     <t>Central African Republic 2008</t>
   </si>
   <si>
+    <t>2008-01-01</t>
+  </si>
+  <si>
     <t>2008-12-31</t>
   </si>
   <si>
-    <t>2008-01-01</t>
-  </si>
-  <si>
     <t>CTCD08</t>
   </si>
   <si>
@@ -4753,24 +4753,24 @@
     <t>Djibouti Joint Appeal 2008: Response Plan for Drought, Food and Nutrition Crisis</t>
   </si>
   <si>
+    <t>2008-08-01</t>
+  </si>
+  <si>
     <t>2009-02-28</t>
   </si>
   <si>
-    <t>2008-08-01</t>
-  </si>
-  <si>
     <t>FGEO0809</t>
   </si>
   <si>
     <t>Georgia Crisis Flash Appeal (Revised) 2008</t>
   </si>
   <si>
+    <t>2008-08-09</t>
+  </si>
+  <si>
     <t>2009-02-09</t>
   </si>
   <si>
-    <t>2008-08-09</t>
-  </si>
-  <si>
     <t>FHTI0809</t>
   </si>
   <si>
@@ -4786,12 +4786,12 @@
     <t>Honduras Flash Appeal (Updated) (November - April) 2008</t>
   </si>
   <si>
+    <t>2008-11-01</t>
+  </si>
+  <si>
     <t>2009-04-30</t>
   </si>
   <si>
-    <t>2008-11-01</t>
-  </si>
-  <si>
     <t>CIRQ08</t>
   </si>
   <si>
@@ -4810,12 +4810,12 @@
     <t>Kyrgyzstan Flash Appeal (Revised) 2008</t>
   </si>
   <si>
+    <t>2008-12-01</t>
+  </si>
+  <si>
     <t>2009-05-31</t>
   </si>
   <si>
-    <t>2008-12-01</t>
-  </si>
-  <si>
     <t>OLAO0809</t>
   </si>
   <si>
@@ -4846,12 +4846,12 @@
     <t>Myanmar Flash Appeal (Revised) 2008</t>
   </si>
   <si>
+    <t>2008-05-01</t>
+  </si>
+  <si>
     <t>2008-11-30</t>
   </si>
   <si>
-    <t>2008-05-01</t>
-  </si>
-  <si>
     <t>ONPL08</t>
   </si>
   <si>
@@ -4948,12 +4948,12 @@
     <t>Bolivia Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2007-02-22</t>
+  </si>
+  <si>
     <t>2007-08-21</t>
   </si>
   <si>
-    <t>2007-02-22</t>
-  </si>
-  <si>
     <t>2007</t>
   </si>
   <si>
@@ -4963,24 +4963,24 @@
     <t>Burkina Faso Floods Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2007-11-01</t>
+  </si>
+  <si>
     <t>2008-01-31</t>
   </si>
   <si>
-    <t>2007-11-01</t>
-  </si>
-  <si>
     <t>CBDI07</t>
   </si>
   <si>
     <t>Burundi 2007</t>
   </si>
   <si>
+    <t>2007-01-01</t>
+  </si>
+  <si>
     <t>2007-12-31</t>
   </si>
   <si>
-    <t>2007-01-01</t>
-  </si>
-  <si>
     <t>CCAF07</t>
   </si>
   <si>
@@ -5020,12 +5020,12 @@
     <t>Ghana Floods Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2007-09-01</t>
+  </si>
+  <si>
     <t>2008-03-31</t>
   </si>
   <si>
-    <t>2007-09-01</t>
-  </si>
-  <si>
     <t>CXGLR07</t>
   </si>
   <si>
@@ -5047,36 +5047,36 @@
     <t>Korea DPR Flash Appeal: Floods Emergency 2007</t>
   </si>
   <si>
+    <t>2007-08-28</t>
+  </si>
+  <si>
     <t>2007-11-30</t>
   </si>
   <si>
-    <t>2007-08-28</t>
-  </si>
-  <si>
     <t>OLBN07</t>
   </si>
   <si>
     <t>Lebanon Crisis Appeal 2007</t>
   </si>
   <si>
+    <t>2007-06-04</t>
+  </si>
+  <si>
     <t>2007-09-03</t>
   </si>
   <si>
-    <t>2007-06-04</t>
-  </si>
-  <si>
     <t>FLSO0708</t>
   </si>
   <si>
     <t>Lesotho Drought Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2007-07-28</t>
+  </si>
+  <si>
     <t>2008-01-28</t>
   </si>
   <si>
-    <t>2007-07-28</t>
-  </si>
-  <si>
     <t>CLBR07</t>
   </si>
   <si>
@@ -5089,24 +5089,24 @@
     <t>Madagascar Floods Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2007-03-15</t>
+  </si>
+  <si>
     <t>2007-09-15</t>
   </si>
   <si>
-    <t>2007-03-15</t>
-  </si>
-  <si>
     <t>FMOZ07</t>
   </si>
   <si>
     <t>Mozambique Floods and Cyclone Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2007-03-01</t>
+  </si>
+  <si>
     <t>2007-06-30</t>
   </si>
   <si>
-    <t>2007-03-01</t>
-  </si>
-  <si>
     <t>ONPL07</t>
   </si>
   <si>
@@ -5119,12 +5119,12 @@
     <t>Nicaragua Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2007-09-07</t>
+  </si>
+  <si>
     <t>2008-02-28</t>
   </si>
   <si>
-    <t>2007-09-07</t>
-  </si>
-  <si>
     <t>ORUS07</t>
   </si>
   <si>
@@ -5137,12 +5137,12 @@
     <t>Pakistan Cyclone and Floods Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2007-07-15</t>
+  </si>
+  <si>
     <t>2007-10-31</t>
   </si>
   <si>
-    <t>2007-07-15</t>
-  </si>
-  <si>
     <t>FPER0708</t>
   </si>
   <si>
@@ -5200,12 +5200,12 @@
     <t>Swaziland Drought Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2007-07-20</t>
+  </si>
+  <si>
     <t>2008-01-20</t>
   </si>
   <si>
-    <t>2007-07-20</t>
-  </si>
-  <si>
     <t>CTLS07</t>
   </si>
   <si>
@@ -5254,12 +5254,12 @@
     <t>Afghanistan Drought Joint Appeal 2006</t>
   </si>
   <si>
+    <t>2006-07-01</t>
+  </si>
+  <si>
     <t>2006-12-31</t>
   </si>
   <si>
-    <t>2006-07-01</t>
-  </si>
-  <si>
     <t>2006</t>
   </si>
   <si>
@@ -5308,24 +5308,24 @@
     <t>Ethiopia Floods Joint Appeal 2006</t>
   </si>
   <si>
+    <t>2006-08-25</t>
+  </si>
+  <si>
     <t>2006-11-25</t>
   </si>
   <si>
-    <t>2006-08-25</t>
-  </si>
-  <si>
     <t>OETH0607</t>
   </si>
   <si>
     <t>Ethiopia: 2006 Govt-UN Joint Emergency Flood Appeal for Somali Region</t>
   </si>
   <si>
+    <t>2006-11-23</t>
+  </si>
+  <si>
     <t>2007-01-22</t>
   </si>
   <si>
-    <t>2006-11-23</t>
-  </si>
-  <si>
     <t>CXGLR06</t>
   </si>
   <si>
@@ -5344,12 +5344,12 @@
     <t>Guinea-Bissau 2006</t>
   </si>
   <si>
+    <t>2006-05-01</t>
+  </si>
+  <si>
     <t>2006-11-30</t>
   </si>
   <si>
-    <t>2006-05-01</t>
-  </si>
-  <si>
     <t>CXHAF06</t>
   </si>
   <si>
@@ -5368,12 +5368,12 @@
     <t>Kenya 2006</t>
   </si>
   <si>
+    <t>2006-10-16</t>
+  </si>
+  <si>
     <t>2007-04-15</t>
   </si>
   <si>
-    <t>2006-10-16</t>
-  </si>
-  <si>
     <t>FKEN06</t>
   </si>
   <si>
@@ -5389,12 +5389,12 @@
     <t>Lebanon Crisis 2006</t>
   </si>
   <si>
+    <t>2006-07-24</t>
+  </si>
+  <si>
     <t>2006-10-23</t>
   </si>
   <si>
-    <t>2006-07-24</t>
-  </si>
-  <si>
     <t>CLBR06</t>
   </si>
   <si>
@@ -5443,12 +5443,12 @@
     <t>Somalia: 2006 Flood Response Plan</t>
   </si>
   <si>
+    <t>2006-12-05</t>
+  </si>
+  <si>
     <t>2007-03-05</t>
   </si>
   <si>
-    <t>2006-12-05</t>
-  </si>
-  <si>
     <t>OLKA06</t>
   </si>
   <si>
@@ -5509,12 +5509,12 @@
     <t>Angola Marburg VHF 2005</t>
   </si>
   <si>
+    <t>2005-04-01</t>
+  </si>
+  <si>
     <t>2005-06-30</t>
   </si>
   <si>
-    <t>2005-04-01</t>
-  </si>
-  <si>
     <t>2005</t>
   </si>
   <si>
@@ -5524,24 +5524,24 @@
     <t>Benin 2005</t>
   </si>
   <si>
+    <t>2005-05-01</t>
+  </si>
+  <si>
     <t>2005-10-31</t>
   </si>
   <si>
-    <t>2005-05-01</t>
-  </si>
-  <si>
     <t>CBDI05</t>
   </si>
   <si>
     <t>Burundi 2005</t>
   </si>
   <si>
+    <t>2005-01-01</t>
+  </si>
+  <si>
     <t>2005-12-31</t>
   </si>
   <si>
-    <t>2005-01-01</t>
-  </si>
-  <si>
     <t>CCAF05</t>
   </si>
   <si>
@@ -5617,12 +5617,12 @@
     <t>Guyana 2005</t>
   </si>
   <si>
+    <t>2005-02-01</t>
+  </si>
+  <si>
     <t>2005-08-01</t>
   </si>
   <si>
-    <t>2005-02-01</t>
-  </si>
-  <si>
     <t>FXINDTSU05</t>
   </si>
   <si>
@@ -5644,12 +5644,12 @@
     <t>Niger 2005</t>
   </si>
   <si>
+    <t>2005-06-01</t>
+  </si>
+  <si>
     <t>2005-09-30</t>
   </si>
   <si>
-    <t>2005-06-01</t>
-  </si>
-  <si>
     <t>CCOG05</t>
   </si>
   <si>
@@ -5668,12 +5668,12 @@
     <t>South Asia Earthquake 2005</t>
   </si>
   <si>
+    <t>2005-10-11</t>
+  </si>
+  <si>
     <t>2006-04-10</t>
   </si>
   <si>
-    <t>2005-10-11</t>
-  </si>
-  <si>
     <t>CSDN05</t>
   </si>
   <si>
@@ -5698,12 +5698,12 @@
     <t>West and Central Africa Region Cholera 2005</t>
   </si>
   <si>
+    <t>2005-11-01</t>
+  </si>
+  <si>
     <t>2006-05-31</t>
   </si>
   <si>
-    <t>2005-11-01</t>
-  </si>
-  <si>
     <t>CPSE05</t>
   </si>
   <si>
@@ -5716,12 +5716,12 @@
     <t>Afghanistan UN-Government Drought Appeal 2004</t>
   </si>
   <si>
+    <t>2004-09-01</t>
+  </si>
+  <si>
     <t>2004-12-31</t>
   </si>
   <si>
-    <t>2004-09-01</t>
-  </si>
-  <si>
     <t>2004</t>
   </si>
   <si>
@@ -5740,24 +5740,24 @@
     <t>Bangladesh 2004</t>
   </si>
   <si>
+    <t>2004-08-01</t>
+  </si>
+  <si>
     <t>2005-01-31</t>
   </si>
   <si>
-    <t>2004-08-01</t>
-  </si>
-  <si>
     <t>FBOL0405</t>
   </si>
   <si>
     <t>Bolivia 2004</t>
   </si>
   <si>
+    <t>2004-11-01</t>
+  </si>
+  <si>
     <t>2005-05-31</t>
   </si>
   <si>
-    <t>2004-11-01</t>
-  </si>
-  <si>
     <t>CBDI04</t>
   </si>
   <si>
@@ -5884,24 +5884,24 @@
     <t>Madagascar 2004</t>
   </si>
   <si>
+    <t>2004-03-19</t>
+  </si>
+  <si>
     <t>2004-06-19</t>
   </si>
   <si>
-    <t>2004-03-19</t>
-  </si>
-  <si>
     <t>FPHL0405</t>
   </si>
   <si>
     <t>Philippines 2004</t>
   </si>
   <si>
+    <t>2004-12-15</t>
+  </si>
+  <si>
     <t>2005-03-15</t>
   </si>
   <si>
-    <t>2004-12-15</t>
-  </si>
-  <si>
     <t>CSLE04</t>
   </si>
   <si>
@@ -5962,12 +5962,12 @@
     <t>Afghanistan TAPA 2003</t>
   </si>
   <si>
+    <t>2003-01-01</t>
+  </si>
+  <si>
     <t>2003-12-31</t>
   </si>
   <si>
-    <t>2003-01-01</t>
-  </si>
-  <si>
     <t>2003</t>
   </si>
   <si>
@@ -5992,12 +5992,12 @@
     <t>Central African Republic 2003</t>
   </si>
   <si>
+    <t>2003-04-01</t>
+  </si>
+  <si>
     <t>2003-06-30</t>
   </si>
   <si>
-    <t>2003-04-01</t>
-  </si>
-  <si>
     <t>CRUS03</t>
   </si>
   <si>
@@ -6022,12 +6022,12 @@
     <t>Côte d'Ivoire and the West Africa Sub-Region 2002-2003</t>
   </si>
   <si>
+    <t>2002-11-01</t>
+  </si>
+  <si>
     <t>2003-01-31</t>
   </si>
   <si>
-    <t>2002-11-01</t>
-  </si>
-  <si>
     <t>CPRK03</t>
   </si>
   <si>
@@ -6064,24 +6064,24 @@
     <t>Haiti (PIR) 2003</t>
   </si>
   <si>
+    <t>2003-03-01</t>
+  </si>
+  <si>
     <t>2003-08-31</t>
   </si>
   <si>
-    <t>2003-03-01</t>
-  </si>
-  <si>
     <t>CLSO0304</t>
   </si>
   <si>
     <t>Humanitarian Crisis in Southern Africa - LESOTHO (July 2003 - June 2004)</t>
   </si>
   <si>
+    <t>2003-07-01</t>
+  </si>
+  <si>
     <t>2004-06-30</t>
   </si>
   <si>
-    <t>2003-07-01</t>
-  </si>
-  <si>
     <t>CMWI03</t>
   </si>
   <si>
@@ -6184,12 +6184,12 @@
     <t>Afghanistan 2002 (ITAP for the Afghan People)</t>
   </si>
   <si>
+    <t>2001-10-01</t>
+  </si>
+  <si>
     <t>2002-12-31</t>
   </si>
   <si>
-    <t>2001-10-01</t>
-  </si>
-  <si>
     <t>2002</t>
   </si>
   <si>
@@ -6370,12 +6370,12 @@
     <t>Afghanistan 2001</t>
   </si>
   <si>
+    <t>2001-01-01</t>
+  </si>
+  <si>
     <t>2001-09-30</t>
   </si>
   <si>
-    <t>2001-01-01</t>
-  </si>
-  <si>
     <t>2001</t>
   </si>
   <si>
@@ -6520,10 +6520,10 @@
     <t>Angola 2000</t>
   </si>
   <si>
+    <t>2000-01-01</t>
+  </si>
+  <si>
     <t>2000-12-31</t>
-  </si>
-  <si>
-    <t>2000-01-01</t>
   </si>
   <si>
     <t>2000</t>
@@ -7055,10 +7055,10 @@
         <v>19</v>
       </c>
       <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" t="s">
         <v>20</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
       </c>
       <c r="G4" t="s">
         <v>13</v>
@@ -7285,10 +7285,10 @@
         <v>34</v>
       </c>
       <c r="E14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" t="s">
         <v>20</v>
-      </c>
-      <c r="F14" t="s">
-        <v>12</v>
       </c>
       <c r="G14" t="s">
         <v>13</v>
@@ -7308,10 +7308,10 @@
         <v>34</v>
       </c>
       <c r="E15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" t="s">
         <v>45</v>
-      </c>
-      <c r="F15" t="s">
-        <v>12</v>
       </c>
       <c r="G15" t="s">
         <v>13</v>
@@ -7354,10 +7354,10 @@
         <v>34</v>
       </c>
       <c r="E17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" t="s">
         <v>50</v>
-      </c>
-      <c r="F17" t="s">
-        <v>12</v>
       </c>
       <c r="G17" t="s">
         <v>13</v>
@@ -7400,10 +7400,10 @@
         <v>34</v>
       </c>
       <c r="E19" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" t="s">
         <v>55</v>
-      </c>
-      <c r="F19" t="s">
-        <v>12</v>
       </c>
       <c r="G19" t="s">
         <v>13</v>
@@ -7423,10 +7423,10 @@
         <v>10</v>
       </c>
       <c r="E20" t="s">
-        <v>11</v>
+        <v>58</v>
       </c>
       <c r="F20" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="G20" t="s">
         <v>13</v>
@@ -7515,10 +7515,10 @@
         <v>19</v>
       </c>
       <c r="E24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" t="s">
         <v>67</v>
-      </c>
-      <c r="F24" t="s">
-        <v>12</v>
       </c>
       <c r="G24" t="s">
         <v>13</v>
@@ -7745,10 +7745,10 @@
         <v>34</v>
       </c>
       <c r="E34" t="s">
-        <v>11</v>
+        <v>88</v>
       </c>
       <c r="F34" t="s">
-        <v>88</v>
+        <v>12</v>
       </c>
       <c r="G34" t="s">
         <v>13</v>
@@ -7929,10 +7929,10 @@
         <v>19</v>
       </c>
       <c r="E42" t="s">
+        <v>11</v>
+      </c>
+      <c r="F42" t="s">
         <v>55</v>
-      </c>
-      <c r="F42" t="s">
-        <v>12</v>
       </c>
       <c r="G42" t="s">
         <v>13</v>
@@ -7975,10 +7975,10 @@
         <v>34</v>
       </c>
       <c r="E44" t="s">
+        <v>11</v>
+      </c>
+      <c r="F44" t="s">
         <v>55</v>
-      </c>
-      <c r="F44" t="s">
-        <v>12</v>
       </c>
       <c r="G44" t="s">
         <v>13</v>
@@ -7998,10 +7998,10 @@
         <v>34</v>
       </c>
       <c r="E45" t="s">
+        <v>11</v>
+      </c>
+      <c r="F45" t="s">
         <v>45</v>
-      </c>
-      <c r="F45" t="s">
-        <v>12</v>
       </c>
       <c r="G45" t="s">
         <v>13</v>
@@ -8067,10 +8067,10 @@
         <v>19</v>
       </c>
       <c r="E48" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="F48" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="G48" t="s">
         <v>115</v>
@@ -8113,10 +8113,10 @@
         <v>19</v>
       </c>
       <c r="E50" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="F50" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="G50" t="s">
         <v>115</v>
@@ -8274,10 +8274,10 @@
         <v>34</v>
       </c>
       <c r="E57" t="s">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="F57" t="s">
-        <v>140</v>
+        <v>114</v>
       </c>
       <c r="G57" t="s">
         <v>115</v>
@@ -8366,10 +8366,10 @@
         <v>19</v>
       </c>
       <c r="E61" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F61" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="G61" t="s">
         <v>115</v>
@@ -8389,10 +8389,10 @@
         <v>34</v>
       </c>
       <c r="E62" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F62" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="G62" t="s">
         <v>115</v>
@@ -8412,10 +8412,10 @@
         <v>34</v>
       </c>
       <c r="E63" t="s">
+        <v>113</v>
+      </c>
+      <c r="F63" t="s">
         <v>154</v>
-      </c>
-      <c r="F63" t="s">
-        <v>114</v>
       </c>
       <c r="G63" t="s">
         <v>115</v>
@@ -8435,10 +8435,10 @@
         <v>34</v>
       </c>
       <c r="E64" t="s">
+        <v>113</v>
+      </c>
+      <c r="F64" t="s">
         <v>157</v>
-      </c>
-      <c r="F64" t="s">
-        <v>114</v>
       </c>
       <c r="G64" t="s">
         <v>115</v>
@@ -8458,10 +8458,10 @@
         <v>34</v>
       </c>
       <c r="E65" t="s">
-        <v>113</v>
+        <v>160</v>
       </c>
       <c r="F65" t="s">
-        <v>160</v>
+        <v>114</v>
       </c>
       <c r="G65" t="s">
         <v>115</v>
@@ -8504,10 +8504,10 @@
         <v>19</v>
       </c>
       <c r="E67" t="s">
+        <v>165</v>
+      </c>
+      <c r="F67" t="s">
         <v>157</v>
-      </c>
-      <c r="F67" t="s">
-        <v>165</v>
       </c>
       <c r="G67" t="s">
         <v>115</v>
@@ -8527,10 +8527,10 @@
         <v>34</v>
       </c>
       <c r="E68" t="s">
-        <v>113</v>
+        <v>168</v>
       </c>
       <c r="F68" t="s">
-        <v>168</v>
+        <v>114</v>
       </c>
       <c r="G68" t="s">
         <v>115</v>
@@ -8596,10 +8596,10 @@
         <v>19</v>
       </c>
       <c r="E71" t="s">
-        <v>113</v>
+        <v>175</v>
       </c>
       <c r="F71" t="s">
-        <v>175</v>
+        <v>114</v>
       </c>
       <c r="G71" t="s">
         <v>115</v>
@@ -8665,10 +8665,10 @@
         <v>19</v>
       </c>
       <c r="E74" t="s">
-        <v>113</v>
+        <v>182</v>
       </c>
       <c r="F74" t="s">
-        <v>182</v>
+        <v>114</v>
       </c>
       <c r="G74" t="s">
         <v>115</v>
@@ -8803,10 +8803,10 @@
         <v>34</v>
       </c>
       <c r="E80" t="s">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="F80" t="s">
-        <v>140</v>
+        <v>114</v>
       </c>
       <c r="G80" t="s">
         <v>115</v>
@@ -9102,10 +9102,10 @@
         <v>19</v>
       </c>
       <c r="E93" t="s">
-        <v>113</v>
+        <v>222</v>
       </c>
       <c r="F93" t="s">
-        <v>222</v>
+        <v>114</v>
       </c>
       <c r="G93" t="s">
         <v>115</v>
@@ -9148,10 +9148,10 @@
         <v>34</v>
       </c>
       <c r="E95" t="s">
-        <v>113</v>
+        <v>227</v>
       </c>
       <c r="F95" t="s">
-        <v>227</v>
+        <v>114</v>
       </c>
       <c r="G95" t="s">
         <v>115</v>
@@ -9171,10 +9171,10 @@
         <v>34</v>
       </c>
       <c r="E96" t="s">
-        <v>113</v>
+        <v>227</v>
       </c>
       <c r="F96" t="s">
-        <v>227</v>
+        <v>114</v>
       </c>
       <c r="G96" t="s">
         <v>115</v>
@@ -9378,10 +9378,10 @@
         <v>34</v>
       </c>
       <c r="E105" t="s">
-        <v>232</v>
+        <v>251</v>
       </c>
       <c r="F105" t="s">
-        <v>251</v>
+        <v>233</v>
       </c>
       <c r="G105" t="s">
         <v>234</v>
@@ -9562,10 +9562,10 @@
         <v>34</v>
       </c>
       <c r="E113" t="s">
-        <v>232</v>
+        <v>268</v>
       </c>
       <c r="F113" t="s">
-        <v>268</v>
+        <v>233</v>
       </c>
       <c r="G113" t="s">
         <v>234</v>
@@ -9769,10 +9769,10 @@
         <v>25</v>
       </c>
       <c r="E122" t="s">
-        <v>279</v>
+        <v>232</v>
       </c>
       <c r="F122" t="s">
-        <v>233</v>
+        <v>280</v>
       </c>
       <c r="G122" t="s">
         <v>234</v>
@@ -9792,10 +9792,10 @@
         <v>19</v>
       </c>
       <c r="E123" t="s">
-        <v>275</v>
+        <v>232</v>
       </c>
       <c r="F123" t="s">
-        <v>233</v>
+        <v>276</v>
       </c>
       <c r="G123" t="s">
         <v>234</v>
@@ -10045,10 +10045,10 @@
         <v>34</v>
       </c>
       <c r="E134" t="s">
-        <v>275</v>
+        <v>316</v>
       </c>
       <c r="F134" t="s">
-        <v>316</v>
+        <v>276</v>
       </c>
       <c r="G134" t="s">
         <v>234</v>
@@ -10091,10 +10091,10 @@
         <v>34</v>
       </c>
       <c r="E136" t="s">
-        <v>275</v>
+        <v>321</v>
       </c>
       <c r="F136" t="s">
-        <v>321</v>
+        <v>276</v>
       </c>
       <c r="G136" t="s">
         <v>234</v>
@@ -10574,10 +10574,10 @@
         <v>34</v>
       </c>
       <c r="E157" t="s">
-        <v>338</v>
+        <v>367</v>
       </c>
       <c r="F157" t="s">
-        <v>368</v>
+        <v>339</v>
       </c>
       <c r="G157" t="s">
         <v>340</v>
@@ -10666,10 +10666,10 @@
         <v>34</v>
       </c>
       <c r="E161" t="s">
+        <v>338</v>
+      </c>
+      <c r="F161" t="s">
         <v>379</v>
-      </c>
-      <c r="F161" t="s">
-        <v>339</v>
       </c>
       <c r="G161" t="s">
         <v>340</v>
@@ -10942,10 +10942,10 @@
         <v>19</v>
       </c>
       <c r="E173" t="s">
-        <v>338</v>
+        <v>408</v>
       </c>
       <c r="F173" t="s">
-        <v>408</v>
+        <v>339</v>
       </c>
       <c r="G173" t="s">
         <v>340</v>
@@ -10965,10 +10965,10 @@
         <v>19</v>
       </c>
       <c r="E174" t="s">
+        <v>408</v>
+      </c>
+      <c r="F174" t="s">
         <v>410</v>
-      </c>
-      <c r="F174" t="s">
-        <v>408</v>
       </c>
       <c r="G174" t="s">
         <v>340</v>
@@ -11172,10 +11172,10 @@
         <v>19</v>
       </c>
       <c r="E183" t="s">
-        <v>338</v>
+        <v>431</v>
       </c>
       <c r="F183" t="s">
-        <v>431</v>
+        <v>339</v>
       </c>
       <c r="G183" t="s">
         <v>340</v>
@@ -11287,10 +11287,10 @@
         <v>34</v>
       </c>
       <c r="E188" t="s">
-        <v>338</v>
+        <v>442</v>
       </c>
       <c r="F188" t="s">
-        <v>442</v>
+        <v>339</v>
       </c>
       <c r="G188" t="s">
         <v>340</v>
@@ -11333,10 +11333,10 @@
         <v>16</v>
       </c>
       <c r="E190" t="s">
+        <v>442</v>
+      </c>
+      <c r="F190" t="s">
         <v>447</v>
-      </c>
-      <c r="F190" t="s">
-        <v>442</v>
       </c>
       <c r="G190" t="s">
         <v>340</v>
@@ -11425,10 +11425,10 @@
         <v>25</v>
       </c>
       <c r="E194" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="F194" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="G194" t="s">
         <v>456</v>
@@ -11448,10 +11448,10 @@
         <v>16</v>
       </c>
       <c r="E195" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="F195" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="G195" t="s">
         <v>456</v>
@@ -11471,10 +11471,10 @@
         <v>25</v>
       </c>
       <c r="E196" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="F196" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="G196" t="s">
         <v>456</v>
@@ -11494,10 +11494,10 @@
         <v>25</v>
       </c>
       <c r="E197" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="F197" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="G197" t="s">
         <v>456</v>
@@ -11517,10 +11517,10 @@
         <v>16</v>
       </c>
       <c r="E198" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="F198" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="G198" t="s">
         <v>456</v>
@@ -11540,10 +11540,10 @@
         <v>25</v>
       </c>
       <c r="E199" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="F199" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="G199" t="s">
         <v>456</v>
@@ -11563,10 +11563,10 @@
         <v>25</v>
       </c>
       <c r="E200" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="F200" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="G200" t="s">
         <v>456</v>
@@ -11586,10 +11586,10 @@
         <v>25</v>
       </c>
       <c r="E201" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="F201" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="G201" t="s">
         <v>456</v>
@@ -11609,10 +11609,10 @@
         <v>25</v>
       </c>
       <c r="E202" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="F202" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="G202" t="s">
         <v>456</v>
@@ -11632,10 +11632,10 @@
         <v>25</v>
       </c>
       <c r="E203" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="F203" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="G203" t="s">
         <v>456</v>
@@ -11655,10 +11655,10 @@
         <v>16</v>
       </c>
       <c r="E204" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="F204" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="G204" t="s">
         <v>456</v>
@@ -11678,10 +11678,10 @@
         <v>25</v>
       </c>
       <c r="E205" t="s">
-        <v>454</v>
+        <v>482</v>
       </c>
       <c r="F205" t="s">
-        <v>482</v>
+        <v>455</v>
       </c>
       <c r="G205" t="s">
         <v>456</v>
@@ -11701,10 +11701,10 @@
         <v>25</v>
       </c>
       <c r="E206" t="s">
-        <v>338</v>
+        <v>482</v>
       </c>
       <c r="F206" t="s">
-        <v>482</v>
+        <v>339</v>
       </c>
       <c r="G206" t="s">
         <v>456</v>
@@ -11747,10 +11747,10 @@
         <v>25</v>
       </c>
       <c r="E208" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="F208" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="G208" t="s">
         <v>456</v>
@@ -11770,10 +11770,10 @@
         <v>25</v>
       </c>
       <c r="E209" t="s">
-        <v>454</v>
+        <v>482</v>
       </c>
       <c r="F209" t="s">
-        <v>482</v>
+        <v>455</v>
       </c>
       <c r="G209" t="s">
         <v>456</v>
@@ -11793,10 +11793,10 @@
         <v>25</v>
       </c>
       <c r="E210" t="s">
-        <v>338</v>
+        <v>482</v>
       </c>
       <c r="F210" t="s">
-        <v>482</v>
+        <v>339</v>
       </c>
       <c r="G210" t="s">
         <v>456</v>
@@ -11839,10 +11839,10 @@
         <v>25</v>
       </c>
       <c r="E212" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="F212" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="G212" t="s">
         <v>456</v>
@@ -11885,10 +11885,10 @@
         <v>25</v>
       </c>
       <c r="E214" t="s">
-        <v>454</v>
+        <v>482</v>
       </c>
       <c r="F214" t="s">
-        <v>482</v>
+        <v>455</v>
       </c>
       <c r="G214" t="s">
         <v>456</v>
@@ -11908,10 +11908,10 @@
         <v>25</v>
       </c>
       <c r="E215" t="s">
-        <v>338</v>
+        <v>482</v>
       </c>
       <c r="F215" t="s">
-        <v>482</v>
+        <v>339</v>
       </c>
       <c r="G215" t="s">
         <v>456</v>
@@ -11931,10 +11931,10 @@
         <v>25</v>
       </c>
       <c r="E216" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="F216" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="G216" t="s">
         <v>456</v>
@@ -11954,10 +11954,10 @@
         <v>34</v>
       </c>
       <c r="E217" t="s">
-        <v>454</v>
+        <v>513</v>
       </c>
       <c r="F217" t="s">
-        <v>513</v>
+        <v>455</v>
       </c>
       <c r="G217" t="s">
         <v>456</v>
@@ -12000,10 +12000,10 @@
         <v>25</v>
       </c>
       <c r="E219" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="F219" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="G219" t="s">
         <v>456</v>
@@ -12023,10 +12023,10 @@
         <v>34</v>
       </c>
       <c r="E220" t="s">
-        <v>388</v>
+        <v>459</v>
       </c>
       <c r="F220" t="s">
-        <v>459</v>
+        <v>389</v>
       </c>
       <c r="G220" t="s">
         <v>456</v>
@@ -12046,10 +12046,10 @@
         <v>34</v>
       </c>
       <c r="E221" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="F221" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="G221" t="s">
         <v>456</v>
@@ -12069,10 +12069,10 @@
         <v>25</v>
       </c>
       <c r="E222" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="F222" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="G222" t="s">
         <v>456</v>
@@ -12092,10 +12092,10 @@
         <v>25</v>
       </c>
       <c r="E223" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="F223" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="G223" t="s">
         <v>456</v>
@@ -12115,10 +12115,10 @@
         <v>25</v>
       </c>
       <c r="E224" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="F224" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="G224" t="s">
         <v>456</v>
@@ -12138,10 +12138,10 @@
         <v>19</v>
       </c>
       <c r="E225" t="s">
-        <v>454</v>
+        <v>532</v>
       </c>
       <c r="F225" t="s">
-        <v>532</v>
+        <v>455</v>
       </c>
       <c r="G225" t="s">
         <v>456</v>
@@ -12161,10 +12161,10 @@
         <v>19</v>
       </c>
       <c r="E226" t="s">
-        <v>454</v>
+        <v>535</v>
       </c>
       <c r="F226" t="s">
-        <v>535</v>
+        <v>455</v>
       </c>
       <c r="G226" t="s">
         <v>456</v>
@@ -12184,10 +12184,10 @@
         <v>25</v>
       </c>
       <c r="E227" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="F227" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="G227" t="s">
         <v>456</v>
@@ -12207,10 +12207,10 @@
         <v>25</v>
       </c>
       <c r="E228" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="F228" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="G228" t="s">
         <v>456</v>
@@ -12230,10 +12230,10 @@
         <v>34</v>
       </c>
       <c r="E229" t="s">
-        <v>454</v>
+        <v>535</v>
       </c>
       <c r="F229" t="s">
-        <v>535</v>
+        <v>455</v>
       </c>
       <c r="G229" t="s">
         <v>456</v>
@@ -12253,10 +12253,10 @@
         <v>19</v>
       </c>
       <c r="E230" t="s">
-        <v>454</v>
+        <v>535</v>
       </c>
       <c r="F230" t="s">
-        <v>535</v>
+        <v>455</v>
       </c>
       <c r="G230" t="s">
         <v>456</v>
@@ -12276,10 +12276,10 @@
         <v>25</v>
       </c>
       <c r="E231" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="F231" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="G231" t="s">
         <v>456</v>
@@ -12299,10 +12299,10 @@
         <v>25</v>
       </c>
       <c r="E232" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="F232" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="G232" t="s">
         <v>456</v>
@@ -12322,10 +12322,10 @@
         <v>16</v>
       </c>
       <c r="E233" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="F233" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="G233" t="s">
         <v>456</v>
@@ -12345,10 +12345,10 @@
         <v>16</v>
       </c>
       <c r="E234" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="F234" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="G234" t="s">
         <v>456</v>
@@ -12368,10 +12368,10 @@
         <v>25</v>
       </c>
       <c r="E235" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="F235" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="G235" t="s">
         <v>456</v>
@@ -12391,10 +12391,10 @@
         <v>25</v>
       </c>
       <c r="E236" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="F236" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="G236" t="s">
         <v>456</v>
@@ -12414,10 +12414,10 @@
         <v>16</v>
       </c>
       <c r="E237" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="F237" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="G237" t="s">
         <v>456</v>
@@ -12437,10 +12437,10 @@
         <v>25</v>
       </c>
       <c r="E238" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="F238" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="G238" t="s">
         <v>456</v>
@@ -12460,10 +12460,10 @@
         <v>25</v>
       </c>
       <c r="E239" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="F239" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="G239" t="s">
         <v>456</v>
@@ -12483,10 +12483,10 @@
         <v>16</v>
       </c>
       <c r="E240" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="F240" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="G240" t="s">
         <v>456</v>
@@ -12506,10 +12506,10 @@
         <v>25</v>
       </c>
       <c r="E241" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="F241" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="G241" t="s">
         <v>456</v>
@@ -12529,10 +12529,10 @@
         <v>25</v>
       </c>
       <c r="E242" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="F242" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="G242" t="s">
         <v>456</v>
@@ -12552,10 +12552,10 @@
         <v>25</v>
       </c>
       <c r="E243" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="F243" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="G243" t="s">
         <v>456</v>
@@ -12575,10 +12575,10 @@
         <v>25</v>
       </c>
       <c r="E244" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="F244" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="G244" t="s">
         <v>456</v>
@@ -12621,10 +12621,10 @@
         <v>19</v>
       </c>
       <c r="E246" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="F246" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="G246" t="s">
         <v>575</v>
@@ -12667,10 +12667,10 @@
         <v>19</v>
       </c>
       <c r="E248" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="F248" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="G248" t="s">
         <v>575</v>
@@ -12759,10 +12759,10 @@
         <v>19</v>
       </c>
       <c r="E252" t="s">
-        <v>573</v>
+        <v>591</v>
       </c>
       <c r="F252" t="s">
-        <v>591</v>
+        <v>574</v>
       </c>
       <c r="G252" t="s">
         <v>575</v>
@@ -12805,10 +12805,10 @@
         <v>25</v>
       </c>
       <c r="E254" t="s">
+        <v>596</v>
+      </c>
+      <c r="F254" t="s">
         <v>459</v>
-      </c>
-      <c r="F254" t="s">
-        <v>596</v>
       </c>
       <c r="G254" t="s">
         <v>575</v>
@@ -12874,10 +12874,10 @@
         <v>19</v>
       </c>
       <c r="E257" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="F257" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="G257" t="s">
         <v>575</v>
@@ -12897,10 +12897,10 @@
         <v>19</v>
       </c>
       <c r="E258" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="F258" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="G258" t="s">
         <v>575</v>
@@ -12920,10 +12920,10 @@
         <v>25</v>
       </c>
       <c r="E259" t="s">
-        <v>573</v>
+        <v>607</v>
       </c>
       <c r="F259" t="s">
-        <v>607</v>
+        <v>574</v>
       </c>
       <c r="G259" t="s">
         <v>575</v>
@@ -13012,10 +13012,10 @@
         <v>19</v>
       </c>
       <c r="E263" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="F263" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="G263" t="s">
         <v>575</v>
@@ -13035,10 +13035,10 @@
         <v>19</v>
       </c>
       <c r="E264" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="F264" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="G264" t="s">
         <v>575</v>
@@ -13081,10 +13081,10 @@
         <v>19</v>
       </c>
       <c r="E266" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="F266" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="G266" t="s">
         <v>575</v>
@@ -13127,10 +13127,10 @@
         <v>19</v>
       </c>
       <c r="E268" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="F268" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="G268" t="s">
         <v>575</v>
@@ -13150,10 +13150,10 @@
         <v>19</v>
       </c>
       <c r="E269" t="s">
-        <v>573</v>
+        <v>607</v>
       </c>
       <c r="F269" t="s">
-        <v>607</v>
+        <v>574</v>
       </c>
       <c r="G269" t="s">
         <v>575</v>
@@ -13173,10 +13173,10 @@
         <v>19</v>
       </c>
       <c r="E270" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="F270" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="G270" t="s">
         <v>575</v>
@@ -13196,10 +13196,10 @@
         <v>19</v>
       </c>
       <c r="E271" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="F271" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="G271" t="s">
         <v>575</v>
@@ -13242,10 +13242,10 @@
         <v>19</v>
       </c>
       <c r="E273" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="F273" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="G273" t="s">
         <v>575</v>
@@ -13288,10 +13288,10 @@
         <v>19</v>
       </c>
       <c r="E275" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="F275" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="G275" t="s">
         <v>575</v>
@@ -13311,10 +13311,10 @@
         <v>19</v>
       </c>
       <c r="E276" t="s">
-        <v>573</v>
+        <v>644</v>
       </c>
       <c r="F276" t="s">
-        <v>644</v>
+        <v>574</v>
       </c>
       <c r="G276" t="s">
         <v>575</v>
@@ -13357,10 +13357,10 @@
         <v>19</v>
       </c>
       <c r="E278" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="F278" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="G278" t="s">
         <v>575</v>
@@ -13403,10 +13403,10 @@
         <v>19</v>
       </c>
       <c r="E280" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="F280" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="G280" t="s">
         <v>575</v>
@@ -13472,10 +13472,10 @@
         <v>19</v>
       </c>
       <c r="E283" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="F283" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="G283" t="s">
         <v>575</v>
@@ -13587,10 +13587,10 @@
         <v>19</v>
       </c>
       <c r="E288" t="s">
-        <v>573</v>
+        <v>644</v>
       </c>
       <c r="F288" t="s">
-        <v>644</v>
+        <v>574</v>
       </c>
       <c r="G288" t="s">
         <v>575</v>
@@ -13610,10 +13610,10 @@
         <v>19</v>
       </c>
       <c r="E289" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="F289" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="G289" t="s">
         <v>575</v>
@@ -13679,10 +13679,10 @@
         <v>19</v>
       </c>
       <c r="E292" t="s">
-        <v>573</v>
+        <v>644</v>
       </c>
       <c r="F292" t="s">
-        <v>644</v>
+        <v>574</v>
       </c>
       <c r="G292" t="s">
         <v>575</v>
@@ -13702,10 +13702,10 @@
         <v>19</v>
       </c>
       <c r="E293" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="F293" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="G293" t="s">
         <v>575</v>
@@ -13863,10 +13863,10 @@
         <v>19</v>
       </c>
       <c r="E300" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="F300" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="G300" t="s">
         <v>575</v>
@@ -13886,10 +13886,10 @@
         <v>19</v>
       </c>
       <c r="E301" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="F301" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="G301" t="s">
         <v>575</v>
@@ -13909,10 +13909,10 @@
         <v>19</v>
       </c>
       <c r="E302" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="F302" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="G302" t="s">
         <v>575</v>
@@ -13955,10 +13955,10 @@
         <v>19</v>
       </c>
       <c r="E304" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="F304" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="G304" t="s">
         <v>575</v>
@@ -14024,10 +14024,10 @@
         <v>19</v>
       </c>
       <c r="E307" t="s">
-        <v>614</v>
+        <v>711</v>
       </c>
       <c r="F307" t="s">
-        <v>711</v>
+        <v>615</v>
       </c>
       <c r="G307" t="s">
         <v>575</v>
@@ -14047,10 +14047,10 @@
         <v>19</v>
       </c>
       <c r="E308" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="F308" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="G308" t="s">
         <v>575</v>
@@ -14392,10 +14392,10 @@
         <v>19</v>
       </c>
       <c r="E323" t="s">
-        <v>718</v>
+        <v>747</v>
       </c>
       <c r="F323" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
       <c r="G323" t="s">
         <v>720</v>
@@ -14438,10 +14438,10 @@
         <v>34</v>
       </c>
       <c r="E325" t="s">
+        <v>718</v>
+      </c>
+      <c r="F325" t="s">
         <v>752</v>
-      </c>
-      <c r="F325" t="s">
-        <v>719</v>
       </c>
       <c r="G325" t="s">
         <v>720</v>
@@ -14576,10 +14576,10 @@
         <v>25</v>
       </c>
       <c r="E331" t="s">
+        <v>718</v>
+      </c>
+      <c r="F331" t="s">
         <v>765</v>
-      </c>
-      <c r="F331" t="s">
-        <v>719</v>
       </c>
       <c r="G331" t="s">
         <v>720</v>
@@ -14875,10 +14875,10 @@
         <v>34</v>
       </c>
       <c r="E344" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="F344" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="G344" t="s">
         <v>720</v>
@@ -14921,10 +14921,10 @@
         <v>19</v>
       </c>
       <c r="E346" t="s">
-        <v>797</v>
+        <v>802</v>
       </c>
       <c r="F346" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="G346" t="s">
         <v>799</v>
@@ -15151,10 +15151,10 @@
         <v>19</v>
       </c>
       <c r="E356" t="s">
-        <v>797</v>
+        <v>823</v>
       </c>
       <c r="F356" t="s">
-        <v>823</v>
+        <v>798</v>
       </c>
       <c r="G356" t="s">
         <v>799</v>
@@ -15381,10 +15381,10 @@
         <v>19</v>
       </c>
       <c r="E366" t="s">
-        <v>797</v>
+        <v>844</v>
       </c>
       <c r="F366" t="s">
-        <v>844</v>
+        <v>798</v>
       </c>
       <c r="G366" t="s">
         <v>799</v>
@@ -15404,10 +15404,10 @@
         <v>16</v>
       </c>
       <c r="E367" t="s">
-        <v>797</v>
+        <v>802</v>
       </c>
       <c r="F367" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="G367" t="s">
         <v>799</v>
@@ -15496,10 +15496,10 @@
         <v>25</v>
       </c>
       <c r="E371" t="s">
+        <v>797</v>
+      </c>
+      <c r="F371" t="s">
         <v>855</v>
-      </c>
-      <c r="F371" t="s">
-        <v>798</v>
       </c>
       <c r="G371" t="s">
         <v>799</v>
@@ -15703,10 +15703,10 @@
         <v>16</v>
       </c>
       <c r="E380" t="s">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="F380" t="s">
-        <v>879</v>
+        <v>873</v>
       </c>
       <c r="G380" t="s">
         <v>874</v>
@@ -15841,10 +15841,10 @@
         <v>19</v>
       </c>
       <c r="E386" t="s">
-        <v>872</v>
+        <v>892</v>
       </c>
       <c r="F386" t="s">
-        <v>892</v>
+        <v>873</v>
       </c>
       <c r="G386" t="s">
         <v>874</v>
@@ -15864,10 +15864,10 @@
         <v>25</v>
       </c>
       <c r="E387" t="s">
-        <v>872</v>
+        <v>895</v>
       </c>
       <c r="F387" t="s">
-        <v>895</v>
+        <v>873</v>
       </c>
       <c r="G387" t="s">
         <v>874</v>
@@ -16002,10 +16002,10 @@
         <v>19</v>
       </c>
       <c r="E393" t="s">
-        <v>872</v>
+        <v>910</v>
       </c>
       <c r="F393" t="s">
-        <v>910</v>
+        <v>873</v>
       </c>
       <c r="G393" t="s">
         <v>874</v>
@@ -16324,10 +16324,10 @@
         <v>25</v>
       </c>
       <c r="E407" t="s">
-        <v>872</v>
+        <v>947</v>
       </c>
       <c r="F407" t="s">
-        <v>947</v>
+        <v>873</v>
       </c>
       <c r="G407" t="s">
         <v>874</v>
@@ -16600,10 +16600,10 @@
         <v>34</v>
       </c>
       <c r="E419" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="F419" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="G419" t="s">
         <v>969</v>
@@ -16646,10 +16646,10 @@
         <v>25</v>
       </c>
       <c r="E421" t="s">
-        <v>967</v>
+        <v>979</v>
       </c>
       <c r="F421" t="s">
-        <v>979</v>
+        <v>968</v>
       </c>
       <c r="G421" t="s">
         <v>969</v>
@@ -16922,10 +16922,10 @@
         <v>34</v>
       </c>
       <c r="E433" t="s">
-        <v>967</v>
+        <v>1008</v>
       </c>
       <c r="F433" t="s">
-        <v>1008</v>
+        <v>968</v>
       </c>
       <c r="G433" t="s">
         <v>969</v>
@@ -16991,10 +16991,10 @@
         <v>34</v>
       </c>
       <c r="E436" t="s">
-        <v>967</v>
+        <v>1015</v>
       </c>
       <c r="F436" t="s">
-        <v>1015</v>
+        <v>968</v>
       </c>
       <c r="G436" t="s">
         <v>969</v>
@@ -17014,10 +17014,10 @@
         <v>25</v>
       </c>
       <c r="E437" t="s">
-        <v>967</v>
+        <v>1018</v>
       </c>
       <c r="F437" t="s">
-        <v>1018</v>
+        <v>968</v>
       </c>
       <c r="G437" t="s">
         <v>969</v>
@@ -17658,10 +17658,10 @@
         <v>34</v>
       </c>
       <c r="E465" t="s">
-        <v>1060</v>
+        <v>1085</v>
       </c>
       <c r="F465" t="s">
-        <v>1085</v>
+        <v>1061</v>
       </c>
       <c r="G465" t="s">
         <v>1062</v>
@@ -17681,10 +17681,10 @@
         <v>34</v>
       </c>
       <c r="E466" t="s">
-        <v>1081</v>
+        <v>1088</v>
       </c>
       <c r="F466" t="s">
-        <v>1088</v>
+        <v>1082</v>
       </c>
       <c r="G466" t="s">
         <v>1062</v>
@@ -17842,10 +17842,10 @@
         <v>34</v>
       </c>
       <c r="E473" t="s">
-        <v>1081</v>
+        <v>1107</v>
       </c>
       <c r="F473" t="s">
-        <v>1107</v>
+        <v>1082</v>
       </c>
       <c r="G473" t="s">
         <v>1062</v>
@@ -18187,10 +18187,10 @@
         <v>1059</v>
       </c>
       <c r="E488" t="s">
-        <v>1136</v>
+        <v>1141</v>
       </c>
       <c r="F488" t="s">
-        <v>1141</v>
+        <v>1137</v>
       </c>
       <c r="G488" t="s">
         <v>1138</v>
@@ -18279,10 +18279,10 @@
         <v>25</v>
       </c>
       <c r="E492" t="s">
+        <v>1136</v>
+      </c>
+      <c r="F492" t="s">
         <v>1150</v>
-      </c>
-      <c r="F492" t="s">
-        <v>1137</v>
       </c>
       <c r="G492" t="s">
         <v>1138</v>
@@ -18325,10 +18325,10 @@
         <v>16</v>
       </c>
       <c r="E494" t="s">
+        <v>1097</v>
+      </c>
+      <c r="F494" t="s">
         <v>1155</v>
-      </c>
-      <c r="F494" t="s">
-        <v>1098</v>
       </c>
       <c r="G494" t="s">
         <v>1138</v>
@@ -18348,10 +18348,10 @@
         <v>19</v>
       </c>
       <c r="E495" t="s">
+        <v>1097</v>
+      </c>
+      <c r="F495" t="s">
         <v>1155</v>
-      </c>
-      <c r="F495" t="s">
-        <v>1098</v>
       </c>
       <c r="G495" t="s">
         <v>1138</v>
@@ -18417,10 +18417,10 @@
         <v>1059</v>
       </c>
       <c r="E498" t="s">
-        <v>1136</v>
+        <v>1164</v>
       </c>
       <c r="F498" t="s">
-        <v>1164</v>
+        <v>1137</v>
       </c>
       <c r="G498" t="s">
         <v>1138</v>
@@ -18509,10 +18509,10 @@
         <v>25</v>
       </c>
       <c r="E502" t="s">
-        <v>1136</v>
+        <v>1173</v>
       </c>
       <c r="F502" t="s">
-        <v>1173</v>
+        <v>1137</v>
       </c>
       <c r="G502" t="s">
         <v>1138</v>
@@ -18670,10 +18670,10 @@
         <v>25</v>
       </c>
       <c r="E509" t="s">
+        <v>1188</v>
+      </c>
+      <c r="F509" t="s">
         <v>1192</v>
-      </c>
-      <c r="F509" t="s">
-        <v>1189</v>
       </c>
       <c r="G509" t="s">
         <v>1138</v>
@@ -18739,10 +18739,10 @@
         <v>19</v>
       </c>
       <c r="E512" t="s">
-        <v>1136</v>
+        <v>1201</v>
       </c>
       <c r="F512" t="s">
-        <v>1201</v>
+        <v>1137</v>
       </c>
       <c r="G512" t="s">
         <v>1138</v>
@@ -18762,10 +18762,10 @@
         <v>25</v>
       </c>
       <c r="E513" t="s">
+        <v>1136</v>
+      </c>
+      <c r="F513" t="s">
         <v>1204</v>
-      </c>
-      <c r="F513" t="s">
-        <v>1137</v>
       </c>
       <c r="G513" t="s">
         <v>1138</v>
@@ -18946,10 +18946,10 @@
         <v>25</v>
       </c>
       <c r="E521" t="s">
-        <v>1136</v>
+        <v>1221</v>
       </c>
       <c r="F521" t="s">
-        <v>1221</v>
+        <v>1137</v>
       </c>
       <c r="G521" t="s">
         <v>1138</v>
@@ -18969,10 +18969,10 @@
         <v>16</v>
       </c>
       <c r="E522" t="s">
-        <v>1136</v>
+        <v>1224</v>
       </c>
       <c r="F522" t="s">
-        <v>1224</v>
+        <v>1137</v>
       </c>
       <c r="G522" t="s">
         <v>1138</v>
@@ -18992,10 +18992,10 @@
         <v>34</v>
       </c>
       <c r="E523" t="s">
-        <v>1136</v>
+        <v>1227</v>
       </c>
       <c r="F523" t="s">
-        <v>1227</v>
+        <v>1137</v>
       </c>
       <c r="G523" t="s">
         <v>1138</v>
@@ -19038,10 +19038,10 @@
         <v>1232</v>
       </c>
       <c r="E525" t="s">
+        <v>1141</v>
+      </c>
+      <c r="F525" t="s">
         <v>1233</v>
-      </c>
-      <c r="F525" t="s">
-        <v>1141</v>
       </c>
       <c r="G525" t="s">
         <v>1234</v>
@@ -19061,10 +19061,10 @@
         <v>1232</v>
       </c>
       <c r="E526" t="s">
+        <v>1141</v>
+      </c>
+      <c r="F526" t="s">
         <v>1233</v>
-      </c>
-      <c r="F526" t="s">
-        <v>1141</v>
       </c>
       <c r="G526" t="s">
         <v>1234</v>
@@ -19084,10 +19084,10 @@
         <v>1232</v>
       </c>
       <c r="E527" t="s">
+        <v>1141</v>
+      </c>
+      <c r="F527" t="s">
         <v>1233</v>
-      </c>
-      <c r="F527" t="s">
-        <v>1141</v>
       </c>
       <c r="G527" t="s">
         <v>1234</v>
@@ -19107,10 +19107,10 @@
         <v>1232</v>
       </c>
       <c r="E528" t="s">
+        <v>1141</v>
+      </c>
+      <c r="F528" t="s">
         <v>1233</v>
-      </c>
-      <c r="F528" t="s">
-        <v>1141</v>
       </c>
       <c r="G528" t="s">
         <v>1234</v>
@@ -19130,10 +19130,10 @@
         <v>19</v>
       </c>
       <c r="E529" t="s">
+        <v>1243</v>
+      </c>
+      <c r="F529" t="s">
         <v>1233</v>
-      </c>
-      <c r="F529" t="s">
-        <v>1243</v>
       </c>
       <c r="G529" t="s">
         <v>1234</v>
@@ -19153,10 +19153,10 @@
         <v>1232</v>
       </c>
       <c r="E530" t="s">
+        <v>1141</v>
+      </c>
+      <c r="F530" t="s">
         <v>1246</v>
-      </c>
-      <c r="F530" t="s">
-        <v>1141</v>
       </c>
       <c r="G530" t="s">
         <v>1234</v>
@@ -19176,10 +19176,10 @@
         <v>1232</v>
       </c>
       <c r="E531" t="s">
+        <v>1141</v>
+      </c>
+      <c r="F531" t="s">
         <v>1233</v>
-      </c>
-      <c r="F531" t="s">
-        <v>1141</v>
       </c>
       <c r="G531" t="s">
         <v>1234</v>
@@ -19199,10 +19199,10 @@
         <v>1232</v>
       </c>
       <c r="E532" t="s">
+        <v>1141</v>
+      </c>
+      <c r="F532" t="s">
         <v>1233</v>
-      </c>
-      <c r="F532" t="s">
-        <v>1141</v>
       </c>
       <c r="G532" t="s">
         <v>1234</v>
@@ -19222,10 +19222,10 @@
         <v>1232</v>
       </c>
       <c r="E533" t="s">
+        <v>1141</v>
+      </c>
+      <c r="F533" t="s">
         <v>1233</v>
-      </c>
-      <c r="F533" t="s">
-        <v>1141</v>
       </c>
       <c r="G533" t="s">
         <v>1234</v>
@@ -19245,10 +19245,10 @@
         <v>1232</v>
       </c>
       <c r="E534" t="s">
+        <v>1141</v>
+      </c>
+      <c r="F534" t="s">
         <v>1233</v>
-      </c>
-      <c r="F534" t="s">
-        <v>1141</v>
       </c>
       <c r="G534" t="s">
         <v>1234</v>
@@ -19268,10 +19268,10 @@
         <v>1232</v>
       </c>
       <c r="E535" t="s">
+        <v>1141</v>
+      </c>
+      <c r="F535" t="s">
         <v>1233</v>
-      </c>
-      <c r="F535" t="s">
-        <v>1141</v>
       </c>
       <c r="G535" t="s">
         <v>1234</v>
@@ -19291,10 +19291,10 @@
         <v>19</v>
       </c>
       <c r="E536" t="s">
+        <v>1259</v>
+      </c>
+      <c r="F536" t="s">
         <v>1233</v>
-      </c>
-      <c r="F536" t="s">
-        <v>1259</v>
       </c>
       <c r="G536" t="s">
         <v>1234</v>
@@ -19314,10 +19314,10 @@
         <v>19</v>
       </c>
       <c r="E537" t="s">
+        <v>1262</v>
+      </c>
+      <c r="F537" t="s">
         <v>1233</v>
-      </c>
-      <c r="F537" t="s">
-        <v>1262</v>
       </c>
       <c r="G537" t="s">
         <v>1234</v>
@@ -19337,10 +19337,10 @@
         <v>1232</v>
       </c>
       <c r="E538" t="s">
+        <v>1141</v>
+      </c>
+      <c r="F538" t="s">
         <v>1233</v>
-      </c>
-      <c r="F538" t="s">
-        <v>1141</v>
       </c>
       <c r="G538" t="s">
         <v>1234</v>
@@ -19360,10 +19360,10 @@
         <v>1232</v>
       </c>
       <c r="E539" t="s">
+        <v>1141</v>
+      </c>
+      <c r="F539" t="s">
         <v>1233</v>
-      </c>
-      <c r="F539" t="s">
-        <v>1141</v>
       </c>
       <c r="G539" t="s">
         <v>1234</v>
@@ -19383,10 +19383,10 @@
         <v>1232</v>
       </c>
       <c r="E540" t="s">
-        <v>1195</v>
+        <v>1141</v>
       </c>
       <c r="F540" t="s">
-        <v>1141</v>
+        <v>1196</v>
       </c>
       <c r="G540" t="s">
         <v>1234</v>
@@ -19406,10 +19406,10 @@
         <v>1232</v>
       </c>
       <c r="E541" t="s">
+        <v>1141</v>
+      </c>
+      <c r="F541" t="s">
         <v>1233</v>
-      </c>
-      <c r="F541" t="s">
-        <v>1141</v>
       </c>
       <c r="G541" t="s">
         <v>1234</v>
@@ -19429,10 +19429,10 @@
         <v>1232</v>
       </c>
       <c r="E542" t="s">
+        <v>1141</v>
+      </c>
+      <c r="F542" t="s">
         <v>1233</v>
-      </c>
-      <c r="F542" t="s">
-        <v>1141</v>
       </c>
       <c r="G542" t="s">
         <v>1234</v>
@@ -19452,10 +19452,10 @@
         <v>1232</v>
       </c>
       <c r="E543" t="s">
+        <v>1141</v>
+      </c>
+      <c r="F543" t="s">
         <v>1233</v>
-      </c>
-      <c r="F543" t="s">
-        <v>1141</v>
       </c>
       <c r="G543" t="s">
         <v>1234</v>
@@ -19475,10 +19475,10 @@
         <v>1232</v>
       </c>
       <c r="E544" t="s">
+        <v>1141</v>
+      </c>
+      <c r="F544" t="s">
         <v>1233</v>
-      </c>
-      <c r="F544" t="s">
-        <v>1141</v>
       </c>
       <c r="G544" t="s">
         <v>1234</v>
@@ -19498,10 +19498,10 @@
         <v>16</v>
       </c>
       <c r="E545" t="s">
+        <v>1141</v>
+      </c>
+      <c r="F545" t="s">
         <v>1279</v>
-      </c>
-      <c r="F545" t="s">
-        <v>1141</v>
       </c>
       <c r="G545" t="s">
         <v>1234</v>
@@ -19521,10 +19521,10 @@
         <v>1232</v>
       </c>
       <c r="E546" t="s">
+        <v>1141</v>
+      </c>
+      <c r="F546" t="s">
         <v>1233</v>
-      </c>
-      <c r="F546" t="s">
-        <v>1141</v>
       </c>
       <c r="G546" t="s">
         <v>1234</v>
@@ -19544,10 +19544,10 @@
         <v>19</v>
       </c>
       <c r="E547" t="s">
+        <v>1141</v>
+      </c>
+      <c r="F547" t="s">
         <v>1233</v>
-      </c>
-      <c r="F547" t="s">
-        <v>1141</v>
       </c>
       <c r="G547" t="s">
         <v>1234</v>
@@ -19590,10 +19590,10 @@
         <v>1232</v>
       </c>
       <c r="E549" t="s">
-        <v>1286</v>
+        <v>1291</v>
       </c>
       <c r="F549" t="s">
-        <v>1291</v>
+        <v>1287</v>
       </c>
       <c r="G549" t="s">
         <v>1288</v>
@@ -19613,10 +19613,10 @@
         <v>1232</v>
       </c>
       <c r="E550" t="s">
-        <v>1286</v>
+        <v>1294</v>
       </c>
       <c r="F550" t="s">
-        <v>1294</v>
+        <v>1287</v>
       </c>
       <c r="G550" t="s">
         <v>1288</v>
@@ -19705,10 +19705,10 @@
         <v>1232</v>
       </c>
       <c r="E554" t="s">
+        <v>1286</v>
+      </c>
+      <c r="F554" t="s">
         <v>1303</v>
-      </c>
-      <c r="F554" t="s">
-        <v>1287</v>
       </c>
       <c r="G554" t="s">
         <v>1288</v>
@@ -19843,10 +19843,10 @@
         <v>1232</v>
       </c>
       <c r="E560" t="s">
-        <v>1286</v>
+        <v>1318</v>
       </c>
       <c r="F560" t="s">
-        <v>1318</v>
+        <v>1287</v>
       </c>
       <c r="G560" t="s">
         <v>1288</v>
@@ -19866,10 +19866,10 @@
         <v>1232</v>
       </c>
       <c r="E561" t="s">
-        <v>1286</v>
+        <v>1318</v>
       </c>
       <c r="F561" t="s">
-        <v>1318</v>
+        <v>1287</v>
       </c>
       <c r="G561" t="s">
         <v>1288</v>
@@ -19912,10 +19912,10 @@
         <v>19</v>
       </c>
       <c r="E563" t="s">
+        <v>1286</v>
+      </c>
+      <c r="F563" t="s">
         <v>1325</v>
-      </c>
-      <c r="F563" t="s">
-        <v>1287</v>
       </c>
       <c r="G563" t="s">
         <v>1288</v>
@@ -20142,10 +20142,10 @@
         <v>1232</v>
       </c>
       <c r="E573" t="s">
+        <v>1348</v>
+      </c>
+      <c r="F573" t="s">
         <v>1233</v>
-      </c>
-      <c r="F573" t="s">
-        <v>1348</v>
       </c>
       <c r="G573" t="s">
         <v>1349</v>
@@ -20165,10 +20165,10 @@
         <v>1232</v>
       </c>
       <c r="E574" t="s">
+        <v>1348</v>
+      </c>
+      <c r="F574" t="s">
         <v>1352</v>
-      </c>
-      <c r="F574" t="s">
-        <v>1348</v>
       </c>
       <c r="G574" t="s">
         <v>1349</v>
@@ -20188,10 +20188,10 @@
         <v>1232</v>
       </c>
       <c r="E575" t="s">
+        <v>1348</v>
+      </c>
+      <c r="F575" t="s">
         <v>1352</v>
-      </c>
-      <c r="F575" t="s">
-        <v>1348</v>
       </c>
       <c r="G575" t="s">
         <v>1349</v>
@@ -20211,10 +20211,10 @@
         <v>1232</v>
       </c>
       <c r="E576" t="s">
+        <v>1348</v>
+      </c>
+      <c r="F576" t="s">
         <v>1352</v>
-      </c>
-      <c r="F576" t="s">
-        <v>1348</v>
       </c>
       <c r="G576" t="s">
         <v>1349</v>
@@ -20234,10 +20234,10 @@
         <v>1232</v>
       </c>
       <c r="E577" t="s">
-        <v>1286</v>
+        <v>1348</v>
       </c>
       <c r="F577" t="s">
-        <v>1348</v>
+        <v>1287</v>
       </c>
       <c r="G577" t="s">
         <v>1349</v>
@@ -20257,10 +20257,10 @@
         <v>1232</v>
       </c>
       <c r="E578" t="s">
+        <v>1361</v>
+      </c>
+      <c r="F578" t="s">
         <v>1352</v>
-      </c>
-      <c r="F578" t="s">
-        <v>1361</v>
       </c>
       <c r="G578" t="s">
         <v>1349</v>
@@ -20303,10 +20303,10 @@
         <v>1232</v>
       </c>
       <c r="E580" t="s">
+        <v>1368</v>
+      </c>
+      <c r="F580" t="s">
         <v>1352</v>
-      </c>
-      <c r="F580" t="s">
-        <v>1368</v>
       </c>
       <c r="G580" t="s">
         <v>1349</v>
@@ -20326,10 +20326,10 @@
         <v>19</v>
       </c>
       <c r="E581" t="s">
+        <v>1371</v>
+      </c>
+      <c r="F581" t="s">
         <v>1352</v>
-      </c>
-      <c r="F581" t="s">
-        <v>1371</v>
       </c>
       <c r="G581" t="s">
         <v>1349</v>
@@ -20349,10 +20349,10 @@
         <v>19</v>
       </c>
       <c r="E582" t="s">
+        <v>1348</v>
+      </c>
+      <c r="F582" t="s">
         <v>1352</v>
-      </c>
-      <c r="F582" t="s">
-        <v>1348</v>
       </c>
       <c r="G582" t="s">
         <v>1349</v>
@@ -20418,10 +20418,10 @@
         <v>1232</v>
       </c>
       <c r="E585" t="s">
+        <v>1348</v>
+      </c>
+      <c r="F585" t="s">
         <v>1352</v>
-      </c>
-      <c r="F585" t="s">
-        <v>1348</v>
       </c>
       <c r="G585" t="s">
         <v>1349</v>
@@ -20464,10 +20464,10 @@
         <v>16</v>
       </c>
       <c r="E587" t="s">
+        <v>1390</v>
+      </c>
+      <c r="F587" t="s">
         <v>1352</v>
-      </c>
-      <c r="F587" t="s">
-        <v>1390</v>
       </c>
       <c r="G587" t="s">
         <v>1349</v>
@@ -20487,10 +20487,10 @@
         <v>1232</v>
       </c>
       <c r="E588" t="s">
+        <v>1393</v>
+      </c>
+      <c r="F588" t="s">
         <v>1352</v>
-      </c>
-      <c r="F588" t="s">
-        <v>1393</v>
       </c>
       <c r="G588" t="s">
         <v>1349</v>
@@ -20510,10 +20510,10 @@
         <v>1232</v>
       </c>
       <c r="E589" t="s">
+        <v>1348</v>
+      </c>
+      <c r="F589" t="s">
         <v>1352</v>
-      </c>
-      <c r="F589" t="s">
-        <v>1348</v>
       </c>
       <c r="G589" t="s">
         <v>1349</v>
@@ -20533,10 +20533,10 @@
         <v>34</v>
       </c>
       <c r="E590" t="s">
+        <v>1348</v>
+      </c>
+      <c r="F590" t="s">
         <v>1352</v>
-      </c>
-      <c r="F590" t="s">
-        <v>1348</v>
       </c>
       <c r="G590" t="s">
         <v>1349</v>
@@ -20556,10 +20556,10 @@
         <v>19</v>
       </c>
       <c r="E591" t="s">
+        <v>1348</v>
+      </c>
+      <c r="F591" t="s">
         <v>1352</v>
-      </c>
-      <c r="F591" t="s">
-        <v>1348</v>
       </c>
       <c r="G591" t="s">
         <v>1349</v>
@@ -20579,10 +20579,10 @@
         <v>1232</v>
       </c>
       <c r="E592" t="s">
+        <v>1348</v>
+      </c>
+      <c r="F592" t="s">
         <v>1402</v>
-      </c>
-      <c r="F592" t="s">
-        <v>1348</v>
       </c>
       <c r="G592" t="s">
         <v>1349</v>
@@ -20602,10 +20602,10 @@
         <v>16</v>
       </c>
       <c r="E593" t="s">
+        <v>1348</v>
+      </c>
+      <c r="F593" t="s">
         <v>1352</v>
-      </c>
-      <c r="F593" t="s">
-        <v>1348</v>
       </c>
       <c r="G593" t="s">
         <v>1349</v>
@@ -20625,10 +20625,10 @@
         <v>1232</v>
       </c>
       <c r="E594" t="s">
+        <v>1348</v>
+      </c>
+      <c r="F594" t="s">
         <v>1352</v>
-      </c>
-      <c r="F594" t="s">
-        <v>1348</v>
       </c>
       <c r="G594" t="s">
         <v>1349</v>
@@ -20648,10 +20648,10 @@
         <v>1232</v>
       </c>
       <c r="E595" t="s">
+        <v>1348</v>
+      </c>
+      <c r="F595" t="s">
         <v>1352</v>
-      </c>
-      <c r="F595" t="s">
-        <v>1348</v>
       </c>
       <c r="G595" t="s">
         <v>1349</v>
@@ -20671,10 +20671,10 @@
         <v>1232</v>
       </c>
       <c r="E596" t="s">
+        <v>1348</v>
+      </c>
+      <c r="F596" t="s">
         <v>1352</v>
-      </c>
-      <c r="F596" t="s">
-        <v>1348</v>
       </c>
       <c r="G596" t="s">
         <v>1349</v>
@@ -20878,10 +20878,10 @@
         <v>34</v>
       </c>
       <c r="E605" t="s">
-        <v>1413</v>
+        <v>1440</v>
       </c>
       <c r="F605" t="s">
-        <v>1440</v>
+        <v>1414</v>
       </c>
       <c r="G605" t="s">
         <v>1415</v>
@@ -20970,10 +20970,10 @@
         <v>1232</v>
       </c>
       <c r="E609" t="s">
+        <v>1451</v>
+      </c>
+      <c r="F609" t="s">
         <v>1390</v>
-      </c>
-      <c r="F609" t="s">
-        <v>1451</v>
       </c>
       <c r="G609" t="s">
         <v>1415</v>
@@ -21016,10 +21016,10 @@
         <v>34</v>
       </c>
       <c r="E611" t="s">
+        <v>1418</v>
+      </c>
+      <c r="F611" t="s">
         <v>1456</v>
-      </c>
-      <c r="F611" t="s">
-        <v>1419</v>
       </c>
       <c r="G611" t="s">
         <v>1415</v>
@@ -21039,10 +21039,10 @@
         <v>19</v>
       </c>
       <c r="E612" t="s">
-        <v>1413</v>
+        <v>1459</v>
       </c>
       <c r="F612" t="s">
-        <v>1459</v>
+        <v>1414</v>
       </c>
       <c r="G612" t="s">
         <v>1415</v>
@@ -21085,10 +21085,10 @@
         <v>1232</v>
       </c>
       <c r="E614" t="s">
-        <v>1413</v>
+        <v>1464</v>
       </c>
       <c r="F614" t="s">
-        <v>1464</v>
+        <v>1414</v>
       </c>
       <c r="G614" t="s">
         <v>1415</v>
@@ -21407,10 +21407,10 @@
         <v>1232</v>
       </c>
       <c r="E628" t="s">
+        <v>1483</v>
+      </c>
+      <c r="F628" t="s">
         <v>1498</v>
-      </c>
-      <c r="F628" t="s">
-        <v>1484</v>
       </c>
       <c r="G628" t="s">
         <v>1485</v>
@@ -21430,10 +21430,10 @@
         <v>34</v>
       </c>
       <c r="E629" t="s">
-        <v>1483</v>
+        <v>1501</v>
       </c>
       <c r="F629" t="s">
-        <v>1501</v>
+        <v>1484</v>
       </c>
       <c r="G629" t="s">
         <v>1485</v>
@@ -21499,10 +21499,10 @@
         <v>34</v>
       </c>
       <c r="E632" t="s">
+        <v>1501</v>
+      </c>
+      <c r="F632" t="s">
         <v>1508</v>
-      </c>
-      <c r="F632" t="s">
-        <v>1501</v>
       </c>
       <c r="G632" t="s">
         <v>1485</v>
@@ -21591,10 +21591,10 @@
         <v>1232</v>
       </c>
       <c r="E636" t="s">
-        <v>1483</v>
+        <v>1521</v>
       </c>
       <c r="F636" t="s">
-        <v>1521</v>
+        <v>1484</v>
       </c>
       <c r="G636" t="s">
         <v>1485</v>
@@ -21729,10 +21729,10 @@
         <v>19</v>
       </c>
       <c r="E642" t="s">
-        <v>1483</v>
+        <v>1538</v>
       </c>
       <c r="F642" t="s">
-        <v>1538</v>
+        <v>1484</v>
       </c>
       <c r="G642" t="s">
         <v>1485</v>
@@ -21752,10 +21752,10 @@
         <v>19</v>
       </c>
       <c r="E643" t="s">
-        <v>1483</v>
+        <v>1541</v>
       </c>
       <c r="F643" t="s">
-        <v>1541</v>
+        <v>1484</v>
       </c>
       <c r="G643" t="s">
         <v>1485</v>
@@ -21821,10 +21821,10 @@
         <v>34</v>
       </c>
       <c r="E646" t="s">
-        <v>1483</v>
+        <v>1548</v>
       </c>
       <c r="F646" t="s">
-        <v>1548</v>
+        <v>1484</v>
       </c>
       <c r="G646" t="s">
         <v>1485</v>
@@ -21936,10 +21936,10 @@
         <v>34</v>
       </c>
       <c r="E651" t="s">
+        <v>1555</v>
+      </c>
+      <c r="F651" t="s">
         <v>1564</v>
-      </c>
-      <c r="F651" t="s">
-        <v>1556</v>
       </c>
       <c r="G651" t="s">
         <v>1557</v>
@@ -22005,10 +22005,10 @@
         <v>19</v>
       </c>
       <c r="E654" t="s">
-        <v>1483</v>
+        <v>1541</v>
       </c>
       <c r="F654" t="s">
-        <v>1541</v>
+        <v>1484</v>
       </c>
       <c r="G654" t="s">
         <v>1557</v>
@@ -22120,10 +22120,10 @@
         <v>34</v>
       </c>
       <c r="E659" t="s">
+        <v>1521</v>
+      </c>
+      <c r="F659" t="s">
         <v>1587</v>
-      </c>
-      <c r="F659" t="s">
-        <v>1521</v>
       </c>
       <c r="G659" t="s">
         <v>1557</v>
@@ -22189,10 +22189,10 @@
         <v>34</v>
       </c>
       <c r="E662" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="F662" t="s">
-        <v>1568</v>
+        <v>1560</v>
       </c>
       <c r="G662" t="s">
         <v>1557</v>
@@ -22235,10 +22235,10 @@
         <v>19</v>
       </c>
       <c r="E664" t="s">
+        <v>1541</v>
+      </c>
+      <c r="F664" t="s">
         <v>1602</v>
-      </c>
-      <c r="F664" t="s">
-        <v>1541</v>
       </c>
       <c r="G664" t="s">
         <v>1557</v>
@@ -22258,10 +22258,10 @@
         <v>1232</v>
       </c>
       <c r="E665" t="s">
-        <v>1567</v>
+        <v>1605</v>
       </c>
       <c r="F665" t="s">
-        <v>1605</v>
+        <v>1568</v>
       </c>
       <c r="G665" t="s">
         <v>1557</v>
@@ -22281,10 +22281,10 @@
         <v>34</v>
       </c>
       <c r="E666" t="s">
-        <v>1555</v>
+        <v>1605</v>
       </c>
       <c r="F666" t="s">
-        <v>1605</v>
+        <v>1556</v>
       </c>
       <c r="G666" t="s">
         <v>1557</v>
@@ -22350,10 +22350,10 @@
         <v>19</v>
       </c>
       <c r="E669" t="s">
+        <v>1541</v>
+      </c>
+      <c r="F669" t="s">
         <v>1587</v>
-      </c>
-      <c r="F669" t="s">
-        <v>1541</v>
       </c>
       <c r="G669" t="s">
         <v>1557</v>
@@ -22396,10 +22396,10 @@
         <v>34</v>
       </c>
       <c r="E671" t="s">
+        <v>1555</v>
+      </c>
+      <c r="F671" t="s">
         <v>1620</v>
-      </c>
-      <c r="F671" t="s">
-        <v>1556</v>
       </c>
       <c r="G671" t="s">
         <v>1557</v>
@@ -22465,10 +22465,10 @@
         <v>19</v>
       </c>
       <c r="E674" t="s">
-        <v>1590</v>
+        <v>1541</v>
       </c>
       <c r="F674" t="s">
-        <v>1541</v>
+        <v>1591</v>
       </c>
       <c r="G674" t="s">
         <v>1557</v>
@@ -22488,10 +22488,10 @@
         <v>34</v>
       </c>
       <c r="E675" t="s">
+        <v>1555</v>
+      </c>
+      <c r="F675" t="s">
         <v>1564</v>
-      </c>
-      <c r="F675" t="s">
-        <v>1556</v>
       </c>
       <c r="G675" t="s">
         <v>1557</v>
@@ -22511,10 +22511,10 @@
         <v>19</v>
       </c>
       <c r="E676" t="s">
-        <v>1567</v>
+        <v>1631</v>
       </c>
       <c r="F676" t="s">
-        <v>1631</v>
+        <v>1568</v>
       </c>
       <c r="G676" t="s">
         <v>1557</v>
@@ -22810,10 +22810,10 @@
         <v>34</v>
       </c>
       <c r="E689" t="s">
+        <v>1649</v>
+      </c>
+      <c r="F689" t="s">
         <v>1665</v>
-      </c>
-      <c r="F689" t="s">
-        <v>1650</v>
       </c>
       <c r="G689" t="s">
         <v>1646</v>
@@ -22879,10 +22879,10 @@
         <v>19</v>
       </c>
       <c r="E692" t="s">
-        <v>1567</v>
+        <v>1674</v>
       </c>
       <c r="F692" t="s">
-        <v>1674</v>
+        <v>1568</v>
       </c>
       <c r="G692" t="s">
         <v>1646</v>
@@ -23132,10 +23132,10 @@
         <v>34</v>
       </c>
       <c r="E703" t="s">
-        <v>1701</v>
+        <v>1711</v>
       </c>
       <c r="F703" t="s">
-        <v>1711</v>
+        <v>1702</v>
       </c>
       <c r="G703" t="s">
         <v>1646</v>
@@ -23178,10 +23178,10 @@
         <v>19</v>
       </c>
       <c r="E705" t="s">
-        <v>1695</v>
+        <v>1716</v>
       </c>
       <c r="F705" t="s">
-        <v>1716</v>
+        <v>1696</v>
       </c>
       <c r="G705" t="s">
         <v>1646</v>
@@ -23224,10 +23224,10 @@
         <v>19</v>
       </c>
       <c r="E707" t="s">
-        <v>1695</v>
+        <v>1653</v>
       </c>
       <c r="F707" t="s">
-        <v>1654</v>
+        <v>1696</v>
       </c>
       <c r="G707" t="s">
         <v>1646</v>
@@ -23247,10 +23247,10 @@
         <v>34</v>
       </c>
       <c r="E708" t="s">
-        <v>1649</v>
+        <v>1723</v>
       </c>
       <c r="F708" t="s">
-        <v>1723</v>
+        <v>1650</v>
       </c>
       <c r="G708" t="s">
         <v>1646</v>
@@ -23316,10 +23316,10 @@
         <v>1232</v>
       </c>
       <c r="E711" t="s">
-        <v>1695</v>
+        <v>1653</v>
       </c>
       <c r="F711" t="s">
-        <v>1654</v>
+        <v>1696</v>
       </c>
       <c r="G711" t="s">
         <v>1646</v>
@@ -23408,10 +23408,10 @@
         <v>34</v>
       </c>
       <c r="E715" t="s">
-        <v>1695</v>
+        <v>1691</v>
       </c>
       <c r="F715" t="s">
-        <v>1692</v>
+        <v>1696</v>
       </c>
       <c r="G715" t="s">
         <v>1646</v>
@@ -23500,10 +23500,10 @@
         <v>1232</v>
       </c>
       <c r="E719" t="s">
-        <v>1746</v>
+        <v>1751</v>
       </c>
       <c r="F719" t="s">
-        <v>1751</v>
+        <v>1747</v>
       </c>
       <c r="G719" t="s">
         <v>1748</v>
@@ -23523,10 +23523,10 @@
         <v>1232</v>
       </c>
       <c r="E720" t="s">
-        <v>1746</v>
+        <v>1751</v>
       </c>
       <c r="F720" t="s">
-        <v>1751</v>
+        <v>1747</v>
       </c>
       <c r="G720" t="s">
         <v>1748</v>
@@ -23546,10 +23546,10 @@
         <v>1232</v>
       </c>
       <c r="E721" t="s">
-        <v>1746</v>
+        <v>1751</v>
       </c>
       <c r="F721" t="s">
-        <v>1751</v>
+        <v>1747</v>
       </c>
       <c r="G721" t="s">
         <v>1748</v>
@@ -23569,10 +23569,10 @@
         <v>1232</v>
       </c>
       <c r="E722" t="s">
-        <v>1746</v>
+        <v>1751</v>
       </c>
       <c r="F722" t="s">
-        <v>1751</v>
+        <v>1747</v>
       </c>
       <c r="G722" t="s">
         <v>1748</v>
@@ -23592,10 +23592,10 @@
         <v>1232</v>
       </c>
       <c r="E723" t="s">
-        <v>1746</v>
+        <v>1751</v>
       </c>
       <c r="F723" t="s">
-        <v>1751</v>
+        <v>1747</v>
       </c>
       <c r="G723" t="s">
         <v>1748</v>
@@ -23615,10 +23615,10 @@
         <v>19</v>
       </c>
       <c r="E724" t="s">
-        <v>1746</v>
+        <v>1751</v>
       </c>
       <c r="F724" t="s">
-        <v>1751</v>
+        <v>1747</v>
       </c>
       <c r="G724" t="s">
         <v>1748</v>
@@ -23684,10 +23684,10 @@
         <v>1232</v>
       </c>
       <c r="E727" t="s">
-        <v>1746</v>
+        <v>1751</v>
       </c>
       <c r="F727" t="s">
-        <v>1751</v>
+        <v>1747</v>
       </c>
       <c r="G727" t="s">
         <v>1748</v>
@@ -23707,10 +23707,10 @@
         <v>1232</v>
       </c>
       <c r="E728" t="s">
-        <v>1746</v>
+        <v>1751</v>
       </c>
       <c r="F728" t="s">
-        <v>1751</v>
+        <v>1747</v>
       </c>
       <c r="G728" t="s">
         <v>1748</v>
@@ -23753,10 +23753,10 @@
         <v>16</v>
       </c>
       <c r="E730" t="s">
-        <v>1746</v>
+        <v>1751</v>
       </c>
       <c r="F730" t="s">
-        <v>1751</v>
+        <v>1747</v>
       </c>
       <c r="G730" t="s">
         <v>1748</v>
@@ -23822,10 +23822,10 @@
         <v>34</v>
       </c>
       <c r="E733" t="s">
-        <v>1746</v>
+        <v>1788</v>
       </c>
       <c r="F733" t="s">
-        <v>1788</v>
+        <v>1747</v>
       </c>
       <c r="G733" t="s">
         <v>1748</v>
@@ -23868,10 +23868,10 @@
         <v>1232</v>
       </c>
       <c r="E735" t="s">
-        <v>1746</v>
+        <v>1751</v>
       </c>
       <c r="F735" t="s">
-        <v>1751</v>
+        <v>1747</v>
       </c>
       <c r="G735" t="s">
         <v>1748</v>
@@ -23891,10 +23891,10 @@
         <v>1232</v>
       </c>
       <c r="E736" t="s">
-        <v>1746</v>
+        <v>1797</v>
       </c>
       <c r="F736" t="s">
-        <v>1797</v>
+        <v>1747</v>
       </c>
       <c r="G736" t="s">
         <v>1748</v>
@@ -23914,10 +23914,10 @@
         <v>19</v>
       </c>
       <c r="E737" t="s">
-        <v>1746</v>
+        <v>1751</v>
       </c>
       <c r="F737" t="s">
-        <v>1751</v>
+        <v>1747</v>
       </c>
       <c r="G737" t="s">
         <v>1748</v>
@@ -23937,10 +23937,10 @@
         <v>19</v>
       </c>
       <c r="E738" t="s">
-        <v>1653</v>
+        <v>1802</v>
       </c>
       <c r="F738" t="s">
-        <v>1802</v>
+        <v>1654</v>
       </c>
       <c r="G738" t="s">
         <v>1748</v>
@@ -23960,10 +23960,10 @@
         <v>1232</v>
       </c>
       <c r="E739" t="s">
-        <v>1746</v>
+        <v>1751</v>
       </c>
       <c r="F739" t="s">
-        <v>1751</v>
+        <v>1747</v>
       </c>
       <c r="G739" t="s">
         <v>1748</v>
@@ -23983,10 +23983,10 @@
         <v>1232</v>
       </c>
       <c r="E740" t="s">
-        <v>1746</v>
+        <v>1751</v>
       </c>
       <c r="F740" t="s">
-        <v>1751</v>
+        <v>1747</v>
       </c>
       <c r="G740" t="s">
         <v>1748</v>
@@ -24029,10 +24029,10 @@
         <v>19</v>
       </c>
       <c r="E742" t="s">
-        <v>1746</v>
+        <v>1813</v>
       </c>
       <c r="F742" t="s">
-        <v>1813</v>
+        <v>1747</v>
       </c>
       <c r="G742" t="s">
         <v>1748</v>
@@ -24052,10 +24052,10 @@
         <v>1232</v>
       </c>
       <c r="E743" t="s">
-        <v>1746</v>
+        <v>1751</v>
       </c>
       <c r="F743" t="s">
-        <v>1751</v>
+        <v>1747</v>
       </c>
       <c r="G743" t="s">
         <v>1748</v>
@@ -24098,10 +24098,10 @@
         <v>34</v>
       </c>
       <c r="E745" t="s">
-        <v>1746</v>
+        <v>1820</v>
       </c>
       <c r="F745" t="s">
-        <v>1820</v>
+        <v>1747</v>
       </c>
       <c r="G745" t="s">
         <v>1748</v>
@@ -24121,10 +24121,10 @@
         <v>1232</v>
       </c>
       <c r="E746" t="s">
-        <v>1746</v>
+        <v>1751</v>
       </c>
       <c r="F746" t="s">
-        <v>1751</v>
+        <v>1747</v>
       </c>
       <c r="G746" t="s">
         <v>1748</v>
@@ -24144,10 +24144,10 @@
         <v>1232</v>
       </c>
       <c r="E747" t="s">
-        <v>1746</v>
+        <v>1751</v>
       </c>
       <c r="F747" t="s">
-        <v>1751</v>
+        <v>1747</v>
       </c>
       <c r="G747" t="s">
         <v>1748</v>
@@ -24167,10 +24167,10 @@
         <v>1232</v>
       </c>
       <c r="E748" t="s">
-        <v>1746</v>
+        <v>1751</v>
       </c>
       <c r="F748" t="s">
-        <v>1751</v>
+        <v>1747</v>
       </c>
       <c r="G748" t="s">
         <v>1748</v>
@@ -24190,10 +24190,10 @@
         <v>1232</v>
       </c>
       <c r="E749" t="s">
-        <v>1746</v>
+        <v>1751</v>
       </c>
       <c r="F749" t="s">
-        <v>1751</v>
+        <v>1747</v>
       </c>
       <c r="G749" t="s">
         <v>1748</v>
@@ -24397,10 +24397,10 @@
         <v>34</v>
       </c>
       <c r="E758" t="s">
-        <v>1836</v>
+        <v>1831</v>
       </c>
       <c r="F758" t="s">
-        <v>1832</v>
+        <v>1837</v>
       </c>
       <c r="G758" t="s">
         <v>1833</v>
@@ -24420,10 +24420,10 @@
         <v>19</v>
       </c>
       <c r="E759" t="s">
-        <v>1840</v>
+        <v>1797</v>
       </c>
       <c r="F759" t="s">
-        <v>1797</v>
+        <v>1841</v>
       </c>
       <c r="G759" t="s">
         <v>1833</v>
@@ -24489,10 +24489,10 @@
         <v>34</v>
       </c>
       <c r="E762" t="s">
+        <v>1797</v>
+      </c>
+      <c r="F762" t="s">
         <v>1862</v>
-      </c>
-      <c r="F762" t="s">
-        <v>1797</v>
       </c>
       <c r="G762" t="s">
         <v>1833</v>
@@ -24558,10 +24558,10 @@
         <v>34</v>
       </c>
       <c r="E765" t="s">
-        <v>1831</v>
+        <v>1840</v>
       </c>
       <c r="F765" t="s">
-        <v>1841</v>
+        <v>1832</v>
       </c>
       <c r="G765" t="s">
         <v>1833</v>
@@ -24581,10 +24581,10 @@
         <v>34</v>
       </c>
       <c r="E766" t="s">
+        <v>1873</v>
+      </c>
+      <c r="F766" t="s">
         <v>1862</v>
-      </c>
-      <c r="F766" t="s">
-        <v>1873</v>
       </c>
       <c r="G766" t="s">
         <v>1833</v>
@@ -24834,10 +24834,10 @@
         <v>1232</v>
       </c>
       <c r="E777" t="s">
-        <v>1900</v>
+        <v>1905</v>
       </c>
       <c r="F777" t="s">
-        <v>1905</v>
+        <v>1901</v>
       </c>
       <c r="G777" t="s">
         <v>1902</v>
@@ -24903,10 +24903,10 @@
         <v>1232</v>
       </c>
       <c r="E780" t="s">
-        <v>1900</v>
+        <v>1905</v>
       </c>
       <c r="F780" t="s">
-        <v>1905</v>
+        <v>1901</v>
       </c>
       <c r="G780" t="s">
         <v>1902</v>
@@ -24926,10 +24926,10 @@
         <v>1232</v>
       </c>
       <c r="E781" t="s">
-        <v>1900</v>
+        <v>1905</v>
       </c>
       <c r="F781" t="s">
-        <v>1905</v>
+        <v>1901</v>
       </c>
       <c r="G781" t="s">
         <v>1902</v>
@@ -24949,10 +24949,10 @@
         <v>1232</v>
       </c>
       <c r="E782" t="s">
-        <v>1900</v>
+        <v>1920</v>
       </c>
       <c r="F782" t="s">
-        <v>1920</v>
+        <v>1901</v>
       </c>
       <c r="G782" t="s">
         <v>1902</v>
@@ -24972,10 +24972,10 @@
         <v>1232</v>
       </c>
       <c r="E783" t="s">
-        <v>1900</v>
+        <v>1905</v>
       </c>
       <c r="F783" t="s">
-        <v>1905</v>
+        <v>1901</v>
       </c>
       <c r="G783" t="s">
         <v>1902</v>
@@ -24995,10 +24995,10 @@
         <v>1232</v>
       </c>
       <c r="E784" t="s">
-        <v>1900</v>
+        <v>1905</v>
       </c>
       <c r="F784" t="s">
-        <v>1905</v>
+        <v>1901</v>
       </c>
       <c r="G784" t="s">
         <v>1902</v>
@@ -25018,10 +25018,10 @@
         <v>1232</v>
       </c>
       <c r="E785" t="s">
-        <v>1900</v>
+        <v>1905</v>
       </c>
       <c r="F785" t="s">
-        <v>1905</v>
+        <v>1901</v>
       </c>
       <c r="G785" t="s">
         <v>1902</v>
@@ -25041,10 +25041,10 @@
         <v>1232</v>
       </c>
       <c r="E786" t="s">
-        <v>1900</v>
+        <v>1905</v>
       </c>
       <c r="F786" t="s">
-        <v>1905</v>
+        <v>1901</v>
       </c>
       <c r="G786" t="s">
         <v>1902</v>
@@ -25064,10 +25064,10 @@
         <v>1232</v>
       </c>
       <c r="E787" t="s">
-        <v>1900</v>
+        <v>1905</v>
       </c>
       <c r="F787" t="s">
-        <v>1905</v>
+        <v>1901</v>
       </c>
       <c r="G787" t="s">
         <v>1902</v>
@@ -25087,10 +25087,10 @@
         <v>1232</v>
       </c>
       <c r="E788" t="s">
-        <v>1900</v>
+        <v>1905</v>
       </c>
       <c r="F788" t="s">
-        <v>1905</v>
+        <v>1901</v>
       </c>
       <c r="G788" t="s">
         <v>1902</v>
@@ -25110,10 +25110,10 @@
         <v>34</v>
       </c>
       <c r="E789" t="s">
+        <v>1900</v>
+      </c>
+      <c r="F789" t="s">
         <v>1935</v>
-      </c>
-      <c r="F789" t="s">
-        <v>1901</v>
       </c>
       <c r="G789" t="s">
         <v>1902</v>
@@ -25133,10 +25133,10 @@
         <v>1232</v>
       </c>
       <c r="E790" t="s">
-        <v>1900</v>
+        <v>1905</v>
       </c>
       <c r="F790" t="s">
-        <v>1905</v>
+        <v>1901</v>
       </c>
       <c r="G790" t="s">
         <v>1902</v>
@@ -25156,10 +25156,10 @@
         <v>34</v>
       </c>
       <c r="E791" t="s">
+        <v>1920</v>
+      </c>
+      <c r="F791" t="s">
         <v>1940</v>
-      </c>
-      <c r="F791" t="s">
-        <v>1920</v>
       </c>
       <c r="G791" t="s">
         <v>1902</v>
@@ -25179,10 +25179,10 @@
         <v>34</v>
       </c>
       <c r="E792" t="s">
+        <v>1943</v>
+      </c>
+      <c r="F792" t="s">
         <v>1935</v>
-      </c>
-      <c r="F792" t="s">
-        <v>1943</v>
       </c>
       <c r="G792" t="s">
         <v>1902</v>
@@ -25202,10 +25202,10 @@
         <v>1232</v>
       </c>
       <c r="E793" t="s">
-        <v>1900</v>
+        <v>1905</v>
       </c>
       <c r="F793" t="s">
-        <v>1905</v>
+        <v>1901</v>
       </c>
       <c r="G793" t="s">
         <v>1902</v>
@@ -25225,10 +25225,10 @@
         <v>34</v>
       </c>
       <c r="E794" t="s">
+        <v>1905</v>
+      </c>
+      <c r="F794" t="s">
         <v>1948</v>
-      </c>
-      <c r="F794" t="s">
-        <v>1905</v>
       </c>
       <c r="G794" t="s">
         <v>1902</v>
@@ -25248,10 +25248,10 @@
         <v>34</v>
       </c>
       <c r="E795" t="s">
-        <v>1900</v>
+        <v>1951</v>
       </c>
       <c r="F795" t="s">
-        <v>1951</v>
+        <v>1901</v>
       </c>
       <c r="G795" t="s">
         <v>1902</v>
@@ -25271,10 +25271,10 @@
         <v>1232</v>
       </c>
       <c r="E796" t="s">
-        <v>1900</v>
+        <v>1905</v>
       </c>
       <c r="F796" t="s">
-        <v>1905</v>
+        <v>1901</v>
       </c>
       <c r="G796" t="s">
         <v>1902</v>
@@ -25340,10 +25340,10 @@
         <v>1232</v>
       </c>
       <c r="E799" t="s">
-        <v>1900</v>
+        <v>1905</v>
       </c>
       <c r="F799" t="s">
-        <v>1905</v>
+        <v>1901</v>
       </c>
       <c r="G799" t="s">
         <v>1902</v>
@@ -25363,10 +25363,10 @@
         <v>1232</v>
       </c>
       <c r="E800" t="s">
-        <v>1900</v>
+        <v>1905</v>
       </c>
       <c r="F800" t="s">
-        <v>1905</v>
+        <v>1901</v>
       </c>
       <c r="G800" t="s">
         <v>1902</v>
@@ -25386,10 +25386,10 @@
         <v>1232</v>
       </c>
       <c r="E801" t="s">
-        <v>1900</v>
+        <v>1905</v>
       </c>
       <c r="F801" t="s">
-        <v>1905</v>
+        <v>1901</v>
       </c>
       <c r="G801" t="s">
         <v>1902</v>
@@ -25409,10 +25409,10 @@
         <v>1232</v>
       </c>
       <c r="E802" t="s">
-        <v>1900</v>
+        <v>1905</v>
       </c>
       <c r="F802" t="s">
-        <v>1905</v>
+        <v>1901</v>
       </c>
       <c r="G802" t="s">
         <v>1902</v>
@@ -25432,10 +25432,10 @@
         <v>1232</v>
       </c>
       <c r="E803" t="s">
-        <v>1900</v>
+        <v>1905</v>
       </c>
       <c r="F803" t="s">
-        <v>1905</v>
+        <v>1901</v>
       </c>
       <c r="G803" t="s">
         <v>1902</v>
@@ -25455,10 +25455,10 @@
         <v>1232</v>
       </c>
       <c r="E804" t="s">
-        <v>1900</v>
+        <v>1905</v>
       </c>
       <c r="F804" t="s">
-        <v>1905</v>
+        <v>1901</v>
       </c>
       <c r="G804" t="s">
         <v>1902</v>
@@ -25478,10 +25478,10 @@
         <v>1232</v>
       </c>
       <c r="E805" t="s">
-        <v>1900</v>
+        <v>1905</v>
       </c>
       <c r="F805" t="s">
-        <v>1905</v>
+        <v>1901</v>
       </c>
       <c r="G805" t="s">
         <v>1902</v>
@@ -25501,10 +25501,10 @@
         <v>1232</v>
       </c>
       <c r="E806" t="s">
-        <v>1900</v>
+        <v>1905</v>
       </c>
       <c r="F806" t="s">
-        <v>1905</v>
+        <v>1901</v>
       </c>
       <c r="G806" t="s">
         <v>1902</v>
@@ -25524,10 +25524,10 @@
         <v>1232</v>
       </c>
       <c r="E807" t="s">
-        <v>1900</v>
+        <v>1905</v>
       </c>
       <c r="F807" t="s">
-        <v>1905</v>
+        <v>1901</v>
       </c>
       <c r="G807" t="s">
         <v>1902</v>
@@ -25685,10 +25685,10 @@
         <v>1232</v>
       </c>
       <c r="E814" t="s">
-        <v>1982</v>
+        <v>1992</v>
       </c>
       <c r="F814" t="s">
-        <v>1993</v>
+        <v>1983</v>
       </c>
       <c r="G814" t="s">
         <v>1984</v>
@@ -25892,10 +25892,10 @@
         <v>1987</v>
       </c>
       <c r="E823" t="s">
-        <v>1982</v>
+        <v>2020</v>
       </c>
       <c r="F823" t="s">
-        <v>2021</v>
+        <v>1983</v>
       </c>
       <c r="G823" t="s">
         <v>1984</v>
@@ -26007,10 +26007,10 @@
         <v>1987</v>
       </c>
       <c r="E828" t="s">
-        <v>1982</v>
+        <v>2020</v>
       </c>
       <c r="F828" t="s">
-        <v>2021</v>
+        <v>1983</v>
       </c>
       <c r="G828" t="s">
         <v>1984</v>
@@ -26053,10 +26053,10 @@
         <v>1987</v>
       </c>
       <c r="E830" t="s">
-        <v>1982</v>
+        <v>1992</v>
       </c>
       <c r="F830" t="s">
-        <v>1993</v>
+        <v>1983</v>
       </c>
       <c r="G830" t="s">
         <v>1984</v>
@@ -26283,10 +26283,10 @@
         <v>1987</v>
       </c>
       <c r="E840" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="F840" t="s">
-        <v>2061</v>
+        <v>2057</v>
       </c>
       <c r="G840" t="s">
         <v>2058</v>
@@ -26306,10 +26306,10 @@
         <v>1987</v>
       </c>
       <c r="E841" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="F841" t="s">
-        <v>2061</v>
+        <v>2057</v>
       </c>
       <c r="G841" t="s">
         <v>2058</v>
@@ -26329,10 +26329,10 @@
         <v>1987</v>
       </c>
       <c r="E842" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="F842" t="s">
-        <v>2061</v>
+        <v>2057</v>
       </c>
       <c r="G842" t="s">
         <v>2058</v>
@@ -26352,10 +26352,10 @@
         <v>1987</v>
       </c>
       <c r="E843" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="F843" t="s">
-        <v>2061</v>
+        <v>2057</v>
       </c>
       <c r="G843" t="s">
         <v>2058</v>
@@ -26375,10 +26375,10 @@
         <v>1987</v>
       </c>
       <c r="E844" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="F844" t="s">
-        <v>2061</v>
+        <v>2057</v>
       </c>
       <c r="G844" t="s">
         <v>2058</v>
@@ -26398,10 +26398,10 @@
         <v>1232</v>
       </c>
       <c r="E845" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="F845" t="s">
-        <v>2061</v>
+        <v>2057</v>
       </c>
       <c r="G845" t="s">
         <v>2058</v>
@@ -26421,10 +26421,10 @@
         <v>1987</v>
       </c>
       <c r="E846" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="F846" t="s">
-        <v>2061</v>
+        <v>2057</v>
       </c>
       <c r="G846" t="s">
         <v>2058</v>
@@ -26444,10 +26444,10 @@
         <v>1987</v>
       </c>
       <c r="E847" t="s">
-        <v>1992</v>
+        <v>2076</v>
       </c>
       <c r="F847" t="s">
-        <v>2076</v>
+        <v>1993</v>
       </c>
       <c r="G847" t="s">
         <v>2058</v>
@@ -26467,10 +26467,10 @@
         <v>1987</v>
       </c>
       <c r="E848" t="s">
-        <v>1992</v>
+        <v>2076</v>
       </c>
       <c r="F848" t="s">
-        <v>2076</v>
+        <v>1993</v>
       </c>
       <c r="G848" t="s">
         <v>2058</v>
@@ -26490,10 +26490,10 @@
         <v>1232</v>
       </c>
       <c r="E849" t="s">
-        <v>1992</v>
+        <v>2076</v>
       </c>
       <c r="F849" t="s">
-        <v>2076</v>
+        <v>1993</v>
       </c>
       <c r="G849" t="s">
         <v>2058</v>
@@ -26513,10 +26513,10 @@
         <v>1987</v>
       </c>
       <c r="E850" t="s">
+        <v>2076</v>
+      </c>
+      <c r="F850" t="s">
         <v>2083</v>
-      </c>
-      <c r="F850" t="s">
-        <v>2076</v>
       </c>
       <c r="G850" t="s">
         <v>2058</v>
@@ -26536,10 +26536,10 @@
         <v>1987</v>
       </c>
       <c r="E851" t="s">
-        <v>1992</v>
+        <v>2076</v>
       </c>
       <c r="F851" t="s">
-        <v>2076</v>
+        <v>1993</v>
       </c>
       <c r="G851" t="s">
         <v>2058</v>
@@ -26559,10 +26559,10 @@
         <v>1987</v>
       </c>
       <c r="E852" t="s">
-        <v>1992</v>
+        <v>2076</v>
       </c>
       <c r="F852" t="s">
-        <v>2076</v>
+        <v>1993</v>
       </c>
       <c r="G852" t="s">
         <v>2058</v>
@@ -26582,10 +26582,10 @@
         <v>1987</v>
       </c>
       <c r="E853" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="F853" t="s">
-        <v>2061</v>
+        <v>2057</v>
       </c>
       <c r="G853" t="s">
         <v>2058</v>
@@ -26605,10 +26605,10 @@
         <v>19</v>
       </c>
       <c r="E854" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="F854" t="s">
-        <v>2061</v>
+        <v>2057</v>
       </c>
       <c r="G854" t="s">
         <v>2058</v>
@@ -26628,10 +26628,10 @@
         <v>19</v>
       </c>
       <c r="E855" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="F855" t="s">
-        <v>2061</v>
+        <v>2057</v>
       </c>
       <c r="G855" t="s">
         <v>2058</v>
@@ -26651,10 +26651,10 @@
         <v>19</v>
       </c>
       <c r="E856" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="F856" t="s">
-        <v>2061</v>
+        <v>2057</v>
       </c>
       <c r="G856" t="s">
         <v>2058</v>
@@ -26674,10 +26674,10 @@
         <v>1987</v>
       </c>
       <c r="E857" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="F857" t="s">
-        <v>2061</v>
+        <v>2057</v>
       </c>
       <c r="G857" t="s">
         <v>2058</v>
@@ -26697,10 +26697,10 @@
         <v>1987</v>
       </c>
       <c r="E858" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="F858" t="s">
-        <v>2061</v>
+        <v>2057</v>
       </c>
       <c r="G858" t="s">
         <v>2058</v>
@@ -26720,10 +26720,10 @@
         <v>19</v>
       </c>
       <c r="E859" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="F859" t="s">
-        <v>2061</v>
+        <v>2057</v>
       </c>
       <c r="G859" t="s">
         <v>2058</v>
@@ -26743,10 +26743,10 @@
         <v>1987</v>
       </c>
       <c r="E860" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="F860" t="s">
-        <v>2061</v>
+        <v>2057</v>
       </c>
       <c r="G860" t="s">
         <v>2058</v>
@@ -26766,10 +26766,10 @@
         <v>1987</v>
       </c>
       <c r="E861" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="F861" t="s">
-        <v>2061</v>
+        <v>2057</v>
       </c>
       <c r="G861" t="s">
         <v>2058</v>
@@ -26789,10 +26789,10 @@
         <v>1232</v>
       </c>
       <c r="E862" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="F862" t="s">
-        <v>2061</v>
+        <v>2057</v>
       </c>
       <c r="G862" t="s">
         <v>2058</v>
@@ -26812,10 +26812,10 @@
         <v>1987</v>
       </c>
       <c r="E863" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="F863" t="s">
-        <v>2061</v>
+        <v>2057</v>
       </c>
       <c r="G863" t="s">
         <v>2058</v>
@@ -26835,10 +26835,10 @@
         <v>1987</v>
       </c>
       <c r="E864" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="F864" t="s">
-        <v>2061</v>
+        <v>2057</v>
       </c>
       <c r="G864" t="s">
         <v>2058</v>
@@ -26858,10 +26858,10 @@
         <v>1987</v>
       </c>
       <c r="E865" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="F865" t="s">
-        <v>2061</v>
+        <v>2057</v>
       </c>
       <c r="G865" t="s">
         <v>2058</v>
@@ -26881,10 +26881,10 @@
         <v>1232</v>
       </c>
       <c r="E866" t="s">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="F866" t="s">
-        <v>2061</v>
+        <v>2057</v>
       </c>
       <c r="G866" t="s">
         <v>2058</v>
@@ -26927,10 +26927,10 @@
         <v>1987</v>
       </c>
       <c r="E868" t="s">
+        <v>2118</v>
+      </c>
+      <c r="F868" t="s">
         <v>2123</v>
-      </c>
-      <c r="F868" t="s">
-        <v>2119</v>
       </c>
       <c r="G868" t="s">
         <v>2120</v>
@@ -26950,10 +26950,10 @@
         <v>1987</v>
       </c>
       <c r="E869" t="s">
+        <v>2118</v>
+      </c>
+      <c r="F869" t="s">
         <v>2123</v>
-      </c>
-      <c r="F869" t="s">
-        <v>2119</v>
       </c>
       <c r="G869" t="s">
         <v>2120</v>
@@ -26973,10 +26973,10 @@
         <v>1987</v>
       </c>
       <c r="E870" t="s">
+        <v>2118</v>
+      </c>
+      <c r="F870" t="s">
         <v>2123</v>
-      </c>
-      <c r="F870" t="s">
-        <v>2119</v>
       </c>
       <c r="G870" t="s">
         <v>2120</v>
@@ -26996,10 +26996,10 @@
         <v>1987</v>
       </c>
       <c r="E871" t="s">
+        <v>2118</v>
+      </c>
+      <c r="F871" t="s">
         <v>2123</v>
-      </c>
-      <c r="F871" t="s">
-        <v>2119</v>
       </c>
       <c r="G871" t="s">
         <v>2120</v>
@@ -27019,10 +27019,10 @@
         <v>19</v>
       </c>
       <c r="E872" t="s">
+        <v>2118</v>
+      </c>
+      <c r="F872" t="s">
         <v>2123</v>
-      </c>
-      <c r="F872" t="s">
-        <v>2119</v>
       </c>
       <c r="G872" t="s">
         <v>2120</v>
@@ -27042,10 +27042,10 @@
         <v>19</v>
       </c>
       <c r="E873" t="s">
+        <v>2118</v>
+      </c>
+      <c r="F873" t="s">
         <v>2123</v>
-      </c>
-      <c r="F873" t="s">
-        <v>2119</v>
       </c>
       <c r="G873" t="s">
         <v>2120</v>
@@ -27065,10 +27065,10 @@
         <v>1987</v>
       </c>
       <c r="E874" t="s">
+        <v>2118</v>
+      </c>
+      <c r="F874" t="s">
         <v>2123</v>
-      </c>
-      <c r="F874" t="s">
-        <v>2119</v>
       </c>
       <c r="G874" t="s">
         <v>2120</v>
@@ -27088,10 +27088,10 @@
         <v>1987</v>
       </c>
       <c r="E875" t="s">
+        <v>2118</v>
+      </c>
+      <c r="F875" t="s">
         <v>2123</v>
-      </c>
-      <c r="F875" t="s">
-        <v>2119</v>
       </c>
       <c r="G875" t="s">
         <v>2120</v>
@@ -27111,10 +27111,10 @@
         <v>1232</v>
       </c>
       <c r="E876" t="s">
+        <v>2118</v>
+      </c>
+      <c r="F876" t="s">
         <v>2123</v>
-      </c>
-      <c r="F876" t="s">
-        <v>2119</v>
       </c>
       <c r="G876" t="s">
         <v>2120</v>
@@ -27134,10 +27134,10 @@
         <v>19</v>
       </c>
       <c r="E877" t="s">
+        <v>2118</v>
+      </c>
+      <c r="F877" t="s">
         <v>2123</v>
-      </c>
-      <c r="F877" t="s">
-        <v>2119</v>
       </c>
       <c r="G877" t="s">
         <v>2120</v>
@@ -27157,10 +27157,10 @@
         <v>1987</v>
       </c>
       <c r="E878" t="s">
+        <v>2118</v>
+      </c>
+      <c r="F878" t="s">
         <v>2123</v>
-      </c>
-      <c r="F878" t="s">
-        <v>2119</v>
       </c>
       <c r="G878" t="s">
         <v>2120</v>
@@ -27180,10 +27180,10 @@
         <v>1987</v>
       </c>
       <c r="E879" t="s">
+        <v>2118</v>
+      </c>
+      <c r="F879" t="s">
         <v>2123</v>
-      </c>
-      <c r="F879" t="s">
-        <v>2119</v>
       </c>
       <c r="G879" t="s">
         <v>2120</v>
@@ -27203,10 +27203,10 @@
         <v>1987</v>
       </c>
       <c r="E880" t="s">
+        <v>2118</v>
+      </c>
+      <c r="F880" t="s">
         <v>2123</v>
-      </c>
-      <c r="F880" t="s">
-        <v>2119</v>
       </c>
       <c r="G880" t="s">
         <v>2120</v>
@@ -27226,10 +27226,10 @@
         <v>1987</v>
       </c>
       <c r="E881" t="s">
+        <v>2118</v>
+      </c>
+      <c r="F881" t="s">
         <v>2123</v>
-      </c>
-      <c r="F881" t="s">
-        <v>2119</v>
       </c>
       <c r="G881" t="s">
         <v>2120</v>
@@ -27249,10 +27249,10 @@
         <v>1987</v>
       </c>
       <c r="E882" t="s">
+        <v>2118</v>
+      </c>
+      <c r="F882" t="s">
         <v>2123</v>
-      </c>
-      <c r="F882" t="s">
-        <v>2119</v>
       </c>
       <c r="G882" t="s">
         <v>2120</v>
@@ -27272,10 +27272,10 @@
         <v>1232</v>
       </c>
       <c r="E883" t="s">
+        <v>2118</v>
+      </c>
+      <c r="F883" t="s">
         <v>2123</v>
-      </c>
-      <c r="F883" t="s">
-        <v>2119</v>
       </c>
       <c r="G883" t="s">
         <v>2120</v>
@@ -27295,10 +27295,10 @@
         <v>1987</v>
       </c>
       <c r="E884" t="s">
+        <v>2118</v>
+      </c>
+      <c r="F884" t="s">
         <v>2123</v>
-      </c>
-      <c r="F884" t="s">
-        <v>2119</v>
       </c>
       <c r="G884" t="s">
         <v>2120</v>
@@ -27318,10 +27318,10 @@
         <v>1987</v>
       </c>
       <c r="E885" t="s">
+        <v>2118</v>
+      </c>
+      <c r="F885" t="s">
         <v>2123</v>
-      </c>
-      <c r="F885" t="s">
-        <v>2119</v>
       </c>
       <c r="G885" t="s">
         <v>2120</v>
@@ -27341,10 +27341,10 @@
         <v>1987</v>
       </c>
       <c r="E886" t="s">
+        <v>2118</v>
+      </c>
+      <c r="F886" t="s">
         <v>2123</v>
-      </c>
-      <c r="F886" t="s">
-        <v>2119</v>
       </c>
       <c r="G886" t="s">
         <v>2120</v>
@@ -27364,10 +27364,10 @@
         <v>19</v>
       </c>
       <c r="E887" t="s">
+        <v>2118</v>
+      </c>
+      <c r="F887" t="s">
         <v>2123</v>
-      </c>
-      <c r="F887" t="s">
-        <v>2119</v>
       </c>
       <c r="G887" t="s">
         <v>2120</v>
@@ -27387,10 +27387,10 @@
         <v>1987</v>
       </c>
       <c r="E888" t="s">
+        <v>2118</v>
+      </c>
+      <c r="F888" t="s">
         <v>2123</v>
-      </c>
-      <c r="F888" t="s">
-        <v>2119</v>
       </c>
       <c r="G888" t="s">
         <v>2120</v>
@@ -27410,10 +27410,10 @@
         <v>1232</v>
       </c>
       <c r="E889" t="s">
+        <v>2118</v>
+      </c>
+      <c r="F889" t="s">
         <v>2123</v>
-      </c>
-      <c r="F889" t="s">
-        <v>2119</v>
       </c>
       <c r="G889" t="s">
         <v>2120</v>
@@ -27548,10 +27548,10 @@
         <v>1987</v>
       </c>
       <c r="E895" t="s">
-        <v>2168</v>
+        <v>2181</v>
       </c>
       <c r="F895" t="s">
-        <v>2181</v>
+        <v>2169</v>
       </c>
       <c r="G895" t="s">
         <v>2170</v>
@@ -27571,10 +27571,10 @@
         <v>1232</v>
       </c>
       <c r="E896" t="s">
-        <v>2168</v>
+        <v>2181</v>
       </c>
       <c r="F896" t="s">
-        <v>2181</v>
+        <v>2169</v>
       </c>
       <c r="G896" t="s">
         <v>2170</v>
@@ -27778,10 +27778,10 @@
         <v>1987</v>
       </c>
       <c r="E905" t="s">
-        <v>2168</v>
+        <v>2201</v>
       </c>
       <c r="F905" t="s">
-        <v>2201</v>
+        <v>2169</v>
       </c>
       <c r="G905" t="s">
         <v>2202</v>
@@ -27801,10 +27801,10 @@
         <v>1987</v>
       </c>
       <c r="E906" t="s">
-        <v>2168</v>
+        <v>2205</v>
       </c>
       <c r="F906" t="s">
-        <v>2205</v>
+        <v>2169</v>
       </c>
       <c r="G906" t="s">
         <v>2202</v>
@@ -27824,10 +27824,10 @@
         <v>1987</v>
       </c>
       <c r="E907" t="s">
-        <v>2168</v>
+        <v>2201</v>
       </c>
       <c r="F907" t="s">
-        <v>2201</v>
+        <v>2169</v>
       </c>
       <c r="G907" t="s">
         <v>2202</v>

--- a/api/1/clv3/xlsx/en/HumanitarianPlan.xlsx
+++ b/api/1/clv3/xlsx/en/HumanitarianPlan.xlsx
@@ -31,12 +31,12 @@
     <t>codeforiati:plan-type</t>
   </si>
   <si>
+    <t>codeforiati:plan-end-date</t>
+  </si>
+  <si>
     <t>codeforiati:plan-year</t>
   </si>
   <si>
-    <t>codeforiati:plan-end-date</t>
-  </si>
-  <si>
     <t>HAFG25</t>
   </si>
   <si>
@@ -52,12 +52,12 @@
     <t>Humanitarian needs and response plan</t>
   </si>
   <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
     <t>2025</t>
   </si>
   <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
     <t>RIRNPAK25</t>
   </si>
   <si>
@@ -358,12 +358,12 @@
     <t>2024-01-01</t>
   </si>
   <si>
+    <t>2024-12-31</t>
+  </si>
+  <si>
     <t>2024</t>
   </si>
   <si>
-    <t>2024-12-31</t>
-  </si>
-  <si>
     <t>RAFG_RRP24</t>
   </si>
   <si>
@@ -715,12 +715,12 @@
     <t>2023-01-01</t>
   </si>
   <si>
+    <t>2023-12-31</t>
+  </si>
+  <si>
     <t>2023</t>
   </si>
   <si>
-    <t>2023-12-31</t>
-  </si>
-  <si>
     <t>RAFG23</t>
   </si>
   <si>
@@ -1033,12 +1033,12 @@
     <t>2022-01-01</t>
   </si>
   <si>
+    <t>2022-12-31</t>
+  </si>
+  <si>
     <t>2022</t>
   </si>
   <si>
-    <t>2022-12-31</t>
-  </si>
-  <si>
     <t>RAFG22</t>
   </si>
   <si>
@@ -1381,12 +1381,12 @@
     <t>2021-09-01</t>
   </si>
   <si>
+    <t>2021-12-31</t>
+  </si>
+  <si>
     <t>2021</t>
   </si>
   <si>
-    <t>2021-12-31</t>
-  </si>
-  <si>
     <t>HAFG21</t>
   </si>
   <si>
@@ -1738,12 +1738,12 @@
     <t>2020-01-01</t>
   </si>
   <si>
+    <t>2020-12-31</t>
+  </si>
+  <si>
     <t>2020</t>
   </si>
   <si>
-    <t>2020-12-31</t>
-  </si>
-  <si>
     <t>OBGD20</t>
   </si>
   <si>
@@ -2173,12 +2173,12 @@
     <t>2019-01-01</t>
   </si>
   <si>
+    <t>2019-12-31</t>
+  </si>
+  <si>
     <t>2019</t>
   </si>
   <si>
-    <t>2019-12-31</t>
-  </si>
-  <si>
     <t>RBGD19</t>
   </si>
   <si>
@@ -2410,12 +2410,12 @@
     <t>2018-01-01</t>
   </si>
   <si>
+    <t>2018-12-31</t>
+  </si>
+  <si>
     <t>2018</t>
   </si>
   <si>
-    <t>2018-12-31</t>
-  </si>
-  <si>
     <t>OBGD18</t>
   </si>
   <si>
@@ -2635,12 +2635,12 @@
     <t>2017-01-01</t>
   </si>
   <si>
+    <t>2017-12-31</t>
+  </si>
+  <si>
     <t>2017</t>
   </si>
   <si>
-    <t>2017-12-31</t>
-  </si>
-  <si>
     <t>HAFG17</t>
   </si>
   <si>
@@ -2926,12 +2926,12 @@
     <t>2016-01-01</t>
   </si>
   <si>
+    <t>2016-12-31</t>
+  </si>
+  <si>
     <t>2016</t>
   </si>
   <si>
-    <t>2016-12-31</t>
-  </si>
-  <si>
     <t>HAFG16</t>
   </si>
   <si>
@@ -3211,12 +3211,12 @@
     <t>Strategic response plan</t>
   </si>
   <si>
+    <t>2015-12-31</t>
+  </si>
+  <si>
     <t>2015</t>
   </si>
   <si>
-    <t>2015-12-31</t>
-  </si>
-  <si>
     <t>HBFA15</t>
   </si>
   <si>
@@ -3442,12 +3442,12 @@
     <t>2014-01-01</t>
   </si>
   <si>
+    <t>2014-12-31</t>
+  </si>
+  <si>
     <t>2014</t>
   </si>
   <si>
-    <t>2014-12-31</t>
-  </si>
-  <si>
     <t>HBFA1314</t>
   </si>
   <si>
@@ -3733,12 +3733,12 @@
     <t>Consolidated appeals process</t>
   </si>
   <si>
+    <t>2013-12-31</t>
+  </si>
+  <si>
     <t>2013</t>
   </si>
   <si>
-    <t>2013-12-31</t>
-  </si>
-  <si>
     <t>CBFA13</t>
   </si>
   <si>
@@ -3895,12 +3895,12 @@
     <t>2012-01-01</t>
   </si>
   <si>
+    <t>2012-12-31</t>
+  </si>
+  <si>
     <t>2012</t>
   </si>
   <si>
-    <t>2012-12-31</t>
-  </si>
-  <si>
     <t>CAFG1112</t>
   </si>
   <si>
@@ -4276,12 +4276,12 @@
     <t>2010-01-01</t>
   </si>
   <si>
+    <t>2010-12-31</t>
+  </si>
+  <si>
     <t>2010</t>
   </si>
   <si>
-    <t>2010-12-31</t>
-  </si>
-  <si>
     <t>OBFA1011</t>
   </si>
   <si>
@@ -4498,12 +4498,12 @@
     <t>2009-01-01</t>
   </si>
   <si>
+    <t>2009-12-31</t>
+  </si>
+  <si>
     <t>2009</t>
   </si>
   <si>
-    <t>2009-12-31</t>
-  </si>
-  <si>
     <t>FBFA0910</t>
   </si>
   <si>
@@ -4720,12 +4720,12 @@
     <t>2008-02-01</t>
   </si>
   <si>
+    <t>2008-06-30</t>
+  </si>
+  <si>
     <t>2008</t>
   </si>
   <si>
-    <t>2008-06-30</t>
-  </si>
-  <si>
     <t>OAFG0809</t>
   </si>
   <si>
@@ -4993,12 +4993,12 @@
     <t>2007-02-22</t>
   </si>
   <si>
+    <t>2007-08-21</t>
+  </si>
+  <si>
     <t>2007</t>
   </si>
   <si>
-    <t>2007-08-21</t>
-  </si>
-  <si>
     <t>FBFA0708</t>
   </si>
   <si>
@@ -5305,12 +5305,12 @@
     <t>2006-07-01</t>
   </si>
   <si>
+    <t>2006-12-31</t>
+  </si>
+  <si>
     <t>2006</t>
   </si>
   <si>
-    <t>2006-12-31</t>
-  </si>
-  <si>
     <t>CBDI06</t>
   </si>
   <si>
@@ -5563,12 +5563,12 @@
     <t>2005-04-01</t>
   </si>
   <si>
+    <t>2005-06-30</t>
+  </si>
+  <si>
     <t>2005</t>
   </si>
   <si>
-    <t>2005-06-30</t>
-  </si>
-  <si>
     <t>FBEN05</t>
   </si>
   <si>
@@ -5779,12 +5779,12 @@
     <t>2004-09-01</t>
   </si>
   <si>
+    <t>2004-12-31</t>
+  </si>
+  <si>
     <t>2004</t>
   </si>
   <si>
-    <t>2004-12-31</t>
-  </si>
-  <si>
     <t>CAGO04</t>
   </si>
   <si>
@@ -6028,12 +6028,12 @@
     <t>2003-01-01</t>
   </si>
   <si>
+    <t>2003-12-31</t>
+  </si>
+  <si>
     <t>2003</t>
   </si>
   <si>
-    <t>2003-12-31</t>
-  </si>
-  <si>
     <t>CAGO03</t>
   </si>
   <si>
@@ -6265,12 +6265,12 @@
     <t>2001-10-01</t>
   </si>
   <si>
+    <t>2002-12-31</t>
+  </si>
+  <si>
     <t>2002</t>
   </si>
   <si>
-    <t>2002-12-31</t>
-  </si>
-  <si>
     <t>CAGO02</t>
   </si>
   <si>
@@ -6457,12 +6457,12 @@
     <t>2001-01-01</t>
   </si>
   <si>
+    <t>2001-09-30</t>
+  </si>
+  <si>
     <t>2001</t>
   </si>
   <si>
-    <t>2001-09-30</t>
-  </si>
-  <si>
     <t>CAGO01</t>
   </si>
   <si>
@@ -6610,10 +6610,10 @@
     <t>2000-01-01</t>
   </si>
   <si>
+    <t>2000-12-31</t>
+  </si>
+  <si>
     <t>2000</t>
-  </si>
-  <si>
-    <t>2000-12-31</t>
   </si>
   <si>
     <t>CBDI00</t>
@@ -7145,10 +7145,10 @@
         <v>19</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G4" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -7375,10 +7375,10 @@
         <v>34</v>
       </c>
       <c r="F14" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G14" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -7398,10 +7398,10 @@
         <v>34</v>
       </c>
       <c r="F15" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="G15" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -7444,10 +7444,10 @@
         <v>34</v>
       </c>
       <c r="F17" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="G17" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -7490,10 +7490,10 @@
         <v>34</v>
       </c>
       <c r="F19" t="s">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="G19" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -7605,10 +7605,10 @@
         <v>19</v>
       </c>
       <c r="F24" t="s">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="G24" t="s">
-        <v>67</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -8019,10 +8019,10 @@
         <v>19</v>
       </c>
       <c r="F42" t="s">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="G42" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -8065,10 +8065,10 @@
         <v>34</v>
       </c>
       <c r="F44" t="s">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="G44" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -8088,10 +8088,10 @@
         <v>34</v>
       </c>
       <c r="F45" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="G45" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -8502,10 +8502,10 @@
         <v>34</v>
       </c>
       <c r="F63" t="s">
-        <v>114</v>
+        <v>154</v>
       </c>
       <c r="G63" t="s">
-        <v>154</v>
+        <v>115</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -8525,10 +8525,10 @@
         <v>34</v>
       </c>
       <c r="F64" t="s">
-        <v>114</v>
+        <v>157</v>
       </c>
       <c r="G64" t="s">
-        <v>157</v>
+        <v>115</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -8594,10 +8594,10 @@
         <v>19</v>
       </c>
       <c r="F67" t="s">
-        <v>114</v>
+        <v>157</v>
       </c>
       <c r="G67" t="s">
-        <v>157</v>
+        <v>115</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -9721,10 +9721,10 @@
         <v>19</v>
       </c>
       <c r="F116" t="s">
-        <v>233</v>
+        <v>276</v>
       </c>
       <c r="G116" t="s">
-        <v>276</v>
+        <v>234</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -9744,10 +9744,10 @@
         <v>19</v>
       </c>
       <c r="F117" t="s">
-        <v>233</v>
+        <v>280</v>
       </c>
       <c r="G117" t="s">
-        <v>280</v>
+        <v>234</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -9859,10 +9859,10 @@
         <v>25</v>
       </c>
       <c r="F122" t="s">
-        <v>233</v>
+        <v>280</v>
       </c>
       <c r="G122" t="s">
-        <v>280</v>
+        <v>234</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -9882,10 +9882,10 @@
         <v>19</v>
       </c>
       <c r="F123" t="s">
-        <v>233</v>
+        <v>276</v>
       </c>
       <c r="G123" t="s">
-        <v>276</v>
+        <v>234</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -10089,10 +10089,10 @@
         <v>16</v>
       </c>
       <c r="F132" t="s">
-        <v>233</v>
+        <v>311</v>
       </c>
       <c r="G132" t="s">
-        <v>311</v>
+        <v>234</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -10135,10 +10135,10 @@
         <v>34</v>
       </c>
       <c r="F134" t="s">
-        <v>233</v>
+        <v>276</v>
       </c>
       <c r="G134" t="s">
-        <v>276</v>
+        <v>234</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -10181,10 +10181,10 @@
         <v>34</v>
       </c>
       <c r="F136" t="s">
-        <v>233</v>
+        <v>276</v>
       </c>
       <c r="G136" t="s">
-        <v>276</v>
+        <v>234</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -10526,10 +10526,10 @@
         <v>19</v>
       </c>
       <c r="F151" t="s">
-        <v>339</v>
+        <v>356</v>
       </c>
       <c r="G151" t="s">
-        <v>356</v>
+        <v>340</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -10641,10 +10641,10 @@
         <v>34</v>
       </c>
       <c r="F156" t="s">
-        <v>339</v>
+        <v>368</v>
       </c>
       <c r="G156" t="s">
-        <v>368</v>
+        <v>340</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -10756,10 +10756,10 @@
         <v>34</v>
       </c>
       <c r="F161" t="s">
-        <v>339</v>
+        <v>379</v>
       </c>
       <c r="G161" t="s">
-        <v>379</v>
+        <v>340</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -10848,10 +10848,10 @@
         <v>34</v>
       </c>
       <c r="F165" t="s">
-        <v>339</v>
+        <v>389</v>
       </c>
       <c r="G165" t="s">
-        <v>389</v>
+        <v>340</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -10894,10 +10894,10 @@
         <v>34</v>
       </c>
       <c r="F167" t="s">
-        <v>339</v>
+        <v>395</v>
       </c>
       <c r="G167" t="s">
-        <v>395</v>
+        <v>340</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -11055,10 +11055,10 @@
         <v>19</v>
       </c>
       <c r="F174" t="s">
-        <v>339</v>
+        <v>410</v>
       </c>
       <c r="G174" t="s">
-        <v>410</v>
+        <v>340</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -11078,10 +11078,10 @@
         <v>19</v>
       </c>
       <c r="F175" t="s">
-        <v>339</v>
+        <v>414</v>
       </c>
       <c r="G175" t="s">
-        <v>414</v>
+        <v>340</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -11423,10 +11423,10 @@
         <v>16</v>
       </c>
       <c r="F190" t="s">
-        <v>339</v>
+        <v>447</v>
       </c>
       <c r="G190" t="s">
-        <v>447</v>
+        <v>340</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -11791,10 +11791,10 @@
         <v>25</v>
       </c>
       <c r="F206" t="s">
-        <v>455</v>
+        <v>339</v>
       </c>
       <c r="G206" t="s">
-        <v>340</v>
+        <v>456</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -11814,10 +11814,10 @@
         <v>34</v>
       </c>
       <c r="F207" t="s">
-        <v>455</v>
+        <v>488</v>
       </c>
       <c r="G207" t="s">
-        <v>488</v>
+        <v>456</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -11883,10 +11883,10 @@
         <v>25</v>
       </c>
       <c r="F210" t="s">
-        <v>455</v>
+        <v>339</v>
       </c>
       <c r="G210" t="s">
-        <v>340</v>
+        <v>456</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -11906,10 +11906,10 @@
         <v>34</v>
       </c>
       <c r="F211" t="s">
-        <v>455</v>
+        <v>498</v>
       </c>
       <c r="G211" t="s">
-        <v>498</v>
+        <v>456</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -11952,10 +11952,10 @@
         <v>34</v>
       </c>
       <c r="F213" t="s">
-        <v>455</v>
+        <v>504</v>
       </c>
       <c r="G213" t="s">
-        <v>504</v>
+        <v>456</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -11998,10 +11998,10 @@
         <v>25</v>
       </c>
       <c r="F215" t="s">
-        <v>455</v>
+        <v>339</v>
       </c>
       <c r="G215" t="s">
-        <v>340</v>
+        <v>456</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -12067,10 +12067,10 @@
         <v>19</v>
       </c>
       <c r="F218" t="s">
-        <v>455</v>
+        <v>517</v>
       </c>
       <c r="G218" t="s">
-        <v>517</v>
+        <v>456</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -12113,10 +12113,10 @@
         <v>34</v>
       </c>
       <c r="F220" t="s">
-        <v>455</v>
+        <v>389</v>
       </c>
       <c r="G220" t="s">
-        <v>389</v>
+        <v>456</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -12895,10 +12895,10 @@
         <v>25</v>
       </c>
       <c r="F254" t="s">
-        <v>574</v>
+        <v>459</v>
       </c>
       <c r="G254" t="s">
-        <v>459</v>
+        <v>575</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -13079,10 +13079,10 @@
         <v>34</v>
       </c>
       <c r="F262" t="s">
-        <v>574</v>
+        <v>615</v>
       </c>
       <c r="G262" t="s">
-        <v>615</v>
+        <v>575</v>
       </c>
     </row>
     <row r="263" spans="1:7">
@@ -13424,10 +13424,10 @@
         <v>34</v>
       </c>
       <c r="F277" t="s">
-        <v>574</v>
+        <v>648</v>
       </c>
       <c r="G277" t="s">
-        <v>648</v>
+        <v>575</v>
       </c>
     </row>
     <row r="278" spans="1:7">
@@ -13470,10 +13470,10 @@
         <v>34</v>
       </c>
       <c r="F279" t="s">
-        <v>574</v>
+        <v>654</v>
       </c>
       <c r="G279" t="s">
-        <v>654</v>
+        <v>575</v>
       </c>
     </row>
     <row r="280" spans="1:7">
@@ -14114,10 +14114,10 @@
         <v>19</v>
       </c>
       <c r="F307" t="s">
-        <v>574</v>
+        <v>615</v>
       </c>
       <c r="G307" t="s">
-        <v>615</v>
+        <v>575</v>
       </c>
     </row>
     <row r="308" spans="1:7">
@@ -14528,10 +14528,10 @@
         <v>34</v>
       </c>
       <c r="F325" t="s">
-        <v>719</v>
+        <v>752</v>
       </c>
       <c r="G325" t="s">
-        <v>752</v>
+        <v>720</v>
       </c>
     </row>
     <row r="326" spans="1:7">
@@ -14666,10 +14666,10 @@
         <v>25</v>
       </c>
       <c r="F331" t="s">
-        <v>719</v>
+        <v>765</v>
       </c>
       <c r="G331" t="s">
-        <v>765</v>
+        <v>720</v>
       </c>
     </row>
     <row r="332" spans="1:7">
@@ -14942,10 +14942,10 @@
         <v>34</v>
       </c>
       <c r="F343" t="s">
-        <v>719</v>
+        <v>791</v>
       </c>
       <c r="G343" t="s">
-        <v>791</v>
+        <v>720</v>
       </c>
     </row>
     <row r="344" spans="1:7">
@@ -14965,10 +14965,10 @@
         <v>34</v>
       </c>
       <c r="F344" t="s">
-        <v>719</v>
+        <v>791</v>
       </c>
       <c r="G344" t="s">
-        <v>791</v>
+        <v>720</v>
       </c>
     </row>
     <row r="345" spans="1:7">
@@ -15586,10 +15586,10 @@
         <v>25</v>
       </c>
       <c r="F371" t="s">
-        <v>798</v>
+        <v>855</v>
       </c>
       <c r="G371" t="s">
-        <v>855</v>
+        <v>799</v>
       </c>
     </row>
     <row r="372" spans="1:7">
@@ -15609,10 +15609,10 @@
         <v>25</v>
       </c>
       <c r="F372" t="s">
-        <v>798</v>
+        <v>859</v>
       </c>
       <c r="G372" t="s">
-        <v>859</v>
+        <v>799</v>
       </c>
     </row>
     <row r="373" spans="1:7">
@@ -15655,10 +15655,10 @@
         <v>25</v>
       </c>
       <c r="F374" t="s">
-        <v>798</v>
+        <v>859</v>
       </c>
       <c r="G374" t="s">
-        <v>859</v>
+        <v>799</v>
       </c>
     </row>
     <row r="375" spans="1:7">
@@ -16000,10 +16000,10 @@
         <v>34</v>
       </c>
       <c r="F389" t="s">
-        <v>873</v>
+        <v>901</v>
       </c>
       <c r="G389" t="s">
-        <v>901</v>
+        <v>874</v>
       </c>
     </row>
     <row r="390" spans="1:7">
@@ -16138,10 +16138,10 @@
         <v>34</v>
       </c>
       <c r="F395" t="s">
-        <v>873</v>
+        <v>916</v>
       </c>
       <c r="G395" t="s">
-        <v>916</v>
+        <v>874</v>
       </c>
     </row>
     <row r="396" spans="1:7">
@@ -16184,10 +16184,10 @@
         <v>34</v>
       </c>
       <c r="F397" t="s">
-        <v>873</v>
+        <v>922</v>
       </c>
       <c r="G397" t="s">
-        <v>922</v>
+        <v>874</v>
       </c>
     </row>
     <row r="398" spans="1:7">
@@ -16253,10 +16253,10 @@
         <v>34</v>
       </c>
       <c r="F400" t="s">
-        <v>873</v>
+        <v>930</v>
       </c>
       <c r="G400" t="s">
-        <v>930</v>
+        <v>874</v>
       </c>
     </row>
     <row r="401" spans="1:7">
@@ -16391,10 +16391,10 @@
         <v>34</v>
       </c>
       <c r="F406" t="s">
-        <v>873</v>
+        <v>944</v>
       </c>
       <c r="G406" t="s">
-        <v>944</v>
+        <v>874</v>
       </c>
     </row>
     <row r="407" spans="1:7">
@@ -16943,10 +16943,10 @@
         <v>34</v>
       </c>
       <c r="F430" t="s">
-        <v>970</v>
+        <v>997</v>
       </c>
       <c r="G430" t="s">
-        <v>997</v>
+        <v>971</v>
       </c>
     </row>
     <row r="431" spans="1:7">
@@ -16966,10 +16966,10 @@
         <v>34</v>
       </c>
       <c r="F431" t="s">
-        <v>970</v>
+        <v>1001</v>
       </c>
       <c r="G431" t="s">
-        <v>1001</v>
+        <v>971</v>
       </c>
     </row>
     <row r="432" spans="1:7">
@@ -17219,10 +17219,10 @@
         <v>34</v>
       </c>
       <c r="F442" t="s">
-        <v>970</v>
+        <v>1028</v>
       </c>
       <c r="G442" t="s">
-        <v>1028</v>
+        <v>971</v>
       </c>
     </row>
     <row r="443" spans="1:7">
@@ -17587,10 +17587,10 @@
         <v>25</v>
       </c>
       <c r="F458" t="s">
-        <v>970</v>
+        <v>1060</v>
       </c>
       <c r="G458" t="s">
-        <v>1060</v>
+        <v>971</v>
       </c>
     </row>
     <row r="459" spans="1:7">
@@ -17817,10 +17817,10 @@
         <v>34</v>
       </c>
       <c r="F468" t="s">
-        <v>1065</v>
+        <v>1086</v>
       </c>
       <c r="G468" t="s">
-        <v>1086</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="469" spans="1:7">
@@ -17863,10 +17863,10 @@
         <v>34</v>
       </c>
       <c r="F470" t="s">
-        <v>1065</v>
+        <v>1086</v>
       </c>
       <c r="G470" t="s">
-        <v>1086</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="471" spans="1:7">
@@ -17886,10 +17886,10 @@
         <v>34</v>
       </c>
       <c r="F471" t="s">
-        <v>1065</v>
+        <v>1096</v>
       </c>
       <c r="G471" t="s">
-        <v>1096</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="472" spans="1:7">
@@ -17932,10 +17932,10 @@
         <v>34</v>
       </c>
       <c r="F473" t="s">
-        <v>1065</v>
+        <v>1102</v>
       </c>
       <c r="G473" t="s">
-        <v>1102</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="474" spans="1:7">
@@ -18024,10 +18024,10 @@
         <v>34</v>
       </c>
       <c r="F477" t="s">
-        <v>1065</v>
+        <v>1086</v>
       </c>
       <c r="G477" t="s">
-        <v>1086</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="478" spans="1:7">
@@ -18484,10 +18484,10 @@
         <v>25</v>
       </c>
       <c r="F497" t="s">
-        <v>1142</v>
+        <v>1155</v>
       </c>
       <c r="G497" t="s">
-        <v>1155</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="498" spans="1:7">
@@ -18530,10 +18530,10 @@
         <v>16</v>
       </c>
       <c r="F499" t="s">
-        <v>1142</v>
+        <v>1160</v>
       </c>
       <c r="G499" t="s">
-        <v>1160</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="500" spans="1:7">
@@ -18553,10 +18553,10 @@
         <v>19</v>
       </c>
       <c r="F500" t="s">
-        <v>1142</v>
+        <v>1160</v>
       </c>
       <c r="G500" t="s">
-        <v>1160</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="501" spans="1:7">
@@ -18829,10 +18829,10 @@
         <v>34</v>
       </c>
       <c r="F512" t="s">
-        <v>1142</v>
+        <v>1190</v>
       </c>
       <c r="G512" t="s">
-        <v>1190</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="513" spans="1:7">
@@ -18852,10 +18852,10 @@
         <v>1064</v>
       </c>
       <c r="F513" t="s">
-        <v>1142</v>
+        <v>1194</v>
       </c>
       <c r="G513" t="s">
-        <v>1194</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="514" spans="1:7">
@@ -18875,10 +18875,10 @@
         <v>25</v>
       </c>
       <c r="F514" t="s">
-        <v>1142</v>
+        <v>1197</v>
       </c>
       <c r="G514" t="s">
-        <v>1197</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="515" spans="1:7">
@@ -18898,10 +18898,10 @@
         <v>34</v>
       </c>
       <c r="F515" t="s">
-        <v>1142</v>
+        <v>1201</v>
       </c>
       <c r="G515" t="s">
-        <v>1201</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="516" spans="1:7">
@@ -18990,10 +18990,10 @@
         <v>25</v>
       </c>
       <c r="F519" t="s">
-        <v>1142</v>
+        <v>1211</v>
       </c>
       <c r="G519" t="s">
-        <v>1211</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="520" spans="1:7">
@@ -19381,10 +19381,10 @@
         <v>1238</v>
       </c>
       <c r="F536" t="s">
-        <v>1239</v>
+        <v>1252</v>
       </c>
       <c r="G536" t="s">
-        <v>1252</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="537" spans="1:7">
@@ -19611,10 +19611,10 @@
         <v>1238</v>
       </c>
       <c r="F546" t="s">
-        <v>1239</v>
+        <v>1201</v>
       </c>
       <c r="G546" t="s">
-        <v>1201</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="547" spans="1:7">
@@ -19726,10 +19726,10 @@
         <v>16</v>
       </c>
       <c r="F551" t="s">
-        <v>1239</v>
+        <v>1285</v>
       </c>
       <c r="G551" t="s">
-        <v>1285</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="552" spans="1:7">
@@ -19933,10 +19933,10 @@
         <v>1238</v>
       </c>
       <c r="F560" t="s">
-        <v>1293</v>
+        <v>1309</v>
       </c>
       <c r="G560" t="s">
-        <v>1309</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="561" spans="1:7">
@@ -20025,10 +20025,10 @@
         <v>34</v>
       </c>
       <c r="F564" t="s">
-        <v>1293</v>
+        <v>1319</v>
       </c>
       <c r="G564" t="s">
-        <v>1319</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="565" spans="1:7">
@@ -20140,10 +20140,10 @@
         <v>19</v>
       </c>
       <c r="F569" t="s">
-        <v>1293</v>
+        <v>1331</v>
       </c>
       <c r="G569" t="s">
-        <v>1331</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="570" spans="1:7">
@@ -20278,10 +20278,10 @@
         <v>1238</v>
       </c>
       <c r="F575" t="s">
-        <v>1293</v>
+        <v>1345</v>
       </c>
       <c r="G575" t="s">
-        <v>1345</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="576" spans="1:7">
@@ -20370,10 +20370,10 @@
         <v>1238</v>
       </c>
       <c r="F579" t="s">
+        <v>1239</v>
+      </c>
+      <c r="G579" t="s">
         <v>1355</v>
-      </c>
-      <c r="G579" t="s">
-        <v>1240</v>
       </c>
     </row>
     <row r="580" spans="1:7">
@@ -20393,10 +20393,10 @@
         <v>1238</v>
       </c>
       <c r="F580" t="s">
+        <v>1358</v>
+      </c>
+      <c r="G580" t="s">
         <v>1355</v>
-      </c>
-      <c r="G580" t="s">
-        <v>1358</v>
       </c>
     </row>
     <row r="581" spans="1:7">
@@ -20416,10 +20416,10 @@
         <v>1238</v>
       </c>
       <c r="F581" t="s">
+        <v>1358</v>
+      </c>
+      <c r="G581" t="s">
         <v>1355</v>
-      </c>
-      <c r="G581" t="s">
-        <v>1358</v>
       </c>
     </row>
     <row r="582" spans="1:7">
@@ -20439,10 +20439,10 @@
         <v>1238</v>
       </c>
       <c r="F582" t="s">
+        <v>1358</v>
+      </c>
+      <c r="G582" t="s">
         <v>1355</v>
-      </c>
-      <c r="G582" t="s">
-        <v>1358</v>
       </c>
     </row>
     <row r="583" spans="1:7">
@@ -20462,10 +20462,10 @@
         <v>1238</v>
       </c>
       <c r="F583" t="s">
+        <v>1293</v>
+      </c>
+      <c r="G583" t="s">
         <v>1355</v>
-      </c>
-      <c r="G583" t="s">
-        <v>1294</v>
       </c>
     </row>
     <row r="584" spans="1:7">
@@ -20485,10 +20485,10 @@
         <v>1238</v>
       </c>
       <c r="F584" t="s">
+        <v>1358</v>
+      </c>
+      <c r="G584" t="s">
         <v>1355</v>
-      </c>
-      <c r="G584" t="s">
-        <v>1358</v>
       </c>
     </row>
     <row r="585" spans="1:7">
@@ -20508,10 +20508,10 @@
         <v>34</v>
       </c>
       <c r="F585" t="s">
+        <v>1371</v>
+      </c>
+      <c r="G585" t="s">
         <v>1355</v>
-      </c>
-      <c r="G585" t="s">
-        <v>1371</v>
       </c>
     </row>
     <row r="586" spans="1:7">
@@ -20531,10 +20531,10 @@
         <v>1238</v>
       </c>
       <c r="F586" t="s">
+        <v>1358</v>
+      </c>
+      <c r="G586" t="s">
         <v>1355</v>
-      </c>
-      <c r="G586" t="s">
-        <v>1358</v>
       </c>
     </row>
     <row r="587" spans="1:7">
@@ -20554,10 +20554,10 @@
         <v>19</v>
       </c>
       <c r="F587" t="s">
+        <v>1358</v>
+      </c>
+      <c r="G587" t="s">
         <v>1355</v>
-      </c>
-      <c r="G587" t="s">
-        <v>1358</v>
       </c>
     </row>
     <row r="588" spans="1:7">
@@ -20577,10 +20577,10 @@
         <v>19</v>
       </c>
       <c r="F588" t="s">
+        <v>1358</v>
+      </c>
+      <c r="G588" t="s">
         <v>1355</v>
-      </c>
-      <c r="G588" t="s">
-        <v>1358</v>
       </c>
     </row>
     <row r="589" spans="1:7">
@@ -20600,10 +20600,10 @@
         <v>34</v>
       </c>
       <c r="F589" t="s">
+        <v>1383</v>
+      </c>
+      <c r="G589" t="s">
         <v>1355</v>
-      </c>
-      <c r="G589" t="s">
-        <v>1383</v>
       </c>
     </row>
     <row r="590" spans="1:7">
@@ -20623,10 +20623,10 @@
         <v>34</v>
       </c>
       <c r="F590" t="s">
+        <v>1387</v>
+      </c>
+      <c r="G590" t="s">
         <v>1355</v>
-      </c>
-      <c r="G590" t="s">
-        <v>1387</v>
       </c>
     </row>
     <row r="591" spans="1:7">
@@ -20646,10 +20646,10 @@
         <v>1238</v>
       </c>
       <c r="F591" t="s">
+        <v>1358</v>
+      </c>
+      <c r="G591" t="s">
         <v>1355</v>
-      </c>
-      <c r="G591" t="s">
-        <v>1358</v>
       </c>
     </row>
     <row r="592" spans="1:7">
@@ -20669,10 +20669,10 @@
         <v>34</v>
       </c>
       <c r="F592" t="s">
+        <v>1393</v>
+      </c>
+      <c r="G592" t="s">
         <v>1355</v>
-      </c>
-      <c r="G592" t="s">
-        <v>1393</v>
       </c>
     </row>
     <row r="593" spans="1:7">
@@ -20692,10 +20692,10 @@
         <v>16</v>
       </c>
       <c r="F593" t="s">
+        <v>1358</v>
+      </c>
+      <c r="G593" t="s">
         <v>1355</v>
-      </c>
-      <c r="G593" t="s">
-        <v>1358</v>
       </c>
     </row>
     <row r="594" spans="1:7">
@@ -20715,10 +20715,10 @@
         <v>1238</v>
       </c>
       <c r="F594" t="s">
+        <v>1358</v>
+      </c>
+      <c r="G594" t="s">
         <v>1355</v>
-      </c>
-      <c r="G594" t="s">
-        <v>1358</v>
       </c>
     </row>
     <row r="595" spans="1:7">
@@ -20738,10 +20738,10 @@
         <v>1238</v>
       </c>
       <c r="F595" t="s">
+        <v>1358</v>
+      </c>
+      <c r="G595" t="s">
         <v>1355</v>
-      </c>
-      <c r="G595" t="s">
-        <v>1358</v>
       </c>
     </row>
     <row r="596" spans="1:7">
@@ -20761,10 +20761,10 @@
         <v>34</v>
       </c>
       <c r="F596" t="s">
+        <v>1358</v>
+      </c>
+      <c r="G596" t="s">
         <v>1355</v>
-      </c>
-      <c r="G596" t="s">
-        <v>1358</v>
       </c>
     </row>
     <row r="597" spans="1:7">
@@ -20784,10 +20784,10 @@
         <v>19</v>
       </c>
       <c r="F597" t="s">
+        <v>1358</v>
+      </c>
+      <c r="G597" t="s">
         <v>1355</v>
-      </c>
-      <c r="G597" t="s">
-        <v>1358</v>
       </c>
     </row>
     <row r="598" spans="1:7">
@@ -20807,10 +20807,10 @@
         <v>1238</v>
       </c>
       <c r="F598" t="s">
+        <v>1408</v>
+      </c>
+      <c r="G598" t="s">
         <v>1355</v>
-      </c>
-      <c r="G598" t="s">
-        <v>1408</v>
       </c>
     </row>
     <row r="599" spans="1:7">
@@ -20830,10 +20830,10 @@
         <v>16</v>
       </c>
       <c r="F599" t="s">
+        <v>1358</v>
+      </c>
+      <c r="G599" t="s">
         <v>1355</v>
-      </c>
-      <c r="G599" t="s">
-        <v>1358</v>
       </c>
     </row>
     <row r="600" spans="1:7">
@@ -20853,10 +20853,10 @@
         <v>1238</v>
       </c>
       <c r="F600" t="s">
+        <v>1358</v>
+      </c>
+      <c r="G600" t="s">
         <v>1355</v>
-      </c>
-      <c r="G600" t="s">
-        <v>1358</v>
       </c>
     </row>
     <row r="601" spans="1:7">
@@ -20876,10 +20876,10 @@
         <v>1238</v>
       </c>
       <c r="F601" t="s">
+        <v>1358</v>
+      </c>
+      <c r="G601" t="s">
         <v>1355</v>
-      </c>
-      <c r="G601" t="s">
-        <v>1358</v>
       </c>
     </row>
     <row r="602" spans="1:7">
@@ -20899,10 +20899,10 @@
         <v>1238</v>
       </c>
       <c r="F602" t="s">
+        <v>1358</v>
+      </c>
+      <c r="G602" t="s">
         <v>1355</v>
-      </c>
-      <c r="G602" t="s">
-        <v>1358</v>
       </c>
     </row>
     <row r="603" spans="1:7">
@@ -20945,10 +20945,10 @@
         <v>19</v>
       </c>
       <c r="F604" t="s">
-        <v>1420</v>
+        <v>1425</v>
       </c>
       <c r="G604" t="s">
-        <v>1425</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="605" spans="1:7">
@@ -21037,10 +21037,10 @@
         <v>34</v>
       </c>
       <c r="F608" t="s">
-        <v>1420</v>
+        <v>1435</v>
       </c>
       <c r="G608" t="s">
-        <v>1435</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="609" spans="1:7">
@@ -21060,10 +21060,10 @@
         <v>34</v>
       </c>
       <c r="F609" t="s">
-        <v>1420</v>
+        <v>1439</v>
       </c>
       <c r="G609" t="s">
-        <v>1439</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="610" spans="1:7">
@@ -21083,10 +21083,10 @@
         <v>1238</v>
       </c>
       <c r="F610" t="s">
-        <v>1420</v>
+        <v>1443</v>
       </c>
       <c r="G610" t="s">
-        <v>1443</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="611" spans="1:7">
@@ -21198,10 +21198,10 @@
         <v>34</v>
       </c>
       <c r="F615" t="s">
-        <v>1420</v>
+        <v>1455</v>
       </c>
       <c r="G615" t="s">
-        <v>1455</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="616" spans="1:7">
@@ -21221,10 +21221,10 @@
         <v>1238</v>
       </c>
       <c r="F616" t="s">
-        <v>1420</v>
+        <v>1396</v>
       </c>
       <c r="G616" t="s">
-        <v>1396</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="617" spans="1:7">
@@ -21267,10 +21267,10 @@
         <v>34</v>
       </c>
       <c r="F618" t="s">
-        <v>1420</v>
+        <v>1463</v>
       </c>
       <c r="G618" t="s">
-        <v>1463</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="619" spans="1:7">
@@ -21635,10 +21635,10 @@
         <v>34</v>
       </c>
       <c r="F634" t="s">
-        <v>1494</v>
+        <v>1499</v>
       </c>
       <c r="G634" t="s">
-        <v>1499</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="635" spans="1:7">
@@ -21727,10 +21727,10 @@
         <v>1238</v>
       </c>
       <c r="F638" t="s">
-        <v>1494</v>
+        <v>1508</v>
       </c>
       <c r="G638" t="s">
-        <v>1508</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="639" spans="1:7">
@@ -21842,10 +21842,10 @@
         <v>34</v>
       </c>
       <c r="F643" t="s">
-        <v>1494</v>
+        <v>1519</v>
       </c>
       <c r="G643" t="s">
-        <v>1519</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="644" spans="1:7">
@@ -21865,10 +21865,10 @@
         <v>34</v>
       </c>
       <c r="F644" t="s">
-        <v>1494</v>
+        <v>1523</v>
       </c>
       <c r="G644" t="s">
-        <v>1523</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="645" spans="1:7">
@@ -21888,10 +21888,10 @@
         <v>34</v>
       </c>
       <c r="F645" t="s">
-        <v>1494</v>
+        <v>1527</v>
       </c>
       <c r="G645" t="s">
-        <v>1527</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="646" spans="1:7">
@@ -21957,10 +21957,10 @@
         <v>34</v>
       </c>
       <c r="F648" t="s">
-        <v>1494</v>
+        <v>1536</v>
       </c>
       <c r="G648" t="s">
-        <v>1536</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="649" spans="1:7">
@@ -22049,10 +22049,10 @@
         <v>19</v>
       </c>
       <c r="F652" t="s">
-        <v>1494</v>
+        <v>1546</v>
       </c>
       <c r="G652" t="s">
-        <v>1546</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="653" spans="1:7">
@@ -22279,10 +22279,10 @@
         <v>19</v>
       </c>
       <c r="F662" t="s">
-        <v>1568</v>
+        <v>1573</v>
       </c>
       <c r="G662" t="s">
-        <v>1573</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="663" spans="1:7">
@@ -22302,10 +22302,10 @@
         <v>34</v>
       </c>
       <c r="F663" t="s">
-        <v>1568</v>
+        <v>1576</v>
       </c>
       <c r="G663" t="s">
-        <v>1576</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="664" spans="1:7">
@@ -22325,10 +22325,10 @@
         <v>1238</v>
       </c>
       <c r="F664" t="s">
-        <v>1568</v>
+        <v>1580</v>
       </c>
       <c r="G664" t="s">
-        <v>1580</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="665" spans="1:7">
@@ -22348,10 +22348,10 @@
         <v>1238</v>
       </c>
       <c r="F665" t="s">
-        <v>1568</v>
+        <v>1580</v>
       </c>
       <c r="G665" t="s">
-        <v>1580</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="666" spans="1:7">
@@ -22371,10 +22371,10 @@
         <v>19</v>
       </c>
       <c r="F666" t="s">
-        <v>1568</v>
+        <v>1494</v>
       </c>
       <c r="G666" t="s">
-        <v>1495</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="667" spans="1:7">
@@ -22394,10 +22394,10 @@
         <v>1238</v>
       </c>
       <c r="F667" t="s">
-        <v>1568</v>
+        <v>1580</v>
       </c>
       <c r="G667" t="s">
-        <v>1580</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="668" spans="1:7">
@@ -22417,10 +22417,10 @@
         <v>1238</v>
       </c>
       <c r="F668" t="s">
-        <v>1568</v>
+        <v>1580</v>
       </c>
       <c r="G668" t="s">
-        <v>1580</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="669" spans="1:7">
@@ -22440,10 +22440,10 @@
         <v>19</v>
       </c>
       <c r="F669" t="s">
-        <v>1568</v>
+        <v>1592</v>
       </c>
       <c r="G669" t="s">
-        <v>1592</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="670" spans="1:7">
@@ -22463,10 +22463,10 @@
         <v>34</v>
       </c>
       <c r="F670" t="s">
-        <v>1568</v>
+        <v>1596</v>
       </c>
       <c r="G670" t="s">
-        <v>1596</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="671" spans="1:7">
@@ -22486,10 +22486,10 @@
         <v>34</v>
       </c>
       <c r="F671" t="s">
-        <v>1568</v>
+        <v>1599</v>
       </c>
       <c r="G671" t="s">
-        <v>1599</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="672" spans="1:7">
@@ -22509,10 +22509,10 @@
         <v>34</v>
       </c>
       <c r="F672" t="s">
-        <v>1568</v>
+        <v>1603</v>
       </c>
       <c r="G672" t="s">
-        <v>1603</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="673" spans="1:7">
@@ -22532,10 +22532,10 @@
         <v>1238</v>
       </c>
       <c r="F673" t="s">
-        <v>1568</v>
+        <v>1580</v>
       </c>
       <c r="G673" t="s">
-        <v>1580</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="674" spans="1:7">
@@ -22555,10 +22555,10 @@
         <v>34</v>
       </c>
       <c r="F674" t="s">
-        <v>1568</v>
+        <v>1572</v>
       </c>
       <c r="G674" t="s">
-        <v>1572</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="675" spans="1:7">
@@ -22578,10 +22578,10 @@
         <v>34</v>
       </c>
       <c r="F675" t="s">
-        <v>1568</v>
+        <v>1611</v>
       </c>
       <c r="G675" t="s">
-        <v>1611</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="676" spans="1:7">
@@ -22601,10 +22601,10 @@
         <v>19</v>
       </c>
       <c r="F676" t="s">
-        <v>1568</v>
+        <v>1614</v>
       </c>
       <c r="G676" t="s">
-        <v>1614</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="677" spans="1:7">
@@ -22624,10 +22624,10 @@
         <v>19</v>
       </c>
       <c r="F677" t="s">
-        <v>1568</v>
+        <v>1580</v>
       </c>
       <c r="G677" t="s">
-        <v>1580</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="678" spans="1:7">
@@ -22647,10 +22647,10 @@
         <v>1238</v>
       </c>
       <c r="F678" t="s">
-        <v>1568</v>
+        <v>1580</v>
       </c>
       <c r="G678" t="s">
-        <v>1580</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="679" spans="1:7">
@@ -22693,10 +22693,10 @@
         <v>34</v>
       </c>
       <c r="F680" t="s">
-        <v>1568</v>
+        <v>1624</v>
       </c>
       <c r="G680" t="s">
-        <v>1624</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="681" spans="1:7">
@@ -22716,10 +22716,10 @@
         <v>19</v>
       </c>
       <c r="F681" t="s">
-        <v>1568</v>
+        <v>1580</v>
       </c>
       <c r="G681" t="s">
-        <v>1580</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="682" spans="1:7">
@@ -22739,10 +22739,10 @@
         <v>19</v>
       </c>
       <c r="F682" t="s">
-        <v>1568</v>
+        <v>1599</v>
       </c>
       <c r="G682" t="s">
-        <v>1599</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="683" spans="1:7">
@@ -22762,10 +22762,10 @@
         <v>1238</v>
       </c>
       <c r="F683" t="s">
-        <v>1568</v>
+        <v>1580</v>
       </c>
       <c r="G683" t="s">
-        <v>1580</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="684" spans="1:7">
@@ -22785,10 +22785,10 @@
         <v>16</v>
       </c>
       <c r="F684" t="s">
-        <v>1568</v>
+        <v>1633</v>
       </c>
       <c r="G684" t="s">
-        <v>1633</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="685" spans="1:7">
@@ -22808,10 +22808,10 @@
         <v>19</v>
       </c>
       <c r="F685" t="s">
-        <v>1568</v>
+        <v>1580</v>
       </c>
       <c r="G685" t="s">
-        <v>1580</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="686" spans="1:7">
@@ -22831,10 +22831,10 @@
         <v>1238</v>
       </c>
       <c r="F686" t="s">
-        <v>1568</v>
+        <v>1580</v>
       </c>
       <c r="G686" t="s">
-        <v>1580</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="687" spans="1:7">
@@ -22854,10 +22854,10 @@
         <v>19</v>
       </c>
       <c r="F687" t="s">
-        <v>1568</v>
+        <v>1603</v>
       </c>
       <c r="G687" t="s">
-        <v>1603</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="688" spans="1:7">
@@ -22877,10 +22877,10 @@
         <v>34</v>
       </c>
       <c r="F688" t="s">
-        <v>1568</v>
+        <v>1576</v>
       </c>
       <c r="G688" t="s">
-        <v>1576</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="689" spans="1:7">
@@ -22900,10 +22900,10 @@
         <v>19</v>
       </c>
       <c r="F689" t="s">
-        <v>1568</v>
+        <v>1580</v>
       </c>
       <c r="G689" t="s">
-        <v>1580</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="690" spans="1:7">
@@ -22923,10 +22923,10 @@
         <v>1238</v>
       </c>
       <c r="F690" t="s">
-        <v>1568</v>
+        <v>1580</v>
       </c>
       <c r="G690" t="s">
-        <v>1580</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="691" spans="1:7">
@@ -22946,10 +22946,10 @@
         <v>16</v>
       </c>
       <c r="F691" t="s">
-        <v>1568</v>
+        <v>1580</v>
       </c>
       <c r="G691" t="s">
-        <v>1580</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="692" spans="1:7">
@@ -22969,10 +22969,10 @@
         <v>1238</v>
       </c>
       <c r="F692" t="s">
-        <v>1568</v>
+        <v>1580</v>
       </c>
       <c r="G692" t="s">
-        <v>1580</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="693" spans="1:7">
@@ -22992,10 +22992,10 @@
         <v>34</v>
       </c>
       <c r="F693" t="s">
-        <v>1568</v>
+        <v>1603</v>
       </c>
       <c r="G693" t="s">
-        <v>1603</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="694" spans="1:7">
@@ -23015,10 +23015,10 @@
         <v>1238</v>
       </c>
       <c r="F694" t="s">
-        <v>1568</v>
+        <v>1580</v>
       </c>
       <c r="G694" t="s">
-        <v>1580</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="695" spans="1:7">
@@ -23038,10 +23038,10 @@
         <v>1238</v>
       </c>
       <c r="F695" t="s">
-        <v>1568</v>
+        <v>1580</v>
       </c>
       <c r="G695" t="s">
-        <v>1580</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="696" spans="1:7">
@@ -23084,10 +23084,10 @@
         <v>34</v>
       </c>
       <c r="F697" t="s">
-        <v>1659</v>
+        <v>1664</v>
       </c>
       <c r="G697" t="s">
-        <v>1664</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="698" spans="1:7">
@@ -23107,10 +23107,10 @@
         <v>1238</v>
       </c>
       <c r="F698" t="s">
-        <v>1659</v>
+        <v>1668</v>
       </c>
       <c r="G698" t="s">
-        <v>1668</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="699" spans="1:7">
@@ -23130,10 +23130,10 @@
         <v>1238</v>
       </c>
       <c r="F699" t="s">
-        <v>1659</v>
+        <v>1668</v>
       </c>
       <c r="G699" t="s">
-        <v>1668</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="700" spans="1:7">
@@ -23153,10 +23153,10 @@
         <v>1238</v>
       </c>
       <c r="F700" t="s">
-        <v>1659</v>
+        <v>1668</v>
       </c>
       <c r="G700" t="s">
-        <v>1668</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="701" spans="1:7">
@@ -23176,10 +23176,10 @@
         <v>1238</v>
       </c>
       <c r="F701" t="s">
-        <v>1659</v>
+        <v>1668</v>
       </c>
       <c r="G701" t="s">
-        <v>1668</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="702" spans="1:7">
@@ -23199,10 +23199,10 @@
         <v>1238</v>
       </c>
       <c r="F702" t="s">
-        <v>1659</v>
+        <v>1668</v>
       </c>
       <c r="G702" t="s">
-        <v>1668</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="703" spans="1:7">
@@ -23222,10 +23222,10 @@
         <v>34</v>
       </c>
       <c r="F703" t="s">
-        <v>1659</v>
+        <v>1679</v>
       </c>
       <c r="G703" t="s">
-        <v>1679</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="704" spans="1:7">
@@ -23245,10 +23245,10 @@
         <v>34</v>
       </c>
       <c r="F704" t="s">
-        <v>1659</v>
+        <v>1683</v>
       </c>
       <c r="G704" t="s">
-        <v>1683</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="705" spans="1:7">
@@ -23268,10 +23268,10 @@
         <v>16</v>
       </c>
       <c r="F705" t="s">
-        <v>1659</v>
+        <v>1668</v>
       </c>
       <c r="G705" t="s">
-        <v>1668</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="706" spans="1:7">
@@ -23291,10 +23291,10 @@
         <v>16</v>
       </c>
       <c r="F706" t="s">
-        <v>1659</v>
+        <v>1580</v>
       </c>
       <c r="G706" t="s">
-        <v>1580</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="707" spans="1:7">
@@ -23314,10 +23314,10 @@
         <v>34</v>
       </c>
       <c r="F707" t="s">
-        <v>1659</v>
+        <v>1692</v>
       </c>
       <c r="G707" t="s">
-        <v>1692</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="708" spans="1:7">
@@ -23337,10 +23337,10 @@
         <v>19</v>
       </c>
       <c r="F708" t="s">
-        <v>1659</v>
+        <v>1696</v>
       </c>
       <c r="G708" t="s">
-        <v>1696</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="709" spans="1:7">
@@ -23360,10 +23360,10 @@
         <v>34</v>
       </c>
       <c r="F709" t="s">
-        <v>1659</v>
+        <v>1700</v>
       </c>
       <c r="G709" t="s">
-        <v>1700</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="710" spans="1:7">
@@ -23383,10 +23383,10 @@
         <v>1238</v>
       </c>
       <c r="F710" t="s">
-        <v>1659</v>
+        <v>1668</v>
       </c>
       <c r="G710" t="s">
-        <v>1668</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="711" spans="1:7">
@@ -23406,10 +23406,10 @@
         <v>34</v>
       </c>
       <c r="F711" t="s">
-        <v>1659</v>
+        <v>1706</v>
       </c>
       <c r="G711" t="s">
-        <v>1706</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="712" spans="1:7">
@@ -23429,10 +23429,10 @@
         <v>34</v>
       </c>
       <c r="F712" t="s">
-        <v>1659</v>
+        <v>1710</v>
       </c>
       <c r="G712" t="s">
-        <v>1710</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="713" spans="1:7">
@@ -23452,10 +23452,10 @@
         <v>19</v>
       </c>
       <c r="F713" t="s">
-        <v>1659</v>
+        <v>1668</v>
       </c>
       <c r="G713" t="s">
-        <v>1668</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="714" spans="1:7">
@@ -23475,10 +23475,10 @@
         <v>34</v>
       </c>
       <c r="F714" t="s">
-        <v>1659</v>
+        <v>1716</v>
       </c>
       <c r="G714" t="s">
-        <v>1716</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="715" spans="1:7">
@@ -23498,10 +23498,10 @@
         <v>19</v>
       </c>
       <c r="F715" t="s">
-        <v>1659</v>
+        <v>1668</v>
       </c>
       <c r="G715" t="s">
-        <v>1668</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="716" spans="1:7">
@@ -23521,10 +23521,10 @@
         <v>34</v>
       </c>
       <c r="F716" t="s">
-        <v>1659</v>
+        <v>1722</v>
       </c>
       <c r="G716" t="s">
-        <v>1722</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="717" spans="1:7">
@@ -23544,10 +23544,10 @@
         <v>34</v>
       </c>
       <c r="F717" t="s">
-        <v>1659</v>
+        <v>1716</v>
       </c>
       <c r="G717" t="s">
-        <v>1716</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="718" spans="1:7">
@@ -23567,10 +23567,10 @@
         <v>1238</v>
       </c>
       <c r="F718" t="s">
-        <v>1659</v>
+        <v>1668</v>
       </c>
       <c r="G718" t="s">
-        <v>1668</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="719" spans="1:7">
@@ -23590,10 +23590,10 @@
         <v>19</v>
       </c>
       <c r="F719" t="s">
-        <v>1659</v>
+        <v>1710</v>
       </c>
       <c r="G719" t="s">
-        <v>1710</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="720" spans="1:7">
@@ -23613,10 +23613,10 @@
         <v>1238</v>
       </c>
       <c r="F720" t="s">
-        <v>1659</v>
+        <v>1668</v>
       </c>
       <c r="G720" t="s">
-        <v>1668</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="721" spans="1:7">
@@ -23636,10 +23636,10 @@
         <v>1238</v>
       </c>
       <c r="F721" t="s">
-        <v>1659</v>
+        <v>1710</v>
       </c>
       <c r="G721" t="s">
-        <v>1710</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="722" spans="1:7">
@@ -23659,10 +23659,10 @@
         <v>19</v>
       </c>
       <c r="F722" t="s">
-        <v>1659</v>
+        <v>1710</v>
       </c>
       <c r="G722" t="s">
-        <v>1710</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="723" spans="1:7">
@@ -23682,10 +23682,10 @@
         <v>34</v>
       </c>
       <c r="F723" t="s">
-        <v>1659</v>
+        <v>1664</v>
       </c>
       <c r="G723" t="s">
-        <v>1664</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="724" spans="1:7">
@@ -23705,10 +23705,10 @@
         <v>1238</v>
       </c>
       <c r="F724" t="s">
-        <v>1659</v>
+        <v>1668</v>
       </c>
       <c r="G724" t="s">
-        <v>1668</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="725" spans="1:7">
@@ -23728,10 +23728,10 @@
         <v>34</v>
       </c>
       <c r="F725" t="s">
-        <v>1659</v>
+        <v>1744</v>
       </c>
       <c r="G725" t="s">
-        <v>1744</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="726" spans="1:7">
@@ -23751,10 +23751,10 @@
         <v>1238</v>
       </c>
       <c r="F726" t="s">
-        <v>1659</v>
+        <v>1710</v>
       </c>
       <c r="G726" t="s">
-        <v>1710</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="727" spans="1:7">
@@ -23774,10 +23774,10 @@
         <v>1238</v>
       </c>
       <c r="F727" t="s">
-        <v>1659</v>
+        <v>1668</v>
       </c>
       <c r="G727" t="s">
-        <v>1668</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="728" spans="1:7">
@@ -23797,10 +23797,10 @@
         <v>34</v>
       </c>
       <c r="F728" t="s">
-        <v>1659</v>
+        <v>1683</v>
       </c>
       <c r="G728" t="s">
-        <v>1683</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="729" spans="1:7">
@@ -23820,10 +23820,10 @@
         <v>16</v>
       </c>
       <c r="F729" t="s">
-        <v>1659</v>
+        <v>1668</v>
       </c>
       <c r="G729" t="s">
-        <v>1668</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="730" spans="1:7">
@@ -23843,10 +23843,10 @@
         <v>1238</v>
       </c>
       <c r="F730" t="s">
-        <v>1659</v>
+        <v>1668</v>
       </c>
       <c r="G730" t="s">
-        <v>1668</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="731" spans="1:7">
@@ -23866,10 +23866,10 @@
         <v>34</v>
       </c>
       <c r="F731" t="s">
-        <v>1659</v>
+        <v>1710</v>
       </c>
       <c r="G731" t="s">
-        <v>1710</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="732" spans="1:7">
@@ -23889,10 +23889,10 @@
         <v>1238</v>
       </c>
       <c r="F732" t="s">
-        <v>1659</v>
+        <v>1668</v>
       </c>
       <c r="G732" t="s">
-        <v>1668</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="733" spans="1:7">
@@ -23912,10 +23912,10 @@
         <v>1238</v>
       </c>
       <c r="F733" t="s">
-        <v>1659</v>
+        <v>1668</v>
       </c>
       <c r="G733" t="s">
-        <v>1668</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="734" spans="1:7">
@@ -24096,10 +24096,10 @@
         <v>19</v>
       </c>
       <c r="F741" t="s">
-        <v>1763</v>
+        <v>1781</v>
       </c>
       <c r="G741" t="s">
-        <v>1781</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="742" spans="1:7">
@@ -24119,10 +24119,10 @@
         <v>19</v>
       </c>
       <c r="F742" t="s">
-        <v>1763</v>
+        <v>1785</v>
       </c>
       <c r="G742" t="s">
-        <v>1785</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="743" spans="1:7">
@@ -24188,10 +24188,10 @@
         <v>34</v>
       </c>
       <c r="F745" t="s">
-        <v>1763</v>
+        <v>1793</v>
       </c>
       <c r="G745" t="s">
-        <v>1793</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="746" spans="1:7">
@@ -24234,10 +24234,10 @@
         <v>34</v>
       </c>
       <c r="F747" t="s">
-        <v>1763</v>
+        <v>1793</v>
       </c>
       <c r="G747" t="s">
-        <v>1793</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="748" spans="1:7">
@@ -24257,10 +24257,10 @@
         <v>34</v>
       </c>
       <c r="F748" t="s">
-        <v>1763</v>
+        <v>1801</v>
       </c>
       <c r="G748" t="s">
-        <v>1801</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="749" spans="1:7">
@@ -24303,10 +24303,10 @@
         <v>34</v>
       </c>
       <c r="F750" t="s">
-        <v>1763</v>
+        <v>1808</v>
       </c>
       <c r="G750" t="s">
-        <v>1808</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="751" spans="1:7">
@@ -24395,10 +24395,10 @@
         <v>19</v>
       </c>
       <c r="F754" t="s">
-        <v>1763</v>
+        <v>1668</v>
       </c>
       <c r="G754" t="s">
-        <v>1668</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="755" spans="1:7">
@@ -24464,10 +24464,10 @@
         <v>34</v>
       </c>
       <c r="F757" t="s">
-        <v>1763</v>
+        <v>1826</v>
       </c>
       <c r="G757" t="s">
-        <v>1826</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="758" spans="1:7">
@@ -24717,10 +24717,10 @@
         <v>34</v>
       </c>
       <c r="F768" t="s">
-        <v>1849</v>
+        <v>1854</v>
       </c>
       <c r="G768" t="s">
-        <v>1854</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="769" spans="1:7">
@@ -24740,10 +24740,10 @@
         <v>1238</v>
       </c>
       <c r="F769" t="s">
-        <v>1849</v>
+        <v>1858</v>
       </c>
       <c r="G769" t="s">
-        <v>1858</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="770" spans="1:7">
@@ -24763,10 +24763,10 @@
         <v>1238</v>
       </c>
       <c r="F770" t="s">
-        <v>1849</v>
+        <v>1858</v>
       </c>
       <c r="G770" t="s">
-        <v>1858</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="771" spans="1:7">
@@ -24786,10 +24786,10 @@
         <v>1238</v>
       </c>
       <c r="F771" t="s">
-        <v>1849</v>
+        <v>1858</v>
       </c>
       <c r="G771" t="s">
-        <v>1858</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="772" spans="1:7">
@@ -24809,10 +24809,10 @@
         <v>1238</v>
       </c>
       <c r="F772" t="s">
-        <v>1849</v>
+        <v>1858</v>
       </c>
       <c r="G772" t="s">
-        <v>1858</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="773" spans="1:7">
@@ -24832,10 +24832,10 @@
         <v>1238</v>
       </c>
       <c r="F773" t="s">
-        <v>1849</v>
+        <v>1858</v>
       </c>
       <c r="G773" t="s">
-        <v>1858</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="774" spans="1:7">
@@ -24855,10 +24855,10 @@
         <v>1238</v>
       </c>
       <c r="F774" t="s">
-        <v>1849</v>
+        <v>1858</v>
       </c>
       <c r="G774" t="s">
-        <v>1858</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="775" spans="1:7">
@@ -24878,10 +24878,10 @@
         <v>34</v>
       </c>
       <c r="F775" t="s">
-        <v>1849</v>
+        <v>1854</v>
       </c>
       <c r="G775" t="s">
-        <v>1854</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="776" spans="1:7">
@@ -24901,10 +24901,10 @@
         <v>19</v>
       </c>
       <c r="F776" t="s">
-        <v>1849</v>
+        <v>1858</v>
       </c>
       <c r="G776" t="s">
-        <v>1858</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="777" spans="1:7">
@@ -24924,10 +24924,10 @@
         <v>1238</v>
       </c>
       <c r="F777" t="s">
-        <v>1849</v>
+        <v>1858</v>
       </c>
       <c r="G777" t="s">
-        <v>1858</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="778" spans="1:7">
@@ -24970,10 +24970,10 @@
         <v>1238</v>
       </c>
       <c r="F779" t="s">
-        <v>1849</v>
+        <v>1858</v>
       </c>
       <c r="G779" t="s">
-        <v>1858</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="780" spans="1:7">
@@ -24993,10 +24993,10 @@
         <v>34</v>
       </c>
       <c r="F780" t="s">
-        <v>1849</v>
+        <v>1881</v>
       </c>
       <c r="G780" t="s">
-        <v>1881</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="781" spans="1:7">
@@ -25016,10 +25016,10 @@
         <v>1238</v>
       </c>
       <c r="F781" t="s">
-        <v>1849</v>
+        <v>1858</v>
       </c>
       <c r="G781" t="s">
-        <v>1858</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="782" spans="1:7">
@@ -25039,10 +25039,10 @@
         <v>34</v>
       </c>
       <c r="F782" t="s">
-        <v>1849</v>
+        <v>1887</v>
       </c>
       <c r="G782" t="s">
-        <v>1887</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="783" spans="1:7">
@@ -25085,10 +25085,10 @@
         <v>34</v>
       </c>
       <c r="F784" t="s">
-        <v>1849</v>
+        <v>1881</v>
       </c>
       <c r="G784" t="s">
-        <v>1881</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="785" spans="1:7">
@@ -25108,10 +25108,10 @@
         <v>34</v>
       </c>
       <c r="F785" t="s">
-        <v>1849</v>
+        <v>1895</v>
       </c>
       <c r="G785" t="s">
-        <v>1895</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="786" spans="1:7">
@@ -25131,10 +25131,10 @@
         <v>1238</v>
       </c>
       <c r="F786" t="s">
-        <v>1849</v>
+        <v>1858</v>
       </c>
       <c r="G786" t="s">
-        <v>1858</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="787" spans="1:7">
@@ -25154,10 +25154,10 @@
         <v>1238</v>
       </c>
       <c r="F787" t="s">
-        <v>1849</v>
+        <v>1858</v>
       </c>
       <c r="G787" t="s">
-        <v>1858</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="788" spans="1:7">
@@ -25177,10 +25177,10 @@
         <v>16</v>
       </c>
       <c r="F788" t="s">
-        <v>1849</v>
+        <v>1903</v>
       </c>
       <c r="G788" t="s">
-        <v>1903</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="789" spans="1:7">
@@ -25200,10 +25200,10 @@
         <v>19</v>
       </c>
       <c r="F789" t="s">
-        <v>1849</v>
+        <v>1858</v>
       </c>
       <c r="G789" t="s">
-        <v>1858</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="790" spans="1:7">
@@ -25223,10 +25223,10 @@
         <v>34</v>
       </c>
       <c r="F790" t="s">
-        <v>1849</v>
+        <v>1909</v>
       </c>
       <c r="G790" t="s">
-        <v>1909</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="791" spans="1:7">
@@ -25246,10 +25246,10 @@
         <v>1238</v>
       </c>
       <c r="F791" t="s">
-        <v>1849</v>
+        <v>1858</v>
       </c>
       <c r="G791" t="s">
-        <v>1858</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="792" spans="1:7">
@@ -25269,10 +25269,10 @@
         <v>1238</v>
       </c>
       <c r="F792" t="s">
-        <v>1849</v>
+        <v>1858</v>
       </c>
       <c r="G792" t="s">
-        <v>1858</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="793" spans="1:7">
@@ -25292,10 +25292,10 @@
         <v>16</v>
       </c>
       <c r="F793" t="s">
-        <v>1849</v>
+        <v>1858</v>
       </c>
       <c r="G793" t="s">
-        <v>1858</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="794" spans="1:7">
@@ -25315,10 +25315,10 @@
         <v>34</v>
       </c>
       <c r="F794" t="s">
-        <v>1849</v>
+        <v>1903</v>
       </c>
       <c r="G794" t="s">
-        <v>1903</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="795" spans="1:7">
@@ -25338,10 +25338,10 @@
         <v>1238</v>
       </c>
       <c r="F795" t="s">
-        <v>1849</v>
+        <v>1858</v>
       </c>
       <c r="G795" t="s">
-        <v>1858</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="796" spans="1:7">
@@ -25407,10 +25407,10 @@
         <v>34</v>
       </c>
       <c r="F798" t="s">
-        <v>1921</v>
+        <v>1929</v>
       </c>
       <c r="G798" t="s">
-        <v>1929</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="799" spans="1:7">
@@ -25430,10 +25430,10 @@
         <v>34</v>
       </c>
       <c r="F799" t="s">
-        <v>1921</v>
+        <v>1933</v>
       </c>
       <c r="G799" t="s">
-        <v>1933</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="800" spans="1:7">
@@ -25683,10 +25683,10 @@
         <v>34</v>
       </c>
       <c r="F810" t="s">
-        <v>1921</v>
+        <v>1957</v>
       </c>
       <c r="G810" t="s">
-        <v>1957</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="811" spans="1:7">
@@ -25729,10 +25729,10 @@
         <v>34</v>
       </c>
       <c r="F812" t="s">
-        <v>1921</v>
+        <v>1962</v>
       </c>
       <c r="G812" t="s">
-        <v>1962</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="813" spans="1:7">
@@ -25752,10 +25752,10 @@
         <v>34</v>
       </c>
       <c r="F813" t="s">
-        <v>1921</v>
+        <v>1957</v>
       </c>
       <c r="G813" t="s">
-        <v>1957</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="814" spans="1:7">
@@ -25798,10 +25798,10 @@
         <v>34</v>
       </c>
       <c r="F815" t="s">
-        <v>1921</v>
+        <v>1970</v>
       </c>
       <c r="G815" t="s">
-        <v>1970</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="816" spans="1:7">
@@ -25867,10 +25867,10 @@
         <v>34</v>
       </c>
       <c r="F818" t="s">
-        <v>1921</v>
+        <v>1979</v>
       </c>
       <c r="G818" t="s">
-        <v>1979</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="819" spans="1:7">
@@ -25890,10 +25890,10 @@
         <v>34</v>
       </c>
       <c r="F819" t="s">
-        <v>1921</v>
+        <v>1983</v>
       </c>
       <c r="G819" t="s">
-        <v>1983</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="820" spans="1:7">
@@ -26189,10 +26189,10 @@
         <v>34</v>
       </c>
       <c r="F832" t="s">
-        <v>2004</v>
+        <v>2014</v>
       </c>
       <c r="G832" t="s">
-        <v>2014</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="833" spans="1:7">
@@ -26281,10 +26281,10 @@
         <v>16</v>
       </c>
       <c r="F836" t="s">
-        <v>2004</v>
+        <v>2024</v>
       </c>
       <c r="G836" t="s">
-        <v>2024</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="837" spans="1:7">
@@ -26327,10 +26327,10 @@
         <v>34</v>
       </c>
       <c r="F838" t="s">
-        <v>2004</v>
+        <v>2024</v>
       </c>
       <c r="G838" t="s">
-        <v>2024</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="839" spans="1:7">
@@ -26488,10 +26488,10 @@
         <v>19</v>
       </c>
       <c r="F845" t="s">
-        <v>2004</v>
+        <v>2041</v>
       </c>
       <c r="G845" t="s">
-        <v>2041</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="846" spans="1:7">
@@ -26511,10 +26511,10 @@
         <v>2008</v>
       </c>
       <c r="F846" t="s">
-        <v>2004</v>
+        <v>2045</v>
       </c>
       <c r="G846" t="s">
-        <v>2045</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="847" spans="1:7">
@@ -26557,10 +26557,10 @@
         <v>2008</v>
       </c>
       <c r="F848" t="s">
-        <v>2004</v>
+        <v>2045</v>
       </c>
       <c r="G848" t="s">
-        <v>2045</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="849" spans="1:7">
@@ -26580,10 +26580,10 @@
         <v>16</v>
       </c>
       <c r="F849" t="s">
-        <v>2004</v>
+        <v>2045</v>
       </c>
       <c r="G849" t="s">
-        <v>2045</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="850" spans="1:7">
@@ -26603,10 +26603,10 @@
         <v>1238</v>
       </c>
       <c r="F850" t="s">
-        <v>2004</v>
+        <v>2045</v>
       </c>
       <c r="G850" t="s">
-        <v>2045</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="851" spans="1:7">
@@ -26626,10 +26626,10 @@
         <v>2008</v>
       </c>
       <c r="F851" t="s">
-        <v>2004</v>
+        <v>2045</v>
       </c>
       <c r="G851" t="s">
-        <v>2045</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="852" spans="1:7">
@@ -26649,10 +26649,10 @@
         <v>2008</v>
       </c>
       <c r="F852" t="s">
-        <v>2004</v>
+        <v>2045</v>
       </c>
       <c r="G852" t="s">
-        <v>2045</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="853" spans="1:7">
@@ -27155,10 +27155,10 @@
         <v>2008</v>
       </c>
       <c r="F874" t="s">
-        <v>2083</v>
+        <v>2014</v>
       </c>
       <c r="G874" t="s">
-        <v>2014</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="875" spans="1:7">
@@ -27178,10 +27178,10 @@
         <v>2008</v>
       </c>
       <c r="F875" t="s">
-        <v>2083</v>
+        <v>2014</v>
       </c>
       <c r="G875" t="s">
-        <v>2014</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="876" spans="1:7">
@@ -27201,10 +27201,10 @@
         <v>16</v>
       </c>
       <c r="F876" t="s">
-        <v>2083</v>
+        <v>2014</v>
       </c>
       <c r="G876" t="s">
-        <v>2014</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="877" spans="1:7">
@@ -27224,10 +27224,10 @@
         <v>1238</v>
       </c>
       <c r="F877" t="s">
-        <v>2083</v>
+        <v>2014</v>
       </c>
       <c r="G877" t="s">
-        <v>2014</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="878" spans="1:7">
@@ -27247,10 +27247,10 @@
         <v>2008</v>
       </c>
       <c r="F878" t="s">
-        <v>2083</v>
+        <v>2112</v>
       </c>
       <c r="G878" t="s">
-        <v>2112</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="879" spans="1:7">
@@ -27270,10 +27270,10 @@
         <v>2008</v>
       </c>
       <c r="F879" t="s">
-        <v>2083</v>
+        <v>2014</v>
       </c>
       <c r="G879" t="s">
-        <v>2014</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="880" spans="1:7">
@@ -27293,10 +27293,10 @@
         <v>2008</v>
       </c>
       <c r="F880" t="s">
-        <v>2083</v>
+        <v>2014</v>
       </c>
       <c r="G880" t="s">
-        <v>2014</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="881" spans="1:7">
@@ -27661,10 +27661,10 @@
         <v>2008</v>
       </c>
       <c r="F896" t="s">
-        <v>2147</v>
+        <v>2151</v>
       </c>
       <c r="G896" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="897" spans="1:7">
@@ -27684,10 +27684,10 @@
         <v>2008</v>
       </c>
       <c r="F897" t="s">
-        <v>2147</v>
+        <v>2151</v>
       </c>
       <c r="G897" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="898" spans="1:7">
@@ -27707,10 +27707,10 @@
         <v>2008</v>
       </c>
       <c r="F898" t="s">
-        <v>2147</v>
+        <v>2151</v>
       </c>
       <c r="G898" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="899" spans="1:7">
@@ -27730,10 +27730,10 @@
         <v>2008</v>
       </c>
       <c r="F899" t="s">
-        <v>2147</v>
+        <v>2151</v>
       </c>
       <c r="G899" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="900" spans="1:7">
@@ -27753,10 +27753,10 @@
         <v>19</v>
       </c>
       <c r="F900" t="s">
-        <v>2147</v>
+        <v>2151</v>
       </c>
       <c r="G900" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="901" spans="1:7">
@@ -27776,10 +27776,10 @@
         <v>16</v>
       </c>
       <c r="F901" t="s">
-        <v>2147</v>
+        <v>2151</v>
       </c>
       <c r="G901" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="902" spans="1:7">
@@ -27799,10 +27799,10 @@
         <v>19</v>
       </c>
       <c r="F902" t="s">
-        <v>2147</v>
+        <v>2151</v>
       </c>
       <c r="G902" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="903" spans="1:7">
@@ -27822,10 +27822,10 @@
         <v>2008</v>
       </c>
       <c r="F903" t="s">
-        <v>2147</v>
+        <v>2151</v>
       </c>
       <c r="G903" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="904" spans="1:7">
@@ -27845,10 +27845,10 @@
         <v>2008</v>
       </c>
       <c r="F904" t="s">
-        <v>2147</v>
+        <v>2151</v>
       </c>
       <c r="G904" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="905" spans="1:7">
@@ -27868,10 +27868,10 @@
         <v>1238</v>
       </c>
       <c r="F905" t="s">
-        <v>2147</v>
+        <v>2151</v>
       </c>
       <c r="G905" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="906" spans="1:7">
@@ -27891,10 +27891,10 @@
         <v>19</v>
       </c>
       <c r="F906" t="s">
-        <v>2147</v>
+        <v>2151</v>
       </c>
       <c r="G906" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="907" spans="1:7">
@@ -27914,10 +27914,10 @@
         <v>2008</v>
       </c>
       <c r="F907" t="s">
-        <v>2147</v>
+        <v>2151</v>
       </c>
       <c r="G907" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="908" spans="1:7">
@@ -27937,10 +27937,10 @@
         <v>2008</v>
       </c>
       <c r="F908" t="s">
-        <v>2147</v>
+        <v>2151</v>
       </c>
       <c r="G908" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="909" spans="1:7">
@@ -27960,10 +27960,10 @@
         <v>2008</v>
       </c>
       <c r="F909" t="s">
-        <v>2147</v>
+        <v>2151</v>
       </c>
       <c r="G909" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="910" spans="1:7">
@@ -27983,10 +27983,10 @@
         <v>2008</v>
       </c>
       <c r="F910" t="s">
-        <v>2147</v>
+        <v>2151</v>
       </c>
       <c r="G910" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="911" spans="1:7">
@@ -28006,10 +28006,10 @@
         <v>2008</v>
       </c>
       <c r="F911" t="s">
-        <v>2147</v>
+        <v>2151</v>
       </c>
       <c r="G911" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="912" spans="1:7">
@@ -28029,10 +28029,10 @@
         <v>1238</v>
       </c>
       <c r="F912" t="s">
-        <v>2147</v>
+        <v>2151</v>
       </c>
       <c r="G912" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="913" spans="1:7">
@@ -28052,10 +28052,10 @@
         <v>2008</v>
       </c>
       <c r="F913" t="s">
-        <v>2147</v>
+        <v>2151</v>
       </c>
       <c r="G913" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="914" spans="1:7">
@@ -28075,10 +28075,10 @@
         <v>2008</v>
       </c>
       <c r="F914" t="s">
-        <v>2147</v>
+        <v>2151</v>
       </c>
       <c r="G914" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="915" spans="1:7">
@@ -28098,10 +28098,10 @@
         <v>2008</v>
       </c>
       <c r="F915" t="s">
-        <v>2147</v>
+        <v>2151</v>
       </c>
       <c r="G915" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="916" spans="1:7">
@@ -28121,10 +28121,10 @@
         <v>19</v>
       </c>
       <c r="F916" t="s">
-        <v>2147</v>
+        <v>2151</v>
       </c>
       <c r="G916" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="917" spans="1:7">
@@ -28144,10 +28144,10 @@
         <v>2008</v>
       </c>
       <c r="F917" t="s">
-        <v>2147</v>
+        <v>2151</v>
       </c>
       <c r="G917" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="918" spans="1:7">
@@ -28167,10 +28167,10 @@
         <v>1238</v>
       </c>
       <c r="F918" t="s">
-        <v>2147</v>
+        <v>2151</v>
       </c>
       <c r="G918" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="919" spans="1:7">

--- a/api/1/clv3/xlsx/en/HumanitarianPlan.xlsx
+++ b/api/1/clv3/xlsx/en/HumanitarianPlan.xlsx
@@ -28,15 +28,15 @@
     <t>codeforiati:plan-type</t>
   </si>
   <si>
+    <t>codeforiati:plan-year</t>
+  </si>
+  <si>
+    <t>codeforiati:plan-start-date</t>
+  </si>
+  <si>
     <t>codeforiati:plan-end-date</t>
   </si>
   <si>
-    <t>codeforiati:plan-start-date</t>
-  </si>
-  <si>
-    <t>codeforiati:plan-year</t>
-  </si>
-  <si>
     <t>HAFG26</t>
   </si>
   <si>
@@ -49,15 +49,15 @@
     <t>Humanitarian needs and response plan</t>
   </si>
   <si>
+    <t>2026</t>
+  </si>
+  <si>
+    <t>2026-01-01</t>
+  </si>
+  <si>
     <t>2026-12-31</t>
   </si>
   <si>
-    <t>2026-01-01</t>
-  </si>
-  <si>
-    <t>2026</t>
-  </si>
-  <si>
     <t>HBFA26</t>
   </si>
   <si>
@@ -115,12 +115,12 @@
     <t>Regional response plan</t>
   </si>
   <si>
+    <t>2026-03-01</t>
+  </si>
+  <si>
     <t>2026-05-31</t>
   </si>
   <si>
-    <t>2026-03-01</t>
-  </si>
-  <si>
     <t>FLBN26</t>
   </si>
   <si>
@@ -241,7 +241,7 @@
     <t>HSYR26</t>
   </si>
   <si>
-    <t>Syrian Arab Republic Humanitarian Response Priorities 2026</t>
+    <t>Syrian Arab Republic Humanitarian Needs and Response Plan 2026</t>
   </si>
   <si>
     <t>RJORLBNTUR26</t>
@@ -301,15 +301,15 @@
     <t>Afghanistan Humanitarian Needs and Response Plan 2025</t>
   </si>
   <si>
+    <t>2025</t>
+  </si>
+  <si>
+    <t>2025-01-01</t>
+  </si>
+  <si>
     <t>2025-12-31</t>
   </si>
   <si>
-    <t>2025-01-01</t>
-  </si>
-  <si>
-    <t>2025</t>
-  </si>
-  <si>
     <t>RIRNPAK25</t>
   </si>
   <si>
@@ -628,15 +628,15 @@
     <t>Afghanistan Humanitarian Needs and Response Plan 2024</t>
   </si>
   <si>
+    <t>2024</t>
+  </si>
+  <si>
+    <t>2024-01-01</t>
+  </si>
+  <si>
     <t>2024-12-31</t>
   </si>
   <si>
-    <t>2024-01-01</t>
-  </si>
-  <si>
-    <t>2024</t>
-  </si>
-  <si>
     <t>RAFG_RRP24</t>
   </si>
   <si>
@@ -982,15 +982,15 @@
     <t>Afghanistan Humanitarian Response Plan 2023</t>
   </si>
   <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>2023-01-01</t>
+  </si>
+  <si>
     <t>2023-12-31</t>
   </si>
   <si>
-    <t>2023-01-01</t>
-  </si>
-  <si>
-    <t>2023</t>
-  </si>
-  <si>
     <t>RAFG23</t>
   </si>
   <si>
@@ -1111,24 +1111,24 @@
     <t>Mongolia Dzud Early Action and Response Plan 2023</t>
   </si>
   <si>
+    <t>2022-12-01</t>
+  </si>
+  <si>
     <t>2023-05-31</t>
   </si>
   <si>
-    <t>2022-12-01</t>
-  </si>
-  <si>
     <t>OMOZ23</t>
   </si>
   <si>
     <t>Mozambique Cyclone Freddy, Floods and Cholera Response Plan 2023</t>
   </si>
   <si>
+    <t>2023-03-01</t>
+  </si>
+  <si>
     <t>2023-09-30</t>
   </si>
   <si>
-    <t>2023-03-01</t>
-  </si>
-  <si>
     <t>HMOZ23</t>
   </si>
   <si>
@@ -1216,12 +1216,12 @@
     <t>Sudan Emergency: Regional Refugee Response Plan 2023</t>
   </si>
   <si>
+    <t>2023-05-01</t>
+  </si>
+  <si>
     <t>2023-10-31</t>
   </si>
   <si>
-    <t>2023-05-01</t>
-  </si>
-  <si>
     <t>HSDN23</t>
   </si>
   <si>
@@ -1300,15 +1300,15 @@
     <t>Afghanistan Humanitarian Response Plan 2022</t>
   </si>
   <si>
+    <t>2022</t>
+  </si>
+  <si>
+    <t>2022-01-01</t>
+  </si>
+  <si>
     <t>2022-12-31</t>
   </si>
   <si>
-    <t>2022-01-01</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
     <t>RAFG22</t>
   </si>
   <si>
@@ -1351,12 +1351,12 @@
     <t>Cuba Hurricane Ian Response - Plan of Action 2022</t>
   </si>
   <si>
+    <t>2022-10-20</t>
+  </si>
+  <si>
     <t>2023-03-31</t>
   </si>
   <si>
-    <t>2022-10-20</t>
-  </si>
-  <si>
     <t>RDRCRRP22</t>
   </si>
   <si>
@@ -1387,12 +1387,12 @@
     <t>Haïti Choléra+ Appel Éclair 2022</t>
   </si>
   <si>
+    <t>2022-10-16</t>
+  </si>
+  <si>
     <t>2023-04-15</t>
   </si>
   <si>
-    <t>2022-10-16</t>
-  </si>
-  <si>
     <t>FHTI22</t>
   </si>
   <si>
@@ -1450,12 +1450,12 @@
     <t>Malawi Flash Appeal 2022</t>
   </si>
   <si>
+    <t>2022-02-26</t>
+  </si>
+  <si>
     <t>2022-05-31</t>
   </si>
   <si>
-    <t>2022-02-26</t>
-  </si>
-  <si>
     <t>HMLI22</t>
   </si>
   <si>
@@ -1468,12 +1468,12 @@
     <t>Mozambique Gombe Emergency Response Plan 2022</t>
   </si>
   <si>
+    <t>2022-04-01</t>
+  </si>
+  <si>
     <t>2022-09-30</t>
   </si>
   <si>
-    <t>2022-04-01</t>
-  </si>
-  <si>
     <t>HMOZ22</t>
   </si>
   <si>
@@ -1525,12 +1525,12 @@
     <t>Philippines Super Typhoon Rai (Odette) Humanitarian Needs and Priorities 2022</t>
   </si>
   <si>
+    <t>2021-12-24</t>
+  </si>
+  <si>
     <t>2022-06-30</t>
   </si>
   <si>
-    <t>2021-12-24</t>
-  </si>
-  <si>
     <t>RREG22</t>
   </si>
   <si>
@@ -1648,15 +1648,15 @@
     <t>Afghanistan Flash Appeal 2021</t>
   </si>
   <si>
+    <t>2021</t>
+  </si>
+  <si>
+    <t>2021-09-01</t>
+  </si>
+  <si>
     <t>2021-12-31</t>
   </si>
   <si>
-    <t>2021-09-01</t>
-  </si>
-  <si>
-    <t>2021</t>
-  </si>
-  <si>
     <t>HAFG21</t>
   </si>
   <si>
@@ -1747,12 +1747,12 @@
     <t>Escalation of Hostilities in the OPT Flash Appeal 2021</t>
   </si>
   <si>
+    <t>2021-05-27</t>
+  </si>
+  <si>
     <t>2021-08-27</t>
   </si>
   <si>
-    <t>2021-05-27</t>
-  </si>
-  <si>
     <t>HETH21</t>
   </si>
   <si>
@@ -1777,12 +1777,12 @@
     <t>Haiti Earthquake Flash Appeal 2021</t>
   </si>
   <si>
+    <t>2021-08-16</t>
+  </si>
+  <si>
     <t>2022-02-15</t>
   </si>
   <si>
-    <t>2021-08-16</t>
-  </si>
-  <si>
     <t>HHTI21</t>
   </si>
   <si>
@@ -1795,12 +1795,12 @@
     <t>Honduras Tropical Storm Eta Flash Appeal 2021</t>
   </si>
   <si>
+    <t>2020-11-15</t>
+  </si>
+  <si>
     <t>2021-06-30</t>
   </si>
   <si>
-    <t>2020-11-15</t>
-  </si>
-  <si>
     <t>HHND21</t>
   </si>
   <si>
@@ -1834,12 +1834,12 @@
     <t>Lebanon Emergency Response Plan 2021</t>
   </si>
   <si>
+    <t>2021-08-03</t>
+  </si>
+  <si>
     <t>2022-07-31</t>
   </si>
   <si>
-    <t>2021-08-03</t>
-  </si>
-  <si>
     <t>HLBY21</t>
   </si>
   <si>
@@ -2005,15 +2005,15 @@
     <t>Afghanistan Humanitarian Response Plan 2020</t>
   </si>
   <si>
+    <t>2020</t>
+  </si>
+  <si>
+    <t>2020-01-01</t>
+  </si>
+  <si>
     <t>2020-12-31</t>
   </si>
   <si>
-    <t>2020-01-01</t>
-  </si>
-  <si>
-    <t>2020</t>
-  </si>
-  <si>
     <t>OBGD20</t>
   </si>
   <si>
@@ -2128,12 +2128,12 @@
     <t>Djibouti Flash Appeal 2020</t>
   </si>
   <si>
+    <t>2019-12-17</t>
+  </si>
+  <si>
     <t>2020-03-31</t>
   </si>
   <si>
-    <t>2019-12-17</t>
-  </si>
-  <si>
     <t>ODJI20</t>
   </si>
   <si>
@@ -2227,12 +2227,12 @@
     <t>Lebanon Flash Appeal 2020</t>
   </si>
   <si>
+    <t>2020-08-05</t>
+  </si>
+  <si>
     <t>2020-11-13</t>
   </si>
   <si>
-    <t>2020-08-05</t>
-  </si>
-  <si>
     <t>OLBN20</t>
   </si>
   <si>
@@ -2245,12 +2245,12 @@
     <t>Lesotho Flash Appeal 2019-2020</t>
   </si>
   <si>
+    <t>2019-11-01</t>
+  </si>
+  <si>
     <t>2020-04-30</t>
   </si>
   <si>
-    <t>2019-11-01</t>
-  </si>
-  <si>
     <t>OLBR20</t>
   </si>
   <si>
@@ -2440,15 +2440,15 @@
     <t>Afghanistan Humanitarian Response Plan 2019</t>
   </si>
   <si>
+    <t>2019</t>
+  </si>
+  <si>
+    <t>2019-01-01</t>
+  </si>
+  <si>
     <t>2019-12-31</t>
   </si>
   <si>
-    <t>2019-01-01</t>
-  </si>
-  <si>
-    <t>2019</t>
-  </si>
-  <si>
     <t>RBGD19</t>
   </si>
   <si>
@@ -2656,12 +2656,12 @@
     <t>Zimbabwe Flash Appeal 2019</t>
   </si>
   <si>
+    <t>2019-02-01</t>
+  </si>
+  <si>
     <t>2020-04-29</t>
   </si>
   <si>
-    <t>2019-02-01</t>
-  </si>
-  <si>
     <t>FZWE1820</t>
   </si>
   <si>
@@ -2677,15 +2677,15 @@
     <t>Afghanistan Humanitarian Response Plan 2018</t>
   </si>
   <si>
+    <t>2018</t>
+  </si>
+  <si>
+    <t>2018-01-01</t>
+  </si>
+  <si>
     <t>2018-12-31</t>
   </si>
   <si>
-    <t>2018-01-01</t>
-  </si>
-  <si>
-    <t>2018</t>
-  </si>
-  <si>
     <t>OBGD18</t>
   </si>
   <si>
@@ -2860,12 +2860,12 @@
     <t>Syrian Arab Republic Humanitarian Response Plan 2018</t>
   </si>
   <si>
+    <t>2018-11-30</t>
+  </si>
+  <si>
     <t>2018-12-30</t>
   </si>
   <si>
-    <t>2018-11-30</t>
-  </si>
-  <si>
     <t>RSYR18</t>
   </si>
   <si>
@@ -2902,15 +2902,15 @@
     <t>Regional Refugee and Migrant Response Plan for Europe 2017</t>
   </si>
   <si>
+    <t>2017</t>
+  </si>
+  <si>
+    <t>2017-01-01</t>
+  </si>
+  <si>
     <t>2017-12-31</t>
   </si>
   <si>
-    <t>2017-01-01</t>
-  </si>
-  <si>
-    <t>2017</t>
-  </si>
-  <si>
     <t>HAFG17</t>
   </si>
   <si>
@@ -2986,12 +2986,12 @@
     <t>Dominica Hurricane Maria Flash Appeal 2017</t>
   </si>
   <si>
+    <t>2017-09-28</t>
+  </si>
+  <si>
     <t>2017-12-29</t>
   </si>
   <si>
-    <t>2017-09-28</t>
-  </si>
-  <si>
     <t>OPRK17</t>
   </si>
   <si>
@@ -3031,12 +3031,12 @@
     <t>Kenya Flash Appeal 2017</t>
   </si>
   <si>
+    <t>2017-02-10</t>
+  </si>
+  <si>
     <t>2017-11-30</t>
   </si>
   <si>
-    <t>2017-02-10</t>
-  </si>
-  <si>
     <t>HLBY17</t>
   </si>
   <si>
@@ -3049,12 +3049,12 @@
     <t>Madagascar Tropical Cyclone Enawo Flash Appeal 2017</t>
   </si>
   <si>
+    <t>2017-03-20</t>
+  </si>
+  <si>
     <t>2017-06-20</t>
   </si>
   <si>
-    <t>2017-03-20</t>
-  </si>
-  <si>
     <t>HMLI17</t>
   </si>
   <si>
@@ -3073,12 +3073,12 @@
     <t>Mozambique Cyclone Dineo Flash Appeal 2017</t>
   </si>
   <si>
+    <t>2017-02-28</t>
+  </si>
+  <si>
     <t>2017-05-31</t>
   </si>
   <si>
-    <t>2017-02-28</t>
-  </si>
-  <si>
     <t>HMMR17</t>
   </si>
   <si>
@@ -3115,12 +3115,12 @@
     <t>Perú Costa Norte Flash Appeal 2017</t>
   </si>
   <si>
+    <t>2017-04-01</t>
+  </si>
+  <si>
     <t>2017-10-31</t>
   </si>
   <si>
-    <t>2017-04-01</t>
-  </si>
-  <si>
     <t>HCOG17</t>
   </si>
   <si>
@@ -3193,15 +3193,15 @@
     <t>Regional Refugee and Migrant Response Plan for Europe 2016</t>
   </si>
   <si>
+    <t>2016</t>
+  </si>
+  <si>
+    <t>2016-01-01</t>
+  </si>
+  <si>
     <t>2016-12-31</t>
   </si>
   <si>
-    <t>2016-01-01</t>
-  </si>
-  <si>
-    <t>2016</t>
-  </si>
-  <si>
     <t>HAFG16</t>
   </si>
   <si>
@@ -3274,24 +3274,24 @@
     <t>Ecuador Terremoto Flash Appeal 2016</t>
   </si>
   <si>
+    <t>2016-04-16</t>
+  </si>
+  <si>
     <t>2016-10-31</t>
   </si>
   <si>
-    <t>2016-04-16</t>
-  </si>
-  <si>
     <t>FFJI16</t>
   </si>
   <si>
     <t>Fiji Tropical Cyclone Winston Flash Appeal 2016</t>
   </si>
   <si>
+    <t>2016-02-20</t>
+  </si>
+  <si>
     <t>2016-05-30</t>
   </si>
   <si>
-    <t>2016-02-20</t>
-  </si>
-  <si>
     <t>HGMB16</t>
   </si>
   <si>
@@ -3367,12 +3367,12 @@
     <t>Iraq Mosul Flash Appeal 2016</t>
   </si>
   <si>
+    <t>2016-07-20</t>
+  </si>
+  <si>
     <t>2016-10-01</t>
   </si>
   <si>
-    <t>2016-07-20</t>
-  </si>
-  <si>
     <t>HMMR16</t>
   </si>
   <si>
@@ -3463,12 +3463,12 @@
     <t>Zimbabwe Humanitarian Response Plan 2016</t>
   </si>
   <si>
+    <t>2016-04-01</t>
+  </si>
+  <si>
     <t>2017-03-31</t>
   </si>
   <si>
-    <t>2016-04-01</t>
-  </si>
-  <si>
     <t>HAFG15</t>
   </si>
   <si>
@@ -3478,15 +3478,15 @@
     <t>Strategic response plan</t>
   </si>
   <si>
+    <t>2015</t>
+  </si>
+  <si>
+    <t>2015-01-01</t>
+  </si>
+  <si>
     <t>2015-12-31</t>
   </si>
   <si>
-    <t>2015-01-01</t>
-  </si>
-  <si>
-    <t>2015</t>
-  </si>
-  <si>
     <t>HBFA15</t>
   </si>
   <si>
@@ -3541,12 +3541,12 @@
     <t>Guatemala Plan de Respuesta Sequia 2015</t>
   </si>
   <si>
+    <t>2014-11-03</t>
+  </si>
+  <si>
     <t>2015-09-30</t>
   </si>
   <si>
-    <t>2014-11-03</t>
-  </si>
-  <si>
     <t>FHTI15</t>
   </si>
   <si>
@@ -3571,12 +3571,12 @@
     <t>Vanuatu Emergency Response Plan for Tropical Cyclone PAM 2015</t>
   </si>
   <si>
+    <t>2015-03-24</t>
+  </si>
+  <si>
     <t>2015-10-31</t>
   </si>
   <si>
-    <t>2015-03-24</t>
-  </si>
-  <si>
     <t>HIRQ15</t>
   </si>
   <si>
@@ -3589,12 +3589,12 @@
     <t>Libya Humanitarian Appeal 2014- 2015</t>
   </si>
   <si>
+    <t>2014-10-01</t>
+  </si>
+  <si>
     <t>2015-05-31</t>
   </si>
   <si>
-    <t>2014-10-01</t>
-  </si>
-  <si>
     <t>HMLI15</t>
   </si>
   <si>
@@ -3709,15 +3709,15 @@
     <t>Afghanistan Strategic Response Plan 2014</t>
   </si>
   <si>
+    <t>2014</t>
+  </si>
+  <si>
+    <t>2014-01-01</t>
+  </si>
+  <si>
     <t>2014-12-31</t>
   </si>
   <si>
-    <t>2014-01-01</t>
-  </si>
-  <si>
-    <t>2014</t>
-  </si>
-  <si>
     <t>HBFA1314</t>
   </si>
   <si>
@@ -3853,24 +3853,24 @@
     <t>Philippines Bohol Earthquake Flash Appeal 2014</t>
   </si>
   <si>
+    <t>2013-10-22</t>
+  </si>
+  <si>
     <t>2014-04-22</t>
   </si>
   <si>
-    <t>2013-10-22</t>
-  </si>
-  <si>
     <t>SPHL1314</t>
   </si>
   <si>
     <t>Philippines Typhoon Haiyan Strategic Response Plan 2014</t>
   </si>
   <si>
+    <t>2013-11-08</t>
+  </si>
+  <si>
     <t>2014-11-07</t>
   </si>
   <si>
-    <t>2013-11-08</t>
-  </si>
-  <si>
     <t>HPHL1314</t>
   </si>
   <si>
@@ -3886,12 +3886,12 @@
     <t>Philippines Zamboanga Crisis Flash Appeal 2014</t>
   </si>
   <si>
+    <t>2013-10-01</t>
+  </si>
+  <si>
     <t>2014-08-31</t>
   </si>
   <si>
-    <t>2013-10-01</t>
-  </si>
-  <si>
     <t>SCOD14</t>
   </si>
   <si>
@@ -4003,12 +4003,12 @@
     <t>Consolidated appeals process</t>
   </si>
   <si>
+    <t>2013</t>
+  </si>
+  <si>
     <t>2013-12-31</t>
   </si>
   <si>
-    <t>2013</t>
-  </si>
-  <si>
     <t>CBFA13</t>
   </si>
   <si>
@@ -4162,15 +4162,15 @@
     <t>2012+ Kenya Emergency Humanitarian Response Plan</t>
   </si>
   <si>
+    <t>2012</t>
+  </si>
+  <si>
+    <t>2012-01-01</t>
+  </si>
+  <si>
     <t>2012-12-31</t>
   </si>
   <si>
-    <t>2012-01-01</t>
-  </si>
-  <si>
-    <t>2012</t>
-  </si>
-  <si>
     <t>CAFG1112</t>
   </si>
   <si>
@@ -4240,12 +4240,12 @@
     <t>Lesotho Food Insecurity (September 2012 - March 2013)</t>
   </si>
   <si>
+    <t>2012-09-18</t>
+  </si>
+  <si>
     <t>2013-03-25</t>
   </si>
   <si>
-    <t>2012-09-18</t>
-  </si>
-  <si>
     <t>CLBR12</t>
   </si>
   <si>
@@ -4318,12 +4318,12 @@
     <t>Syria Humanitarian Assistance Response Plan (SHARP) 2012</t>
   </si>
   <si>
+    <t>2012-06-05</t>
+  </si>
+  <si>
     <t>2012-12-05</t>
   </si>
   <si>
-    <t>2012-06-05</t>
-  </si>
-  <si>
     <t>CYEM12</t>
   </si>
   <si>
@@ -4348,12 +4348,12 @@
     <t>2011+ Kenya Emergency Humanitarian Response Plan</t>
   </si>
   <si>
+    <t>2011</t>
+  </si>
+  <si>
     <t>2011-01-01</t>
   </si>
   <si>
-    <t>2011</t>
-  </si>
-  <si>
     <t>CAFG11</t>
   </si>
   <si>
@@ -4396,12 +4396,12 @@
     <t>El Salvador Flash Appeal (October 2011 - April 2012)</t>
   </si>
   <si>
+    <t>2011-10-25</t>
+  </si>
+  <si>
     <t>2012-04-25</t>
   </si>
   <si>
-    <t>2011-10-25</t>
-  </si>
-  <si>
     <t>CHTI1011</t>
   </si>
   <si>
@@ -4432,24 +4432,24 @@
     <t>Namibia Flash Appeal (April - October 2011)</t>
   </si>
   <si>
+    <t>2011-04-11</t>
+  </si>
+  <si>
     <t>2011-10-11</t>
   </si>
   <si>
-    <t>2011-04-11</t>
-  </si>
-  <si>
     <t>FNIC1112</t>
   </si>
   <si>
     <t>Nicaragua Flash Appeal (October 2011 - April 2012)</t>
   </si>
   <si>
+    <t>2011-10-27</t>
+  </si>
+  <si>
     <t>2012-04-26</t>
   </si>
   <si>
-    <t>2011-10-27</t>
-  </si>
-  <si>
     <t>CNER11</t>
   </si>
   <si>
@@ -4462,12 +4462,12 @@
     <t>Pakistan Rapid Response Plan Floods 2011 (September - March 2012)</t>
   </si>
   <si>
+    <t>2011-09-15</t>
+  </si>
+  <si>
     <t>2012-06-30</t>
   </si>
   <si>
-    <t>2011-09-15</t>
-  </si>
-  <si>
     <t>FXLBYREG11</t>
   </si>
   <si>
@@ -4543,27 +4543,27 @@
     <t>Afghanistan Humanitarian Action Plan 2010</t>
   </si>
   <si>
+    <t>2010</t>
+  </si>
+  <si>
+    <t>2010-01-01</t>
+  </si>
+  <si>
     <t>2010-12-31</t>
   </si>
   <si>
-    <t>2010-01-01</t>
-  </si>
-  <si>
-    <t>2010</t>
-  </si>
-  <si>
     <t>OBFA1011</t>
   </si>
   <si>
     <t>Burkina Faso Emergency Humanitarian Action Plan 2010</t>
   </si>
   <si>
+    <t>2010-08-01</t>
+  </si>
+  <si>
     <t>2011-01-31</t>
   </si>
   <si>
-    <t>2010-08-01</t>
-  </si>
-  <si>
     <t>CCAF10</t>
   </si>
   <si>
@@ -4588,36 +4588,36 @@
     <t>El Salvador Flash Appeal (Revised) (November 2009 - May 2010)</t>
   </si>
   <si>
+    <t>2009-11-01</t>
+  </si>
+  <si>
     <t>2010-05-31</t>
   </si>
   <si>
-    <t>2009-11-01</t>
-  </si>
-  <si>
     <t>FGTM10</t>
   </si>
   <si>
     <t>Guatemala Flash Appeal (Revised) (June - December 2010)</t>
   </si>
   <si>
+    <t>2010-06-10</t>
+  </si>
+  <si>
     <t>2010-12-09</t>
   </si>
   <si>
-    <t>2010-06-10</t>
-  </si>
-  <si>
     <t>CGTM10</t>
   </si>
   <si>
     <t>Guatemala Food Insecurity and Acute Malnutrition Appeal 2010</t>
   </si>
   <si>
+    <t>2010-02-12</t>
+  </si>
+  <si>
     <t>2010-08-11</t>
   </si>
   <si>
-    <t>2010-02-12</t>
-  </si>
-  <si>
     <t>FHTI10</t>
   </si>
   <si>
@@ -4648,12 +4648,12 @@
     <t>Kyrgyzstan Flash Appeal (Revised) (June 2010 - June 2011)</t>
   </si>
   <si>
+    <t>2010-06-01</t>
+  </si>
+  <si>
     <t>2011-06-30</t>
   </si>
   <si>
-    <t>2010-06-01</t>
-  </si>
-  <si>
     <t>CMNG1011</t>
   </si>
   <si>
@@ -4765,27 +4765,27 @@
     <t>Afghanistan Humanitarian Action Plan 2009</t>
   </si>
   <si>
+    <t>2009</t>
+  </si>
+  <si>
+    <t>2009-01-01</t>
+  </si>
+  <si>
     <t>2009-12-31</t>
   </si>
   <si>
-    <t>2009-01-01</t>
-  </si>
-  <si>
-    <t>2009</t>
-  </si>
-  <si>
     <t>FBFA0910</t>
   </si>
   <si>
     <t>Burkina Faso Flash Appeal (September 2009 - February 2010)</t>
   </si>
   <si>
+    <t>2009-09-10</t>
+  </si>
+  <si>
     <t>2010-03-09</t>
   </si>
   <si>
-    <t>2009-09-10</t>
-  </si>
-  <si>
     <t>CCAF09</t>
   </si>
   <si>
@@ -4852,24 +4852,24 @@
     <t>Madagascar Flash Appeal (Revised) (April - October 2009)</t>
   </si>
   <si>
+    <t>2009-04-01</t>
+  </si>
+  <si>
     <t>2009-10-31</t>
   </si>
   <si>
-    <t>2009-04-01</t>
-  </si>
-  <si>
     <t>FNAM09</t>
   </si>
   <si>
     <t>Namibia Flash Appeal (Revised) (March - November 2009)</t>
   </si>
   <si>
+    <t>2009-03-20</t>
+  </si>
+  <si>
     <t>2009-09-30</t>
   </si>
   <si>
-    <t>2009-03-20</t>
-  </si>
-  <si>
     <t>ONPL09</t>
   </si>
   <si>
@@ -4891,12 +4891,12 @@
     <t>Philippines Flash Appeal (Revised) (October 2009 - March 2010)</t>
   </si>
   <si>
+    <t>2009-10-03</t>
+  </si>
+  <si>
     <t>2010-03-31</t>
   </si>
   <si>
-    <t>2009-10-03</t>
-  </si>
-  <si>
     <t>CSOM09</t>
   </si>
   <si>
@@ -4921,12 +4921,12 @@
     <t>Syria Drought Response Plan (Revised) (July 2009 - June 2010)</t>
   </si>
   <si>
+    <t>2009-07-15</t>
+  </si>
+  <si>
     <t>2010-06-14</t>
   </si>
   <si>
-    <t>2009-07-15</t>
-  </si>
-  <si>
     <t>OTJK09</t>
   </si>
   <si>
@@ -4987,27 +4987,27 @@
     <t>Afghanistan Joint Appeal 2008: Humanitarian Consequences of Rise in Food Prices (February - June 2008)</t>
   </si>
   <si>
+    <t>2008</t>
+  </si>
+  <si>
+    <t>2008-02-01</t>
+  </si>
+  <si>
     <t>2008-06-30</t>
   </si>
   <si>
-    <t>2008-02-01</t>
-  </si>
-  <si>
-    <t>2008</t>
-  </si>
-  <si>
     <t>OAFG0809</t>
   </si>
   <si>
     <t>Afghanistan Joint Emergency Appeal 2008: High Food Price and Drought Crisis (July 2008 - June 2009)</t>
   </si>
   <si>
+    <t>2008-07-01</t>
+  </si>
+  <si>
     <t>2009-06-30</t>
   </si>
   <si>
-    <t>2008-07-01</t>
-  </si>
-  <si>
     <t>FBOL08</t>
   </si>
   <si>
@@ -5023,12 +5023,12 @@
     <t>Central African Republic 2008</t>
   </si>
   <si>
+    <t>2008-01-01</t>
+  </si>
+  <si>
     <t>2008-12-31</t>
   </si>
   <si>
-    <t>2008-01-01</t>
-  </si>
-  <si>
     <t>CTCD08</t>
   </si>
   <si>
@@ -5059,24 +5059,24 @@
     <t>Djibouti Joint Appeal 2008: Response Plan for Drought, Food and Nutrition Crisis</t>
   </si>
   <si>
+    <t>2008-08-01</t>
+  </si>
+  <si>
     <t>2009-02-28</t>
   </si>
   <si>
-    <t>2008-08-01</t>
-  </si>
-  <si>
     <t>FGEO0809</t>
   </si>
   <si>
     <t>Georgia Crisis Flash Appeal (Revised) 2008</t>
   </si>
   <si>
+    <t>2008-08-09</t>
+  </si>
+  <si>
     <t>2009-02-09</t>
   </si>
   <si>
-    <t>2008-08-09</t>
-  </si>
-  <si>
     <t>FHTI0809</t>
   </si>
   <si>
@@ -5092,12 +5092,12 @@
     <t>Honduras Flash Appeal (Updated) (November - April) 2008</t>
   </si>
   <si>
+    <t>2008-11-01</t>
+  </si>
+  <si>
     <t>2009-04-30</t>
   </si>
   <si>
-    <t>2008-11-01</t>
-  </si>
-  <si>
     <t>CIRQ08</t>
   </si>
   <si>
@@ -5116,12 +5116,12 @@
     <t>Kyrgyzstan Flash Appeal (Revised) 2008</t>
   </si>
   <si>
+    <t>2008-12-01</t>
+  </si>
+  <si>
     <t>2009-05-31</t>
   </si>
   <si>
-    <t>2008-12-01</t>
-  </si>
-  <si>
     <t>OLAO0809</t>
   </si>
   <si>
@@ -5155,12 +5155,12 @@
     <t>Myanmar Flash Appeal (Revised) 2008</t>
   </si>
   <si>
+    <t>2008-05-01</t>
+  </si>
+  <si>
     <t>2008-11-30</t>
   </si>
   <si>
-    <t>2008-05-01</t>
-  </si>
-  <si>
     <t>ONPL08</t>
   </si>
   <si>
@@ -5260,39 +5260,39 @@
     <t>Bolivia Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2007</t>
+  </si>
+  <si>
+    <t>2007-02-22</t>
+  </si>
+  <si>
     <t>2007-08-21</t>
   </si>
   <si>
-    <t>2007-02-22</t>
-  </si>
-  <si>
-    <t>2007</t>
-  </si>
-  <si>
     <t>FBFA0708</t>
   </si>
   <si>
     <t>Burkina Faso Floods Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2007-11-01</t>
+  </si>
+  <si>
     <t>2008-01-31</t>
   </si>
   <si>
-    <t>2007-11-01</t>
-  </si>
-  <si>
     <t>CBDI07</t>
   </si>
   <si>
     <t>Burundi 2007</t>
   </si>
   <si>
+    <t>2007-01-01</t>
+  </si>
+  <si>
     <t>2007-12-31</t>
   </si>
   <si>
-    <t>2007-01-01</t>
-  </si>
-  <si>
     <t>CCAF07</t>
   </si>
   <si>
@@ -5332,12 +5332,12 @@
     <t>Ghana Floods Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2007-09-01</t>
+  </si>
+  <si>
     <t>2008-03-31</t>
   </si>
   <si>
-    <t>2007-09-01</t>
-  </si>
-  <si>
     <t>CXGLR07</t>
   </si>
   <si>
@@ -5359,36 +5359,36 @@
     <t>Korea DPR Flash Appeal: Floods Emergency 2007</t>
   </si>
   <si>
+    <t>2007-08-28</t>
+  </si>
+  <si>
     <t>2007-11-30</t>
   </si>
   <si>
-    <t>2007-08-28</t>
-  </si>
-  <si>
     <t>OLBN07</t>
   </si>
   <si>
     <t>Lebanon Crisis Appeal 2007</t>
   </si>
   <si>
+    <t>2007-06-04</t>
+  </si>
+  <si>
     <t>2007-09-03</t>
   </si>
   <si>
-    <t>2007-06-04</t>
-  </si>
-  <si>
     <t>FLSO0708</t>
   </si>
   <si>
     <t>Lesotho Drought Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2007-07-28</t>
+  </si>
+  <si>
     <t>2008-01-28</t>
   </si>
   <si>
-    <t>2007-07-28</t>
-  </si>
-  <si>
     <t>CLBR07</t>
   </si>
   <si>
@@ -5401,24 +5401,24 @@
     <t>Madagascar Floods Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2007-03-15</t>
+  </si>
+  <si>
     <t>2007-09-15</t>
   </si>
   <si>
-    <t>2007-03-15</t>
-  </si>
-  <si>
     <t>FMOZ07</t>
   </si>
   <si>
     <t>Mozambique Floods and Cyclone Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2007-03-01</t>
+  </si>
+  <si>
     <t>2007-06-30</t>
   </si>
   <si>
-    <t>2007-03-01</t>
-  </si>
-  <si>
     <t>ONPL07</t>
   </si>
   <si>
@@ -5431,12 +5431,12 @@
     <t>Nicaragua Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2007-09-07</t>
+  </si>
+  <si>
     <t>2008-02-28</t>
   </si>
   <si>
-    <t>2007-09-07</t>
-  </si>
-  <si>
     <t>ORUS07</t>
   </si>
   <si>
@@ -5449,12 +5449,12 @@
     <t>Pakistan Cyclone and Floods Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2007-07-15</t>
+  </si>
+  <si>
     <t>2007-10-31</t>
   </si>
   <si>
-    <t>2007-07-15</t>
-  </si>
-  <si>
     <t>FPER0708</t>
   </si>
   <si>
@@ -5515,12 +5515,12 @@
     <t>Swaziland Drought Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2007-07-20</t>
+  </si>
+  <si>
     <t>2008-01-20</t>
   </si>
   <si>
-    <t>2007-07-20</t>
-  </si>
-  <si>
     <t>CTLS07</t>
   </si>
   <si>
@@ -5572,15 +5572,15 @@
     <t>Afghanistan Drought Joint Appeal 2006</t>
   </si>
   <si>
+    <t>2006</t>
+  </si>
+  <si>
+    <t>2006-07-01</t>
+  </si>
+  <si>
     <t>2006-12-31</t>
   </si>
   <si>
-    <t>2006-07-01</t>
-  </si>
-  <si>
-    <t>2006</t>
-  </si>
-  <si>
     <t>CBDI06</t>
   </si>
   <si>
@@ -5626,24 +5626,24 @@
     <t>Ethiopia Floods Joint Appeal 2006</t>
   </si>
   <si>
+    <t>2006-08-25</t>
+  </si>
+  <si>
     <t>2006-11-25</t>
   </si>
   <si>
-    <t>2006-08-25</t>
-  </si>
-  <si>
     <t>OETH0607</t>
   </si>
   <si>
     <t>Ethiopia: 2006 Govt-UN Joint Emergency Flood Appeal for Somali Region</t>
   </si>
   <si>
+    <t>2006-11-23</t>
+  </si>
+  <si>
     <t>2007-01-22</t>
   </si>
   <si>
-    <t>2006-11-23</t>
-  </si>
-  <si>
     <t>CXGLR06</t>
   </si>
   <si>
@@ -5662,12 +5662,12 @@
     <t>Guinea-Bissau 2006</t>
   </si>
   <si>
+    <t>2006-05-01</t>
+  </si>
+  <si>
     <t>2006-11-30</t>
   </si>
   <si>
-    <t>2006-05-01</t>
-  </si>
-  <si>
     <t>CXHAF06</t>
   </si>
   <si>
@@ -5686,12 +5686,12 @@
     <t>Kenya 2006</t>
   </si>
   <si>
+    <t>2006-10-16</t>
+  </si>
+  <si>
     <t>2007-04-15</t>
   </si>
   <si>
-    <t>2006-10-16</t>
-  </si>
-  <si>
     <t>FKEN06</t>
   </si>
   <si>
@@ -5707,12 +5707,12 @@
     <t>Lebanon Crisis 2006</t>
   </si>
   <si>
+    <t>2006-07-24</t>
+  </si>
+  <si>
     <t>2006-10-23</t>
   </si>
   <si>
-    <t>2006-07-24</t>
-  </si>
-  <si>
     <t>CLBR06</t>
   </si>
   <si>
@@ -5761,12 +5761,12 @@
     <t>Somalia: 2006 Flood Response Plan</t>
   </si>
   <si>
+    <t>2006-12-05</t>
+  </si>
+  <si>
     <t>2007-03-05</t>
   </si>
   <si>
-    <t>2006-12-05</t>
-  </si>
-  <si>
     <t>OLKA06</t>
   </si>
   <si>
@@ -5830,39 +5830,39 @@
     <t>Angola Marburg VHF 2005</t>
   </si>
   <si>
+    <t>2005</t>
+  </si>
+  <si>
+    <t>2005-04-01</t>
+  </si>
+  <si>
     <t>2005-06-30</t>
   </si>
   <si>
-    <t>2005-04-01</t>
-  </si>
-  <si>
-    <t>2005</t>
-  </si>
-  <si>
     <t>FBEN05</t>
   </si>
   <si>
     <t>Benin 2005</t>
   </si>
   <si>
+    <t>2005-05-01</t>
+  </si>
+  <si>
     <t>2005-10-31</t>
   </si>
   <si>
-    <t>2005-05-01</t>
-  </si>
-  <si>
     <t>CBDI05</t>
   </si>
   <si>
     <t>Burundi 2005</t>
   </si>
   <si>
+    <t>2005-01-01</t>
+  </si>
+  <si>
     <t>2005-12-31</t>
   </si>
   <si>
-    <t>2005-01-01</t>
-  </si>
-  <si>
     <t>CCAF05</t>
   </si>
   <si>
@@ -5944,12 +5944,12 @@
     <t>Guyana 2005</t>
   </si>
   <si>
+    <t>2005-02-01</t>
+  </si>
+  <si>
     <t>2005-08-01</t>
   </si>
   <si>
-    <t>2005-02-01</t>
-  </si>
-  <si>
     <t>FXINDTSU05</t>
   </si>
   <si>
@@ -5968,12 +5968,12 @@
     <t>Niger 2005</t>
   </si>
   <si>
+    <t>2005-06-01</t>
+  </si>
+  <si>
     <t>2005-09-30</t>
   </si>
   <si>
-    <t>2005-06-01</t>
-  </si>
-  <si>
     <t>CCOG05</t>
   </si>
   <si>
@@ -5992,12 +5992,12 @@
     <t>West and Central Africa Region Cholera 2005</t>
   </si>
   <si>
+    <t>2005-11-01</t>
+  </si>
+  <si>
     <t>2006-05-31</t>
   </si>
   <si>
-    <t>2005-11-01</t>
-  </si>
-  <si>
     <t>OSDN05</t>
   </si>
   <si>
@@ -6010,12 +6010,12 @@
     <t>South Asia Earthquake 2005</t>
   </si>
   <si>
+    <t>2005-10-11</t>
+  </si>
+  <si>
     <t>2006-04-10</t>
   </si>
   <si>
-    <t>2005-10-11</t>
-  </si>
-  <si>
     <t>CSDN05</t>
   </si>
   <si>
@@ -6046,15 +6046,15 @@
     <t>Afghanistan UN-Government Drought Appeal 2004</t>
   </si>
   <si>
+    <t>2004</t>
+  </si>
+  <si>
+    <t>2004-09-01</t>
+  </si>
+  <si>
     <t>2004-12-31</t>
   </si>
   <si>
-    <t>2004-09-01</t>
-  </si>
-  <si>
-    <t>2004</t>
-  </si>
-  <si>
     <t>CAGO04</t>
   </si>
   <si>
@@ -6070,24 +6070,24 @@
     <t>Bangladesh 2004</t>
   </si>
   <si>
+    <t>2004-08-01</t>
+  </si>
+  <si>
     <t>2005-01-31</t>
   </si>
   <si>
-    <t>2004-08-01</t>
-  </si>
-  <si>
     <t>FBOL0405</t>
   </si>
   <si>
     <t>Bolivia 2004</t>
   </si>
   <si>
+    <t>2004-11-01</t>
+  </si>
+  <si>
     <t>2005-05-31</t>
   </si>
   <si>
-    <t>2004-11-01</t>
-  </si>
-  <si>
     <t>CBDI04</t>
   </si>
   <si>
@@ -6220,24 +6220,24 @@
     <t>Madagascar 2004</t>
   </si>
   <si>
+    <t>2004-03-19</t>
+  </si>
+  <si>
     <t>2004-06-19</t>
   </si>
   <si>
-    <t>2004-03-19</t>
-  </si>
-  <si>
     <t>FPHL0405</t>
   </si>
   <si>
     <t>Philippines 2004</t>
   </si>
   <si>
+    <t>2004-12-15</t>
+  </si>
+  <si>
     <t>2005-03-15</t>
   </si>
   <si>
-    <t>2004-12-15</t>
-  </si>
-  <si>
     <t>CSLE04</t>
   </si>
   <si>
@@ -6295,15 +6295,15 @@
     <t>Afghanistan TAPA 2003</t>
   </si>
   <si>
+    <t>2003</t>
+  </si>
+  <si>
+    <t>2003-01-01</t>
+  </si>
+  <si>
     <t>2003-12-31</t>
   </si>
   <si>
-    <t>2003-01-01</t>
-  </si>
-  <si>
-    <t>2003</t>
-  </si>
-  <si>
     <t>CAGO03</t>
   </si>
   <si>
@@ -6325,12 +6325,12 @@
     <t>Central African Republic 2003</t>
   </si>
   <si>
+    <t>2003-04-01</t>
+  </si>
+  <si>
     <t>2003-06-30</t>
   </si>
   <si>
-    <t>2003-04-01</t>
-  </si>
-  <si>
     <t>CRUS03</t>
   </si>
   <si>
@@ -6355,12 +6355,12 @@
     <t>Côte d'Ivoire and the West Africa Sub-Region 2002-2003</t>
   </si>
   <si>
+    <t>2002-11-01</t>
+  </si>
+  <si>
     <t>2003-01-31</t>
   </si>
   <si>
-    <t>2002-11-01</t>
-  </si>
-  <si>
     <t>CCIV03</t>
   </si>
   <si>
@@ -6406,24 +6406,24 @@
     <t>Haiti (PIR) 2003</t>
   </si>
   <si>
+    <t>2003-03-01</t>
+  </si>
+  <si>
     <t>2003-08-31</t>
   </si>
   <si>
-    <t>2003-03-01</t>
-  </si>
-  <si>
     <t>CLSO0304</t>
   </si>
   <si>
     <t>Humanitarian Crisis in Southern Africa - LESOTHO (July 2003 - June 2004)</t>
   </si>
   <si>
+    <t>2003-07-01</t>
+  </si>
+  <si>
     <t>2004-06-30</t>
   </si>
   <si>
-    <t>2003-07-01</t>
-  </si>
-  <si>
     <t>CMWI03</t>
   </si>
   <si>
@@ -6532,15 +6532,15 @@
     <t>Afghanistan 2002 (ITAP for the Afghan People)</t>
   </si>
   <si>
+    <t>2002</t>
+  </si>
+  <si>
+    <t>2001-10-01</t>
+  </si>
+  <si>
     <t>2002-12-31</t>
   </si>
   <si>
-    <t>2001-10-01</t>
-  </si>
-  <si>
-    <t>2002</t>
-  </si>
-  <si>
     <t>CAGO02</t>
   </si>
   <si>
@@ -6724,15 +6724,15 @@
     <t>Afghanistan 2001</t>
   </si>
   <si>
+    <t>2001</t>
+  </si>
+  <si>
+    <t>2001-01-01</t>
+  </si>
+  <si>
     <t>2001-09-30</t>
   </si>
   <si>
-    <t>2001-01-01</t>
-  </si>
-  <si>
-    <t>2001</t>
-  </si>
-  <si>
     <t>CAGO01</t>
   </si>
   <si>
@@ -6877,13 +6877,13 @@
     <t>Angola 2000</t>
   </si>
   <si>
+    <t>2000</t>
+  </si>
+  <si>
+    <t>2000-01-01</t>
+  </si>
+  <si>
     <t>2000-12-31</t>
-  </si>
-  <si>
-    <t>2000-01-01</t>
-  </si>
-  <si>
-    <t>2000</t>
   </si>
   <si>
     <t>CBDI00</t>
@@ -7550,13 +7550,13 @@
         <v>32</v>
       </c>
       <c r="E10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" t="s">
         <v>33</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>34</v>
-      </c>
-      <c r="G10" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -7573,13 +7573,13 @@
         <v>25</v>
       </c>
       <c r="E11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G11" t="s">
         <v>37</v>
-      </c>
-      <c r="F11" t="s">
-        <v>34</v>
-      </c>
-      <c r="G11" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -7596,13 +7596,13 @@
         <v>25</v>
       </c>
       <c r="E12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" t="s">
         <v>33</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>34</v>
-      </c>
-      <c r="G12" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -7734,13 +7734,13 @@
         <v>22</v>
       </c>
       <c r="E18" t="s">
-        <v>52</v>
+        <v>11</v>
       </c>
       <c r="F18" t="s">
         <v>12</v>
       </c>
       <c r="G18" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -7918,13 +7918,13 @@
         <v>22</v>
       </c>
       <c r="E26" t="s">
-        <v>52</v>
+        <v>11</v>
       </c>
       <c r="F26" t="s">
         <v>69</v>
       </c>
       <c r="G26" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -8148,13 +8148,13 @@
         <v>22</v>
       </c>
       <c r="E36" t="s">
-        <v>90</v>
+        <v>11</v>
       </c>
       <c r="F36" t="s">
         <v>12</v>
       </c>
       <c r="G36" t="s">
-        <v>13</v>
+        <v>90</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -8240,13 +8240,13 @@
         <v>22</v>
       </c>
       <c r="E40" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="F40" t="s">
         <v>96</v>
       </c>
       <c r="G40" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -8493,13 +8493,13 @@
         <v>25</v>
       </c>
       <c r="E51" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="F51" t="s">
         <v>96</v>
       </c>
       <c r="G51" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -8516,13 +8516,13 @@
         <v>25</v>
       </c>
       <c r="E52" t="s">
-        <v>129</v>
+        <v>95</v>
       </c>
       <c r="F52" t="s">
         <v>96</v>
       </c>
       <c r="G52" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -8562,13 +8562,13 @@
         <v>25</v>
       </c>
       <c r="E54" t="s">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="F54" t="s">
         <v>96</v>
       </c>
       <c r="G54" t="s">
-        <v>97</v>
+        <v>134</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -8608,13 +8608,13 @@
         <v>25</v>
       </c>
       <c r="E56" t="s">
-        <v>139</v>
+        <v>95</v>
       </c>
       <c r="F56" t="s">
         <v>96</v>
       </c>
       <c r="G56" t="s">
-        <v>97</v>
+        <v>139</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -8746,13 +8746,13 @@
         <v>22</v>
       </c>
       <c r="E62" t="s">
-        <v>154</v>
+        <v>95</v>
       </c>
       <c r="F62" t="s">
         <v>96</v>
       </c>
       <c r="G62" t="s">
-        <v>97</v>
+        <v>154</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -9160,13 +9160,13 @@
         <v>22</v>
       </c>
       <c r="E80" t="s">
-        <v>139</v>
+        <v>95</v>
       </c>
       <c r="F80" t="s">
         <v>96</v>
       </c>
       <c r="G80" t="s">
-        <v>97</v>
+        <v>139</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -9183,13 +9183,13 @@
         <v>22</v>
       </c>
       <c r="E81" t="s">
-        <v>139</v>
+        <v>95</v>
       </c>
       <c r="F81" t="s">
         <v>96</v>
       </c>
       <c r="G81" t="s">
-        <v>97</v>
+        <v>139</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -9252,13 +9252,13 @@
         <v>25</v>
       </c>
       <c r="E84" t="s">
-        <v>139</v>
+        <v>95</v>
       </c>
       <c r="F84" t="s">
         <v>96</v>
       </c>
       <c r="G84" t="s">
-        <v>97</v>
+        <v>139</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -9275,13 +9275,13 @@
         <v>25</v>
       </c>
       <c r="E85" t="s">
-        <v>129</v>
+        <v>95</v>
       </c>
       <c r="F85" t="s">
         <v>96</v>
       </c>
       <c r="G85" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -9689,13 +9689,13 @@
         <v>25</v>
       </c>
       <c r="E103" t="s">
-        <v>245</v>
+        <v>204</v>
       </c>
       <c r="F103" t="s">
         <v>205</v>
       </c>
       <c r="G103" t="s">
-        <v>206</v>
+        <v>245</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -9712,13 +9712,13 @@
         <v>25</v>
       </c>
       <c r="E104" t="s">
-        <v>248</v>
+        <v>204</v>
       </c>
       <c r="F104" t="s">
         <v>205</v>
       </c>
       <c r="G104" t="s">
-        <v>206</v>
+        <v>248</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -9781,13 +9781,13 @@
         <v>22</v>
       </c>
       <c r="E107" t="s">
-        <v>248</v>
+        <v>204</v>
       </c>
       <c r="F107" t="s">
         <v>256</v>
       </c>
       <c r="G107" t="s">
-        <v>206</v>
+        <v>248</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -10908,13 +10908,13 @@
         <v>22</v>
       </c>
       <c r="E156" t="s">
+        <v>322</v>
+      </c>
+      <c r="F156" t="s">
         <v>365</v>
       </c>
-      <c r="F156" t="s">
+      <c r="G156" t="s">
         <v>366</v>
-      </c>
-      <c r="G156" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -10931,13 +10931,13 @@
         <v>22</v>
       </c>
       <c r="E157" t="s">
+        <v>322</v>
+      </c>
+      <c r="F157" t="s">
         <v>369</v>
       </c>
-      <c r="F157" t="s">
+      <c r="G157" t="s">
         <v>370</v>
-      </c>
-      <c r="G157" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -11046,13 +11046,13 @@
         <v>107</v>
       </c>
       <c r="E162" t="s">
-        <v>369</v>
+        <v>322</v>
       </c>
       <c r="F162" t="s">
         <v>323</v>
       </c>
       <c r="G162" t="s">
-        <v>324</v>
+        <v>370</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -11069,13 +11069,13 @@
         <v>22</v>
       </c>
       <c r="E163" t="s">
-        <v>365</v>
+        <v>322</v>
       </c>
       <c r="F163" t="s">
         <v>323</v>
       </c>
       <c r="G163" t="s">
-        <v>324</v>
+        <v>366</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -11276,13 +11276,13 @@
         <v>32</v>
       </c>
       <c r="E172" t="s">
+        <v>322</v>
+      </c>
+      <c r="F172" t="s">
         <v>400</v>
       </c>
-      <c r="F172" t="s">
+      <c r="G172" t="s">
         <v>401</v>
-      </c>
-      <c r="G172" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -11322,13 +11322,13 @@
         <v>25</v>
       </c>
       <c r="E174" t="s">
-        <v>365</v>
+        <v>322</v>
       </c>
       <c r="F174" t="s">
         <v>406</v>
       </c>
       <c r="G174" t="s">
-        <v>324</v>
+        <v>366</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -11368,13 +11368,13 @@
         <v>25</v>
       </c>
       <c r="E176" t="s">
-        <v>365</v>
+        <v>322</v>
       </c>
       <c r="F176" t="s">
         <v>411</v>
       </c>
       <c r="G176" t="s">
-        <v>324</v>
+        <v>366</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -11713,13 +11713,13 @@
         <v>22</v>
       </c>
       <c r="E191" t="s">
+        <v>428</v>
+      </c>
+      <c r="F191" t="s">
         <v>445</v>
       </c>
-      <c r="F191" t="s">
+      <c r="G191" t="s">
         <v>446</v>
-      </c>
-      <c r="G191" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -11828,13 +11828,13 @@
         <v>25</v>
       </c>
       <c r="E196" t="s">
+        <v>428</v>
+      </c>
+      <c r="F196" t="s">
         <v>457</v>
       </c>
-      <c r="F196" t="s">
+      <c r="G196" t="s">
         <v>458</v>
-      </c>
-      <c r="G196" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -11854,7 +11854,7 @@
         <v>428</v>
       </c>
       <c r="F197" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="G197" t="s">
         <v>430</v>
@@ -11943,13 +11943,13 @@
         <v>25</v>
       </c>
       <c r="E201" t="s">
-        <v>469</v>
+        <v>428</v>
       </c>
       <c r="F201" t="s">
         <v>429</v>
       </c>
       <c r="G201" t="s">
-        <v>430</v>
+        <v>469</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -12035,13 +12035,13 @@
         <v>25</v>
       </c>
       <c r="E205" t="s">
+        <v>428</v>
+      </c>
+      <c r="F205" t="s">
         <v>478</v>
       </c>
-      <c r="F205" t="s">
+      <c r="G205" t="s">
         <v>479</v>
-      </c>
-      <c r="G205" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -12081,13 +12081,13 @@
         <v>25</v>
       </c>
       <c r="E207" t="s">
+        <v>428</v>
+      </c>
+      <c r="F207" t="s">
         <v>484</v>
       </c>
-      <c r="F207" t="s">
+      <c r="G207" t="s">
         <v>485</v>
-      </c>
-      <c r="G207" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -12242,13 +12242,13 @@
         <v>22</v>
       </c>
       <c r="E214" t="s">
-        <v>500</v>
+        <v>428</v>
       </c>
       <c r="F214" t="s">
         <v>498</v>
       </c>
       <c r="G214" t="s">
-        <v>430</v>
+        <v>500</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -12265,13 +12265,13 @@
         <v>22</v>
       </c>
       <c r="E215" t="s">
+        <v>428</v>
+      </c>
+      <c r="F215" t="s">
         <v>503</v>
       </c>
-      <c r="F215" t="s">
+      <c r="G215" t="s">
         <v>504</v>
-      </c>
-      <c r="G215" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -12610,13 +12610,13 @@
         <v>32</v>
       </c>
       <c r="E230" t="s">
-        <v>537</v>
+        <v>428</v>
       </c>
       <c r="F230" t="s">
         <v>532</v>
       </c>
       <c r="G230" t="s">
-        <v>430</v>
+        <v>537</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -12978,13 +12978,13 @@
         <v>107</v>
       </c>
       <c r="E246" t="s">
-        <v>428</v>
+        <v>544</v>
       </c>
       <c r="F246" t="s">
         <v>572</v>
       </c>
       <c r="G246" t="s">
-        <v>546</v>
+        <v>430</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -13001,13 +13001,13 @@
         <v>25</v>
       </c>
       <c r="E247" t="s">
+        <v>544</v>
+      </c>
+      <c r="F247" t="s">
         <v>577</v>
       </c>
-      <c r="F247" t="s">
+      <c r="G247" t="s">
         <v>578</v>
-      </c>
-      <c r="G247" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="248" spans="1:7">
@@ -13070,13 +13070,13 @@
         <v>107</v>
       </c>
       <c r="E250" t="s">
-        <v>428</v>
+        <v>544</v>
       </c>
       <c r="F250" t="s">
         <v>572</v>
       </c>
       <c r="G250" t="s">
-        <v>546</v>
+        <v>430</v>
       </c>
     </row>
     <row r="251" spans="1:7">
@@ -13093,13 +13093,13 @@
         <v>25</v>
       </c>
       <c r="E251" t="s">
+        <v>544</v>
+      </c>
+      <c r="F251" t="s">
         <v>587</v>
       </c>
-      <c r="F251" t="s">
+      <c r="G251" t="s">
         <v>588</v>
-      </c>
-      <c r="G251" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="252" spans="1:7">
@@ -13139,13 +13139,13 @@
         <v>25</v>
       </c>
       <c r="E253" t="s">
+        <v>544</v>
+      </c>
+      <c r="F253" t="s">
         <v>593</v>
       </c>
-      <c r="F253" t="s">
+      <c r="G253" t="s">
         <v>594</v>
-      </c>
-      <c r="G253" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="254" spans="1:7">
@@ -13185,13 +13185,13 @@
         <v>107</v>
       </c>
       <c r="E255" t="s">
-        <v>428</v>
+        <v>544</v>
       </c>
       <c r="F255" t="s">
         <v>572</v>
       </c>
       <c r="G255" t="s">
-        <v>546</v>
+        <v>430</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -13254,13 +13254,13 @@
         <v>22</v>
       </c>
       <c r="E258" t="s">
+        <v>544</v>
+      </c>
+      <c r="F258" t="s">
         <v>606</v>
       </c>
-      <c r="F258" t="s">
+      <c r="G258" t="s">
         <v>607</v>
-      </c>
-      <c r="G258" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="259" spans="1:7">
@@ -13300,13 +13300,13 @@
         <v>25</v>
       </c>
       <c r="E260" t="s">
-        <v>478</v>
+        <v>544</v>
       </c>
       <c r="F260" t="s">
         <v>549</v>
       </c>
       <c r="G260" t="s">
-        <v>546</v>
+        <v>479</v>
       </c>
     </row>
     <row r="261" spans="1:7">
@@ -14082,13 +14082,13 @@
         <v>107</v>
       </c>
       <c r="E294" t="s">
-        <v>549</v>
+        <v>663</v>
       </c>
       <c r="F294" t="s">
         <v>686</v>
       </c>
       <c r="G294" t="s">
-        <v>665</v>
+        <v>549</v>
       </c>
     </row>
     <row r="295" spans="1:7">
@@ -14266,13 +14266,13 @@
         <v>25</v>
       </c>
       <c r="E302" t="s">
+        <v>663</v>
+      </c>
+      <c r="F302" t="s">
         <v>704</v>
       </c>
-      <c r="F302" t="s">
+      <c r="G302" t="s">
         <v>705</v>
-      </c>
-      <c r="G302" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="303" spans="1:7">
@@ -14611,13 +14611,13 @@
         <v>25</v>
       </c>
       <c r="E317" t="s">
+        <v>663</v>
+      </c>
+      <c r="F317" t="s">
         <v>737</v>
       </c>
-      <c r="F317" t="s">
+      <c r="G317" t="s">
         <v>738</v>
-      </c>
-      <c r="G317" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="318" spans="1:7">
@@ -14657,13 +14657,13 @@
         <v>25</v>
       </c>
       <c r="E319" t="s">
+        <v>663</v>
+      </c>
+      <c r="F319" t="s">
         <v>743</v>
       </c>
-      <c r="F319" t="s">
+      <c r="G319" t="s">
         <v>744</v>
-      </c>
-      <c r="G319" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="320" spans="1:7">
@@ -15301,13 +15301,13 @@
         <v>22</v>
       </c>
       <c r="E347" t="s">
-        <v>704</v>
+        <v>663</v>
       </c>
       <c r="F347" t="s">
         <v>801</v>
       </c>
       <c r="G347" t="s">
-        <v>665</v>
+        <v>705</v>
       </c>
     </row>
     <row r="348" spans="1:7">
@@ -15715,13 +15715,13 @@
         <v>25</v>
       </c>
       <c r="E365" t="s">
-        <v>842</v>
+        <v>808</v>
       </c>
       <c r="F365" t="s">
         <v>809</v>
       </c>
       <c r="G365" t="s">
-        <v>810</v>
+        <v>842</v>
       </c>
     </row>
     <row r="366" spans="1:7">
@@ -15853,13 +15853,13 @@
         <v>107</v>
       </c>
       <c r="E371" t="s">
-        <v>855</v>
+        <v>808</v>
       </c>
       <c r="F371" t="s">
         <v>809</v>
       </c>
       <c r="G371" t="s">
-        <v>810</v>
+        <v>855</v>
       </c>
     </row>
     <row r="372" spans="1:7">
@@ -16129,13 +16129,13 @@
         <v>25</v>
       </c>
       <c r="E383" t="s">
+        <v>808</v>
+      </c>
+      <c r="F383" t="s">
         <v>880</v>
       </c>
-      <c r="F383" t="s">
+      <c r="G383" t="s">
         <v>881</v>
-      </c>
-      <c r="G383" t="s">
-        <v>810</v>
       </c>
     </row>
     <row r="384" spans="1:7">
@@ -16152,13 +16152,13 @@
         <v>25</v>
       </c>
       <c r="E384" t="s">
-        <v>880</v>
+        <v>808</v>
       </c>
       <c r="F384" t="s">
         <v>884</v>
       </c>
       <c r="G384" t="s">
-        <v>810</v>
+        <v>881</v>
       </c>
     </row>
     <row r="385" spans="1:7">
@@ -16773,13 +16773,13 @@
         <v>107</v>
       </c>
       <c r="E411" t="s">
-        <v>945</v>
+        <v>887</v>
       </c>
       <c r="F411" t="s">
         <v>888</v>
       </c>
       <c r="G411" t="s">
-        <v>889</v>
+        <v>945</v>
       </c>
     </row>
     <row r="412" spans="1:7">
@@ -16796,13 +16796,13 @@
         <v>107</v>
       </c>
       <c r="E412" t="s">
+        <v>887</v>
+      </c>
+      <c r="F412" t="s">
         <v>948</v>
       </c>
-      <c r="F412" t="s">
+      <c r="G412" t="s">
         <v>949</v>
-      </c>
-      <c r="G412" t="s">
-        <v>889</v>
       </c>
     </row>
     <row r="413" spans="1:7">
@@ -16842,13 +16842,13 @@
         <v>107</v>
       </c>
       <c r="E414" t="s">
+        <v>887</v>
+      </c>
+      <c r="F414" t="s">
         <v>948</v>
       </c>
-      <c r="F414" t="s">
+      <c r="G414" t="s">
         <v>949</v>
-      </c>
-      <c r="G414" t="s">
-        <v>889</v>
       </c>
     </row>
     <row r="415" spans="1:7">
@@ -17187,13 +17187,13 @@
         <v>25</v>
       </c>
       <c r="E429" t="s">
+        <v>962</v>
+      </c>
+      <c r="F429" t="s">
         <v>990</v>
       </c>
-      <c r="F429" t="s">
+      <c r="G429" t="s">
         <v>991</v>
-      </c>
-      <c r="G429" t="s">
-        <v>964</v>
       </c>
     </row>
     <row r="430" spans="1:7">
@@ -17325,13 +17325,13 @@
         <v>25</v>
       </c>
       <c r="E435" t="s">
+        <v>962</v>
+      </c>
+      <c r="F435" t="s">
         <v>1005</v>
       </c>
-      <c r="F435" t="s">
+      <c r="G435" t="s">
         <v>1006</v>
-      </c>
-      <c r="G435" t="s">
-        <v>964</v>
       </c>
     </row>
     <row r="436" spans="1:7">
@@ -17371,13 +17371,13 @@
         <v>25</v>
       </c>
       <c r="E437" t="s">
+        <v>962</v>
+      </c>
+      <c r="F437" t="s">
         <v>1011</v>
       </c>
-      <c r="F437" t="s">
+      <c r="G437" t="s">
         <v>1012</v>
-      </c>
-      <c r="G437" t="s">
-        <v>964</v>
       </c>
     </row>
     <row r="438" spans="1:7">
@@ -17440,13 +17440,13 @@
         <v>25</v>
       </c>
       <c r="E440" t="s">
+        <v>962</v>
+      </c>
+      <c r="F440" t="s">
         <v>1019</v>
       </c>
-      <c r="F440" t="s">
+      <c r="G440" t="s">
         <v>1020</v>
-      </c>
-      <c r="G440" t="s">
-        <v>964</v>
       </c>
     </row>
     <row r="441" spans="1:7">
@@ -17578,13 +17578,13 @@
         <v>25</v>
       </c>
       <c r="E446" t="s">
+        <v>962</v>
+      </c>
+      <c r="F446" t="s">
         <v>1033</v>
       </c>
-      <c r="F446" t="s">
+      <c r="G446" t="s">
         <v>1034</v>
-      </c>
-      <c r="G446" t="s">
-        <v>964</v>
       </c>
     </row>
     <row r="447" spans="1:7">
@@ -18130,13 +18130,13 @@
         <v>25</v>
       </c>
       <c r="E470" t="s">
+        <v>1059</v>
+      </c>
+      <c r="F470" t="s">
         <v>1086</v>
       </c>
-      <c r="F470" t="s">
+      <c r="G470" t="s">
         <v>1087</v>
-      </c>
-      <c r="G470" t="s">
-        <v>1061</v>
       </c>
     </row>
     <row r="471" spans="1:7">
@@ -18153,13 +18153,13 @@
         <v>25</v>
       </c>
       <c r="E471" t="s">
+        <v>1059</v>
+      </c>
+      <c r="F471" t="s">
         <v>1090</v>
       </c>
-      <c r="F471" t="s">
+      <c r="G471" t="s">
         <v>1091</v>
-      </c>
-      <c r="G471" t="s">
-        <v>1061</v>
       </c>
     </row>
     <row r="472" spans="1:7">
@@ -18406,13 +18406,13 @@
         <v>25</v>
       </c>
       <c r="E482" t="s">
+        <v>1059</v>
+      </c>
+      <c r="F482" t="s">
         <v>1117</v>
       </c>
-      <c r="F482" t="s">
+      <c r="G482" t="s">
         <v>1118</v>
-      </c>
-      <c r="G482" t="s">
-        <v>1061</v>
       </c>
     </row>
     <row r="483" spans="1:7">
@@ -18774,13 +18774,13 @@
         <v>107</v>
       </c>
       <c r="E498" t="s">
+        <v>1059</v>
+      </c>
+      <c r="F498" t="s">
         <v>1149</v>
       </c>
-      <c r="F498" t="s">
+      <c r="G498" t="s">
         <v>1150</v>
-      </c>
-      <c r="G498" t="s">
-        <v>1061</v>
       </c>
     </row>
     <row r="499" spans="1:7">
@@ -19004,13 +19004,13 @@
         <v>25</v>
       </c>
       <c r="E508" t="s">
+        <v>1154</v>
+      </c>
+      <c r="F508" t="s">
         <v>1175</v>
       </c>
-      <c r="F508" t="s">
+      <c r="G508" t="s">
         <v>1176</v>
-      </c>
-      <c r="G508" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="509" spans="1:7">
@@ -19050,13 +19050,13 @@
         <v>25</v>
       </c>
       <c r="E510" t="s">
-        <v>1175</v>
+        <v>1154</v>
       </c>
       <c r="F510" t="s">
         <v>1182</v>
       </c>
       <c r="G510" t="s">
-        <v>1156</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="511" spans="1:7">
@@ -19073,13 +19073,13 @@
         <v>25</v>
       </c>
       <c r="E511" t="s">
+        <v>1154</v>
+      </c>
+      <c r="F511" t="s">
         <v>1185</v>
       </c>
-      <c r="F511" t="s">
+      <c r="G511" t="s">
         <v>1186</v>
-      </c>
-      <c r="G511" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="512" spans="1:7">
@@ -19119,13 +19119,13 @@
         <v>25</v>
       </c>
       <c r="E513" t="s">
+        <v>1154</v>
+      </c>
+      <c r="F513" t="s">
         <v>1191</v>
       </c>
-      <c r="F513" t="s">
+      <c r="G513" t="s">
         <v>1192</v>
-      </c>
-      <c r="G513" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="514" spans="1:7">
@@ -19211,13 +19211,13 @@
         <v>25</v>
       </c>
       <c r="E517" t="s">
-        <v>1175</v>
+        <v>1154</v>
       </c>
       <c r="F517" t="s">
         <v>1201</v>
       </c>
       <c r="G517" t="s">
-        <v>1156</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="518" spans="1:7">
@@ -19671,13 +19671,13 @@
         <v>107</v>
       </c>
       <c r="E537" t="s">
-        <v>1245</v>
+        <v>1231</v>
       </c>
       <c r="F537" t="s">
         <v>1232</v>
       </c>
       <c r="G537" t="s">
-        <v>1233</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="538" spans="1:7">
@@ -19717,13 +19717,13 @@
         <v>32</v>
       </c>
       <c r="E539" t="s">
+        <v>1231</v>
+      </c>
+      <c r="F539" t="s">
+        <v>1191</v>
+      </c>
+      <c r="G539" t="s">
         <v>1250</v>
-      </c>
-      <c r="F539" t="s">
-        <v>1192</v>
-      </c>
-      <c r="G539" t="s">
-        <v>1233</v>
       </c>
     </row>
     <row r="540" spans="1:7">
@@ -19740,13 +19740,13 @@
         <v>22</v>
       </c>
       <c r="E540" t="s">
+        <v>1231</v>
+      </c>
+      <c r="F540" t="s">
+        <v>1191</v>
+      </c>
+      <c r="G540" t="s">
         <v>1250</v>
-      </c>
-      <c r="F540" t="s">
-        <v>1192</v>
-      </c>
-      <c r="G540" t="s">
-        <v>1233</v>
       </c>
     </row>
     <row r="541" spans="1:7">
@@ -20016,13 +20016,13 @@
         <v>25</v>
       </c>
       <c r="E552" t="s">
+        <v>1231</v>
+      </c>
+      <c r="F552" t="s">
         <v>1279</v>
       </c>
-      <c r="F552" t="s">
+      <c r="G552" t="s">
         <v>1280</v>
-      </c>
-      <c r="G552" t="s">
-        <v>1233</v>
       </c>
     </row>
     <row r="553" spans="1:7">
@@ -20039,13 +20039,13 @@
         <v>1153</v>
       </c>
       <c r="E553" t="s">
+        <v>1231</v>
+      </c>
+      <c r="F553" t="s">
         <v>1283</v>
       </c>
-      <c r="F553" t="s">
+      <c r="G553" t="s">
         <v>1284</v>
-      </c>
-      <c r="G553" t="s">
-        <v>1233</v>
       </c>
     </row>
     <row r="554" spans="1:7">
@@ -20062,13 +20062,13 @@
         <v>107</v>
       </c>
       <c r="E554" t="s">
+        <v>1231</v>
+      </c>
+      <c r="F554" t="s">
+        <v>1283</v>
+      </c>
+      <c r="G554" t="s">
         <v>1287</v>
-      </c>
-      <c r="F554" t="s">
-        <v>1284</v>
-      </c>
-      <c r="G554" t="s">
-        <v>1233</v>
       </c>
     </row>
     <row r="555" spans="1:7">
@@ -20085,13 +20085,13 @@
         <v>25</v>
       </c>
       <c r="E555" t="s">
+        <v>1231</v>
+      </c>
+      <c r="F555" t="s">
         <v>1290</v>
       </c>
-      <c r="F555" t="s">
+      <c r="G555" t="s">
         <v>1291</v>
-      </c>
-      <c r="G555" t="s">
-        <v>1233</v>
       </c>
     </row>
     <row r="556" spans="1:7">
@@ -20177,13 +20177,13 @@
         <v>107</v>
       </c>
       <c r="E559" t="s">
-        <v>1301</v>
+        <v>1231</v>
       </c>
       <c r="F559" t="s">
         <v>1232</v>
       </c>
       <c r="G559" t="s">
-        <v>1233</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="560" spans="1:7">
@@ -20568,13 +20568,13 @@
         <v>1328</v>
       </c>
       <c r="E576" t="s">
-        <v>1342</v>
+        <v>1329</v>
       </c>
       <c r="F576" t="s">
         <v>1236</v>
       </c>
       <c r="G576" t="s">
-        <v>1330</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="577" spans="1:7">
@@ -20798,13 +20798,13 @@
         <v>1328</v>
       </c>
       <c r="E586" t="s">
-        <v>1290</v>
+        <v>1329</v>
       </c>
       <c r="F586" t="s">
         <v>1236</v>
       </c>
       <c r="G586" t="s">
-        <v>1330</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="587" spans="1:7">
@@ -20913,13 +20913,13 @@
         <v>32</v>
       </c>
       <c r="E591" t="s">
-        <v>1375</v>
+        <v>1329</v>
       </c>
       <c r="F591" t="s">
         <v>1236</v>
       </c>
       <c r="G591" t="s">
-        <v>1330</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="592" spans="1:7">
@@ -21120,13 +21120,13 @@
         <v>1328</v>
       </c>
       <c r="E600" t="s">
-        <v>1399</v>
+        <v>1382</v>
       </c>
       <c r="F600" t="s">
         <v>1383</v>
       </c>
       <c r="G600" t="s">
-        <v>1384</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="601" spans="1:7">
@@ -21212,13 +21212,13 @@
         <v>25</v>
       </c>
       <c r="E604" t="s">
+        <v>1382</v>
+      </c>
+      <c r="F604" t="s">
         <v>1408</v>
       </c>
-      <c r="F604" t="s">
+      <c r="G604" t="s">
         <v>1409</v>
-      </c>
-      <c r="G604" t="s">
-        <v>1384</v>
       </c>
     </row>
     <row r="605" spans="1:7">
@@ -21327,13 +21327,13 @@
         <v>22</v>
       </c>
       <c r="E609" t="s">
-        <v>1421</v>
+        <v>1382</v>
       </c>
       <c r="F609" t="s">
         <v>1383</v>
       </c>
       <c r="G609" t="s">
-        <v>1384</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="610" spans="1:7">
@@ -21465,13 +21465,13 @@
         <v>1328</v>
       </c>
       <c r="E615" t="s">
+        <v>1382</v>
+      </c>
+      <c r="F615" t="s">
         <v>1434</v>
       </c>
-      <c r="F615" t="s">
+      <c r="G615" t="s">
         <v>1435</v>
-      </c>
-      <c r="G615" t="s">
-        <v>1384</v>
       </c>
     </row>
     <row r="616" spans="1:7">
@@ -21557,13 +21557,13 @@
         <v>1328</v>
       </c>
       <c r="E619" t="s">
-        <v>1329</v>
+        <v>1444</v>
       </c>
       <c r="F619" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="G619" t="s">
-        <v>1445</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="620" spans="1:7">
@@ -21580,13 +21580,13 @@
         <v>1328</v>
       </c>
       <c r="E620" t="s">
+        <v>1444</v>
+      </c>
+      <c r="F620" t="s">
+        <v>1445</v>
+      </c>
+      <c r="G620" t="s">
         <v>1448</v>
-      </c>
-      <c r="F620" t="s">
-        <v>1444</v>
-      </c>
-      <c r="G620" t="s">
-        <v>1445</v>
       </c>
     </row>
     <row r="621" spans="1:7">
@@ -21603,13 +21603,13 @@
         <v>1328</v>
       </c>
       <c r="E621" t="s">
+        <v>1444</v>
+      </c>
+      <c r="F621" t="s">
+        <v>1445</v>
+      </c>
+      <c r="G621" t="s">
         <v>1448</v>
-      </c>
-      <c r="F621" t="s">
-        <v>1444</v>
-      </c>
-      <c r="G621" t="s">
-        <v>1445</v>
       </c>
     </row>
     <row r="622" spans="1:7">
@@ -21626,13 +21626,13 @@
         <v>1328</v>
       </c>
       <c r="E622" t="s">
+        <v>1444</v>
+      </c>
+      <c r="F622" t="s">
+        <v>1445</v>
+      </c>
+      <c r="G622" t="s">
         <v>1448</v>
-      </c>
-      <c r="F622" t="s">
-        <v>1444</v>
-      </c>
-      <c r="G622" t="s">
-        <v>1445</v>
       </c>
     </row>
     <row r="623" spans="1:7">
@@ -21649,13 +21649,13 @@
         <v>1328</v>
       </c>
       <c r="E623" t="s">
-        <v>1382</v>
+        <v>1444</v>
       </c>
       <c r="F623" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="G623" t="s">
-        <v>1445</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="624" spans="1:7">
@@ -21672,13 +21672,13 @@
         <v>1328</v>
       </c>
       <c r="E624" t="s">
-        <v>1448</v>
+        <v>1444</v>
       </c>
       <c r="F624" t="s">
         <v>1457</v>
       </c>
       <c r="G624" t="s">
-        <v>1445</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="625" spans="1:7">
@@ -21695,13 +21695,13 @@
         <v>25</v>
       </c>
       <c r="E625" t="s">
+        <v>1444</v>
+      </c>
+      <c r="F625" t="s">
         <v>1460</v>
       </c>
-      <c r="F625" t="s">
+      <c r="G625" t="s">
         <v>1461</v>
-      </c>
-      <c r="G625" t="s">
-        <v>1445</v>
       </c>
     </row>
     <row r="626" spans="1:7">
@@ -21718,13 +21718,13 @@
         <v>1328</v>
       </c>
       <c r="E626" t="s">
-        <v>1448</v>
+        <v>1444</v>
       </c>
       <c r="F626" t="s">
         <v>1464</v>
       </c>
       <c r="G626" t="s">
-        <v>1445</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="627" spans="1:7">
@@ -21741,13 +21741,13 @@
         <v>22</v>
       </c>
       <c r="E627" t="s">
-        <v>1448</v>
+        <v>1444</v>
       </c>
       <c r="F627" t="s">
         <v>1467</v>
       </c>
       <c r="G627" t="s">
-        <v>1445</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="628" spans="1:7">
@@ -21764,13 +21764,13 @@
         <v>22</v>
       </c>
       <c r="E628" t="s">
+        <v>1444</v>
+      </c>
+      <c r="F628" t="s">
+        <v>1445</v>
+      </c>
+      <c r="G628" t="s">
         <v>1448</v>
-      </c>
-      <c r="F628" t="s">
-        <v>1444</v>
-      </c>
-      <c r="G628" t="s">
-        <v>1445</v>
       </c>
     </row>
     <row r="629" spans="1:7">
@@ -21787,13 +21787,13 @@
         <v>25</v>
       </c>
       <c r="E629" t="s">
+        <v>1444</v>
+      </c>
+      <c r="F629" t="s">
         <v>1472</v>
       </c>
-      <c r="F629" t="s">
+      <c r="G629" t="s">
         <v>1473</v>
-      </c>
-      <c r="G629" t="s">
-        <v>1445</v>
       </c>
     </row>
     <row r="630" spans="1:7">
@@ -21810,13 +21810,13 @@
         <v>25</v>
       </c>
       <c r="E630" t="s">
+        <v>1444</v>
+      </c>
+      <c r="F630" t="s">
         <v>1476</v>
       </c>
-      <c r="F630" t="s">
+      <c r="G630" t="s">
         <v>1477</v>
-      </c>
-      <c r="G630" t="s">
-        <v>1445</v>
       </c>
     </row>
     <row r="631" spans="1:7">
@@ -21833,13 +21833,13 @@
         <v>1328</v>
       </c>
       <c r="E631" t="s">
+        <v>1444</v>
+      </c>
+      <c r="F631" t="s">
+        <v>1445</v>
+      </c>
+      <c r="G631" t="s">
         <v>1448</v>
-      </c>
-      <c r="F631" t="s">
-        <v>1444</v>
-      </c>
-      <c r="G631" t="s">
-        <v>1445</v>
       </c>
     </row>
     <row r="632" spans="1:7">
@@ -21856,13 +21856,13 @@
         <v>25</v>
       </c>
       <c r="E632" t="s">
+        <v>1444</v>
+      </c>
+      <c r="F632" t="s">
         <v>1482</v>
       </c>
-      <c r="F632" t="s">
+      <c r="G632" t="s">
         <v>1483</v>
-      </c>
-      <c r="G632" t="s">
-        <v>1445</v>
       </c>
     </row>
     <row r="633" spans="1:7">
@@ -21879,13 +21879,13 @@
         <v>32</v>
       </c>
       <c r="E633" t="s">
-        <v>1448</v>
+        <v>1444</v>
       </c>
       <c r="F633" t="s">
         <v>1486</v>
       </c>
       <c r="G633" t="s">
-        <v>1445</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="634" spans="1:7">
@@ -21902,13 +21902,13 @@
         <v>1328</v>
       </c>
       <c r="E634" t="s">
-        <v>1448</v>
+        <v>1444</v>
       </c>
       <c r="F634" t="s">
         <v>1489</v>
       </c>
       <c r="G634" t="s">
-        <v>1445</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="635" spans="1:7">
@@ -21925,13 +21925,13 @@
         <v>1328</v>
       </c>
       <c r="E635" t="s">
+        <v>1444</v>
+      </c>
+      <c r="F635" t="s">
+        <v>1445</v>
+      </c>
+      <c r="G635" t="s">
         <v>1448</v>
-      </c>
-      <c r="F635" t="s">
-        <v>1444</v>
-      </c>
-      <c r="G635" t="s">
-        <v>1445</v>
       </c>
     </row>
     <row r="636" spans="1:7">
@@ -21948,13 +21948,13 @@
         <v>25</v>
       </c>
       <c r="E636" t="s">
+        <v>1444</v>
+      </c>
+      <c r="F636" t="s">
+        <v>1445</v>
+      </c>
+      <c r="G636" t="s">
         <v>1448</v>
-      </c>
-      <c r="F636" t="s">
-        <v>1444</v>
-      </c>
-      <c r="G636" t="s">
-        <v>1445</v>
       </c>
     </row>
     <row r="637" spans="1:7">
@@ -21971,13 +21971,13 @@
         <v>22</v>
       </c>
       <c r="E637" t="s">
+        <v>1444</v>
+      </c>
+      <c r="F637" t="s">
+        <v>1445</v>
+      </c>
+      <c r="G637" t="s">
         <v>1448</v>
-      </c>
-      <c r="F637" t="s">
-        <v>1444</v>
-      </c>
-      <c r="G637" t="s">
-        <v>1445</v>
       </c>
     </row>
     <row r="638" spans="1:7">
@@ -21994,13 +21994,13 @@
         <v>1328</v>
       </c>
       <c r="E638" t="s">
+        <v>1444</v>
+      </c>
+      <c r="F638" t="s">
+        <v>1445</v>
+      </c>
+      <c r="G638" t="s">
         <v>1498</v>
-      </c>
-      <c r="F638" t="s">
-        <v>1444</v>
-      </c>
-      <c r="G638" t="s">
-        <v>1445</v>
       </c>
     </row>
     <row r="639" spans="1:7">
@@ -22017,13 +22017,13 @@
         <v>32</v>
       </c>
       <c r="E639" t="s">
+        <v>1444</v>
+      </c>
+      <c r="F639" t="s">
+        <v>1445</v>
+      </c>
+      <c r="G639" t="s">
         <v>1448</v>
-      </c>
-      <c r="F639" t="s">
-        <v>1444</v>
-      </c>
-      <c r="G639" t="s">
-        <v>1445</v>
       </c>
     </row>
     <row r="640" spans="1:7">
@@ -22040,13 +22040,13 @@
         <v>1328</v>
       </c>
       <c r="E640" t="s">
+        <v>1444</v>
+      </c>
+      <c r="F640" t="s">
+        <v>1445</v>
+      </c>
+      <c r="G640" t="s">
         <v>1448</v>
-      </c>
-      <c r="F640" t="s">
-        <v>1444</v>
-      </c>
-      <c r="G640" t="s">
-        <v>1445</v>
       </c>
     </row>
     <row r="641" spans="1:7">
@@ -22063,13 +22063,13 @@
         <v>1328</v>
       </c>
       <c r="E641" t="s">
+        <v>1444</v>
+      </c>
+      <c r="F641" t="s">
+        <v>1445</v>
+      </c>
+      <c r="G641" t="s">
         <v>1448</v>
-      </c>
-      <c r="F641" t="s">
-        <v>1444</v>
-      </c>
-      <c r="G641" t="s">
-        <v>1445</v>
       </c>
     </row>
     <row r="642" spans="1:7">
@@ -22086,13 +22086,13 @@
         <v>1328</v>
       </c>
       <c r="E642" t="s">
+        <v>1444</v>
+      </c>
+      <c r="F642" t="s">
+        <v>1445</v>
+      </c>
+      <c r="G642" t="s">
         <v>1448</v>
-      </c>
-      <c r="F642" t="s">
-        <v>1444</v>
-      </c>
-      <c r="G642" t="s">
-        <v>1445</v>
       </c>
     </row>
     <row r="643" spans="1:7">
@@ -22132,13 +22132,13 @@
         <v>22</v>
       </c>
       <c r="E644" t="s">
+        <v>1509</v>
+      </c>
+      <c r="F644" t="s">
         <v>1514</v>
       </c>
-      <c r="F644" t="s">
+      <c r="G644" t="s">
         <v>1515</v>
-      </c>
-      <c r="G644" t="s">
-        <v>1511</v>
       </c>
     </row>
     <row r="645" spans="1:7">
@@ -22224,13 +22224,13 @@
         <v>25</v>
       </c>
       <c r="E648" t="s">
+        <v>1509</v>
+      </c>
+      <c r="F648" t="s">
         <v>1524</v>
       </c>
-      <c r="F648" t="s">
+      <c r="G648" t="s">
         <v>1525</v>
-      </c>
-      <c r="G648" t="s">
-        <v>1511</v>
       </c>
     </row>
     <row r="649" spans="1:7">
@@ -22247,13 +22247,13 @@
         <v>25</v>
       </c>
       <c r="E649" t="s">
+        <v>1509</v>
+      </c>
+      <c r="F649" t="s">
         <v>1528</v>
       </c>
-      <c r="F649" t="s">
+      <c r="G649" t="s">
         <v>1529</v>
-      </c>
-      <c r="G649" t="s">
-        <v>1511</v>
       </c>
     </row>
     <row r="650" spans="1:7">
@@ -22270,13 +22270,13 @@
         <v>1328</v>
       </c>
       <c r="E650" t="s">
+        <v>1509</v>
+      </c>
+      <c r="F650" t="s">
         <v>1532</v>
       </c>
-      <c r="F650" t="s">
+      <c r="G650" t="s">
         <v>1533</v>
-      </c>
-      <c r="G650" t="s">
-        <v>1511</v>
       </c>
     </row>
     <row r="651" spans="1:7">
@@ -22385,13 +22385,13 @@
         <v>25</v>
       </c>
       <c r="E655" t="s">
+        <v>1509</v>
+      </c>
+      <c r="F655" t="s">
         <v>1544</v>
       </c>
-      <c r="F655" t="s">
+      <c r="G655" t="s">
         <v>1545</v>
-      </c>
-      <c r="G655" t="s">
-        <v>1511</v>
       </c>
     </row>
     <row r="656" spans="1:7">
@@ -22408,13 +22408,13 @@
         <v>1328</v>
       </c>
       <c r="E656" t="s">
-        <v>1486</v>
+        <v>1509</v>
       </c>
       <c r="F656" t="s">
         <v>1548</v>
       </c>
       <c r="G656" t="s">
-        <v>1511</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="657" spans="1:7">
@@ -22454,13 +22454,13 @@
         <v>25</v>
       </c>
       <c r="E658" t="s">
+        <v>1509</v>
+      </c>
+      <c r="F658" t="s">
+        <v>1514</v>
+      </c>
+      <c r="G658" t="s">
         <v>1553</v>
-      </c>
-      <c r="F658" t="s">
-        <v>1515</v>
-      </c>
-      <c r="G658" t="s">
-        <v>1511</v>
       </c>
     </row>
     <row r="659" spans="1:7">
@@ -22822,13 +22822,13 @@
         <v>25</v>
       </c>
       <c r="E674" t="s">
+        <v>1583</v>
+      </c>
+      <c r="F674" t="s">
         <v>1588</v>
       </c>
-      <c r="F674" t="s">
+      <c r="G674" t="s">
         <v>1589</v>
-      </c>
-      <c r="G674" t="s">
-        <v>1585</v>
       </c>
     </row>
     <row r="675" spans="1:7">
@@ -22914,13 +22914,13 @@
         <v>1328</v>
       </c>
       <c r="E678" t="s">
-        <v>1598</v>
+        <v>1583</v>
       </c>
       <c r="F678" t="s">
         <v>1584</v>
       </c>
       <c r="G678" t="s">
-        <v>1585</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="679" spans="1:7">
@@ -23029,13 +23029,13 @@
         <v>25</v>
       </c>
       <c r="E683" t="s">
-        <v>1609</v>
+        <v>1583</v>
       </c>
       <c r="F683" t="s">
         <v>1601</v>
       </c>
       <c r="G683" t="s">
-        <v>1585</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="684" spans="1:7">
@@ -23052,13 +23052,13 @@
         <v>25</v>
       </c>
       <c r="E684" t="s">
+        <v>1583</v>
+      </c>
+      <c r="F684" t="s">
         <v>1612</v>
       </c>
-      <c r="F684" t="s">
+      <c r="G684" t="s">
         <v>1613</v>
-      </c>
-      <c r="G684" t="s">
-        <v>1585</v>
       </c>
     </row>
     <row r="685" spans="1:7">
@@ -23075,13 +23075,13 @@
         <v>25</v>
       </c>
       <c r="E685" t="s">
+        <v>1583</v>
+      </c>
+      <c r="F685" t="s">
         <v>1616</v>
       </c>
-      <c r="F685" t="s">
+      <c r="G685" t="s">
         <v>1617</v>
-      </c>
-      <c r="G685" t="s">
-        <v>1585</v>
       </c>
     </row>
     <row r="686" spans="1:7">
@@ -23144,13 +23144,13 @@
         <v>25</v>
       </c>
       <c r="E688" t="s">
+        <v>1583</v>
+      </c>
+      <c r="F688" t="s">
         <v>1625</v>
       </c>
-      <c r="F688" t="s">
+      <c r="G688" t="s">
         <v>1626</v>
-      </c>
-      <c r="G688" t="s">
-        <v>1585</v>
       </c>
     </row>
     <row r="689" spans="1:7">
@@ -23236,13 +23236,13 @@
         <v>22</v>
       </c>
       <c r="E692" t="s">
+        <v>1583</v>
+      </c>
+      <c r="F692" t="s">
         <v>1635</v>
       </c>
-      <c r="F692" t="s">
+      <c r="G692" t="s">
         <v>1636</v>
-      </c>
-      <c r="G692" t="s">
-        <v>1585</v>
       </c>
     </row>
     <row r="693" spans="1:7">
@@ -23466,13 +23466,13 @@
         <v>22</v>
       </c>
       <c r="E702" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F702" t="s">
         <v>1662</v>
       </c>
-      <c r="F702" t="s">
+      <c r="G702" t="s">
         <v>1663</v>
-      </c>
-      <c r="G702" t="s">
-        <v>1659</v>
       </c>
     </row>
     <row r="703" spans="1:7">
@@ -23489,13 +23489,13 @@
         <v>25</v>
       </c>
       <c r="E703" t="s">
-        <v>1666</v>
+        <v>1657</v>
       </c>
       <c r="F703" t="s">
         <v>1658</v>
       </c>
       <c r="G703" t="s">
-        <v>1659</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="704" spans="1:7">
@@ -23512,13 +23512,13 @@
         <v>1328</v>
       </c>
       <c r="E704" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F704" t="s">
         <v>1669</v>
       </c>
-      <c r="F704" t="s">
+      <c r="G704" t="s">
         <v>1670</v>
-      </c>
-      <c r="G704" t="s">
-        <v>1659</v>
       </c>
     </row>
     <row r="705" spans="1:7">
@@ -23535,13 +23535,13 @@
         <v>1328</v>
       </c>
       <c r="E705" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F705" t="s">
         <v>1669</v>
       </c>
-      <c r="F705" t="s">
+      <c r="G705" t="s">
         <v>1670</v>
-      </c>
-      <c r="G705" t="s">
-        <v>1659</v>
       </c>
     </row>
     <row r="706" spans="1:7">
@@ -23558,13 +23558,13 @@
         <v>22</v>
       </c>
       <c r="E706" t="s">
-        <v>1583</v>
+        <v>1657</v>
       </c>
       <c r="F706" t="s">
         <v>1642</v>
       </c>
       <c r="G706" t="s">
-        <v>1659</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="707" spans="1:7">
@@ -23581,13 +23581,13 @@
         <v>1328</v>
       </c>
       <c r="E707" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F707" t="s">
         <v>1669</v>
       </c>
-      <c r="F707" t="s">
+      <c r="G707" t="s">
         <v>1670</v>
-      </c>
-      <c r="G707" t="s">
-        <v>1659</v>
       </c>
     </row>
     <row r="708" spans="1:7">
@@ -23604,13 +23604,13 @@
         <v>1328</v>
       </c>
       <c r="E708" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F708" t="s">
         <v>1669</v>
       </c>
-      <c r="F708" t="s">
+      <c r="G708" t="s">
         <v>1670</v>
-      </c>
-      <c r="G708" t="s">
-        <v>1659</v>
       </c>
     </row>
     <row r="709" spans="1:7">
@@ -23627,13 +23627,13 @@
         <v>22</v>
       </c>
       <c r="E709" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F709" t="s">
         <v>1681</v>
       </c>
-      <c r="F709" t="s">
+      <c r="G709" t="s">
         <v>1682</v>
-      </c>
-      <c r="G709" t="s">
-        <v>1659</v>
       </c>
     </row>
     <row r="710" spans="1:7">
@@ -23650,13 +23650,13 @@
         <v>25</v>
       </c>
       <c r="E710" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F710" t="s">
         <v>1685</v>
       </c>
-      <c r="F710" t="s">
+      <c r="G710" t="s">
         <v>1686</v>
-      </c>
-      <c r="G710" t="s">
-        <v>1659</v>
       </c>
     </row>
     <row r="711" spans="1:7">
@@ -23673,13 +23673,13 @@
         <v>25</v>
       </c>
       <c r="E711" t="s">
-        <v>1689</v>
+        <v>1657</v>
       </c>
       <c r="F711" t="s">
         <v>1622</v>
       </c>
       <c r="G711" t="s">
-        <v>1659</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="712" spans="1:7">
@@ -23696,13 +23696,13 @@
         <v>25</v>
       </c>
       <c r="E712" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F712" t="s">
         <v>1692</v>
       </c>
-      <c r="F712" t="s">
+      <c r="G712" t="s">
         <v>1693</v>
-      </c>
-      <c r="G712" t="s">
-        <v>1659</v>
       </c>
     </row>
     <row r="713" spans="1:7">
@@ -23719,13 +23719,13 @@
         <v>1328</v>
       </c>
       <c r="E713" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F713" t="s">
         <v>1669</v>
       </c>
-      <c r="F713" t="s">
+      <c r="G713" t="s">
         <v>1670</v>
-      </c>
-      <c r="G713" t="s">
-        <v>1659</v>
       </c>
     </row>
     <row r="714" spans="1:7">
@@ -23742,13 +23742,13 @@
         <v>25</v>
       </c>
       <c r="E714" t="s">
-        <v>1663</v>
+        <v>1657</v>
       </c>
       <c r="F714" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="G714" t="s">
-        <v>1659</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="715" spans="1:7">
@@ -23765,13 +23765,13 @@
         <v>25</v>
       </c>
       <c r="E715" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F715" t="s">
         <v>1700</v>
       </c>
-      <c r="F715" t="s">
+      <c r="G715" t="s">
         <v>1701</v>
-      </c>
-      <c r="G715" t="s">
-        <v>1659</v>
       </c>
     </row>
     <row r="716" spans="1:7">
@@ -23788,13 +23788,13 @@
         <v>22</v>
       </c>
       <c r="E716" t="s">
-        <v>1704</v>
+        <v>1657</v>
       </c>
       <c r="F716" t="s">
         <v>1642</v>
       </c>
       <c r="G716" t="s">
-        <v>1659</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="717" spans="1:7">
@@ -23811,13 +23811,13 @@
         <v>22</v>
       </c>
       <c r="E717" t="s">
-        <v>1669</v>
+        <v>1657</v>
       </c>
       <c r="F717" t="s">
         <v>1707</v>
       </c>
       <c r="G717" t="s">
-        <v>1659</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="718" spans="1:7">
@@ -23834,13 +23834,13 @@
         <v>1328</v>
       </c>
       <c r="E718" t="s">
-        <v>1669</v>
+        <v>1657</v>
       </c>
       <c r="F718" t="s">
         <v>1707</v>
       </c>
       <c r="G718" t="s">
-        <v>1659</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="719" spans="1:7">
@@ -23880,13 +23880,13 @@
         <v>25</v>
       </c>
       <c r="E720" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F720" t="s">
         <v>1713</v>
       </c>
-      <c r="F720" t="s">
+      <c r="G720" t="s">
         <v>1714</v>
-      </c>
-      <c r="G720" t="s">
-        <v>1659</v>
       </c>
     </row>
     <row r="721" spans="1:7">
@@ -23903,13 +23903,13 @@
         <v>22</v>
       </c>
       <c r="E721" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F721" t="s">
         <v>1669</v>
       </c>
-      <c r="F721" t="s">
+      <c r="G721" t="s">
         <v>1670</v>
-      </c>
-      <c r="G721" t="s">
-        <v>1659</v>
       </c>
     </row>
     <row r="722" spans="1:7">
@@ -23926,13 +23926,13 @@
         <v>22</v>
       </c>
       <c r="E722" t="s">
-        <v>1689</v>
+        <v>1657</v>
       </c>
       <c r="F722" t="s">
         <v>1642</v>
       </c>
       <c r="G722" t="s">
-        <v>1659</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="723" spans="1:7">
@@ -23949,13 +23949,13 @@
         <v>1328</v>
       </c>
       <c r="E723" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F723" t="s">
         <v>1669</v>
       </c>
-      <c r="F723" t="s">
+      <c r="G723" t="s">
         <v>1670</v>
-      </c>
-      <c r="G723" t="s">
-        <v>1659</v>
       </c>
     </row>
     <row r="724" spans="1:7">
@@ -23972,13 +23972,13 @@
         <v>32</v>
       </c>
       <c r="E724" t="s">
-        <v>1723</v>
+        <v>1657</v>
       </c>
       <c r="F724" t="s">
         <v>1658</v>
       </c>
       <c r="G724" t="s">
-        <v>1659</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="725" spans="1:7">
@@ -23995,13 +23995,13 @@
         <v>22</v>
       </c>
       <c r="E725" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F725" t="s">
         <v>1669</v>
       </c>
-      <c r="F725" t="s">
+      <c r="G725" t="s">
         <v>1670</v>
-      </c>
-      <c r="G725" t="s">
-        <v>1659</v>
       </c>
     </row>
     <row r="726" spans="1:7">
@@ -24018,13 +24018,13 @@
         <v>1328</v>
       </c>
       <c r="E726" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F726" t="s">
         <v>1669</v>
       </c>
-      <c r="F726" t="s">
+      <c r="G726" t="s">
         <v>1670</v>
-      </c>
-      <c r="G726" t="s">
-        <v>1659</v>
       </c>
     </row>
     <row r="727" spans="1:7">
@@ -24041,13 +24041,13 @@
         <v>22</v>
       </c>
       <c r="E727" t="s">
-        <v>1692</v>
+        <v>1657</v>
       </c>
       <c r="F727" t="s">
         <v>1642</v>
       </c>
       <c r="G727" t="s">
-        <v>1659</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="728" spans="1:7">
@@ -24064,13 +24064,13 @@
         <v>25</v>
       </c>
       <c r="E728" t="s">
-        <v>1666</v>
+        <v>1657</v>
       </c>
       <c r="F728" t="s">
         <v>1658</v>
       </c>
       <c r="G728" t="s">
-        <v>1659</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="729" spans="1:7">
@@ -24087,13 +24087,13 @@
         <v>22</v>
       </c>
       <c r="E729" t="s">
-        <v>1669</v>
+        <v>1657</v>
       </c>
       <c r="F729" t="s">
         <v>1734</v>
       </c>
       <c r="G729" t="s">
-        <v>1659</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="730" spans="1:7">
@@ -24110,13 +24110,13 @@
         <v>1328</v>
       </c>
       <c r="E730" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F730" t="s">
         <v>1669</v>
       </c>
-      <c r="F730" t="s">
+      <c r="G730" t="s">
         <v>1670</v>
-      </c>
-      <c r="G730" t="s">
-        <v>1659</v>
       </c>
     </row>
     <row r="731" spans="1:7">
@@ -24133,13 +24133,13 @@
         <v>32</v>
       </c>
       <c r="E731" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F731" t="s">
         <v>1669</v>
       </c>
-      <c r="F731" t="s">
+      <c r="G731" t="s">
         <v>1670</v>
-      </c>
-      <c r="G731" t="s">
-        <v>1659</v>
       </c>
     </row>
     <row r="732" spans="1:7">
@@ -24156,13 +24156,13 @@
         <v>1328</v>
       </c>
       <c r="E732" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F732" t="s">
         <v>1669</v>
       </c>
-      <c r="F732" t="s">
+      <c r="G732" t="s">
         <v>1670</v>
-      </c>
-      <c r="G732" t="s">
-        <v>1659</v>
       </c>
     </row>
     <row r="733" spans="1:7">
@@ -24179,13 +24179,13 @@
         <v>25</v>
       </c>
       <c r="E733" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F733" t="s">
         <v>1692</v>
       </c>
-      <c r="F733" t="s">
+      <c r="G733" t="s">
         <v>1693</v>
-      </c>
-      <c r="G733" t="s">
-        <v>1659</v>
       </c>
     </row>
     <row r="734" spans="1:7">
@@ -24202,13 +24202,13 @@
         <v>1328</v>
       </c>
       <c r="E734" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F734" t="s">
         <v>1669</v>
       </c>
-      <c r="F734" t="s">
+      <c r="G734" t="s">
         <v>1670</v>
-      </c>
-      <c r="G734" t="s">
-        <v>1659</v>
       </c>
     </row>
     <row r="735" spans="1:7">
@@ -24225,13 +24225,13 @@
         <v>1328</v>
       </c>
       <c r="E735" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F735" t="s">
         <v>1669</v>
       </c>
-      <c r="F735" t="s">
+      <c r="G735" t="s">
         <v>1670</v>
-      </c>
-      <c r="G735" t="s">
-        <v>1659</v>
       </c>
     </row>
     <row r="736" spans="1:7">
@@ -24271,13 +24271,13 @@
         <v>25</v>
       </c>
       <c r="E737" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F737" t="s">
         <v>1753</v>
       </c>
-      <c r="F737" t="s">
+      <c r="G737" t="s">
         <v>1754</v>
-      </c>
-      <c r="G737" t="s">
-        <v>1750</v>
       </c>
     </row>
     <row r="738" spans="1:7">
@@ -24294,13 +24294,13 @@
         <v>1328</v>
       </c>
       <c r="E738" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F738" t="s">
         <v>1757</v>
       </c>
-      <c r="F738" t="s">
+      <c r="G738" t="s">
         <v>1758</v>
-      </c>
-      <c r="G738" t="s">
-        <v>1750</v>
       </c>
     </row>
     <row r="739" spans="1:7">
@@ -24317,13 +24317,13 @@
         <v>1328</v>
       </c>
       <c r="E739" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F739" t="s">
         <v>1757</v>
       </c>
-      <c r="F739" t="s">
+      <c r="G739" t="s">
         <v>1758</v>
-      </c>
-      <c r="G739" t="s">
-        <v>1750</v>
       </c>
     </row>
     <row r="740" spans="1:7">
@@ -24340,13 +24340,13 @@
         <v>1328</v>
       </c>
       <c r="E740" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F740" t="s">
         <v>1757</v>
       </c>
-      <c r="F740" t="s">
+      <c r="G740" t="s">
         <v>1758</v>
-      </c>
-      <c r="G740" t="s">
-        <v>1750</v>
       </c>
     </row>
     <row r="741" spans="1:7">
@@ -24363,13 +24363,13 @@
         <v>1328</v>
       </c>
       <c r="E741" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F741" t="s">
         <v>1757</v>
       </c>
-      <c r="F741" t="s">
+      <c r="G741" t="s">
         <v>1758</v>
-      </c>
-      <c r="G741" t="s">
-        <v>1750</v>
       </c>
     </row>
     <row r="742" spans="1:7">
@@ -24386,13 +24386,13 @@
         <v>1328</v>
       </c>
       <c r="E742" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F742" t="s">
         <v>1757</v>
       </c>
-      <c r="F742" t="s">
+      <c r="G742" t="s">
         <v>1758</v>
-      </c>
-      <c r="G742" t="s">
-        <v>1750</v>
       </c>
     </row>
     <row r="743" spans="1:7">
@@ -24409,13 +24409,13 @@
         <v>25</v>
       </c>
       <c r="E743" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F743" t="s">
+        <v>1753</v>
+      </c>
+      <c r="G743" t="s">
         <v>1769</v>
-      </c>
-      <c r="F743" t="s">
-        <v>1754</v>
-      </c>
-      <c r="G743" t="s">
-        <v>1750</v>
       </c>
     </row>
     <row r="744" spans="1:7">
@@ -24432,13 +24432,13 @@
         <v>25</v>
       </c>
       <c r="E744" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F744" t="s">
         <v>1772</v>
       </c>
-      <c r="F744" t="s">
+      <c r="G744" t="s">
         <v>1773</v>
-      </c>
-      <c r="G744" t="s">
-        <v>1750</v>
       </c>
     </row>
     <row r="745" spans="1:7">
@@ -24455,13 +24455,13 @@
         <v>32</v>
       </c>
       <c r="E745" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F745" t="s">
         <v>1757</v>
       </c>
-      <c r="F745" t="s">
+      <c r="G745" t="s">
         <v>1758</v>
-      </c>
-      <c r="G745" t="s">
-        <v>1750</v>
       </c>
     </row>
     <row r="746" spans="1:7">
@@ -24478,13 +24478,13 @@
         <v>32</v>
       </c>
       <c r="E746" t="s">
-        <v>1669</v>
+        <v>1748</v>
       </c>
       <c r="F746" t="s">
         <v>1778</v>
       </c>
       <c r="G746" t="s">
-        <v>1750</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="747" spans="1:7">
@@ -24501,13 +24501,13 @@
         <v>25</v>
       </c>
       <c r="E747" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F747" t="s">
         <v>1781</v>
       </c>
-      <c r="F747" t="s">
+      <c r="G747" t="s">
         <v>1782</v>
-      </c>
-      <c r="G747" t="s">
-        <v>1750</v>
       </c>
     </row>
     <row r="748" spans="1:7">
@@ -24524,13 +24524,13 @@
         <v>22</v>
       </c>
       <c r="E748" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F748" t="s">
         <v>1785</v>
       </c>
-      <c r="F748" t="s">
+      <c r="G748" t="s">
         <v>1786</v>
-      </c>
-      <c r="G748" t="s">
-        <v>1750</v>
       </c>
     </row>
     <row r="749" spans="1:7">
@@ -24547,13 +24547,13 @@
         <v>25</v>
       </c>
       <c r="E749" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F749" t="s">
         <v>1789</v>
       </c>
-      <c r="F749" t="s">
+      <c r="G749" t="s">
         <v>1790</v>
-      </c>
-      <c r="G749" t="s">
-        <v>1750</v>
       </c>
     </row>
     <row r="750" spans="1:7">
@@ -24570,13 +24570,13 @@
         <v>1328</v>
       </c>
       <c r="E750" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F750" t="s">
         <v>1757</v>
       </c>
-      <c r="F750" t="s">
+      <c r="G750" t="s">
         <v>1758</v>
-      </c>
-      <c r="G750" t="s">
-        <v>1750</v>
       </c>
     </row>
     <row r="751" spans="1:7">
@@ -24593,13 +24593,13 @@
         <v>25</v>
       </c>
       <c r="E751" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F751" t="s">
         <v>1795</v>
       </c>
-      <c r="F751" t="s">
+      <c r="G751" t="s">
         <v>1796</v>
-      </c>
-      <c r="G751" t="s">
-        <v>1750</v>
       </c>
     </row>
     <row r="752" spans="1:7">
@@ -24616,13 +24616,13 @@
         <v>25</v>
       </c>
       <c r="E752" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F752" t="s">
         <v>1799</v>
       </c>
-      <c r="F752" t="s">
+      <c r="G752" t="s">
         <v>1800</v>
-      </c>
-      <c r="G752" t="s">
-        <v>1750</v>
       </c>
     </row>
     <row r="753" spans="1:7">
@@ -24639,13 +24639,13 @@
         <v>22</v>
       </c>
       <c r="E753" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F753" t="s">
         <v>1757</v>
       </c>
-      <c r="F753" t="s">
+      <c r="G753" t="s">
         <v>1758</v>
-      </c>
-      <c r="G753" t="s">
-        <v>1750</v>
       </c>
     </row>
     <row r="754" spans="1:7">
@@ -24662,13 +24662,13 @@
         <v>25</v>
       </c>
       <c r="E754" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F754" t="s">
         <v>1805</v>
       </c>
-      <c r="F754" t="s">
+      <c r="G754" t="s">
         <v>1806</v>
-      </c>
-      <c r="G754" t="s">
-        <v>1750</v>
       </c>
     </row>
     <row r="755" spans="1:7">
@@ -24685,13 +24685,13 @@
         <v>22</v>
       </c>
       <c r="E755" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F755" t="s">
         <v>1757</v>
       </c>
-      <c r="F755" t="s">
+      <c r="G755" t="s">
         <v>1758</v>
-      </c>
-      <c r="G755" t="s">
-        <v>1750</v>
       </c>
     </row>
     <row r="756" spans="1:7">
@@ -24708,13 +24708,13 @@
         <v>25</v>
       </c>
       <c r="E756" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F756" t="s">
         <v>1811</v>
       </c>
-      <c r="F756" t="s">
+      <c r="G756" t="s">
         <v>1812</v>
-      </c>
-      <c r="G756" t="s">
-        <v>1750</v>
       </c>
     </row>
     <row r="757" spans="1:7">
@@ -24731,13 +24731,13 @@
         <v>25</v>
       </c>
       <c r="E757" t="s">
-        <v>1805</v>
+        <v>1748</v>
       </c>
       <c r="F757" t="s">
         <v>1815</v>
       </c>
       <c r="G757" t="s">
-        <v>1750</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="758" spans="1:7">
@@ -24754,13 +24754,13 @@
         <v>1328</v>
       </c>
       <c r="E758" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F758" t="s">
         <v>1757</v>
       </c>
-      <c r="F758" t="s">
+      <c r="G758" t="s">
         <v>1758</v>
-      </c>
-      <c r="G758" t="s">
-        <v>1750</v>
       </c>
     </row>
     <row r="759" spans="1:7">
@@ -24777,13 +24777,13 @@
         <v>22</v>
       </c>
       <c r="E759" t="s">
-        <v>1799</v>
+        <v>1748</v>
       </c>
       <c r="F759" t="s">
         <v>1820</v>
       </c>
       <c r="G759" t="s">
-        <v>1750</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="760" spans="1:7">
@@ -24800,13 +24800,13 @@
         <v>1328</v>
       </c>
       <c r="E760" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F760" t="s">
         <v>1757</v>
       </c>
-      <c r="F760" t="s">
+      <c r="G760" t="s">
         <v>1758</v>
-      </c>
-      <c r="G760" t="s">
-        <v>1750</v>
       </c>
     </row>
     <row r="761" spans="1:7">
@@ -24823,13 +24823,13 @@
         <v>1328</v>
       </c>
       <c r="E761" t="s">
-        <v>1799</v>
+        <v>1748</v>
       </c>
       <c r="F761" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="G761" t="s">
-        <v>1750</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="762" spans="1:7">
@@ -24846,13 +24846,13 @@
         <v>22</v>
       </c>
       <c r="E762" t="s">
-        <v>1799</v>
+        <v>1748</v>
       </c>
       <c r="F762" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="G762" t="s">
-        <v>1750</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="763" spans="1:7">
@@ -24869,13 +24869,13 @@
         <v>25</v>
       </c>
       <c r="E763" t="s">
-        <v>1753</v>
+        <v>1748</v>
       </c>
       <c r="F763" t="s">
         <v>1828</v>
       </c>
       <c r="G763" t="s">
-        <v>1750</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="764" spans="1:7">
@@ -24892,13 +24892,13 @@
         <v>1328</v>
       </c>
       <c r="E764" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F764" t="s">
         <v>1757</v>
       </c>
-      <c r="F764" t="s">
+      <c r="G764" t="s">
         <v>1758</v>
-      </c>
-      <c r="G764" t="s">
-        <v>1750</v>
       </c>
     </row>
     <row r="765" spans="1:7">
@@ -24915,13 +24915,13 @@
         <v>25</v>
       </c>
       <c r="E765" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F765" t="s">
         <v>1833</v>
       </c>
-      <c r="F765" t="s">
+      <c r="G765" t="s">
         <v>1834</v>
-      </c>
-      <c r="G765" t="s">
-        <v>1750</v>
       </c>
     </row>
     <row r="766" spans="1:7">
@@ -24938,13 +24938,13 @@
         <v>1328</v>
       </c>
       <c r="E766" t="s">
-        <v>1799</v>
+        <v>1748</v>
       </c>
       <c r="F766" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="G766" t="s">
-        <v>1750</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="767" spans="1:7">
@@ -24961,13 +24961,13 @@
         <v>1328</v>
       </c>
       <c r="E767" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F767" t="s">
         <v>1757</v>
       </c>
-      <c r="F767" t="s">
+      <c r="G767" t="s">
         <v>1758</v>
-      </c>
-      <c r="G767" t="s">
-        <v>1750</v>
       </c>
     </row>
     <row r="768" spans="1:7">
@@ -24984,13 +24984,13 @@
         <v>25</v>
       </c>
       <c r="E768" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F768" t="s">
         <v>1772</v>
       </c>
-      <c r="F768" t="s">
+      <c r="G768" t="s">
         <v>1773</v>
-      </c>
-      <c r="G768" t="s">
-        <v>1750</v>
       </c>
     </row>
     <row r="769" spans="1:7">
@@ -25007,13 +25007,13 @@
         <v>32</v>
       </c>
       <c r="E769" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F769" t="s">
         <v>1757</v>
       </c>
-      <c r="F769" t="s">
+      <c r="G769" t="s">
         <v>1758</v>
-      </c>
-      <c r="G769" t="s">
-        <v>1750</v>
       </c>
     </row>
     <row r="770" spans="1:7">
@@ -25030,13 +25030,13 @@
         <v>1328</v>
       </c>
       <c r="E770" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F770" t="s">
         <v>1757</v>
       </c>
-      <c r="F770" t="s">
+      <c r="G770" t="s">
         <v>1758</v>
-      </c>
-      <c r="G770" t="s">
-        <v>1750</v>
       </c>
     </row>
     <row r="771" spans="1:7">
@@ -25053,13 +25053,13 @@
         <v>25</v>
       </c>
       <c r="E771" t="s">
-        <v>1799</v>
+        <v>1748</v>
       </c>
       <c r="F771" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="G771" t="s">
-        <v>1750</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="772" spans="1:7">
@@ -25076,13 +25076,13 @@
         <v>1328</v>
       </c>
       <c r="E772" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F772" t="s">
         <v>1757</v>
       </c>
-      <c r="F772" t="s">
+      <c r="G772" t="s">
         <v>1758</v>
-      </c>
-      <c r="G772" t="s">
-        <v>1750</v>
       </c>
     </row>
     <row r="773" spans="1:7">
@@ -25099,13 +25099,13 @@
         <v>1328</v>
       </c>
       <c r="E773" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F773" t="s">
         <v>1757</v>
       </c>
-      <c r="F773" t="s">
+      <c r="G773" t="s">
         <v>1758</v>
-      </c>
-      <c r="G773" t="s">
-        <v>1750</v>
       </c>
     </row>
     <row r="774" spans="1:7">
@@ -25283,13 +25283,13 @@
         <v>22</v>
       </c>
       <c r="E781" t="s">
+        <v>1852</v>
+      </c>
+      <c r="F781" t="s">
         <v>1870</v>
       </c>
-      <c r="F781" t="s">
+      <c r="G781" t="s">
         <v>1871</v>
-      </c>
-      <c r="G781" t="s">
-        <v>1854</v>
       </c>
     </row>
     <row r="782" spans="1:7">
@@ -25306,13 +25306,13 @@
         <v>22</v>
       </c>
       <c r="E782" t="s">
+        <v>1852</v>
+      </c>
+      <c r="F782" t="s">
         <v>1874</v>
       </c>
-      <c r="F782" t="s">
+      <c r="G782" t="s">
         <v>1875</v>
-      </c>
-      <c r="G782" t="s">
-        <v>1854</v>
       </c>
     </row>
     <row r="783" spans="1:7">
@@ -25375,13 +25375,13 @@
         <v>25</v>
       </c>
       <c r="E785" t="s">
+        <v>1852</v>
+      </c>
+      <c r="F785" t="s">
         <v>1882</v>
       </c>
-      <c r="F785" t="s">
+      <c r="G785" t="s">
         <v>1883</v>
-      </c>
-      <c r="G785" t="s">
-        <v>1854</v>
       </c>
     </row>
     <row r="786" spans="1:7">
@@ -25421,13 +25421,13 @@
         <v>25</v>
       </c>
       <c r="E787" t="s">
+        <v>1852</v>
+      </c>
+      <c r="F787" t="s">
         <v>1882</v>
       </c>
-      <c r="F787" t="s">
+      <c r="G787" t="s">
         <v>1883</v>
-      </c>
-      <c r="G787" t="s">
-        <v>1854</v>
       </c>
     </row>
     <row r="788" spans="1:7">
@@ -25444,13 +25444,13 @@
         <v>25</v>
       </c>
       <c r="E788" t="s">
+        <v>1852</v>
+      </c>
+      <c r="F788" t="s">
         <v>1890</v>
       </c>
-      <c r="F788" t="s">
+      <c r="G788" t="s">
         <v>1891</v>
-      </c>
-      <c r="G788" t="s">
-        <v>1854</v>
       </c>
     </row>
     <row r="789" spans="1:7">
@@ -25490,13 +25490,13 @@
         <v>25</v>
       </c>
       <c r="E790" t="s">
+        <v>1852</v>
+      </c>
+      <c r="F790" t="s">
         <v>1897</v>
       </c>
-      <c r="F790" t="s">
+      <c r="G790" t="s">
         <v>1898</v>
-      </c>
-      <c r="G790" t="s">
-        <v>1854</v>
       </c>
     </row>
     <row r="791" spans="1:7">
@@ -25582,13 +25582,13 @@
         <v>22</v>
       </c>
       <c r="E794" t="s">
-        <v>1757</v>
+        <v>1852</v>
       </c>
       <c r="F794" t="s">
         <v>1908</v>
       </c>
       <c r="G794" t="s">
-        <v>1854</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="795" spans="1:7">
@@ -25651,13 +25651,13 @@
         <v>25</v>
       </c>
       <c r="E797" t="s">
+        <v>1852</v>
+      </c>
+      <c r="F797" t="s">
         <v>1915</v>
       </c>
-      <c r="F797" t="s">
+      <c r="G797" t="s">
         <v>1916</v>
-      </c>
-      <c r="G797" t="s">
-        <v>1854</v>
       </c>
     </row>
     <row r="798" spans="1:7">
@@ -25904,13 +25904,13 @@
         <v>25</v>
       </c>
       <c r="E808" t="s">
+        <v>1938</v>
+      </c>
+      <c r="F808" t="s">
         <v>1943</v>
       </c>
-      <c r="F808" t="s">
+      <c r="G808" t="s">
         <v>1944</v>
-      </c>
-      <c r="G808" t="s">
-        <v>1940</v>
       </c>
     </row>
     <row r="809" spans="1:7">
@@ -25927,13 +25927,13 @@
         <v>1328</v>
       </c>
       <c r="E809" t="s">
+        <v>1938</v>
+      </c>
+      <c r="F809" t="s">
         <v>1947</v>
       </c>
-      <c r="F809" t="s">
+      <c r="G809" t="s">
         <v>1948</v>
-      </c>
-      <c r="G809" t="s">
-        <v>1940</v>
       </c>
     </row>
     <row r="810" spans="1:7">
@@ -25950,13 +25950,13 @@
         <v>1328</v>
       </c>
       <c r="E810" t="s">
+        <v>1938</v>
+      </c>
+      <c r="F810" t="s">
         <v>1947</v>
       </c>
-      <c r="F810" t="s">
+      <c r="G810" t="s">
         <v>1948</v>
-      </c>
-      <c r="G810" t="s">
-        <v>1940</v>
       </c>
     </row>
     <row r="811" spans="1:7">
@@ -25973,13 +25973,13 @@
         <v>1328</v>
       </c>
       <c r="E811" t="s">
+        <v>1938</v>
+      </c>
+      <c r="F811" t="s">
         <v>1947</v>
       </c>
-      <c r="F811" t="s">
+      <c r="G811" t="s">
         <v>1948</v>
-      </c>
-      <c r="G811" t="s">
-        <v>1940</v>
       </c>
     </row>
     <row r="812" spans="1:7">
@@ -25996,13 +25996,13 @@
         <v>1328</v>
       </c>
       <c r="E812" t="s">
+        <v>1938</v>
+      </c>
+      <c r="F812" t="s">
         <v>1947</v>
       </c>
-      <c r="F812" t="s">
+      <c r="G812" t="s">
         <v>1948</v>
-      </c>
-      <c r="G812" t="s">
-        <v>1940</v>
       </c>
     </row>
     <row r="813" spans="1:7">
@@ -26019,13 +26019,13 @@
         <v>1328</v>
       </c>
       <c r="E813" t="s">
+        <v>1938</v>
+      </c>
+      <c r="F813" t="s">
         <v>1947</v>
       </c>
-      <c r="F813" t="s">
+      <c r="G813" t="s">
         <v>1948</v>
-      </c>
-      <c r="G813" t="s">
-        <v>1940</v>
       </c>
     </row>
     <row r="814" spans="1:7">
@@ -26042,13 +26042,13 @@
         <v>1328</v>
       </c>
       <c r="E814" t="s">
+        <v>1938</v>
+      </c>
+      <c r="F814" t="s">
         <v>1947</v>
       </c>
-      <c r="F814" t="s">
+      <c r="G814" t="s">
         <v>1948</v>
-      </c>
-      <c r="G814" t="s">
-        <v>1940</v>
       </c>
     </row>
     <row r="815" spans="1:7">
@@ -26065,13 +26065,13 @@
         <v>25</v>
       </c>
       <c r="E815" t="s">
-        <v>1943</v>
+        <v>1938</v>
       </c>
       <c r="F815" t="s">
         <v>1939</v>
       </c>
       <c r="G815" t="s">
-        <v>1940</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="816" spans="1:7">
@@ -26088,13 +26088,13 @@
         <v>22</v>
       </c>
       <c r="E816" t="s">
-        <v>1947</v>
+        <v>1938</v>
       </c>
       <c r="F816" t="s">
         <v>1903</v>
       </c>
       <c r="G816" t="s">
-        <v>1940</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="817" spans="1:7">
@@ -26111,13 +26111,13 @@
         <v>1328</v>
       </c>
       <c r="E817" t="s">
+        <v>1938</v>
+      </c>
+      <c r="F817" t="s">
         <v>1947</v>
       </c>
-      <c r="F817" t="s">
+      <c r="G817" t="s">
         <v>1948</v>
-      </c>
-      <c r="G817" t="s">
-        <v>1940</v>
       </c>
     </row>
     <row r="818" spans="1:7">
@@ -26137,7 +26137,7 @@
         <v>1938</v>
       </c>
       <c r="F818" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="G818" t="s">
         <v>1940</v>
@@ -26157,13 +26157,13 @@
         <v>1328</v>
       </c>
       <c r="E819" t="s">
+        <v>1938</v>
+      </c>
+      <c r="F819" t="s">
         <v>1947</v>
       </c>
-      <c r="F819" t="s">
+      <c r="G819" t="s">
         <v>1948</v>
-      </c>
-      <c r="G819" t="s">
-        <v>1940</v>
       </c>
     </row>
     <row r="820" spans="1:7">
@@ -26180,13 +26180,13 @@
         <v>25</v>
       </c>
       <c r="E820" t="s">
-        <v>1971</v>
+        <v>1938</v>
       </c>
       <c r="F820" t="s">
         <v>1903</v>
       </c>
       <c r="G820" t="s">
-        <v>1940</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="821" spans="1:7">
@@ -26203,13 +26203,13 @@
         <v>1328</v>
       </c>
       <c r="E821" t="s">
+        <v>1938</v>
+      </c>
+      <c r="F821" t="s">
         <v>1947</v>
       </c>
-      <c r="F821" t="s">
+      <c r="G821" t="s">
         <v>1948</v>
-      </c>
-      <c r="G821" t="s">
-        <v>1940</v>
       </c>
     </row>
     <row r="822" spans="1:7">
@@ -26226,13 +26226,13 @@
         <v>25</v>
       </c>
       <c r="E822" t="s">
+        <v>1938</v>
+      </c>
+      <c r="F822" t="s">
         <v>1976</v>
       </c>
-      <c r="F822" t="s">
+      <c r="G822" t="s">
         <v>1977</v>
-      </c>
-      <c r="G822" t="s">
-        <v>1940</v>
       </c>
     </row>
     <row r="823" spans="1:7">
@@ -26252,7 +26252,7 @@
         <v>1938</v>
       </c>
       <c r="F823" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="G823" t="s">
         <v>1940</v>
@@ -26272,13 +26272,13 @@
         <v>25</v>
       </c>
       <c r="E824" t="s">
-        <v>1971</v>
+        <v>1938</v>
       </c>
       <c r="F824" t="s">
         <v>1981</v>
       </c>
       <c r="G824" t="s">
-        <v>1940</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="825" spans="1:7">
@@ -26295,13 +26295,13 @@
         <v>25</v>
       </c>
       <c r="E825" t="s">
+        <v>1938</v>
+      </c>
+      <c r="F825" t="s">
         <v>1984</v>
       </c>
-      <c r="F825" t="s">
+      <c r="G825" t="s">
         <v>1985</v>
-      </c>
-      <c r="G825" t="s">
-        <v>1940</v>
       </c>
     </row>
     <row r="826" spans="1:7">
@@ -26318,13 +26318,13 @@
         <v>1328</v>
       </c>
       <c r="E826" t="s">
+        <v>1938</v>
+      </c>
+      <c r="F826" t="s">
         <v>1947</v>
       </c>
-      <c r="F826" t="s">
+      <c r="G826" t="s">
         <v>1948</v>
-      </c>
-      <c r="G826" t="s">
-        <v>1940</v>
       </c>
     </row>
     <row r="827" spans="1:7">
@@ -26341,13 +26341,13 @@
         <v>1328</v>
       </c>
       <c r="E827" t="s">
+        <v>1938</v>
+      </c>
+      <c r="F827" t="s">
         <v>1947</v>
       </c>
-      <c r="F827" t="s">
+      <c r="G827" t="s">
         <v>1948</v>
-      </c>
-      <c r="G827" t="s">
-        <v>1940</v>
       </c>
     </row>
     <row r="828" spans="1:7">
@@ -26364,13 +26364,13 @@
         <v>32</v>
       </c>
       <c r="E828" t="s">
+        <v>1938</v>
+      </c>
+      <c r="F828" t="s">
         <v>1992</v>
       </c>
-      <c r="F828" t="s">
+      <c r="G828" t="s">
         <v>1993</v>
-      </c>
-      <c r="G828" t="s">
-        <v>1940</v>
       </c>
     </row>
     <row r="829" spans="1:7">
@@ -26387,13 +26387,13 @@
         <v>22</v>
       </c>
       <c r="E829" t="s">
+        <v>1938</v>
+      </c>
+      <c r="F829" t="s">
         <v>1947</v>
       </c>
-      <c r="F829" t="s">
+      <c r="G829" t="s">
         <v>1948</v>
-      </c>
-      <c r="G829" t="s">
-        <v>1940</v>
       </c>
     </row>
     <row r="830" spans="1:7">
@@ -26410,13 +26410,13 @@
         <v>25</v>
       </c>
       <c r="E830" t="s">
+        <v>1938</v>
+      </c>
+      <c r="F830" t="s">
         <v>1998</v>
       </c>
-      <c r="F830" t="s">
+      <c r="G830" t="s">
         <v>1999</v>
-      </c>
-      <c r="G830" t="s">
-        <v>1940</v>
       </c>
     </row>
     <row r="831" spans="1:7">
@@ -26433,13 +26433,13 @@
         <v>1328</v>
       </c>
       <c r="E831" t="s">
+        <v>1938</v>
+      </c>
+      <c r="F831" t="s">
         <v>1947</v>
       </c>
-      <c r="F831" t="s">
+      <c r="G831" t="s">
         <v>1948</v>
-      </c>
-      <c r="G831" t="s">
-        <v>1940</v>
       </c>
     </row>
     <row r="832" spans="1:7">
@@ -26456,13 +26456,13 @@
         <v>1328</v>
       </c>
       <c r="E832" t="s">
+        <v>1938</v>
+      </c>
+      <c r="F832" t="s">
         <v>1947</v>
       </c>
-      <c r="F832" t="s">
+      <c r="G832" t="s">
         <v>1948</v>
-      </c>
-      <c r="G832" t="s">
-        <v>1940</v>
       </c>
     </row>
     <row r="833" spans="1:7">
@@ -26479,13 +26479,13 @@
         <v>32</v>
       </c>
       <c r="E833" t="s">
+        <v>1938</v>
+      </c>
+      <c r="F833" t="s">
         <v>1947</v>
       </c>
-      <c r="F833" t="s">
+      <c r="G833" t="s">
         <v>1948</v>
-      </c>
-      <c r="G833" t="s">
-        <v>1940</v>
       </c>
     </row>
     <row r="834" spans="1:7">
@@ -26502,13 +26502,13 @@
         <v>25</v>
       </c>
       <c r="E834" t="s">
+        <v>1938</v>
+      </c>
+      <c r="F834" t="s">
         <v>1992</v>
       </c>
-      <c r="F834" t="s">
+      <c r="G834" t="s">
         <v>1993</v>
-      </c>
-      <c r="G834" t="s">
-        <v>1940</v>
       </c>
     </row>
     <row r="835" spans="1:7">
@@ -26525,13 +26525,13 @@
         <v>1328</v>
       </c>
       <c r="E835" t="s">
+        <v>1938</v>
+      </c>
+      <c r="F835" t="s">
         <v>1947</v>
       </c>
-      <c r="F835" t="s">
+      <c r="G835" t="s">
         <v>1948</v>
-      </c>
-      <c r="G835" t="s">
-        <v>1940</v>
       </c>
     </row>
     <row r="836" spans="1:7">
@@ -26594,13 +26594,13 @@
         <v>25</v>
       </c>
       <c r="E838" t="s">
+        <v>2010</v>
+      </c>
+      <c r="F838" t="s">
         <v>2018</v>
       </c>
-      <c r="F838" t="s">
+      <c r="G838" t="s">
         <v>2019</v>
-      </c>
-      <c r="G838" t="s">
-        <v>2012</v>
       </c>
     </row>
     <row r="839" spans="1:7">
@@ -26617,13 +26617,13 @@
         <v>25</v>
       </c>
       <c r="E839" t="s">
+        <v>2010</v>
+      </c>
+      <c r="F839" t="s">
         <v>2022</v>
       </c>
-      <c r="F839" t="s">
+      <c r="G839" t="s">
         <v>2023</v>
-      </c>
-      <c r="G839" t="s">
-        <v>2012</v>
       </c>
     </row>
     <row r="840" spans="1:7">
@@ -26870,13 +26870,13 @@
         <v>25</v>
       </c>
       <c r="E850" t="s">
-        <v>2047</v>
+        <v>2010</v>
       </c>
       <c r="F850" t="s">
         <v>2011</v>
       </c>
       <c r="G850" t="s">
-        <v>2012</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="851" spans="1:7">
@@ -26916,13 +26916,13 @@
         <v>25</v>
       </c>
       <c r="E852" t="s">
-        <v>2052</v>
+        <v>2010</v>
       </c>
       <c r="F852" t="s">
         <v>2030</v>
       </c>
       <c r="G852" t="s">
-        <v>2012</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="853" spans="1:7">
@@ -26939,13 +26939,13 @@
         <v>25</v>
       </c>
       <c r="E853" t="s">
-        <v>2047</v>
+        <v>2010</v>
       </c>
       <c r="F853" t="s">
         <v>2055</v>
       </c>
       <c r="G853" t="s">
-        <v>2012</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="854" spans="1:7">
@@ -26985,13 +26985,13 @@
         <v>25</v>
       </c>
       <c r="E855" t="s">
-        <v>2060</v>
+        <v>2010</v>
       </c>
       <c r="F855" t="s">
         <v>2015</v>
       </c>
       <c r="G855" t="s">
-        <v>2012</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="856" spans="1:7">
@@ -27054,13 +27054,13 @@
         <v>25</v>
       </c>
       <c r="E858" t="s">
+        <v>2010</v>
+      </c>
+      <c r="F858" t="s">
         <v>2068</v>
       </c>
-      <c r="F858" t="s">
+      <c r="G858" t="s">
         <v>2069</v>
-      </c>
-      <c r="G858" t="s">
-        <v>2012</v>
       </c>
     </row>
     <row r="859" spans="1:7">
@@ -27077,13 +27077,13 @@
         <v>25</v>
       </c>
       <c r="E859" t="s">
+        <v>2010</v>
+      </c>
+      <c r="F859" t="s">
         <v>2072</v>
       </c>
-      <c r="F859" t="s">
+      <c r="G859" t="s">
         <v>2073</v>
-      </c>
-      <c r="G859" t="s">
-        <v>2012</v>
       </c>
     </row>
     <row r="860" spans="1:7">
@@ -27376,13 +27376,13 @@
         <v>25</v>
       </c>
       <c r="E872" t="s">
+        <v>2093</v>
+      </c>
+      <c r="F872" t="s">
         <v>2103</v>
       </c>
-      <c r="F872" t="s">
+      <c r="G872" t="s">
         <v>2104</v>
-      </c>
-      <c r="G872" t="s">
-        <v>2095</v>
       </c>
     </row>
     <row r="873" spans="1:7">
@@ -27448,7 +27448,7 @@
         <v>2093</v>
       </c>
       <c r="F875" t="s">
-        <v>2104</v>
+        <v>2103</v>
       </c>
       <c r="G875" t="s">
         <v>2095</v>
@@ -27468,13 +27468,13 @@
         <v>32</v>
       </c>
       <c r="E876" t="s">
+        <v>2093</v>
+      </c>
+      <c r="F876" t="s">
         <v>2113</v>
       </c>
-      <c r="F876" t="s">
+      <c r="G876" t="s">
         <v>2114</v>
-      </c>
-      <c r="G876" t="s">
-        <v>2095</v>
       </c>
     </row>
     <row r="877" spans="1:7">
@@ -27494,7 +27494,7 @@
         <v>2093</v>
       </c>
       <c r="F877" t="s">
-        <v>2104</v>
+        <v>2103</v>
       </c>
       <c r="G877" t="s">
         <v>2095</v>
@@ -27514,13 +27514,13 @@
         <v>25</v>
       </c>
       <c r="E878" t="s">
+        <v>2093</v>
+      </c>
+      <c r="F878" t="s">
         <v>2113</v>
       </c>
-      <c r="F878" t="s">
+      <c r="G878" t="s">
         <v>2114</v>
-      </c>
-      <c r="G878" t="s">
-        <v>2095</v>
       </c>
     </row>
     <row r="879" spans="1:7">
@@ -27675,13 +27675,13 @@
         <v>22</v>
       </c>
       <c r="E885" t="s">
+        <v>2093</v>
+      </c>
+      <c r="F885" t="s">
         <v>2130</v>
       </c>
-      <c r="F885" t="s">
+      <c r="G885" t="s">
         <v>2131</v>
-      </c>
-      <c r="G885" t="s">
-        <v>2095</v>
       </c>
     </row>
     <row r="886" spans="1:7">
@@ -27698,13 +27698,13 @@
         <v>2098</v>
       </c>
       <c r="E886" t="s">
+        <v>2093</v>
+      </c>
+      <c r="F886" t="s">
         <v>2134</v>
       </c>
-      <c r="F886" t="s">
+      <c r="G886" t="s">
         <v>2135</v>
-      </c>
-      <c r="G886" t="s">
-        <v>2095</v>
       </c>
     </row>
     <row r="887" spans="1:7">
@@ -27724,7 +27724,7 @@
         <v>2093</v>
       </c>
       <c r="F887" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
       <c r="G887" t="s">
         <v>2095</v>
@@ -27744,13 +27744,13 @@
         <v>2098</v>
       </c>
       <c r="E888" t="s">
+        <v>2093</v>
+      </c>
+      <c r="F888" t="s">
         <v>2134</v>
       </c>
-      <c r="F888" t="s">
+      <c r="G888" t="s">
         <v>2135</v>
-      </c>
-      <c r="G888" t="s">
-        <v>2095</v>
       </c>
     </row>
     <row r="889" spans="1:7">
@@ -27767,13 +27767,13 @@
         <v>32</v>
       </c>
       <c r="E889" t="s">
+        <v>2093</v>
+      </c>
+      <c r="F889" t="s">
         <v>2134</v>
       </c>
-      <c r="F889" t="s">
+      <c r="G889" t="s">
         <v>2135</v>
-      </c>
-      <c r="G889" t="s">
-        <v>2095</v>
       </c>
     </row>
     <row r="890" spans="1:7">
@@ -27790,13 +27790,13 @@
         <v>1328</v>
       </c>
       <c r="E890" t="s">
+        <v>2093</v>
+      </c>
+      <c r="F890" t="s">
         <v>2134</v>
       </c>
-      <c r="F890" t="s">
+      <c r="G890" t="s">
         <v>2135</v>
-      </c>
-      <c r="G890" t="s">
-        <v>2095</v>
       </c>
     </row>
     <row r="891" spans="1:7">
@@ -27813,13 +27813,13 @@
         <v>2098</v>
       </c>
       <c r="E891" t="s">
+        <v>2093</v>
+      </c>
+      <c r="F891" t="s">
         <v>2134</v>
       </c>
-      <c r="F891" t="s">
+      <c r="G891" t="s">
         <v>2135</v>
-      </c>
-      <c r="G891" t="s">
-        <v>2095</v>
       </c>
     </row>
     <row r="892" spans="1:7">
@@ -27836,13 +27836,13 @@
         <v>2098</v>
       </c>
       <c r="E892" t="s">
+        <v>2093</v>
+      </c>
+      <c r="F892" t="s">
         <v>2134</v>
       </c>
-      <c r="F892" t="s">
+      <c r="G892" t="s">
         <v>2135</v>
-      </c>
-      <c r="G892" t="s">
-        <v>2095</v>
       </c>
     </row>
     <row r="893" spans="1:7">
@@ -27862,7 +27862,7 @@
         <v>2093</v>
       </c>
       <c r="F893" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
       <c r="G893" t="s">
         <v>2095</v>
@@ -27908,7 +27908,7 @@
         <v>2093</v>
       </c>
       <c r="F895" t="s">
-        <v>2104</v>
+        <v>2103</v>
       </c>
       <c r="G895" t="s">
         <v>2095</v>
@@ -27931,7 +27931,7 @@
         <v>2093</v>
       </c>
       <c r="F896" t="s">
-        <v>2104</v>
+        <v>2103</v>
       </c>
       <c r="G896" t="s">
         <v>2095</v>
@@ -28342,13 +28342,13 @@
         <v>2098</v>
       </c>
       <c r="E914" t="s">
-        <v>2103</v>
+        <v>2172</v>
       </c>
       <c r="F914" t="s">
         <v>2194</v>
       </c>
       <c r="G914" t="s">
-        <v>2174</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="915" spans="1:7">
@@ -28365,13 +28365,13 @@
         <v>2098</v>
       </c>
       <c r="E915" t="s">
-        <v>2103</v>
+        <v>2172</v>
       </c>
       <c r="F915" t="s">
         <v>2194</v>
       </c>
       <c r="G915" t="s">
-        <v>2174</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="916" spans="1:7">
@@ -28388,13 +28388,13 @@
         <v>32</v>
       </c>
       <c r="E916" t="s">
-        <v>2103</v>
+        <v>2172</v>
       </c>
       <c r="F916" t="s">
         <v>2194</v>
       </c>
       <c r="G916" t="s">
-        <v>2174</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="917" spans="1:7">
@@ -28411,13 +28411,13 @@
         <v>1328</v>
       </c>
       <c r="E917" t="s">
-        <v>2103</v>
+        <v>2172</v>
       </c>
       <c r="F917" t="s">
         <v>2194</v>
       </c>
       <c r="G917" t="s">
-        <v>2174</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="918" spans="1:7">
@@ -28434,13 +28434,13 @@
         <v>2098</v>
       </c>
       <c r="E918" t="s">
-        <v>2202</v>
+        <v>2172</v>
       </c>
       <c r="F918" t="s">
         <v>2194</v>
       </c>
       <c r="G918" t="s">
-        <v>2174</v>
+        <v>2202</v>
       </c>
     </row>
     <row r="919" spans="1:7">
@@ -28457,13 +28457,13 @@
         <v>2098</v>
       </c>
       <c r="E919" t="s">
-        <v>2103</v>
+        <v>2172</v>
       </c>
       <c r="F919" t="s">
         <v>2194</v>
       </c>
       <c r="G919" t="s">
-        <v>2174</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="920" spans="1:7">
@@ -28480,13 +28480,13 @@
         <v>2098</v>
       </c>
       <c r="E920" t="s">
-        <v>2103</v>
+        <v>2172</v>
       </c>
       <c r="F920" t="s">
         <v>2194</v>
       </c>
       <c r="G920" t="s">
-        <v>2174</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="921" spans="1:7">
@@ -28848,13 +28848,13 @@
         <v>2098</v>
       </c>
       <c r="E936" t="s">
-        <v>2241</v>
+        <v>2236</v>
       </c>
       <c r="F936" t="s">
         <v>2237</v>
       </c>
       <c r="G936" t="s">
-        <v>2238</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="937" spans="1:7">
@@ -28871,13 +28871,13 @@
         <v>2098</v>
       </c>
       <c r="E937" t="s">
-        <v>2241</v>
+        <v>2236</v>
       </c>
       <c r="F937" t="s">
         <v>2237</v>
       </c>
       <c r="G937" t="s">
-        <v>2238</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="938" spans="1:7">
@@ -28894,13 +28894,13 @@
         <v>2098</v>
       </c>
       <c r="E938" t="s">
-        <v>2241</v>
+        <v>2236</v>
       </c>
       <c r="F938" t="s">
         <v>2237</v>
       </c>
       <c r="G938" t="s">
-        <v>2238</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="939" spans="1:7">
@@ -28917,13 +28917,13 @@
         <v>2098</v>
       </c>
       <c r="E939" t="s">
-        <v>2241</v>
+        <v>2236</v>
       </c>
       <c r="F939" t="s">
         <v>2237</v>
       </c>
       <c r="G939" t="s">
-        <v>2238</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="940" spans="1:7">
@@ -28940,13 +28940,13 @@
         <v>22</v>
       </c>
       <c r="E940" t="s">
-        <v>2241</v>
+        <v>2236</v>
       </c>
       <c r="F940" t="s">
         <v>2237</v>
       </c>
       <c r="G940" t="s">
-        <v>2238</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="941" spans="1:7">
@@ -28963,13 +28963,13 @@
         <v>32</v>
       </c>
       <c r="E941" t="s">
-        <v>2241</v>
+        <v>2236</v>
       </c>
       <c r="F941" t="s">
         <v>2237</v>
       </c>
       <c r="G941" t="s">
-        <v>2238</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="942" spans="1:7">
@@ -28986,13 +28986,13 @@
         <v>22</v>
       </c>
       <c r="E942" t="s">
-        <v>2241</v>
+        <v>2236</v>
       </c>
       <c r="F942" t="s">
         <v>2237</v>
       </c>
       <c r="G942" t="s">
-        <v>2238</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="943" spans="1:7">
@@ -29009,13 +29009,13 @@
         <v>2098</v>
       </c>
       <c r="E943" t="s">
-        <v>2241</v>
+        <v>2236</v>
       </c>
       <c r="F943" t="s">
         <v>2237</v>
       </c>
       <c r="G943" t="s">
-        <v>2238</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="944" spans="1:7">
@@ -29032,13 +29032,13 @@
         <v>2098</v>
       </c>
       <c r="E944" t="s">
-        <v>2241</v>
+        <v>2236</v>
       </c>
       <c r="F944" t="s">
         <v>2237</v>
       </c>
       <c r="G944" t="s">
-        <v>2238</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="945" spans="1:7">
@@ -29055,13 +29055,13 @@
         <v>1328</v>
       </c>
       <c r="E945" t="s">
-        <v>2241</v>
+        <v>2236</v>
       </c>
       <c r="F945" t="s">
         <v>2237</v>
       </c>
       <c r="G945" t="s">
-        <v>2238</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="946" spans="1:7">
@@ -29078,13 +29078,13 @@
         <v>22</v>
       </c>
       <c r="E946" t="s">
-        <v>2241</v>
+        <v>2236</v>
       </c>
       <c r="F946" t="s">
         <v>2237</v>
       </c>
       <c r="G946" t="s">
-        <v>2238</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="947" spans="1:7">
@@ -29101,13 +29101,13 @@
         <v>2098</v>
       </c>
       <c r="E947" t="s">
-        <v>2241</v>
+        <v>2236</v>
       </c>
       <c r="F947" t="s">
         <v>2237</v>
       </c>
       <c r="G947" t="s">
-        <v>2238</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="948" spans="1:7">
@@ -29124,13 +29124,13 @@
         <v>2098</v>
       </c>
       <c r="E948" t="s">
-        <v>2241</v>
+        <v>2236</v>
       </c>
       <c r="F948" t="s">
         <v>2237</v>
       </c>
       <c r="G948" t="s">
-        <v>2238</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="949" spans="1:7">
@@ -29147,13 +29147,13 @@
         <v>2098</v>
       </c>
       <c r="E949" t="s">
-        <v>2241</v>
+        <v>2236</v>
       </c>
       <c r="F949" t="s">
         <v>2237</v>
       </c>
       <c r="G949" t="s">
-        <v>2238</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="950" spans="1:7">
@@ -29170,13 +29170,13 @@
         <v>2098</v>
       </c>
       <c r="E950" t="s">
-        <v>2241</v>
+        <v>2236</v>
       </c>
       <c r="F950" t="s">
         <v>2237</v>
       </c>
       <c r="G950" t="s">
-        <v>2238</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="951" spans="1:7">
@@ -29193,13 +29193,13 @@
         <v>2098</v>
       </c>
       <c r="E951" t="s">
-        <v>2241</v>
+        <v>2236</v>
       </c>
       <c r="F951" t="s">
         <v>2237</v>
       </c>
       <c r="G951" t="s">
-        <v>2238</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="952" spans="1:7">
@@ -29216,13 +29216,13 @@
         <v>1328</v>
       </c>
       <c r="E952" t="s">
-        <v>2241</v>
+        <v>2236</v>
       </c>
       <c r="F952" t="s">
         <v>2237</v>
       </c>
       <c r="G952" t="s">
-        <v>2238</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="953" spans="1:7">
@@ -29239,13 +29239,13 @@
         <v>2098</v>
       </c>
       <c r="E953" t="s">
-        <v>2241</v>
+        <v>2236</v>
       </c>
       <c r="F953" t="s">
         <v>2237</v>
       </c>
       <c r="G953" t="s">
-        <v>2238</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="954" spans="1:7">
@@ -29262,13 +29262,13 @@
         <v>2098</v>
       </c>
       <c r="E954" t="s">
-        <v>2241</v>
+        <v>2236</v>
       </c>
       <c r="F954" t="s">
         <v>2237</v>
       </c>
       <c r="G954" t="s">
-        <v>2238</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="955" spans="1:7">
@@ -29285,13 +29285,13 @@
         <v>2098</v>
       </c>
       <c r="E955" t="s">
-        <v>2241</v>
+        <v>2236</v>
       </c>
       <c r="F955" t="s">
         <v>2237</v>
       </c>
       <c r="G955" t="s">
-        <v>2238</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="956" spans="1:7">
@@ -29308,13 +29308,13 @@
         <v>22</v>
       </c>
       <c r="E956" t="s">
-        <v>2241</v>
+        <v>2236</v>
       </c>
       <c r="F956" t="s">
         <v>2237</v>
       </c>
       <c r="G956" t="s">
-        <v>2238</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="957" spans="1:7">
@@ -29331,13 +29331,13 @@
         <v>2098</v>
       </c>
       <c r="E957" t="s">
-        <v>2241</v>
+        <v>2236</v>
       </c>
       <c r="F957" t="s">
         <v>2237</v>
       </c>
       <c r="G957" t="s">
-        <v>2238</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="958" spans="1:7">
@@ -29354,13 +29354,13 @@
         <v>1328</v>
       </c>
       <c r="E958" t="s">
-        <v>2241</v>
+        <v>2236</v>
       </c>
       <c r="F958" t="s">
         <v>2237</v>
       </c>
       <c r="G958" t="s">
-        <v>2238</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="959" spans="1:7">

--- a/api/1/clv3/xlsx/en/HumanitarianPlan.xlsx
+++ b/api/1/clv3/xlsx/en/HumanitarianPlan.xlsx
@@ -31,12 +31,12 @@
     <t>codeforiati:plan-year</t>
   </si>
   <si>
+    <t>codeforiati:plan-end-date</t>
+  </si>
+  <si>
     <t>codeforiati:plan-start-date</t>
   </si>
   <si>
-    <t>codeforiati:plan-end-date</t>
-  </si>
-  <si>
     <t>HAFG26</t>
   </si>
   <si>
@@ -52,12 +52,12 @@
     <t>2026</t>
   </si>
   <si>
+    <t>2026-12-31</t>
+  </si>
+  <si>
     <t>2026-01-01</t>
   </si>
   <si>
-    <t>2026-12-31</t>
-  </si>
-  <si>
     <t>HBFA26</t>
   </si>
   <si>
@@ -115,12 +115,12 @@
     <t>Regional response plan</t>
   </si>
   <si>
+    <t>2026-05-31</t>
+  </si>
+  <si>
     <t>2026-03-01</t>
   </si>
   <si>
-    <t>2026-05-31</t>
-  </si>
-  <si>
     <t>FLBN26</t>
   </si>
   <si>
@@ -304,12 +304,12 @@
     <t>2025</t>
   </si>
   <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
     <t>2025-01-01</t>
   </si>
   <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
     <t>RIRNPAK25</t>
   </si>
   <si>
@@ -631,12 +631,12 @@
     <t>2024</t>
   </si>
   <si>
+    <t>2024-12-31</t>
+  </si>
+  <si>
     <t>2024-01-01</t>
   </si>
   <si>
-    <t>2024-12-31</t>
-  </si>
-  <si>
     <t>RAFG_RRP24</t>
   </si>
   <si>
@@ -985,12 +985,12 @@
     <t>2023</t>
   </si>
   <si>
+    <t>2023-12-31</t>
+  </si>
+  <si>
     <t>2023-01-01</t>
   </si>
   <si>
-    <t>2023-12-31</t>
-  </si>
-  <si>
     <t>RAFG23</t>
   </si>
   <si>
@@ -1111,24 +1111,24 @@
     <t>Mongolia Dzud Early Action and Response Plan 2023</t>
   </si>
   <si>
+    <t>2023-05-31</t>
+  </si>
+  <si>
     <t>2022-12-01</t>
   </si>
   <si>
-    <t>2023-05-31</t>
-  </si>
-  <si>
     <t>OMOZ23</t>
   </si>
   <si>
     <t>Mozambique Cyclone Freddy, Floods and Cholera Response Plan 2023</t>
   </si>
   <si>
+    <t>2023-09-30</t>
+  </si>
+  <si>
     <t>2023-03-01</t>
   </si>
   <si>
-    <t>2023-09-30</t>
-  </si>
-  <si>
     <t>HMOZ23</t>
   </si>
   <si>
@@ -1216,12 +1216,12 @@
     <t>Sudan Emergency: Regional Refugee Response Plan 2023</t>
   </si>
   <si>
+    <t>2023-10-31</t>
+  </si>
+  <si>
     <t>2023-05-01</t>
   </si>
   <si>
-    <t>2023-10-31</t>
-  </si>
-  <si>
     <t>HSDN23</t>
   </si>
   <si>
@@ -1303,12 +1303,12 @@
     <t>2022</t>
   </si>
   <si>
+    <t>2022-12-31</t>
+  </si>
+  <si>
     <t>2022-01-01</t>
   </si>
   <si>
-    <t>2022-12-31</t>
-  </si>
-  <si>
     <t>RAFG22</t>
   </si>
   <si>
@@ -1351,12 +1351,12 @@
     <t>Cuba Hurricane Ian Response - Plan of Action 2022</t>
   </si>
   <si>
+    <t>2023-03-31</t>
+  </si>
+  <si>
     <t>2022-10-20</t>
   </si>
   <si>
-    <t>2023-03-31</t>
-  </si>
-  <si>
     <t>RDRCRRP22</t>
   </si>
   <si>
@@ -1387,12 +1387,12 @@
     <t>Haïti Choléra+ Appel Éclair 2022</t>
   </si>
   <si>
+    <t>2023-04-15</t>
+  </si>
+  <si>
     <t>2022-10-16</t>
   </si>
   <si>
-    <t>2023-04-15</t>
-  </si>
-  <si>
     <t>FHTI22</t>
   </si>
   <si>
@@ -1450,12 +1450,12 @@
     <t>Malawi Flash Appeal 2022</t>
   </si>
   <si>
+    <t>2022-05-31</t>
+  </si>
+  <si>
     <t>2022-02-26</t>
   </si>
   <si>
-    <t>2022-05-31</t>
-  </si>
-  <si>
     <t>HMLI22</t>
   </si>
   <si>
@@ -1468,12 +1468,12 @@
     <t>Mozambique Gombe Emergency Response Plan 2022</t>
   </si>
   <si>
+    <t>2022-09-30</t>
+  </si>
+  <si>
     <t>2022-04-01</t>
   </si>
   <si>
-    <t>2022-09-30</t>
-  </si>
-  <si>
     <t>HMOZ22</t>
   </si>
   <si>
@@ -1525,12 +1525,12 @@
     <t>Philippines Super Typhoon Rai (Odette) Humanitarian Needs and Priorities 2022</t>
   </si>
   <si>
+    <t>2022-06-30</t>
+  </si>
+  <si>
     <t>2021-12-24</t>
   </si>
   <si>
-    <t>2022-06-30</t>
-  </si>
-  <si>
     <t>RREG22</t>
   </si>
   <si>
@@ -1651,12 +1651,12 @@
     <t>2021</t>
   </si>
   <si>
+    <t>2021-12-31</t>
+  </si>
+  <si>
     <t>2021-09-01</t>
   </si>
   <si>
-    <t>2021-12-31</t>
-  </si>
-  <si>
     <t>HAFG21</t>
   </si>
   <si>
@@ -1747,12 +1747,12 @@
     <t>Escalation of Hostilities in the OPT Flash Appeal 2021</t>
   </si>
   <si>
+    <t>2021-08-27</t>
+  </si>
+  <si>
     <t>2021-05-27</t>
   </si>
   <si>
-    <t>2021-08-27</t>
-  </si>
-  <si>
     <t>HETH21</t>
   </si>
   <si>
@@ -1777,12 +1777,12 @@
     <t>Haiti Earthquake Flash Appeal 2021</t>
   </si>
   <si>
+    <t>2022-02-15</t>
+  </si>
+  <si>
     <t>2021-08-16</t>
   </si>
   <si>
-    <t>2022-02-15</t>
-  </si>
-  <si>
     <t>HHTI21</t>
   </si>
   <si>
@@ -1795,12 +1795,12 @@
     <t>Honduras Tropical Storm Eta Flash Appeal 2021</t>
   </si>
   <si>
+    <t>2021-06-30</t>
+  </si>
+  <si>
     <t>2020-11-15</t>
   </si>
   <si>
-    <t>2021-06-30</t>
-  </si>
-  <si>
     <t>HHND21</t>
   </si>
   <si>
@@ -1834,12 +1834,12 @@
     <t>Lebanon Emergency Response Plan 2021</t>
   </si>
   <si>
+    <t>2022-07-31</t>
+  </si>
+  <si>
     <t>2021-08-03</t>
   </si>
   <si>
-    <t>2022-07-31</t>
-  </si>
-  <si>
     <t>HLBY21</t>
   </si>
   <si>
@@ -2008,12 +2008,12 @@
     <t>2020</t>
   </si>
   <si>
+    <t>2020-12-31</t>
+  </si>
+  <si>
     <t>2020-01-01</t>
   </si>
   <si>
-    <t>2020-12-31</t>
-  </si>
-  <si>
     <t>OBGD20</t>
   </si>
   <si>
@@ -2128,12 +2128,12 @@
     <t>Djibouti Flash Appeal 2020</t>
   </si>
   <si>
+    <t>2020-03-31</t>
+  </si>
+  <si>
     <t>2019-12-17</t>
   </si>
   <si>
-    <t>2020-03-31</t>
-  </si>
-  <si>
     <t>ODJI20</t>
   </si>
   <si>
@@ -2227,12 +2227,12 @@
     <t>Lebanon Flash Appeal 2020</t>
   </si>
   <si>
+    <t>2020-11-13</t>
+  </si>
+  <si>
     <t>2020-08-05</t>
   </si>
   <si>
-    <t>2020-11-13</t>
-  </si>
-  <si>
     <t>OLBN20</t>
   </si>
   <si>
@@ -2245,12 +2245,12 @@
     <t>Lesotho Flash Appeal 2019-2020</t>
   </si>
   <si>
+    <t>2020-04-30</t>
+  </si>
+  <si>
     <t>2019-11-01</t>
   </si>
   <si>
-    <t>2020-04-30</t>
-  </si>
-  <si>
     <t>OLBR20</t>
   </si>
   <si>
@@ -2443,12 +2443,12 @@
     <t>2019</t>
   </si>
   <si>
+    <t>2019-12-31</t>
+  </si>
+  <si>
     <t>2019-01-01</t>
   </si>
   <si>
-    <t>2019-12-31</t>
-  </si>
-  <si>
     <t>RBGD19</t>
   </si>
   <si>
@@ -2656,12 +2656,12 @@
     <t>Zimbabwe Flash Appeal 2019</t>
   </si>
   <si>
+    <t>2020-04-29</t>
+  </si>
+  <si>
     <t>2019-02-01</t>
   </si>
   <si>
-    <t>2020-04-29</t>
-  </si>
-  <si>
     <t>FZWE1820</t>
   </si>
   <si>
@@ -2680,12 +2680,12 @@
     <t>2018</t>
   </si>
   <si>
+    <t>2018-12-31</t>
+  </si>
+  <si>
     <t>2018-01-01</t>
   </si>
   <si>
-    <t>2018-12-31</t>
-  </si>
-  <si>
     <t>OBGD18</t>
   </si>
   <si>
@@ -2860,12 +2860,12 @@
     <t>Syrian Arab Republic Humanitarian Response Plan 2018</t>
   </si>
   <si>
+    <t>2018-12-30</t>
+  </si>
+  <si>
     <t>2018-11-30</t>
   </si>
   <si>
-    <t>2018-12-30</t>
-  </si>
-  <si>
     <t>RSYR18</t>
   </si>
   <si>
@@ -2905,12 +2905,12 @@
     <t>2017</t>
   </si>
   <si>
+    <t>2017-12-31</t>
+  </si>
+  <si>
     <t>2017-01-01</t>
   </si>
   <si>
-    <t>2017-12-31</t>
-  </si>
-  <si>
     <t>HAFG17</t>
   </si>
   <si>
@@ -2986,12 +2986,12 @@
     <t>Dominica Hurricane Maria Flash Appeal 2017</t>
   </si>
   <si>
+    <t>2017-12-29</t>
+  </si>
+  <si>
     <t>2017-09-28</t>
   </si>
   <si>
-    <t>2017-12-29</t>
-  </si>
-  <si>
     <t>OPRK17</t>
   </si>
   <si>
@@ -3031,12 +3031,12 @@
     <t>Kenya Flash Appeal 2017</t>
   </si>
   <si>
+    <t>2017-11-30</t>
+  </si>
+  <si>
     <t>2017-02-10</t>
   </si>
   <si>
-    <t>2017-11-30</t>
-  </si>
-  <si>
     <t>HLBY17</t>
   </si>
   <si>
@@ -3049,12 +3049,12 @@
     <t>Madagascar Tropical Cyclone Enawo Flash Appeal 2017</t>
   </si>
   <si>
+    <t>2017-06-20</t>
+  </si>
+  <si>
     <t>2017-03-20</t>
   </si>
   <si>
-    <t>2017-06-20</t>
-  </si>
-  <si>
     <t>HMLI17</t>
   </si>
   <si>
@@ -3073,12 +3073,12 @@
     <t>Mozambique Cyclone Dineo Flash Appeal 2017</t>
   </si>
   <si>
+    <t>2017-05-31</t>
+  </si>
+  <si>
     <t>2017-02-28</t>
   </si>
   <si>
-    <t>2017-05-31</t>
-  </si>
-  <si>
     <t>HMMR17</t>
   </si>
   <si>
@@ -3115,12 +3115,12 @@
     <t>Perú Costa Norte Flash Appeal 2017</t>
   </si>
   <si>
+    <t>2017-10-31</t>
+  </si>
+  <si>
     <t>2017-04-01</t>
   </si>
   <si>
-    <t>2017-10-31</t>
-  </si>
-  <si>
     <t>HCOG17</t>
   </si>
   <si>
@@ -3196,12 +3196,12 @@
     <t>2016</t>
   </si>
   <si>
+    <t>2016-12-31</t>
+  </si>
+  <si>
     <t>2016-01-01</t>
   </si>
   <si>
-    <t>2016-12-31</t>
-  </si>
-  <si>
     <t>HAFG16</t>
   </si>
   <si>
@@ -3274,24 +3274,24 @@
     <t>Ecuador Terremoto Flash Appeal 2016</t>
   </si>
   <si>
+    <t>2016-10-31</t>
+  </si>
+  <si>
     <t>2016-04-16</t>
   </si>
   <si>
-    <t>2016-10-31</t>
-  </si>
-  <si>
     <t>FFJI16</t>
   </si>
   <si>
     <t>Fiji Tropical Cyclone Winston Flash Appeal 2016</t>
   </si>
   <si>
+    <t>2016-05-30</t>
+  </si>
+  <si>
     <t>2016-02-20</t>
   </si>
   <si>
-    <t>2016-05-30</t>
-  </si>
-  <si>
     <t>HGMB16</t>
   </si>
   <si>
@@ -3367,12 +3367,12 @@
     <t>Iraq Mosul Flash Appeal 2016</t>
   </si>
   <si>
+    <t>2016-10-01</t>
+  </si>
+  <si>
     <t>2016-07-20</t>
   </si>
   <si>
-    <t>2016-10-01</t>
-  </si>
-  <si>
     <t>HMMR16</t>
   </si>
   <si>
@@ -3463,12 +3463,12 @@
     <t>Zimbabwe Humanitarian Response Plan 2016</t>
   </si>
   <si>
+    <t>2017-03-31</t>
+  </si>
+  <si>
     <t>2016-04-01</t>
   </si>
   <si>
-    <t>2017-03-31</t>
-  </si>
-  <si>
     <t>HAFG15</t>
   </si>
   <si>
@@ -3481,12 +3481,12 @@
     <t>2015</t>
   </si>
   <si>
+    <t>2015-12-31</t>
+  </si>
+  <si>
     <t>2015-01-01</t>
   </si>
   <si>
-    <t>2015-12-31</t>
-  </si>
-  <si>
     <t>HBFA15</t>
   </si>
   <si>
@@ -3541,12 +3541,12 @@
     <t>Guatemala Plan de Respuesta Sequia 2015</t>
   </si>
   <si>
+    <t>2015-09-30</t>
+  </si>
+  <si>
     <t>2014-11-03</t>
   </si>
   <si>
-    <t>2015-09-30</t>
-  </si>
-  <si>
     <t>FHTI15</t>
   </si>
   <si>
@@ -3571,12 +3571,12 @@
     <t>Vanuatu Emergency Response Plan for Tropical Cyclone PAM 2015</t>
   </si>
   <si>
+    <t>2015-10-31</t>
+  </si>
+  <si>
     <t>2015-03-24</t>
   </si>
   <si>
-    <t>2015-10-31</t>
-  </si>
-  <si>
     <t>HIRQ15</t>
   </si>
   <si>
@@ -3589,12 +3589,12 @@
     <t>Libya Humanitarian Appeal 2014- 2015</t>
   </si>
   <si>
+    <t>2015-05-31</t>
+  </si>
+  <si>
     <t>2014-10-01</t>
   </si>
   <si>
-    <t>2015-05-31</t>
-  </si>
-  <si>
     <t>HMLI15</t>
   </si>
   <si>
@@ -3712,12 +3712,12 @@
     <t>2014</t>
   </si>
   <si>
+    <t>2014-12-31</t>
+  </si>
+  <si>
     <t>2014-01-01</t>
   </si>
   <si>
-    <t>2014-12-31</t>
-  </si>
-  <si>
     <t>HBFA1314</t>
   </si>
   <si>
@@ -3853,24 +3853,24 @@
     <t>Philippines Bohol Earthquake Flash Appeal 2014</t>
   </si>
   <si>
+    <t>2014-04-22</t>
+  </si>
+  <si>
     <t>2013-10-22</t>
   </si>
   <si>
-    <t>2014-04-22</t>
-  </si>
-  <si>
     <t>SPHL1314</t>
   </si>
   <si>
     <t>Philippines Typhoon Haiyan Strategic Response Plan 2014</t>
   </si>
   <si>
+    <t>2014-11-07</t>
+  </si>
+  <si>
     <t>2013-11-08</t>
   </si>
   <si>
-    <t>2014-11-07</t>
-  </si>
-  <si>
     <t>HPHL1314</t>
   </si>
   <si>
@@ -3886,12 +3886,12 @@
     <t>Philippines Zamboanga Crisis Flash Appeal 2014</t>
   </si>
   <si>
+    <t>2014-08-31</t>
+  </si>
+  <si>
     <t>2013-10-01</t>
   </si>
   <si>
-    <t>2014-08-31</t>
-  </si>
-  <si>
     <t>SCOD14</t>
   </si>
   <si>
@@ -4165,12 +4165,12 @@
     <t>2012</t>
   </si>
   <si>
+    <t>2012-12-31</t>
+  </si>
+  <si>
     <t>2012-01-01</t>
   </si>
   <si>
-    <t>2012-12-31</t>
-  </si>
-  <si>
     <t>CAFG1112</t>
   </si>
   <si>
@@ -4240,12 +4240,12 @@
     <t>Lesotho Food Insecurity (September 2012 - March 2013)</t>
   </si>
   <si>
+    <t>2013-03-25</t>
+  </si>
+  <si>
     <t>2012-09-18</t>
   </si>
   <si>
-    <t>2013-03-25</t>
-  </si>
-  <si>
     <t>CLBR12</t>
   </si>
   <si>
@@ -4318,12 +4318,12 @@
     <t>Syria Humanitarian Assistance Response Plan (SHARP) 2012</t>
   </si>
   <si>
+    <t>2012-12-05</t>
+  </si>
+  <si>
     <t>2012-06-05</t>
   </si>
   <si>
-    <t>2012-12-05</t>
-  </si>
-  <si>
     <t>CYEM12</t>
   </si>
   <si>
@@ -4396,12 +4396,12 @@
     <t>El Salvador Flash Appeal (October 2011 - April 2012)</t>
   </si>
   <si>
+    <t>2012-04-25</t>
+  </si>
+  <si>
     <t>2011-10-25</t>
   </si>
   <si>
-    <t>2012-04-25</t>
-  </si>
-  <si>
     <t>CHTI1011</t>
   </si>
   <si>
@@ -4432,24 +4432,24 @@
     <t>Namibia Flash Appeal (April - October 2011)</t>
   </si>
   <si>
+    <t>2011-10-11</t>
+  </si>
+  <si>
     <t>2011-04-11</t>
   </si>
   <si>
-    <t>2011-10-11</t>
-  </si>
-  <si>
     <t>FNIC1112</t>
   </si>
   <si>
     <t>Nicaragua Flash Appeal (October 2011 - April 2012)</t>
   </si>
   <si>
+    <t>2012-04-26</t>
+  </si>
+  <si>
     <t>2011-10-27</t>
   </si>
   <si>
-    <t>2012-04-26</t>
-  </si>
-  <si>
     <t>CNER11</t>
   </si>
   <si>
@@ -4462,12 +4462,12 @@
     <t>Pakistan Rapid Response Plan Floods 2011 (September - March 2012)</t>
   </si>
   <si>
+    <t>2012-06-30</t>
+  </si>
+  <si>
     <t>2011-09-15</t>
   </si>
   <si>
-    <t>2012-06-30</t>
-  </si>
-  <si>
     <t>FXLBYREG11</t>
   </si>
   <si>
@@ -4546,24 +4546,24 @@
     <t>2010</t>
   </si>
   <si>
+    <t>2010-12-31</t>
+  </si>
+  <si>
     <t>2010-01-01</t>
   </si>
   <si>
-    <t>2010-12-31</t>
-  </si>
-  <si>
     <t>OBFA1011</t>
   </si>
   <si>
     <t>Burkina Faso Emergency Humanitarian Action Plan 2010</t>
   </si>
   <si>
+    <t>2011-01-31</t>
+  </si>
+  <si>
     <t>2010-08-01</t>
   </si>
   <si>
-    <t>2011-01-31</t>
-  </si>
-  <si>
     <t>CCAF10</t>
   </si>
   <si>
@@ -4588,36 +4588,36 @@
     <t>El Salvador Flash Appeal (Revised) (November 2009 - May 2010)</t>
   </si>
   <si>
+    <t>2010-05-31</t>
+  </si>
+  <si>
     <t>2009-11-01</t>
   </si>
   <si>
-    <t>2010-05-31</t>
-  </si>
-  <si>
     <t>FGTM10</t>
   </si>
   <si>
     <t>Guatemala Flash Appeal (Revised) (June - December 2010)</t>
   </si>
   <si>
+    <t>2010-12-09</t>
+  </si>
+  <si>
     <t>2010-06-10</t>
   </si>
   <si>
-    <t>2010-12-09</t>
-  </si>
-  <si>
     <t>CGTM10</t>
   </si>
   <si>
     <t>Guatemala Food Insecurity and Acute Malnutrition Appeal 2010</t>
   </si>
   <si>
+    <t>2010-08-11</t>
+  </si>
+  <si>
     <t>2010-02-12</t>
   </si>
   <si>
-    <t>2010-08-11</t>
-  </si>
-  <si>
     <t>FHTI10</t>
   </si>
   <si>
@@ -4648,12 +4648,12 @@
     <t>Kyrgyzstan Flash Appeal (Revised) (June 2010 - June 2011)</t>
   </si>
   <si>
+    <t>2011-06-30</t>
+  </si>
+  <si>
     <t>2010-06-01</t>
   </si>
   <si>
-    <t>2011-06-30</t>
-  </si>
-  <si>
     <t>CMNG1011</t>
   </si>
   <si>
@@ -4768,24 +4768,24 @@
     <t>2009</t>
   </si>
   <si>
+    <t>2009-12-31</t>
+  </si>
+  <si>
     <t>2009-01-01</t>
   </si>
   <si>
-    <t>2009-12-31</t>
-  </si>
-  <si>
     <t>FBFA0910</t>
   </si>
   <si>
     <t>Burkina Faso Flash Appeal (September 2009 - February 2010)</t>
   </si>
   <si>
+    <t>2010-03-09</t>
+  </si>
+  <si>
     <t>2009-09-10</t>
   </si>
   <si>
-    <t>2010-03-09</t>
-  </si>
-  <si>
     <t>CCAF09</t>
   </si>
   <si>
@@ -4852,24 +4852,24 @@
     <t>Madagascar Flash Appeal (Revised) (April - October 2009)</t>
   </si>
   <si>
+    <t>2009-10-31</t>
+  </si>
+  <si>
     <t>2009-04-01</t>
   </si>
   <si>
-    <t>2009-10-31</t>
-  </si>
-  <si>
     <t>FNAM09</t>
   </si>
   <si>
     <t>Namibia Flash Appeal (Revised) (March - November 2009)</t>
   </si>
   <si>
+    <t>2009-09-30</t>
+  </si>
+  <si>
     <t>2009-03-20</t>
   </si>
   <si>
-    <t>2009-09-30</t>
-  </si>
-  <si>
     <t>ONPL09</t>
   </si>
   <si>
@@ -4891,12 +4891,12 @@
     <t>Philippines Flash Appeal (Revised) (October 2009 - March 2010)</t>
   </si>
   <si>
+    <t>2010-03-31</t>
+  </si>
+  <si>
     <t>2009-10-03</t>
   </si>
   <si>
-    <t>2010-03-31</t>
-  </si>
-  <si>
     <t>CSOM09</t>
   </si>
   <si>
@@ -4921,12 +4921,12 @@
     <t>Syria Drought Response Plan (Revised) (July 2009 - June 2010)</t>
   </si>
   <si>
+    <t>2010-06-14</t>
+  </si>
+  <si>
     <t>2009-07-15</t>
   </si>
   <si>
-    <t>2010-06-14</t>
-  </si>
-  <si>
     <t>OTJK09</t>
   </si>
   <si>
@@ -4990,24 +4990,24 @@
     <t>2008</t>
   </si>
   <si>
+    <t>2008-06-30</t>
+  </si>
+  <si>
     <t>2008-02-01</t>
   </si>
   <si>
-    <t>2008-06-30</t>
-  </si>
-  <si>
     <t>OAFG0809</t>
   </si>
   <si>
     <t>Afghanistan Joint Emergency Appeal 2008: High Food Price and Drought Crisis (July 2008 - June 2009)</t>
   </si>
   <si>
+    <t>2009-06-30</t>
+  </si>
+  <si>
     <t>2008-07-01</t>
   </si>
   <si>
-    <t>2009-06-30</t>
-  </si>
-  <si>
     <t>FBOL08</t>
   </si>
   <si>
@@ -5023,12 +5023,12 @@
     <t>Central African Republic 2008</t>
   </si>
   <si>
+    <t>2008-12-31</t>
+  </si>
+  <si>
     <t>2008-01-01</t>
   </si>
   <si>
-    <t>2008-12-31</t>
-  </si>
-  <si>
     <t>CTCD08</t>
   </si>
   <si>
@@ -5059,24 +5059,24 @@
     <t>Djibouti Joint Appeal 2008: Response Plan for Drought, Food and Nutrition Crisis</t>
   </si>
   <si>
+    <t>2009-02-28</t>
+  </si>
+  <si>
     <t>2008-08-01</t>
   </si>
   <si>
-    <t>2009-02-28</t>
-  </si>
-  <si>
     <t>FGEO0809</t>
   </si>
   <si>
     <t>Georgia Crisis Flash Appeal (Revised) 2008</t>
   </si>
   <si>
+    <t>2009-02-09</t>
+  </si>
+  <si>
     <t>2008-08-09</t>
   </si>
   <si>
-    <t>2009-02-09</t>
-  </si>
-  <si>
     <t>FHTI0809</t>
   </si>
   <si>
@@ -5092,12 +5092,12 @@
     <t>Honduras Flash Appeal (Updated) (November - April) 2008</t>
   </si>
   <si>
+    <t>2009-04-30</t>
+  </si>
+  <si>
     <t>2008-11-01</t>
   </si>
   <si>
-    <t>2009-04-30</t>
-  </si>
-  <si>
     <t>CIRQ08</t>
   </si>
   <si>
@@ -5116,12 +5116,12 @@
     <t>Kyrgyzstan Flash Appeal (Revised) 2008</t>
   </si>
   <si>
+    <t>2009-05-31</t>
+  </si>
+  <si>
     <t>2008-12-01</t>
   </si>
   <si>
-    <t>2009-05-31</t>
-  </si>
-  <si>
     <t>OLAO0809</t>
   </si>
   <si>
@@ -5155,12 +5155,12 @@
     <t>Myanmar Flash Appeal (Revised) 2008</t>
   </si>
   <si>
+    <t>2008-11-30</t>
+  </si>
+  <si>
     <t>2008-05-01</t>
   </si>
   <si>
-    <t>2008-11-30</t>
-  </si>
-  <si>
     <t>ONPL08</t>
   </si>
   <si>
@@ -5263,36 +5263,36 @@
     <t>2007</t>
   </si>
   <si>
+    <t>2007-08-21</t>
+  </si>
+  <si>
     <t>2007-02-22</t>
   </si>
   <si>
-    <t>2007-08-21</t>
-  </si>
-  <si>
     <t>FBFA0708</t>
   </si>
   <si>
     <t>Burkina Faso Floods Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2008-01-31</t>
+  </si>
+  <si>
     <t>2007-11-01</t>
   </si>
   <si>
-    <t>2008-01-31</t>
-  </si>
-  <si>
     <t>CBDI07</t>
   </si>
   <si>
     <t>Burundi 2007</t>
   </si>
   <si>
+    <t>2007-12-31</t>
+  </si>
+  <si>
     <t>2007-01-01</t>
   </si>
   <si>
-    <t>2007-12-31</t>
-  </si>
-  <si>
     <t>CCAF07</t>
   </si>
   <si>
@@ -5332,12 +5332,12 @@
     <t>Ghana Floods Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2008-03-31</t>
+  </si>
+  <si>
     <t>2007-09-01</t>
   </si>
   <si>
-    <t>2008-03-31</t>
-  </si>
-  <si>
     <t>CXGLR07</t>
   </si>
   <si>
@@ -5359,36 +5359,36 @@
     <t>Korea DPR Flash Appeal: Floods Emergency 2007</t>
   </si>
   <si>
+    <t>2007-11-30</t>
+  </si>
+  <si>
     <t>2007-08-28</t>
   </si>
   <si>
-    <t>2007-11-30</t>
-  </si>
-  <si>
     <t>OLBN07</t>
   </si>
   <si>
     <t>Lebanon Crisis Appeal 2007</t>
   </si>
   <si>
+    <t>2007-09-03</t>
+  </si>
+  <si>
     <t>2007-06-04</t>
   </si>
   <si>
-    <t>2007-09-03</t>
-  </si>
-  <si>
     <t>FLSO0708</t>
   </si>
   <si>
     <t>Lesotho Drought Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2008-01-28</t>
+  </si>
+  <si>
     <t>2007-07-28</t>
   </si>
   <si>
-    <t>2008-01-28</t>
-  </si>
-  <si>
     <t>CLBR07</t>
   </si>
   <si>
@@ -5401,24 +5401,24 @@
     <t>Madagascar Floods Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2007-09-15</t>
+  </si>
+  <si>
     <t>2007-03-15</t>
   </si>
   <si>
-    <t>2007-09-15</t>
-  </si>
-  <si>
     <t>FMOZ07</t>
   </si>
   <si>
     <t>Mozambique Floods and Cyclone Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2007-06-30</t>
+  </si>
+  <si>
     <t>2007-03-01</t>
   </si>
   <si>
-    <t>2007-06-30</t>
-  </si>
-  <si>
     <t>ONPL07</t>
   </si>
   <si>
@@ -5431,12 +5431,12 @@
     <t>Nicaragua Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2008-02-28</t>
+  </si>
+  <si>
     <t>2007-09-07</t>
   </si>
   <si>
-    <t>2008-02-28</t>
-  </si>
-  <si>
     <t>ORUS07</t>
   </si>
   <si>
@@ -5449,12 +5449,12 @@
     <t>Pakistan Cyclone and Floods Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2007-10-31</t>
+  </si>
+  <si>
     <t>2007-07-15</t>
   </si>
   <si>
-    <t>2007-10-31</t>
-  </si>
-  <si>
     <t>FPER0708</t>
   </si>
   <si>
@@ -5515,12 +5515,12 @@
     <t>Swaziland Drought Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2008-01-20</t>
+  </si>
+  <si>
     <t>2007-07-20</t>
   </si>
   <si>
-    <t>2008-01-20</t>
-  </si>
-  <si>
     <t>CTLS07</t>
   </si>
   <si>
@@ -5575,12 +5575,12 @@
     <t>2006</t>
   </si>
   <si>
+    <t>2006-12-31</t>
+  </si>
+  <si>
     <t>2006-07-01</t>
   </si>
   <si>
-    <t>2006-12-31</t>
-  </si>
-  <si>
     <t>CBDI06</t>
   </si>
   <si>
@@ -5626,24 +5626,24 @@
     <t>Ethiopia Floods Joint Appeal 2006</t>
   </si>
   <si>
+    <t>2006-11-25</t>
+  </si>
+  <si>
     <t>2006-08-25</t>
   </si>
   <si>
-    <t>2006-11-25</t>
-  </si>
-  <si>
     <t>OETH0607</t>
   </si>
   <si>
     <t>Ethiopia: 2006 Govt-UN Joint Emergency Flood Appeal for Somali Region</t>
   </si>
   <si>
+    <t>2007-01-22</t>
+  </si>
+  <si>
     <t>2006-11-23</t>
   </si>
   <si>
-    <t>2007-01-22</t>
-  </si>
-  <si>
     <t>CXGLR06</t>
   </si>
   <si>
@@ -5662,12 +5662,12 @@
     <t>Guinea-Bissau 2006</t>
   </si>
   <si>
+    <t>2006-11-30</t>
+  </si>
+  <si>
     <t>2006-05-01</t>
   </si>
   <si>
-    <t>2006-11-30</t>
-  </si>
-  <si>
     <t>CXHAF06</t>
   </si>
   <si>
@@ -5686,12 +5686,12 @@
     <t>Kenya 2006</t>
   </si>
   <si>
+    <t>2007-04-15</t>
+  </si>
+  <si>
     <t>2006-10-16</t>
   </si>
   <si>
-    <t>2007-04-15</t>
-  </si>
-  <si>
     <t>FKEN06</t>
   </si>
   <si>
@@ -5707,12 +5707,12 @@
     <t>Lebanon Crisis 2006</t>
   </si>
   <si>
+    <t>2006-10-23</t>
+  </si>
+  <si>
     <t>2006-07-24</t>
   </si>
   <si>
-    <t>2006-10-23</t>
-  </si>
-  <si>
     <t>CLBR06</t>
   </si>
   <si>
@@ -5761,12 +5761,12 @@
     <t>Somalia: 2006 Flood Response Plan</t>
   </si>
   <si>
+    <t>2007-03-05</t>
+  </si>
+  <si>
     <t>2006-12-05</t>
   </si>
   <si>
-    <t>2007-03-05</t>
-  </si>
-  <si>
     <t>OLKA06</t>
   </si>
   <si>
@@ -5833,36 +5833,36 @@
     <t>2005</t>
   </si>
   <si>
+    <t>2005-06-30</t>
+  </si>
+  <si>
     <t>2005-04-01</t>
   </si>
   <si>
-    <t>2005-06-30</t>
-  </si>
-  <si>
     <t>FBEN05</t>
   </si>
   <si>
     <t>Benin 2005</t>
   </si>
   <si>
+    <t>2005-10-31</t>
+  </si>
+  <si>
     <t>2005-05-01</t>
   </si>
   <si>
-    <t>2005-10-31</t>
-  </si>
-  <si>
     <t>CBDI05</t>
   </si>
   <si>
     <t>Burundi 2005</t>
   </si>
   <si>
+    <t>2005-12-31</t>
+  </si>
+  <si>
     <t>2005-01-01</t>
   </si>
   <si>
-    <t>2005-12-31</t>
-  </si>
-  <si>
     <t>CCAF05</t>
   </si>
   <si>
@@ -5944,12 +5944,12 @@
     <t>Guyana 2005</t>
   </si>
   <si>
+    <t>2005-08-01</t>
+  </si>
+  <si>
     <t>2005-02-01</t>
   </si>
   <si>
-    <t>2005-08-01</t>
-  </si>
-  <si>
     <t>FXINDTSU05</t>
   </si>
   <si>
@@ -5968,12 +5968,12 @@
     <t>Niger 2005</t>
   </si>
   <si>
+    <t>2005-09-30</t>
+  </si>
+  <si>
     <t>2005-06-01</t>
   </si>
   <si>
-    <t>2005-09-30</t>
-  </si>
-  <si>
     <t>CCOG05</t>
   </si>
   <si>
@@ -5992,12 +5992,12 @@
     <t>West and Central Africa Region Cholera 2005</t>
   </si>
   <si>
+    <t>2006-05-31</t>
+  </si>
+  <si>
     <t>2005-11-01</t>
   </si>
   <si>
-    <t>2006-05-31</t>
-  </si>
-  <si>
     <t>OSDN05</t>
   </si>
   <si>
@@ -6010,12 +6010,12 @@
     <t>South Asia Earthquake 2005</t>
   </si>
   <si>
+    <t>2006-04-10</t>
+  </si>
+  <si>
     <t>2005-10-11</t>
   </si>
   <si>
-    <t>2006-04-10</t>
-  </si>
-  <si>
     <t>CSDN05</t>
   </si>
   <si>
@@ -6049,12 +6049,12 @@
     <t>2004</t>
   </si>
   <si>
+    <t>2004-12-31</t>
+  </si>
+  <si>
     <t>2004-09-01</t>
   </si>
   <si>
-    <t>2004-12-31</t>
-  </si>
-  <si>
     <t>CAGO04</t>
   </si>
   <si>
@@ -6070,24 +6070,24 @@
     <t>Bangladesh 2004</t>
   </si>
   <si>
+    <t>2005-01-31</t>
+  </si>
+  <si>
     <t>2004-08-01</t>
   </si>
   <si>
-    <t>2005-01-31</t>
-  </si>
-  <si>
     <t>FBOL0405</t>
   </si>
   <si>
     <t>Bolivia 2004</t>
   </si>
   <si>
+    <t>2005-05-31</t>
+  </si>
+  <si>
     <t>2004-11-01</t>
   </si>
   <si>
-    <t>2005-05-31</t>
-  </si>
-  <si>
     <t>CBDI04</t>
   </si>
   <si>
@@ -6220,24 +6220,24 @@
     <t>Madagascar 2004</t>
   </si>
   <si>
+    <t>2004-06-19</t>
+  </si>
+  <si>
     <t>2004-03-19</t>
   </si>
   <si>
-    <t>2004-06-19</t>
-  </si>
-  <si>
     <t>FPHL0405</t>
   </si>
   <si>
     <t>Philippines 2004</t>
   </si>
   <si>
+    <t>2005-03-15</t>
+  </si>
+  <si>
     <t>2004-12-15</t>
   </si>
   <si>
-    <t>2005-03-15</t>
-  </si>
-  <si>
     <t>CSLE04</t>
   </si>
   <si>
@@ -6298,12 +6298,12 @@
     <t>2003</t>
   </si>
   <si>
+    <t>2003-12-31</t>
+  </si>
+  <si>
     <t>2003-01-01</t>
   </si>
   <si>
-    <t>2003-12-31</t>
-  </si>
-  <si>
     <t>CAGO03</t>
   </si>
   <si>
@@ -6325,12 +6325,12 @@
     <t>Central African Republic 2003</t>
   </si>
   <si>
+    <t>2003-06-30</t>
+  </si>
+  <si>
     <t>2003-04-01</t>
   </si>
   <si>
-    <t>2003-06-30</t>
-  </si>
-  <si>
     <t>CRUS03</t>
   </si>
   <si>
@@ -6355,12 +6355,12 @@
     <t>Côte d'Ivoire and the West Africa Sub-Region 2002-2003</t>
   </si>
   <si>
+    <t>2003-01-31</t>
+  </si>
+  <si>
     <t>2002-11-01</t>
   </si>
   <si>
-    <t>2003-01-31</t>
-  </si>
-  <si>
     <t>CCIV03</t>
   </si>
   <si>
@@ -6406,24 +6406,24 @@
     <t>Haiti (PIR) 2003</t>
   </si>
   <si>
+    <t>2003-08-31</t>
+  </si>
+  <si>
     <t>2003-03-01</t>
   </si>
   <si>
-    <t>2003-08-31</t>
-  </si>
-  <si>
     <t>CLSO0304</t>
   </si>
   <si>
     <t>Humanitarian Crisis in Southern Africa - LESOTHO (July 2003 - June 2004)</t>
   </si>
   <si>
+    <t>2004-06-30</t>
+  </si>
+  <si>
     <t>2003-07-01</t>
   </si>
   <si>
-    <t>2004-06-30</t>
-  </si>
-  <si>
     <t>CMWI03</t>
   </si>
   <si>
@@ -6535,12 +6535,12 @@
     <t>2002</t>
   </si>
   <si>
+    <t>2002-12-31</t>
+  </si>
+  <si>
     <t>2001-10-01</t>
   </si>
   <si>
-    <t>2002-12-31</t>
-  </si>
-  <si>
     <t>CAGO02</t>
   </si>
   <si>
@@ -6727,12 +6727,12 @@
     <t>2001</t>
   </si>
   <si>
+    <t>2001-09-30</t>
+  </si>
+  <si>
     <t>2001-01-01</t>
   </si>
   <si>
-    <t>2001-09-30</t>
-  </si>
-  <si>
     <t>CAGO01</t>
   </si>
   <si>
@@ -6880,10 +6880,10 @@
     <t>2000</t>
   </si>
   <si>
+    <t>2000-12-31</t>
+  </si>
+  <si>
     <t>2000-01-01</t>
-  </si>
-  <si>
-    <t>2000-12-31</t>
   </si>
   <si>
     <t>CBDI00</t>
@@ -7576,10 +7576,10 @@
         <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G11" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -7737,10 +7737,10 @@
         <v>11</v>
       </c>
       <c r="F18" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="G18" t="s">
-        <v>52</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -7921,10 +7921,10 @@
         <v>11</v>
       </c>
       <c r="F26" t="s">
+        <v>52</v>
+      </c>
+      <c r="G26" t="s">
         <v>69</v>
-      </c>
-      <c r="G26" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -8151,10 +8151,10 @@
         <v>11</v>
       </c>
       <c r="F36" t="s">
-        <v>12</v>
+        <v>90</v>
       </c>
       <c r="G36" t="s">
-        <v>90</v>
+        <v>13</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -8243,10 +8243,10 @@
         <v>95</v>
       </c>
       <c r="F40" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="G40" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -8335,10 +8335,10 @@
         <v>95</v>
       </c>
       <c r="F44" t="s">
+        <v>96</v>
+      </c>
+      <c r="G44" t="s">
         <v>112</v>
-      </c>
-      <c r="G44" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -8496,10 +8496,10 @@
         <v>95</v>
       </c>
       <c r="F51" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="G51" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -8519,10 +8519,10 @@
         <v>95</v>
       </c>
       <c r="F52" t="s">
-        <v>96</v>
+        <v>129</v>
       </c>
       <c r="G52" t="s">
-        <v>129</v>
+        <v>97</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -8565,10 +8565,10 @@
         <v>95</v>
       </c>
       <c r="F54" t="s">
-        <v>96</v>
+        <v>134</v>
       </c>
       <c r="G54" t="s">
-        <v>134</v>
+        <v>97</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -8611,10 +8611,10 @@
         <v>95</v>
       </c>
       <c r="F56" t="s">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="G56" t="s">
-        <v>139</v>
+        <v>97</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -8634,10 +8634,10 @@
         <v>95</v>
       </c>
       <c r="F57" t="s">
+        <v>96</v>
+      </c>
+      <c r="G57" t="s">
         <v>142</v>
-      </c>
-      <c r="G57" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -8726,10 +8726,10 @@
         <v>95</v>
       </c>
       <c r="F61" t="s">
+        <v>96</v>
+      </c>
+      <c r="G61" t="s">
         <v>151</v>
-      </c>
-      <c r="G61" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -8749,10 +8749,10 @@
         <v>95</v>
       </c>
       <c r="F62" t="s">
-        <v>96</v>
+        <v>154</v>
       </c>
       <c r="G62" t="s">
-        <v>154</v>
+        <v>97</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -8979,10 +8979,10 @@
         <v>95</v>
       </c>
       <c r="F72" t="s">
+        <v>96</v>
+      </c>
+      <c r="G72" t="s">
         <v>175</v>
-      </c>
-      <c r="G72" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -9163,10 +9163,10 @@
         <v>95</v>
       </c>
       <c r="F80" t="s">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="G80" t="s">
-        <v>139</v>
+        <v>97</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -9186,10 +9186,10 @@
         <v>95</v>
       </c>
       <c r="F81" t="s">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="G81" t="s">
-        <v>139</v>
+        <v>97</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -9209,10 +9209,10 @@
         <v>95</v>
       </c>
       <c r="F82" t="s">
+        <v>96</v>
+      </c>
+      <c r="G82" t="s">
         <v>195</v>
-      </c>
-      <c r="G82" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -9255,10 +9255,10 @@
         <v>95</v>
       </c>
       <c r="F84" t="s">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="G84" t="s">
-        <v>139</v>
+        <v>97</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -9278,10 +9278,10 @@
         <v>95</v>
       </c>
       <c r="F85" t="s">
-        <v>96</v>
+        <v>129</v>
       </c>
       <c r="G85" t="s">
-        <v>129</v>
+        <v>97</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -9347,10 +9347,10 @@
         <v>204</v>
       </c>
       <c r="F88" t="s">
+        <v>205</v>
+      </c>
+      <c r="G88" t="s">
         <v>211</v>
-      </c>
-      <c r="G88" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -9393,10 +9393,10 @@
         <v>204</v>
       </c>
       <c r="F90" t="s">
+        <v>205</v>
+      </c>
+      <c r="G90" t="s">
         <v>216</v>
-      </c>
-      <c r="G90" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -9554,10 +9554,10 @@
         <v>204</v>
       </c>
       <c r="F97" t="s">
+        <v>205</v>
+      </c>
+      <c r="G97" t="s">
         <v>231</v>
-      </c>
-      <c r="G97" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -9646,10 +9646,10 @@
         <v>204</v>
       </c>
       <c r="F101" t="s">
+        <v>205</v>
+      </c>
+      <c r="G101" t="s">
         <v>240</v>
-      </c>
-      <c r="G101" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -9669,10 +9669,10 @@
         <v>204</v>
       </c>
       <c r="F102" t="s">
+        <v>205</v>
+      </c>
+      <c r="G102" t="s">
         <v>240</v>
-      </c>
-      <c r="G102" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -9692,10 +9692,10 @@
         <v>204</v>
       </c>
       <c r="F103" t="s">
-        <v>205</v>
+        <v>245</v>
       </c>
       <c r="G103" t="s">
-        <v>245</v>
+        <v>206</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -9715,10 +9715,10 @@
         <v>204</v>
       </c>
       <c r="F104" t="s">
-        <v>205</v>
+        <v>248</v>
       </c>
       <c r="G104" t="s">
-        <v>248</v>
+        <v>206</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -9738,10 +9738,10 @@
         <v>204</v>
       </c>
       <c r="F105" t="s">
+        <v>205</v>
+      </c>
+      <c r="G105" t="s">
         <v>251</v>
-      </c>
-      <c r="G105" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -9784,10 +9784,10 @@
         <v>204</v>
       </c>
       <c r="F107" t="s">
+        <v>248</v>
+      </c>
+      <c r="G107" t="s">
         <v>256</v>
-      </c>
-      <c r="G107" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -9807,10 +9807,10 @@
         <v>204</v>
       </c>
       <c r="F108" t="s">
+        <v>205</v>
+      </c>
+      <c r="G108" t="s">
         <v>259</v>
-      </c>
-      <c r="G108" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -9876,10 +9876,10 @@
         <v>204</v>
       </c>
       <c r="F111" t="s">
+        <v>205</v>
+      </c>
+      <c r="G111" t="s">
         <v>266</v>
-      </c>
-      <c r="G111" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -9945,10 +9945,10 @@
         <v>204</v>
       </c>
       <c r="F114" t="s">
+        <v>205</v>
+      </c>
+      <c r="G114" t="s">
         <v>273</v>
-      </c>
-      <c r="G114" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -10083,10 +10083,10 @@
         <v>204</v>
       </c>
       <c r="F120" t="s">
+        <v>205</v>
+      </c>
+      <c r="G120" t="s">
         <v>231</v>
-      </c>
-      <c r="G120" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -10382,10 +10382,10 @@
         <v>204</v>
       </c>
       <c r="F133" t="s">
+        <v>205</v>
+      </c>
+      <c r="G133" t="s">
         <v>312</v>
-      </c>
-      <c r="G133" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -10428,10 +10428,10 @@
         <v>204</v>
       </c>
       <c r="F135" t="s">
+        <v>205</v>
+      </c>
+      <c r="G135" t="s">
         <v>317</v>
-      </c>
-      <c r="G135" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -10451,10 +10451,10 @@
         <v>204</v>
       </c>
       <c r="F136" t="s">
+        <v>205</v>
+      </c>
+      <c r="G136" t="s">
         <v>317</v>
-      </c>
-      <c r="G136" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -10658,10 +10658,10 @@
         <v>322</v>
       </c>
       <c r="F145" t="s">
+        <v>323</v>
+      </c>
+      <c r="G145" t="s">
         <v>341</v>
-      </c>
-      <c r="G145" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -10842,10 +10842,10 @@
         <v>322</v>
       </c>
       <c r="F153" t="s">
+        <v>323</v>
+      </c>
+      <c r="G153" t="s">
         <v>358</v>
-      </c>
-      <c r="G153" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -11049,10 +11049,10 @@
         <v>322</v>
       </c>
       <c r="F162" t="s">
-        <v>323</v>
+        <v>369</v>
       </c>
       <c r="G162" t="s">
-        <v>370</v>
+        <v>324</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -11072,10 +11072,10 @@
         <v>322</v>
       </c>
       <c r="F163" t="s">
-        <v>323</v>
+        <v>365</v>
       </c>
       <c r="G163" t="s">
-        <v>366</v>
+        <v>324</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -11325,10 +11325,10 @@
         <v>322</v>
       </c>
       <c r="F174" t="s">
+        <v>365</v>
+      </c>
+      <c r="G174" t="s">
         <v>406</v>
-      </c>
-      <c r="G174" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -11371,10 +11371,10 @@
         <v>322</v>
       </c>
       <c r="F176" t="s">
+        <v>365</v>
+      </c>
+      <c r="G176" t="s">
         <v>411</v>
-      </c>
-      <c r="G176" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -11854,10 +11854,10 @@
         <v>428</v>
       </c>
       <c r="F197" t="s">
-        <v>457</v>
+        <v>429</v>
       </c>
       <c r="G197" t="s">
-        <v>430</v>
+        <v>458</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -11946,10 +11946,10 @@
         <v>428</v>
       </c>
       <c r="F201" t="s">
-        <v>429</v>
+        <v>469</v>
       </c>
       <c r="G201" t="s">
-        <v>469</v>
+        <v>430</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -12222,10 +12222,10 @@
         <v>428</v>
       </c>
       <c r="F213" t="s">
+        <v>429</v>
+      </c>
+      <c r="G213" t="s">
         <v>498</v>
-      </c>
-      <c r="G213" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -12245,10 +12245,10 @@
         <v>428</v>
       </c>
       <c r="F214" t="s">
+        <v>500</v>
+      </c>
+      <c r="G214" t="s">
         <v>498</v>
-      </c>
-      <c r="G214" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -12452,10 +12452,10 @@
         <v>428</v>
       </c>
       <c r="F223" t="s">
+        <v>429</v>
+      </c>
+      <c r="G223" t="s">
         <v>521</v>
-      </c>
-      <c r="G223" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -12567,10 +12567,10 @@
         <v>428</v>
       </c>
       <c r="F228" t="s">
+        <v>429</v>
+      </c>
+      <c r="G228" t="s">
         <v>532</v>
-      </c>
-      <c r="G228" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -12613,10 +12613,10 @@
         <v>428</v>
       </c>
       <c r="F230" t="s">
+        <v>537</v>
+      </c>
+      <c r="G230" t="s">
         <v>532</v>
-      </c>
-      <c r="G230" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -12705,10 +12705,10 @@
         <v>544</v>
       </c>
       <c r="F234" t="s">
+        <v>545</v>
+      </c>
+      <c r="G234" t="s">
         <v>549</v>
-      </c>
-      <c r="G234" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -12728,10 +12728,10 @@
         <v>544</v>
       </c>
       <c r="F235" t="s">
+        <v>545</v>
+      </c>
+      <c r="G235" t="s">
         <v>549</v>
-      </c>
-      <c r="G235" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -12751,10 +12751,10 @@
         <v>544</v>
       </c>
       <c r="F236" t="s">
+        <v>545</v>
+      </c>
+      <c r="G236" t="s">
         <v>549</v>
-      </c>
-      <c r="G236" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="237" spans="1:7">
@@ -12774,10 +12774,10 @@
         <v>544</v>
       </c>
       <c r="F237" t="s">
+        <v>545</v>
+      </c>
+      <c r="G237" t="s">
         <v>549</v>
-      </c>
-      <c r="G237" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="238" spans="1:7">
@@ -12797,10 +12797,10 @@
         <v>544</v>
       </c>
       <c r="F238" t="s">
+        <v>545</v>
+      </c>
+      <c r="G238" t="s">
         <v>549</v>
-      </c>
-      <c r="G238" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="239" spans="1:7">
@@ -12820,10 +12820,10 @@
         <v>544</v>
       </c>
       <c r="F239" t="s">
+        <v>545</v>
+      </c>
+      <c r="G239" t="s">
         <v>549</v>
-      </c>
-      <c r="G239" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="240" spans="1:7">
@@ -12843,10 +12843,10 @@
         <v>544</v>
       </c>
       <c r="F240" t="s">
+        <v>545</v>
+      </c>
+      <c r="G240" t="s">
         <v>549</v>
-      </c>
-      <c r="G240" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="241" spans="1:7">
@@ -12866,10 +12866,10 @@
         <v>544</v>
       </c>
       <c r="F241" t="s">
+        <v>545</v>
+      </c>
+      <c r="G241" t="s">
         <v>549</v>
-      </c>
-      <c r="G241" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="242" spans="1:7">
@@ -12889,10 +12889,10 @@
         <v>544</v>
       </c>
       <c r="F242" t="s">
+        <v>545</v>
+      </c>
+      <c r="G242" t="s">
         <v>549</v>
-      </c>
-      <c r="G242" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="243" spans="1:7">
@@ -12912,10 +12912,10 @@
         <v>544</v>
       </c>
       <c r="F243" t="s">
+        <v>545</v>
+      </c>
+      <c r="G243" t="s">
         <v>549</v>
-      </c>
-      <c r="G243" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="244" spans="1:7">
@@ -12935,10 +12935,10 @@
         <v>544</v>
       </c>
       <c r="F244" t="s">
+        <v>545</v>
+      </c>
+      <c r="G244" t="s">
         <v>549</v>
-      </c>
-      <c r="G244" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="245" spans="1:7">
@@ -12958,10 +12958,10 @@
         <v>544</v>
       </c>
       <c r="F245" t="s">
+        <v>545</v>
+      </c>
+      <c r="G245" t="s">
         <v>572</v>
-      </c>
-      <c r="G245" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="246" spans="1:7">
@@ -12981,10 +12981,10 @@
         <v>544</v>
       </c>
       <c r="F246" t="s">
+        <v>429</v>
+      </c>
+      <c r="G246" t="s">
         <v>572</v>
-      </c>
-      <c r="G246" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -13027,10 +13027,10 @@
         <v>544</v>
       </c>
       <c r="F248" t="s">
+        <v>545</v>
+      </c>
+      <c r="G248" t="s">
         <v>549</v>
-      </c>
-      <c r="G248" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="249" spans="1:7">
@@ -13050,10 +13050,10 @@
         <v>544</v>
       </c>
       <c r="F249" t="s">
+        <v>545</v>
+      </c>
+      <c r="G249" t="s">
         <v>572</v>
-      </c>
-      <c r="G249" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="250" spans="1:7">
@@ -13073,10 +13073,10 @@
         <v>544</v>
       </c>
       <c r="F250" t="s">
+        <v>429</v>
+      </c>
+      <c r="G250" t="s">
         <v>572</v>
-      </c>
-      <c r="G250" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="251" spans="1:7">
@@ -13119,10 +13119,10 @@
         <v>544</v>
       </c>
       <c r="F252" t="s">
+        <v>545</v>
+      </c>
+      <c r="G252" t="s">
         <v>549</v>
-      </c>
-      <c r="G252" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="253" spans="1:7">
@@ -13165,10 +13165,10 @@
         <v>544</v>
       </c>
       <c r="F254" t="s">
+        <v>545</v>
+      </c>
+      <c r="G254" t="s">
         <v>572</v>
-      </c>
-      <c r="G254" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -13188,10 +13188,10 @@
         <v>544</v>
       </c>
       <c r="F255" t="s">
+        <v>429</v>
+      </c>
+      <c r="G255" t="s">
         <v>572</v>
-      </c>
-      <c r="G255" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -13211,10 +13211,10 @@
         <v>544</v>
       </c>
       <c r="F256" t="s">
+        <v>545</v>
+      </c>
+      <c r="G256" t="s">
         <v>549</v>
-      </c>
-      <c r="G256" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="257" spans="1:7">
@@ -13234,10 +13234,10 @@
         <v>544</v>
       </c>
       <c r="F257" t="s">
+        <v>545</v>
+      </c>
+      <c r="G257" t="s">
         <v>603</v>
-      </c>
-      <c r="G257" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="258" spans="1:7">
@@ -13280,10 +13280,10 @@
         <v>544</v>
       </c>
       <c r="F259" t="s">
+        <v>545</v>
+      </c>
+      <c r="G259" t="s">
         <v>549</v>
-      </c>
-      <c r="G259" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="260" spans="1:7">
@@ -13303,10 +13303,10 @@
         <v>544</v>
       </c>
       <c r="F260" t="s">
+        <v>478</v>
+      </c>
+      <c r="G260" t="s">
         <v>549</v>
-      </c>
-      <c r="G260" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="261" spans="1:7">
@@ -13326,10 +13326,10 @@
         <v>544</v>
       </c>
       <c r="F261" t="s">
+        <v>545</v>
+      </c>
+      <c r="G261" t="s">
         <v>549</v>
-      </c>
-      <c r="G261" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="262" spans="1:7">
@@ -13349,10 +13349,10 @@
         <v>544</v>
       </c>
       <c r="F262" t="s">
+        <v>545</v>
+      </c>
+      <c r="G262" t="s">
         <v>549</v>
-      </c>
-      <c r="G262" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="263" spans="1:7">
@@ -13372,10 +13372,10 @@
         <v>544</v>
       </c>
       <c r="F263" t="s">
+        <v>545</v>
+      </c>
+      <c r="G263" t="s">
         <v>549</v>
-      </c>
-      <c r="G263" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="264" spans="1:7">
@@ -13395,10 +13395,10 @@
         <v>544</v>
       </c>
       <c r="F264" t="s">
+        <v>545</v>
+      </c>
+      <c r="G264" t="s">
         <v>549</v>
-      </c>
-      <c r="G264" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="265" spans="1:7">
@@ -13418,10 +13418,10 @@
         <v>544</v>
       </c>
       <c r="F265" t="s">
+        <v>545</v>
+      </c>
+      <c r="G265" t="s">
         <v>622</v>
-      </c>
-      <c r="G265" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="266" spans="1:7">
@@ -13441,10 +13441,10 @@
         <v>544</v>
       </c>
       <c r="F266" t="s">
+        <v>545</v>
+      </c>
+      <c r="G266" t="s">
         <v>625</v>
-      </c>
-      <c r="G266" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="267" spans="1:7">
@@ -13464,10 +13464,10 @@
         <v>544</v>
       </c>
       <c r="F267" t="s">
+        <v>545</v>
+      </c>
+      <c r="G267" t="s">
         <v>549</v>
-      </c>
-      <c r="G267" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="268" spans="1:7">
@@ -13487,10 +13487,10 @@
         <v>544</v>
       </c>
       <c r="F268" t="s">
+        <v>545</v>
+      </c>
+      <c r="G268" t="s">
         <v>549</v>
-      </c>
-      <c r="G268" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="269" spans="1:7">
@@ -13510,10 +13510,10 @@
         <v>544</v>
       </c>
       <c r="F269" t="s">
+        <v>545</v>
+      </c>
+      <c r="G269" t="s">
         <v>625</v>
-      </c>
-      <c r="G269" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="270" spans="1:7">
@@ -13533,10 +13533,10 @@
         <v>544</v>
       </c>
       <c r="F270" t="s">
+        <v>545</v>
+      </c>
+      <c r="G270" t="s">
         <v>625</v>
-      </c>
-      <c r="G270" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="271" spans="1:7">
@@ -13556,10 +13556,10 @@
         <v>544</v>
       </c>
       <c r="F271" t="s">
+        <v>545</v>
+      </c>
+      <c r="G271" t="s">
         <v>549</v>
-      </c>
-      <c r="G271" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="272" spans="1:7">
@@ -13579,10 +13579,10 @@
         <v>544</v>
       </c>
       <c r="F272" t="s">
+        <v>545</v>
+      </c>
+      <c r="G272" t="s">
         <v>549</v>
-      </c>
-      <c r="G272" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="273" spans="1:7">
@@ -13602,10 +13602,10 @@
         <v>544</v>
       </c>
       <c r="F273" t="s">
+        <v>545</v>
+      </c>
+      <c r="G273" t="s">
         <v>549</v>
-      </c>
-      <c r="G273" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="274" spans="1:7">
@@ -13625,10 +13625,10 @@
         <v>544</v>
       </c>
       <c r="F274" t="s">
+        <v>545</v>
+      </c>
+      <c r="G274" t="s">
         <v>549</v>
-      </c>
-      <c r="G274" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="275" spans="1:7">
@@ -13648,10 +13648,10 @@
         <v>544</v>
       </c>
       <c r="F275" t="s">
+        <v>545</v>
+      </c>
+      <c r="G275" t="s">
         <v>549</v>
-      </c>
-      <c r="G275" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="276" spans="1:7">
@@ -13671,10 +13671,10 @@
         <v>544</v>
       </c>
       <c r="F276" t="s">
+        <v>545</v>
+      </c>
+      <c r="G276" t="s">
         <v>549</v>
-      </c>
-      <c r="G276" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="277" spans="1:7">
@@ -13694,10 +13694,10 @@
         <v>544</v>
       </c>
       <c r="F277" t="s">
+        <v>545</v>
+      </c>
+      <c r="G277" t="s">
         <v>549</v>
-      </c>
-      <c r="G277" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="278" spans="1:7">
@@ -13717,10 +13717,10 @@
         <v>544</v>
       </c>
       <c r="F278" t="s">
+        <v>545</v>
+      </c>
+      <c r="G278" t="s">
         <v>549</v>
-      </c>
-      <c r="G278" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="279" spans="1:7">
@@ -13740,10 +13740,10 @@
         <v>544</v>
       </c>
       <c r="F279" t="s">
+        <v>545</v>
+      </c>
+      <c r="G279" t="s">
         <v>549</v>
-      </c>
-      <c r="G279" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="280" spans="1:7">
@@ -13763,10 +13763,10 @@
         <v>544</v>
       </c>
       <c r="F280" t="s">
+        <v>545</v>
+      </c>
+      <c r="G280" t="s">
         <v>549</v>
-      </c>
-      <c r="G280" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="281" spans="1:7">
@@ -13786,10 +13786,10 @@
         <v>544</v>
       </c>
       <c r="F281" t="s">
+        <v>545</v>
+      </c>
+      <c r="G281" t="s">
         <v>549</v>
-      </c>
-      <c r="G281" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="282" spans="1:7">
@@ -13809,10 +13809,10 @@
         <v>544</v>
       </c>
       <c r="F282" t="s">
+        <v>545</v>
+      </c>
+      <c r="G282" t="s">
         <v>549</v>
-      </c>
-      <c r="G282" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="283" spans="1:7">
@@ -13832,10 +13832,10 @@
         <v>544</v>
       </c>
       <c r="F283" t="s">
+        <v>545</v>
+      </c>
+      <c r="G283" t="s">
         <v>549</v>
-      </c>
-      <c r="G283" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="284" spans="1:7">
@@ -13855,10 +13855,10 @@
         <v>544</v>
       </c>
       <c r="F284" t="s">
+        <v>545</v>
+      </c>
+      <c r="G284" t="s">
         <v>549</v>
-      </c>
-      <c r="G284" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="285" spans="1:7">
@@ -13901,10 +13901,10 @@
         <v>663</v>
       </c>
       <c r="F286" t="s">
+        <v>664</v>
+      </c>
+      <c r="G286" t="s">
         <v>668</v>
-      </c>
-      <c r="G286" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="287" spans="1:7">
@@ -13947,10 +13947,10 @@
         <v>663</v>
       </c>
       <c r="F288" t="s">
+        <v>664</v>
+      </c>
+      <c r="G288" t="s">
         <v>668</v>
-      </c>
-      <c r="G288" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="289" spans="1:7">
@@ -14039,10 +14039,10 @@
         <v>663</v>
       </c>
       <c r="F292" t="s">
+        <v>664</v>
+      </c>
+      <c r="G292" t="s">
         <v>681</v>
-      </c>
-      <c r="G292" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="293" spans="1:7">
@@ -14085,10 +14085,10 @@
         <v>663</v>
       </c>
       <c r="F294" t="s">
+        <v>549</v>
+      </c>
+      <c r="G294" t="s">
         <v>686</v>
-      </c>
-      <c r="G294" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="295" spans="1:7">
@@ -14154,10 +14154,10 @@
         <v>663</v>
       </c>
       <c r="F297" t="s">
+        <v>664</v>
+      </c>
+      <c r="G297" t="s">
         <v>668</v>
-      </c>
-      <c r="G297" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="298" spans="1:7">
@@ -14177,10 +14177,10 @@
         <v>663</v>
       </c>
       <c r="F298" t="s">
+        <v>664</v>
+      </c>
+      <c r="G298" t="s">
         <v>668</v>
-      </c>
-      <c r="G298" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="299" spans="1:7">
@@ -14200,10 +14200,10 @@
         <v>663</v>
       </c>
       <c r="F299" t="s">
+        <v>664</v>
+      </c>
+      <c r="G299" t="s">
         <v>697</v>
-      </c>
-      <c r="G299" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="300" spans="1:7">
@@ -14292,10 +14292,10 @@
         <v>663</v>
       </c>
       <c r="F303" t="s">
+        <v>664</v>
+      </c>
+      <c r="G303" t="s">
         <v>668</v>
-      </c>
-      <c r="G303" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="304" spans="1:7">
@@ -14315,10 +14315,10 @@
         <v>663</v>
       </c>
       <c r="F304" t="s">
+        <v>664</v>
+      </c>
+      <c r="G304" t="s">
         <v>668</v>
-      </c>
-      <c r="G304" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="305" spans="1:7">
@@ -14361,10 +14361,10 @@
         <v>663</v>
       </c>
       <c r="F306" t="s">
+        <v>664</v>
+      </c>
+      <c r="G306" t="s">
         <v>668</v>
-      </c>
-      <c r="G306" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="307" spans="1:7">
@@ -14407,10 +14407,10 @@
         <v>663</v>
       </c>
       <c r="F308" t="s">
+        <v>664</v>
+      </c>
+      <c r="G308" t="s">
         <v>668</v>
-      </c>
-      <c r="G308" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="309" spans="1:7">
@@ -14430,10 +14430,10 @@
         <v>663</v>
       </c>
       <c r="F309" t="s">
+        <v>664</v>
+      </c>
+      <c r="G309" t="s">
         <v>697</v>
-      </c>
-      <c r="G309" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="310" spans="1:7">
@@ -14453,10 +14453,10 @@
         <v>663</v>
       </c>
       <c r="F310" t="s">
+        <v>664</v>
+      </c>
+      <c r="G310" t="s">
         <v>668</v>
-      </c>
-      <c r="G310" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="311" spans="1:7">
@@ -14476,10 +14476,10 @@
         <v>663</v>
       </c>
       <c r="F311" t="s">
+        <v>664</v>
+      </c>
+      <c r="G311" t="s">
         <v>668</v>
-      </c>
-      <c r="G311" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="312" spans="1:7">
@@ -14522,10 +14522,10 @@
         <v>663</v>
       </c>
       <c r="F313" t="s">
+        <v>664</v>
+      </c>
+      <c r="G313" t="s">
         <v>668</v>
-      </c>
-      <c r="G313" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="314" spans="1:7">
@@ -14568,10 +14568,10 @@
         <v>663</v>
       </c>
       <c r="F315" t="s">
+        <v>664</v>
+      </c>
+      <c r="G315" t="s">
         <v>668</v>
-      </c>
-      <c r="G315" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="316" spans="1:7">
@@ -14591,10 +14591,10 @@
         <v>663</v>
       </c>
       <c r="F316" t="s">
+        <v>664</v>
+      </c>
+      <c r="G316" t="s">
         <v>734</v>
-      </c>
-      <c r="G316" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="317" spans="1:7">
@@ -14637,10 +14637,10 @@
         <v>663</v>
       </c>
       <c r="F318" t="s">
+        <v>664</v>
+      </c>
+      <c r="G318" t="s">
         <v>668</v>
-      </c>
-      <c r="G318" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="319" spans="1:7">
@@ -14683,10 +14683,10 @@
         <v>663</v>
       </c>
       <c r="F320" t="s">
+        <v>664</v>
+      </c>
+      <c r="G320" t="s">
         <v>668</v>
-      </c>
-      <c r="G320" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="321" spans="1:7">
@@ -14752,10 +14752,10 @@
         <v>663</v>
       </c>
       <c r="F323" t="s">
+        <v>664</v>
+      </c>
+      <c r="G323" t="s">
         <v>668</v>
-      </c>
-      <c r="G323" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="324" spans="1:7">
@@ -14867,10 +14867,10 @@
         <v>663</v>
       </c>
       <c r="F328" t="s">
+        <v>664</v>
+      </c>
+      <c r="G328" t="s">
         <v>734</v>
-      </c>
-      <c r="G328" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="329" spans="1:7">
@@ -14890,10 +14890,10 @@
         <v>663</v>
       </c>
       <c r="F329" t="s">
+        <v>664</v>
+      </c>
+      <c r="G329" t="s">
         <v>668</v>
-      </c>
-      <c r="G329" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="330" spans="1:7">
@@ -14959,10 +14959,10 @@
         <v>663</v>
       </c>
       <c r="F332" t="s">
+        <v>664</v>
+      </c>
+      <c r="G332" t="s">
         <v>734</v>
-      </c>
-      <c r="G332" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="333" spans="1:7">
@@ -14982,10 +14982,10 @@
         <v>663</v>
       </c>
       <c r="F333" t="s">
+        <v>664</v>
+      </c>
+      <c r="G333" t="s">
         <v>668</v>
-      </c>
-      <c r="G333" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="334" spans="1:7">
@@ -15143,10 +15143,10 @@
         <v>663</v>
       </c>
       <c r="F340" t="s">
+        <v>664</v>
+      </c>
+      <c r="G340" t="s">
         <v>668</v>
-      </c>
-      <c r="G340" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="341" spans="1:7">
@@ -15166,10 +15166,10 @@
         <v>663</v>
       </c>
       <c r="F341" t="s">
+        <v>664</v>
+      </c>
+      <c r="G341" t="s">
         <v>668</v>
-      </c>
-      <c r="G341" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="342" spans="1:7">
@@ -15189,10 +15189,10 @@
         <v>663</v>
       </c>
       <c r="F342" t="s">
+        <v>664</v>
+      </c>
+      <c r="G342" t="s">
         <v>668</v>
-      </c>
-      <c r="G342" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="343" spans="1:7">
@@ -15235,10 +15235,10 @@
         <v>663</v>
       </c>
       <c r="F344" t="s">
+        <v>664</v>
+      </c>
+      <c r="G344" t="s">
         <v>668</v>
-      </c>
-      <c r="G344" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="345" spans="1:7">
@@ -15304,10 +15304,10 @@
         <v>663</v>
       </c>
       <c r="F347" t="s">
+        <v>704</v>
+      </c>
+      <c r="G347" t="s">
         <v>801</v>
-      </c>
-      <c r="G347" t="s">
-        <v>705</v>
       </c>
     </row>
     <row r="348" spans="1:7">
@@ -15327,10 +15327,10 @@
         <v>663</v>
       </c>
       <c r="F348" t="s">
+        <v>664</v>
+      </c>
+      <c r="G348" t="s">
         <v>668</v>
-      </c>
-      <c r="G348" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="349" spans="1:7">
@@ -15672,10 +15672,10 @@
         <v>808</v>
       </c>
       <c r="F363" t="s">
+        <v>809</v>
+      </c>
+      <c r="G363" t="s">
         <v>837</v>
-      </c>
-      <c r="G363" t="s">
-        <v>810</v>
       </c>
     </row>
     <row r="364" spans="1:7">
@@ -15718,10 +15718,10 @@
         <v>808</v>
       </c>
       <c r="F365" t="s">
-        <v>809</v>
+        <v>842</v>
       </c>
       <c r="G365" t="s">
-        <v>842</v>
+        <v>810</v>
       </c>
     </row>
     <row r="366" spans="1:7">
@@ -15856,10 +15856,10 @@
         <v>808</v>
       </c>
       <c r="F371" t="s">
-        <v>809</v>
+        <v>855</v>
       </c>
       <c r="G371" t="s">
-        <v>855</v>
+        <v>810</v>
       </c>
     </row>
     <row r="372" spans="1:7">
@@ -16155,10 +16155,10 @@
         <v>808</v>
       </c>
       <c r="F384" t="s">
+        <v>880</v>
+      </c>
+      <c r="G384" t="s">
         <v>884</v>
-      </c>
-      <c r="G384" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="385" spans="1:7">
@@ -16201,10 +16201,10 @@
         <v>887</v>
       </c>
       <c r="F386" t="s">
+        <v>888</v>
+      </c>
+      <c r="G386" t="s">
         <v>892</v>
-      </c>
-      <c r="G386" t="s">
-        <v>889</v>
       </c>
     </row>
     <row r="387" spans="1:7">
@@ -16431,10 +16431,10 @@
         <v>887</v>
       </c>
       <c r="F396" t="s">
+        <v>888</v>
+      </c>
+      <c r="G396" t="s">
         <v>913</v>
-      </c>
-      <c r="G396" t="s">
-        <v>889</v>
       </c>
     </row>
     <row r="397" spans="1:7">
@@ -16661,10 +16661,10 @@
         <v>887</v>
       </c>
       <c r="F406" t="s">
+        <v>888</v>
+      </c>
+      <c r="G406" t="s">
         <v>934</v>
-      </c>
-      <c r="G406" t="s">
-        <v>889</v>
       </c>
     </row>
     <row r="407" spans="1:7">
@@ -16684,10 +16684,10 @@
         <v>887</v>
       </c>
       <c r="F407" t="s">
+        <v>888</v>
+      </c>
+      <c r="G407" t="s">
         <v>892</v>
-      </c>
-      <c r="G407" t="s">
-        <v>889</v>
       </c>
     </row>
     <row r="408" spans="1:7">
@@ -16776,10 +16776,10 @@
         <v>887</v>
       </c>
       <c r="F411" t="s">
-        <v>888</v>
+        <v>945</v>
       </c>
       <c r="G411" t="s">
-        <v>945</v>
+        <v>889</v>
       </c>
     </row>
     <row r="412" spans="1:7">
@@ -16983,10 +16983,10 @@
         <v>962</v>
       </c>
       <c r="F420" t="s">
+        <v>963</v>
+      </c>
+      <c r="G420" t="s">
         <v>969</v>
-      </c>
-      <c r="G420" t="s">
-        <v>964</v>
       </c>
     </row>
     <row r="421" spans="1:7">
@@ -17121,10 +17121,10 @@
         <v>962</v>
       </c>
       <c r="F426" t="s">
+        <v>963</v>
+      </c>
+      <c r="G426" t="s">
         <v>982</v>
-      </c>
-      <c r="G426" t="s">
-        <v>964</v>
       </c>
     </row>
     <row r="427" spans="1:7">
@@ -17144,10 +17144,10 @@
         <v>962</v>
       </c>
       <c r="F427" t="s">
+        <v>963</v>
+      </c>
+      <c r="G427" t="s">
         <v>985</v>
-      </c>
-      <c r="G427" t="s">
-        <v>964</v>
       </c>
     </row>
     <row r="428" spans="1:7">
@@ -17282,10 +17282,10 @@
         <v>962</v>
       </c>
       <c r="F433" t="s">
+        <v>963</v>
+      </c>
+      <c r="G433" t="s">
         <v>1000</v>
-      </c>
-      <c r="G433" t="s">
-        <v>964</v>
       </c>
     </row>
     <row r="434" spans="1:7">
@@ -17604,10 +17604,10 @@
         <v>962</v>
       </c>
       <c r="F447" t="s">
+        <v>963</v>
+      </c>
+      <c r="G447" t="s">
         <v>1037</v>
-      </c>
-      <c r="G447" t="s">
-        <v>964</v>
       </c>
     </row>
     <row r="448" spans="1:7">
@@ -17627,10 +17627,10 @@
         <v>962</v>
       </c>
       <c r="F448" t="s">
+        <v>963</v>
+      </c>
+      <c r="G448" t="s">
         <v>1000</v>
-      </c>
-      <c r="G448" t="s">
-        <v>964</v>
       </c>
     </row>
     <row r="449" spans="1:7">
@@ -17650,10 +17650,10 @@
         <v>962</v>
       </c>
       <c r="F449" t="s">
+        <v>963</v>
+      </c>
+      <c r="G449" t="s">
         <v>969</v>
-      </c>
-      <c r="G449" t="s">
-        <v>964</v>
       </c>
     </row>
     <row r="450" spans="1:7">
@@ -17926,10 +17926,10 @@
         <v>1059</v>
       </c>
       <c r="F461" t="s">
+        <v>1060</v>
+      </c>
+      <c r="G461" t="s">
         <v>1066</v>
-      </c>
-      <c r="G461" t="s">
-        <v>1061</v>
       </c>
     </row>
     <row r="462" spans="1:7">
@@ -17972,10 +17972,10 @@
         <v>1059</v>
       </c>
       <c r="F463" t="s">
+        <v>1060</v>
+      </c>
+      <c r="G463" t="s">
         <v>1071</v>
-      </c>
-      <c r="G463" t="s">
-        <v>1061</v>
       </c>
     </row>
     <row r="464" spans="1:7">
@@ -18248,10 +18248,10 @@
         <v>1059</v>
       </c>
       <c r="F475" t="s">
+        <v>1060</v>
+      </c>
+      <c r="G475" t="s">
         <v>1100</v>
-      </c>
-      <c r="G475" t="s">
-        <v>1061</v>
       </c>
     </row>
     <row r="476" spans="1:7">
@@ -18317,10 +18317,10 @@
         <v>1059</v>
       </c>
       <c r="F478" t="s">
+        <v>1060</v>
+      </c>
+      <c r="G478" t="s">
         <v>1107</v>
-      </c>
-      <c r="G478" t="s">
-        <v>1061</v>
       </c>
     </row>
     <row r="479" spans="1:7">
@@ -18340,10 +18340,10 @@
         <v>1059</v>
       </c>
       <c r="F479" t="s">
+        <v>1060</v>
+      </c>
+      <c r="G479" t="s">
         <v>1110</v>
-      </c>
-      <c r="G479" t="s">
-        <v>1061</v>
       </c>
     </row>
     <row r="480" spans="1:7">
@@ -19030,10 +19030,10 @@
         <v>1154</v>
       </c>
       <c r="F509" t="s">
+        <v>1155</v>
+      </c>
+      <c r="G509" t="s">
         <v>1179</v>
-      </c>
-      <c r="G509" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="510" spans="1:7">
@@ -19053,10 +19053,10 @@
         <v>1154</v>
       </c>
       <c r="F510" t="s">
+        <v>1175</v>
+      </c>
+      <c r="G510" t="s">
         <v>1182</v>
-      </c>
-      <c r="G510" t="s">
-        <v>1176</v>
       </c>
     </row>
     <row r="511" spans="1:7">
@@ -19214,10 +19214,10 @@
         <v>1154</v>
       </c>
       <c r="F517" t="s">
+        <v>1175</v>
+      </c>
+      <c r="G517" t="s">
         <v>1201</v>
-      </c>
-      <c r="G517" t="s">
-        <v>1176</v>
       </c>
     </row>
     <row r="518" spans="1:7">
@@ -19582,10 +19582,10 @@
         <v>1231</v>
       </c>
       <c r="F533" t="s">
+        <v>1232</v>
+      </c>
+      <c r="G533" t="s">
         <v>1236</v>
-      </c>
-      <c r="G533" t="s">
-        <v>1233</v>
       </c>
     </row>
     <row r="534" spans="1:7">
@@ -19674,10 +19674,10 @@
         <v>1231</v>
       </c>
       <c r="F537" t="s">
-        <v>1232</v>
+        <v>1245</v>
       </c>
       <c r="G537" t="s">
-        <v>1245</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="538" spans="1:7">
@@ -19720,10 +19720,10 @@
         <v>1231</v>
       </c>
       <c r="F539" t="s">
-        <v>1191</v>
+        <v>1250</v>
       </c>
       <c r="G539" t="s">
-        <v>1250</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="540" spans="1:7">
@@ -19743,10 +19743,10 @@
         <v>1231</v>
       </c>
       <c r="F540" t="s">
-        <v>1191</v>
+        <v>1250</v>
       </c>
       <c r="G540" t="s">
-        <v>1250</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="541" spans="1:7">
@@ -19812,10 +19812,10 @@
         <v>1231</v>
       </c>
       <c r="F543" t="s">
+        <v>1232</v>
+      </c>
+      <c r="G543" t="s">
         <v>1259</v>
-      </c>
-      <c r="G543" t="s">
-        <v>1233</v>
       </c>
     </row>
     <row r="544" spans="1:7">
@@ -19904,10 +19904,10 @@
         <v>1231</v>
       </c>
       <c r="F547" t="s">
+        <v>1232</v>
+      </c>
+      <c r="G547" t="s">
         <v>1268</v>
-      </c>
-      <c r="G547" t="s">
-        <v>1233</v>
       </c>
     </row>
     <row r="548" spans="1:7">
@@ -20065,10 +20065,10 @@
         <v>1231</v>
       </c>
       <c r="F554" t="s">
-        <v>1283</v>
+        <v>1287</v>
       </c>
       <c r="G554" t="s">
-        <v>1287</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="555" spans="1:7">
@@ -20134,10 +20134,10 @@
         <v>1231</v>
       </c>
       <c r="F557" t="s">
+        <v>1232</v>
+      </c>
+      <c r="G557" t="s">
         <v>1296</v>
-      </c>
-      <c r="G557" t="s">
-        <v>1233</v>
       </c>
     </row>
     <row r="558" spans="1:7">
@@ -20180,10 +20180,10 @@
         <v>1231</v>
       </c>
       <c r="F559" t="s">
-        <v>1232</v>
+        <v>1301</v>
       </c>
       <c r="G559" t="s">
-        <v>1301</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="560" spans="1:7">
@@ -20364,10 +20364,10 @@
         <v>1231</v>
       </c>
       <c r="F567" t="s">
+        <v>1232</v>
+      </c>
+      <c r="G567" t="s">
         <v>1317</v>
-      </c>
-      <c r="G567" t="s">
-        <v>1233</v>
       </c>
     </row>
     <row r="568" spans="1:7">
@@ -20387,10 +20387,10 @@
         <v>1231</v>
       </c>
       <c r="F568" t="s">
+        <v>1232</v>
+      </c>
+      <c r="G568" t="s">
         <v>1320</v>
-      </c>
-      <c r="G568" t="s">
-        <v>1233</v>
       </c>
     </row>
     <row r="569" spans="1:7">
@@ -20410,10 +20410,10 @@
         <v>1231</v>
       </c>
       <c r="F569" t="s">
+        <v>1232</v>
+      </c>
+      <c r="G569" t="s">
         <v>1323</v>
-      </c>
-      <c r="G569" t="s">
-        <v>1233</v>
       </c>
     </row>
     <row r="570" spans="1:7">
@@ -20456,10 +20456,10 @@
         <v>1329</v>
       </c>
       <c r="F571" t="s">
+        <v>1330</v>
+      </c>
+      <c r="G571" t="s">
         <v>1236</v>
-      </c>
-      <c r="G571" t="s">
-        <v>1330</v>
       </c>
     </row>
     <row r="572" spans="1:7">
@@ -20479,10 +20479,10 @@
         <v>1329</v>
       </c>
       <c r="F572" t="s">
+        <v>1330</v>
+      </c>
+      <c r="G572" t="s">
         <v>1236</v>
-      </c>
-      <c r="G572" t="s">
-        <v>1330</v>
       </c>
     </row>
     <row r="573" spans="1:7">
@@ -20502,10 +20502,10 @@
         <v>1329</v>
       </c>
       <c r="F573" t="s">
+        <v>1330</v>
+      </c>
+      <c r="G573" t="s">
         <v>1236</v>
-      </c>
-      <c r="G573" t="s">
-        <v>1330</v>
       </c>
     </row>
     <row r="574" spans="1:7">
@@ -20525,10 +20525,10 @@
         <v>1329</v>
       </c>
       <c r="F574" t="s">
+        <v>1330</v>
+      </c>
+      <c r="G574" t="s">
         <v>1236</v>
-      </c>
-      <c r="G574" t="s">
-        <v>1330</v>
       </c>
     </row>
     <row r="575" spans="1:7">
@@ -20548,10 +20548,10 @@
         <v>1329</v>
       </c>
       <c r="F575" t="s">
+        <v>1330</v>
+      </c>
+      <c r="G575" t="s">
         <v>1339</v>
-      </c>
-      <c r="G575" t="s">
-        <v>1330</v>
       </c>
     </row>
     <row r="576" spans="1:7">
@@ -20571,10 +20571,10 @@
         <v>1329</v>
       </c>
       <c r="F576" t="s">
+        <v>1342</v>
+      </c>
+      <c r="G576" t="s">
         <v>1236</v>
-      </c>
-      <c r="G576" t="s">
-        <v>1342</v>
       </c>
     </row>
     <row r="577" spans="1:7">
@@ -20594,10 +20594,10 @@
         <v>1329</v>
       </c>
       <c r="F577" t="s">
+        <v>1330</v>
+      </c>
+      <c r="G577" t="s">
         <v>1236</v>
-      </c>
-      <c r="G577" t="s">
-        <v>1330</v>
       </c>
     </row>
     <row r="578" spans="1:7">
@@ -20617,10 +20617,10 @@
         <v>1329</v>
       </c>
       <c r="F578" t="s">
+        <v>1330</v>
+      </c>
+      <c r="G578" t="s">
         <v>1236</v>
-      </c>
-      <c r="G578" t="s">
-        <v>1330</v>
       </c>
     </row>
     <row r="579" spans="1:7">
@@ -20640,10 +20640,10 @@
         <v>1329</v>
       </c>
       <c r="F579" t="s">
+        <v>1330</v>
+      </c>
+      <c r="G579" t="s">
         <v>1236</v>
-      </c>
-      <c r="G579" t="s">
-        <v>1330</v>
       </c>
     </row>
     <row r="580" spans="1:7">
@@ -20663,10 +20663,10 @@
         <v>1329</v>
       </c>
       <c r="F580" t="s">
+        <v>1330</v>
+      </c>
+      <c r="G580" t="s">
         <v>1236</v>
-      </c>
-      <c r="G580" t="s">
-        <v>1330</v>
       </c>
     </row>
     <row r="581" spans="1:7">
@@ -20686,10 +20686,10 @@
         <v>1329</v>
       </c>
       <c r="F581" t="s">
+        <v>1330</v>
+      </c>
+      <c r="G581" t="s">
         <v>1236</v>
-      </c>
-      <c r="G581" t="s">
-        <v>1330</v>
       </c>
     </row>
     <row r="582" spans="1:7">
@@ -20709,10 +20709,10 @@
         <v>1329</v>
       </c>
       <c r="F582" t="s">
+        <v>1330</v>
+      </c>
+      <c r="G582" t="s">
         <v>1355</v>
-      </c>
-      <c r="G582" t="s">
-        <v>1330</v>
       </c>
     </row>
     <row r="583" spans="1:7">
@@ -20732,10 +20732,10 @@
         <v>1329</v>
       </c>
       <c r="F583" t="s">
+        <v>1330</v>
+      </c>
+      <c r="G583" t="s">
         <v>1358</v>
-      </c>
-      <c r="G583" t="s">
-        <v>1330</v>
       </c>
     </row>
     <row r="584" spans="1:7">
@@ -20755,10 +20755,10 @@
         <v>1329</v>
       </c>
       <c r="F584" t="s">
+        <v>1330</v>
+      </c>
+      <c r="G584" t="s">
         <v>1236</v>
-      </c>
-      <c r="G584" t="s">
-        <v>1330</v>
       </c>
     </row>
     <row r="585" spans="1:7">
@@ -20778,10 +20778,10 @@
         <v>1329</v>
       </c>
       <c r="F585" t="s">
+        <v>1330</v>
+      </c>
+      <c r="G585" t="s">
         <v>1236</v>
-      </c>
-      <c r="G585" t="s">
-        <v>1330</v>
       </c>
     </row>
     <row r="586" spans="1:7">
@@ -20801,10 +20801,10 @@
         <v>1329</v>
       </c>
       <c r="F586" t="s">
+        <v>1290</v>
+      </c>
+      <c r="G586" t="s">
         <v>1236</v>
-      </c>
-      <c r="G586" t="s">
-        <v>1291</v>
       </c>
     </row>
     <row r="587" spans="1:7">
@@ -20824,10 +20824,10 @@
         <v>1329</v>
       </c>
       <c r="F587" t="s">
+        <v>1330</v>
+      </c>
+      <c r="G587" t="s">
         <v>1236</v>
-      </c>
-      <c r="G587" t="s">
-        <v>1330</v>
       </c>
     </row>
     <row r="588" spans="1:7">
@@ -20847,10 +20847,10 @@
         <v>1329</v>
       </c>
       <c r="F588" t="s">
+        <v>1330</v>
+      </c>
+      <c r="G588" t="s">
         <v>1236</v>
-      </c>
-      <c r="G588" t="s">
-        <v>1330</v>
       </c>
     </row>
     <row r="589" spans="1:7">
@@ -20870,10 +20870,10 @@
         <v>1329</v>
       </c>
       <c r="F589" t="s">
+        <v>1330</v>
+      </c>
+      <c r="G589" t="s">
         <v>1236</v>
-      </c>
-      <c r="G589" t="s">
-        <v>1330</v>
       </c>
     </row>
     <row r="590" spans="1:7">
@@ -20893,10 +20893,10 @@
         <v>1329</v>
       </c>
       <c r="F590" t="s">
+        <v>1330</v>
+      </c>
+      <c r="G590" t="s">
         <v>1236</v>
-      </c>
-      <c r="G590" t="s">
-        <v>1330</v>
       </c>
     </row>
     <row r="591" spans="1:7">
@@ -20916,10 +20916,10 @@
         <v>1329</v>
       </c>
       <c r="F591" t="s">
+        <v>1375</v>
+      </c>
+      <c r="G591" t="s">
         <v>1236</v>
-      </c>
-      <c r="G591" t="s">
-        <v>1375</v>
       </c>
     </row>
     <row r="592" spans="1:7">
@@ -20939,10 +20939,10 @@
         <v>1329</v>
       </c>
       <c r="F592" t="s">
+        <v>1330</v>
+      </c>
+      <c r="G592" t="s">
         <v>1236</v>
-      </c>
-      <c r="G592" t="s">
-        <v>1330</v>
       </c>
     </row>
     <row r="593" spans="1:7">
@@ -20962,10 +20962,10 @@
         <v>1329</v>
       </c>
       <c r="F593" t="s">
+        <v>1330</v>
+      </c>
+      <c r="G593" t="s">
         <v>1236</v>
-      </c>
-      <c r="G593" t="s">
-        <v>1330</v>
       </c>
     </row>
     <row r="594" spans="1:7">
@@ -21008,10 +21008,10 @@
         <v>1382</v>
       </c>
       <c r="F595" t="s">
+        <v>1383</v>
+      </c>
+      <c r="G595" t="s">
         <v>1387</v>
-      </c>
-      <c r="G595" t="s">
-        <v>1384</v>
       </c>
     </row>
     <row r="596" spans="1:7">
@@ -21031,10 +21031,10 @@
         <v>1382</v>
       </c>
       <c r="F596" t="s">
+        <v>1383</v>
+      </c>
+      <c r="G596" t="s">
         <v>1390</v>
-      </c>
-      <c r="G596" t="s">
-        <v>1384</v>
       </c>
     </row>
     <row r="597" spans="1:7">
@@ -21123,10 +21123,10 @@
         <v>1382</v>
       </c>
       <c r="F600" t="s">
-        <v>1383</v>
+        <v>1399</v>
       </c>
       <c r="G600" t="s">
-        <v>1399</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="601" spans="1:7">
@@ -21261,10 +21261,10 @@
         <v>1382</v>
       </c>
       <c r="F606" t="s">
+        <v>1383</v>
+      </c>
+      <c r="G606" t="s">
         <v>1414</v>
-      </c>
-      <c r="G606" t="s">
-        <v>1384</v>
       </c>
     </row>
     <row r="607" spans="1:7">
@@ -21284,10 +21284,10 @@
         <v>1382</v>
       </c>
       <c r="F607" t="s">
+        <v>1383</v>
+      </c>
+      <c r="G607" t="s">
         <v>1414</v>
-      </c>
-      <c r="G607" t="s">
-        <v>1384</v>
       </c>
     </row>
     <row r="608" spans="1:7">
@@ -21330,10 +21330,10 @@
         <v>1382</v>
       </c>
       <c r="F609" t="s">
-        <v>1383</v>
+        <v>1421</v>
       </c>
       <c r="G609" t="s">
-        <v>1421</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="610" spans="1:7">
@@ -21560,10 +21560,10 @@
         <v>1444</v>
       </c>
       <c r="F619" t="s">
+        <v>1330</v>
+      </c>
+      <c r="G619" t="s">
         <v>1445</v>
-      </c>
-      <c r="G619" t="s">
-        <v>1330</v>
       </c>
     </row>
     <row r="620" spans="1:7">
@@ -21583,10 +21583,10 @@
         <v>1444</v>
       </c>
       <c r="F620" t="s">
+        <v>1448</v>
+      </c>
+      <c r="G620" t="s">
         <v>1445</v>
-      </c>
-      <c r="G620" t="s">
-        <v>1448</v>
       </c>
     </row>
     <row r="621" spans="1:7">
@@ -21606,10 +21606,10 @@
         <v>1444</v>
       </c>
       <c r="F621" t="s">
+        <v>1448</v>
+      </c>
+      <c r="G621" t="s">
         <v>1445</v>
-      </c>
-      <c r="G621" t="s">
-        <v>1448</v>
       </c>
     </row>
     <row r="622" spans="1:7">
@@ -21629,10 +21629,10 @@
         <v>1444</v>
       </c>
       <c r="F622" t="s">
+        <v>1448</v>
+      </c>
+      <c r="G622" t="s">
         <v>1445</v>
-      </c>
-      <c r="G622" t="s">
-        <v>1448</v>
       </c>
     </row>
     <row r="623" spans="1:7">
@@ -21652,10 +21652,10 @@
         <v>1444</v>
       </c>
       <c r="F623" t="s">
+        <v>1383</v>
+      </c>
+      <c r="G623" t="s">
         <v>1445</v>
-      </c>
-      <c r="G623" t="s">
-        <v>1384</v>
       </c>
     </row>
     <row r="624" spans="1:7">
@@ -21675,10 +21675,10 @@
         <v>1444</v>
       </c>
       <c r="F624" t="s">
+        <v>1448</v>
+      </c>
+      <c r="G624" t="s">
         <v>1457</v>
-      </c>
-      <c r="G624" t="s">
-        <v>1448</v>
       </c>
     </row>
     <row r="625" spans="1:7">
@@ -21721,10 +21721,10 @@
         <v>1444</v>
       </c>
       <c r="F626" t="s">
+        <v>1448</v>
+      </c>
+      <c r="G626" t="s">
         <v>1464</v>
-      </c>
-      <c r="G626" t="s">
-        <v>1448</v>
       </c>
     </row>
     <row r="627" spans="1:7">
@@ -21744,10 +21744,10 @@
         <v>1444</v>
       </c>
       <c r="F627" t="s">
+        <v>1448</v>
+      </c>
+      <c r="G627" t="s">
         <v>1467</v>
-      </c>
-      <c r="G627" t="s">
-        <v>1448</v>
       </c>
     </row>
     <row r="628" spans="1:7">
@@ -21767,10 +21767,10 @@
         <v>1444</v>
       </c>
       <c r="F628" t="s">
+        <v>1448</v>
+      </c>
+      <c r="G628" t="s">
         <v>1445</v>
-      </c>
-      <c r="G628" t="s">
-        <v>1448</v>
       </c>
     </row>
     <row r="629" spans="1:7">
@@ -21836,10 +21836,10 @@
         <v>1444</v>
       </c>
       <c r="F631" t="s">
+        <v>1448</v>
+      </c>
+      <c r="G631" t="s">
         <v>1445</v>
-      </c>
-      <c r="G631" t="s">
-        <v>1448</v>
       </c>
     </row>
     <row r="632" spans="1:7">
@@ -21882,10 +21882,10 @@
         <v>1444</v>
       </c>
       <c r="F633" t="s">
+        <v>1448</v>
+      </c>
+      <c r="G633" t="s">
         <v>1486</v>
-      </c>
-      <c r="G633" t="s">
-        <v>1448</v>
       </c>
     </row>
     <row r="634" spans="1:7">
@@ -21905,10 +21905,10 @@
         <v>1444</v>
       </c>
       <c r="F634" t="s">
+        <v>1448</v>
+      </c>
+      <c r="G634" t="s">
         <v>1489</v>
-      </c>
-      <c r="G634" t="s">
-        <v>1448</v>
       </c>
     </row>
     <row r="635" spans="1:7">
@@ -21928,10 +21928,10 @@
         <v>1444</v>
       </c>
       <c r="F635" t="s">
+        <v>1448</v>
+      </c>
+      <c r="G635" t="s">
         <v>1445</v>
-      </c>
-      <c r="G635" t="s">
-        <v>1448</v>
       </c>
     </row>
     <row r="636" spans="1:7">
@@ -21951,10 +21951,10 @@
         <v>1444</v>
       </c>
       <c r="F636" t="s">
+        <v>1448</v>
+      </c>
+      <c r="G636" t="s">
         <v>1445</v>
-      </c>
-      <c r="G636" t="s">
-        <v>1448</v>
       </c>
     </row>
     <row r="637" spans="1:7">
@@ -21974,10 +21974,10 @@
         <v>1444</v>
       </c>
       <c r="F637" t="s">
+        <v>1448</v>
+      </c>
+      <c r="G637" t="s">
         <v>1445</v>
-      </c>
-      <c r="G637" t="s">
-        <v>1448</v>
       </c>
     </row>
     <row r="638" spans="1:7">
@@ -21997,10 +21997,10 @@
         <v>1444</v>
       </c>
       <c r="F638" t="s">
+        <v>1498</v>
+      </c>
+      <c r="G638" t="s">
         <v>1445</v>
-      </c>
-      <c r="G638" t="s">
-        <v>1498</v>
       </c>
     </row>
     <row r="639" spans="1:7">
@@ -22020,10 +22020,10 @@
         <v>1444</v>
       </c>
       <c r="F639" t="s">
+        <v>1448</v>
+      </c>
+      <c r="G639" t="s">
         <v>1445</v>
-      </c>
-      <c r="G639" t="s">
-        <v>1448</v>
       </c>
     </row>
     <row r="640" spans="1:7">
@@ -22043,10 +22043,10 @@
         <v>1444</v>
       </c>
       <c r="F640" t="s">
+        <v>1448</v>
+      </c>
+      <c r="G640" t="s">
         <v>1445</v>
-      </c>
-      <c r="G640" t="s">
-        <v>1448</v>
       </c>
     </row>
     <row r="641" spans="1:7">
@@ -22066,10 +22066,10 @@
         <v>1444</v>
       </c>
       <c r="F641" t="s">
+        <v>1448</v>
+      </c>
+      <c r="G641" t="s">
         <v>1445</v>
-      </c>
-      <c r="G641" t="s">
-        <v>1448</v>
       </c>
     </row>
     <row r="642" spans="1:7">
@@ -22089,10 +22089,10 @@
         <v>1444</v>
       </c>
       <c r="F642" t="s">
+        <v>1448</v>
+      </c>
+      <c r="G642" t="s">
         <v>1445</v>
-      </c>
-      <c r="G642" t="s">
-        <v>1448</v>
       </c>
     </row>
     <row r="643" spans="1:7">
@@ -22296,10 +22296,10 @@
         <v>1509</v>
       </c>
       <c r="F651" t="s">
+        <v>1510</v>
+      </c>
+      <c r="G651" t="s">
         <v>1536</v>
-      </c>
-      <c r="G651" t="s">
-        <v>1511</v>
       </c>
     </row>
     <row r="652" spans="1:7">
@@ -22411,10 +22411,10 @@
         <v>1509</v>
       </c>
       <c r="F656" t="s">
+        <v>1486</v>
+      </c>
+      <c r="G656" t="s">
         <v>1548</v>
-      </c>
-      <c r="G656" t="s">
-        <v>1486</v>
       </c>
     </row>
     <row r="657" spans="1:7">
@@ -22457,10 +22457,10 @@
         <v>1509</v>
       </c>
       <c r="F658" t="s">
-        <v>1514</v>
+        <v>1553</v>
       </c>
       <c r="G658" t="s">
-        <v>1553</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="659" spans="1:7">
@@ -22480,10 +22480,10 @@
         <v>1509</v>
       </c>
       <c r="F659" t="s">
+        <v>1510</v>
+      </c>
+      <c r="G659" t="s">
         <v>1556</v>
-      </c>
-      <c r="G659" t="s">
-        <v>1511</v>
       </c>
     </row>
     <row r="660" spans="1:7">
@@ -22503,10 +22503,10 @@
         <v>1509</v>
       </c>
       <c r="F660" t="s">
+        <v>1510</v>
+      </c>
+      <c r="G660" t="s">
         <v>1556</v>
-      </c>
-      <c r="G660" t="s">
-        <v>1511</v>
       </c>
     </row>
     <row r="661" spans="1:7">
@@ -22549,10 +22549,10 @@
         <v>1509</v>
       </c>
       <c r="F662" t="s">
+        <v>1510</v>
+      </c>
+      <c r="G662" t="s">
         <v>1562</v>
-      </c>
-      <c r="G662" t="s">
-        <v>1511</v>
       </c>
     </row>
     <row r="663" spans="1:7">
@@ -22917,10 +22917,10 @@
         <v>1583</v>
       </c>
       <c r="F678" t="s">
-        <v>1584</v>
+        <v>1598</v>
       </c>
       <c r="G678" t="s">
-        <v>1598</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="679" spans="1:7">
@@ -22940,10 +22940,10 @@
         <v>1583</v>
       </c>
       <c r="F679" t="s">
+        <v>1584</v>
+      </c>
+      <c r="G679" t="s">
         <v>1601</v>
-      </c>
-      <c r="G679" t="s">
-        <v>1585</v>
       </c>
     </row>
     <row r="680" spans="1:7">
@@ -23032,10 +23032,10 @@
         <v>1583</v>
       </c>
       <c r="F683" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G683" t="s">
         <v>1601</v>
-      </c>
-      <c r="G683" t="s">
-        <v>1609</v>
       </c>
     </row>
     <row r="684" spans="1:7">
@@ -23124,10 +23124,10 @@
         <v>1583</v>
       </c>
       <c r="F687" t="s">
+        <v>1584</v>
+      </c>
+      <c r="G687" t="s">
         <v>1622</v>
-      </c>
-      <c r="G687" t="s">
-        <v>1585</v>
       </c>
     </row>
     <row r="688" spans="1:7">
@@ -23262,10 +23262,10 @@
         <v>1583</v>
       </c>
       <c r="F693" t="s">
+        <v>1584</v>
+      </c>
+      <c r="G693" t="s">
         <v>1639</v>
-      </c>
-      <c r="G693" t="s">
-        <v>1585</v>
       </c>
     </row>
     <row r="694" spans="1:7">
@@ -23285,10 +23285,10 @@
         <v>1583</v>
       </c>
       <c r="F694" t="s">
+        <v>1584</v>
+      </c>
+      <c r="G694" t="s">
         <v>1642</v>
-      </c>
-      <c r="G694" t="s">
-        <v>1585</v>
       </c>
     </row>
     <row r="695" spans="1:7">
@@ -23377,10 +23377,10 @@
         <v>1583</v>
       </c>
       <c r="F698" t="s">
+        <v>1584</v>
+      </c>
+      <c r="G698" t="s">
         <v>1650</v>
-      </c>
-      <c r="G698" t="s">
-        <v>1585</v>
       </c>
     </row>
     <row r="699" spans="1:7">
@@ -23492,10 +23492,10 @@
         <v>1657</v>
       </c>
       <c r="F703" t="s">
-        <v>1658</v>
+        <v>1666</v>
       </c>
       <c r="G703" t="s">
-        <v>1666</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="704" spans="1:7">
@@ -23561,10 +23561,10 @@
         <v>1657</v>
       </c>
       <c r="F706" t="s">
+        <v>1584</v>
+      </c>
+      <c r="G706" t="s">
         <v>1642</v>
-      </c>
-      <c r="G706" t="s">
-        <v>1585</v>
       </c>
     </row>
     <row r="707" spans="1:7">
@@ -23676,10 +23676,10 @@
         <v>1657</v>
       </c>
       <c r="F711" t="s">
+        <v>1689</v>
+      </c>
+      <c r="G711" t="s">
         <v>1622</v>
-      </c>
-      <c r="G711" t="s">
-        <v>1689</v>
       </c>
     </row>
     <row r="712" spans="1:7">
@@ -23745,10 +23745,10 @@
         <v>1657</v>
       </c>
       <c r="F714" t="s">
-        <v>1669</v>
+        <v>1663</v>
       </c>
       <c r="G714" t="s">
-        <v>1662</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="715" spans="1:7">
@@ -23791,10 +23791,10 @@
         <v>1657</v>
       </c>
       <c r="F716" t="s">
+        <v>1704</v>
+      </c>
+      <c r="G716" t="s">
         <v>1642</v>
-      </c>
-      <c r="G716" t="s">
-        <v>1704</v>
       </c>
     </row>
     <row r="717" spans="1:7">
@@ -23814,10 +23814,10 @@
         <v>1657</v>
       </c>
       <c r="F717" t="s">
+        <v>1669</v>
+      </c>
+      <c r="G717" t="s">
         <v>1707</v>
-      </c>
-      <c r="G717" t="s">
-        <v>1670</v>
       </c>
     </row>
     <row r="718" spans="1:7">
@@ -23837,10 +23837,10 @@
         <v>1657</v>
       </c>
       <c r="F718" t="s">
+        <v>1669</v>
+      </c>
+      <c r="G718" t="s">
         <v>1707</v>
-      </c>
-      <c r="G718" t="s">
-        <v>1670</v>
       </c>
     </row>
     <row r="719" spans="1:7">
@@ -23860,10 +23860,10 @@
         <v>1657</v>
       </c>
       <c r="F719" t="s">
+        <v>1658</v>
+      </c>
+      <c r="G719" t="s">
         <v>1707</v>
-      </c>
-      <c r="G719" t="s">
-        <v>1659</v>
       </c>
     </row>
     <row r="720" spans="1:7">
@@ -23929,10 +23929,10 @@
         <v>1657</v>
       </c>
       <c r="F722" t="s">
+        <v>1689</v>
+      </c>
+      <c r="G722" t="s">
         <v>1642</v>
-      </c>
-      <c r="G722" t="s">
-        <v>1689</v>
       </c>
     </row>
     <row r="723" spans="1:7">
@@ -23975,10 +23975,10 @@
         <v>1657</v>
       </c>
       <c r="F724" t="s">
-        <v>1658</v>
+        <v>1723</v>
       </c>
       <c r="G724" t="s">
-        <v>1723</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="725" spans="1:7">
@@ -24044,10 +24044,10 @@
         <v>1657</v>
       </c>
       <c r="F727" t="s">
+        <v>1692</v>
+      </c>
+      <c r="G727" t="s">
         <v>1642</v>
-      </c>
-      <c r="G727" t="s">
-        <v>1693</v>
       </c>
     </row>
     <row r="728" spans="1:7">
@@ -24067,10 +24067,10 @@
         <v>1657</v>
       </c>
       <c r="F728" t="s">
-        <v>1658</v>
+        <v>1666</v>
       </c>
       <c r="G728" t="s">
-        <v>1666</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="729" spans="1:7">
@@ -24090,10 +24090,10 @@
         <v>1657</v>
       </c>
       <c r="F729" t="s">
+        <v>1669</v>
+      </c>
+      <c r="G729" t="s">
         <v>1734</v>
-      </c>
-      <c r="G729" t="s">
-        <v>1670</v>
       </c>
     </row>
     <row r="730" spans="1:7">
@@ -24412,10 +24412,10 @@
         <v>1748</v>
       </c>
       <c r="F743" t="s">
-        <v>1753</v>
+        <v>1769</v>
       </c>
       <c r="G743" t="s">
-        <v>1769</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="744" spans="1:7">
@@ -24481,10 +24481,10 @@
         <v>1748</v>
       </c>
       <c r="F746" t="s">
+        <v>1669</v>
+      </c>
+      <c r="G746" t="s">
         <v>1778</v>
-      </c>
-      <c r="G746" t="s">
-        <v>1670</v>
       </c>
     </row>
     <row r="747" spans="1:7">
@@ -24734,10 +24734,10 @@
         <v>1748</v>
       </c>
       <c r="F757" t="s">
+        <v>1805</v>
+      </c>
+      <c r="G757" t="s">
         <v>1815</v>
-      </c>
-      <c r="G757" t="s">
-        <v>1806</v>
       </c>
     </row>
     <row r="758" spans="1:7">
@@ -24780,10 +24780,10 @@
         <v>1748</v>
       </c>
       <c r="F759" t="s">
+        <v>1799</v>
+      </c>
+      <c r="G759" t="s">
         <v>1820</v>
-      </c>
-      <c r="G759" t="s">
-        <v>1800</v>
       </c>
     </row>
     <row r="760" spans="1:7">
@@ -24826,10 +24826,10 @@
         <v>1748</v>
       </c>
       <c r="F761" t="s">
-        <v>1757</v>
+        <v>1799</v>
       </c>
       <c r="G761" t="s">
-        <v>1800</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="762" spans="1:7">
@@ -24849,10 +24849,10 @@
         <v>1748</v>
       </c>
       <c r="F762" t="s">
-        <v>1757</v>
+        <v>1799</v>
       </c>
       <c r="G762" t="s">
-        <v>1800</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="763" spans="1:7">
@@ -24872,10 +24872,10 @@
         <v>1748</v>
       </c>
       <c r="F763" t="s">
+        <v>1753</v>
+      </c>
+      <c r="G763" t="s">
         <v>1828</v>
-      </c>
-      <c r="G763" t="s">
-        <v>1754</v>
       </c>
     </row>
     <row r="764" spans="1:7">
@@ -24941,10 +24941,10 @@
         <v>1748</v>
       </c>
       <c r="F766" t="s">
-        <v>1757</v>
+        <v>1799</v>
       </c>
       <c r="G766" t="s">
-        <v>1800</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="767" spans="1:7">
@@ -25056,10 +25056,10 @@
         <v>1748</v>
       </c>
       <c r="F771" t="s">
-        <v>1795</v>
+        <v>1799</v>
       </c>
       <c r="G771" t="s">
-        <v>1800</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="772" spans="1:7">
@@ -25148,10 +25148,10 @@
         <v>1852</v>
       </c>
       <c r="F775" t="s">
+        <v>1853</v>
+      </c>
+      <c r="G775" t="s">
         <v>1857</v>
-      </c>
-      <c r="G775" t="s">
-        <v>1854</v>
       </c>
     </row>
     <row r="776" spans="1:7">
@@ -25171,10 +25171,10 @@
         <v>1852</v>
       </c>
       <c r="F776" t="s">
+        <v>1853</v>
+      </c>
+      <c r="G776" t="s">
         <v>1857</v>
-      </c>
-      <c r="G776" t="s">
-        <v>1854</v>
       </c>
     </row>
     <row r="777" spans="1:7">
@@ -25194,10 +25194,10 @@
         <v>1852</v>
       </c>
       <c r="F777" t="s">
+        <v>1853</v>
+      </c>
+      <c r="G777" t="s">
         <v>1857</v>
-      </c>
-      <c r="G777" t="s">
-        <v>1854</v>
       </c>
     </row>
     <row r="778" spans="1:7">
@@ -25217,10 +25217,10 @@
         <v>1852</v>
       </c>
       <c r="F778" t="s">
+        <v>1853</v>
+      </c>
+      <c r="G778" t="s">
         <v>1857</v>
-      </c>
-      <c r="G778" t="s">
-        <v>1854</v>
       </c>
     </row>
     <row r="779" spans="1:7">
@@ -25240,10 +25240,10 @@
         <v>1852</v>
       </c>
       <c r="F779" t="s">
+        <v>1853</v>
+      </c>
+      <c r="G779" t="s">
         <v>1857</v>
-      </c>
-      <c r="G779" t="s">
-        <v>1854</v>
       </c>
     </row>
     <row r="780" spans="1:7">
@@ -25263,10 +25263,10 @@
         <v>1852</v>
       </c>
       <c r="F780" t="s">
+        <v>1853</v>
+      </c>
+      <c r="G780" t="s">
         <v>1857</v>
-      </c>
-      <c r="G780" t="s">
-        <v>1854</v>
       </c>
     </row>
     <row r="781" spans="1:7">
@@ -25332,10 +25332,10 @@
         <v>1852</v>
       </c>
       <c r="F783" t="s">
+        <v>1853</v>
+      </c>
+      <c r="G783" t="s">
         <v>1857</v>
-      </c>
-      <c r="G783" t="s">
-        <v>1854</v>
       </c>
     </row>
     <row r="784" spans="1:7">
@@ -25355,10 +25355,10 @@
         <v>1852</v>
       </c>
       <c r="F784" t="s">
+        <v>1853</v>
+      </c>
+      <c r="G784" t="s">
         <v>1857</v>
-      </c>
-      <c r="G784" t="s">
-        <v>1854</v>
       </c>
     </row>
     <row r="785" spans="1:7">
@@ -25401,10 +25401,10 @@
         <v>1852</v>
       </c>
       <c r="F786" t="s">
+        <v>1853</v>
+      </c>
+      <c r="G786" t="s">
         <v>1857</v>
-      </c>
-      <c r="G786" t="s">
-        <v>1854</v>
       </c>
     </row>
     <row r="787" spans="1:7">
@@ -25470,10 +25470,10 @@
         <v>1852</v>
       </c>
       <c r="F789" t="s">
+        <v>1853</v>
+      </c>
+      <c r="G789" t="s">
         <v>1894</v>
-      </c>
-      <c r="G789" t="s">
-        <v>1854</v>
       </c>
     </row>
     <row r="790" spans="1:7">
@@ -25516,10 +25516,10 @@
         <v>1852</v>
       </c>
       <c r="F791" t="s">
+        <v>1853</v>
+      </c>
+      <c r="G791" t="s">
         <v>1857</v>
-      </c>
-      <c r="G791" t="s">
-        <v>1854</v>
       </c>
     </row>
     <row r="792" spans="1:7">
@@ -25539,10 +25539,10 @@
         <v>1852</v>
       </c>
       <c r="F792" t="s">
+        <v>1853</v>
+      </c>
+      <c r="G792" t="s">
         <v>1903</v>
-      </c>
-      <c r="G792" t="s">
-        <v>1854</v>
       </c>
     </row>
     <row r="793" spans="1:7">
@@ -25562,10 +25562,10 @@
         <v>1852</v>
       </c>
       <c r="F793" t="s">
+        <v>1853</v>
+      </c>
+      <c r="G793" t="s">
         <v>1857</v>
-      </c>
-      <c r="G793" t="s">
-        <v>1854</v>
       </c>
     </row>
     <row r="794" spans="1:7">
@@ -25585,10 +25585,10 @@
         <v>1852</v>
       </c>
       <c r="F794" t="s">
+        <v>1757</v>
+      </c>
+      <c r="G794" t="s">
         <v>1908</v>
-      </c>
-      <c r="G794" t="s">
-        <v>1758</v>
       </c>
     </row>
     <row r="795" spans="1:7">
@@ -25608,10 +25608,10 @@
         <v>1852</v>
       </c>
       <c r="F795" t="s">
+        <v>1853</v>
+      </c>
+      <c r="G795" t="s">
         <v>1857</v>
-      </c>
-      <c r="G795" t="s">
-        <v>1854</v>
       </c>
     </row>
     <row r="796" spans="1:7">
@@ -25631,10 +25631,10 @@
         <v>1852</v>
       </c>
       <c r="F796" t="s">
+        <v>1853</v>
+      </c>
+      <c r="G796" t="s">
         <v>1857</v>
-      </c>
-      <c r="G796" t="s">
-        <v>1854</v>
       </c>
     </row>
     <row r="797" spans="1:7">
@@ -25677,10 +25677,10 @@
         <v>1852</v>
       </c>
       <c r="F798" t="s">
+        <v>1853</v>
+      </c>
+      <c r="G798" t="s">
         <v>1919</v>
-      </c>
-      <c r="G798" t="s">
-        <v>1854</v>
       </c>
     </row>
     <row r="799" spans="1:7">
@@ -25700,10 +25700,10 @@
         <v>1852</v>
       </c>
       <c r="F799" t="s">
+        <v>1853</v>
+      </c>
+      <c r="G799" t="s">
         <v>1857</v>
-      </c>
-      <c r="G799" t="s">
-        <v>1854</v>
       </c>
     </row>
     <row r="800" spans="1:7">
@@ -25746,10 +25746,10 @@
         <v>1852</v>
       </c>
       <c r="F801" t="s">
+        <v>1853</v>
+      </c>
+      <c r="G801" t="s">
         <v>1926</v>
-      </c>
-      <c r="G801" t="s">
-        <v>1854</v>
       </c>
     </row>
     <row r="802" spans="1:7">
@@ -25769,10 +25769,10 @@
         <v>1852</v>
       </c>
       <c r="F802" t="s">
+        <v>1853</v>
+      </c>
+      <c r="G802" t="s">
         <v>1857</v>
-      </c>
-      <c r="G802" t="s">
-        <v>1854</v>
       </c>
     </row>
     <row r="803" spans="1:7">
@@ -25792,10 +25792,10 @@
         <v>1852</v>
       </c>
       <c r="F803" t="s">
+        <v>1853</v>
+      </c>
+      <c r="G803" t="s">
         <v>1857</v>
-      </c>
-      <c r="G803" t="s">
-        <v>1854</v>
       </c>
     </row>
     <row r="804" spans="1:7">
@@ -25815,10 +25815,10 @@
         <v>1852</v>
       </c>
       <c r="F804" t="s">
+        <v>1853</v>
+      </c>
+      <c r="G804" t="s">
         <v>1857</v>
-      </c>
-      <c r="G804" t="s">
-        <v>1854</v>
       </c>
     </row>
     <row r="805" spans="1:7">
@@ -25838,10 +25838,10 @@
         <v>1852</v>
       </c>
       <c r="F805" t="s">
+        <v>1853</v>
+      </c>
+      <c r="G805" t="s">
         <v>1857</v>
-      </c>
-      <c r="G805" t="s">
-        <v>1854</v>
       </c>
     </row>
     <row r="806" spans="1:7">
@@ -25861,10 +25861,10 @@
         <v>1852</v>
       </c>
       <c r="F806" t="s">
+        <v>1853</v>
+      </c>
+      <c r="G806" t="s">
         <v>1857</v>
-      </c>
-      <c r="G806" t="s">
-        <v>1854</v>
       </c>
     </row>
     <row r="807" spans="1:7">
@@ -26068,10 +26068,10 @@
         <v>1938</v>
       </c>
       <c r="F815" t="s">
-        <v>1939</v>
+        <v>1943</v>
       </c>
       <c r="G815" t="s">
-        <v>1944</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="816" spans="1:7">
@@ -26091,10 +26091,10 @@
         <v>1938</v>
       </c>
       <c r="F816" t="s">
+        <v>1947</v>
+      </c>
+      <c r="G816" t="s">
         <v>1903</v>
-      </c>
-      <c r="G816" t="s">
-        <v>1948</v>
       </c>
     </row>
     <row r="817" spans="1:7">
@@ -26137,10 +26137,10 @@
         <v>1938</v>
       </c>
       <c r="F818" t="s">
-        <v>1947</v>
+        <v>1939</v>
       </c>
       <c r="G818" t="s">
-        <v>1940</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="819" spans="1:7">
@@ -26183,10 +26183,10 @@
         <v>1938</v>
       </c>
       <c r="F820" t="s">
+        <v>1971</v>
+      </c>
+      <c r="G820" t="s">
         <v>1903</v>
-      </c>
-      <c r="G820" t="s">
-        <v>1971</v>
       </c>
     </row>
     <row r="821" spans="1:7">
@@ -26252,10 +26252,10 @@
         <v>1938</v>
       </c>
       <c r="F823" t="s">
-        <v>1947</v>
+        <v>1939</v>
       </c>
       <c r="G823" t="s">
-        <v>1940</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="824" spans="1:7">
@@ -26275,10 +26275,10 @@
         <v>1938</v>
       </c>
       <c r="F824" t="s">
+        <v>1971</v>
+      </c>
+      <c r="G824" t="s">
         <v>1981</v>
-      </c>
-      <c r="G824" t="s">
-        <v>1971</v>
       </c>
     </row>
     <row r="825" spans="1:7">
@@ -26574,10 +26574,10 @@
         <v>2010</v>
       </c>
       <c r="F837" t="s">
+        <v>2011</v>
+      </c>
+      <c r="G837" t="s">
         <v>2015</v>
-      </c>
-      <c r="G837" t="s">
-        <v>2012</v>
       </c>
     </row>
     <row r="838" spans="1:7">
@@ -26643,10 +26643,10 @@
         <v>2010</v>
       </c>
       <c r="F840" t="s">
+        <v>2011</v>
+      </c>
+      <c r="G840" t="s">
         <v>2015</v>
-      </c>
-      <c r="G840" t="s">
-        <v>2012</v>
       </c>
     </row>
     <row r="841" spans="1:7">
@@ -26666,10 +26666,10 @@
         <v>2010</v>
       </c>
       <c r="F841" t="s">
+        <v>2011</v>
+      </c>
+      <c r="G841" t="s">
         <v>2015</v>
-      </c>
-      <c r="G841" t="s">
-        <v>2012</v>
       </c>
     </row>
     <row r="842" spans="1:7">
@@ -26689,10 +26689,10 @@
         <v>2010</v>
       </c>
       <c r="F842" t="s">
+        <v>2011</v>
+      </c>
+      <c r="G842" t="s">
         <v>2030</v>
-      </c>
-      <c r="G842" t="s">
-        <v>2012</v>
       </c>
     </row>
     <row r="843" spans="1:7">
@@ -26712,10 +26712,10 @@
         <v>2010</v>
       </c>
       <c r="F843" t="s">
+        <v>2011</v>
+      </c>
+      <c r="G843" t="s">
         <v>2015</v>
-      </c>
-      <c r="G843" t="s">
-        <v>2012</v>
       </c>
     </row>
     <row r="844" spans="1:7">
@@ -26735,10 +26735,10 @@
         <v>2010</v>
       </c>
       <c r="F844" t="s">
+        <v>2011</v>
+      </c>
+      <c r="G844" t="s">
         <v>2015</v>
-      </c>
-      <c r="G844" t="s">
-        <v>2012</v>
       </c>
     </row>
     <row r="845" spans="1:7">
@@ -26758,10 +26758,10 @@
         <v>2010</v>
       </c>
       <c r="F845" t="s">
+        <v>2011</v>
+      </c>
+      <c r="G845" t="s">
         <v>2015</v>
-      </c>
-      <c r="G845" t="s">
-        <v>2012</v>
       </c>
     </row>
     <row r="846" spans="1:7">
@@ -26781,10 +26781,10 @@
         <v>2010</v>
       </c>
       <c r="F846" t="s">
+        <v>2011</v>
+      </c>
+      <c r="G846" t="s">
         <v>2015</v>
-      </c>
-      <c r="G846" t="s">
-        <v>2012</v>
       </c>
     </row>
     <row r="847" spans="1:7">
@@ -26804,10 +26804,10 @@
         <v>2010</v>
       </c>
       <c r="F847" t="s">
+        <v>2011</v>
+      </c>
+      <c r="G847" t="s">
         <v>2015</v>
-      </c>
-      <c r="G847" t="s">
-        <v>2012</v>
       </c>
     </row>
     <row r="848" spans="1:7">
@@ -26827,10 +26827,10 @@
         <v>2010</v>
       </c>
       <c r="F848" t="s">
+        <v>2011</v>
+      </c>
+      <c r="G848" t="s">
         <v>2015</v>
-      </c>
-      <c r="G848" t="s">
-        <v>2012</v>
       </c>
     </row>
     <row r="849" spans="1:7">
@@ -26850,10 +26850,10 @@
         <v>2010</v>
       </c>
       <c r="F849" t="s">
+        <v>2011</v>
+      </c>
+      <c r="G849" t="s">
         <v>2015</v>
-      </c>
-      <c r="G849" t="s">
-        <v>2012</v>
       </c>
     </row>
     <row r="850" spans="1:7">
@@ -26873,10 +26873,10 @@
         <v>2010</v>
       </c>
       <c r="F850" t="s">
-        <v>2011</v>
+        <v>2047</v>
       </c>
       <c r="G850" t="s">
-        <v>2047</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="851" spans="1:7">
@@ -26896,10 +26896,10 @@
         <v>2010</v>
       </c>
       <c r="F851" t="s">
+        <v>2011</v>
+      </c>
+      <c r="G851" t="s">
         <v>2015</v>
-      </c>
-      <c r="G851" t="s">
-        <v>2012</v>
       </c>
     </row>
     <row r="852" spans="1:7">
@@ -26919,10 +26919,10 @@
         <v>2010</v>
       </c>
       <c r="F852" t="s">
+        <v>2052</v>
+      </c>
+      <c r="G852" t="s">
         <v>2030</v>
-      </c>
-      <c r="G852" t="s">
-        <v>2052</v>
       </c>
     </row>
     <row r="853" spans="1:7">
@@ -26942,10 +26942,10 @@
         <v>2010</v>
       </c>
       <c r="F853" t="s">
+        <v>2047</v>
+      </c>
+      <c r="G853" t="s">
         <v>2055</v>
-      </c>
-      <c r="G853" t="s">
-        <v>2047</v>
       </c>
     </row>
     <row r="854" spans="1:7">
@@ -26965,10 +26965,10 @@
         <v>2010</v>
       </c>
       <c r="F854" t="s">
+        <v>2011</v>
+      </c>
+      <c r="G854" t="s">
         <v>2015</v>
-      </c>
-      <c r="G854" t="s">
-        <v>2012</v>
       </c>
     </row>
     <row r="855" spans="1:7">
@@ -26988,10 +26988,10 @@
         <v>2010</v>
       </c>
       <c r="F855" t="s">
+        <v>2060</v>
+      </c>
+      <c r="G855" t="s">
         <v>2015</v>
-      </c>
-      <c r="G855" t="s">
-        <v>2060</v>
       </c>
     </row>
     <row r="856" spans="1:7">
@@ -27011,10 +27011,10 @@
         <v>2010</v>
       </c>
       <c r="F856" t="s">
+        <v>2011</v>
+      </c>
+      <c r="G856" t="s">
         <v>2063</v>
-      </c>
-      <c r="G856" t="s">
-        <v>2012</v>
       </c>
     </row>
     <row r="857" spans="1:7">
@@ -27034,10 +27034,10 @@
         <v>2010</v>
       </c>
       <c r="F857" t="s">
+        <v>2011</v>
+      </c>
+      <c r="G857" t="s">
         <v>2015</v>
-      </c>
-      <c r="G857" t="s">
-        <v>2012</v>
       </c>
     </row>
     <row r="858" spans="1:7">
@@ -27103,10 +27103,10 @@
         <v>2010</v>
       </c>
       <c r="F860" t="s">
+        <v>2011</v>
+      </c>
+      <c r="G860" t="s">
         <v>2015</v>
-      </c>
-      <c r="G860" t="s">
-        <v>2012</v>
       </c>
     </row>
     <row r="861" spans="1:7">
@@ -27126,10 +27126,10 @@
         <v>2010</v>
       </c>
       <c r="F861" t="s">
+        <v>2011</v>
+      </c>
+      <c r="G861" t="s">
         <v>2015</v>
-      </c>
-      <c r="G861" t="s">
-        <v>2012</v>
       </c>
     </row>
     <row r="862" spans="1:7">
@@ -27149,10 +27149,10 @@
         <v>2010</v>
       </c>
       <c r="F862" t="s">
+        <v>2011</v>
+      </c>
+      <c r="G862" t="s">
         <v>2015</v>
-      </c>
-      <c r="G862" t="s">
-        <v>2012</v>
       </c>
     </row>
     <row r="863" spans="1:7">
@@ -27172,10 +27172,10 @@
         <v>2010</v>
       </c>
       <c r="F863" t="s">
+        <v>2011</v>
+      </c>
+      <c r="G863" t="s">
         <v>2015</v>
-      </c>
-      <c r="G863" t="s">
-        <v>2012</v>
       </c>
     </row>
     <row r="864" spans="1:7">
@@ -27195,10 +27195,10 @@
         <v>2010</v>
       </c>
       <c r="F864" t="s">
+        <v>2011</v>
+      </c>
+      <c r="G864" t="s">
         <v>2015</v>
-      </c>
-      <c r="G864" t="s">
-        <v>2012</v>
       </c>
     </row>
     <row r="865" spans="1:7">
@@ -27218,10 +27218,10 @@
         <v>2010</v>
       </c>
       <c r="F865" t="s">
+        <v>2011</v>
+      </c>
+      <c r="G865" t="s">
         <v>2015</v>
-      </c>
-      <c r="G865" t="s">
-        <v>2012</v>
       </c>
     </row>
     <row r="866" spans="1:7">
@@ -27241,10 +27241,10 @@
         <v>2010</v>
       </c>
       <c r="F866" t="s">
+        <v>2011</v>
+      </c>
+      <c r="G866" t="s">
         <v>2015</v>
-      </c>
-      <c r="G866" t="s">
-        <v>2012</v>
       </c>
     </row>
     <row r="867" spans="1:7">
@@ -27264,10 +27264,10 @@
         <v>2010</v>
       </c>
       <c r="F867" t="s">
+        <v>2011</v>
+      </c>
+      <c r="G867" t="s">
         <v>2015</v>
-      </c>
-      <c r="G867" t="s">
-        <v>2012</v>
       </c>
     </row>
     <row r="868" spans="1:7">
@@ -27287,10 +27287,10 @@
         <v>2010</v>
       </c>
       <c r="F868" t="s">
+        <v>2011</v>
+      </c>
+      <c r="G868" t="s">
         <v>2015</v>
-      </c>
-      <c r="G868" t="s">
-        <v>2012</v>
       </c>
     </row>
     <row r="869" spans="1:7">
@@ -27448,10 +27448,10 @@
         <v>2093</v>
       </c>
       <c r="F875" t="s">
-        <v>2103</v>
+        <v>2094</v>
       </c>
       <c r="G875" t="s">
-        <v>2095</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="876" spans="1:7">
@@ -27494,10 +27494,10 @@
         <v>2093</v>
       </c>
       <c r="F877" t="s">
-        <v>2103</v>
+        <v>2094</v>
       </c>
       <c r="G877" t="s">
-        <v>2095</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="878" spans="1:7">
@@ -27724,10 +27724,10 @@
         <v>2093</v>
       </c>
       <c r="F887" t="s">
-        <v>2134</v>
+        <v>2094</v>
       </c>
       <c r="G887" t="s">
-        <v>2095</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="888" spans="1:7">
@@ -27862,10 +27862,10 @@
         <v>2093</v>
       </c>
       <c r="F893" t="s">
-        <v>2134</v>
+        <v>2094</v>
       </c>
       <c r="G893" t="s">
-        <v>2095</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="894" spans="1:7">
@@ -27908,10 +27908,10 @@
         <v>2093</v>
       </c>
       <c r="F895" t="s">
-        <v>2103</v>
+        <v>2094</v>
       </c>
       <c r="G895" t="s">
-        <v>2095</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="896" spans="1:7">
@@ -27931,10 +27931,10 @@
         <v>2093</v>
       </c>
       <c r="F896" t="s">
-        <v>2103</v>
+        <v>2094</v>
       </c>
       <c r="G896" t="s">
-        <v>2095</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="897" spans="1:7">
@@ -28161,10 +28161,10 @@
         <v>2172</v>
       </c>
       <c r="F906" t="s">
+        <v>2173</v>
+      </c>
+      <c r="G906" t="s">
         <v>2177</v>
-      </c>
-      <c r="G906" t="s">
-        <v>2174</v>
       </c>
     </row>
     <row r="907" spans="1:7">
@@ -28184,10 +28184,10 @@
         <v>2172</v>
       </c>
       <c r="F907" t="s">
+        <v>2173</v>
+      </c>
+      <c r="G907" t="s">
         <v>2177</v>
-      </c>
-      <c r="G907" t="s">
-        <v>2174</v>
       </c>
     </row>
     <row r="908" spans="1:7">
@@ -28207,10 +28207,10 @@
         <v>2172</v>
       </c>
       <c r="F908" t="s">
+        <v>2173</v>
+      </c>
+      <c r="G908" t="s">
         <v>2177</v>
-      </c>
-      <c r="G908" t="s">
-        <v>2174</v>
       </c>
     </row>
     <row r="909" spans="1:7">
@@ -28230,10 +28230,10 @@
         <v>2172</v>
       </c>
       <c r="F909" t="s">
+        <v>2173</v>
+      </c>
+      <c r="G909" t="s">
         <v>2177</v>
-      </c>
-      <c r="G909" t="s">
-        <v>2174</v>
       </c>
     </row>
     <row r="910" spans="1:7">
@@ -28253,10 +28253,10 @@
         <v>2172</v>
       </c>
       <c r="F910" t="s">
+        <v>2173</v>
+      </c>
+      <c r="G910" t="s">
         <v>2177</v>
-      </c>
-      <c r="G910" t="s">
-        <v>2174</v>
       </c>
     </row>
     <row r="911" spans="1:7">
@@ -28276,10 +28276,10 @@
         <v>2172</v>
       </c>
       <c r="F911" t="s">
+        <v>2173</v>
+      </c>
+      <c r="G911" t="s">
         <v>2177</v>
-      </c>
-      <c r="G911" t="s">
-        <v>2174</v>
       </c>
     </row>
     <row r="912" spans="1:7">
@@ -28299,10 +28299,10 @@
         <v>2172</v>
       </c>
       <c r="F912" t="s">
+        <v>2173</v>
+      </c>
+      <c r="G912" t="s">
         <v>2177</v>
-      </c>
-      <c r="G912" t="s">
-        <v>2174</v>
       </c>
     </row>
     <row r="913" spans="1:7">
@@ -28322,10 +28322,10 @@
         <v>2172</v>
       </c>
       <c r="F913" t="s">
+        <v>2173</v>
+      </c>
+      <c r="G913" t="s">
         <v>2177</v>
-      </c>
-      <c r="G913" t="s">
-        <v>2174</v>
       </c>
     </row>
     <row r="914" spans="1:7">
@@ -28345,10 +28345,10 @@
         <v>2172</v>
       </c>
       <c r="F914" t="s">
+        <v>2103</v>
+      </c>
+      <c r="G914" t="s">
         <v>2194</v>
-      </c>
-      <c r="G914" t="s">
-        <v>2104</v>
       </c>
     </row>
     <row r="915" spans="1:7">
@@ -28368,10 +28368,10 @@
         <v>2172</v>
       </c>
       <c r="F915" t="s">
+        <v>2103</v>
+      </c>
+      <c r="G915" t="s">
         <v>2194</v>
-      </c>
-      <c r="G915" t="s">
-        <v>2104</v>
       </c>
     </row>
     <row r="916" spans="1:7">
@@ -28391,10 +28391,10 @@
         <v>2172</v>
       </c>
       <c r="F916" t="s">
+        <v>2103</v>
+      </c>
+      <c r="G916" t="s">
         <v>2194</v>
-      </c>
-      <c r="G916" t="s">
-        <v>2104</v>
       </c>
     </row>
     <row r="917" spans="1:7">
@@ -28414,10 +28414,10 @@
         <v>2172</v>
       </c>
       <c r="F917" t="s">
+        <v>2103</v>
+      </c>
+      <c r="G917" t="s">
         <v>2194</v>
-      </c>
-      <c r="G917" t="s">
-        <v>2104</v>
       </c>
     </row>
     <row r="918" spans="1:7">
@@ -28437,10 +28437,10 @@
         <v>2172</v>
       </c>
       <c r="F918" t="s">
+        <v>2202</v>
+      </c>
+      <c r="G918" t="s">
         <v>2194</v>
-      </c>
-      <c r="G918" t="s">
-        <v>2202</v>
       </c>
     </row>
     <row r="919" spans="1:7">
@@ -28460,10 +28460,10 @@
         <v>2172</v>
       </c>
       <c r="F919" t="s">
+        <v>2103</v>
+      </c>
+      <c r="G919" t="s">
         <v>2194</v>
-      </c>
-      <c r="G919" t="s">
-        <v>2104</v>
       </c>
     </row>
     <row r="920" spans="1:7">
@@ -28483,10 +28483,10 @@
         <v>2172</v>
       </c>
       <c r="F920" t="s">
+        <v>2103</v>
+      </c>
+      <c r="G920" t="s">
         <v>2194</v>
-      </c>
-      <c r="G920" t="s">
-        <v>2104</v>
       </c>
     </row>
     <row r="921" spans="1:7">
@@ -28506,10 +28506,10 @@
         <v>2172</v>
       </c>
       <c r="F921" t="s">
+        <v>2173</v>
+      </c>
+      <c r="G921" t="s">
         <v>2177</v>
-      </c>
-      <c r="G921" t="s">
-        <v>2174</v>
       </c>
     </row>
     <row r="922" spans="1:7">
@@ -28529,10 +28529,10 @@
         <v>2172</v>
       </c>
       <c r="F922" t="s">
+        <v>2173</v>
+      </c>
+      <c r="G922" t="s">
         <v>2177</v>
-      </c>
-      <c r="G922" t="s">
-        <v>2174</v>
       </c>
     </row>
     <row r="923" spans="1:7">
@@ -28552,10 +28552,10 @@
         <v>2172</v>
       </c>
       <c r="F923" t="s">
+        <v>2173</v>
+      </c>
+      <c r="G923" t="s">
         <v>2177</v>
-      </c>
-      <c r="G923" t="s">
-        <v>2174</v>
       </c>
     </row>
     <row r="924" spans="1:7">
@@ -28575,10 +28575,10 @@
         <v>2172</v>
       </c>
       <c r="F924" t="s">
+        <v>2173</v>
+      </c>
+      <c r="G924" t="s">
         <v>2177</v>
-      </c>
-      <c r="G924" t="s">
-        <v>2174</v>
       </c>
     </row>
     <row r="925" spans="1:7">
@@ -28598,10 +28598,10 @@
         <v>2172</v>
       </c>
       <c r="F925" t="s">
+        <v>2173</v>
+      </c>
+      <c r="G925" t="s">
         <v>2177</v>
-      </c>
-      <c r="G925" t="s">
-        <v>2174</v>
       </c>
     </row>
     <row r="926" spans="1:7">
@@ -28621,10 +28621,10 @@
         <v>2172</v>
       </c>
       <c r="F926" t="s">
+        <v>2173</v>
+      </c>
+      <c r="G926" t="s">
         <v>2177</v>
-      </c>
-      <c r="G926" t="s">
-        <v>2174</v>
       </c>
     </row>
     <row r="927" spans="1:7">
@@ -28644,10 +28644,10 @@
         <v>2172</v>
       </c>
       <c r="F927" t="s">
+        <v>2173</v>
+      </c>
+      <c r="G927" t="s">
         <v>2177</v>
-      </c>
-      <c r="G927" t="s">
-        <v>2174</v>
       </c>
     </row>
     <row r="928" spans="1:7">
@@ -28667,10 +28667,10 @@
         <v>2172</v>
       </c>
       <c r="F928" t="s">
+        <v>2173</v>
+      </c>
+      <c r="G928" t="s">
         <v>2177</v>
-      </c>
-      <c r="G928" t="s">
-        <v>2174</v>
       </c>
     </row>
     <row r="929" spans="1:7">
@@ -28690,10 +28690,10 @@
         <v>2172</v>
       </c>
       <c r="F929" t="s">
+        <v>2173</v>
+      </c>
+      <c r="G929" t="s">
         <v>2177</v>
-      </c>
-      <c r="G929" t="s">
-        <v>2174</v>
       </c>
     </row>
     <row r="930" spans="1:7">
@@ -28713,10 +28713,10 @@
         <v>2172</v>
       </c>
       <c r="F930" t="s">
+        <v>2173</v>
+      </c>
+      <c r="G930" t="s">
         <v>2177</v>
-      </c>
-      <c r="G930" t="s">
-        <v>2174</v>
       </c>
     </row>
     <row r="931" spans="1:7">
@@ -28736,10 +28736,10 @@
         <v>2172</v>
       </c>
       <c r="F931" t="s">
+        <v>2173</v>
+      </c>
+      <c r="G931" t="s">
         <v>2177</v>
-      </c>
-      <c r="G931" t="s">
-        <v>2174</v>
       </c>
     </row>
     <row r="932" spans="1:7">
@@ -28759,10 +28759,10 @@
         <v>2172</v>
       </c>
       <c r="F932" t="s">
+        <v>2173</v>
+      </c>
+      <c r="G932" t="s">
         <v>2177</v>
-      </c>
-      <c r="G932" t="s">
-        <v>2174</v>
       </c>
     </row>
     <row r="933" spans="1:7">
@@ -28782,10 +28782,10 @@
         <v>2172</v>
       </c>
       <c r="F933" t="s">
+        <v>2173</v>
+      </c>
+      <c r="G933" t="s">
         <v>2177</v>
-      </c>
-      <c r="G933" t="s">
-        <v>2174</v>
       </c>
     </row>
     <row r="934" spans="1:7">
@@ -28805,10 +28805,10 @@
         <v>2172</v>
       </c>
       <c r="F934" t="s">
+        <v>2173</v>
+      </c>
+      <c r="G934" t="s">
         <v>2177</v>
-      </c>
-      <c r="G934" t="s">
-        <v>2174</v>
       </c>
     </row>
     <row r="935" spans="1:7">
@@ -28851,10 +28851,10 @@
         <v>2236</v>
       </c>
       <c r="F936" t="s">
-        <v>2237</v>
+        <v>2241</v>
       </c>
       <c r="G936" t="s">
-        <v>2241</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="937" spans="1:7">
@@ -28874,10 +28874,10 @@
         <v>2236</v>
       </c>
       <c r="F937" t="s">
-        <v>2237</v>
+        <v>2241</v>
       </c>
       <c r="G937" t="s">
-        <v>2241</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="938" spans="1:7">
@@ -28897,10 +28897,10 @@
         <v>2236</v>
       </c>
       <c r="F938" t="s">
-        <v>2237</v>
+        <v>2241</v>
       </c>
       <c r="G938" t="s">
-        <v>2241</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="939" spans="1:7">
@@ -28920,10 +28920,10 @@
         <v>2236</v>
       </c>
       <c r="F939" t="s">
-        <v>2237</v>
+        <v>2241</v>
       </c>
       <c r="G939" t="s">
-        <v>2241</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="940" spans="1:7">
@@ -28943,10 +28943,10 @@
         <v>2236</v>
       </c>
       <c r="F940" t="s">
-        <v>2237</v>
+        <v>2241</v>
       </c>
       <c r="G940" t="s">
-        <v>2241</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="941" spans="1:7">
@@ -28966,10 +28966,10 @@
         <v>2236</v>
       </c>
       <c r="F941" t="s">
-        <v>2237</v>
+        <v>2241</v>
       </c>
       <c r="G941" t="s">
-        <v>2241</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="942" spans="1:7">
@@ -28989,10 +28989,10 @@
         <v>2236</v>
       </c>
       <c r="F942" t="s">
-        <v>2237</v>
+        <v>2241</v>
       </c>
       <c r="G942" t="s">
-        <v>2241</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="943" spans="1:7">
@@ -29012,10 +29012,10 @@
         <v>2236</v>
       </c>
       <c r="F943" t="s">
-        <v>2237</v>
+        <v>2241</v>
       </c>
       <c r="G943" t="s">
-        <v>2241</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="944" spans="1:7">
@@ -29035,10 +29035,10 @@
         <v>2236</v>
       </c>
       <c r="F944" t="s">
-        <v>2237</v>
+        <v>2241</v>
       </c>
       <c r="G944" t="s">
-        <v>2241</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="945" spans="1:7">
@@ -29058,10 +29058,10 @@
         <v>2236</v>
       </c>
       <c r="F945" t="s">
-        <v>2237</v>
+        <v>2241</v>
       </c>
       <c r="G945" t="s">
-        <v>2241</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="946" spans="1:7">
@@ -29081,10 +29081,10 @@
         <v>2236</v>
       </c>
       <c r="F946" t="s">
-        <v>2237</v>
+        <v>2241</v>
       </c>
       <c r="G946" t="s">
-        <v>2241</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="947" spans="1:7">
@@ -29104,10 +29104,10 @@
         <v>2236</v>
       </c>
       <c r="F947" t="s">
-        <v>2237</v>
+        <v>2241</v>
       </c>
       <c r="G947" t="s">
-        <v>2241</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="948" spans="1:7">
@@ -29127,10 +29127,10 @@
         <v>2236</v>
       </c>
       <c r="F948" t="s">
-        <v>2237</v>
+        <v>2241</v>
       </c>
       <c r="G948" t="s">
-        <v>2241</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="949" spans="1:7">
@@ -29150,10 +29150,10 @@
         <v>2236</v>
       </c>
       <c r="F949" t="s">
-        <v>2237</v>
+        <v>2241</v>
       </c>
       <c r="G949" t="s">
-        <v>2241</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="950" spans="1:7">
@@ -29173,10 +29173,10 @@
         <v>2236</v>
       </c>
       <c r="F950" t="s">
-        <v>2237</v>
+        <v>2241</v>
       </c>
       <c r="G950" t="s">
-        <v>2241</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="951" spans="1:7">
@@ -29196,10 +29196,10 @@
         <v>2236</v>
       </c>
       <c r="F951" t="s">
-        <v>2237</v>
+        <v>2241</v>
       </c>
       <c r="G951" t="s">
-        <v>2241</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="952" spans="1:7">
@@ -29219,10 +29219,10 @@
         <v>2236</v>
       </c>
       <c r="F952" t="s">
-        <v>2237</v>
+        <v>2241</v>
       </c>
       <c r="G952" t="s">
-        <v>2241</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="953" spans="1:7">
@@ -29242,10 +29242,10 @@
         <v>2236</v>
       </c>
       <c r="F953" t="s">
-        <v>2237</v>
+        <v>2241</v>
       </c>
       <c r="G953" t="s">
-        <v>2241</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="954" spans="1:7">
@@ -29265,10 +29265,10 @@
         <v>2236</v>
       </c>
       <c r="F954" t="s">
-        <v>2237</v>
+        <v>2241</v>
       </c>
       <c r="G954" t="s">
-        <v>2241</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="955" spans="1:7">
@@ -29288,10 +29288,10 @@
         <v>2236</v>
       </c>
       <c r="F955" t="s">
-        <v>2237</v>
+        <v>2241</v>
       </c>
       <c r="G955" t="s">
-        <v>2241</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="956" spans="1:7">
@@ -29311,10 +29311,10 @@
         <v>2236</v>
       </c>
       <c r="F956" t="s">
-        <v>2237</v>
+        <v>2241</v>
       </c>
       <c r="G956" t="s">
-        <v>2241</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="957" spans="1:7">
@@ -29334,10 +29334,10 @@
         <v>2236</v>
       </c>
       <c r="F957" t="s">
-        <v>2237</v>
+        <v>2241</v>
       </c>
       <c r="G957" t="s">
-        <v>2241</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="958" spans="1:7">
@@ -29357,10 +29357,10 @@
         <v>2236</v>
       </c>
       <c r="F958" t="s">
-        <v>2237</v>
+        <v>2241</v>
       </c>
       <c r="G958" t="s">
-        <v>2241</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="959" spans="1:7">
@@ -29495,10 +29495,10 @@
         <v>2287</v>
       </c>
       <c r="F964" t="s">
+        <v>2288</v>
+      </c>
+      <c r="G964" t="s">
         <v>2300</v>
-      </c>
-      <c r="G964" t="s">
-        <v>2289</v>
       </c>
     </row>
     <row r="965" spans="1:7">
@@ -29518,10 +29518,10 @@
         <v>2287</v>
       </c>
       <c r="F965" t="s">
+        <v>2288</v>
+      </c>
+      <c r="G965" t="s">
         <v>2300</v>
-      </c>
-      <c r="G965" t="s">
-        <v>2289</v>
       </c>
     </row>
     <row r="966" spans="1:7">
@@ -29725,10 +29725,10 @@
         <v>2287</v>
       </c>
       <c r="F974" t="s">
+        <v>2288</v>
+      </c>
+      <c r="G974" t="s">
         <v>2320</v>
-      </c>
-      <c r="G974" t="s">
-        <v>2289</v>
       </c>
     </row>
     <row r="975" spans="1:7">
@@ -29771,10 +29771,10 @@
         <v>2287</v>
       </c>
       <c r="F976" t="s">
+        <v>2288</v>
+      </c>
+      <c r="G976" t="s">
         <v>2324</v>
-      </c>
-      <c r="G976" t="s">
-        <v>2289</v>
       </c>
     </row>
     <row r="977" spans="1:7">
@@ -29794,10 +29794,10 @@
         <v>2287</v>
       </c>
       <c r="F977" t="s">
+        <v>2288</v>
+      </c>
+      <c r="G977" t="s">
         <v>2320</v>
-      </c>
-      <c r="G977" t="s">
-        <v>2289</v>
       </c>
     </row>
   </sheetData>

--- a/api/1/clv3/xlsx/en/HumanitarianPlan.xlsx
+++ b/api/1/clv3/xlsx/en/HumanitarianPlan.xlsx
@@ -28,15 +28,15 @@
     <t>codeforiati:plan-type</t>
   </si>
   <si>
+    <t>codeforiati:plan-end-date</t>
+  </si>
+  <si>
+    <t>codeforiati:plan-start-date</t>
+  </si>
+  <si>
     <t>codeforiati:plan-year</t>
   </si>
   <si>
-    <t>codeforiati:plan-end-date</t>
-  </si>
-  <si>
-    <t>codeforiati:plan-start-date</t>
-  </si>
-  <si>
     <t>HAFG26</t>
   </si>
   <si>
@@ -49,15 +49,15 @@
     <t>Humanitarian needs and response plan</t>
   </si>
   <si>
+    <t>2026-12-31</t>
+  </si>
+  <si>
+    <t>2026-01-01</t>
+  </si>
+  <si>
     <t>2026</t>
   </si>
   <si>
-    <t>2026-12-31</t>
-  </si>
-  <si>
-    <t>2026-01-01</t>
-  </si>
-  <si>
     <t>HBFA26</t>
   </si>
   <si>
@@ -301,15 +301,15 @@
     <t>Afghanistan Humanitarian Needs and Response Plan 2025</t>
   </si>
   <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
+    <t>2025-01-01</t>
+  </si>
+  <si>
     <t>2025</t>
   </si>
   <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
-    <t>2025-01-01</t>
-  </si>
-  <si>
     <t>RIRNPAK25</t>
   </si>
   <si>
@@ -628,15 +628,15 @@
     <t>Afghanistan Humanitarian Needs and Response Plan 2024</t>
   </si>
   <si>
+    <t>2024-12-31</t>
+  </si>
+  <si>
+    <t>2024-01-01</t>
+  </si>
+  <si>
     <t>2024</t>
   </si>
   <si>
-    <t>2024-12-31</t>
-  </si>
-  <si>
-    <t>2024-01-01</t>
-  </si>
-  <si>
     <t>RAFG_RRP24</t>
   </si>
   <si>
@@ -982,15 +982,15 @@
     <t>Afghanistan Humanitarian Response Plan 2023</t>
   </si>
   <si>
+    <t>2023-12-31</t>
+  </si>
+  <si>
+    <t>2023-01-01</t>
+  </si>
+  <si>
     <t>2023</t>
   </si>
   <si>
-    <t>2023-12-31</t>
-  </si>
-  <si>
-    <t>2023-01-01</t>
-  </si>
-  <si>
     <t>RAFG23</t>
   </si>
   <si>
@@ -1300,15 +1300,15 @@
     <t>Afghanistan Humanitarian Response Plan 2022</t>
   </si>
   <si>
+    <t>2022-12-31</t>
+  </si>
+  <si>
+    <t>2022-01-01</t>
+  </si>
+  <si>
     <t>2022</t>
   </si>
   <si>
-    <t>2022-12-31</t>
-  </si>
-  <si>
-    <t>2022-01-01</t>
-  </si>
-  <si>
     <t>RAFG22</t>
   </si>
   <si>
@@ -1648,15 +1648,15 @@
     <t>Afghanistan Flash Appeal 2021</t>
   </si>
   <si>
+    <t>2021-12-31</t>
+  </si>
+  <si>
+    <t>2021-09-01</t>
+  </si>
+  <si>
     <t>2021</t>
   </si>
   <si>
-    <t>2021-12-31</t>
-  </si>
-  <si>
-    <t>2021-09-01</t>
-  </si>
-  <si>
     <t>HAFG21</t>
   </si>
   <si>
@@ -2005,15 +2005,15 @@
     <t>Afghanistan Humanitarian Response Plan 2020</t>
   </si>
   <si>
+    <t>2020-12-31</t>
+  </si>
+  <si>
+    <t>2020-01-01</t>
+  </si>
+  <si>
     <t>2020</t>
   </si>
   <si>
-    <t>2020-12-31</t>
-  </si>
-  <si>
-    <t>2020-01-01</t>
-  </si>
-  <si>
     <t>OBGD20</t>
   </si>
   <si>
@@ -2440,15 +2440,15 @@
     <t>Afghanistan Humanitarian Response Plan 2019</t>
   </si>
   <si>
+    <t>2019-12-31</t>
+  </si>
+  <si>
+    <t>2019-01-01</t>
+  </si>
+  <si>
     <t>2019</t>
   </si>
   <si>
-    <t>2019-12-31</t>
-  </si>
-  <si>
-    <t>2019-01-01</t>
-  </si>
-  <si>
     <t>RBGD19</t>
   </si>
   <si>
@@ -2677,15 +2677,15 @@
     <t>Afghanistan Humanitarian Response Plan 2018</t>
   </si>
   <si>
+    <t>2018-12-31</t>
+  </si>
+  <si>
+    <t>2018-01-01</t>
+  </si>
+  <si>
     <t>2018</t>
   </si>
   <si>
-    <t>2018-12-31</t>
-  </si>
-  <si>
-    <t>2018-01-01</t>
-  </si>
-  <si>
     <t>OBGD18</t>
   </si>
   <si>
@@ -2902,15 +2902,15 @@
     <t>Regional Refugee and Migrant Response Plan for Europe 2017</t>
   </si>
   <si>
+    <t>2017-12-31</t>
+  </si>
+  <si>
+    <t>2017-01-01</t>
+  </si>
+  <si>
     <t>2017</t>
   </si>
   <si>
-    <t>2017-12-31</t>
-  </si>
-  <si>
-    <t>2017-01-01</t>
-  </si>
-  <si>
     <t>HAFG17</t>
   </si>
   <si>
@@ -3193,15 +3193,15 @@
     <t>Regional Refugee and Migrant Response Plan for Europe 2016</t>
   </si>
   <si>
+    <t>2016-12-31</t>
+  </si>
+  <si>
+    <t>2016-01-01</t>
+  </si>
+  <si>
     <t>2016</t>
   </si>
   <si>
-    <t>2016-12-31</t>
-  </si>
-  <si>
-    <t>2016-01-01</t>
-  </si>
-  <si>
     <t>HAFG16</t>
   </si>
   <si>
@@ -3478,15 +3478,15 @@
     <t>Strategic response plan</t>
   </si>
   <si>
+    <t>2015-12-31</t>
+  </si>
+  <si>
+    <t>2015-01-01</t>
+  </si>
+  <si>
     <t>2015</t>
   </si>
   <si>
-    <t>2015-12-31</t>
-  </si>
-  <si>
-    <t>2015-01-01</t>
-  </si>
-  <si>
     <t>HBFA15</t>
   </si>
   <si>
@@ -3709,15 +3709,15 @@
     <t>Afghanistan Strategic Response Plan 2014</t>
   </si>
   <si>
+    <t>2014-12-31</t>
+  </si>
+  <si>
+    <t>2014-01-01</t>
+  </si>
+  <si>
     <t>2014</t>
   </si>
   <si>
-    <t>2014-12-31</t>
-  </si>
-  <si>
-    <t>2014-01-01</t>
-  </si>
-  <si>
     <t>HBFA1314</t>
   </si>
   <si>
@@ -4003,12 +4003,12 @@
     <t>Consolidated appeals process</t>
   </si>
   <si>
+    <t>2013-12-31</t>
+  </si>
+  <si>
     <t>2013</t>
   </si>
   <si>
-    <t>2013-12-31</t>
-  </si>
-  <si>
     <t>CBFA13</t>
   </si>
   <si>
@@ -4162,15 +4162,15 @@
     <t>2012+ Kenya Emergency Humanitarian Response Plan</t>
   </si>
   <si>
+    <t>2012-12-31</t>
+  </si>
+  <si>
+    <t>2012-01-01</t>
+  </si>
+  <si>
     <t>2012</t>
   </si>
   <si>
-    <t>2012-12-31</t>
-  </si>
-  <si>
-    <t>2012-01-01</t>
-  </si>
-  <si>
     <t>CAFG1112</t>
   </si>
   <si>
@@ -4348,12 +4348,12 @@
     <t>2011+ Kenya Emergency Humanitarian Response Plan</t>
   </si>
   <si>
+    <t>2011-01-01</t>
+  </si>
+  <si>
     <t>2011</t>
   </si>
   <si>
-    <t>2011-01-01</t>
-  </si>
-  <si>
     <t>CAFG11</t>
   </si>
   <si>
@@ -4543,15 +4543,15 @@
     <t>Afghanistan Humanitarian Action Plan 2010</t>
   </si>
   <si>
+    <t>2010-12-31</t>
+  </si>
+  <si>
+    <t>2010-01-01</t>
+  </si>
+  <si>
     <t>2010</t>
   </si>
   <si>
-    <t>2010-12-31</t>
-  </si>
-  <si>
-    <t>2010-01-01</t>
-  </si>
-  <si>
     <t>OBFA1011</t>
   </si>
   <si>
@@ -4765,15 +4765,15 @@
     <t>Afghanistan Humanitarian Action Plan 2009</t>
   </si>
   <si>
+    <t>2009-12-31</t>
+  </si>
+  <si>
+    <t>2009-01-01</t>
+  </si>
+  <si>
     <t>2009</t>
   </si>
   <si>
-    <t>2009-12-31</t>
-  </si>
-  <si>
-    <t>2009-01-01</t>
-  </si>
-  <si>
     <t>FBFA0910</t>
   </si>
   <si>
@@ -4987,15 +4987,15 @@
     <t>Afghanistan Joint Appeal 2008: Humanitarian Consequences of Rise in Food Prices (February - June 2008)</t>
   </si>
   <si>
+    <t>2008-06-30</t>
+  </si>
+  <si>
+    <t>2008-02-01</t>
+  </si>
+  <si>
     <t>2008</t>
   </si>
   <si>
-    <t>2008-06-30</t>
-  </si>
-  <si>
-    <t>2008-02-01</t>
-  </si>
-  <si>
     <t>OAFG0809</t>
   </si>
   <si>
@@ -5260,15 +5260,15 @@
     <t>Bolivia Flash Appeal 2007</t>
   </si>
   <si>
+    <t>2007-08-21</t>
+  </si>
+  <si>
+    <t>2007-02-22</t>
+  </si>
+  <si>
     <t>2007</t>
   </si>
   <si>
-    <t>2007-08-21</t>
-  </si>
-  <si>
-    <t>2007-02-22</t>
-  </si>
-  <si>
     <t>FBFA0708</t>
   </si>
   <si>
@@ -5572,15 +5572,15 @@
     <t>Afghanistan Drought Joint Appeal 2006</t>
   </si>
   <si>
+    <t>2006-12-31</t>
+  </si>
+  <si>
+    <t>2006-07-01</t>
+  </si>
+  <si>
     <t>2006</t>
   </si>
   <si>
-    <t>2006-12-31</t>
-  </si>
-  <si>
-    <t>2006-07-01</t>
-  </si>
-  <si>
     <t>CBDI06</t>
   </si>
   <si>
@@ -5830,15 +5830,15 @@
     <t>Angola Marburg VHF 2005</t>
   </si>
   <si>
+    <t>2005-06-30</t>
+  </si>
+  <si>
+    <t>2005-04-01</t>
+  </si>
+  <si>
     <t>2005</t>
   </si>
   <si>
-    <t>2005-06-30</t>
-  </si>
-  <si>
-    <t>2005-04-01</t>
-  </si>
-  <si>
     <t>FBEN05</t>
   </si>
   <si>
@@ -6046,15 +6046,15 @@
     <t>Afghanistan UN-Government Drought Appeal 2004</t>
   </si>
   <si>
+    <t>2004-12-31</t>
+  </si>
+  <si>
+    <t>2004-09-01</t>
+  </si>
+  <si>
     <t>2004</t>
   </si>
   <si>
-    <t>2004-12-31</t>
-  </si>
-  <si>
-    <t>2004-09-01</t>
-  </si>
-  <si>
     <t>CAGO04</t>
   </si>
   <si>
@@ -6295,15 +6295,15 @@
     <t>Afghanistan TAPA 2003</t>
   </si>
   <si>
+    <t>2003-12-31</t>
+  </si>
+  <si>
+    <t>2003-01-01</t>
+  </si>
+  <si>
     <t>2003</t>
   </si>
   <si>
-    <t>2003-12-31</t>
-  </si>
-  <si>
-    <t>2003-01-01</t>
-  </si>
-  <si>
     <t>CAGO03</t>
   </si>
   <si>
@@ -6532,15 +6532,15 @@
     <t>Afghanistan 2002 (ITAP for the Afghan People)</t>
   </si>
   <si>
+    <t>2002-12-31</t>
+  </si>
+  <si>
+    <t>2001-10-01</t>
+  </si>
+  <si>
     <t>2002</t>
   </si>
   <si>
-    <t>2002-12-31</t>
-  </si>
-  <si>
-    <t>2001-10-01</t>
-  </si>
-  <si>
     <t>CAGO02</t>
   </si>
   <si>
@@ -6724,15 +6724,15 @@
     <t>Afghanistan 2001</t>
   </si>
   <si>
+    <t>2001-09-30</t>
+  </si>
+  <si>
+    <t>2001-01-01</t>
+  </si>
+  <si>
     <t>2001</t>
   </si>
   <si>
-    <t>2001-09-30</t>
-  </si>
-  <si>
-    <t>2001-01-01</t>
-  </si>
-  <si>
     <t>CAGO01</t>
   </si>
   <si>
@@ -6877,13 +6877,13 @@
     <t>Angola 2000</t>
   </si>
   <si>
+    <t>2000-12-31</t>
+  </si>
+  <si>
+    <t>2000-01-01</t>
+  </si>
+  <si>
     <t>2000</t>
-  </si>
-  <si>
-    <t>2000-12-31</t>
-  </si>
-  <si>
-    <t>2000-01-01</t>
   </si>
   <si>
     <t>CBDI00</t>
@@ -7550,13 +7550,13 @@
         <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="F10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G10" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -7573,13 +7573,13 @@
         <v>25</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="F11" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G11" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -7596,13 +7596,13 @@
         <v>25</v>
       </c>
       <c r="E12" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="F12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G12" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -7734,10 +7734,10 @@
         <v>22</v>
       </c>
       <c r="E18" t="s">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="F18" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="G18" t="s">
         <v>13</v>
@@ -7918,13 +7918,13 @@
         <v>22</v>
       </c>
       <c r="E26" t="s">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="F26" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="G26" t="s">
-        <v>69</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -8148,10 +8148,10 @@
         <v>22</v>
       </c>
       <c r="E36" t="s">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="F36" t="s">
-        <v>90</v>
+        <v>12</v>
       </c>
       <c r="G36" t="s">
         <v>13</v>
@@ -8240,10 +8240,10 @@
         <v>22</v>
       </c>
       <c r="E40" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="F40" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="G40" t="s">
         <v>97</v>
@@ -8335,10 +8335,10 @@
         <v>95</v>
       </c>
       <c r="F44" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="G44" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -8493,10 +8493,10 @@
         <v>25</v>
       </c>
       <c r="E51" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="F51" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="G51" t="s">
         <v>97</v>
@@ -8516,10 +8516,10 @@
         <v>25</v>
       </c>
       <c r="E52" t="s">
-        <v>95</v>
+        <v>129</v>
       </c>
       <c r="F52" t="s">
-        <v>129</v>
+        <v>96</v>
       </c>
       <c r="G52" t="s">
         <v>97</v>
@@ -8562,10 +8562,10 @@
         <v>25</v>
       </c>
       <c r="E54" t="s">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="F54" t="s">
-        <v>134</v>
+        <v>96</v>
       </c>
       <c r="G54" t="s">
         <v>97</v>
@@ -8608,10 +8608,10 @@
         <v>25</v>
       </c>
       <c r="E56" t="s">
-        <v>95</v>
+        <v>139</v>
       </c>
       <c r="F56" t="s">
-        <v>139</v>
+        <v>96</v>
       </c>
       <c r="G56" t="s">
         <v>97</v>
@@ -8634,10 +8634,10 @@
         <v>95</v>
       </c>
       <c r="F57" t="s">
-        <v>96</v>
+        <v>142</v>
       </c>
       <c r="G57" t="s">
-        <v>142</v>
+        <v>97</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -8726,10 +8726,10 @@
         <v>95</v>
       </c>
       <c r="F61" t="s">
-        <v>96</v>
+        <v>151</v>
       </c>
       <c r="G61" t="s">
-        <v>151</v>
+        <v>97</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -8746,10 +8746,10 @@
         <v>22</v>
       </c>
       <c r="E62" t="s">
-        <v>95</v>
+        <v>154</v>
       </c>
       <c r="F62" t="s">
-        <v>154</v>
+        <v>96</v>
       </c>
       <c r="G62" t="s">
         <v>97</v>
@@ -8979,10 +8979,10 @@
         <v>95</v>
       </c>
       <c r="F72" t="s">
-        <v>96</v>
+        <v>175</v>
       </c>
       <c r="G72" t="s">
-        <v>175</v>
+        <v>97</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -9160,10 +9160,10 @@
         <v>22</v>
       </c>
       <c r="E80" t="s">
-        <v>95</v>
+        <v>139</v>
       </c>
       <c r="F80" t="s">
-        <v>139</v>
+        <v>96</v>
       </c>
       <c r="G80" t="s">
         <v>97</v>
@@ -9183,10 +9183,10 @@
         <v>22</v>
       </c>
       <c r="E81" t="s">
-        <v>95</v>
+        <v>139</v>
       </c>
       <c r="F81" t="s">
-        <v>139</v>
+        <v>96</v>
       </c>
       <c r="G81" t="s">
         <v>97</v>
@@ -9209,10 +9209,10 @@
         <v>95</v>
       </c>
       <c r="F82" t="s">
-        <v>96</v>
+        <v>195</v>
       </c>
       <c r="G82" t="s">
-        <v>195</v>
+        <v>97</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -9252,10 +9252,10 @@
         <v>25</v>
       </c>
       <c r="E84" t="s">
-        <v>95</v>
+        <v>139</v>
       </c>
       <c r="F84" t="s">
-        <v>139</v>
+        <v>96</v>
       </c>
       <c r="G84" t="s">
         <v>97</v>
@@ -9275,10 +9275,10 @@
         <v>25</v>
       </c>
       <c r="E85" t="s">
-        <v>95</v>
+        <v>129</v>
       </c>
       <c r="F85" t="s">
-        <v>129</v>
+        <v>96</v>
       </c>
       <c r="G85" t="s">
         <v>97</v>
@@ -9347,10 +9347,10 @@
         <v>204</v>
       </c>
       <c r="F88" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="G88" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -9393,10 +9393,10 @@
         <v>204</v>
       </c>
       <c r="F90" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="G90" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -9554,10 +9554,10 @@
         <v>204</v>
       </c>
       <c r="F97" t="s">
-        <v>205</v>
+        <v>231</v>
       </c>
       <c r="G97" t="s">
-        <v>231</v>
+        <v>206</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -9646,10 +9646,10 @@
         <v>204</v>
       </c>
       <c r="F101" t="s">
-        <v>205</v>
+        <v>240</v>
       </c>
       <c r="G101" t="s">
-        <v>240</v>
+        <v>206</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -9669,10 +9669,10 @@
         <v>204</v>
       </c>
       <c r="F102" t="s">
-        <v>205</v>
+        <v>240</v>
       </c>
       <c r="G102" t="s">
-        <v>240</v>
+        <v>206</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -9689,10 +9689,10 @@
         <v>25</v>
       </c>
       <c r="E103" t="s">
-        <v>204</v>
+        <v>245</v>
       </c>
       <c r="F103" t="s">
-        <v>245</v>
+        <v>205</v>
       </c>
       <c r="G103" t="s">
         <v>206</v>
@@ -9712,10 +9712,10 @@
         <v>25</v>
       </c>
       <c r="E104" t="s">
-        <v>204</v>
+        <v>248</v>
       </c>
       <c r="F104" t="s">
-        <v>248</v>
+        <v>205</v>
       </c>
       <c r="G104" t="s">
         <v>206</v>
@@ -9738,10 +9738,10 @@
         <v>204</v>
       </c>
       <c r="F105" t="s">
-        <v>205</v>
+        <v>251</v>
       </c>
       <c r="G105" t="s">
-        <v>251</v>
+        <v>206</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -9781,13 +9781,13 @@
         <v>22</v>
       </c>
       <c r="E107" t="s">
-        <v>204</v>
+        <v>248</v>
       </c>
       <c r="F107" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="G107" t="s">
-        <v>256</v>
+        <v>206</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -9807,10 +9807,10 @@
         <v>204</v>
       </c>
       <c r="F108" t="s">
-        <v>205</v>
+        <v>259</v>
       </c>
       <c r="G108" t="s">
-        <v>259</v>
+        <v>206</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -9876,10 +9876,10 @@
         <v>204</v>
       </c>
       <c r="F111" t="s">
-        <v>205</v>
+        <v>266</v>
       </c>
       <c r="G111" t="s">
-        <v>266</v>
+        <v>206</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -9945,10 +9945,10 @@
         <v>204</v>
       </c>
       <c r="F114" t="s">
-        <v>205</v>
+        <v>273</v>
       </c>
       <c r="G114" t="s">
-        <v>273</v>
+        <v>206</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -10083,10 +10083,10 @@
         <v>204</v>
       </c>
       <c r="F120" t="s">
-        <v>205</v>
+        <v>231</v>
       </c>
       <c r="G120" t="s">
-        <v>231</v>
+        <v>206</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -10382,10 +10382,10 @@
         <v>204</v>
       </c>
       <c r="F133" t="s">
-        <v>205</v>
+        <v>312</v>
       </c>
       <c r="G133" t="s">
-        <v>312</v>
+        <v>206</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -10428,10 +10428,10 @@
         <v>204</v>
       </c>
       <c r="F135" t="s">
-        <v>205</v>
+        <v>317</v>
       </c>
       <c r="G135" t="s">
-        <v>317</v>
+        <v>206</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -10451,10 +10451,10 @@
         <v>204</v>
       </c>
       <c r="F136" t="s">
-        <v>205</v>
+        <v>317</v>
       </c>
       <c r="G136" t="s">
-        <v>317</v>
+        <v>206</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -10658,10 +10658,10 @@
         <v>322</v>
       </c>
       <c r="F145" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="G145" t="s">
-        <v>341</v>
+        <v>324</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -10842,10 +10842,10 @@
         <v>322</v>
       </c>
       <c r="F153" t="s">
-        <v>323</v>
+        <v>358</v>
       </c>
       <c r="G153" t="s">
-        <v>358</v>
+        <v>324</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -10908,13 +10908,13 @@
         <v>22</v>
       </c>
       <c r="E156" t="s">
-        <v>322</v>
+        <v>365</v>
       </c>
       <c r="F156" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G156" t="s">
-        <v>366</v>
+        <v>324</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -10931,13 +10931,13 @@
         <v>22</v>
       </c>
       <c r="E157" t="s">
-        <v>322</v>
+        <v>369</v>
       </c>
       <c r="F157" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="G157" t="s">
-        <v>370</v>
+        <v>324</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -11046,10 +11046,10 @@
         <v>107</v>
       </c>
       <c r="E162" t="s">
-        <v>322</v>
+        <v>369</v>
       </c>
       <c r="F162" t="s">
-        <v>369</v>
+        <v>323</v>
       </c>
       <c r="G162" t="s">
         <v>324</v>
@@ -11069,10 +11069,10 @@
         <v>22</v>
       </c>
       <c r="E163" t="s">
-        <v>322</v>
+        <v>365</v>
       </c>
       <c r="F163" t="s">
-        <v>365</v>
+        <v>323</v>
       </c>
       <c r="G163" t="s">
         <v>324</v>
@@ -11276,13 +11276,13 @@
         <v>32</v>
       </c>
       <c r="E172" t="s">
-        <v>322</v>
+        <v>400</v>
       </c>
       <c r="F172" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G172" t="s">
-        <v>401</v>
+        <v>324</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -11322,13 +11322,13 @@
         <v>25</v>
       </c>
       <c r="E174" t="s">
-        <v>322</v>
+        <v>365</v>
       </c>
       <c r="F174" t="s">
-        <v>365</v>
+        <v>406</v>
       </c>
       <c r="G174" t="s">
-        <v>406</v>
+        <v>324</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -11368,13 +11368,13 @@
         <v>25</v>
       </c>
       <c r="E176" t="s">
-        <v>322</v>
+        <v>365</v>
       </c>
       <c r="F176" t="s">
-        <v>365</v>
+        <v>411</v>
       </c>
       <c r="G176" t="s">
-        <v>411</v>
+        <v>324</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -11713,13 +11713,13 @@
         <v>22</v>
       </c>
       <c r="E191" t="s">
-        <v>428</v>
+        <v>445</v>
       </c>
       <c r="F191" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="G191" t="s">
-        <v>446</v>
+        <v>430</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -11828,13 +11828,13 @@
         <v>25</v>
       </c>
       <c r="E196" t="s">
-        <v>428</v>
+        <v>457</v>
       </c>
       <c r="F196" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="G196" t="s">
-        <v>458</v>
+        <v>430</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -11854,10 +11854,10 @@
         <v>428</v>
       </c>
       <c r="F197" t="s">
-        <v>429</v>
+        <v>458</v>
       </c>
       <c r="G197" t="s">
-        <v>458</v>
+        <v>430</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -11943,10 +11943,10 @@
         <v>25</v>
       </c>
       <c r="E201" t="s">
-        <v>428</v>
+        <v>469</v>
       </c>
       <c r="F201" t="s">
-        <v>469</v>
+        <v>429</v>
       </c>
       <c r="G201" t="s">
         <v>430</v>
@@ -12035,13 +12035,13 @@
         <v>25</v>
       </c>
       <c r="E205" t="s">
-        <v>428</v>
+        <v>478</v>
       </c>
       <c r="F205" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="G205" t="s">
-        <v>479</v>
+        <v>430</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -12081,13 +12081,13 @@
         <v>25</v>
       </c>
       <c r="E207" t="s">
-        <v>428</v>
+        <v>484</v>
       </c>
       <c r="F207" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="G207" t="s">
-        <v>485</v>
+        <v>430</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -12222,10 +12222,10 @@
         <v>428</v>
       </c>
       <c r="F213" t="s">
-        <v>429</v>
+        <v>498</v>
       </c>
       <c r="G213" t="s">
-        <v>498</v>
+        <v>430</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -12242,13 +12242,13 @@
         <v>22</v>
       </c>
       <c r="E214" t="s">
-        <v>428</v>
+        <v>500</v>
       </c>
       <c r="F214" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G214" t="s">
-        <v>498</v>
+        <v>430</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -12265,13 +12265,13 @@
         <v>22</v>
       </c>
       <c r="E215" t="s">
-        <v>428</v>
+        <v>503</v>
       </c>
       <c r="F215" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="G215" t="s">
-        <v>504</v>
+        <v>430</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -12452,10 +12452,10 @@
         <v>428</v>
       </c>
       <c r="F223" t="s">
-        <v>429</v>
+        <v>521</v>
       </c>
       <c r="G223" t="s">
-        <v>521</v>
+        <v>430</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -12567,10 +12567,10 @@
         <v>428</v>
       </c>
       <c r="F228" t="s">
-        <v>429</v>
+        <v>532</v>
       </c>
       <c r="G228" t="s">
-        <v>532</v>
+        <v>430</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -12610,13 +12610,13 @@
         <v>32</v>
       </c>
       <c r="E230" t="s">
-        <v>428</v>
+        <v>537</v>
       </c>
       <c r="F230" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="G230" t="s">
-        <v>532</v>
+        <v>430</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -12705,10 +12705,10 @@
         <v>544</v>
       </c>
       <c r="F234" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="G234" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -12728,10 +12728,10 @@
         <v>544</v>
       </c>
       <c r="F235" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="G235" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -12751,10 +12751,10 @@
         <v>544</v>
       </c>
       <c r="F236" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="G236" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="237" spans="1:7">
@@ -12774,10 +12774,10 @@
         <v>544</v>
       </c>
       <c r="F237" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="G237" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="238" spans="1:7">
@@ -12797,10 +12797,10 @@
         <v>544</v>
       </c>
       <c r="F238" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="G238" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="239" spans="1:7">
@@ -12820,10 +12820,10 @@
         <v>544</v>
       </c>
       <c r="F239" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="G239" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="240" spans="1:7">
@@ -12843,10 +12843,10 @@
         <v>544</v>
       </c>
       <c r="F240" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="G240" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="241" spans="1:7">
@@ -12866,10 +12866,10 @@
         <v>544</v>
       </c>
       <c r="F241" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="G241" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="242" spans="1:7">
@@ -12889,10 +12889,10 @@
         <v>544</v>
       </c>
       <c r="F242" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="G242" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="243" spans="1:7">
@@ -12912,10 +12912,10 @@
         <v>544</v>
       </c>
       <c r="F243" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="G243" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="244" spans="1:7">
@@ -12935,10 +12935,10 @@
         <v>544</v>
       </c>
       <c r="F244" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="G244" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="245" spans="1:7">
@@ -12958,10 +12958,10 @@
         <v>544</v>
       </c>
       <c r="F245" t="s">
-        <v>545</v>
+        <v>572</v>
       </c>
       <c r="G245" t="s">
-        <v>572</v>
+        <v>546</v>
       </c>
     </row>
     <row r="246" spans="1:7">
@@ -12978,13 +12978,13 @@
         <v>107</v>
       </c>
       <c r="E246" t="s">
-        <v>544</v>
+        <v>428</v>
       </c>
       <c r="F246" t="s">
-        <v>429</v>
+        <v>572</v>
       </c>
       <c r="G246" t="s">
-        <v>572</v>
+        <v>546</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -13001,13 +13001,13 @@
         <v>25</v>
       </c>
       <c r="E247" t="s">
-        <v>544</v>
+        <v>577</v>
       </c>
       <c r="F247" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="G247" t="s">
-        <v>578</v>
+        <v>546</v>
       </c>
     </row>
     <row r="248" spans="1:7">
@@ -13027,10 +13027,10 @@
         <v>544</v>
       </c>
       <c r="F248" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="G248" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="249" spans="1:7">
@@ -13050,10 +13050,10 @@
         <v>544</v>
       </c>
       <c r="F249" t="s">
-        <v>545</v>
+        <v>572</v>
       </c>
       <c r="G249" t="s">
-        <v>572</v>
+        <v>546</v>
       </c>
     </row>
     <row r="250" spans="1:7">
@@ -13070,13 +13070,13 @@
         <v>107</v>
       </c>
       <c r="E250" t="s">
-        <v>544</v>
+        <v>428</v>
       </c>
       <c r="F250" t="s">
-        <v>429</v>
+        <v>572</v>
       </c>
       <c r="G250" t="s">
-        <v>572</v>
+        <v>546</v>
       </c>
     </row>
     <row r="251" spans="1:7">
@@ -13093,13 +13093,13 @@
         <v>25</v>
       </c>
       <c r="E251" t="s">
-        <v>544</v>
+        <v>587</v>
       </c>
       <c r="F251" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="G251" t="s">
-        <v>588</v>
+        <v>546</v>
       </c>
     </row>
     <row r="252" spans="1:7">
@@ -13119,10 +13119,10 @@
         <v>544</v>
       </c>
       <c r="F252" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="G252" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="253" spans="1:7">
@@ -13139,13 +13139,13 @@
         <v>25</v>
       </c>
       <c r="E253" t="s">
-        <v>544</v>
+        <v>593</v>
       </c>
       <c r="F253" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="G253" t="s">
-        <v>594</v>
+        <v>546</v>
       </c>
     </row>
     <row r="254" spans="1:7">
@@ -13165,10 +13165,10 @@
         <v>544</v>
       </c>
       <c r="F254" t="s">
-        <v>545</v>
+        <v>572</v>
       </c>
       <c r="G254" t="s">
-        <v>572</v>
+        <v>546</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -13185,13 +13185,13 @@
         <v>107</v>
       </c>
       <c r="E255" t="s">
-        <v>544</v>
+        <v>428</v>
       </c>
       <c r="F255" t="s">
-        <v>429</v>
+        <v>572</v>
       </c>
       <c r="G255" t="s">
-        <v>572</v>
+        <v>546</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -13211,10 +13211,10 @@
         <v>544</v>
       </c>
       <c r="F256" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="G256" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="257" spans="1:7">
@@ -13234,10 +13234,10 @@
         <v>544</v>
       </c>
       <c r="F257" t="s">
-        <v>545</v>
+        <v>603</v>
       </c>
       <c r="G257" t="s">
-        <v>603</v>
+        <v>546</v>
       </c>
     </row>
     <row r="258" spans="1:7">
@@ -13254,13 +13254,13 @@
         <v>22</v>
       </c>
       <c r="E258" t="s">
-        <v>544</v>
+        <v>606</v>
       </c>
       <c r="F258" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="G258" t="s">
-        <v>607</v>
+        <v>546</v>
       </c>
     </row>
     <row r="259" spans="1:7">
@@ -13280,10 +13280,10 @@
         <v>544</v>
       </c>
       <c r="F259" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="G259" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="260" spans="1:7">
@@ -13300,13 +13300,13 @@
         <v>25</v>
       </c>
       <c r="E260" t="s">
-        <v>544</v>
+        <v>478</v>
       </c>
       <c r="F260" t="s">
-        <v>478</v>
+        <v>549</v>
       </c>
       <c r="G260" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="261" spans="1:7">
@@ -13326,10 +13326,10 @@
         <v>544</v>
       </c>
       <c r="F261" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="G261" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="262" spans="1:7">
@@ -13349,10 +13349,10 @@
         <v>544</v>
       </c>
       <c r="F262" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="G262" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="263" spans="1:7">
@@ -13372,10 +13372,10 @@
         <v>544</v>
       </c>
       <c r="F263" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="G263" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="264" spans="1:7">
@@ -13395,10 +13395,10 @@
         <v>544</v>
       </c>
       <c r="F264" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="G264" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="265" spans="1:7">
@@ -13418,10 +13418,10 @@
         <v>544</v>
       </c>
       <c r="F265" t="s">
-        <v>545</v>
+        <v>622</v>
       </c>
       <c r="G265" t="s">
-        <v>622</v>
+        <v>546</v>
       </c>
     </row>
     <row r="266" spans="1:7">
@@ -13441,10 +13441,10 @@
         <v>544</v>
       </c>
       <c r="F266" t="s">
-        <v>545</v>
+        <v>625</v>
       </c>
       <c r="G266" t="s">
-        <v>625</v>
+        <v>546</v>
       </c>
     </row>
     <row r="267" spans="1:7">
@@ -13464,10 +13464,10 @@
         <v>544</v>
       </c>
       <c r="F267" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="G267" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="268" spans="1:7">
@@ -13487,10 +13487,10 @@
         <v>544</v>
       </c>
       <c r="F268" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="G268" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="269" spans="1:7">
@@ -13510,10 +13510,10 @@
         <v>544</v>
       </c>
       <c r="F269" t="s">
-        <v>545</v>
+        <v>625</v>
       </c>
       <c r="G269" t="s">
-        <v>625</v>
+        <v>546</v>
       </c>
     </row>
     <row r="270" spans="1:7">
@@ -13533,10 +13533,10 @@
         <v>544</v>
       </c>
       <c r="F270" t="s">
-        <v>545</v>
+        <v>625</v>
       </c>
       <c r="G270" t="s">
-        <v>625</v>
+        <v>546</v>
       </c>
     </row>
     <row r="271" spans="1:7">
@@ -13556,10 +13556,10 @@
         <v>544</v>
       </c>
       <c r="F271" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="G271" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="272" spans="1:7">
@@ -13579,10 +13579,10 @@
         <v>544</v>
       </c>
       <c r="F272" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="G272" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="273" spans="1:7">
@@ -13602,10 +13602,10 @@
         <v>544</v>
       </c>
       <c r="F273" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="G273" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="274" spans="1:7">
@@ -13625,10 +13625,10 @@
         <v>544</v>
       </c>
       <c r="F274" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="G274" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="275" spans="1:7">
@@ -13648,10 +13648,10 @@
         <v>544</v>
       </c>
       <c r="F275" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="G275" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="276" spans="1:7">
@@ -13671,10 +13671,10 @@
         <v>544</v>
       </c>
       <c r="F276" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="G276" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="277" spans="1:7">
@@ -13694,10 +13694,10 @@
         <v>544</v>
       </c>
       <c r="F277" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="G277" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="278" spans="1:7">
@@ -13717,10 +13717,10 @@
         <v>544</v>
       </c>
       <c r="F278" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="G278" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="279" spans="1:7">
@@ -13740,10 +13740,10 @@
         <v>544</v>
       </c>
       <c r="F279" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="G279" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="280" spans="1:7">
@@ -13763,10 +13763,10 @@
         <v>544</v>
       </c>
       <c r="F280" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="G280" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="281" spans="1:7">
@@ -13786,10 +13786,10 @@
         <v>544</v>
       </c>
       <c r="F281" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="G281" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="282" spans="1:7">
@@ -13809,10 +13809,10 @@
         <v>544</v>
       </c>
       <c r="F282" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="G282" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="283" spans="1:7">
@@ -13832,10 +13832,10 @@
         <v>544</v>
       </c>
       <c r="F283" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="G283" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="284" spans="1:7">
@@ -13855,10 +13855,10 @@
         <v>544</v>
       </c>
       <c r="F284" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="G284" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="285" spans="1:7">
@@ -13901,10 +13901,10 @@
         <v>663</v>
       </c>
       <c r="F286" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G286" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
     </row>
     <row r="287" spans="1:7">
@@ -13947,10 +13947,10 @@
         <v>663</v>
       </c>
       <c r="F288" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G288" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
     </row>
     <row r="289" spans="1:7">
@@ -14039,10 +14039,10 @@
         <v>663</v>
       </c>
       <c r="F292" t="s">
-        <v>664</v>
+        <v>681</v>
       </c>
       <c r="G292" t="s">
-        <v>681</v>
+        <v>665</v>
       </c>
     </row>
     <row r="293" spans="1:7">
@@ -14082,13 +14082,13 @@
         <v>107</v>
       </c>
       <c r="E294" t="s">
-        <v>663</v>
+        <v>549</v>
       </c>
       <c r="F294" t="s">
-        <v>549</v>
+        <v>686</v>
       </c>
       <c r="G294" t="s">
-        <v>686</v>
+        <v>665</v>
       </c>
     </row>
     <row r="295" spans="1:7">
@@ -14154,10 +14154,10 @@
         <v>663</v>
       </c>
       <c r="F297" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G297" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
     </row>
     <row r="298" spans="1:7">
@@ -14177,10 +14177,10 @@
         <v>663</v>
       </c>
       <c r="F298" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G298" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
     </row>
     <row r="299" spans="1:7">
@@ -14200,10 +14200,10 @@
         <v>663</v>
       </c>
       <c r="F299" t="s">
-        <v>664</v>
+        <v>697</v>
       </c>
       <c r="G299" t="s">
-        <v>697</v>
+        <v>665</v>
       </c>
     </row>
     <row r="300" spans="1:7">
@@ -14266,13 +14266,13 @@
         <v>25</v>
       </c>
       <c r="E302" t="s">
-        <v>663</v>
+        <v>704</v>
       </c>
       <c r="F302" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="G302" t="s">
-        <v>705</v>
+        <v>665</v>
       </c>
     </row>
     <row r="303" spans="1:7">
@@ -14292,10 +14292,10 @@
         <v>663</v>
       </c>
       <c r="F303" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G303" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
     </row>
     <row r="304" spans="1:7">
@@ -14315,10 +14315,10 @@
         <v>663</v>
       </c>
       <c r="F304" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G304" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
     </row>
     <row r="305" spans="1:7">
@@ -14361,10 +14361,10 @@
         <v>663</v>
       </c>
       <c r="F306" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G306" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
     </row>
     <row r="307" spans="1:7">
@@ -14407,10 +14407,10 @@
         <v>663</v>
       </c>
       <c r="F308" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G308" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
     </row>
     <row r="309" spans="1:7">
@@ -14430,10 +14430,10 @@
         <v>663</v>
       </c>
       <c r="F309" t="s">
-        <v>664</v>
+        <v>697</v>
       </c>
       <c r="G309" t="s">
-        <v>697</v>
+        <v>665</v>
       </c>
     </row>
     <row r="310" spans="1:7">
@@ -14453,10 +14453,10 @@
         <v>663</v>
       </c>
       <c r="F310" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G310" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
     </row>
     <row r="311" spans="1:7">
@@ -14476,10 +14476,10 @@
         <v>663</v>
       </c>
       <c r="F311" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G311" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
     </row>
     <row r="312" spans="1:7">
@@ -14522,10 +14522,10 @@
         <v>663</v>
       </c>
       <c r="F313" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G313" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
     </row>
     <row r="314" spans="1:7">
@@ -14568,10 +14568,10 @@
         <v>663</v>
       </c>
       <c r="F315" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G315" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
     </row>
     <row r="316" spans="1:7">
@@ -14591,10 +14591,10 @@
         <v>663</v>
       </c>
       <c r="F316" t="s">
-        <v>664</v>
+        <v>734</v>
       </c>
       <c r="G316" t="s">
-        <v>734</v>
+        <v>665</v>
       </c>
     </row>
     <row r="317" spans="1:7">
@@ -14611,13 +14611,13 @@
         <v>25</v>
       </c>
       <c r="E317" t="s">
-        <v>663</v>
+        <v>737</v>
       </c>
       <c r="F317" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="G317" t="s">
-        <v>738</v>
+        <v>665</v>
       </c>
     </row>
     <row r="318" spans="1:7">
@@ -14637,10 +14637,10 @@
         <v>663</v>
       </c>
       <c r="F318" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G318" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
     </row>
     <row r="319" spans="1:7">
@@ -14657,13 +14657,13 @@
         <v>25</v>
       </c>
       <c r="E319" t="s">
-        <v>663</v>
+        <v>743</v>
       </c>
       <c r="F319" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="G319" t="s">
-        <v>744</v>
+        <v>665</v>
       </c>
     </row>
     <row r="320" spans="1:7">
@@ -14683,10 +14683,10 @@
         <v>663</v>
       </c>
       <c r="F320" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G320" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
     </row>
     <row r="321" spans="1:7">
@@ -14752,10 +14752,10 @@
         <v>663</v>
       </c>
       <c r="F323" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G323" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
     </row>
     <row r="324" spans="1:7">
@@ -14867,10 +14867,10 @@
         <v>663</v>
       </c>
       <c r="F328" t="s">
-        <v>664</v>
+        <v>734</v>
       </c>
       <c r="G328" t="s">
-        <v>734</v>
+        <v>665</v>
       </c>
     </row>
     <row r="329" spans="1:7">
@@ -14890,10 +14890,10 @@
         <v>663</v>
       </c>
       <c r="F329" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G329" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
     </row>
     <row r="330" spans="1:7">
@@ -14959,10 +14959,10 @@
         <v>663</v>
       </c>
       <c r="F332" t="s">
-        <v>664</v>
+        <v>734</v>
       </c>
       <c r="G332" t="s">
-        <v>734</v>
+        <v>665</v>
       </c>
     </row>
     <row r="333" spans="1:7">
@@ -14982,10 +14982,10 @@
         <v>663</v>
       </c>
       <c r="F333" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G333" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
     </row>
     <row r="334" spans="1:7">
@@ -15143,10 +15143,10 @@
         <v>663</v>
       </c>
       <c r="F340" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G340" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
     </row>
     <row r="341" spans="1:7">
@@ -15166,10 +15166,10 @@
         <v>663</v>
       </c>
       <c r="F341" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G341" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
     </row>
     <row r="342" spans="1:7">
@@ -15189,10 +15189,10 @@
         <v>663</v>
       </c>
       <c r="F342" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G342" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
     </row>
     <row r="343" spans="1:7">
@@ -15235,10 +15235,10 @@
         <v>663</v>
       </c>
       <c r="F344" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G344" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
     </row>
     <row r="345" spans="1:7">
@@ -15301,13 +15301,13 @@
         <v>22</v>
       </c>
       <c r="E347" t="s">
-        <v>663</v>
+        <v>704</v>
       </c>
       <c r="F347" t="s">
-        <v>704</v>
+        <v>801</v>
       </c>
       <c r="G347" t="s">
-        <v>801</v>
+        <v>665</v>
       </c>
     </row>
     <row r="348" spans="1:7">
@@ -15327,10 +15327,10 @@
         <v>663</v>
       </c>
       <c r="F348" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G348" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
     </row>
     <row r="349" spans="1:7">
@@ -15672,10 +15672,10 @@
         <v>808</v>
       </c>
       <c r="F363" t="s">
-        <v>809</v>
+        <v>837</v>
       </c>
       <c r="G363" t="s">
-        <v>837</v>
+        <v>810</v>
       </c>
     </row>
     <row r="364" spans="1:7">
@@ -15715,10 +15715,10 @@
         <v>25</v>
       </c>
       <c r="E365" t="s">
-        <v>808</v>
+        <v>842</v>
       </c>
       <c r="F365" t="s">
-        <v>842</v>
+        <v>809</v>
       </c>
       <c r="G365" t="s">
         <v>810</v>
@@ -15853,10 +15853,10 @@
         <v>107</v>
       </c>
       <c r="E371" t="s">
-        <v>808</v>
+        <v>855</v>
       </c>
       <c r="F371" t="s">
-        <v>855</v>
+        <v>809</v>
       </c>
       <c r="G371" t="s">
         <v>810</v>
@@ -16129,13 +16129,13 @@
         <v>25</v>
       </c>
       <c r="E383" t="s">
-        <v>808</v>
+        <v>880</v>
       </c>
       <c r="F383" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="G383" t="s">
-        <v>881</v>
+        <v>810</v>
       </c>
     </row>
     <row r="384" spans="1:7">
@@ -16152,13 +16152,13 @@
         <v>25</v>
       </c>
       <c r="E384" t="s">
-        <v>808</v>
+        <v>880</v>
       </c>
       <c r="F384" t="s">
-        <v>880</v>
+        <v>884</v>
       </c>
       <c r="G384" t="s">
-        <v>884</v>
+        <v>810</v>
       </c>
     </row>
     <row r="385" spans="1:7">
@@ -16201,10 +16201,10 @@
         <v>887</v>
       </c>
       <c r="F386" t="s">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="G386" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
     </row>
     <row r="387" spans="1:7">
@@ -16431,10 +16431,10 @@
         <v>887</v>
       </c>
       <c r="F396" t="s">
-        <v>888</v>
+        <v>913</v>
       </c>
       <c r="G396" t="s">
-        <v>913</v>
+        <v>889</v>
       </c>
     </row>
     <row r="397" spans="1:7">
@@ -16661,10 +16661,10 @@
         <v>887</v>
       </c>
       <c r="F406" t="s">
-        <v>888</v>
+        <v>934</v>
       </c>
       <c r="G406" t="s">
-        <v>934</v>
+        <v>889</v>
       </c>
     </row>
     <row r="407" spans="1:7">
@@ -16684,10 +16684,10 @@
         <v>887</v>
       </c>
       <c r="F407" t="s">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="G407" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
     </row>
     <row r="408" spans="1:7">
@@ -16773,10 +16773,10 @@
         <v>107</v>
       </c>
       <c r="E411" t="s">
-        <v>887</v>
+        <v>945</v>
       </c>
       <c r="F411" t="s">
-        <v>945</v>
+        <v>888</v>
       </c>
       <c r="G411" t="s">
         <v>889</v>
@@ -16796,13 +16796,13 @@
         <v>107</v>
       </c>
       <c r="E412" t="s">
-        <v>887</v>
+        <v>948</v>
       </c>
       <c r="F412" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="G412" t="s">
-        <v>949</v>
+        <v>889</v>
       </c>
     </row>
     <row r="413" spans="1:7">
@@ -16842,13 +16842,13 @@
         <v>107</v>
       </c>
       <c r="E414" t="s">
-        <v>887</v>
+        <v>948</v>
       </c>
       <c r="F414" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="G414" t="s">
-        <v>949</v>
+        <v>889</v>
       </c>
     </row>
     <row r="415" spans="1:7">
@@ -16983,10 +16983,10 @@
         <v>962</v>
       </c>
       <c r="F420" t="s">
-        <v>963</v>
+        <v>969</v>
       </c>
       <c r="G420" t="s">
-        <v>969</v>
+        <v>964</v>
       </c>
     </row>
     <row r="421" spans="1:7">
@@ -17121,10 +17121,10 @@
         <v>962</v>
       </c>
       <c r="F426" t="s">
-        <v>963</v>
+        <v>982</v>
       </c>
       <c r="G426" t="s">
-        <v>982</v>
+        <v>964</v>
       </c>
     </row>
     <row r="427" spans="1:7">
@@ -17144,10 +17144,10 @@
         <v>962</v>
       </c>
       <c r="F427" t="s">
-        <v>963</v>
+        <v>985</v>
       </c>
       <c r="G427" t="s">
-        <v>985</v>
+        <v>964</v>
       </c>
     </row>
     <row r="428" spans="1:7">
@@ -17187,13 +17187,13 @@
         <v>25</v>
       </c>
       <c r="E429" t="s">
-        <v>962</v>
+        <v>990</v>
       </c>
       <c r="F429" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="G429" t="s">
-        <v>991</v>
+        <v>964</v>
       </c>
     </row>
     <row r="430" spans="1:7">
@@ -17282,10 +17282,10 @@
         <v>962</v>
       </c>
       <c r="F433" t="s">
-        <v>963</v>
+        <v>1000</v>
       </c>
       <c r="G433" t="s">
-        <v>1000</v>
+        <v>964</v>
       </c>
     </row>
     <row r="434" spans="1:7">
@@ -17325,13 +17325,13 @@
         <v>25</v>
       </c>
       <c r="E435" t="s">
-        <v>962</v>
+        <v>1005</v>
       </c>
       <c r="F435" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="G435" t="s">
-        <v>1006</v>
+        <v>964</v>
       </c>
     </row>
     <row r="436" spans="1:7">
@@ -17371,13 +17371,13 @@
         <v>25</v>
       </c>
       <c r="E437" t="s">
-        <v>962</v>
+        <v>1011</v>
       </c>
       <c r="F437" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="G437" t="s">
-        <v>1012</v>
+        <v>964</v>
       </c>
     </row>
     <row r="438" spans="1:7">
@@ -17440,13 +17440,13 @@
         <v>25</v>
       </c>
       <c r="E440" t="s">
-        <v>962</v>
+        <v>1019</v>
       </c>
       <c r="F440" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="G440" t="s">
-        <v>1020</v>
+        <v>964</v>
       </c>
     </row>
     <row r="441" spans="1:7">
@@ -17578,13 +17578,13 @@
         <v>25</v>
       </c>
       <c r="E446" t="s">
-        <v>962</v>
+        <v>1033</v>
       </c>
       <c r="F446" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="G446" t="s">
-        <v>1034</v>
+        <v>964</v>
       </c>
     </row>
     <row r="447" spans="1:7">
@@ -17604,10 +17604,10 @@
         <v>962</v>
       </c>
       <c r="F447" t="s">
-        <v>963</v>
+        <v>1037</v>
       </c>
       <c r="G447" t="s">
-        <v>1037</v>
+        <v>964</v>
       </c>
     </row>
     <row r="448" spans="1:7">
@@ -17627,10 +17627,10 @@
         <v>962</v>
       </c>
       <c r="F448" t="s">
-        <v>963</v>
+        <v>1000</v>
       </c>
       <c r="G448" t="s">
-        <v>1000</v>
+        <v>964</v>
       </c>
     </row>
     <row r="449" spans="1:7">
@@ -17650,10 +17650,10 @@
         <v>962</v>
       </c>
       <c r="F449" t="s">
-        <v>963</v>
+        <v>969</v>
       </c>
       <c r="G449" t="s">
-        <v>969</v>
+        <v>964</v>
       </c>
     </row>
     <row r="450" spans="1:7">
@@ -17926,10 +17926,10 @@
         <v>1059</v>
       </c>
       <c r="F461" t="s">
-        <v>1060</v>
+        <v>1066</v>
       </c>
       <c r="G461" t="s">
-        <v>1066</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="462" spans="1:7">
@@ -17972,10 +17972,10 @@
         <v>1059</v>
       </c>
       <c r="F463" t="s">
-        <v>1060</v>
+        <v>1071</v>
       </c>
       <c r="G463" t="s">
-        <v>1071</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="464" spans="1:7">
@@ -18130,13 +18130,13 @@
         <v>25</v>
       </c>
       <c r="E470" t="s">
-        <v>1059</v>
+        <v>1086</v>
       </c>
       <c r="F470" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="G470" t="s">
-        <v>1087</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="471" spans="1:7">
@@ -18153,13 +18153,13 @@
         <v>25</v>
       </c>
       <c r="E471" t="s">
-        <v>1059</v>
+        <v>1090</v>
       </c>
       <c r="F471" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="G471" t="s">
-        <v>1091</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="472" spans="1:7">
@@ -18248,10 +18248,10 @@
         <v>1059</v>
       </c>
       <c r="F475" t="s">
-        <v>1060</v>
+        <v>1100</v>
       </c>
       <c r="G475" t="s">
-        <v>1100</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="476" spans="1:7">
@@ -18317,10 +18317,10 @@
         <v>1059</v>
       </c>
       <c r="F478" t="s">
-        <v>1060</v>
+        <v>1107</v>
       </c>
       <c r="G478" t="s">
-        <v>1107</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="479" spans="1:7">
@@ -18340,10 +18340,10 @@
         <v>1059</v>
       </c>
       <c r="F479" t="s">
-        <v>1060</v>
+        <v>1110</v>
       </c>
       <c r="G479" t="s">
-        <v>1110</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="480" spans="1:7">
@@ -18406,13 +18406,13 @@
         <v>25</v>
       </c>
       <c r="E482" t="s">
-        <v>1059</v>
+        <v>1117</v>
       </c>
       <c r="F482" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="G482" t="s">
-        <v>1118</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="483" spans="1:7">
@@ -18774,13 +18774,13 @@
         <v>107</v>
       </c>
       <c r="E498" t="s">
-        <v>1059</v>
+        <v>1149</v>
       </c>
       <c r="F498" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="G498" t="s">
-        <v>1150</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="499" spans="1:7">
@@ -19004,13 +19004,13 @@
         <v>25</v>
       </c>
       <c r="E508" t="s">
-        <v>1154</v>
+        <v>1175</v>
       </c>
       <c r="F508" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="G508" t="s">
-        <v>1176</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="509" spans="1:7">
@@ -19030,10 +19030,10 @@
         <v>1154</v>
       </c>
       <c r="F509" t="s">
-        <v>1155</v>
+        <v>1179</v>
       </c>
       <c r="G509" t="s">
-        <v>1179</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="510" spans="1:7">
@@ -19050,13 +19050,13 @@
         <v>25</v>
       </c>
       <c r="E510" t="s">
-        <v>1154</v>
+        <v>1175</v>
       </c>
       <c r="F510" t="s">
-        <v>1175</v>
+        <v>1182</v>
       </c>
       <c r="G510" t="s">
-        <v>1182</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="511" spans="1:7">
@@ -19073,13 +19073,13 @@
         <v>25</v>
       </c>
       <c r="E511" t="s">
-        <v>1154</v>
+        <v>1185</v>
       </c>
       <c r="F511" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="G511" t="s">
-        <v>1186</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="512" spans="1:7">
@@ -19119,13 +19119,13 @@
         <v>25</v>
       </c>
       <c r="E513" t="s">
-        <v>1154</v>
+        <v>1191</v>
       </c>
       <c r="F513" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="G513" t="s">
-        <v>1192</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="514" spans="1:7">
@@ -19211,13 +19211,13 @@
         <v>25</v>
       </c>
       <c r="E517" t="s">
-        <v>1154</v>
+        <v>1175</v>
       </c>
       <c r="F517" t="s">
-        <v>1175</v>
+        <v>1201</v>
       </c>
       <c r="G517" t="s">
-        <v>1201</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="518" spans="1:7">
@@ -19582,10 +19582,10 @@
         <v>1231</v>
       </c>
       <c r="F533" t="s">
-        <v>1232</v>
+        <v>1236</v>
       </c>
       <c r="G533" t="s">
-        <v>1236</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="534" spans="1:7">
@@ -19671,10 +19671,10 @@
         <v>107</v>
       </c>
       <c r="E537" t="s">
-        <v>1231</v>
+        <v>1245</v>
       </c>
       <c r="F537" t="s">
-        <v>1245</v>
+        <v>1232</v>
       </c>
       <c r="G537" t="s">
         <v>1233</v>
@@ -19717,13 +19717,13 @@
         <v>32</v>
       </c>
       <c r="E539" t="s">
-        <v>1231</v>
+        <v>1250</v>
       </c>
       <c r="F539" t="s">
-        <v>1250</v>
+        <v>1192</v>
       </c>
       <c r="G539" t="s">
-        <v>1192</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="540" spans="1:7">
@@ -19740,13 +19740,13 @@
         <v>22</v>
       </c>
       <c r="E540" t="s">
-        <v>1231</v>
+        <v>1250</v>
       </c>
       <c r="F540" t="s">
-        <v>1250</v>
+        <v>1192</v>
       </c>
       <c r="G540" t="s">
-        <v>1192</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="541" spans="1:7">
@@ -19812,10 +19812,10 @@
         <v>1231</v>
       </c>
       <c r="F543" t="s">
-        <v>1232</v>
+        <v>1259</v>
       </c>
       <c r="G543" t="s">
-        <v>1259</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="544" spans="1:7">
@@ -19904,10 +19904,10 @@
         <v>1231</v>
       </c>
       <c r="F547" t="s">
-        <v>1232</v>
+        <v>1268</v>
       </c>
       <c r="G547" t="s">
-        <v>1268</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="548" spans="1:7">
@@ -20016,13 +20016,13 @@
         <v>25</v>
       </c>
       <c r="E552" t="s">
-        <v>1231</v>
+        <v>1279</v>
       </c>
       <c r="F552" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="G552" t="s">
-        <v>1280</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="553" spans="1:7">
@@ -20039,13 +20039,13 @@
         <v>1153</v>
       </c>
       <c r="E553" t="s">
-        <v>1231</v>
+        <v>1283</v>
       </c>
       <c r="F553" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="G553" t="s">
-        <v>1284</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="554" spans="1:7">
@@ -20062,13 +20062,13 @@
         <v>107</v>
       </c>
       <c r="E554" t="s">
-        <v>1231</v>
+        <v>1287</v>
       </c>
       <c r="F554" t="s">
-        <v>1287</v>
+        <v>1284</v>
       </c>
       <c r="G554" t="s">
-        <v>1284</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="555" spans="1:7">
@@ -20085,13 +20085,13 @@
         <v>25</v>
       </c>
       <c r="E555" t="s">
-        <v>1231</v>
+        <v>1290</v>
       </c>
       <c r="F555" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="G555" t="s">
-        <v>1291</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="556" spans="1:7">
@@ -20134,10 +20134,10 @@
         <v>1231</v>
       </c>
       <c r="F557" t="s">
-        <v>1232</v>
+        <v>1296</v>
       </c>
       <c r="G557" t="s">
-        <v>1296</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="558" spans="1:7">
@@ -20177,10 +20177,10 @@
         <v>107</v>
       </c>
       <c r="E559" t="s">
-        <v>1231</v>
+        <v>1301</v>
       </c>
       <c r="F559" t="s">
-        <v>1301</v>
+        <v>1232</v>
       </c>
       <c r="G559" t="s">
         <v>1233</v>
@@ -20364,10 +20364,10 @@
         <v>1231</v>
       </c>
       <c r="F567" t="s">
-        <v>1232</v>
+        <v>1317</v>
       </c>
       <c r="G567" t="s">
-        <v>1317</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="568" spans="1:7">
@@ -20387,10 +20387,10 @@
         <v>1231</v>
       </c>
       <c r="F568" t="s">
-        <v>1232</v>
+        <v>1320</v>
       </c>
       <c r="G568" t="s">
-        <v>1320</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="569" spans="1:7">
@@ -20410,10 +20410,10 @@
         <v>1231</v>
       </c>
       <c r="F569" t="s">
-        <v>1232</v>
+        <v>1323</v>
       </c>
       <c r="G569" t="s">
-        <v>1323</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="570" spans="1:7">
@@ -20456,10 +20456,10 @@
         <v>1329</v>
       </c>
       <c r="F571" t="s">
+        <v>1236</v>
+      </c>
+      <c r="G571" t="s">
         <v>1330</v>
-      </c>
-      <c r="G571" t="s">
-        <v>1236</v>
       </c>
     </row>
     <row r="572" spans="1:7">
@@ -20479,10 +20479,10 @@
         <v>1329</v>
       </c>
       <c r="F572" t="s">
+        <v>1236</v>
+      </c>
+      <c r="G572" t="s">
         <v>1330</v>
-      </c>
-      <c r="G572" t="s">
-        <v>1236</v>
       </c>
     </row>
     <row r="573" spans="1:7">
@@ -20502,10 +20502,10 @@
         <v>1329</v>
       </c>
       <c r="F573" t="s">
+        <v>1236</v>
+      </c>
+      <c r="G573" t="s">
         <v>1330</v>
-      </c>
-      <c r="G573" t="s">
-        <v>1236</v>
       </c>
     </row>
     <row r="574" spans="1:7">
@@ -20525,10 +20525,10 @@
         <v>1329</v>
       </c>
       <c r="F574" t="s">
+        <v>1236</v>
+      </c>
+      <c r="G574" t="s">
         <v>1330</v>
-      </c>
-      <c r="G574" t="s">
-        <v>1236</v>
       </c>
     </row>
     <row r="575" spans="1:7">
@@ -20548,10 +20548,10 @@
         <v>1329</v>
       </c>
       <c r="F575" t="s">
+        <v>1339</v>
+      </c>
+      <c r="G575" t="s">
         <v>1330</v>
-      </c>
-      <c r="G575" t="s">
-        <v>1339</v>
       </c>
     </row>
     <row r="576" spans="1:7">
@@ -20568,13 +20568,13 @@
         <v>1328</v>
       </c>
       <c r="E576" t="s">
-        <v>1329</v>
+        <v>1342</v>
       </c>
       <c r="F576" t="s">
-        <v>1342</v>
+        <v>1236</v>
       </c>
       <c r="G576" t="s">
-        <v>1236</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="577" spans="1:7">
@@ -20594,10 +20594,10 @@
         <v>1329</v>
       </c>
       <c r="F577" t="s">
+        <v>1236</v>
+      </c>
+      <c r="G577" t="s">
         <v>1330</v>
-      </c>
-      <c r="G577" t="s">
-        <v>1236</v>
       </c>
     </row>
     <row r="578" spans="1:7">
@@ -20617,10 +20617,10 @@
         <v>1329</v>
       </c>
       <c r="F578" t="s">
+        <v>1236</v>
+      </c>
+      <c r="G578" t="s">
         <v>1330</v>
-      </c>
-      <c r="G578" t="s">
-        <v>1236</v>
       </c>
     </row>
     <row r="579" spans="1:7">
@@ -20640,10 +20640,10 @@
         <v>1329</v>
       </c>
       <c r="F579" t="s">
+        <v>1236</v>
+      </c>
+      <c r="G579" t="s">
         <v>1330</v>
-      </c>
-      <c r="G579" t="s">
-        <v>1236</v>
       </c>
     </row>
     <row r="580" spans="1:7">
@@ -20663,10 +20663,10 @@
         <v>1329</v>
       </c>
       <c r="F580" t="s">
+        <v>1236</v>
+      </c>
+      <c r="G580" t="s">
         <v>1330</v>
-      </c>
-      <c r="G580" t="s">
-        <v>1236</v>
       </c>
     </row>
     <row r="581" spans="1:7">
@@ -20686,10 +20686,10 @@
         <v>1329</v>
       </c>
       <c r="F581" t="s">
+        <v>1236</v>
+      </c>
+      <c r="G581" t="s">
         <v>1330</v>
-      </c>
-      <c r="G581" t="s">
-        <v>1236</v>
       </c>
     </row>
     <row r="582" spans="1:7">
@@ -20709,10 +20709,10 @@
         <v>1329</v>
       </c>
       <c r="F582" t="s">
+        <v>1355</v>
+      </c>
+      <c r="G582" t="s">
         <v>1330</v>
-      </c>
-      <c r="G582" t="s">
-        <v>1355</v>
       </c>
     </row>
     <row r="583" spans="1:7">
@@ -20732,10 +20732,10 @@
         <v>1329</v>
       </c>
       <c r="F583" t="s">
+        <v>1358</v>
+      </c>
+      <c r="G583" t="s">
         <v>1330</v>
-      </c>
-      <c r="G583" t="s">
-        <v>1358</v>
       </c>
     </row>
     <row r="584" spans="1:7">
@@ -20755,10 +20755,10 @@
         <v>1329</v>
       </c>
       <c r="F584" t="s">
+        <v>1236</v>
+      </c>
+      <c r="G584" t="s">
         <v>1330</v>
-      </c>
-      <c r="G584" t="s">
-        <v>1236</v>
       </c>
     </row>
     <row r="585" spans="1:7">
@@ -20778,10 +20778,10 @@
         <v>1329</v>
       </c>
       <c r="F585" t="s">
+        <v>1236</v>
+      </c>
+      <c r="G585" t="s">
         <v>1330</v>
-      </c>
-      <c r="G585" t="s">
-        <v>1236</v>
       </c>
     </row>
     <row r="586" spans="1:7">
@@ -20798,13 +20798,13 @@
         <v>1328</v>
       </c>
       <c r="E586" t="s">
-        <v>1329</v>
+        <v>1290</v>
       </c>
       <c r="F586" t="s">
-        <v>1290</v>
+        <v>1236</v>
       </c>
       <c r="G586" t="s">
-        <v>1236</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="587" spans="1:7">
@@ -20824,10 +20824,10 @@
         <v>1329</v>
       </c>
       <c r="F587" t="s">
+        <v>1236</v>
+      </c>
+      <c r="G587" t="s">
         <v>1330</v>
-      </c>
-      <c r="G587" t="s">
-        <v>1236</v>
       </c>
     </row>
     <row r="588" spans="1:7">
@@ -20847,10 +20847,10 @@
         <v>1329</v>
       </c>
       <c r="F588" t="s">
+        <v>1236</v>
+      </c>
+      <c r="G588" t="s">
         <v>1330</v>
-      </c>
-      <c r="G588" t="s">
-        <v>1236</v>
       </c>
     </row>
     <row r="589" spans="1:7">
@@ -20870,10 +20870,10 @@
         <v>1329</v>
       </c>
       <c r="F589" t="s">
+        <v>1236</v>
+      </c>
+      <c r="G589" t="s">
         <v>1330</v>
-      </c>
-      <c r="G589" t="s">
-        <v>1236</v>
       </c>
     </row>
     <row r="590" spans="1:7">
@@ -20893,10 +20893,10 @@
         <v>1329</v>
       </c>
       <c r="F590" t="s">
+        <v>1236</v>
+      </c>
+      <c r="G590" t="s">
         <v>1330</v>
-      </c>
-      <c r="G590" t="s">
-        <v>1236</v>
       </c>
     </row>
     <row r="591" spans="1:7">
@@ -20913,13 +20913,13 @@
         <v>32</v>
       </c>
       <c r="E591" t="s">
-        <v>1329</v>
+        <v>1375</v>
       </c>
       <c r="F591" t="s">
-        <v>1375</v>
+        <v>1236</v>
       </c>
       <c r="G591" t="s">
-        <v>1236</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="592" spans="1:7">
@@ -20939,10 +20939,10 @@
         <v>1329</v>
       </c>
       <c r="F592" t="s">
+        <v>1236</v>
+      </c>
+      <c r="G592" t="s">
         <v>1330</v>
-      </c>
-      <c r="G592" t="s">
-        <v>1236</v>
       </c>
     </row>
     <row r="593" spans="1:7">
@@ -20962,10 +20962,10 @@
         <v>1329</v>
       </c>
       <c r="F593" t="s">
+        <v>1236</v>
+      </c>
+      <c r="G593" t="s">
         <v>1330</v>
-      </c>
-      <c r="G593" t="s">
-        <v>1236</v>
       </c>
     </row>
     <row r="594" spans="1:7">
@@ -21008,10 +21008,10 @@
         <v>1382</v>
       </c>
       <c r="F595" t="s">
-        <v>1383</v>
+        <v>1387</v>
       </c>
       <c r="G595" t="s">
-        <v>1387</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="596" spans="1:7">
@@ -21031,10 +21031,10 @@
         <v>1382</v>
       </c>
       <c r="F596" t="s">
-        <v>1383</v>
+        <v>1390</v>
       </c>
       <c r="G596" t="s">
-        <v>1390</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="597" spans="1:7">
@@ -21120,10 +21120,10 @@
         <v>1328</v>
       </c>
       <c r="E600" t="s">
-        <v>1382</v>
+        <v>1399</v>
       </c>
       <c r="F600" t="s">
-        <v>1399</v>
+        <v>1383</v>
       </c>
       <c r="G600" t="s">
         <v>1384</v>
@@ -21212,13 +21212,13 @@
         <v>25</v>
       </c>
       <c r="E604" t="s">
-        <v>1382</v>
+        <v>1408</v>
       </c>
       <c r="F604" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="G604" t="s">
-        <v>1409</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="605" spans="1:7">
@@ -21261,10 +21261,10 @@
         <v>1382</v>
       </c>
       <c r="F606" t="s">
-        <v>1383</v>
+        <v>1414</v>
       </c>
       <c r="G606" t="s">
-        <v>1414</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="607" spans="1:7">
@@ -21284,10 +21284,10 @@
         <v>1382</v>
       </c>
       <c r="F607" t="s">
-        <v>1383</v>
+        <v>1414</v>
       </c>
       <c r="G607" t="s">
-        <v>1414</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="608" spans="1:7">
@@ -21327,10 +21327,10 @@
         <v>22</v>
       </c>
       <c r="E609" t="s">
-        <v>1382</v>
+        <v>1421</v>
       </c>
       <c r="F609" t="s">
-        <v>1421</v>
+        <v>1383</v>
       </c>
       <c r="G609" t="s">
         <v>1384</v>
@@ -21465,13 +21465,13 @@
         <v>1328</v>
       </c>
       <c r="E615" t="s">
-        <v>1382</v>
+        <v>1434</v>
       </c>
       <c r="F615" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="G615" t="s">
-        <v>1435</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="616" spans="1:7">
@@ -21557,10 +21557,10 @@
         <v>1328</v>
       </c>
       <c r="E619" t="s">
+        <v>1329</v>
+      </c>
+      <c r="F619" t="s">
         <v>1444</v>
-      </c>
-      <c r="F619" t="s">
-        <v>1330</v>
       </c>
       <c r="G619" t="s">
         <v>1445</v>
@@ -21580,10 +21580,10 @@
         <v>1328</v>
       </c>
       <c r="E620" t="s">
+        <v>1448</v>
+      </c>
+      <c r="F620" t="s">
         <v>1444</v>
-      </c>
-      <c r="F620" t="s">
-        <v>1448</v>
       </c>
       <c r="G620" t="s">
         <v>1445</v>
@@ -21603,10 +21603,10 @@
         <v>1328</v>
       </c>
       <c r="E621" t="s">
+        <v>1448</v>
+      </c>
+      <c r="F621" t="s">
         <v>1444</v>
-      </c>
-      <c r="F621" t="s">
-        <v>1448</v>
       </c>
       <c r="G621" t="s">
         <v>1445</v>
@@ -21626,10 +21626,10 @@
         <v>1328</v>
       </c>
       <c r="E622" t="s">
+        <v>1448</v>
+      </c>
+      <c r="F622" t="s">
         <v>1444</v>
-      </c>
-      <c r="F622" t="s">
-        <v>1448</v>
       </c>
       <c r="G622" t="s">
         <v>1445</v>
@@ -21649,10 +21649,10 @@
         <v>1328</v>
       </c>
       <c r="E623" t="s">
+        <v>1382</v>
+      </c>
+      <c r="F623" t="s">
         <v>1444</v>
-      </c>
-      <c r="F623" t="s">
-        <v>1383</v>
       </c>
       <c r="G623" t="s">
         <v>1445</v>
@@ -21672,13 +21672,13 @@
         <v>1328</v>
       </c>
       <c r="E624" t="s">
-        <v>1444</v>
+        <v>1448</v>
       </c>
       <c r="F624" t="s">
-        <v>1448</v>
+        <v>1457</v>
       </c>
       <c r="G624" t="s">
-        <v>1457</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="625" spans="1:7">
@@ -21695,13 +21695,13 @@
         <v>25</v>
       </c>
       <c r="E625" t="s">
-        <v>1444</v>
+        <v>1460</v>
       </c>
       <c r="F625" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="G625" t="s">
-        <v>1461</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="626" spans="1:7">
@@ -21718,13 +21718,13 @@
         <v>1328</v>
       </c>
       <c r="E626" t="s">
-        <v>1444</v>
+        <v>1448</v>
       </c>
       <c r="F626" t="s">
-        <v>1448</v>
+        <v>1464</v>
       </c>
       <c r="G626" t="s">
-        <v>1464</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="627" spans="1:7">
@@ -21741,13 +21741,13 @@
         <v>22</v>
       </c>
       <c r="E627" t="s">
-        <v>1444</v>
+        <v>1448</v>
       </c>
       <c r="F627" t="s">
-        <v>1448</v>
+        <v>1467</v>
       </c>
       <c r="G627" t="s">
-        <v>1467</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="628" spans="1:7">
@@ -21764,10 +21764,10 @@
         <v>22</v>
       </c>
       <c r="E628" t="s">
+        <v>1448</v>
+      </c>
+      <c r="F628" t="s">
         <v>1444</v>
-      </c>
-      <c r="F628" t="s">
-        <v>1448</v>
       </c>
       <c r="G628" t="s">
         <v>1445</v>
@@ -21787,13 +21787,13 @@
         <v>25</v>
       </c>
       <c r="E629" t="s">
-        <v>1444</v>
+        <v>1472</v>
       </c>
       <c r="F629" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="G629" t="s">
-        <v>1473</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="630" spans="1:7">
@@ -21810,13 +21810,13 @@
         <v>25</v>
       </c>
       <c r="E630" t="s">
-        <v>1444</v>
+        <v>1476</v>
       </c>
       <c r="F630" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="G630" t="s">
-        <v>1477</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="631" spans="1:7">
@@ -21833,10 +21833,10 @@
         <v>1328</v>
       </c>
       <c r="E631" t="s">
+        <v>1448</v>
+      </c>
+      <c r="F631" t="s">
         <v>1444</v>
-      </c>
-      <c r="F631" t="s">
-        <v>1448</v>
       </c>
       <c r="G631" t="s">
         <v>1445</v>
@@ -21856,13 +21856,13 @@
         <v>25</v>
       </c>
       <c r="E632" t="s">
-        <v>1444</v>
+        <v>1482</v>
       </c>
       <c r="F632" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="G632" t="s">
-        <v>1483</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="633" spans="1:7">
@@ -21879,13 +21879,13 @@
         <v>32</v>
       </c>
       <c r="E633" t="s">
-        <v>1444</v>
+        <v>1448</v>
       </c>
       <c r="F633" t="s">
-        <v>1448</v>
+        <v>1486</v>
       </c>
       <c r="G633" t="s">
-        <v>1486</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="634" spans="1:7">
@@ -21902,13 +21902,13 @@
         <v>1328</v>
       </c>
       <c r="E634" t="s">
-        <v>1444</v>
+        <v>1448</v>
       </c>
       <c r="F634" t="s">
-        <v>1448</v>
+        <v>1489</v>
       </c>
       <c r="G634" t="s">
-        <v>1489</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="635" spans="1:7">
@@ -21925,10 +21925,10 @@
         <v>1328</v>
       </c>
       <c r="E635" t="s">
+        <v>1448</v>
+      </c>
+      <c r="F635" t="s">
         <v>1444</v>
-      </c>
-      <c r="F635" t="s">
-        <v>1448</v>
       </c>
       <c r="G635" t="s">
         <v>1445</v>
@@ -21948,10 +21948,10 @@
         <v>25</v>
       </c>
       <c r="E636" t="s">
+        <v>1448</v>
+      </c>
+      <c r="F636" t="s">
         <v>1444</v>
-      </c>
-      <c r="F636" t="s">
-        <v>1448</v>
       </c>
       <c r="G636" t="s">
         <v>1445</v>
@@ -21971,10 +21971,10 @@
         <v>22</v>
       </c>
       <c r="E637" t="s">
+        <v>1448</v>
+      </c>
+      <c r="F637" t="s">
         <v>1444</v>
-      </c>
-      <c r="F637" t="s">
-        <v>1448</v>
       </c>
       <c r="G637" t="s">
         <v>1445</v>
@@ -21994,10 +21994,10 @@
         <v>1328</v>
       </c>
       <c r="E638" t="s">
+        <v>1498</v>
+      </c>
+      <c r="F638" t="s">
         <v>1444</v>
-      </c>
-      <c r="F638" t="s">
-        <v>1498</v>
       </c>
       <c r="G638" t="s">
         <v>1445</v>
@@ -22017,10 +22017,10 @@
         <v>32</v>
       </c>
       <c r="E639" t="s">
+        <v>1448</v>
+      </c>
+      <c r="F639" t="s">
         <v>1444</v>
-      </c>
-      <c r="F639" t="s">
-        <v>1448</v>
       </c>
       <c r="G639" t="s">
         <v>1445</v>
@@ -22040,10 +22040,10 @@
         <v>1328</v>
       </c>
       <c r="E640" t="s">
+        <v>1448</v>
+      </c>
+      <c r="F640" t="s">
         <v>1444</v>
-      </c>
-      <c r="F640" t="s">
-        <v>1448</v>
       </c>
       <c r="G640" t="s">
         <v>1445</v>
@@ -22063,10 +22063,10 @@
         <v>1328</v>
       </c>
       <c r="E641" t="s">
+        <v>1448</v>
+      </c>
+      <c r="F641" t="s">
         <v>1444</v>
-      </c>
-      <c r="F641" t="s">
-        <v>1448</v>
       </c>
       <c r="G641" t="s">
         <v>1445</v>
@@ -22086,10 +22086,10 @@
         <v>1328</v>
       </c>
       <c r="E642" t="s">
+        <v>1448</v>
+      </c>
+      <c r="F642" t="s">
         <v>1444</v>
-      </c>
-      <c r="F642" t="s">
-        <v>1448</v>
       </c>
       <c r="G642" t="s">
         <v>1445</v>
@@ -22132,13 +22132,13 @@
         <v>22</v>
       </c>
       <c r="E644" t="s">
-        <v>1509</v>
+        <v>1514</v>
       </c>
       <c r="F644" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="G644" t="s">
-        <v>1515</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="645" spans="1:7">
@@ -22224,13 +22224,13 @@
         <v>25</v>
       </c>
       <c r="E648" t="s">
-        <v>1509</v>
+        <v>1524</v>
       </c>
       <c r="F648" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="G648" t="s">
-        <v>1525</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="649" spans="1:7">
@@ -22247,13 +22247,13 @@
         <v>25</v>
       </c>
       <c r="E649" t="s">
-        <v>1509</v>
+        <v>1528</v>
       </c>
       <c r="F649" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="G649" t="s">
-        <v>1529</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="650" spans="1:7">
@@ -22270,13 +22270,13 @@
         <v>1328</v>
       </c>
       <c r="E650" t="s">
-        <v>1509</v>
+        <v>1532</v>
       </c>
       <c r="F650" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="G650" t="s">
-        <v>1533</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="651" spans="1:7">
@@ -22296,10 +22296,10 @@
         <v>1509</v>
       </c>
       <c r="F651" t="s">
-        <v>1510</v>
+        <v>1536</v>
       </c>
       <c r="G651" t="s">
-        <v>1536</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="652" spans="1:7">
@@ -22385,13 +22385,13 @@
         <v>25</v>
       </c>
       <c r="E655" t="s">
-        <v>1509</v>
+        <v>1544</v>
       </c>
       <c r="F655" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="G655" t="s">
-        <v>1545</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="656" spans="1:7">
@@ -22408,13 +22408,13 @@
         <v>1328</v>
       </c>
       <c r="E656" t="s">
-        <v>1509</v>
+        <v>1486</v>
       </c>
       <c r="F656" t="s">
-        <v>1486</v>
+        <v>1548</v>
       </c>
       <c r="G656" t="s">
-        <v>1548</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="657" spans="1:7">
@@ -22454,13 +22454,13 @@
         <v>25</v>
       </c>
       <c r="E658" t="s">
-        <v>1509</v>
+        <v>1553</v>
       </c>
       <c r="F658" t="s">
-        <v>1553</v>
+        <v>1515</v>
       </c>
       <c r="G658" t="s">
-        <v>1515</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="659" spans="1:7">
@@ -22480,10 +22480,10 @@
         <v>1509</v>
       </c>
       <c r="F659" t="s">
-        <v>1510</v>
+        <v>1556</v>
       </c>
       <c r="G659" t="s">
-        <v>1556</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="660" spans="1:7">
@@ -22503,10 +22503,10 @@
         <v>1509</v>
       </c>
       <c r="F660" t="s">
-        <v>1510</v>
+        <v>1556</v>
       </c>
       <c r="G660" t="s">
-        <v>1556</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="661" spans="1:7">
@@ -22549,10 +22549,10 @@
         <v>1509</v>
       </c>
       <c r="F662" t="s">
-        <v>1510</v>
+        <v>1562</v>
       </c>
       <c r="G662" t="s">
-        <v>1562</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="663" spans="1:7">
@@ -22822,13 +22822,13 @@
         <v>25</v>
       </c>
       <c r="E674" t="s">
-        <v>1583</v>
+        <v>1588</v>
       </c>
       <c r="F674" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="G674" t="s">
-        <v>1589</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="675" spans="1:7">
@@ -22914,10 +22914,10 @@
         <v>1328</v>
       </c>
       <c r="E678" t="s">
-        <v>1583</v>
+        <v>1598</v>
       </c>
       <c r="F678" t="s">
-        <v>1598</v>
+        <v>1584</v>
       </c>
       <c r="G678" t="s">
         <v>1585</v>
@@ -22940,10 +22940,10 @@
         <v>1583</v>
       </c>
       <c r="F679" t="s">
-        <v>1584</v>
+        <v>1601</v>
       </c>
       <c r="G679" t="s">
-        <v>1601</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="680" spans="1:7">
@@ -23029,13 +23029,13 @@
         <v>25</v>
       </c>
       <c r="E683" t="s">
-        <v>1583</v>
+        <v>1609</v>
       </c>
       <c r="F683" t="s">
-        <v>1609</v>
+        <v>1601</v>
       </c>
       <c r="G683" t="s">
-        <v>1601</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="684" spans="1:7">
@@ -23052,13 +23052,13 @@
         <v>25</v>
       </c>
       <c r="E684" t="s">
-        <v>1583</v>
+        <v>1612</v>
       </c>
       <c r="F684" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="G684" t="s">
-        <v>1613</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="685" spans="1:7">
@@ -23075,13 +23075,13 @@
         <v>25</v>
       </c>
       <c r="E685" t="s">
-        <v>1583</v>
+        <v>1616</v>
       </c>
       <c r="F685" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="G685" t="s">
-        <v>1617</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="686" spans="1:7">
@@ -23124,10 +23124,10 @@
         <v>1583</v>
       </c>
       <c r="F687" t="s">
-        <v>1584</v>
+        <v>1622</v>
       </c>
       <c r="G687" t="s">
-        <v>1622</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="688" spans="1:7">
@@ -23144,13 +23144,13 @@
         <v>25</v>
       </c>
       <c r="E688" t="s">
-        <v>1583</v>
+        <v>1625</v>
       </c>
       <c r="F688" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="G688" t="s">
-        <v>1626</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="689" spans="1:7">
@@ -23236,13 +23236,13 @@
         <v>22</v>
       </c>
       <c r="E692" t="s">
-        <v>1583</v>
+        <v>1635</v>
       </c>
       <c r="F692" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="G692" t="s">
-        <v>1636</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="693" spans="1:7">
@@ -23262,10 +23262,10 @@
         <v>1583</v>
       </c>
       <c r="F693" t="s">
-        <v>1584</v>
+        <v>1639</v>
       </c>
       <c r="G693" t="s">
-        <v>1639</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="694" spans="1:7">
@@ -23285,10 +23285,10 @@
         <v>1583</v>
       </c>
       <c r="F694" t="s">
-        <v>1584</v>
+        <v>1642</v>
       </c>
       <c r="G694" t="s">
-        <v>1642</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="695" spans="1:7">
@@ -23377,10 +23377,10 @@
         <v>1583</v>
       </c>
       <c r="F698" t="s">
-        <v>1584</v>
+        <v>1650</v>
       </c>
       <c r="G698" t="s">
-        <v>1650</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="699" spans="1:7">
@@ -23466,13 +23466,13 @@
         <v>22</v>
       </c>
       <c r="E702" t="s">
-        <v>1657</v>
+        <v>1662</v>
       </c>
       <c r="F702" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="G702" t="s">
-        <v>1663</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="703" spans="1:7">
@@ -23489,10 +23489,10 @@
         <v>25</v>
       </c>
       <c r="E703" t="s">
-        <v>1657</v>
+        <v>1666</v>
       </c>
       <c r="F703" t="s">
-        <v>1666</v>
+        <v>1658</v>
       </c>
       <c r="G703" t="s">
         <v>1659</v>
@@ -23512,13 +23512,13 @@
         <v>1328</v>
       </c>
       <c r="E704" t="s">
-        <v>1657</v>
+        <v>1669</v>
       </c>
       <c r="F704" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="G704" t="s">
-        <v>1670</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="705" spans="1:7">
@@ -23535,13 +23535,13 @@
         <v>1328</v>
       </c>
       <c r="E705" t="s">
-        <v>1657</v>
+        <v>1669</v>
       </c>
       <c r="F705" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="G705" t="s">
-        <v>1670</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="706" spans="1:7">
@@ -23558,13 +23558,13 @@
         <v>22</v>
       </c>
       <c r="E706" t="s">
-        <v>1657</v>
+        <v>1583</v>
       </c>
       <c r="F706" t="s">
-        <v>1584</v>
+        <v>1642</v>
       </c>
       <c r="G706" t="s">
-        <v>1642</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="707" spans="1:7">
@@ -23581,13 +23581,13 @@
         <v>1328</v>
       </c>
       <c r="E707" t="s">
-        <v>1657</v>
+        <v>1669</v>
       </c>
       <c r="F707" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="G707" t="s">
-        <v>1670</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="708" spans="1:7">
@@ -23604,13 +23604,13 @@
         <v>1328</v>
       </c>
       <c r="E708" t="s">
-        <v>1657</v>
+        <v>1669</v>
       </c>
       <c r="F708" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="G708" t="s">
-        <v>1670</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="709" spans="1:7">
@@ -23627,13 +23627,13 @@
         <v>22</v>
       </c>
       <c r="E709" t="s">
-        <v>1657</v>
+        <v>1681</v>
       </c>
       <c r="F709" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="G709" t="s">
-        <v>1682</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="710" spans="1:7">
@@ -23650,13 +23650,13 @@
         <v>25</v>
       </c>
       <c r="E710" t="s">
-        <v>1657</v>
+        <v>1685</v>
       </c>
       <c r="F710" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="G710" t="s">
-        <v>1686</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="711" spans="1:7">
@@ -23673,13 +23673,13 @@
         <v>25</v>
       </c>
       <c r="E711" t="s">
-        <v>1657</v>
+        <v>1689</v>
       </c>
       <c r="F711" t="s">
-        <v>1689</v>
+        <v>1622</v>
       </c>
       <c r="G711" t="s">
-        <v>1622</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="712" spans="1:7">
@@ -23696,13 +23696,13 @@
         <v>25</v>
       </c>
       <c r="E712" t="s">
-        <v>1657</v>
+        <v>1692</v>
       </c>
       <c r="F712" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="G712" t="s">
-        <v>1693</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="713" spans="1:7">
@@ -23719,13 +23719,13 @@
         <v>1328</v>
       </c>
       <c r="E713" t="s">
-        <v>1657</v>
+        <v>1669</v>
       </c>
       <c r="F713" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="G713" t="s">
-        <v>1670</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="714" spans="1:7">
@@ -23742,13 +23742,13 @@
         <v>25</v>
       </c>
       <c r="E714" t="s">
-        <v>1657</v>
+        <v>1663</v>
       </c>
       <c r="F714" t="s">
-        <v>1663</v>
+        <v>1670</v>
       </c>
       <c r="G714" t="s">
-        <v>1670</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="715" spans="1:7">
@@ -23765,13 +23765,13 @@
         <v>25</v>
       </c>
       <c r="E715" t="s">
-        <v>1657</v>
+        <v>1700</v>
       </c>
       <c r="F715" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="G715" t="s">
-        <v>1701</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="716" spans="1:7">
@@ -23788,13 +23788,13 @@
         <v>22</v>
       </c>
       <c r="E716" t="s">
-        <v>1657</v>
+        <v>1704</v>
       </c>
       <c r="F716" t="s">
-        <v>1704</v>
+        <v>1642</v>
       </c>
       <c r="G716" t="s">
-        <v>1642</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="717" spans="1:7">
@@ -23811,13 +23811,13 @@
         <v>22</v>
       </c>
       <c r="E717" t="s">
-        <v>1657</v>
+        <v>1669</v>
       </c>
       <c r="F717" t="s">
-        <v>1669</v>
+        <v>1707</v>
       </c>
       <c r="G717" t="s">
-        <v>1707</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="718" spans="1:7">
@@ -23834,13 +23834,13 @@
         <v>1328</v>
       </c>
       <c r="E718" t="s">
-        <v>1657</v>
+        <v>1669</v>
       </c>
       <c r="F718" t="s">
-        <v>1669</v>
+        <v>1707</v>
       </c>
       <c r="G718" t="s">
-        <v>1707</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="719" spans="1:7">
@@ -23860,10 +23860,10 @@
         <v>1657</v>
       </c>
       <c r="F719" t="s">
-        <v>1658</v>
+        <v>1707</v>
       </c>
       <c r="G719" t="s">
-        <v>1707</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="720" spans="1:7">
@@ -23880,13 +23880,13 @@
         <v>25</v>
       </c>
       <c r="E720" t="s">
-        <v>1657</v>
+        <v>1713</v>
       </c>
       <c r="F720" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="G720" t="s">
-        <v>1714</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="721" spans="1:7">
@@ -23903,13 +23903,13 @@
         <v>22</v>
       </c>
       <c r="E721" t="s">
-        <v>1657</v>
+        <v>1669</v>
       </c>
       <c r="F721" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="G721" t="s">
-        <v>1670</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="722" spans="1:7">
@@ -23926,13 +23926,13 @@
         <v>22</v>
       </c>
       <c r="E722" t="s">
-        <v>1657</v>
+        <v>1689</v>
       </c>
       <c r="F722" t="s">
-        <v>1689</v>
+        <v>1642</v>
       </c>
       <c r="G722" t="s">
-        <v>1642</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="723" spans="1:7">
@@ -23949,13 +23949,13 @@
         <v>1328</v>
       </c>
       <c r="E723" t="s">
-        <v>1657</v>
+        <v>1669</v>
       </c>
       <c r="F723" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="G723" t="s">
-        <v>1670</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="724" spans="1:7">
@@ -23972,10 +23972,10 @@
         <v>32</v>
       </c>
       <c r="E724" t="s">
-        <v>1657</v>
+        <v>1723</v>
       </c>
       <c r="F724" t="s">
-        <v>1723</v>
+        <v>1658</v>
       </c>
       <c r="G724" t="s">
         <v>1659</v>
@@ -23995,13 +23995,13 @@
         <v>22</v>
       </c>
       <c r="E725" t="s">
-        <v>1657</v>
+        <v>1669</v>
       </c>
       <c r="F725" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="G725" t="s">
-        <v>1670</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="726" spans="1:7">
@@ -24018,13 +24018,13 @@
         <v>1328</v>
       </c>
       <c r="E726" t="s">
-        <v>1657</v>
+        <v>1669</v>
       </c>
       <c r="F726" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="G726" t="s">
-        <v>1670</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="727" spans="1:7">
@@ -24041,13 +24041,13 @@
         <v>22</v>
       </c>
       <c r="E727" t="s">
-        <v>1657</v>
+        <v>1692</v>
       </c>
       <c r="F727" t="s">
-        <v>1692</v>
+        <v>1642</v>
       </c>
       <c r="G727" t="s">
-        <v>1642</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="728" spans="1:7">
@@ -24064,10 +24064,10 @@
         <v>25</v>
       </c>
       <c r="E728" t="s">
-        <v>1657</v>
+        <v>1666</v>
       </c>
       <c r="F728" t="s">
-        <v>1666</v>
+        <v>1658</v>
       </c>
       <c r="G728" t="s">
         <v>1659</v>
@@ -24087,13 +24087,13 @@
         <v>22</v>
       </c>
       <c r="E729" t="s">
-        <v>1657</v>
+        <v>1669</v>
       </c>
       <c r="F729" t="s">
-        <v>1669</v>
+        <v>1734</v>
       </c>
       <c r="G729" t="s">
-        <v>1734</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="730" spans="1:7">
@@ -24110,13 +24110,13 @@
         <v>1328</v>
       </c>
       <c r="E730" t="s">
-        <v>1657</v>
+        <v>1669</v>
       </c>
       <c r="F730" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="G730" t="s">
-        <v>1670</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="731" spans="1:7">
@@ -24133,13 +24133,13 @@
         <v>32</v>
       </c>
       <c r="E731" t="s">
-        <v>1657</v>
+        <v>1669</v>
       </c>
       <c r="F731" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="G731" t="s">
-        <v>1670</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="732" spans="1:7">
@@ -24156,13 +24156,13 @@
         <v>1328</v>
       </c>
       <c r="E732" t="s">
-        <v>1657</v>
+        <v>1669</v>
       </c>
       <c r="F732" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="G732" t="s">
-        <v>1670</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="733" spans="1:7">
@@ -24179,13 +24179,13 @@
         <v>25</v>
       </c>
       <c r="E733" t="s">
-        <v>1657</v>
+        <v>1692</v>
       </c>
       <c r="F733" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="G733" t="s">
-        <v>1693</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="734" spans="1:7">
@@ -24202,13 +24202,13 @@
         <v>1328</v>
       </c>
       <c r="E734" t="s">
-        <v>1657</v>
+        <v>1669</v>
       </c>
       <c r="F734" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="G734" t="s">
-        <v>1670</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="735" spans="1:7">
@@ -24225,13 +24225,13 @@
         <v>1328</v>
       </c>
       <c r="E735" t="s">
-        <v>1657</v>
+        <v>1669</v>
       </c>
       <c r="F735" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="G735" t="s">
-        <v>1670</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="736" spans="1:7">
@@ -24271,13 +24271,13 @@
         <v>25</v>
       </c>
       <c r="E737" t="s">
-        <v>1748</v>
+        <v>1753</v>
       </c>
       <c r="F737" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="G737" t="s">
-        <v>1754</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="738" spans="1:7">
@@ -24294,13 +24294,13 @@
         <v>1328</v>
       </c>
       <c r="E738" t="s">
-        <v>1748</v>
+        <v>1757</v>
       </c>
       <c r="F738" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="G738" t="s">
-        <v>1758</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="739" spans="1:7">
@@ -24317,13 +24317,13 @@
         <v>1328</v>
       </c>
       <c r="E739" t="s">
-        <v>1748</v>
+        <v>1757</v>
       </c>
       <c r="F739" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="G739" t="s">
-        <v>1758</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="740" spans="1:7">
@@ -24340,13 +24340,13 @@
         <v>1328</v>
       </c>
       <c r="E740" t="s">
-        <v>1748</v>
+        <v>1757</v>
       </c>
       <c r="F740" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="G740" t="s">
-        <v>1758</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="741" spans="1:7">
@@ -24363,13 +24363,13 @@
         <v>1328</v>
       </c>
       <c r="E741" t="s">
-        <v>1748</v>
+        <v>1757</v>
       </c>
       <c r="F741" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="G741" t="s">
-        <v>1758</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="742" spans="1:7">
@@ -24386,13 +24386,13 @@
         <v>1328</v>
       </c>
       <c r="E742" t="s">
-        <v>1748</v>
+        <v>1757</v>
       </c>
       <c r="F742" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="G742" t="s">
-        <v>1758</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="743" spans="1:7">
@@ -24409,13 +24409,13 @@
         <v>25</v>
       </c>
       <c r="E743" t="s">
-        <v>1748</v>
+        <v>1769</v>
       </c>
       <c r="F743" t="s">
-        <v>1769</v>
+        <v>1754</v>
       </c>
       <c r="G743" t="s">
-        <v>1754</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="744" spans="1:7">
@@ -24432,13 +24432,13 @@
         <v>25</v>
       </c>
       <c r="E744" t="s">
-        <v>1748</v>
+        <v>1772</v>
       </c>
       <c r="F744" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="G744" t="s">
-        <v>1773</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="745" spans="1:7">
@@ -24455,13 +24455,13 @@
         <v>32</v>
       </c>
       <c r="E745" t="s">
-        <v>1748</v>
+        <v>1757</v>
       </c>
       <c r="F745" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="G745" t="s">
-        <v>1758</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="746" spans="1:7">
@@ -24478,13 +24478,13 @@
         <v>32</v>
       </c>
       <c r="E746" t="s">
-        <v>1748</v>
+        <v>1669</v>
       </c>
       <c r="F746" t="s">
-        <v>1669</v>
+        <v>1778</v>
       </c>
       <c r="G746" t="s">
-        <v>1778</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="747" spans="1:7">
@@ -24501,13 +24501,13 @@
         <v>25</v>
       </c>
       <c r="E747" t="s">
-        <v>1748</v>
+        <v>1781</v>
       </c>
       <c r="F747" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="G747" t="s">
-        <v>1782</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="748" spans="1:7">
@@ -24524,13 +24524,13 @@
         <v>22</v>
       </c>
       <c r="E748" t="s">
-        <v>1748</v>
+        <v>1785</v>
       </c>
       <c r="F748" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="G748" t="s">
-        <v>1786</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="749" spans="1:7">
@@ -24547,13 +24547,13 @@
         <v>25</v>
       </c>
       <c r="E749" t="s">
-        <v>1748</v>
+        <v>1789</v>
       </c>
       <c r="F749" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="G749" t="s">
-        <v>1790</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="750" spans="1:7">
@@ -24570,13 +24570,13 @@
         <v>1328</v>
       </c>
       <c r="E750" t="s">
-        <v>1748</v>
+        <v>1757</v>
       </c>
       <c r="F750" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="G750" t="s">
-        <v>1758</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="751" spans="1:7">
@@ -24593,13 +24593,13 @@
         <v>25</v>
       </c>
       <c r="E751" t="s">
-        <v>1748</v>
+        <v>1795</v>
       </c>
       <c r="F751" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
       <c r="G751" t="s">
-        <v>1796</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="752" spans="1:7">
@@ -24616,13 +24616,13 @@
         <v>25</v>
       </c>
       <c r="E752" t="s">
-        <v>1748</v>
+        <v>1799</v>
       </c>
       <c r="F752" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="G752" t="s">
-        <v>1800</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="753" spans="1:7">
@@ -24639,13 +24639,13 @@
         <v>22</v>
       </c>
       <c r="E753" t="s">
-        <v>1748</v>
+        <v>1757</v>
       </c>
       <c r="F753" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="G753" t="s">
-        <v>1758</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="754" spans="1:7">
@@ -24662,13 +24662,13 @@
         <v>25</v>
       </c>
       <c r="E754" t="s">
-        <v>1748</v>
+        <v>1805</v>
       </c>
       <c r="F754" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="G754" t="s">
-        <v>1806</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="755" spans="1:7">
@@ -24685,13 +24685,13 @@
         <v>22</v>
       </c>
       <c r="E755" t="s">
-        <v>1748</v>
+        <v>1757</v>
       </c>
       <c r="F755" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="G755" t="s">
-        <v>1758</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="756" spans="1:7">
@@ -24708,13 +24708,13 @@
         <v>25</v>
       </c>
       <c r="E756" t="s">
-        <v>1748</v>
+        <v>1811</v>
       </c>
       <c r="F756" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="G756" t="s">
-        <v>1812</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="757" spans="1:7">
@@ -24731,13 +24731,13 @@
         <v>25</v>
       </c>
       <c r="E757" t="s">
-        <v>1748</v>
+        <v>1805</v>
       </c>
       <c r="F757" t="s">
-        <v>1805</v>
+        <v>1815</v>
       </c>
       <c r="G757" t="s">
-        <v>1815</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="758" spans="1:7">
@@ -24754,13 +24754,13 @@
         <v>1328</v>
       </c>
       <c r="E758" t="s">
-        <v>1748</v>
+        <v>1757</v>
       </c>
       <c r="F758" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="G758" t="s">
-        <v>1758</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="759" spans="1:7">
@@ -24777,13 +24777,13 @@
         <v>22</v>
       </c>
       <c r="E759" t="s">
-        <v>1748</v>
+        <v>1799</v>
       </c>
       <c r="F759" t="s">
-        <v>1799</v>
+        <v>1820</v>
       </c>
       <c r="G759" t="s">
-        <v>1820</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="760" spans="1:7">
@@ -24800,13 +24800,13 @@
         <v>1328</v>
       </c>
       <c r="E760" t="s">
-        <v>1748</v>
+        <v>1757</v>
       </c>
       <c r="F760" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="G760" t="s">
-        <v>1758</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="761" spans="1:7">
@@ -24823,13 +24823,13 @@
         <v>1328</v>
       </c>
       <c r="E761" t="s">
-        <v>1748</v>
+        <v>1799</v>
       </c>
       <c r="F761" t="s">
-        <v>1799</v>
+        <v>1758</v>
       </c>
       <c r="G761" t="s">
-        <v>1758</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="762" spans="1:7">
@@ -24846,13 +24846,13 @@
         <v>22</v>
       </c>
       <c r="E762" t="s">
-        <v>1748</v>
+        <v>1799</v>
       </c>
       <c r="F762" t="s">
-        <v>1799</v>
+        <v>1758</v>
       </c>
       <c r="G762" t="s">
-        <v>1758</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="763" spans="1:7">
@@ -24869,13 +24869,13 @@
         <v>25</v>
       </c>
       <c r="E763" t="s">
-        <v>1748</v>
+        <v>1753</v>
       </c>
       <c r="F763" t="s">
-        <v>1753</v>
+        <v>1828</v>
       </c>
       <c r="G763" t="s">
-        <v>1828</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="764" spans="1:7">
@@ -24892,13 +24892,13 @@
         <v>1328</v>
       </c>
       <c r="E764" t="s">
-        <v>1748</v>
+        <v>1757</v>
       </c>
       <c r="F764" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="G764" t="s">
-        <v>1758</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="765" spans="1:7">
@@ -24915,13 +24915,13 @@
         <v>25</v>
       </c>
       <c r="E765" t="s">
-        <v>1748</v>
+        <v>1833</v>
       </c>
       <c r="F765" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="G765" t="s">
-        <v>1834</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="766" spans="1:7">
@@ -24938,13 +24938,13 @@
         <v>1328</v>
       </c>
       <c r="E766" t="s">
-        <v>1748</v>
+        <v>1799</v>
       </c>
       <c r="F766" t="s">
-        <v>1799</v>
+        <v>1758</v>
       </c>
       <c r="G766" t="s">
-        <v>1758</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="767" spans="1:7">
@@ -24961,13 +24961,13 @@
         <v>1328</v>
       </c>
       <c r="E767" t="s">
-        <v>1748</v>
+        <v>1757</v>
       </c>
       <c r="F767" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="G767" t="s">
-        <v>1758</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="768" spans="1:7">
@@ -24984,13 +24984,13 @@
         <v>25</v>
       </c>
       <c r="E768" t="s">
-        <v>1748</v>
+        <v>1772</v>
       </c>
       <c r="F768" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="G768" t="s">
-        <v>1773</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="769" spans="1:7">
@@ -25007,13 +25007,13 @@
         <v>32</v>
       </c>
       <c r="E769" t="s">
-        <v>1748</v>
+        <v>1757</v>
       </c>
       <c r="F769" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="G769" t="s">
-        <v>1758</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="770" spans="1:7">
@@ -25030,13 +25030,13 @@
         <v>1328</v>
       </c>
       <c r="E770" t="s">
-        <v>1748</v>
+        <v>1757</v>
       </c>
       <c r="F770" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="G770" t="s">
-        <v>1758</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="771" spans="1:7">
@@ -25053,13 +25053,13 @@
         <v>25</v>
       </c>
       <c r="E771" t="s">
-        <v>1748</v>
+        <v>1799</v>
       </c>
       <c r="F771" t="s">
-        <v>1799</v>
+        <v>1796</v>
       </c>
       <c r="G771" t="s">
-        <v>1796</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="772" spans="1:7">
@@ -25076,13 +25076,13 @@
         <v>1328</v>
       </c>
       <c r="E772" t="s">
-        <v>1748</v>
+        <v>1757</v>
       </c>
       <c r="F772" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="G772" t="s">
-        <v>1758</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="773" spans="1:7">
@@ -25099,13 +25099,13 @@
         <v>1328</v>
       </c>
       <c r="E773" t="s">
-        <v>1748</v>
+        <v>1757</v>
       </c>
       <c r="F773" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="G773" t="s">
-        <v>1758</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="774" spans="1:7">
@@ -25148,10 +25148,10 @@
         <v>1852</v>
       </c>
       <c r="F775" t="s">
-        <v>1853</v>
+        <v>1857</v>
       </c>
       <c r="G775" t="s">
-        <v>1857</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="776" spans="1:7">
@@ -25171,10 +25171,10 @@
         <v>1852</v>
       </c>
       <c r="F776" t="s">
-        <v>1853</v>
+        <v>1857</v>
       </c>
       <c r="G776" t="s">
-        <v>1857</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="777" spans="1:7">
@@ -25194,10 +25194,10 @@
         <v>1852</v>
       </c>
       <c r="F777" t="s">
-        <v>1853</v>
+        <v>1857</v>
       </c>
       <c r="G777" t="s">
-        <v>1857</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="778" spans="1:7">
@@ -25217,10 +25217,10 @@
         <v>1852</v>
       </c>
       <c r="F778" t="s">
-        <v>1853</v>
+        <v>1857</v>
       </c>
       <c r="G778" t="s">
-        <v>1857</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="779" spans="1:7">
@@ -25240,10 +25240,10 @@
         <v>1852</v>
       </c>
       <c r="F779" t="s">
-        <v>1853</v>
+        <v>1857</v>
       </c>
       <c r="G779" t="s">
-        <v>1857</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="780" spans="1:7">
@@ -25263,10 +25263,10 @@
         <v>1852</v>
       </c>
       <c r="F780" t="s">
-        <v>1853</v>
+        <v>1857</v>
       </c>
       <c r="G780" t="s">
-        <v>1857</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="781" spans="1:7">
@@ -25283,13 +25283,13 @@
         <v>22</v>
       </c>
       <c r="E781" t="s">
-        <v>1852</v>
+        <v>1870</v>
       </c>
       <c r="F781" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
       <c r="G781" t="s">
-        <v>1871</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="782" spans="1:7">
@@ -25306,13 +25306,13 @@
         <v>22</v>
       </c>
       <c r="E782" t="s">
-        <v>1852</v>
+        <v>1874</v>
       </c>
       <c r="F782" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
       <c r="G782" t="s">
-        <v>1875</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="783" spans="1:7">
@@ -25332,10 +25332,10 @@
         <v>1852</v>
       </c>
       <c r="F783" t="s">
-        <v>1853</v>
+        <v>1857</v>
       </c>
       <c r="G783" t="s">
-        <v>1857</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="784" spans="1:7">
@@ -25355,10 +25355,10 @@
         <v>1852</v>
       </c>
       <c r="F784" t="s">
-        <v>1853</v>
+        <v>1857</v>
       </c>
       <c r="G784" t="s">
-        <v>1857</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="785" spans="1:7">
@@ -25375,13 +25375,13 @@
         <v>25</v>
       </c>
       <c r="E785" t="s">
-        <v>1852</v>
+        <v>1882</v>
       </c>
       <c r="F785" t="s">
-        <v>1882</v>
+        <v>1883</v>
       </c>
       <c r="G785" t="s">
-        <v>1883</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="786" spans="1:7">
@@ -25401,10 +25401,10 @@
         <v>1852</v>
       </c>
       <c r="F786" t="s">
-        <v>1853</v>
+        <v>1857</v>
       </c>
       <c r="G786" t="s">
-        <v>1857</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="787" spans="1:7">
@@ -25421,13 +25421,13 @@
         <v>25</v>
       </c>
       <c r="E787" t="s">
-        <v>1852</v>
+        <v>1882</v>
       </c>
       <c r="F787" t="s">
-        <v>1882</v>
+        <v>1883</v>
       </c>
       <c r="G787" t="s">
-        <v>1883</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="788" spans="1:7">
@@ -25444,13 +25444,13 @@
         <v>25</v>
       </c>
       <c r="E788" t="s">
-        <v>1852</v>
+        <v>1890</v>
       </c>
       <c r="F788" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
       <c r="G788" t="s">
-        <v>1891</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="789" spans="1:7">
@@ -25470,10 +25470,10 @@
         <v>1852</v>
       </c>
       <c r="F789" t="s">
-        <v>1853</v>
+        <v>1894</v>
       </c>
       <c r="G789" t="s">
-        <v>1894</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="790" spans="1:7">
@@ -25490,13 +25490,13 @@
         <v>25</v>
       </c>
       <c r="E790" t="s">
-        <v>1852</v>
+        <v>1897</v>
       </c>
       <c r="F790" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
       <c r="G790" t="s">
-        <v>1898</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="791" spans="1:7">
@@ -25516,10 +25516,10 @@
         <v>1852</v>
       </c>
       <c r="F791" t="s">
-        <v>1853</v>
+        <v>1857</v>
       </c>
       <c r="G791" t="s">
-        <v>1857</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="792" spans="1:7">
@@ -25539,10 +25539,10 @@
         <v>1852</v>
       </c>
       <c r="F792" t="s">
-        <v>1853</v>
+        <v>1903</v>
       </c>
       <c r="G792" t="s">
-        <v>1903</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="793" spans="1:7">
@@ -25562,10 +25562,10 @@
         <v>1852</v>
       </c>
       <c r="F793" t="s">
-        <v>1853</v>
+        <v>1857</v>
       </c>
       <c r="G793" t="s">
-        <v>1857</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="794" spans="1:7">
@@ -25582,13 +25582,13 @@
         <v>22</v>
       </c>
       <c r="E794" t="s">
-        <v>1852</v>
+        <v>1757</v>
       </c>
       <c r="F794" t="s">
-        <v>1757</v>
+        <v>1908</v>
       </c>
       <c r="G794" t="s">
-        <v>1908</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="795" spans="1:7">
@@ -25608,10 +25608,10 @@
         <v>1852</v>
       </c>
       <c r="F795" t="s">
-        <v>1853</v>
+        <v>1857</v>
       </c>
       <c r="G795" t="s">
-        <v>1857</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="796" spans="1:7">
@@ -25631,10 +25631,10 @@
         <v>1852</v>
       </c>
       <c r="F796" t="s">
-        <v>1853</v>
+        <v>1857</v>
       </c>
       <c r="G796" t="s">
-        <v>1857</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="797" spans="1:7">
@@ -25651,13 +25651,13 @@
         <v>25</v>
       </c>
       <c r="E797" t="s">
-        <v>1852</v>
+        <v>1915</v>
       </c>
       <c r="F797" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="G797" t="s">
-        <v>1916</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="798" spans="1:7">
@@ -25677,10 +25677,10 @@
         <v>1852</v>
       </c>
       <c r="F798" t="s">
-        <v>1853</v>
+        <v>1919</v>
       </c>
       <c r="G798" t="s">
-        <v>1919</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="799" spans="1:7">
@@ -25700,10 +25700,10 @@
         <v>1852</v>
       </c>
       <c r="F799" t="s">
-        <v>1853</v>
+        <v>1857</v>
       </c>
       <c r="G799" t="s">
-        <v>1857</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="800" spans="1:7">
@@ -25746,10 +25746,10 @@
         <v>1852</v>
       </c>
       <c r="F801" t="s">
-        <v>1853</v>
+        <v>1926</v>
       </c>
       <c r="G801" t="s">
-        <v>1926</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="802" spans="1:7">
@@ -25769,10 +25769,10 @@
         <v>1852</v>
       </c>
       <c r="F802" t="s">
-        <v>1853</v>
+        <v>1857</v>
       </c>
       <c r="G802" t="s">
-        <v>1857</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="803" spans="1:7">
@@ -25792,10 +25792,10 @@
         <v>1852</v>
       </c>
       <c r="F803" t="s">
-        <v>1853</v>
+        <v>1857</v>
       </c>
       <c r="G803" t="s">
-        <v>1857</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="804" spans="1:7">
@@ -25815,10 +25815,10 @@
         <v>1852</v>
       </c>
       <c r="F804" t="s">
-        <v>1853</v>
+        <v>1857</v>
       </c>
       <c r="G804" t="s">
-        <v>1857</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="805" spans="1:7">
@@ -25838,10 +25838,10 @@
         <v>1852</v>
       </c>
       <c r="F805" t="s">
-        <v>1853</v>
+        <v>1857</v>
       </c>
       <c r="G805" t="s">
-        <v>1857</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="806" spans="1:7">
@@ -25861,10 +25861,10 @@
         <v>1852</v>
       </c>
       <c r="F806" t="s">
-        <v>1853</v>
+        <v>1857</v>
       </c>
       <c r="G806" t="s">
-        <v>1857</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="807" spans="1:7">
@@ -25904,13 +25904,13 @@
         <v>25</v>
       </c>
       <c r="E808" t="s">
-        <v>1938</v>
+        <v>1943</v>
       </c>
       <c r="F808" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="G808" t="s">
-        <v>1944</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="809" spans="1:7">
@@ -25927,13 +25927,13 @@
         <v>1328</v>
       </c>
       <c r="E809" t="s">
-        <v>1938</v>
+        <v>1947</v>
       </c>
       <c r="F809" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="G809" t="s">
-        <v>1948</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="810" spans="1:7">
@@ -25950,13 +25950,13 @@
         <v>1328</v>
       </c>
       <c r="E810" t="s">
-        <v>1938</v>
+        <v>1947</v>
       </c>
       <c r="F810" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="G810" t="s">
-        <v>1948</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="811" spans="1:7">
@@ -25973,13 +25973,13 @@
         <v>1328</v>
       </c>
       <c r="E811" t="s">
-        <v>1938</v>
+        <v>1947</v>
       </c>
       <c r="F811" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="G811" t="s">
-        <v>1948</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="812" spans="1:7">
@@ -25996,13 +25996,13 @@
         <v>1328</v>
       </c>
       <c r="E812" t="s">
-        <v>1938</v>
+        <v>1947</v>
       </c>
       <c r="F812" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="G812" t="s">
-        <v>1948</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="813" spans="1:7">
@@ -26019,13 +26019,13 @@
         <v>1328</v>
       </c>
       <c r="E813" t="s">
-        <v>1938</v>
+        <v>1947</v>
       </c>
       <c r="F813" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="G813" t="s">
-        <v>1948</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="814" spans="1:7">
@@ -26042,13 +26042,13 @@
         <v>1328</v>
       </c>
       <c r="E814" t="s">
-        <v>1938</v>
+        <v>1947</v>
       </c>
       <c r="F814" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="G814" t="s">
-        <v>1948</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="815" spans="1:7">
@@ -26065,10 +26065,10 @@
         <v>25</v>
       </c>
       <c r="E815" t="s">
-        <v>1938</v>
+        <v>1943</v>
       </c>
       <c r="F815" t="s">
-        <v>1943</v>
+        <v>1939</v>
       </c>
       <c r="G815" t="s">
         <v>1940</v>
@@ -26088,13 +26088,13 @@
         <v>22</v>
       </c>
       <c r="E816" t="s">
-        <v>1938</v>
+        <v>1947</v>
       </c>
       <c r="F816" t="s">
-        <v>1947</v>
+        <v>1903</v>
       </c>
       <c r="G816" t="s">
-        <v>1903</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="817" spans="1:7">
@@ -26111,13 +26111,13 @@
         <v>1328</v>
       </c>
       <c r="E817" t="s">
-        <v>1938</v>
+        <v>1947</v>
       </c>
       <c r="F817" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="G817" t="s">
-        <v>1948</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="818" spans="1:7">
@@ -26137,10 +26137,10 @@
         <v>1938</v>
       </c>
       <c r="F818" t="s">
-        <v>1939</v>
+        <v>1948</v>
       </c>
       <c r="G818" t="s">
-        <v>1948</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="819" spans="1:7">
@@ -26157,13 +26157,13 @@
         <v>1328</v>
       </c>
       <c r="E819" t="s">
-        <v>1938</v>
+        <v>1947</v>
       </c>
       <c r="F819" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="G819" t="s">
-        <v>1948</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="820" spans="1:7">
@@ -26180,13 +26180,13 @@
         <v>25</v>
       </c>
       <c r="E820" t="s">
-        <v>1938</v>
+        <v>1971</v>
       </c>
       <c r="F820" t="s">
-        <v>1971</v>
+        <v>1903</v>
       </c>
       <c r="G820" t="s">
-        <v>1903</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="821" spans="1:7">
@@ -26203,13 +26203,13 @@
         <v>1328</v>
       </c>
       <c r="E821" t="s">
-        <v>1938</v>
+        <v>1947</v>
       </c>
       <c r="F821" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="G821" t="s">
-        <v>1948</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="822" spans="1:7">
@@ -26226,13 +26226,13 @@
         <v>25</v>
       </c>
       <c r="E822" t="s">
-        <v>1938</v>
+        <v>1976</v>
       </c>
       <c r="F822" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="G822" t="s">
-        <v>1977</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="823" spans="1:7">
@@ -26252,10 +26252,10 @@
         <v>1938</v>
       </c>
       <c r="F823" t="s">
-        <v>1939</v>
+        <v>1948</v>
       </c>
       <c r="G823" t="s">
-        <v>1948</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="824" spans="1:7">
@@ -26272,13 +26272,13 @@
         <v>25</v>
       </c>
       <c r="E824" t="s">
-        <v>1938</v>
+        <v>1971</v>
       </c>
       <c r="F824" t="s">
-        <v>1971</v>
+        <v>1981</v>
       </c>
       <c r="G824" t="s">
-        <v>1981</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="825" spans="1:7">
@@ -26295,13 +26295,13 @@
         <v>25</v>
       </c>
       <c r="E825" t="s">
-        <v>1938</v>
+        <v>1984</v>
       </c>
       <c r="F825" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="G825" t="s">
-        <v>1985</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="826" spans="1:7">
@@ -26318,13 +26318,13 @@
         <v>1328</v>
       </c>
       <c r="E826" t="s">
-        <v>1938</v>
+        <v>1947</v>
       </c>
       <c r="F826" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="G826" t="s">
-        <v>1948</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="827" spans="1:7">
@@ -26341,13 +26341,13 @@
         <v>1328</v>
       </c>
       <c r="E827" t="s">
-        <v>1938</v>
+        <v>1947</v>
       </c>
       <c r="F827" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="G827" t="s">
-        <v>1948</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="828" spans="1:7">
@@ -26364,13 +26364,13 @@
         <v>32</v>
       </c>
       <c r="E828" t="s">
-        <v>1938</v>
+        <v>1992</v>
       </c>
       <c r="F828" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="G828" t="s">
-        <v>1993</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="829" spans="1:7">
@@ -26387,13 +26387,13 @@
         <v>22</v>
       </c>
       <c r="E829" t="s">
-        <v>1938</v>
+        <v>1947</v>
       </c>
       <c r="F829" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="G829" t="s">
-        <v>1948</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="830" spans="1:7">
@@ -26410,13 +26410,13 @@
         <v>25</v>
       </c>
       <c r="E830" t="s">
-        <v>1938</v>
+        <v>1998</v>
       </c>
       <c r="F830" t="s">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="G830" t="s">
-        <v>1999</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="831" spans="1:7">
@@ -26433,13 +26433,13 @@
         <v>1328</v>
       </c>
       <c r="E831" t="s">
-        <v>1938</v>
+        <v>1947</v>
       </c>
       <c r="F831" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="G831" t="s">
-        <v>1948</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="832" spans="1:7">
@@ -26456,13 +26456,13 @@
         <v>1328</v>
       </c>
       <c r="E832" t="s">
-        <v>1938</v>
+        <v>1947</v>
       </c>
       <c r="F832" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="G832" t="s">
-        <v>1948</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="833" spans="1:7">
@@ -26479,13 +26479,13 @@
         <v>32</v>
       </c>
       <c r="E833" t="s">
-        <v>1938</v>
+        <v>1947</v>
       </c>
       <c r="F833" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="G833" t="s">
-        <v>1948</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="834" spans="1:7">
@@ -26502,13 +26502,13 @@
         <v>25</v>
       </c>
       <c r="E834" t="s">
-        <v>1938</v>
+        <v>1992</v>
       </c>
       <c r="F834" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="G834" t="s">
-        <v>1993</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="835" spans="1:7">
@@ -26525,13 +26525,13 @@
         <v>1328</v>
       </c>
       <c r="E835" t="s">
-        <v>1938</v>
+        <v>1947</v>
       </c>
       <c r="F835" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="G835" t="s">
-        <v>1948</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="836" spans="1:7">
@@ -26574,10 +26574,10 @@
         <v>2010</v>
       </c>
       <c r="F837" t="s">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="G837" t="s">
-        <v>2015</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="838" spans="1:7">
@@ -26594,13 +26594,13 @@
         <v>25</v>
       </c>
       <c r="E838" t="s">
-        <v>2010</v>
+        <v>2018</v>
       </c>
       <c r="F838" t="s">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="G838" t="s">
-        <v>2019</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="839" spans="1:7">
@@ -26617,13 +26617,13 @@
         <v>25</v>
       </c>
       <c r="E839" t="s">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="F839" t="s">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="G839" t="s">
-        <v>2023</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="840" spans="1:7">
@@ -26643,10 +26643,10 @@
         <v>2010</v>
       </c>
       <c r="F840" t="s">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="G840" t="s">
-        <v>2015</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="841" spans="1:7">
@@ -26666,10 +26666,10 @@
         <v>2010</v>
       </c>
       <c r="F841" t="s">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="G841" t="s">
-        <v>2015</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="842" spans="1:7">
@@ -26689,10 +26689,10 @@
         <v>2010</v>
       </c>
       <c r="F842" t="s">
-        <v>2011</v>
+        <v>2030</v>
       </c>
       <c r="G842" t="s">
-        <v>2030</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="843" spans="1:7">
@@ -26712,10 +26712,10 @@
         <v>2010</v>
       </c>
       <c r="F843" t="s">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="G843" t="s">
-        <v>2015</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="844" spans="1:7">
@@ -26735,10 +26735,10 @@
         <v>2010</v>
       </c>
       <c r="F844" t="s">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="G844" t="s">
-        <v>2015</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="845" spans="1:7">
@@ -26758,10 +26758,10 @@
         <v>2010</v>
       </c>
       <c r="F845" t="s">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="G845" t="s">
-        <v>2015</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="846" spans="1:7">
@@ -26781,10 +26781,10 @@
         <v>2010</v>
       </c>
       <c r="F846" t="s">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="G846" t="s">
-        <v>2015</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="847" spans="1:7">
@@ -26804,10 +26804,10 @@
         <v>2010</v>
       </c>
       <c r="F847" t="s">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="G847" t="s">
-        <v>2015</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="848" spans="1:7">
@@ -26827,10 +26827,10 @@
         <v>2010</v>
       </c>
       <c r="F848" t="s">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="G848" t="s">
-        <v>2015</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="849" spans="1:7">
@@ -26850,10 +26850,10 @@
         <v>2010</v>
       </c>
       <c r="F849" t="s">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="G849" t="s">
-        <v>2015</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="850" spans="1:7">
@@ -26870,10 +26870,10 @@
         <v>25</v>
       </c>
       <c r="E850" t="s">
-        <v>2010</v>
+        <v>2047</v>
       </c>
       <c r="F850" t="s">
-        <v>2047</v>
+        <v>2011</v>
       </c>
       <c r="G850" t="s">
         <v>2012</v>
@@ -26896,10 +26896,10 @@
         <v>2010</v>
       </c>
       <c r="F851" t="s">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="G851" t="s">
-        <v>2015</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="852" spans="1:7">
@@ -26916,13 +26916,13 @@
         <v>25</v>
       </c>
       <c r="E852" t="s">
-        <v>2010</v>
+        <v>2052</v>
       </c>
       <c r="F852" t="s">
-        <v>2052</v>
+        <v>2030</v>
       </c>
       <c r="G852" t="s">
-        <v>2030</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="853" spans="1:7">
@@ -26939,13 +26939,13 @@
         <v>25</v>
       </c>
       <c r="E853" t="s">
-        <v>2010</v>
+        <v>2047</v>
       </c>
       <c r="F853" t="s">
-        <v>2047</v>
+        <v>2055</v>
       </c>
       <c r="G853" t="s">
-        <v>2055</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="854" spans="1:7">
@@ -26965,10 +26965,10 @@
         <v>2010</v>
       </c>
       <c r="F854" t="s">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="G854" t="s">
-        <v>2015</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="855" spans="1:7">
@@ -26985,13 +26985,13 @@
         <v>25</v>
       </c>
       <c r="E855" t="s">
-        <v>2010</v>
+        <v>2060</v>
       </c>
       <c r="F855" t="s">
-        <v>2060</v>
+        <v>2015</v>
       </c>
       <c r="G855" t="s">
-        <v>2015</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="856" spans="1:7">
@@ -27011,10 +27011,10 @@
         <v>2010</v>
       </c>
       <c r="F856" t="s">
-        <v>2011</v>
+        <v>2063</v>
       </c>
       <c r="G856" t="s">
-        <v>2063</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="857" spans="1:7">
@@ -27034,10 +27034,10 @@
         <v>2010</v>
       </c>
       <c r="F857" t="s">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="G857" t="s">
-        <v>2015</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="858" spans="1:7">
@@ -27054,13 +27054,13 @@
         <v>25</v>
       </c>
       <c r="E858" t="s">
-        <v>2010</v>
+        <v>2068</v>
       </c>
       <c r="F858" t="s">
-        <v>2068</v>
+        <v>2069</v>
       </c>
       <c r="G858" t="s">
-        <v>2069</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="859" spans="1:7">
@@ -27077,13 +27077,13 @@
         <v>25</v>
       </c>
       <c r="E859" t="s">
-        <v>2010</v>
+        <v>2072</v>
       </c>
       <c r="F859" t="s">
-        <v>2072</v>
+        <v>2073</v>
       </c>
       <c r="G859" t="s">
-        <v>2073</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="860" spans="1:7">
@@ -27103,10 +27103,10 @@
         <v>2010</v>
       </c>
       <c r="F860" t="s">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="G860" t="s">
-        <v>2015</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="861" spans="1:7">
@@ -27126,10 +27126,10 @@
         <v>2010</v>
       </c>
       <c r="F861" t="s">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="G861" t="s">
-        <v>2015</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="862" spans="1:7">
@@ -27149,10 +27149,10 @@
         <v>2010</v>
       </c>
       <c r="F862" t="s">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="G862" t="s">
-        <v>2015</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="863" spans="1:7">
@@ -27172,10 +27172,10 @@
         <v>2010</v>
       </c>
       <c r="F863" t="s">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="G863" t="s">
-        <v>2015</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="864" spans="1:7">
@@ -27195,10 +27195,10 @@
         <v>2010</v>
       </c>
       <c r="F864" t="s">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="G864" t="s">
-        <v>2015</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="865" spans="1:7">
@@ -27218,10 +27218,10 @@
         <v>2010</v>
       </c>
       <c r="F865" t="s">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="G865" t="s">
-        <v>2015</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="866" spans="1:7">
@@ -27241,10 +27241,10 @@
         <v>2010</v>
       </c>
       <c r="F866" t="s">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="G866" t="s">
-        <v>2015</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="867" spans="1:7">
@@ -27264,10 +27264,10 @@
         <v>2010</v>
       </c>
       <c r="F867" t="s">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="G867" t="s">
-        <v>2015</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="868" spans="1:7">
@@ -27287,10 +27287,10 @@
         <v>2010</v>
       </c>
       <c r="F868" t="s">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="G868" t="s">
-        <v>2015</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="869" spans="1:7">
@@ -27376,13 +27376,13 @@
         <v>25</v>
       </c>
       <c r="E872" t="s">
-        <v>2093</v>
+        <v>2103</v>
       </c>
       <c r="F872" t="s">
-        <v>2103</v>
+        <v>2104</v>
       </c>
       <c r="G872" t="s">
-        <v>2104</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="873" spans="1:7">
@@ -27448,10 +27448,10 @@
         <v>2093</v>
       </c>
       <c r="F875" t="s">
-        <v>2094</v>
+        <v>2104</v>
       </c>
       <c r="G875" t="s">
-        <v>2104</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="876" spans="1:7">
@@ -27468,13 +27468,13 @@
         <v>32</v>
       </c>
       <c r="E876" t="s">
-        <v>2093</v>
+        <v>2113</v>
       </c>
       <c r="F876" t="s">
-        <v>2113</v>
+        <v>2114</v>
       </c>
       <c r="G876" t="s">
-        <v>2114</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="877" spans="1:7">
@@ -27494,10 +27494,10 @@
         <v>2093</v>
       </c>
       <c r="F877" t="s">
-        <v>2094</v>
+        <v>2104</v>
       </c>
       <c r="G877" t="s">
-        <v>2104</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="878" spans="1:7">
@@ -27514,13 +27514,13 @@
         <v>25</v>
       </c>
       <c r="E878" t="s">
-        <v>2093</v>
+        <v>2113</v>
       </c>
       <c r="F878" t="s">
-        <v>2113</v>
+        <v>2114</v>
       </c>
       <c r="G878" t="s">
-        <v>2114</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="879" spans="1:7">
@@ -27675,13 +27675,13 @@
         <v>22</v>
       </c>
       <c r="E885" t="s">
-        <v>2093</v>
+        <v>2130</v>
       </c>
       <c r="F885" t="s">
-        <v>2130</v>
+        <v>2131</v>
       </c>
       <c r="G885" t="s">
-        <v>2131</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="886" spans="1:7">
@@ -27698,13 +27698,13 @@
         <v>2098</v>
       </c>
       <c r="E886" t="s">
-        <v>2093</v>
+        <v>2134</v>
       </c>
       <c r="F886" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="G886" t="s">
-        <v>2135</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="887" spans="1:7">
@@ -27724,10 +27724,10 @@
         <v>2093</v>
       </c>
       <c r="F887" t="s">
-        <v>2094</v>
+        <v>2135</v>
       </c>
       <c r="G887" t="s">
-        <v>2135</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="888" spans="1:7">
@@ -27744,13 +27744,13 @@
         <v>2098</v>
       </c>
       <c r="E888" t="s">
-        <v>2093</v>
+        <v>2134</v>
       </c>
       <c r="F888" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="G888" t="s">
-        <v>2135</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="889" spans="1:7">
@@ -27767,13 +27767,13 @@
         <v>32</v>
       </c>
       <c r="E889" t="s">
-        <v>2093</v>
+        <v>2134</v>
       </c>
       <c r="F889" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="G889" t="s">
-        <v>2135</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="890" spans="1:7">
@@ -27790,13 +27790,13 @@
         <v>1328</v>
       </c>
       <c r="E890" t="s">
-        <v>2093</v>
+        <v>2134</v>
       </c>
       <c r="F890" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="G890" t="s">
-        <v>2135</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="891" spans="1:7">
@@ -27813,13 +27813,13 @@
         <v>2098</v>
       </c>
       <c r="E891" t="s">
-        <v>2093</v>
+        <v>2134</v>
       </c>
       <c r="F891" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="G891" t="s">
-        <v>2135</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="892" spans="1:7">
@@ -27836,13 +27836,13 @@
         <v>2098</v>
       </c>
       <c r="E892" t="s">
-        <v>2093</v>
+        <v>2134</v>
       </c>
       <c r="F892" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="G892" t="s">
-        <v>2135</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="893" spans="1:7">
@@ -27862,10 +27862,10 @@
         <v>2093</v>
       </c>
       <c r="F893" t="s">
-        <v>2094</v>
+        <v>2135</v>
       </c>
       <c r="G893" t="s">
-        <v>2135</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="894" spans="1:7">
@@ -27908,10 +27908,10 @@
         <v>2093</v>
       </c>
       <c r="F895" t="s">
-        <v>2094</v>
+        <v>2104</v>
       </c>
       <c r="G895" t="s">
-        <v>2104</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="896" spans="1:7">
@@ -27931,10 +27931,10 @@
         <v>2093</v>
       </c>
       <c r="F896" t="s">
-        <v>2094</v>
+        <v>2104</v>
       </c>
       <c r="G896" t="s">
-        <v>2104</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="897" spans="1:7">
@@ -28161,10 +28161,10 @@
         <v>2172</v>
       </c>
       <c r="F906" t="s">
-        <v>2173</v>
+        <v>2177</v>
       </c>
       <c r="G906" t="s">
-        <v>2177</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="907" spans="1:7">
@@ -28184,10 +28184,10 @@
         <v>2172</v>
       </c>
       <c r="F907" t="s">
-        <v>2173</v>
+        <v>2177</v>
       </c>
       <c r="G907" t="s">
-        <v>2177</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="908" spans="1:7">
@@ -28207,10 +28207,10 @@
         <v>2172</v>
       </c>
       <c r="F908" t="s">
-        <v>2173</v>
+        <v>2177</v>
       </c>
       <c r="G908" t="s">
-        <v>2177</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="909" spans="1:7">
@@ -28230,10 +28230,10 @@
         <v>2172</v>
       </c>
       <c r="F909" t="s">
-        <v>2173</v>
+        <v>2177</v>
       </c>
       <c r="G909" t="s">
-        <v>2177</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="910" spans="1:7">
@@ -28253,10 +28253,10 @@
         <v>2172</v>
       </c>
       <c r="F910" t="s">
-        <v>2173</v>
+        <v>2177</v>
       </c>
       <c r="G910" t="s">
-        <v>2177</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="911" spans="1:7">
@@ -28276,10 +28276,10 @@
         <v>2172</v>
       </c>
       <c r="F911" t="s">
-        <v>2173</v>
+        <v>2177</v>
       </c>
       <c r="G911" t="s">
-        <v>2177</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="912" spans="1:7">
@@ -28299,10 +28299,10 @@
         <v>2172</v>
       </c>
       <c r="F912" t="s">
-        <v>2173</v>
+        <v>2177</v>
       </c>
       <c r="G912" t="s">
-        <v>2177</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="913" spans="1:7">
@@ -28322,10 +28322,10 @@
         <v>2172</v>
       </c>
       <c r="F913" t="s">
-        <v>2173</v>
+        <v>2177</v>
       </c>
       <c r="G913" t="s">
-        <v>2177</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="914" spans="1:7">
@@ -28342,13 +28342,13 @@
         <v>2098</v>
       </c>
       <c r="E914" t="s">
-        <v>2172</v>
+        <v>2103</v>
       </c>
       <c r="F914" t="s">
-        <v>2103</v>
+        <v>2194</v>
       </c>
       <c r="G914" t="s">
-        <v>2194</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="915" spans="1:7">
@@ -28365,13 +28365,13 @@
         <v>2098</v>
       </c>
       <c r="E915" t="s">
-        <v>2172</v>
+        <v>2103</v>
       </c>
       <c r="F915" t="s">
-        <v>2103</v>
+        <v>2194</v>
       </c>
       <c r="G915" t="s">
-        <v>2194</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="916" spans="1:7">
@@ -28388,13 +28388,13 @@
         <v>32</v>
       </c>
       <c r="E916" t="s">
-        <v>2172</v>
+        <v>2103</v>
       </c>
       <c r="F916" t="s">
-        <v>2103</v>
+        <v>2194</v>
       </c>
       <c r="G916" t="s">
-        <v>2194</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="917" spans="1:7">
@@ -28411,13 +28411,13 @@
         <v>1328</v>
       </c>
       <c r="E917" t="s">
-        <v>2172</v>
+        <v>2103</v>
       </c>
       <c r="F917" t="s">
-        <v>2103</v>
+        <v>2194</v>
       </c>
       <c r="G917" t="s">
-        <v>2194</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="918" spans="1:7">
@@ -28434,13 +28434,13 @@
         <v>2098</v>
       </c>
       <c r="E918" t="s">
-        <v>2172</v>
+        <v>2202</v>
       </c>
       <c r="F918" t="s">
-        <v>2202</v>
+        <v>2194</v>
       </c>
       <c r="G918" t="s">
-        <v>2194</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="919" spans="1:7">
@@ -28457,13 +28457,13 @@
         <v>2098</v>
       </c>
       <c r="E919" t="s">
-        <v>2172</v>
+        <v>2103</v>
       </c>
       <c r="F919" t="s">
-        <v>2103</v>
+        <v>2194</v>
       </c>
       <c r="G919" t="s">
-        <v>2194</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="920" spans="1:7">
@@ -28480,13 +28480,13 @@
         <v>2098</v>
       </c>
       <c r="E920" t="s">
-        <v>2172</v>
+        <v>2103</v>
       </c>
       <c r="F920" t="s">
-        <v>2103</v>
+        <v>2194</v>
       </c>
       <c r="G920" t="s">
-        <v>2194</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="921" spans="1:7">
@@ -28506,10 +28506,10 @@
         <v>2172</v>
       </c>
       <c r="F921" t="s">
-        <v>2173</v>
+        <v>2177</v>
       </c>
       <c r="G921" t="s">
-        <v>2177</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="922" spans="1:7">
@@ -28529,10 +28529,10 @@
         <v>2172</v>
       </c>
       <c r="F922" t="s">
-        <v>2173</v>
+        <v>2177</v>
       </c>
       <c r="G922" t="s">
-        <v>2177</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="923" spans="1:7">
@@ -28552,10 +28552,10 @@
         <v>2172</v>
       </c>
       <c r="F923" t="s">
-        <v>2173</v>
+        <v>2177</v>
       </c>
       <c r="G923" t="s">
-        <v>2177</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="924" spans="1:7">
@@ -28575,10 +28575,10 @@
         <v>2172</v>
       </c>
       <c r="F924" t="s">
-        <v>2173</v>
+        <v>2177</v>
       </c>
       <c r="G924" t="s">
-        <v>2177</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="925" spans="1:7">
@@ -28598,10 +28598,10 @@
         <v>2172</v>
       </c>
       <c r="F925" t="s">
-        <v>2173</v>
+        <v>2177</v>
       </c>
       <c r="G925" t="s">
-        <v>2177</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="926" spans="1:7">
@@ -28621,10 +28621,10 @@
         <v>2172</v>
       </c>
       <c r="F926" t="s">
-        <v>2173</v>
+        <v>2177</v>
       </c>
       <c r="G926" t="s">
-        <v>2177</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="927" spans="1:7">
@@ -28644,10 +28644,10 @@
         <v>2172</v>
       </c>
       <c r="F927" t="s">
-        <v>2173</v>
+        <v>2177</v>
       </c>
       <c r="G927" t="s">
-        <v>2177</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="928" spans="1:7">
@@ -28667,10 +28667,10 @@
         <v>2172</v>
       </c>
       <c r="F928" t="s">
-        <v>2173</v>
+        <v>2177</v>
       </c>
       <c r="G928" t="s">
-        <v>2177</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="929" spans="1:7">
@@ -28690,10 +28690,10 @@
         <v>2172</v>
       </c>
       <c r="F929" t="s">
-        <v>2173</v>
+        <v>2177</v>
       </c>
       <c r="G929" t="s">
-        <v>2177</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="930" spans="1:7">
@@ -28713,10 +28713,10 @@
         <v>2172</v>
       </c>
       <c r="F930" t="s">
-        <v>2173</v>
+        <v>2177</v>
       </c>
       <c r="G930" t="s">
-        <v>2177</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="931" spans="1:7">
@@ -28736,10 +28736,10 @@
         <v>2172</v>
       </c>
       <c r="F931" t="s">
-        <v>2173</v>
+        <v>2177</v>
       </c>
       <c r="G931" t="s">
-        <v>2177</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="932" spans="1:7">
@@ -28759,10 +28759,10 @@
         <v>2172</v>
       </c>
       <c r="F932" t="s">
-        <v>2173</v>
+        <v>2177</v>
       </c>
       <c r="G932" t="s">
-        <v>2177</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="933" spans="1:7">
@@ -28782,10 +28782,10 @@
         <v>2172</v>
       </c>
       <c r="F933" t="s">
-        <v>2173</v>
+        <v>2177</v>
       </c>
       <c r="G933" t="s">
-        <v>2177</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="934" spans="1:7">
@@ -28805,10 +28805,10 @@
         <v>2172</v>
       </c>
       <c r="F934" t="s">
-        <v>2173</v>
+        <v>2177</v>
       </c>
       <c r="G934" t="s">
-        <v>2177</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="935" spans="1:7">
@@ -28848,10 +28848,10 @@
         <v>2098</v>
       </c>
       <c r="E936" t="s">
-        <v>2236</v>
+        <v>2241</v>
       </c>
       <c r="F936" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="G936" t="s">
         <v>2238</v>
@@ -28871,10 +28871,10 @@
         <v>2098</v>
       </c>
       <c r="E937" t="s">
-        <v>2236</v>
+        <v>2241</v>
       </c>
       <c r="F937" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="G937" t="s">
         <v>2238</v>
@@ -28894,10 +28894,10 @@
         <v>2098</v>
       </c>
       <c r="E938" t="s">
-        <v>2236</v>
+        <v>2241</v>
       </c>
       <c r="F938" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="G938" t="s">
         <v>2238</v>
@@ -28917,10 +28917,10 @@
         <v>2098</v>
       </c>
       <c r="E939" t="s">
-        <v>2236</v>
+        <v>2241</v>
       </c>
       <c r="F939" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="G939" t="s">
         <v>2238</v>
@@ -28940,10 +28940,10 @@
         <v>22</v>
       </c>
       <c r="E940" t="s">
-        <v>2236</v>
+        <v>2241</v>
       </c>
       <c r="F940" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="G940" t="s">
         <v>2238</v>
@@ -28963,10 +28963,10 @@
         <v>32</v>
       </c>
       <c r="E941" t="s">
-        <v>2236</v>
+        <v>2241</v>
       </c>
       <c r="F941" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="G941" t="s">
         <v>2238</v>
@@ -28986,10 +28986,10 @@
         <v>22</v>
       </c>
       <c r="E942" t="s">
-        <v>2236</v>
+        <v>2241</v>
       </c>
       <c r="F942" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="G942" t="s">
         <v>2238</v>
@@ -29009,10 +29009,10 @@
         <v>2098</v>
       </c>
       <c r="E943" t="s">
-        <v>2236</v>
+        <v>2241</v>
       </c>
       <c r="F943" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="G943" t="s">
         <v>2238</v>
@@ -29032,10 +29032,10 @@
         <v>2098</v>
       </c>
       <c r="E944" t="s">
-        <v>2236</v>
+        <v>2241</v>
       </c>
       <c r="F944" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="G944" t="s">
         <v>2238</v>
@@ -29055,10 +29055,10 @@
         <v>1328</v>
       </c>
       <c r="E945" t="s">
-        <v>2236</v>
+        <v>2241</v>
       </c>
       <c r="F945" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="G945" t="s">
         <v>2238</v>
@@ -29078,10 +29078,10 @@
         <v>22</v>
       </c>
       <c r="E946" t="s">
-        <v>2236</v>
+        <v>2241</v>
       </c>
       <c r="F946" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="G946" t="s">
         <v>2238</v>
@@ -29101,10 +29101,10 @@
         <v>2098</v>
       </c>
       <c r="E947" t="s">
-        <v>2236</v>
+        <v>2241</v>
       </c>
       <c r="F947" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="G947" t="s">
         <v>2238</v>
@@ -29124,10 +29124,10 @@
         <v>2098</v>
       </c>
       <c r="E948" t="s">
-        <v>2236</v>
+        <v>2241</v>
       </c>
       <c r="F948" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="G948" t="s">
         <v>2238</v>
@@ -29147,10 +29147,10 @@
         <v>2098</v>
       </c>
       <c r="E949" t="s">
-        <v>2236</v>
+        <v>2241</v>
       </c>
       <c r="F949" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="G949" t="s">
         <v>2238</v>
@@ -29170,10 +29170,10 @@
         <v>2098</v>
       </c>
       <c r="E950" t="s">
-        <v>2236</v>
+        <v>2241</v>
       </c>
       <c r="F950" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="G950" t="s">
         <v>2238</v>
@@ -29193,10 +29193,10 @@
         <v>2098</v>
       </c>
       <c r="E951" t="s">
-        <v>2236</v>
+        <v>2241</v>
       </c>
       <c r="F951" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="G951" t="s">
         <v>2238</v>
@@ -29216,10 +29216,10 @@
         <v>1328</v>
       </c>
       <c r="E952" t="s">
-        <v>2236</v>
+        <v>2241</v>
       </c>
       <c r="F952" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="G952" t="s">
         <v>2238</v>
@@ -29239,10 +29239,10 @@
         <v>2098</v>
       </c>
       <c r="E953" t="s">
-        <v>2236</v>
+        <v>2241</v>
       </c>
       <c r="F953" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="G953" t="s">
         <v>2238</v>
@@ -29262,10 +29262,10 @@
         <v>2098</v>
       </c>
       <c r="E954" t="s">
-        <v>2236</v>
+        <v>2241</v>
       </c>
       <c r="F954" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="G954" t="s">
         <v>2238</v>
@@ -29285,10 +29285,10 @@
         <v>2098</v>
       </c>
       <c r="E955" t="s">
-        <v>2236</v>
+        <v>2241</v>
       </c>
       <c r="F955" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="G955" t="s">
         <v>2238</v>
@@ -29308,10 +29308,10 @@
         <v>22</v>
       </c>
       <c r="E956" t="s">
-        <v>2236</v>
+        <v>2241</v>
       </c>
       <c r="F956" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="G956" t="s">
         <v>2238</v>
@@ -29331,10 +29331,10 @@
         <v>2098</v>
       </c>
       <c r="E957" t="s">
-        <v>2236</v>
+        <v>2241</v>
       </c>
       <c r="F957" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="G957" t="s">
         <v>2238</v>
@@ -29354,10 +29354,10 @@
         <v>1328</v>
       </c>
       <c r="E958" t="s">
-        <v>2236</v>
+        <v>2241</v>
       </c>
       <c r="F958" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="G958" t="s">
         <v>2238</v>
@@ -29495,10 +29495,10 @@
         <v>2287</v>
       </c>
       <c r="F964" t="s">
-        <v>2288</v>
+        <v>2300</v>
       </c>
       <c r="G964" t="s">
-        <v>2300</v>
+        <v>2289</v>
       </c>
     </row>
     <row r="965" spans="1:7">
@@ -29518,10 +29518,10 @@
         <v>2287</v>
       </c>
       <c r="F965" t="s">
-        <v>2288</v>
+        <v>2300</v>
       </c>
       <c r="G965" t="s">
-        <v>2300</v>
+        <v>2289</v>
       </c>
     </row>
     <row r="966" spans="1:7">
@@ -29725,10 +29725,10 @@
         <v>2287</v>
       </c>
       <c r="F974" t="s">
-        <v>2288</v>
+        <v>2320</v>
       </c>
       <c r="G974" t="s">
-        <v>2320</v>
+        <v>2289</v>
       </c>
     </row>
     <row r="975" spans="1:7">
@@ -29771,10 +29771,10 @@
         <v>2287</v>
       </c>
       <c r="F976" t="s">
-        <v>2288</v>
+        <v>2324</v>
       </c>
       <c r="G976" t="s">
-        <v>2324</v>
+        <v>2289</v>
       </c>
     </row>
     <row r="977" spans="1:7">
@@ -29794,10 +29794,10 @@
         <v>2287</v>
       </c>
       <c r="F977" t="s">
-        <v>2288</v>
+        <v>2320</v>
       </c>
       <c r="G977" t="s">
-        <v>2320</v>
+        <v>2289</v>
       </c>
     </row>
   </sheetData>
